--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" tabRatio="500" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Свод" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="533">
   <si>
     <t>Бюджет проектного офиса «Таза Қазақстан» (ЦАКФ) на октябрь–декабрь 2026 и 2027 год — СВОД, ₸</t>
   </si>
@@ -1724,6 +1724,9 @@
   </si>
   <si>
     <t>Проект от 07.10.2026 (v13). Штат — по структуре и штатке 01.10.2026: 30 человек (Фонд с экспертной группой — 9, проектный офис — 21); с 21.10.2026 — 18, с 01.2027 — 1 (Ахантаева), с 02.2027 — 11 (в т.ч. экспертная группа и Абулхан); аутсорс — 7 позиций, расчёт — на листе «Аутсорс», в бюджете. Аренда — БЦ «Сыганак», ул. Сыганак, 70: аппарат ЦАКФ — 701–702 (7 этаж, 119,7 м²), проектный офис — 316 (3 этаж, 193 м²); к оплате 344,0 м² (+10% общих зон), 2 платных парковочных места; в 2026 — с 21.10. Проекты и мероприятия — по статьям проектного офиса, однотипные объединены, — на листе «Проекты (вне бюджета)», в ИТОГО не входят. В оснащении — ламинатор, переплётчик, сетевые фильтры, удлинители, кабель-канал, стойка для ТВ. Суммы пересчитываются от листов «Параметры», «Штат», «Командировки», «Оснащение и офис», «Канцелярия», «Смета фото-видео».</t>
+  </si>
+  <si>
+    <t>ВСЕГО за 2026-27 гг.:</t>
   </si>
 </sst>
 </file>
@@ -1937,7 +1940,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1951,7 +1954,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1959,7 +1961,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1967,14 +1968,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -1995,7 +1991,6 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2021,11 +2016,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2039,13 +2029,68 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2314,513 +2359,514 @@
   <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="72.7109375" customWidth="1"/>
-    <col min="2" max="4" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="72.7109375" style="4" customWidth="1"/>
+    <col min="2" max="4" width="19.7109375" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:4" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="210" x14ac:dyDescent="0.25">
+      <c r="A2" s="48" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="54">
+      <c r="C4" s="43">
         <v>2027</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" s="44" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <f>SUMIF(Штат!E5:E41,"штат",Штат!G5:G41)</f>
         <v>30</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <f>B5</f>
         <v>30</v>
       </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="48"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="4">
         <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!F5:F41,"новая")</f>
         <v>26</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="48"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <f>Штат!G43</f>
         <v>21</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <f>B7</f>
         <v>21</v>
       </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="48"/>
+    </row>
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="49">
         <f>SUMIFS(Штат!N5:N41,Штат!E5:E41,"штат")</f>
         <v>58691747.741935484</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="49">
         <f>SUMIFS(Штат!O5:O41,Штат!E5:E41,"штат")</f>
         <v>419273990</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="50">
         <f>C8/12</f>
         <v>34939499.166666664</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="49">
         <f>Аутсорс!K11</f>
         <v>15843354.83870968</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="49">
         <f>Аутсорс!L11</f>
         <v>80736000</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="50">
         <f>C9/12</f>
         <v>6728000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="49">
         <f>Штат!P42</f>
         <v>23115060</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="49">
         <f>Штат!Q42</f>
         <v>139757996.66666666</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="50">
         <f>C10/12</f>
         <v>11646499.722222222</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="49">
         <f>Штат!R42</f>
         <v>854387.09677419392</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="49">
         <f>Штат!S42</f>
         <v>6631000</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="50">
         <f>C11/12</f>
         <v>552583.33333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="49">
         <f>Командировки!I26</f>
         <v>7246775.9408602165</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="49">
         <f>Командировки!J26</f>
         <v>37657517.125</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="50">
         <f>C12/12</f>
         <v>3138126.4270833335</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I180,'Оснащение и офис'!A5:A180,"Оснащение")</f>
         <v>41176218</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J180,'Оснащение и офис'!A5:A180,"Оснащение")</f>
         <v>0</v>
       </c>
-      <c r="D13" s="19"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="50"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I180,'Оснащение и офис'!A5:A180,"Офис")</f>
         <v>22133074.967741936</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J180,'Оснащение и офис'!A5:A180,"Офис")</f>
         <v>69498297</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="50">
         <f>C14/12</f>
         <v>5791524.75</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="51">
         <f>'Оснащение и офис'!I38</f>
         <v>11670050.217741936</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="51">
         <f>'Оснащение и офис'!J38</f>
         <v>59469297</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="51">
         <f>C15/12</f>
         <v>4955774.75</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="51">
         <f>'Оснащение и офис'!I39</f>
         <v>4955774.75</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="51">
         <f>'Оснащение и офис'!J39</f>
         <v>0</v>
       </c>
-      <c r="D16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="51"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I180,'Оснащение и офис'!A5:A180,"Цифровые")</f>
         <v>820500</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J180,'Оснащение и офис'!A5:A180,"Цифровые")</f>
         <v>9282000</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="50">
         <f t="shared" ref="D17:D25" si="0">C17/12</f>
         <v>773500</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I180,'Оснащение и офис'!A5:A180,"Медиа")</f>
         <v>3325000</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J180,'Оснащение и офис'!A5:A180,"Медиа")</f>
         <v>25300000</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="50">
         <f t="shared" si="0"/>
         <v>2108333.3333333335</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="56" t="s">
+    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="45" t="s">
         <v>493</v>
       </c>
-      <c r="B19" s="57">
-        <f>'Проекты (вне бюджета)'!I16</f>
+      <c r="B19" s="52">
+        <f>'Проекты (вне бюджета)'!G16</f>
         <v>213000000</v>
       </c>
-      <c r="C19" s="57">
-        <f>'Проекты (вне бюджета)'!J16</f>
+      <c r="C19" s="52">
+        <f>'Проекты (вне бюджета)'!H16</f>
         <v>1530000000</v>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="53">
         <f t="shared" si="0"/>
         <v>127500000</v>
       </c>
-      <c r="E19" s="59" t="s">
+      <c r="E19" s="46" t="s">
         <v>422</v>
       </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I180,'Оснащение и офис'!A5:A180,"Прочие")</f>
         <v>5300000</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J180,'Оснащение и офис'!A5:A180,"Прочие")</f>
         <v>9400000</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="50">
         <f t="shared" si="0"/>
         <v>783333.33333333337</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="55">
         <f>B8+B9+B10+B11+B12+B13+B14+B17+B18+B20</f>
         <v>178506118.58602151</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="55">
         <f>C8+C9+C10+C11+C12+C13+C14+C17+C18+C20</f>
         <v>797536800.79166663</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="56">
         <f t="shared" si="0"/>
         <v>66461400.065972216</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="49">
         <f>B21*Резерв</f>
         <v>17850611.858602151</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="49">
         <f>C21*Резерв</f>
         <v>79753680.079166666</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="50">
         <f t="shared" si="0"/>
         <v>6646140.0065972218</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="57">
         <f>B21+B22</f>
         <v>196356730.44462365</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="57">
         <f>C21+C22</f>
         <v>877290480.87083328</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="58">
         <f t="shared" si="0"/>
         <v>73107540.072569445</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="49">
         <f>B23*НДС</f>
         <v>31417076.871139783</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="49">
         <f>C23*НДС</f>
         <v>140366476.93933332</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="50">
         <f t="shared" si="0"/>
         <v>11697206.41161111</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="49">
+      <c r="B25" s="59">
         <f>B23+B24</f>
         <v>227773807.31576344</v>
       </c>
-      <c r="C25" s="50">
+      <c r="C25" s="60">
         <f>C23+C24</f>
         <v>1017656957.8101666</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="56">
         <f t="shared" si="0"/>
         <v>84804746.484180555</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="24">
+      <c r="B26" s="61"/>
+      <c r="C26" s="62">
         <f>B25+C25</f>
         <v>1245430765.1259301</v>
       </c>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="D26" s="48"/>
+    </row>
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="40" t="s">
         <v>494</v>
       </c>
-      <c r="B27" s="60" t="s">
+      <c r="B27" s="63" t="s">
         <v>529</v>
       </c>
-      <c r="C27" s="51">
+      <c r="C27" s="64">
         <f>B19+C19</f>
         <v>1743000000</v>
       </c>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="D27" s="48"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
+    <row r="33" spans="1:2" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="49">
         <f>Аренда_мес</f>
         <v>4955774.75</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="55">
         <f>Аренда_с_НДС</f>
         <v>5748698.71</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="49">
         <f>Аренда_депозит</f>
         <v>4955774.75</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="37" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="49">
         <f>Аренда_мес-6296700</f>
         <v>-1340925.25</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="38" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="49">
         <f>Аренда_мес-5000000</f>
         <v>-44225.25</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="39" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="49">
         <f>(5000000-Коммун_мес-Парковка_мест*Парковка_цена)/Площадь_офиса</f>
         <v>13628.572986016221</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="49">
         <f>'Оснащение и офис'!I13</f>
         <v>360000</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="49">
         <f>'Оснащение и офис'!E14</f>
         <v>841000</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="49">
         <f>Канцелярия!F22</f>
         <v>240750</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="43" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="49">
         <f>SUM('Оснащение и офис'!I20:I23)</f>
         <v>182213</v>
       </c>
@@ -2850,13 +2896,13 @@
       <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2864,7 +2910,7 @@
       <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="11">
         <v>85000</v>
       </c>
       <c r="C4" t="s">
@@ -2875,7 +2921,7 @@
       <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <v>4325</v>
       </c>
       <c r="C5" t="s">
@@ -2886,7 +2932,7 @@
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>0.06</v>
       </c>
       <c r="C6" t="s">
@@ -2897,7 +2943,7 @@
       <c r="A7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C7" t="s">
@@ -2908,7 +2954,7 @@
       <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>0.05</v>
       </c>
       <c r="C8" t="s">
@@ -2919,7 +2965,7 @@
       <c r="A9" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>7</v>
       </c>
       <c r="C9" t="s">
@@ -2930,7 +2976,7 @@
       <c r="A10" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>0.03</v>
       </c>
       <c r="C10" t="s">
@@ -2941,7 +2987,7 @@
       <c r="A11" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <v>40</v>
       </c>
       <c r="C11" t="s">
@@ -2952,7 +2998,7 @@
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="11">
         <v>0.1</v>
       </c>
       <c r="C12" t="s">
@@ -2963,7 +3009,7 @@
       <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="11">
         <v>0.02</v>
       </c>
       <c r="C13" t="s">
@@ -2974,7 +3020,7 @@
       <c r="A14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="11">
         <v>0</v>
       </c>
       <c r="C14" t="s">
@@ -2985,7 +3031,7 @@
       <c r="A15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="11">
         <v>4</v>
       </c>
       <c r="C15" t="s">
@@ -2996,7 +3042,7 @@
       <c r="A16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="11">
         <v>200000</v>
       </c>
       <c r="C16" t="s">
@@ -3007,7 +3053,7 @@
       <c r="A17" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="11">
         <v>28000</v>
       </c>
       <c r="C17" t="s">
@@ -3018,7 +3064,7 @@
       <c r="A18" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="11">
         <v>530</v>
       </c>
       <c r="C18" t="s">
@@ -3029,7 +3075,7 @@
       <c r="A19" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="11">
         <v>2</v>
       </c>
       <c r="C19" t="s">
@@ -3040,7 +3086,7 @@
       <c r="A20" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="11">
         <v>90000</v>
       </c>
       <c r="C20" t="s">
@@ -3051,7 +3097,7 @@
       <c r="A21" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="11">
         <v>30000</v>
       </c>
       <c r="C21" t="s">
@@ -3062,7 +3108,7 @@
       <c r="A22" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="11">
         <v>15000</v>
       </c>
       <c r="C22" t="s">
@@ -3073,7 +3119,7 @@
       <c r="A23" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="11">
         <v>3</v>
       </c>
       <c r="C23" t="s">
@@ -3084,7 +3130,7 @@
       <c r="A24" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="11">
         <v>2</v>
       </c>
       <c r="C24" t="s">
@@ -3095,7 +3141,7 @@
       <c r="A25" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="11">
         <f>Авиа_РК+Отель_РК*Ночей_РК+Сут_РК*МРП*Дней_РК+Трансп_РК</f>
         <v>190950</v>
       </c>
@@ -3107,7 +3153,7 @@
       <c r="A26" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="11">
         <f>Трансп_РК+Сут_РК*МРП</f>
         <v>23650</v>
       </c>
@@ -3119,7 +3165,7 @@
       <c r="A27" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="11">
         <v>900</v>
       </c>
       <c r="C27" t="s">
@@ -3130,7 +3176,7 @@
       <c r="A28" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="11">
         <v>150</v>
       </c>
       <c r="C28" t="s">
@@ -3141,7 +3187,7 @@
       <c r="A29" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="11">
         <v>150</v>
       </c>
       <c r="C29" t="s">
@@ -3152,7 +3198,7 @@
       <c r="A30" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="11">
         <v>5</v>
       </c>
       <c r="C30" t="s">
@@ -3163,7 +3209,7 @@
       <c r="A31" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="11">
         <v>4</v>
       </c>
       <c r="C31" t="s">
@@ -3174,7 +3220,7 @@
       <c r="A32" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="11">
         <v>50</v>
       </c>
       <c r="C32" t="s">
@@ -3185,7 +3231,7 @@
       <c r="A33" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="11">
         <f>(Авиа_межд+Отель_межд*Ночей_межд+Сут_межд*Дней_межд+Страх_межд)*Курс</f>
         <v>1219000</v>
       </c>
@@ -3197,7 +3243,7 @@
       <c r="A34" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="11">
         <f>Площадь_офиса*Ставка_аренды_м2+Коммун_мес+Парковка_мест*Парковка_цена</f>
         <v>4955774.75</v>
       </c>
@@ -3209,7 +3255,7 @@
       <c r="A35" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="11">
         <v>1</v>
       </c>
       <c r="C35" t="s">
@@ -3220,7 +3266,7 @@
       <c r="A36" t="s">
         <v>82</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="11">
         <v>0.1</v>
       </c>
       <c r="C36" t="s">
@@ -3231,7 +3277,7 @@
       <c r="A37" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="11">
         <v>0.16</v>
       </c>
       <c r="C37" t="s">
@@ -3295,8 +3341,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
+    <row r="47" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
         <v>435</v>
       </c>
     </row>
@@ -3304,7 +3350,7 @@
       <c r="A48" t="s">
         <v>254</v>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="16">
         <f>ROUND((52.2+21.4+12.4+33.7+193)*1.1,2)</f>
         <v>343.97</v>
       </c>
@@ -3385,7 +3431,7 @@
       <c r="A55" t="s">
         <v>344</v>
       </c>
-      <c r="B55" s="26">
+      <c r="B55" s="19">
         <f>11/31+2</f>
         <v>2.3548387096774195</v>
       </c>
@@ -3394,7 +3440,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="10" t="s">
         <v>331</v>
       </c>
     </row>
@@ -3402,7 +3448,7 @@
       <c r="A57" t="s">
         <v>332</v>
       </c>
-      <c r="B57" s="25">
+      <c r="B57" s="18">
         <v>0.1</v>
       </c>
       <c r="C57" t="s">
@@ -3413,7 +3459,7 @@
       <c r="A58" t="s">
         <v>346</v>
       </c>
-      <c r="B58" s="26">
+      <c r="B58" s="19">
         <f>Аренда_мес_2026</f>
         <v>2.3548387096774195</v>
       </c>
@@ -3524,3023 +3570,3023 @@
       <c r="W4" s="4"/>
     </row>
     <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27">
-        <v>1</v>
-      </c>
-      <c r="B5" s="27" t="s">
+      <c r="A5" s="20">
+        <v>1</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>450</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="G5" s="27">
-        <v>1</v>
-      </c>
-      <c r="H5" s="29">
+      <c r="G5" s="20">
+        <v>1</v>
+      </c>
+      <c r="H5" s="22">
         <v>1600000</v>
       </c>
-      <c r="I5" s="27">
-        <v>1</v>
-      </c>
-      <c r="J5" s="29">
+      <c r="I5" s="20">
+        <v>1</v>
+      </c>
+      <c r="J5" s="22">
         <f t="shared" ref="J5:J34" si="0">IF(E5="штат",ROUND(Ставка_СН*H5*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H5+Ставка_СО*MIN(H5*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H5,Кап_ООСМС*МЗП),0),ROUND(H5*НДС,0))</f>
         <v>218230</v>
       </c>
-      <c r="K5" s="29">
+      <c r="K5" s="22">
         <f t="shared" ref="K5:K34" si="1">G5*(H5+J5)</f>
         <v>1818230</v>
       </c>
-      <c r="L5" s="30">
+      <c r="L5" s="23">
         <f t="shared" ref="L5:L41" si="2">IF(AND(F5="новая",I5=1),Мес_2026_новые,MAX(0,4-I5))</f>
         <v>3</v>
       </c>
-      <c r="M5" s="27">
+      <c r="M5" s="20">
         <f t="shared" ref="M5:M34" si="3">MAX(0,MIN(12,16-MAX(I5,4)))</f>
         <v>12</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="22">
         <f t="shared" ref="N5:N34" si="4">K5*L5</f>
         <v>5454690</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="22">
         <f t="shared" ref="O5:O34" si="5">K5*M5</f>
         <v>21818760</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="22">
         <f t="shared" ref="P5:P41" si="6">IF(AND(E5="штат",L5&gt;0),(H5+J5)*G5,0)</f>
         <v>1818230</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="22">
         <f t="shared" ref="Q5:Q34" si="7">IF(E5="штат",Премия_KPI*H5*(1+J5/H5)*G5*M5/12,0)</f>
         <v>7272920.0000000009</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="22">
         <f t="shared" ref="R5:R34" si="8">IF(E5="штат",(ДМС+ОСНС)*G5*L5/12,0)</f>
         <v>57000</v>
       </c>
-      <c r="S5" s="29">
+      <c r="S5" s="22">
         <f t="shared" ref="S5:S34" si="9">IF(E5="штат",(ДМС+ОСНС)*G5*M5/12,0)</f>
         <v>228000</v>
       </c>
-      <c r="T5" s="29">
+      <c r="T5" s="22">
         <f t="shared" ref="T5:T34" si="10">N5+P5+R5</f>
         <v>7329920</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="22">
         <f t="shared" ref="U5:U34" si="11">O5+Q5+S5</f>
         <v>29319680</v>
       </c>
-      <c r="V5" s="27" t="s">
+      <c r="V5" s="20" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
+      <c r="A6" s="20">
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="20" t="s">
         <v>450</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="27">
-        <v>1</v>
-      </c>
-      <c r="H6" s="29">
+      <c r="G6" s="20">
+        <v>1</v>
+      </c>
+      <c r="H6" s="22">
         <v>1400000</v>
       </c>
-      <c r="I6" s="27">
-        <v>1</v>
-      </c>
-      <c r="J6" s="29">
+      <c r="I6" s="20">
+        <v>1</v>
+      </c>
+      <c r="J6" s="22">
         <f t="shared" si="0"/>
         <v>194670</v>
       </c>
-      <c r="K6" s="29">
+      <c r="K6" s="22">
         <f t="shared" si="1"/>
         <v>1594670</v>
       </c>
-      <c r="L6" s="30">
+      <c r="L6" s="23">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="M6" s="27">
+      <c r="M6" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="22">
         <f>K6*L6</f>
         <v>4784010</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="22">
         <f>K6*M6</f>
         <v>19136040</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="22">
         <f t="shared" si="6"/>
         <v>1594670</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="22">
         <f t="shared" si="7"/>
         <v>6378680.0000000009</v>
       </c>
-      <c r="R6" s="29">
+      <c r="R6" s="22">
         <f t="shared" si="8"/>
         <v>57000</v>
       </c>
-      <c r="S6" s="29">
+      <c r="S6" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T6" s="29">
+      <c r="T6" s="22">
         <f t="shared" si="10"/>
         <v>6435680</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="22">
         <f t="shared" si="11"/>
         <v>25742720</v>
       </c>
-      <c r="V6" s="27" t="s">
+      <c r="V6" s="20" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
+      <c r="A7" s="20">
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="20" t="s">
         <v>450</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="G7" s="27">
-        <v>1</v>
-      </c>
-      <c r="H7" s="29">
+      <c r="G7" s="20">
+        <v>1</v>
+      </c>
+      <c r="H7" s="22">
         <v>1400000</v>
       </c>
-      <c r="I7" s="27">
-        <v>1</v>
-      </c>
-      <c r="J7" s="29">
+      <c r="I7" s="20">
+        <v>1</v>
+      </c>
+      <c r="J7" s="22">
         <f t="shared" si="0"/>
         <v>194670</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="22">
         <f t="shared" si="1"/>
         <v>1594670</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="23">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="M7" s="27">
+      <c r="M7" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N7" s="29">
+      <c r="N7" s="22">
         <f>K7*L7</f>
         <v>4784010</v>
       </c>
-      <c r="O7" s="29">
+      <c r="O7" s="22">
         <f>K7*M7</f>
         <v>19136040</v>
       </c>
-      <c r="P7" s="29">
+      <c r="P7" s="22">
         <f t="shared" si="6"/>
         <v>1594670</v>
       </c>
-      <c r="Q7" s="29">
+      <c r="Q7" s="22">
         <f t="shared" si="7"/>
         <v>6378680.0000000009</v>
       </c>
-      <c r="R7" s="29">
+      <c r="R7" s="22">
         <f t="shared" si="8"/>
         <v>57000</v>
       </c>
-      <c r="S7" s="29">
+      <c r="S7" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T7" s="29">
+      <c r="T7" s="22">
         <f t="shared" si="10"/>
         <v>6435680</v>
       </c>
-      <c r="U7" s="29">
+      <c r="U7" s="22">
         <f t="shared" si="11"/>
         <v>25742720</v>
       </c>
-      <c r="V7" s="27" t="s">
+      <c r="V7" s="20" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
+      <c r="A8" s="20">
         <v>4</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="21" t="s">
         <v>454</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G8" s="27">
-        <v>1</v>
-      </c>
-      <c r="H8" s="29">
+      <c r="G8" s="20">
+        <v>1</v>
+      </c>
+      <c r="H8" s="22">
         <v>1400000</v>
       </c>
-      <c r="I8" s="27">
-        <v>1</v>
-      </c>
-      <c r="J8" s="29">
+      <c r="I8" s="20">
+        <v>1</v>
+      </c>
+      <c r="J8" s="22">
         <f t="shared" si="0"/>
         <v>194670</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="22">
         <f t="shared" si="1"/>
         <v>1594670</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N8" s="29">
+      <c r="N8" s="22">
         <f t="shared" si="4"/>
         <v>3755190.6451612907</v>
       </c>
-      <c r="O8" s="29">
+      <c r="O8" s="22">
         <f t="shared" si="5"/>
         <v>19136040</v>
       </c>
-      <c r="P8" s="29">
+      <c r="P8" s="22">
         <f t="shared" si="6"/>
         <v>1594670</v>
       </c>
-      <c r="Q8" s="29">
+      <c r="Q8" s="22">
         <f t="shared" si="7"/>
         <v>6378680.0000000009</v>
       </c>
-      <c r="R8" s="29">
+      <c r="R8" s="22">
         <f t="shared" si="8"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S8" s="29">
+      <c r="S8" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T8" s="29">
+      <c r="T8" s="22">
         <f t="shared" si="10"/>
         <v>5394602.5806451617</v>
       </c>
-      <c r="U8" s="29">
+      <c r="U8" s="22">
         <f t="shared" si="11"/>
         <v>25742720</v>
       </c>
-      <c r="V8" s="27" t="s">
+      <c r="V8" s="20" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31">
+      <c r="A9" s="24">
         <v>5</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="25" t="s">
         <v>456</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G9" s="31">
-        <v>1</v>
-      </c>
-      <c r="H9" s="33">
+      <c r="G9" s="24">
+        <v>1</v>
+      </c>
+      <c r="H9" s="26">
         <v>1300000</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="24">
         <v>4</v>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="26">
         <f t="shared" si="0"/>
         <v>182890</v>
       </c>
-      <c r="K9" s="33">
+      <c r="K9" s="26">
         <f t="shared" si="1"/>
         <v>1482890</v>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M9" s="31">
+      <c r="M9" s="24">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O9" s="33">
+      <c r="O9" s="26">
         <f t="shared" si="5"/>
         <v>17794680</v>
       </c>
-      <c r="P9" s="33">
+      <c r="P9" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="33">
+      <c r="Q9" s="26">
         <f t="shared" si="7"/>
         <v>5931560</v>
       </c>
-      <c r="R9" s="33">
+      <c r="R9" s="26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S9" s="33">
+      <c r="S9" s="26">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T9" s="33">
+      <c r="T9" s="26">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U9" s="33">
+      <c r="U9" s="26">
         <f t="shared" si="11"/>
         <v>23954240</v>
       </c>
-      <c r="V9" s="31" t="s">
+      <c r="V9" s="24" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
+      <c r="A10" s="20">
         <v>6</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G10" s="27">
-        <v>1</v>
-      </c>
-      <c r="H10" s="29">
+      <c r="G10" s="20">
+        <v>1</v>
+      </c>
+      <c r="H10" s="22">
         <v>1000000</v>
       </c>
-      <c r="I10" s="27">
-        <v>1</v>
-      </c>
-      <c r="J10" s="29">
+      <c r="I10" s="20">
+        <v>1</v>
+      </c>
+      <c r="J10" s="22">
         <f t="shared" si="0"/>
         <v>147550</v>
       </c>
-      <c r="K10" s="29">
+      <c r="K10" s="22">
         <f t="shared" si="1"/>
         <v>1147550</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M10" s="27">
+      <c r="M10" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N10" s="29">
+      <c r="N10" s="22">
         <f t="shared" si="4"/>
         <v>2702295.1612903229</v>
       </c>
-      <c r="O10" s="29">
+      <c r="O10" s="22">
         <f t="shared" si="5"/>
         <v>13770600</v>
       </c>
-      <c r="P10" s="29">
+      <c r="P10" s="22">
         <f t="shared" si="6"/>
         <v>1147550</v>
       </c>
-      <c r="Q10" s="29">
+      <c r="Q10" s="22">
         <f t="shared" si="7"/>
         <v>4590200</v>
       </c>
-      <c r="R10" s="29">
+      <c r="R10" s="22">
         <f t="shared" si="8"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S10" s="29">
+      <c r="S10" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T10" s="29">
+      <c r="T10" s="22">
         <f t="shared" si="10"/>
         <v>3894587.0967741939</v>
       </c>
-      <c r="U10" s="29">
+      <c r="U10" s="22">
         <f t="shared" si="11"/>
         <v>18588800</v>
       </c>
-      <c r="V10" s="27" t="s">
+      <c r="V10" s="20" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31">
+      <c r="A11" s="24">
         <v>7</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="25" t="s">
         <v>380</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="25" t="s">
         <v>378</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G11" s="31">
-        <v>1</v>
-      </c>
-      <c r="H11" s="33">
+      <c r="G11" s="24">
+        <v>1</v>
+      </c>
+      <c r="H11" s="26">
         <v>1000000</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="24">
         <v>5</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="26">
         <f t="shared" ref="J11" si="12">IF(E11="штат",ROUND(Ставка_СН*H11*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H11+Ставка_СО*MIN(H11*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H11,Кап_ООСМС*МЗП),0),ROUND(H11*НДС,0))</f>
         <v>147550</v>
       </c>
-      <c r="K11" s="33">
+      <c r="K11" s="26">
         <f t="shared" ref="K11" si="13">G11*(H11+J11)</f>
         <v>1147550</v>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="27">
         <f t="shared" ref="L11" si="14">IF(AND(F11="новая",I11=1),Мес_2026_новые,MAX(0,4-I11))</f>
         <v>0</v>
       </c>
-      <c r="M11" s="31">
+      <c r="M11" s="24">
         <f t="shared" ref="M11" si="15">MAX(0,MIN(12,16-MAX(I11,4)))</f>
         <v>11</v>
       </c>
-      <c r="N11" s="33">
+      <c r="N11" s="26">
         <f t="shared" ref="N11" si="16">K11*L11</f>
         <v>0</v>
       </c>
-      <c r="O11" s="33">
+      <c r="O11" s="26">
         <f t="shared" ref="O11" si="17">K11*M11</f>
         <v>12623050</v>
       </c>
-      <c r="P11" s="33">
+      <c r="P11" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="33">
+      <c r="Q11" s="26">
         <f t="shared" ref="Q11" si="18">IF(E11="штат",Премия_KPI*H11*(1+J11/H11)*G11*M11/12,0)</f>
         <v>4207683.333333333</v>
       </c>
-      <c r="R11" s="33">
+      <c r="R11" s="26">
         <f t="shared" ref="R11" si="19">IF(E11="штат",(ДМС+ОСНС)*G11*L11/12,0)</f>
         <v>0</v>
       </c>
-      <c r="S11" s="33">
+      <c r="S11" s="26">
         <f t="shared" ref="S11" si="20">IF(E11="штат",(ДМС+ОСНС)*G11*M11/12,0)</f>
         <v>209000</v>
       </c>
-      <c r="T11" s="33">
+      <c r="T11" s="26">
         <f t="shared" ref="T11" si="21">N11+P11+R11</f>
         <v>0</v>
       </c>
-      <c r="U11" s="33">
+      <c r="U11" s="26">
         <f t="shared" ref="U11" si="22">O11+Q11+S11</f>
         <v>17039733.333333332</v>
       </c>
-      <c r="V11" s="31" t="s">
+      <c r="V11" s="24" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31">
+      <c r="A12" s="24">
         <v>8</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="25" t="s">
         <v>381</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="25" t="s">
         <v>378</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G12" s="31">
-        <v>1</v>
-      </c>
-      <c r="H12" s="33">
+      <c r="G12" s="24">
+        <v>1</v>
+      </c>
+      <c r="H12" s="26">
         <v>700000</v>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="24">
         <v>5</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="26">
         <f t="shared" si="0"/>
         <v>112210</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="26">
         <f t="shared" si="1"/>
         <v>812210</v>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M12" s="31">
+      <c r="M12" s="24">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O12" s="33">
+      <c r="O12" s="26">
         <f t="shared" si="5"/>
         <v>8934310</v>
       </c>
-      <c r="P12" s="33">
+      <c r="P12" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="33">
+      <c r="Q12" s="26">
         <f t="shared" si="7"/>
         <v>2978103.3333333326</v>
       </c>
-      <c r="R12" s="33">
+      <c r="R12" s="26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S12" s="33">
+      <c r="S12" s="26">
         <f t="shared" si="9"/>
         <v>209000</v>
       </c>
-      <c r="T12" s="33">
+      <c r="T12" s="26">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U12" s="33">
+      <c r="U12" s="26">
         <f t="shared" si="11"/>
         <v>12121413.333333332</v>
       </c>
-      <c r="V12" s="31" t="s">
+      <c r="V12" s="24" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="31">
+      <c r="A13" s="24">
         <v>9</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="25" t="s">
         <v>378</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G13" s="31">
-        <v>1</v>
-      </c>
-      <c r="H13" s="33">
+      <c r="G13" s="24">
+        <v>1</v>
+      </c>
+      <c r="H13" s="26">
         <v>700000</v>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="24">
         <v>5</v>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="26">
         <f t="shared" si="0"/>
         <v>112210</v>
       </c>
-      <c r="K13" s="33">
+      <c r="K13" s="26">
         <f t="shared" si="1"/>
         <v>812210</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M13" s="31">
+      <c r="M13" s="24">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="N13" s="33">
+      <c r="N13" s="26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O13" s="33">
+      <c r="O13" s="26">
         <f t="shared" si="5"/>
         <v>8934310</v>
       </c>
-      <c r="P13" s="33">
+      <c r="P13" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="33">
+      <c r="Q13" s="26">
         <f t="shared" si="7"/>
         <v>2978103.3333333326</v>
       </c>
-      <c r="R13" s="33">
+      <c r="R13" s="26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S13" s="33">
+      <c r="S13" s="26">
         <f t="shared" si="9"/>
         <v>209000</v>
       </c>
-      <c r="T13" s="33">
+      <c r="T13" s="26">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U13" s="33">
+      <c r="U13" s="26">
         <f t="shared" si="11"/>
         <v>12121413.333333332</v>
       </c>
-      <c r="V13" s="31" t="s">
+      <c r="V13" s="24" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="31">
+      <c r="A14" s="24">
         <v>10</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="24" t="s">
         <v>460</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="25" t="s">
         <v>461</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="25" t="s">
         <v>462</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G14" s="31">
-        <v>1</v>
-      </c>
-      <c r="H14" s="33">
+      <c r="G14" s="24">
+        <v>1</v>
+      </c>
+      <c r="H14" s="26">
         <v>1300000</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="24">
         <v>5</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="26">
         <f t="shared" si="0"/>
         <v>182890</v>
       </c>
-      <c r="K14" s="33">
+      <c r="K14" s="26">
         <f t="shared" si="1"/>
         <v>1482890</v>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="24">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="N14" s="33">
+      <c r="N14" s="26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O14" s="33">
+      <c r="O14" s="26">
         <f t="shared" si="5"/>
         <v>16311790</v>
       </c>
-      <c r="P14" s="33">
+      <c r="P14" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="33">
+      <c r="Q14" s="26">
         <f t="shared" si="7"/>
         <v>5437263.333333333</v>
       </c>
-      <c r="R14" s="33">
+      <c r="R14" s="26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S14" s="33">
+      <c r="S14" s="26">
         <f t="shared" si="9"/>
         <v>209000</v>
       </c>
-      <c r="T14" s="33">
+      <c r="T14" s="26">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U14" s="33">
+      <c r="U14" s="26">
         <f t="shared" si="11"/>
         <v>21958053.333333332</v>
       </c>
-      <c r="V14" s="31" t="s">
+      <c r="V14" s="24" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31">
+      <c r="A15" s="24">
         <v>11</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="24" t="s">
         <v>460</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="25" t="s">
         <v>414</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="25" t="s">
         <v>464</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G15" s="31">
-        <v>1</v>
-      </c>
-      <c r="H15" s="33">
+      <c r="G15" s="24">
+        <v>1</v>
+      </c>
+      <c r="H15" s="26">
         <v>800000</v>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="24">
         <v>5</v>
       </c>
-      <c r="J15" s="33">
+      <c r="J15" s="26">
         <f t="shared" si="0"/>
         <v>123990</v>
       </c>
-      <c r="K15" s="33">
+      <c r="K15" s="26">
         <f t="shared" si="1"/>
         <v>923990</v>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M15" s="31">
+      <c r="M15" s="24">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="N15" s="33">
+      <c r="N15" s="26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O15" s="33">
+      <c r="O15" s="26">
         <f t="shared" si="5"/>
         <v>10163890</v>
       </c>
-      <c r="P15" s="33">
+      <c r="P15" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="33">
+      <c r="Q15" s="26">
         <f t="shared" si="7"/>
         <v>3387963.3333333335</v>
       </c>
-      <c r="R15" s="33">
+      <c r="R15" s="26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S15" s="33">
+      <c r="S15" s="26">
         <f t="shared" si="9"/>
         <v>209000</v>
       </c>
-      <c r="T15" s="33">
+      <c r="T15" s="26">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U15" s="33">
+      <c r="U15" s="26">
         <f t="shared" si="11"/>
         <v>13760853.333333334</v>
       </c>
-      <c r="V15" s="31" t="s">
+      <c r="V15" s="24" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="31">
+      <c r="A16" s="24">
         <v>12</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="24" t="s">
         <v>460</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="25" t="s">
         <v>413</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="25" t="s">
         <v>464</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G16" s="31">
-        <v>1</v>
-      </c>
-      <c r="H16" s="33">
+      <c r="G16" s="24">
+        <v>1</v>
+      </c>
+      <c r="H16" s="26">
         <v>800000</v>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="24">
         <v>5</v>
       </c>
-      <c r="J16" s="33">
+      <c r="J16" s="26">
         <f t="shared" si="0"/>
         <v>123990</v>
       </c>
-      <c r="K16" s="33">
+      <c r="K16" s="26">
         <f t="shared" si="1"/>
         <v>923990</v>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M16" s="31">
+      <c r="M16" s="24">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="N16" s="33">
+      <c r="N16" s="26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O16" s="33">
+      <c r="O16" s="26">
         <f t="shared" si="5"/>
         <v>10163890</v>
       </c>
-      <c r="P16" s="33">
+      <c r="P16" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="33">
+      <c r="Q16" s="26">
         <f t="shared" si="7"/>
         <v>3387963.3333333335</v>
       </c>
-      <c r="R16" s="33">
+      <c r="R16" s="26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S16" s="33">
+      <c r="S16" s="26">
         <f t="shared" si="9"/>
         <v>209000</v>
       </c>
-      <c r="T16" s="33">
+      <c r="T16" s="26">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U16" s="33">
+      <c r="U16" s="26">
         <f t="shared" si="11"/>
         <v>13760853.333333334</v>
       </c>
-      <c r="V16" s="31" t="s">
+      <c r="V16" s="24" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="31">
+      <c r="A17" s="24">
         <v>13</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="25" t="s">
         <v>384</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="25" t="s">
         <v>456</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G17" s="31">
-        <v>1</v>
-      </c>
-      <c r="H17" s="33">
+      <c r="G17" s="24">
+        <v>1</v>
+      </c>
+      <c r="H17" s="26">
         <v>1300000</v>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="24">
         <v>5</v>
       </c>
-      <c r="J17" s="33">
+      <c r="J17" s="26">
         <f t="shared" ref="J17:J18" si="23">IF(E17="штат",ROUND(Ставка_СН*H17*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H17+Ставка_СО*MIN(H17*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H17,Кап_ООСМС*МЗП),0),ROUND(H17*НДС,0))</f>
         <v>182890</v>
       </c>
-      <c r="K17" s="33">
+      <c r="K17" s="26">
         <f t="shared" ref="K17:K18" si="24">G17*(H17+J17)</f>
         <v>1482890</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="27">
         <f t="shared" ref="L17:L18" si="25">IF(AND(F17="новая",I17=1),Мес_2026_новые,MAX(0,4-I17))</f>
         <v>0</v>
       </c>
-      <c r="M17" s="31">
+      <c r="M17" s="24">
         <f t="shared" ref="M17:M18" si="26">MAX(0,MIN(12,16-MAX(I17,4)))</f>
         <v>11</v>
       </c>
-      <c r="N17" s="33">
+      <c r="N17" s="26">
         <f t="shared" ref="N17:N18" si="27">K17*L17</f>
         <v>0</v>
       </c>
-      <c r="O17" s="33">
+      <c r="O17" s="26">
         <f t="shared" ref="O17:O18" si="28">K17*M17</f>
         <v>16311790</v>
       </c>
-      <c r="P17" s="33">
+      <c r="P17" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="33">
+      <c r="Q17" s="26">
         <f t="shared" ref="Q17:Q18" si="29">IF(E17="штат",Премия_KPI*H17*(1+J17/H17)*G17*M17/12,0)</f>
         <v>5437263.333333333</v>
       </c>
-      <c r="R17" s="33">
+      <c r="R17" s="26">
         <f t="shared" ref="R17:R18" si="30">IF(E17="штат",(ДМС+ОСНС)*G17*L17/12,0)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="33">
+      <c r="S17" s="26">
         <f t="shared" ref="S17:S18" si="31">IF(E17="штат",(ДМС+ОСНС)*G17*M17/12,0)</f>
         <v>209000</v>
       </c>
-      <c r="T17" s="33">
+      <c r="T17" s="26">
         <f t="shared" ref="T17:T18" si="32">N17+P17+R17</f>
         <v>0</v>
       </c>
-      <c r="U17" s="33">
+      <c r="U17" s="26">
         <f t="shared" ref="U17:U18" si="33">O17+Q17+S17</f>
         <v>21958053.333333332</v>
       </c>
-      <c r="V17" s="31" t="s">
+      <c r="V17" s="24" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="27">
+      <c r="A18" s="20">
         <v>14</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="21" t="s">
         <v>468</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G18" s="27">
-        <v>1</v>
-      </c>
-      <c r="H18" s="29">
+      <c r="G18" s="20">
+        <v>1</v>
+      </c>
+      <c r="H18" s="22">
         <v>1100000</v>
       </c>
-      <c r="I18" s="27">
-        <v>1</v>
-      </c>
-      <c r="J18" s="29">
+      <c r="I18" s="20">
+        <v>1</v>
+      </c>
+      <c r="J18" s="22">
         <f t="shared" si="23"/>
         <v>159330</v>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="22">
         <f t="shared" si="24"/>
         <v>1259330</v>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="23">
         <f t="shared" si="25"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M18" s="27">
+      <c r="M18" s="20">
         <f t="shared" si="26"/>
         <v>12</v>
       </c>
-      <c r="N18" s="29">
+      <c r="N18" s="22">
         <f t="shared" si="27"/>
         <v>2965519.0322580645</v>
       </c>
-      <c r="O18" s="29">
+      <c r="O18" s="22">
         <f t="shared" si="28"/>
         <v>15111960</v>
       </c>
-      <c r="P18" s="29">
+      <c r="P18" s="22">
         <f t="shared" si="6"/>
         <v>1259330</v>
       </c>
-      <c r="Q18" s="29">
+      <c r="Q18" s="22">
         <f t="shared" si="29"/>
         <v>5037320</v>
       </c>
-      <c r="R18" s="29">
+      <c r="R18" s="22">
         <f t="shared" si="30"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S18" s="29">
+      <c r="S18" s="22">
         <f t="shared" si="31"/>
         <v>228000</v>
       </c>
-      <c r="T18" s="29">
+      <c r="T18" s="22">
         <f t="shared" si="32"/>
         <v>4269590.9677419355</v>
       </c>
-      <c r="U18" s="29">
+      <c r="U18" s="22">
         <f t="shared" si="33"/>
         <v>20377280</v>
       </c>
-      <c r="V18" s="27" t="s">
+      <c r="V18" s="20" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27">
+      <c r="A19" s="20">
         <v>15</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="21" t="s">
         <v>385</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G19" s="27">
-        <v>1</v>
-      </c>
-      <c r="H19" s="29">
+      <c r="G19" s="20">
+        <v>1</v>
+      </c>
+      <c r="H19" s="22">
         <v>1000000</v>
       </c>
-      <c r="I19" s="27">
-        <v>1</v>
-      </c>
-      <c r="J19" s="29">
+      <c r="I19" s="20">
+        <v>1</v>
+      </c>
+      <c r="J19" s="22">
         <f t="shared" si="0"/>
         <v>147550</v>
       </c>
-      <c r="K19" s="29">
+      <c r="K19" s="22">
         <f t="shared" si="1"/>
         <v>1147550</v>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M19" s="27">
+      <c r="M19" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N19" s="29">
+      <c r="N19" s="22">
         <f t="shared" si="4"/>
         <v>2702295.1612903229</v>
       </c>
-      <c r="O19" s="29">
+      <c r="O19" s="22">
         <f t="shared" si="5"/>
         <v>13770600</v>
       </c>
-      <c r="P19" s="29">
+      <c r="P19" s="22">
         <f t="shared" si="6"/>
         <v>1147550</v>
       </c>
-      <c r="Q19" s="29">
+      <c r="Q19" s="22">
         <f t="shared" si="7"/>
         <v>4590200</v>
       </c>
-      <c r="R19" s="29">
+      <c r="R19" s="22">
         <f t="shared" si="8"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S19" s="29">
+      <c r="S19" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T19" s="29">
+      <c r="T19" s="22">
         <f t="shared" si="10"/>
         <v>3894587.0967741939</v>
       </c>
-      <c r="U19" s="29">
+      <c r="U19" s="22">
         <f t="shared" si="11"/>
         <v>18588800</v>
       </c>
-      <c r="V19" s="27" t="s">
+      <c r="V19" s="20" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31">
+      <c r="A20" s="24">
         <v>16</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="25" t="s">
         <v>385</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="25" t="s">
         <v>386</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G20" s="31">
-        <v>1</v>
-      </c>
-      <c r="H20" s="33">
+      <c r="G20" s="24">
+        <v>1</v>
+      </c>
+      <c r="H20" s="26">
         <v>1000000</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="24">
         <v>5</v>
       </c>
-      <c r="J20" s="33">
+      <c r="J20" s="26">
         <f t="shared" si="0"/>
         <v>147550</v>
       </c>
-      <c r="K20" s="33">
+      <c r="K20" s="26">
         <f t="shared" si="1"/>
         <v>1147550</v>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M20" s="31">
+      <c r="M20" s="24">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="N20" s="33">
+      <c r="N20" s="26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O20" s="33">
+      <c r="O20" s="26">
         <f t="shared" si="5"/>
         <v>12623050</v>
       </c>
-      <c r="P20" s="33">
+      <c r="P20" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="33">
+      <c r="Q20" s="26">
         <f t="shared" si="7"/>
         <v>4207683.333333333</v>
       </c>
-      <c r="R20" s="33">
+      <c r="R20" s="26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S20" s="33">
+      <c r="S20" s="26">
         <f t="shared" si="9"/>
         <v>209000</v>
       </c>
-      <c r="T20" s="33">
+      <c r="T20" s="26">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U20" s="33">
+      <c r="U20" s="26">
         <f t="shared" si="11"/>
         <v>17039733.333333332</v>
       </c>
-      <c r="V20" s="31" t="s">
+      <c r="V20" s="24" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27">
+      <c r="A21" s="20">
         <v>17</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="21" t="s">
         <v>385</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F21" s="27" t="s">
+      <c r="F21" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G21" s="27">
-        <v>1</v>
-      </c>
-      <c r="H21" s="29">
+      <c r="G21" s="20">
+        <v>1</v>
+      </c>
+      <c r="H21" s="22">
         <v>1000000</v>
       </c>
-      <c r="I21" s="27">
-        <v>1</v>
-      </c>
-      <c r="J21" s="29">
+      <c r="I21" s="20">
+        <v>1</v>
+      </c>
+      <c r="J21" s="22">
         <f t="shared" si="0"/>
         <v>147550</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="22">
         <f t="shared" si="1"/>
         <v>1147550</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M21" s="27">
+      <c r="M21" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="22">
         <f t="shared" si="4"/>
         <v>2702295.1612903229</v>
       </c>
-      <c r="O21" s="29">
+      <c r="O21" s="22">
         <f t="shared" si="5"/>
         <v>13770600</v>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="22">
         <f t="shared" si="6"/>
         <v>1147550</v>
       </c>
-      <c r="Q21" s="29">
+      <c r="Q21" s="22">
         <f t="shared" si="7"/>
         <v>4590200</v>
       </c>
-      <c r="R21" s="29">
+      <c r="R21" s="22">
         <f t="shared" si="8"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S21" s="29">
+      <c r="S21" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T21" s="29">
+      <c r="T21" s="22">
         <f t="shared" si="10"/>
         <v>3894587.0967741939</v>
       </c>
-      <c r="U21" s="29">
+      <c r="U21" s="22">
         <f t="shared" si="11"/>
         <v>18588800</v>
       </c>
-      <c r="V21" s="27" t="s">
+      <c r="V21" s="20" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27">
+      <c r="A22" s="20">
         <v>18</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G22" s="27">
-        <v>1</v>
-      </c>
-      <c r="H22" s="29">
+      <c r="G22" s="20">
+        <v>1</v>
+      </c>
+      <c r="H22" s="22">
         <v>1000000</v>
       </c>
-      <c r="I22" s="27">
-        <v>1</v>
-      </c>
-      <c r="J22" s="29">
+      <c r="I22" s="20">
+        <v>1</v>
+      </c>
+      <c r="J22" s="22">
         <f t="shared" si="0"/>
         <v>147550</v>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="22">
         <f t="shared" si="1"/>
         <v>1147550</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M22" s="27">
+      <c r="M22" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N22" s="29">
+      <c r="N22" s="22">
         <f t="shared" si="4"/>
         <v>2702295.1612903229</v>
       </c>
-      <c r="O22" s="29">
+      <c r="O22" s="22">
         <f t="shared" si="5"/>
         <v>13770600</v>
       </c>
-      <c r="P22" s="29">
+      <c r="P22" s="22">
         <f t="shared" si="6"/>
         <v>1147550</v>
       </c>
-      <c r="Q22" s="29">
+      <c r="Q22" s="22">
         <f t="shared" si="7"/>
         <v>4590200</v>
       </c>
-      <c r="R22" s="29">
+      <c r="R22" s="22">
         <f t="shared" si="8"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S22" s="29">
+      <c r="S22" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T22" s="29">
+      <c r="T22" s="22">
         <f t="shared" si="10"/>
         <v>3894587.0967741939</v>
       </c>
-      <c r="U22" s="29">
+      <c r="U22" s="22">
         <f t="shared" si="11"/>
         <v>18588800</v>
       </c>
-      <c r="V22" s="27" t="s">
+      <c r="V22" s="20" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27">
+      <c r="A23" s="20">
         <v>19</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F23" s="27" t="s">
+      <c r="F23" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G23" s="27">
-        <v>1</v>
-      </c>
-      <c r="H23" s="29">
+      <c r="G23" s="20">
+        <v>1</v>
+      </c>
+      <c r="H23" s="22">
         <v>700000</v>
       </c>
-      <c r="I23" s="27">
-        <v>1</v>
-      </c>
-      <c r="J23" s="29">
+      <c r="I23" s="20">
+        <v>1</v>
+      </c>
+      <c r="J23" s="22">
         <f t="shared" si="0"/>
         <v>112210</v>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="22">
         <f t="shared" si="1"/>
         <v>812210</v>
       </c>
-      <c r="L23" s="30">
+      <c r="L23" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M23" s="27">
+      <c r="M23" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N23" s="29">
+      <c r="N23" s="22">
         <f t="shared" si="4"/>
         <v>1912623.548387097</v>
       </c>
-      <c r="O23" s="29">
+      <c r="O23" s="22">
         <f t="shared" si="5"/>
         <v>9746520</v>
       </c>
-      <c r="P23" s="29">
+      <c r="P23" s="22">
         <f t="shared" si="6"/>
         <v>812210</v>
       </c>
-      <c r="Q23" s="29">
+      <c r="Q23" s="22">
         <f t="shared" si="7"/>
         <v>3248839.9999999995</v>
       </c>
-      <c r="R23" s="29">
+      <c r="R23" s="22">
         <f t="shared" si="8"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S23" s="29">
+      <c r="S23" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T23" s="29">
+      <c r="T23" s="22">
         <f t="shared" si="10"/>
         <v>2769575.4838709682</v>
       </c>
-      <c r="U23" s="29">
+      <c r="U23" s="22">
         <f t="shared" si="11"/>
         <v>13223360</v>
       </c>
-      <c r="V23" s="27" t="s">
+      <c r="V23" s="20" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31">
+      <c r="A24" s="24">
         <v>20</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="25" t="s">
         <v>389</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="25" t="s">
         <v>386</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G24" s="31">
-        <v>1</v>
-      </c>
-      <c r="H24" s="33">
+      <c r="G24" s="24">
+        <v>1</v>
+      </c>
+      <c r="H24" s="26">
         <v>700000</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="24">
         <v>5</v>
       </c>
-      <c r="J24" s="33">
+      <c r="J24" s="26">
         <f t="shared" si="0"/>
         <v>112210</v>
       </c>
-      <c r="K24" s="33">
+      <c r="K24" s="26">
         <f t="shared" si="1"/>
         <v>812210</v>
       </c>
-      <c r="L24" s="34">
+      <c r="L24" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="24">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="26">
         <f t="shared" si="5"/>
         <v>8934310</v>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="26">
         <f t="shared" si="7"/>
         <v>2978103.3333333326</v>
       </c>
-      <c r="R24" s="33">
+      <c r="R24" s="26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S24" s="33">
+      <c r="S24" s="26">
         <f t="shared" si="9"/>
         <v>209000</v>
       </c>
-      <c r="T24" s="33">
+      <c r="T24" s="26">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U24" s="33">
+      <c r="U24" s="26">
         <f t="shared" si="11"/>
         <v>12121413.333333332</v>
       </c>
-      <c r="V24" s="31" t="s">
+      <c r="V24" s="24" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="31">
+      <c r="A25" s="24">
         <v>21</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="25" t="s">
         <v>389</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="25" t="s">
         <v>386</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F25" s="31" t="s">
+      <c r="F25" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G25" s="31">
-        <v>1</v>
-      </c>
-      <c r="H25" s="33">
+      <c r="G25" s="24">
+        <v>1</v>
+      </c>
+      <c r="H25" s="26">
         <v>700000</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="24">
         <v>5</v>
       </c>
-      <c r="J25" s="33">
+      <c r="J25" s="26">
         <f t="shared" ref="J25:J26" si="34">IF(E25="штат",ROUND(Ставка_СН*H25*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H25+Ставка_СО*MIN(H25*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H25,Кап_ООСМС*МЗП),0),ROUND(H25*НДС,0))</f>
         <v>112210</v>
       </c>
-      <c r="K25" s="33">
+      <c r="K25" s="26">
         <f t="shared" ref="K25:K26" si="35">G25*(H25+J25)</f>
         <v>812210</v>
       </c>
-      <c r="L25" s="34">
+      <c r="L25" s="27">
         <f t="shared" ref="L25:L26" si="36">IF(AND(F25="новая",I25=1),Мес_2026_новые,MAX(0,4-I25))</f>
         <v>0</v>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="24">
         <f t="shared" ref="M25:M26" si="37">MAX(0,MIN(12,16-MAX(I25,4)))</f>
         <v>11</v>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="26">
         <f t="shared" ref="N25:N26" si="38">K25*L25</f>
         <v>0</v>
       </c>
-      <c r="O25" s="33">
+      <c r="O25" s="26">
         <f t="shared" ref="O25:O26" si="39">K25*M25</f>
         <v>8934310</v>
       </c>
-      <c r="P25" s="33">
+      <c r="P25" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="33">
+      <c r="Q25" s="26">
         <f t="shared" ref="Q25:Q26" si="40">IF(E25="штат",Премия_KPI*H25*(1+J25/H25)*G25*M25/12,0)</f>
         <v>2978103.3333333326</v>
       </c>
-      <c r="R25" s="33">
+      <c r="R25" s="26">
         <f t="shared" ref="R25:R26" si="41">IF(E25="штат",(ДМС+ОСНС)*G25*L25/12,0)</f>
         <v>0</v>
       </c>
-      <c r="S25" s="33">
+      <c r="S25" s="26">
         <f t="shared" ref="S25:S26" si="42">IF(E25="штат",(ДМС+ОСНС)*G25*M25/12,0)</f>
         <v>209000</v>
       </c>
-      <c r="T25" s="33">
+      <c r="T25" s="26">
         <f t="shared" ref="T25:T26" si="43">N25+P25+R25</f>
         <v>0</v>
       </c>
-      <c r="U25" s="33">
+      <c r="U25" s="26">
         <f t="shared" ref="U25:U26" si="44">O25+Q25+S25</f>
         <v>12121413.333333332</v>
       </c>
-      <c r="V25" s="31" t="s">
+      <c r="V25" s="24" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31">
+      <c r="A26" s="24">
         <v>22</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="25" t="s">
         <v>410</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="25" t="s">
         <v>386</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F26" s="31" t="s">
+      <c r="F26" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G26" s="31">
-        <v>1</v>
-      </c>
-      <c r="H26" s="33">
+      <c r="G26" s="24">
+        <v>1</v>
+      </c>
+      <c r="H26" s="26">
         <v>800000</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="24">
         <v>5</v>
       </c>
-      <c r="J26" s="33">
+      <c r="J26" s="26">
         <f t="shared" si="34"/>
         <v>123990</v>
       </c>
-      <c r="K26" s="33">
+      <c r="K26" s="26">
         <f t="shared" si="35"/>
         <v>923990</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="27">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="M26" s="31">
+      <c r="M26" s="24">
         <f t="shared" si="37"/>
         <v>11</v>
       </c>
-      <c r="N26" s="33">
+      <c r="N26" s="26">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="O26" s="33">
+      <c r="O26" s="26">
         <f t="shared" si="39"/>
         <v>10163890</v>
       </c>
-      <c r="P26" s="33">
+      <c r="P26" s="26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="33">
+      <c r="Q26" s="26">
         <f t="shared" si="40"/>
         <v>3387963.3333333335</v>
       </c>
-      <c r="R26" s="33">
+      <c r="R26" s="26">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="S26" s="33">
+      <c r="S26" s="26">
         <f t="shared" si="42"/>
         <v>209000</v>
       </c>
-      <c r="T26" s="33">
+      <c r="T26" s="26">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="U26" s="33">
+      <c r="U26" s="26">
         <f t="shared" si="44"/>
         <v>13760853.333333334</v>
       </c>
-      <c r="V26" s="31" t="s">
+      <c r="V26" s="24" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="27">
+      <c r="A27" s="20">
         <v>23</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="20" t="s">
         <v>392</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="21" t="s">
         <v>456</v>
       </c>
-      <c r="E27" s="27" t="s">
+      <c r="E27" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F27" s="27" t="s">
+      <c r="F27" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="27">
-        <v>1</v>
-      </c>
-      <c r="H27" s="29">
+      <c r="G27" s="20">
+        <v>1</v>
+      </c>
+      <c r="H27" s="22">
         <v>1300000</v>
       </c>
-      <c r="I27" s="27">
-        <v>1</v>
-      </c>
-      <c r="J27" s="29">
+      <c r="I27" s="20">
+        <v>1</v>
+      </c>
+      <c r="J27" s="22">
         <f t="shared" ref="J27" si="45">IF(E27="штат",ROUND(Ставка_СН*H27*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H27+Ставка_СО*MIN(H27*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H27,Кап_ООСМС*МЗП),0),ROUND(H27*НДС,0))</f>
         <v>182890</v>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="22">
         <f t="shared" ref="K27" si="46">G27*(H27+J27)</f>
         <v>1482890</v>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="23">
         <f t="shared" ref="L27" si="47">IF(AND(F27="новая",I27=1),Мес_2026_новые,MAX(0,4-I27))</f>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M27" s="27">
+      <c r="M27" s="20">
         <f t="shared" ref="M27" si="48">MAX(0,MIN(12,16-MAX(I27,4)))</f>
         <v>12</v>
       </c>
-      <c r="N27" s="29">
+      <c r="N27" s="22">
         <f t="shared" ref="N27" si="49">K27*L27</f>
         <v>3491966.7741935486</v>
       </c>
-      <c r="O27" s="29">
+      <c r="O27" s="22">
         <f t="shared" ref="O27" si="50">K27*M27</f>
         <v>17794680</v>
       </c>
-      <c r="P27" s="29">
+      <c r="P27" s="22">
         <f t="shared" si="6"/>
         <v>1482890</v>
       </c>
-      <c r="Q27" s="29">
+      <c r="Q27" s="22">
         <f t="shared" ref="Q27" si="51">IF(E27="штат",Премия_KPI*H27*(1+J27/H27)*G27*M27/12,0)</f>
         <v>5931560</v>
       </c>
-      <c r="R27" s="29">
+      <c r="R27" s="22">
         <f t="shared" ref="R27" si="52">IF(E27="штат",(ДМС+ОСНС)*G27*L27/12,0)</f>
         <v>44741.93548387097</v>
       </c>
-      <c r="S27" s="29">
+      <c r="S27" s="22">
         <f t="shared" ref="S27" si="53">IF(E27="штат",(ДМС+ОСНС)*G27*M27/12,0)</f>
         <v>228000</v>
       </c>
-      <c r="T27" s="29">
+      <c r="T27" s="22">
         <f t="shared" ref="T27" si="54">N27+P27+R27</f>
         <v>5019598.7096774196</v>
       </c>
-      <c r="U27" s="29">
+      <c r="U27" s="22">
         <f t="shared" ref="U27" si="55">O27+Q27+S27</f>
         <v>23954240</v>
       </c>
-      <c r="V27" s="27" t="s">
+      <c r="V27" s="20" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="35">
+      <c r="A28" s="28">
         <v>24</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="29" t="s">
         <v>474</v>
       </c>
-      <c r="D28" s="36" t="s">
+      <c r="D28" s="29" t="s">
         <v>378</v>
       </c>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="G28" s="35">
-        <v>0</v>
-      </c>
-      <c r="H28" s="37">
+      <c r="G28" s="28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="30">
         <v>1000000</v>
       </c>
-      <c r="I28" s="35">
-        <v>1</v>
-      </c>
-      <c r="J28" s="37">
+      <c r="I28" s="28">
+        <v>1</v>
+      </c>
+      <c r="J28" s="30">
         <f t="shared" si="0"/>
         <v>160000</v>
       </c>
-      <c r="K28" s="37">
+      <c r="K28" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="38">
+      <c r="L28" s="31">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M28" s="35">
+      <c r="M28" s="28">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N28" s="37">
+      <c r="N28" s="30">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O28" s="37">
+      <c r="O28" s="30">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P28" s="37">
+      <c r="P28" s="30">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="37">
+      <c r="Q28" s="30">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R28" s="37">
+      <c r="R28" s="30">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S28" s="37">
+      <c r="S28" s="30">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T28" s="37">
+      <c r="T28" s="30">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U28" s="37">
+      <c r="U28" s="30">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="V28" s="35" t="s">
+      <c r="V28" s="28" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="27">
+      <c r="A29" s="20">
         <v>25</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="20" t="s">
         <v>395</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="21" t="s">
         <v>456</v>
       </c>
-      <c r="E29" s="27" t="s">
+      <c r="E29" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="27" t="s">
+      <c r="F29" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="27">
-        <v>1</v>
-      </c>
-      <c r="H29" s="29">
+      <c r="G29" s="20">
+        <v>1</v>
+      </c>
+      <c r="H29" s="22">
         <v>1300000</v>
       </c>
-      <c r="I29" s="27">
-        <v>1</v>
-      </c>
-      <c r="J29" s="29">
+      <c r="I29" s="20">
+        <v>1</v>
+      </c>
+      <c r="J29" s="22">
         <f t="shared" si="0"/>
         <v>182890</v>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="22">
         <f t="shared" si="1"/>
         <v>1482890</v>
       </c>
-      <c r="L29" s="30">
+      <c r="L29" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M29" s="27">
+      <c r="M29" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N29" s="29">
+      <c r="N29" s="22">
         <f t="shared" si="4"/>
         <v>3491966.7741935486</v>
       </c>
-      <c r="O29" s="29">
+      <c r="O29" s="22">
         <f t="shared" si="5"/>
         <v>17794680</v>
       </c>
-      <c r="P29" s="29">
+      <c r="P29" s="22">
         <f t="shared" si="6"/>
         <v>1482890</v>
       </c>
-      <c r="Q29" s="29">
+      <c r="Q29" s="22">
         <f t="shared" si="7"/>
         <v>5931560</v>
       </c>
-      <c r="R29" s="29">
+      <c r="R29" s="22">
         <f t="shared" si="8"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S29" s="29">
+      <c r="S29" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T29" s="29">
+      <c r="T29" s="22">
         <f t="shared" si="10"/>
         <v>5019598.7096774196</v>
       </c>
-      <c r="U29" s="29">
+      <c r="U29" s="22">
         <f t="shared" si="11"/>
         <v>23954240</v>
       </c>
-      <c r="V29" s="27" t="s">
+      <c r="V29" s="20" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27">
+      <c r="A30" s="20">
         <v>26</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="20" t="s">
         <v>395</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="21" t="s">
         <v>398</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="27">
-        <v>1</v>
-      </c>
-      <c r="H30" s="29">
+      <c r="G30" s="20">
+        <v>1</v>
+      </c>
+      <c r="H30" s="22">
         <v>1000000</v>
       </c>
-      <c r="I30" s="27">
-        <v>1</v>
-      </c>
-      <c r="J30" s="29">
+      <c r="I30" s="20">
+        <v>1</v>
+      </c>
+      <c r="J30" s="22">
         <f t="shared" si="0"/>
         <v>147550</v>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="22">
         <f t="shared" si="1"/>
         <v>1147550</v>
       </c>
-      <c r="L30" s="30">
+      <c r="L30" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M30" s="27">
+      <c r="M30" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N30" s="29">
+      <c r="N30" s="22">
         <f t="shared" si="4"/>
         <v>2702295.1612903229</v>
       </c>
-      <c r="O30" s="29">
+      <c r="O30" s="22">
         <f t="shared" si="5"/>
         <v>13770600</v>
       </c>
-      <c r="P30" s="29">
+      <c r="P30" s="22">
         <f t="shared" si="6"/>
         <v>1147550</v>
       </c>
-      <c r="Q30" s="29">
+      <c r="Q30" s="22">
         <f t="shared" si="7"/>
         <v>4590200</v>
       </c>
-      <c r="R30" s="29">
+      <c r="R30" s="22">
         <f t="shared" si="8"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S30" s="29">
+      <c r="S30" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T30" s="29">
+      <c r="T30" s="22">
         <f t="shared" si="10"/>
         <v>3894587.0967741939</v>
       </c>
-      <c r="U30" s="29">
+      <c r="U30" s="22">
         <f t="shared" si="11"/>
         <v>18588800</v>
       </c>
-      <c r="V30" s="27" t="s">
+      <c r="V30" s="20" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="35">
+      <c r="A31" s="28">
         <v>27</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="29" t="s">
         <v>404</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="E31" s="35" t="s">
+      <c r="E31" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="F31" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="G31" s="35">
-        <v>0</v>
-      </c>
-      <c r="H31" s="37">
+      <c r="G31" s="28">
+        <v>0</v>
+      </c>
+      <c r="H31" s="30">
         <v>1000000</v>
       </c>
-      <c r="I31" s="35">
-        <v>1</v>
-      </c>
-      <c r="J31" s="37">
+      <c r="I31" s="28">
+        <v>1</v>
+      </c>
+      <c r="J31" s="30">
         <f t="shared" si="0"/>
         <v>160000</v>
       </c>
-      <c r="K31" s="37">
+      <c r="K31" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L31" s="38">
+      <c r="L31" s="31">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="28">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="30">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O31" s="37">
+      <c r="O31" s="30">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P31" s="37">
+      <c r="P31" s="30">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="37">
+      <c r="Q31" s="30">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R31" s="37">
+      <c r="R31" s="30">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S31" s="37">
+      <c r="S31" s="30">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T31" s="37">
+      <c r="T31" s="30">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U31" s="37">
+      <c r="U31" s="30">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="V31" s="35" t="s">
+      <c r="V31" s="28" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="35">
+      <c r="A32" s="28">
         <v>28</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="29" t="s">
         <v>405</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="D32" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="E32" s="35" t="s">
+      <c r="E32" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="F32" s="35" t="s">
+      <c r="F32" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="35">
-        <v>0</v>
-      </c>
-      <c r="H32" s="37">
+      <c r="G32" s="28">
+        <v>0</v>
+      </c>
+      <c r="H32" s="30">
         <v>700000</v>
       </c>
-      <c r="I32" s="35">
-        <v>1</v>
-      </c>
-      <c r="J32" s="37">
+      <c r="I32" s="28">
+        <v>1</v>
+      </c>
+      <c r="J32" s="30">
         <f t="shared" ref="J32" si="56">IF(E32="штат",ROUND(Ставка_СН*H32*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H32+Ставка_СО*MIN(H32*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H32,Кап_ООСМС*МЗП),0),ROUND(H32*НДС,0))</f>
         <v>112000</v>
       </c>
-      <c r="K32" s="37">
+      <c r="K32" s="30">
         <f t="shared" ref="K32" si="57">G32*(H32+J32)</f>
         <v>0</v>
       </c>
-      <c r="L32" s="38">
+      <c r="L32" s="31">
         <f t="shared" ref="L32" si="58">IF(AND(F32="новая",I32=1),Мес_2026_новые,MAX(0,4-I32))</f>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M32" s="35">
+      <c r="M32" s="28">
         <f t="shared" ref="M32" si="59">MAX(0,MIN(12,16-MAX(I32,4)))</f>
         <v>12</v>
       </c>
-      <c r="N32" s="37">
+      <c r="N32" s="30">
         <f t="shared" ref="N32" si="60">K32*L32</f>
         <v>0</v>
       </c>
-      <c r="O32" s="37">
+      <c r="O32" s="30">
         <f t="shared" ref="O32" si="61">K32*M32</f>
         <v>0</v>
       </c>
-      <c r="P32" s="37">
+      <c r="P32" s="30">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="37">
+      <c r="Q32" s="30">
         <f t="shared" ref="Q32" si="62">IF(E32="штат",Премия_KPI*H32*(1+J32/H32)*G32*M32/12,0)</f>
         <v>0</v>
       </c>
-      <c r="R32" s="37">
+      <c r="R32" s="30">
         <f t="shared" ref="R32" si="63">IF(E32="штат",(ДМС+ОСНС)*G32*L32/12,0)</f>
         <v>0</v>
       </c>
-      <c r="S32" s="37">
+      <c r="S32" s="30">
         <f t="shared" ref="S32" si="64">IF(E32="штат",(ДМС+ОСНС)*G32*M32/12,0)</f>
         <v>0</v>
       </c>
-      <c r="T32" s="37">
+      <c r="T32" s="30">
         <f t="shared" ref="T32" si="65">N32+P32+R32</f>
         <v>0</v>
       </c>
-      <c r="U32" s="37">
+      <c r="U32" s="30">
         <f t="shared" ref="U32" si="66">O32+Q32+S32</f>
         <v>0</v>
       </c>
-      <c r="V32" s="35" t="s">
+      <c r="V32" s="28" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="35">
+      <c r="A33" s="28">
         <v>29</v>
       </c>
-      <c r="B33" s="35" t="s">
+      <c r="B33" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="29" t="s">
         <v>406</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="E33" s="35" t="s">
+      <c r="E33" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="F33" s="35" t="s">
+      <c r="F33" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="35">
-        <v>0</v>
-      </c>
-      <c r="H33" s="37">
+      <c r="G33" s="28">
+        <v>0</v>
+      </c>
+      <c r="H33" s="30">
         <v>700000</v>
       </c>
-      <c r="I33" s="35">
-        <v>1</v>
-      </c>
-      <c r="J33" s="37">
+      <c r="I33" s="28">
+        <v>1</v>
+      </c>
+      <c r="J33" s="30">
         <f t="shared" si="0"/>
         <v>112000</v>
       </c>
-      <c r="K33" s="37">
+      <c r="K33" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L33" s="38">
+      <c r="L33" s="31">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="28">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N33" s="37">
+      <c r="N33" s="30">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O33" s="37">
+      <c r="O33" s="30">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P33" s="37">
+      <c r="P33" s="30">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="37">
+      <c r="Q33" s="30">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R33" s="37">
+      <c r="R33" s="30">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S33" s="37">
+      <c r="S33" s="30">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T33" s="37">
+      <c r="T33" s="30">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U33" s="37">
+      <c r="U33" s="30">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="V33" s="35" t="s">
+      <c r="V33" s="28" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="27">
+      <c r="A34" s="20">
         <v>30</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="20" t="s">
         <v>395</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="21" t="s">
         <v>400</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="E34" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="27">
-        <v>1</v>
-      </c>
-      <c r="H34" s="29">
+      <c r="G34" s="20">
+        <v>1</v>
+      </c>
+      <c r="H34" s="22">
         <v>1000000</v>
       </c>
-      <c r="I34" s="27">
-        <v>1</v>
-      </c>
-      <c r="J34" s="29">
+      <c r="I34" s="20">
+        <v>1</v>
+      </c>
+      <c r="J34" s="22">
         <f t="shared" si="0"/>
         <v>147550</v>
       </c>
-      <c r="K34" s="29">
+      <c r="K34" s="22">
         <f t="shared" si="1"/>
         <v>1147550</v>
       </c>
-      <c r="L34" s="30">
+      <c r="L34" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M34" s="27">
+      <c r="M34" s="20">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N34" s="29">
+      <c r="N34" s="22">
         <f t="shared" si="4"/>
         <v>2702295.1612903229</v>
       </c>
-      <c r="O34" s="29">
+      <c r="O34" s="22">
         <f t="shared" si="5"/>
         <v>13770600</v>
       </c>
-      <c r="P34" s="29">
+      <c r="P34" s="22">
         <f t="shared" si="6"/>
         <v>1147550</v>
       </c>
-      <c r="Q34" s="29">
+      <c r="Q34" s="22">
         <f t="shared" si="7"/>
         <v>4590200</v>
       </c>
-      <c r="R34" s="29">
+      <c r="R34" s="22">
         <f t="shared" si="8"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S34" s="29">
+      <c r="S34" s="22">
         <f t="shared" si="9"/>
         <v>228000</v>
       </c>
-      <c r="T34" s="29">
+      <c r="T34" s="22">
         <f t="shared" si="10"/>
         <v>3894587.0967741939</v>
       </c>
-      <c r="U34" s="29">
+      <c r="U34" s="22">
         <f t="shared" si="11"/>
         <v>18588800</v>
       </c>
-      <c r="V34" s="27" t="s">
+      <c r="V34" s="20" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="27">
+      <c r="A35" s="20">
         <v>31</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="20" t="s">
         <v>395</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="E35" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F35" s="27" t="s">
+      <c r="F35" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="27">
-        <v>1</v>
-      </c>
-      <c r="H35" s="29">
+      <c r="G35" s="20">
+        <v>1</v>
+      </c>
+      <c r="H35" s="22">
         <v>700000</v>
       </c>
-      <c r="I35" s="27">
-        <v>1</v>
-      </c>
-      <c r="J35" s="29">
+      <c r="I35" s="20">
+        <v>1</v>
+      </c>
+      <c r="J35" s="22">
         <f t="shared" ref="J35:J41" si="67">IF(E35="штат",ROUND(Ставка_СН*H35*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H35+Ставка_СО*MIN(H35*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H35,Кап_ООСМС*МЗП),0),ROUND(H35*НДС,0))</f>
         <v>112210</v>
       </c>
-      <c r="K35" s="29">
+      <c r="K35" s="22">
         <f t="shared" ref="K35:K41" si="68">G35*(H35+J35)</f>
         <v>812210</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M35" s="27">
+      <c r="M35" s="20">
         <f t="shared" ref="M35:M41" si="69">MAX(0,MIN(12,16-MAX(I35,4)))</f>
         <v>12</v>
       </c>
-      <c r="N35" s="29">
+      <c r="N35" s="22">
         <f t="shared" ref="N35:N41" si="70">K35*L35</f>
         <v>1912623.548387097</v>
       </c>
-      <c r="O35" s="29">
+      <c r="O35" s="22">
         <f t="shared" ref="O35:O41" si="71">K35*M35</f>
         <v>9746520</v>
       </c>
-      <c r="P35" s="29">
+      <c r="P35" s="22">
         <f t="shared" si="6"/>
         <v>812210</v>
       </c>
-      <c r="Q35" s="29">
+      <c r="Q35" s="22">
         <f t="shared" ref="Q35:Q41" si="72">IF(E35="штат",Премия_KPI*H35*(1+J35/H35)*G35*M35/12,0)</f>
         <v>3248839.9999999995</v>
       </c>
-      <c r="R35" s="29">
+      <c r="R35" s="22">
         <f t="shared" ref="R35:R41" si="73">IF(E35="штат",(ДМС+ОСНС)*G35*L35/12,0)</f>
         <v>44741.93548387097</v>
       </c>
-      <c r="S35" s="29">
+      <c r="S35" s="22">
         <f t="shared" ref="S35:S41" si="74">IF(E35="штат",(ДМС+ОСНС)*G35*M35/12,0)</f>
         <v>228000</v>
       </c>
-      <c r="T35" s="29">
+      <c r="T35" s="22">
         <f t="shared" ref="T35:T41" si="75">N35+P35+R35</f>
         <v>2769575.4838709682</v>
       </c>
-      <c r="U35" s="29">
+      <c r="U35" s="22">
         <f t="shared" ref="U35:U41" si="76">O35+Q35+S35</f>
         <v>13223360</v>
       </c>
-      <c r="V35" s="27" t="s">
+      <c r="V35" s="20" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="35">
+      <c r="A36" s="28">
         <v>32</v>
       </c>
-      <c r="B36" s="35" t="s">
+      <c r="B36" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="29" t="s">
         <v>407</v>
       </c>
-      <c r="D36" s="36" t="s">
+      <c r="D36" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="E36" s="35" t="s">
+      <c r="E36" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="F36" s="35" t="s">
+      <c r="F36" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="G36" s="35">
-        <v>0</v>
-      </c>
-      <c r="H36" s="37">
+      <c r="G36" s="28">
+        <v>0</v>
+      </c>
+      <c r="H36" s="30">
         <v>700000</v>
       </c>
-      <c r="I36" s="35">
-        <v>1</v>
-      </c>
-      <c r="J36" s="37">
+      <c r="I36" s="28">
+        <v>1</v>
+      </c>
+      <c r="J36" s="30">
         <f t="shared" si="67"/>
         <v>112000</v>
       </c>
-      <c r="K36" s="37">
+      <c r="K36" s="30">
         <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="L36" s="38">
+      <c r="L36" s="31">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="28">
         <f t="shared" si="69"/>
         <v>12</v>
       </c>
-      <c r="N36" s="37">
+      <c r="N36" s="30">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="O36" s="37">
+      <c r="O36" s="30">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="P36" s="37">
+      <c r="P36" s="30">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="37">
+      <c r="Q36" s="30">
         <f t="shared" si="72"/>
         <v>0</v>
       </c>
-      <c r="R36" s="37">
+      <c r="R36" s="30">
         <f t="shared" si="73"/>
         <v>0</v>
       </c>
-      <c r="S36" s="37">
+      <c r="S36" s="30">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="T36" s="37">
+      <c r="T36" s="30">
         <f t="shared" si="75"/>
         <v>0</v>
       </c>
-      <c r="U36" s="37">
+      <c r="U36" s="30">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="V36" s="35" t="s">
+      <c r="V36" s="28" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="27">
+      <c r="A37" s="20">
         <v>33</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="20" t="s">
         <v>475</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E37" s="27" t="s">
+      <c r="E37" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F37" s="27" t="s">
+      <c r="F37" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="G37" s="27">
-        <v>1</v>
-      </c>
-      <c r="H37" s="29">
+      <c r="G37" s="20">
+        <v>1</v>
+      </c>
+      <c r="H37" s="22">
         <v>1400000</v>
       </c>
-      <c r="I37" s="27">
-        <v>1</v>
-      </c>
-      <c r="J37" s="29">
+      <c r="I37" s="20">
+        <v>1</v>
+      </c>
+      <c r="J37" s="22">
         <f t="shared" si="67"/>
         <v>194670</v>
       </c>
-      <c r="K37" s="29">
+      <c r="K37" s="22">
         <f t="shared" si="68"/>
         <v>1594670</v>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="23">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="M37" s="27">
+      <c r="M37" s="20">
         <f t="shared" si="69"/>
         <v>12</v>
       </c>
-      <c r="N37" s="29">
+      <c r="N37" s="22">
         <f t="shared" si="70"/>
         <v>4784010</v>
       </c>
-      <c r="O37" s="29">
+      <c r="O37" s="22">
         <f t="shared" si="71"/>
         <v>19136040</v>
       </c>
-      <c r="P37" s="29">
+      <c r="P37" s="22">
         <f t="shared" si="6"/>
         <v>1594670</v>
       </c>
-      <c r="Q37" s="29">
+      <c r="Q37" s="22">
         <f t="shared" si="72"/>
         <v>6378680.0000000009</v>
       </c>
-      <c r="R37" s="29">
+      <c r="R37" s="22">
         <f t="shared" si="73"/>
         <v>57000</v>
       </c>
-      <c r="S37" s="29">
+      <c r="S37" s="22">
         <f t="shared" si="74"/>
         <v>228000</v>
       </c>
-      <c r="T37" s="29">
+      <c r="T37" s="22">
         <f t="shared" si="75"/>
         <v>6435680</v>
       </c>
-      <c r="U37" s="29">
+      <c r="U37" s="22">
         <f t="shared" si="76"/>
         <v>25742720</v>
       </c>
-      <c r="V37" s="27" t="s">
+      <c r="V37" s="20" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="27">
+      <c r="A38" s="20">
         <v>34</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="20" t="s">
         <v>475</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="E38" s="27" t="s">
+      <c r="E38" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F38" s="27" t="s">
+      <c r="F38" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G38" s="27">
-        <v>1</v>
-      </c>
-      <c r="H38" s="29">
+      <c r="G38" s="20">
+        <v>1</v>
+      </c>
+      <c r="H38" s="22">
         <v>700000</v>
       </c>
-      <c r="I38" s="27">
-        <v>1</v>
-      </c>
-      <c r="J38" s="29">
+      <c r="I38" s="20">
+        <v>1</v>
+      </c>
+      <c r="J38" s="22">
         <f t="shared" si="67"/>
         <v>112210</v>
       </c>
-      <c r="K38" s="29">
+      <c r="K38" s="22">
         <f t="shared" si="68"/>
         <v>812210</v>
       </c>
-      <c r="L38" s="30">
+      <c r="L38" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M38" s="27">
+      <c r="M38" s="20">
         <f t="shared" si="69"/>
         <v>12</v>
       </c>
-      <c r="N38" s="29">
+      <c r="N38" s="22">
         <f t="shared" si="70"/>
         <v>1912623.548387097</v>
       </c>
-      <c r="O38" s="29">
+      <c r="O38" s="22">
         <f t="shared" si="71"/>
         <v>9746520</v>
       </c>
-      <c r="P38" s="29">
+      <c r="P38" s="22">
         <f t="shared" si="6"/>
         <v>812210</v>
       </c>
-      <c r="Q38" s="29">
+      <c r="Q38" s="22">
         <f t="shared" si="72"/>
         <v>3248839.9999999995</v>
       </c>
-      <c r="R38" s="29">
+      <c r="R38" s="22">
         <f t="shared" si="73"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S38" s="29">
+      <c r="S38" s="22">
         <f t="shared" si="74"/>
         <v>228000</v>
       </c>
-      <c r="T38" s="29">
+      <c r="T38" s="22">
         <f t="shared" si="75"/>
         <v>2769575.4838709682</v>
       </c>
-      <c r="U38" s="29">
+      <c r="U38" s="22">
         <f t="shared" si="76"/>
         <v>13223360</v>
       </c>
-      <c r="V38" s="27" t="s">
+      <c r="V38" s="20" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="27">
+      <c r="A39" s="20">
         <v>35</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="20" t="s">
         <v>475</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="21" t="s">
         <v>476</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="21" t="s">
         <v>462</v>
       </c>
-      <c r="E39" s="27" t="s">
+      <c r="E39" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G39" s="27">
-        <v>1</v>
-      </c>
-      <c r="H39" s="29">
+      <c r="G39" s="20">
+        <v>1</v>
+      </c>
+      <c r="H39" s="22">
         <v>1200000</v>
       </c>
-      <c r="I39" s="27">
-        <v>1</v>
-      </c>
-      <c r="J39" s="29">
+      <c r="I39" s="20">
+        <v>1</v>
+      </c>
+      <c r="J39" s="22">
         <f t="shared" si="67"/>
         <v>171110</v>
       </c>
-      <c r="K39" s="29">
+      <c r="K39" s="22">
         <f t="shared" si="68"/>
         <v>1371110</v>
       </c>
-      <c r="L39" s="30">
+      <c r="L39" s="23">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M39" s="27">
+      <c r="M39" s="20">
         <f t="shared" si="69"/>
         <v>12</v>
       </c>
-      <c r="N39" s="29">
+      <c r="N39" s="22">
         <f t="shared" si="70"/>
         <v>3228742.9032258065</v>
       </c>
-      <c r="O39" s="29">
+      <c r="O39" s="22">
         <f t="shared" si="71"/>
         <v>16453320</v>
       </c>
-      <c r="P39" s="29">
+      <c r="P39" s="22">
         <f t="shared" si="6"/>
         <v>1371110</v>
       </c>
-      <c r="Q39" s="29">
+      <c r="Q39" s="22">
         <f t="shared" si="72"/>
         <v>5484440</v>
       </c>
-      <c r="R39" s="29">
+      <c r="R39" s="22">
         <f t="shared" si="73"/>
         <v>44741.93548387097</v>
       </c>
-      <c r="S39" s="29">
+      <c r="S39" s="22">
         <f t="shared" si="74"/>
         <v>228000</v>
       </c>
-      <c r="T39" s="29">
+      <c r="T39" s="22">
         <f t="shared" si="75"/>
         <v>4644594.8387096776</v>
       </c>
-      <c r="U39" s="29">
+      <c r="U39" s="22">
         <f t="shared" si="76"/>
         <v>22165760</v>
       </c>
-      <c r="V39" s="27" t="s">
+      <c r="V39" s="20" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="35">
+      <c r="A40" s="28">
         <v>36</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="28" t="s">
         <v>475</v>
       </c>
-      <c r="C40" s="36" t="s">
+      <c r="C40" s="29" t="s">
         <v>478</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="E40" s="35" t="s">
+      <c r="E40" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="F40" s="35" t="s">
+      <c r="F40" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="G40" s="35">
-        <v>0</v>
-      </c>
-      <c r="H40" s="37">
+      <c r="G40" s="28">
+        <v>0</v>
+      </c>
+      <c r="H40" s="30">
         <v>1000000</v>
       </c>
-      <c r="I40" s="35">
-        <v>1</v>
-      </c>
-      <c r="J40" s="37">
+      <c r="I40" s="28">
+        <v>1</v>
+      </c>
+      <c r="J40" s="30">
         <f t="shared" si="67"/>
         <v>160000</v>
       </c>
-      <c r="K40" s="37">
+      <c r="K40" s="30">
         <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="L40" s="38">
+      <c r="L40" s="31">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M40" s="35">
+      <c r="M40" s="28">
         <f t="shared" si="69"/>
         <v>12</v>
       </c>
-      <c r="N40" s="37">
+      <c r="N40" s="30">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="O40" s="37">
+      <c r="O40" s="30">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="P40" s="37">
+      <c r="P40" s="30">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q40" s="37">
+      <c r="Q40" s="30">
         <f t="shared" si="72"/>
         <v>0</v>
       </c>
-      <c r="R40" s="37">
+      <c r="R40" s="30">
         <f t="shared" si="73"/>
         <v>0</v>
       </c>
-      <c r="S40" s="37">
+      <c r="S40" s="30">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="T40" s="37">
+      <c r="T40" s="30">
         <f t="shared" si="75"/>
         <v>0</v>
       </c>
-      <c r="U40" s="37">
+      <c r="U40" s="30">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="V40" s="35" t="s">
+      <c r="V40" s="28" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="35">
+      <c r="A41" s="28">
         <v>37</v>
       </c>
-      <c r="B41" s="35" t="s">
+      <c r="B41" s="28" t="s">
         <v>475</v>
       </c>
-      <c r="C41" s="36" t="s">
+      <c r="C41" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="D41" s="36" t="s">
+      <c r="D41" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="E41" s="35" t="s">
+      <c r="E41" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="F41" s="35" t="s">
+      <c r="F41" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="G41" s="35">
-        <v>0</v>
-      </c>
-      <c r="H41" s="37">
+      <c r="G41" s="28">
+        <v>0</v>
+      </c>
+      <c r="H41" s="30">
         <v>700000</v>
       </c>
-      <c r="I41" s="35">
-        <v>1</v>
-      </c>
-      <c r="J41" s="37">
+      <c r="I41" s="28">
+        <v>1</v>
+      </c>
+      <c r="J41" s="30">
         <f t="shared" si="67"/>
         <v>112000</v>
       </c>
-      <c r="K41" s="37">
+      <c r="K41" s="30">
         <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="L41" s="38">
+      <c r="L41" s="31">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M41" s="35">
+      <c r="M41" s="28">
         <f t="shared" si="69"/>
         <v>12</v>
       </c>
-      <c r="N41" s="37">
+      <c r="N41" s="30">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="O41" s="37">
+      <c r="O41" s="30">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="P41" s="37">
+      <c r="P41" s="30">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q41" s="37">
+      <c r="Q41" s="30">
         <f t="shared" si="72"/>
         <v>0</v>
       </c>
-      <c r="R41" s="37">
+      <c r="R41" s="30">
         <f t="shared" si="73"/>
         <v>0</v>
       </c>
-      <c r="S41" s="37">
+      <c r="S41" s="30">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="T41" s="37">
+      <c r="T41" s="30">
         <f t="shared" si="75"/>
         <v>0</v>
       </c>
-      <c r="U41" s="37">
+      <c r="U41" s="30">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="V41" s="35" t="s">
+      <c r="V41" s="28" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12" t="s">
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12">
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10">
         <f>SUM(G5:G41)</f>
         <v>30</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="8">
         <f>SUMPRODUCT(G5:G41,H5:H41)</f>
         <v>31300000</v>
       </c>
-      <c r="I42" s="12"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9">
+      <c r="I42" s="10"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8">
         <f>SUM(K5:K41)</f>
         <v>35879640</v>
       </c>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="9">
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="8">
         <f>SUM(N5:N41)</f>
         <v>58691747.741935484</v>
       </c>
-      <c r="O42" s="9">
+      <c r="O42" s="8">
         <f t="shared" ref="O42:U42" si="77">SUM(O5:O41)</f>
         <v>419273990</v>
       </c>
-      <c r="P42" s="9">
+      <c r="P42" s="8">
         <f t="shared" si="77"/>
         <v>23115060</v>
       </c>
-      <c r="Q42" s="9">
+      <c r="Q42" s="8">
         <f t="shared" si="77"/>
         <v>139757996.66666666</v>
       </c>
-      <c r="R42" s="9">
+      <c r="R42" s="8">
         <f t="shared" si="77"/>
         <v>854387.09677419392</v>
       </c>
-      <c r="S42" s="9">
+      <c r="S42" s="8">
         <f t="shared" si="77"/>
         <v>6631000</v>
       </c>
-      <c r="T42" s="9">
+      <c r="T42" s="8">
         <f t="shared" si="77"/>
         <v>82661194.838709667</v>
       </c>
-      <c r="U42" s="9">
+      <c r="U42" s="8">
         <f t="shared" si="77"/>
         <v>565662986.66666663</v>
       </c>
-      <c r="V42" s="12"/>
+      <c r="V42" s="10"/>
     </row>
     <row r="43" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
@@ -6579,17 +6625,17 @@
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="40" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" style="40" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" style="40" customWidth="1"/>
-    <col min="4" max="4" width="44.7109375" style="40" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="40" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="40" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="40" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="40" customWidth="1"/>
-    <col min="9" max="10" width="8.7109375" style="40" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="40" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="40"/>
+    <col min="1" max="1" width="4.7109375" style="32" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" style="32" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" style="32" customWidth="1"/>
+    <col min="4" max="4" width="44.7109375" style="32" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="32" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="32" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="32" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="32" customWidth="1"/>
+    <col min="9" max="10" width="8.7109375" style="32" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="32" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
@@ -6598,378 +6644,378 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="33" t="s">
         <v>273</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="33" t="s">
         <v>496</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="33" t="s">
         <v>497</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="33" t="s">
         <v>498</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="33" t="s">
         <v>499</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="L3" s="41">
+      <c r="L3" s="33">
         <v>2027</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="42">
-        <v>1</v>
-      </c>
-      <c r="B4" s="43" t="s">
+      <c r="A4" s="34">
+        <v>1</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>500</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="35" t="s">
         <v>501</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="36">
         <v>1000000</v>
       </c>
-      <c r="F4" s="44">
+      <c r="F4" s="36">
         <f t="shared" ref="F4:F10" si="0">E4*НДС</f>
         <v>160000</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="36">
         <f t="shared" ref="G4:G10" si="1">E4+F4</f>
         <v>1160000</v>
       </c>
-      <c r="H4" s="42">
-        <v>1</v>
-      </c>
-      <c r="I4" s="45">
+      <c r="H4" s="34">
+        <v>1</v>
+      </c>
+      <c r="I4" s="37">
         <f t="shared" ref="I4:I10" si="2">IF(H4=1,Мес_2026_новые,MAX(0,4-H4))</f>
         <v>2.3548387096774195</v>
       </c>
-      <c r="J4" s="45">
+      <c r="J4" s="37">
         <f t="shared" ref="J4:J10" si="3">MAX(0,MIN(12,16-MAX(H4,4)))</f>
         <v>12</v>
       </c>
-      <c r="K4" s="44">
+      <c r="K4" s="36">
         <f t="shared" ref="K4:K10" si="4">G4*I4</f>
         <v>2731612.9032258065</v>
       </c>
-      <c r="L4" s="44">
+      <c r="L4" s="36">
         <f t="shared" ref="L4:L10" si="5">G4*J4</f>
         <v>13920000</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="42">
+      <c r="A5" s="34">
         <v>2</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="35" t="s">
         <v>502</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="35" t="s">
         <v>503</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="36">
         <v>700000</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="36">
         <f t="shared" si="0"/>
         <v>112000</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="36">
         <f t="shared" si="1"/>
         <v>812000</v>
       </c>
-      <c r="H5" s="42">
-        <v>1</v>
-      </c>
-      <c r="I5" s="45">
+      <c r="H5" s="34">
+        <v>1</v>
+      </c>
+      <c r="I5" s="37">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="37">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="36">
         <f t="shared" si="4"/>
         <v>1912129.0322580647</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="36">
         <f t="shared" si="5"/>
         <v>9744000</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="42">
+      <c r="A6" s="34">
         <v>3</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="35" t="s">
         <v>504</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="35" t="s">
         <v>505</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="35" t="s">
         <v>506</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="36">
         <v>1000000</v>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="36">
         <f t="shared" si="0"/>
         <v>160000</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="36">
         <f t="shared" si="1"/>
         <v>1160000</v>
       </c>
-      <c r="H6" s="42">
-        <v>1</v>
-      </c>
-      <c r="I6" s="45">
+      <c r="H6" s="34">
+        <v>1</v>
+      </c>
+      <c r="I6" s="37">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="37">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="K6" s="44">
+      <c r="K6" s="36">
         <f t="shared" si="4"/>
         <v>2731612.9032258065</v>
       </c>
-      <c r="L6" s="44">
+      <c r="L6" s="36">
         <f t="shared" si="5"/>
         <v>13920000</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="42">
+      <c r="A7" s="34">
         <v>4</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="35" t="s">
         <v>507</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="35" t="s">
         <v>508</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="35" t="s">
         <v>509</v>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="36">
         <v>1000000</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="36">
         <f t="shared" si="0"/>
         <v>160000</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="36">
         <f t="shared" si="1"/>
         <v>1160000</v>
       </c>
-      <c r="H7" s="42">
-        <v>1</v>
-      </c>
-      <c r="I7" s="45">
+      <c r="H7" s="34">
+        <v>1</v>
+      </c>
+      <c r="I7" s="37">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="J7" s="45">
+      <c r="J7" s="37">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="K7" s="44">
+      <c r="K7" s="36">
         <f t="shared" si="4"/>
         <v>2731612.9032258065</v>
       </c>
-      <c r="L7" s="44">
+      <c r="L7" s="36">
         <f t="shared" si="5"/>
         <v>13920000</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="42">
+      <c r="A8" s="34">
         <v>5</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="35" t="s">
         <v>510</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="35" t="s">
         <v>508</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="35" t="s">
         <v>511</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="36">
         <v>700000</v>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="36">
         <f t="shared" si="0"/>
         <v>112000</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="36">
         <f t="shared" si="1"/>
         <v>812000</v>
       </c>
-      <c r="H8" s="42">
-        <v>1</v>
-      </c>
-      <c r="I8" s="45">
+      <c r="H8" s="34">
+        <v>1</v>
+      </c>
+      <c r="I8" s="37">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="J8" s="45">
+      <c r="J8" s="37">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="K8" s="44">
+      <c r="K8" s="36">
         <f t="shared" si="4"/>
         <v>1912129.0322580647</v>
       </c>
-      <c r="L8" s="44">
+      <c r="L8" s="36">
         <f t="shared" si="5"/>
         <v>9744000</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="42">
+      <c r="A9" s="34">
         <v>6</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="35" t="s">
         <v>512</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="35" t="s">
         <v>508</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" s="35" t="s">
         <v>513</v>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="36">
         <v>700000</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="36">
         <f t="shared" si="0"/>
         <v>112000</v>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="36">
         <f t="shared" si="1"/>
         <v>812000</v>
       </c>
-      <c r="H9" s="42">
-        <v>1</v>
-      </c>
-      <c r="I9" s="45">
+      <c r="H9" s="34">
+        <v>1</v>
+      </c>
+      <c r="I9" s="37">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="J9" s="45">
+      <c r="J9" s="37">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="K9" s="44">
+      <c r="K9" s="36">
         <f t="shared" si="4"/>
         <v>1912129.0322580647</v>
       </c>
-      <c r="L9" s="44">
+      <c r="L9" s="36">
         <f t="shared" si="5"/>
         <v>9744000</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="42">
+      <c r="A10" s="34">
         <v>7</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="35" t="s">
         <v>514</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="35" t="s">
         <v>508</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="35" t="s">
         <v>515</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="36">
         <v>700000</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="36">
         <f t="shared" si="0"/>
         <v>112000</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="36">
         <f t="shared" si="1"/>
         <v>812000</v>
       </c>
-      <c r="H10" s="42">
-        <v>1</v>
-      </c>
-      <c r="I10" s="45">
+      <c r="H10" s="34">
+        <v>1</v>
+      </c>
+      <c r="I10" s="37">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="J10" s="45">
+      <c r="J10" s="37">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="K10" s="44">
+      <c r="K10" s="36">
         <f t="shared" si="4"/>
         <v>1912129.0322580647</v>
       </c>
-      <c r="L10" s="44">
+      <c r="L10" s="36">
         <f t="shared" si="5"/>
         <v>9744000</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="46"/>
-      <c r="B11" s="46" t="s">
+      <c r="A11" s="38"/>
+      <c r="B11" s="38" t="s">
         <v>516</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="47">
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="39">
         <f>SUM(E4:E10)</f>
         <v>5800000</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="39">
         <f>SUM(F4:F10)</f>
         <v>928000</v>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="39">
         <f>SUM(G4:G10)</f>
         <v>6728000</v>
       </c>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="47">
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="39">
         <f>SUM(K4:K10)</f>
         <v>15843354.83870968</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="39">
         <f>SUM(L4:L10)</f>
         <v>80736000</v>
       </c>
@@ -7044,16 +7090,16 @@
         <f>Штат!G5</f>
         <v>1</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="12">
         <v>4</v>
       </c>
-      <c r="E5" s="14">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14">
-        <v>1</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="E5" s="12">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12">
+        <v>1</v>
+      </c>
+      <c r="G5" s="19">
         <f>Штат!L5</f>
         <v>3</v>
       </c>
@@ -7079,16 +7125,16 @@
         <f>Штат!G6</f>
         <v>1</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <v>6</v>
       </c>
-      <c r="E6" s="14">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14">
-        <v>1</v>
-      </c>
-      <c r="G6" s="26">
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <v>1</v>
+      </c>
+      <c r="G6" s="19">
         <f>Штат!L6</f>
         <v>3</v>
       </c>
@@ -7114,16 +7160,16 @@
         <f>Штат!G7</f>
         <v>1</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="12">
         <v>2</v>
       </c>
-      <c r="E7" s="14">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14">
-        <v>0</v>
-      </c>
-      <c r="G7" s="26">
+      <c r="E7" s="12">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0</v>
+      </c>
+      <c r="G7" s="19">
         <f>Штат!L7</f>
         <v>3</v>
       </c>
@@ -7149,16 +7195,16 @@
         <f>Штат!G37</f>
         <v>1</v>
       </c>
-      <c r="D8" s="14">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14">
-        <v>0</v>
-      </c>
-      <c r="G8" s="26">
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="19">
         <f>Штат!L37</f>
         <v>3</v>
       </c>
@@ -7184,16 +7230,16 @@
         <f>Штат!G39</f>
         <v>1</v>
       </c>
-      <c r="D9" s="14">
-        <v>1</v>
-      </c>
-      <c r="E9" s="14">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14">
-        <v>1</v>
-      </c>
-      <c r="G9" s="26">
+      <c r="D9" s="12">
+        <v>1</v>
+      </c>
+      <c r="E9" s="12">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
+        <v>1</v>
+      </c>
+      <c r="G9" s="19">
         <f>Штат!L39</f>
         <v>2.3548387096774195</v>
       </c>
@@ -7219,16 +7265,16 @@
         <f>Штат!G8</f>
         <v>1</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="12">
         <v>10</v>
       </c>
-      <c r="E10" s="14">
-        <v>0</v>
-      </c>
-      <c r="F10" s="14">
-        <v>1</v>
-      </c>
-      <c r="G10" s="26">
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>1</v>
+      </c>
+      <c r="G10" s="19">
         <f>Штат!L8</f>
         <v>2.3548387096774195</v>
       </c>
@@ -7253,16 +7299,16 @@
         <f>SUM(Штат!G9:G13)</f>
         <v>5</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="12">
         <v>3</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <v>3</v>
       </c>
-      <c r="F11" s="14">
-        <v>0</v>
-      </c>
-      <c r="G11" s="26">
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="19">
         <f>Штат!L10</f>
         <v>2.3548387096774195</v>
       </c>
@@ -7287,16 +7333,16 @@
         <f>SUM(Штат!G17:G26)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="12">
         <v>6</v>
       </c>
-      <c r="E12" s="14">
-        <v>0</v>
-      </c>
-      <c r="F12" s="14">
-        <v>0</v>
-      </c>
-      <c r="G12" s="26">
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="19">
         <f>Штат!L19</f>
         <v>2.3548387096774195</v>
       </c>
@@ -7321,16 +7367,16 @@
         <f>SUM(Штат!G14:G16)</f>
         <v>3</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="12">
         <v>3</v>
       </c>
-      <c r="E13" s="14">
-        <v>0</v>
-      </c>
-      <c r="F13" s="14">
-        <v>0</v>
-      </c>
-      <c r="G13" s="26">
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="G13" s="19">
         <f>Штат!L16</f>
         <v>0</v>
       </c>
@@ -7355,16 +7401,16 @@
         <f>SUM(Штат!G27:G28)</f>
         <v>1</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="14">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14">
-        <v>0</v>
-      </c>
-      <c r="G14" s="26">
+      <c r="D14" s="12">
+        <v>1</v>
+      </c>
+      <c r="E14" s="12">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12">
+        <v>0</v>
+      </c>
+      <c r="G14" s="19">
         <f>Штат!L27</f>
         <v>2.3548387096774195</v>
       </c>
@@ -7389,16 +7435,16 @@
         <f>SUM(Штат!G29:G36)</f>
         <v>4</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="12">
         <v>4</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="12">
         <v>4</v>
       </c>
-      <c r="F15" s="14">
-        <v>0</v>
-      </c>
-      <c r="G15" s="26">
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="19">
         <f>Штат!L29</f>
         <v>2.3548387096774195</v>
       </c>
@@ -7417,9 +7463,9 @@
     </row>
     <row r="16" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7431,9 +7477,9 @@
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7445,9 +7491,9 @@
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7459,9 +7505,9 @@
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7473,9 +7519,9 @@
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7487,9 +7533,9 @@
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7501,9 +7547,9 @@
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7515,9 +7561,9 @@
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7529,9 +7575,9 @@
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7543,9 +7589,9 @@
     </row>
     <row r="25" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
       <c r="I25" s="5">
         <f>C25*(D25/12*G25*Поездка_РК)</f>
         <v>0</v>
@@ -7556,21 +7602,21 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="9">
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="8">
         <f>SUM(I5:I25)</f>
         <v>7246775.9408602165</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="8">
         <f>SUM(J5:J25)</f>
         <v>37657517.125</v>
       </c>
@@ -7650,16 +7696,16 @@
       <c r="C5" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="12">
         <v>25</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="13">
         <v>450000</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="12">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -7684,16 +7730,16 @@
       <c r="C6" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <v>5</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="13">
         <v>900000</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -7718,16 +7764,16 @@
       <c r="C7" t="s">
         <v>148</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="12">
         <v>15</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="13">
         <v>100000</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="12">
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -7752,16 +7798,16 @@
       <c r="C8" t="s">
         <v>151</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <v>19</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="13">
         <v>200000</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="12">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
@@ -7786,16 +7832,16 @@
       <c r="C9" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <v>5</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="13">
         <v>500000</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="12">
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
@@ -7820,16 +7866,16 @@
       <c r="C10" t="s">
         <v>148</v>
       </c>
-      <c r="D10" s="14">
-        <v>1</v>
-      </c>
-      <c r="E10" s="15">
+      <c r="D10" s="12">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13">
         <v>800000</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="12">
         <v>1</v>
       </c>
       <c r="H10" s="4"/>
@@ -7852,16 +7898,16 @@
       <c r="C11" t="s">
         <v>148</v>
       </c>
-      <c r="D11" s="14">
-        <v>1</v>
-      </c>
-      <c r="E11" s="15">
+      <c r="D11" s="12">
+        <v>1</v>
+      </c>
+      <c r="E11" s="13">
         <v>500000</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="12">
         <v>1</v>
       </c>
       <c r="H11" s="4"/>
@@ -7884,16 +7930,16 @@
       <c r="C12" t="s">
         <v>148</v>
       </c>
-      <c r="D12" s="14">
-        <v>1</v>
-      </c>
-      <c r="E12" s="15">
+      <c r="D12" s="12">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13">
         <v>450000</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="12">
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -7918,16 +7964,16 @@
       <c r="C13" t="s">
         <v>142</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="12">
         <v>6</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="13">
         <v>60000</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="12">
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -7952,17 +7998,17 @@
       <c r="C14" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
+      <c r="D14" s="12">
+        <v>1</v>
+      </c>
+      <c r="E14" s="13">
         <f>(D8*E8+D9*E9+D10*E10+D11*E11+D12*E12+D13*E13)*Сборка_мебели_проц</f>
         <v>841000</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="12">
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -7987,16 +8033,16 @@
       <c r="C15" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
+      <c r="D15" s="12">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13">
         <v>2500000</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="12">
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -8021,16 +8067,16 @@
       <c r="C16" t="s">
         <v>148</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
+      <c r="D16" s="12">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13">
         <v>300000</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="12">
         <v>1</v>
       </c>
       <c r="H16" s="4"/>
@@ -8053,16 +8099,16 @@
       <c r="C17" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="12">
         <v>2</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="13">
         <v>280000</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="12">
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -8087,16 +8133,16 @@
       <c r="C18" t="s">
         <v>142</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="12">
         <v>4</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="13">
         <v>55000</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="12">
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -8121,16 +8167,16 @@
       <c r="C19" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="14">
-        <v>1</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="D19" s="12">
+        <v>1</v>
+      </c>
+      <c r="E19" s="13">
         <v>300000</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="12">
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -8155,17 +8201,17 @@
       <c r="C20" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="D20" s="12">
+        <v>1</v>
+      </c>
+      <c r="E20" s="13">
         <f>ROUND(42340/(1+НДС),0)</f>
         <v>36500</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="12">
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -8190,17 +8236,17 @@
       <c r="C21" t="s">
         <v>356</v>
       </c>
-      <c r="D21" s="14">
-        <v>1</v>
-      </c>
-      <c r="E21" s="15">
+      <c r="D21" s="12">
+        <v>1</v>
+      </c>
+      <c r="E21" s="13">
         <f>ROUND(6000/(1+НДС),0)</f>
         <v>5172</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="12">
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -8225,17 +8271,17 @@
       <c r="C22" t="s">
         <v>142</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
+      <c r="D22" s="12">
+        <v>1</v>
+      </c>
+      <c r="E22" s="13">
         <f>ROUND(114327/(1+НДС),0)</f>
         <v>98558</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="12">
         <v>1</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -8260,17 +8306,17 @@
       <c r="C23" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
+      <c r="D23" s="12">
+        <v>1</v>
+      </c>
+      <c r="E23" s="13">
         <f>ROUND((100*55+100*68+100*26+100*37+100*57+100*244)/(1+НДС),0)</f>
         <v>41983</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="12">
         <v>1</v>
       </c>
       <c r="H23" s="4" t="s">
@@ -8295,17 +8341,17 @@
       <c r="C24" t="s">
         <v>142</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="12">
         <v>31</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="13">
         <f>ROUND(4118/(1+НДС),0)</f>
         <v>3550</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="12">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -8330,17 +8376,17 @@
       <c r="C25" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="12">
         <v>5</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="13">
         <f>ROUND(6101/(1+НДС),0)</f>
         <v>5259</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="12">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -8365,17 +8411,17 @@
       <c r="C26" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="12">
         <v>4</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="13">
         <f>ROUND(7235/(1+НДС),0)</f>
         <v>6237</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="12">
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
@@ -8400,17 +8446,17 @@
       <c r="C27" t="s">
         <v>142</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="12">
         <v>5</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="13">
         <f>ROUND(9039/(1+НДС),0)</f>
         <v>7792</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="12">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -8435,16 +8481,16 @@
       <c r="C28" t="s">
         <v>142</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="D28" s="12">
+        <v>1</v>
+      </c>
+      <c r="E28" s="13">
         <v>450000</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="12">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -8469,17 +8515,17 @@
       <c r="C29" t="s">
         <v>142</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
+      <c r="D29" s="12">
+        <v>1</v>
+      </c>
+      <c r="E29" s="13">
         <f>ROUND(57852/(1+НДС),0)</f>
         <v>49872</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="12">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
@@ -8504,16 +8550,16 @@
       <c r="C30" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
+      <c r="D30" s="12">
+        <v>1</v>
+      </c>
+      <c r="E30" s="13">
         <v>300000</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="12">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -8538,16 +8584,16 @@
       <c r="C31" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
+      <c r="D31" s="12">
+        <v>1</v>
+      </c>
+      <c r="E31" s="13">
         <v>800000</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="12">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
@@ -8572,16 +8618,16 @@
       <c r="C32" t="s">
         <v>142</v>
       </c>
-      <c r="D32" s="14">
-        <v>1</v>
-      </c>
-      <c r="E32" s="15">
+      <c r="D32" s="12">
+        <v>1</v>
+      </c>
+      <c r="E32" s="13">
         <v>700000</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="12">
         <v>1</v>
       </c>
       <c r="H32" s="4"/>
@@ -8604,17 +8650,17 @@
       <c r="C33" t="s">
         <v>162</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
+      <c r="D33" s="12">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13">
         <f>'Смета фото-видео'!G35</f>
         <v>7062880</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="12">
         <v>1</v>
       </c>
       <c r="H33" s="4" t="s">
@@ -8639,16 +8685,16 @@
       <c r="C34" t="s">
         <v>148</v>
       </c>
-      <c r="D34" s="14">
-        <v>1</v>
-      </c>
-      <c r="E34" s="15">
+      <c r="D34" s="12">
+        <v>1</v>
+      </c>
+      <c r="E34" s="13">
         <v>400000</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="12">
         <v>1</v>
       </c>
       <c r="H34" s="4"/>
@@ -8671,16 +8717,16 @@
       <c r="C35" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="14">
-        <v>1</v>
-      </c>
-      <c r="E35" s="15">
+      <c r="D35" s="12">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13">
         <v>150000</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="12">
         <v>1</v>
       </c>
       <c r="H35" s="4"/>
@@ -8703,16 +8749,16 @@
       <c r="C36" t="s">
         <v>148</v>
       </c>
-      <c r="D36" s="14">
-        <v>1</v>
-      </c>
-      <c r="E36" s="15">
+      <c r="D36" s="12">
+        <v>1</v>
+      </c>
+      <c r="E36" s="13">
         <v>400000</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="12">
         <v>1</v>
       </c>
       <c r="H36" s="4"/>
@@ -8735,16 +8781,16 @@
       <c r="C37" t="s">
         <v>148</v>
       </c>
-      <c r="D37" s="14">
-        <v>1</v>
-      </c>
-      <c r="E37" s="15">
+      <c r="D37" s="12">
+        <v>1</v>
+      </c>
+      <c r="E37" s="13">
         <v>100000</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="12">
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
@@ -8769,17 +8815,17 @@
       <c r="C38" t="s">
         <v>170</v>
       </c>
-      <c r="D38" s="14">
-        <v>1</v>
-      </c>
-      <c r="E38" s="15">
+      <c r="D38" s="12">
+        <v>1</v>
+      </c>
+      <c r="E38" s="13">
         <f>Аренда_мес</f>
         <v>4955774.75</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G38" s="14">
+      <c r="G38" s="12">
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
@@ -8804,17 +8850,17 @@
       <c r="C39" t="s">
         <v>172</v>
       </c>
-      <c r="D39" s="14">
-        <v>1</v>
-      </c>
-      <c r="E39" s="15">
+      <c r="D39" s="12">
+        <v>1</v>
+      </c>
+      <c r="E39" s="13">
         <f>Аренда_мес*Депозит_мес</f>
         <v>4955774.75</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="12">
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
@@ -8839,16 +8885,16 @@
       <c r="C40" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="14">
-        <v>1</v>
-      </c>
-      <c r="E40" s="15">
+      <c r="D40" s="12">
+        <v>1</v>
+      </c>
+      <c r="E40" s="13">
         <v>3000000</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="12">
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
@@ -8873,16 +8919,16 @@
       <c r="C41" t="s">
         <v>170</v>
       </c>
-      <c r="D41" s="14">
-        <v>1</v>
-      </c>
-      <c r="E41" s="15">
+      <c r="D41" s="12">
+        <v>1</v>
+      </c>
+      <c r="E41" s="13">
         <v>50000</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="12">
         <v>1</v>
       </c>
       <c r="H41" s="4"/>
@@ -8905,16 +8951,16 @@
       <c r="C42" t="s">
         <v>170</v>
       </c>
-      <c r="D42" s="14">
-        <v>1</v>
-      </c>
-      <c r="E42" s="15">
+      <c r="D42" s="12">
+        <v>1</v>
+      </c>
+      <c r="E42" s="13">
         <v>60000</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="12">
         <v>1</v>
       </c>
       <c r="H42" s="4"/>
@@ -8937,16 +8983,16 @@
       <c r="C43" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="14">
-        <v>1</v>
-      </c>
-      <c r="E43" s="15">
+      <c r="D43" s="12">
+        <v>1</v>
+      </c>
+      <c r="E43" s="13">
         <v>50000</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="12">
         <v>1</v>
       </c>
       <c r="H43" s="4"/>
@@ -8969,16 +9015,16 @@
       <c r="C44" t="s">
         <v>180</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="12">
         <v>25</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="13">
         <v>5000</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="12">
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
@@ -9003,16 +9049,16 @@
       <c r="C45" t="s">
         <v>170</v>
       </c>
-      <c r="D45" s="14">
-        <v>1</v>
-      </c>
-      <c r="E45" s="15">
+      <c r="D45" s="12">
+        <v>1</v>
+      </c>
+      <c r="E45" s="13">
         <v>60000</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G45" s="14">
+      <c r="G45" s="12">
         <v>1</v>
       </c>
       <c r="H45" s="4"/>
@@ -9035,17 +9081,17 @@
       <c r="C46" t="s">
         <v>170</v>
       </c>
-      <c r="D46" s="14">
-        <v>1</v>
-      </c>
-      <c r="E46" s="15">
+      <c r="D46" s="12">
+        <v>1</v>
+      </c>
+      <c r="E46" s="13">
         <f>Канцелярия!F22</f>
         <v>240750</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G46" s="14">
+      <c r="G46" s="12">
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
@@ -9070,16 +9116,16 @@
       <c r="C47" t="s">
         <v>170</v>
       </c>
-      <c r="D47" s="14">
-        <v>0</v>
-      </c>
-      <c r="E47" s="15">
+      <c r="D47" s="12">
+        <v>0</v>
+      </c>
+      <c r="E47" s="13">
         <v>200000</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G47" s="14">
+      <c r="G47" s="12">
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
@@ -9104,16 +9150,16 @@
       <c r="C48" t="s">
         <v>170</v>
       </c>
-      <c r="D48" s="14">
-        <v>1</v>
-      </c>
-      <c r="E48" s="15">
+      <c r="D48" s="12">
+        <v>1</v>
+      </c>
+      <c r="E48" s="13">
         <v>150000</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G48" s="14">
+      <c r="G48" s="12">
         <v>1</v>
       </c>
       <c r="H48" s="4"/>
@@ -9136,16 +9182,16 @@
       <c r="C49" t="s">
         <v>170</v>
       </c>
-      <c r="D49" s="14">
-        <v>1</v>
-      </c>
-      <c r="E49" s="15">
+      <c r="D49" s="12">
+        <v>1</v>
+      </c>
+      <c r="E49" s="13">
         <v>100000</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G49" s="14">
+      <c r="G49" s="12">
         <v>1</v>
       </c>
       <c r="H49" s="4"/>
@@ -9168,16 +9214,16 @@
       <c r="C50" t="s">
         <v>188</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="12">
         <v>25</v>
       </c>
-      <c r="E50" s="15">
+      <c r="E50" s="13">
         <v>7000</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G50" s="14">
+      <c r="G50" s="12">
         <v>1</v>
       </c>
       <c r="H50" s="4" t="s">
@@ -9202,16 +9248,16 @@
       <c r="C51" t="s">
         <v>188</v>
       </c>
-      <c r="D51" s="14">
+      <c r="D51" s="12">
         <v>3</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="13">
         <v>7500</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G51" s="14">
+      <c r="G51" s="12">
         <v>1</v>
       </c>
       <c r="H51" s="4"/>
@@ -9234,16 +9280,16 @@
       <c r="C52" t="s">
         <v>191</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="12">
         <v>2</v>
       </c>
-      <c r="E52" s="15">
+      <c r="E52" s="13">
         <v>30000</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G52" s="14">
+      <c r="G52" s="12">
         <v>1</v>
       </c>
       <c r="H52" s="4" t="s">
@@ -9268,16 +9314,16 @@
       <c r="C53" t="s">
         <v>191</v>
       </c>
-      <c r="D53" s="14">
+      <c r="D53" s="12">
         <v>2</v>
       </c>
-      <c r="E53" s="15">
+      <c r="E53" s="13">
         <v>8000</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G53" s="14">
+      <c r="G53" s="12">
         <v>1</v>
       </c>
       <c r="H53" s="4"/>
@@ -9300,16 +9346,16 @@
       <c r="C54" t="s">
         <v>170</v>
       </c>
-      <c r="D54" s="14">
-        <v>1</v>
-      </c>
-      <c r="E54" s="15">
+      <c r="D54" s="12">
+        <v>1</v>
+      </c>
+      <c r="E54" s="13">
         <v>200000</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G54" s="14">
+      <c r="G54" s="12">
         <v>4</v>
       </c>
       <c r="H54" s="4" t="s">
@@ -9334,16 +9380,16 @@
       <c r="C55" t="s">
         <v>170</v>
       </c>
-      <c r="D55" s="14">
-        <v>1</v>
-      </c>
-      <c r="E55" s="15">
+      <c r="D55" s="12">
+        <v>1</v>
+      </c>
+      <c r="E55" s="13">
         <v>300000</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G55" s="14">
+      <c r="G55" s="12">
         <v>4</v>
       </c>
       <c r="H55" s="4" t="s">
@@ -9368,12 +9414,12 @@
       <c r="C56" t="s">
         <v>366</v>
       </c>
-      <c r="D56" s="14"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="14" t="s">
+      <c r="D56" s="12"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G56" s="14"/>
+      <c r="G56" s="12"/>
       <c r="H56" s="4"/>
       <c r="I56" s="5">
         <v>2000000</v>
@@ -9392,16 +9438,16 @@
       <c r="C57" t="s">
         <v>200</v>
       </c>
-      <c r="D57" s="14">
-        <v>1</v>
-      </c>
-      <c r="E57" s="15">
+      <c r="D57" s="12">
+        <v>1</v>
+      </c>
+      <c r="E57" s="13">
         <v>5000000</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F57" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="G57" s="14">
+      <c r="G57" s="12">
         <v>1</v>
       </c>
       <c r="H57" s="4"/>
@@ -9424,16 +9470,16 @@
       <c r="C58" t="s">
         <v>170</v>
       </c>
-      <c r="D58" s="14">
-        <v>1</v>
-      </c>
-      <c r="E58" s="15">
+      <c r="D58" s="12">
+        <v>1</v>
+      </c>
+      <c r="E58" s="13">
         <v>25000</v>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F58" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G58" s="14">
+      <c r="G58" s="12">
         <v>1</v>
       </c>
       <c r="H58" s="4"/>
@@ -9456,16 +9502,16 @@
       <c r="C59" t="s">
         <v>200</v>
       </c>
-      <c r="D59" s="14">
-        <v>0</v>
-      </c>
-      <c r="E59" s="15">
+      <c r="D59" s="12">
+        <v>0</v>
+      </c>
+      <c r="E59" s="13">
         <v>10000000</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="G59" s="14">
+      <c r="G59" s="12">
         <v>1</v>
       </c>
       <c r="H59" s="4" t="s">
@@ -9490,16 +9536,16 @@
       <c r="C60" t="s">
         <v>205</v>
       </c>
-      <c r="D60" s="14">
-        <v>1</v>
-      </c>
-      <c r="E60" s="15">
+      <c r="D60" s="12">
+        <v>1</v>
+      </c>
+      <c r="E60" s="13">
         <v>700000</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G60" s="14">
+      <c r="G60" s="12">
         <v>1</v>
       </c>
       <c r="H60" s="4" t="s">
@@ -9524,16 +9570,16 @@
       <c r="C61" t="s">
         <v>208</v>
       </c>
-      <c r="D61" s="14">
+      <c r="D61" s="12">
         <v>25</v>
       </c>
-      <c r="E61" s="15">
+      <c r="E61" s="13">
         <v>150000</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="G61" s="14">
+      <c r="G61" s="12">
         <v>1</v>
       </c>
       <c r="H61" s="4"/>
@@ -9556,16 +9602,16 @@
       <c r="C62" t="s">
         <v>200</v>
       </c>
-      <c r="D62" s="14">
-        <v>1</v>
-      </c>
-      <c r="E62" s="15">
+      <c r="D62" s="12">
+        <v>1</v>
+      </c>
+      <c r="E62" s="13">
         <v>2000000</v>
       </c>
-      <c r="F62" s="14" t="s">
+      <c r="F62" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="G62" s="14">
+      <c r="G62" s="12">
         <v>1</v>
       </c>
       <c r="H62" s="4"/>
@@ -9588,16 +9634,16 @@
       <c r="C63" t="s">
         <v>200</v>
       </c>
-      <c r="D63" s="14">
+      <c r="D63" s="12">
         <v>2</v>
       </c>
-      <c r="E63" s="15">
+      <c r="E63" s="13">
         <v>3000000</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="F63" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="G63" s="14">
+      <c r="G63" s="12">
         <v>0</v>
       </c>
       <c r="H63" s="4"/>
@@ -9618,16 +9664,16 @@
       <c r="C64" t="s">
         <v>200</v>
       </c>
-      <c r="D64" s="14">
-        <v>1</v>
-      </c>
-      <c r="E64" s="15">
+      <c r="D64" s="12">
+        <v>1</v>
+      </c>
+      <c r="E64" s="13">
         <v>500000</v>
       </c>
-      <c r="F64" s="14" t="s">
+      <c r="F64" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="G64" s="14">
+      <c r="G64" s="12">
         <v>1</v>
       </c>
       <c r="H64" s="4"/>
@@ -9650,16 +9696,16 @@
       <c r="C65" t="s">
         <v>200</v>
       </c>
-      <c r="D65" s="14">
-        <v>1</v>
-      </c>
-      <c r="E65" s="15">
+      <c r="D65" s="12">
+        <v>1</v>
+      </c>
+      <c r="E65" s="13">
         <v>150000</v>
       </c>
-      <c r="F65" s="14" t="s">
+      <c r="F65" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="G65" s="14">
+      <c r="G65" s="12">
         <v>1</v>
       </c>
       <c r="H65" s="4"/>
@@ -9683,7 +9729,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -9691,21 +9737,20 @@
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="7" width="10.7109375" customWidth="1"/>
-    <col min="8" max="8" width="55.7109375" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="15" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="13" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>134</v>
       </c>
@@ -9725,17 +9770,13 @@
         <v>137</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="J4" s="3">
+      <c r="H4" s="3">
         <v>2027</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>488</v>
       </c>
@@ -9745,21 +9786,19 @@
       <c r="C5" t="s">
         <v>366</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="14" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5">
+      <c r="G5" s="5">
         <v>6000000</v>
       </c>
-      <c r="J5" s="5">
+      <c r="H5" s="5">
         <v>12000000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>488</v>
       </c>
@@ -9769,21 +9808,19 @@
       <c r="C6" t="s">
         <v>366</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="14" t="s">
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5">
+      <c r="G6" s="5">
         <v>2000000</v>
       </c>
-      <c r="J6" s="5">
+      <c r="H6" s="5">
         <v>8000000</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>488</v>
       </c>
@@ -9793,21 +9830,19 @@
       <c r="C7" t="s">
         <v>366</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="14" t="s">
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5">
+      <c r="G7" s="5">
         <v>10000000</v>
       </c>
-      <c r="J7" s="5">
+      <c r="H7" s="5">
         <v>300000000</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>488</v>
       </c>
@@ -9817,21 +9852,19 @@
       <c r="C8" t="s">
         <v>366</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="14" t="s">
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
         <v>500000000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>488</v>
       </c>
@@ -9841,21 +9874,19 @@
       <c r="C9" t="s">
         <v>366</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="14" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
         <v>45000000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>488</v>
       </c>
@@ -9865,21 +9896,19 @@
       <c r="C10" t="s">
         <v>366</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="14" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
         <v>25000000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>488</v>
       </c>
@@ -9889,21 +9918,19 @@
       <c r="C11" t="s">
         <v>366</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="14" t="s">
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5">
+      <c r="G11" s="5">
         <v>30000000</v>
       </c>
-      <c r="J11" s="5">
+      <c r="H11" s="5">
         <v>120000000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>488</v>
       </c>
@@ -9913,21 +9940,19 @@
       <c r="C12" t="s">
         <v>366</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="14" t="s">
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="5">
+      <c r="G12" s="5">
         <v>15000000</v>
       </c>
-      <c r="J12" s="5">
+      <c r="H12" s="5">
         <v>120000000</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>488</v>
       </c>
@@ -9937,21 +9962,19 @@
       <c r="C13" t="s">
         <v>366</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="14" t="s">
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="5">
+      <c r="G13" s="5">
         <v>50000000</v>
       </c>
-      <c r="J13" s="5">
+      <c r="H13" s="5">
         <v>300000000</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>488</v>
       </c>
@@ -9961,44 +9984,53 @@
       <c r="C14" t="s">
         <v>366</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="14" t="s">
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="5">
+      <c r="G14" s="5">
         <v>100000000</v>
       </c>
-      <c r="J14" s="5">
+      <c r="H14" s="5">
         <v>100000000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="12" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
         <v>483</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="9">
-        <f>SUM(I5:I14)</f>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="8">
+        <f>SUM(G5:G14)</f>
         <v>213000000</v>
       </c>
-      <c r="J16" s="9">
-        <f>SUM(J5:J14)</f>
+      <c r="H16" s="8">
+        <f>SUM(H5:H14)</f>
         <v>1530000000</v>
       </c>
     </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="G18" s="65">
+        <f>G16+H16</f>
+        <v>1743000000</v>
+      </c>
+      <c r="H18" s="66"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G18:H18"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -10021,8 +10053,8 @@
     <col min="7" max="7" width="48.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>270</v>
       </c>
     </row>
@@ -10031,26 +10063,26 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>139</v>
       </c>
     </row>
@@ -10064,7 +10096,7 @@
       <c r="C5" t="s">
         <v>278</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="16">
         <v>7</v>
       </c>
       <c r="E5" s="5">
@@ -10088,7 +10120,7 @@
       <c r="C6" t="s">
         <v>278</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="16">
         <v>0.5</v>
       </c>
       <c r="E6" s="5">
@@ -10112,7 +10144,7 @@
       <c r="C7" t="s">
         <v>282</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="16">
         <v>1</v>
       </c>
       <c r="E7" s="5">
@@ -10136,7 +10168,7 @@
       <c r="C8" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="16">
         <v>0.5</v>
       </c>
       <c r="E8" s="5">
@@ -10160,7 +10192,7 @@
       <c r="C9" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="16">
         <v>20</v>
       </c>
       <c r="E9" s="5">
@@ -10184,7 +10216,7 @@
       <c r="C10" t="s">
         <v>148</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="16">
         <v>20</v>
       </c>
       <c r="E10" s="5">
@@ -10208,7 +10240,7 @@
       <c r="C11" t="s">
         <v>148</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="16">
         <v>10</v>
       </c>
       <c r="E11" s="5">
@@ -10232,7 +10264,7 @@
       <c r="C12" t="s">
         <v>148</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="16">
         <v>0.5</v>
       </c>
       <c r="E12" s="5">
@@ -10256,7 +10288,7 @@
       <c r="C13" t="s">
         <v>148</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="16">
         <v>1</v>
       </c>
       <c r="E13" s="5">
@@ -10280,7 +10312,7 @@
       <c r="C14" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="16">
         <v>0.5</v>
       </c>
       <c r="E14" s="5">
@@ -10301,7 +10333,7 @@
       <c r="C15" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="16">
         <v>1</v>
       </c>
       <c r="E15" s="5">
@@ -10325,7 +10357,7 @@
       <c r="C16" t="s">
         <v>148</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="16">
         <v>0.5</v>
       </c>
       <c r="E16" s="5">
@@ -10349,7 +10381,7 @@
       <c r="C17" t="s">
         <v>148</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="16">
         <v>0.2</v>
       </c>
       <c r="E17" s="5">
@@ -10373,7 +10405,7 @@
       <c r="C18" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="16">
         <v>1</v>
       </c>
       <c r="E18" s="5">
@@ -10397,7 +10429,7 @@
       <c r="C19" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="16">
         <v>0.2</v>
       </c>
       <c r="E19" s="5">
@@ -10418,7 +10450,7 @@
       <c r="C20" t="s">
         <v>308</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="16">
         <v>20</v>
       </c>
       <c r="E20" s="5">
@@ -10442,7 +10474,7 @@
       <c r="C21" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="16">
         <v>1</v>
       </c>
       <c r="E21" s="5">
@@ -10456,13 +10488,13 @@
         <v>311</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="12" t="s">
+    <row r="22" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="D22" s="52"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9">
+      <c r="D22" s="41"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8">
         <f>SUM(F5:F21)</f>
         <v>240750</v>
       </c>
@@ -10471,7 +10503,7 @@
       <c r="B23" t="s">
         <v>313</v>
       </c>
-      <c r="D23" s="18"/>
+      <c r="D23" s="16"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5">
         <f>F22*12</f>
@@ -10546,15 +10578,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -10821,15 +10853,15 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8">
         <f>SUM(G6:G16)</f>
         <v>5517890</v>
       </c>
@@ -10839,15 +10871,15 @@
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
@@ -10976,15 +11008,15 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12" t="s">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9">
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8">
         <f>SUM(G20:G25)</f>
         <v>970000</v>
       </c>
@@ -10994,15 +11026,15 @@
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
@@ -11089,15 +11121,15 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12" t="s">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9">
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8">
         <f>SUM(G29:G32)</f>
         <v>574990</v>
       </c>
@@ -11107,15 +11139,15 @@
       <c r="G34" s="5"/>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="16"/>
-      <c r="B35" s="16" t="s">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17">
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15">
         <f>G17+G26+G33</f>
         <v>7062880</v>
       </c>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" tabRatio="500" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" tabRatio="500" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Свод" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="567">
   <si>
     <t>Бюджет проектного офиса «Таза Қазақстан» (ЦАКФ) на октябрь–декабрь 2026 и 2027 год — СВОД, ₸</t>
   </si>
@@ -1405,9 +1405,6 @@
     <t>Стол совещаний на 12 — 2 (ноутбуки участников), ТВ и ВКС — 1, МФУ и сетевое оборудование — 1, кухонная зона — 1. b2bcompany.kz на 30.09.2026 — 6 101 ₸ с НДС (код 51417), в бюджете без НДС (÷1,16): https://b2bcompany.kz/catalog/ofisnaya_tekhnika_i_aksessuary/elektrotovary/setevye_filtry/51417/</t>
   </si>
   <si>
-    <t>6. Оснащение (разово): ноутбуки, мебель и стеллажи с их сборкой, МФУ А3 и 2 МФУ А4, ламинатор и переплётчик, удлинители (сетевые фильтры), фото-видео, сеть</t>
-  </si>
-  <si>
     <t>Мобильная стойка для ТВ на колёсах, 32–65″ (A-case AVA1500-60-1P)</t>
   </si>
   <si>
@@ -1435,45 +1432,12 @@
     <t>Прокладка удлинителей по полу через проходы от колонн к блокам столов и к столу совещаний — ≈10 м. Kaspi.kz (Астана) на 30.09.2026 — 9 039 ₸ с НДС за 2 м, в бюджете без НДС (÷1,16): https://kaspi.kz/shop/p/iek-kabel--kanal-profil-pvh-70h16h2000-mm-115737589/</t>
   </si>
   <si>
-    <t>Аренда — БЦ «Сыганак», ул. Сыганак, 70: 701–702 (7 этаж, аппарат ЦАКФ) + 316 (3 этаж, проектный офис)</t>
-  </si>
-  <si>
-    <t>Площадь к оплате, м²: 7 этаж — 701 (52,2) + 701а (21,4) + 701б (12,4) + 702 (33,7) = 119,7 по плану БЦ; 3 этаж — 316 (193, калькулятор БЦ); итого 312,7 + 10% мест общего пользования. Холл 14,4 м² не берём</t>
-  </si>
-  <si>
-    <t>Ставка аренды со скидкой, ₸ за 1 м² в месяц без НДС и без коммунальных (условия БЦ от 22.09.2026; для 316 — допущение, такие же)</t>
-  </si>
-  <si>
-    <t>Коммунальные, ₸ в месяц без НДС: ≈675 ₸/м² (ориентир БЦ 300 000 на 444,2 м²) × площадь к оплате; уточнить</t>
-  </si>
-  <si>
     <t>Парковка — 2 платных места (указание 30.09.2026)</t>
   </si>
   <si>
-    <t>Парковка, ₸ за 1 место в месяц без НДС — ориентир 40 000, уточнить у БЦ</t>
-  </si>
-  <si>
-    <t>Аренда офисов с коммунальными и парковкой, ₸ в месяц без НДС (БЦ «Сыганак», 701–702 + 316 — расчёт ниже)</t>
-  </si>
-  <si>
-    <t>БЦ «Сыганак»: 701–702 (7 этаж, 119,7 м²) + 316 (3 этаж, 193 м²) = 312,7 м² + 10% МОП = 344,0 м² × 13 500 ₸ + коммунальные ≈232 000 + парковка 2 × 40 000 = 4 955 775 ₸/мес без НДС (5 748 699 ₸ с НДС). Смета: D:\Аренда\Смета аренды — БЦ Сыганак, 701–702 (7 эт.) + 316 (3 эт.). В 2026 — с 21.10 (≈2,35 мес.)</t>
-  </si>
-  <si>
-    <t>оценка; уточнить после осмотра помещений 701–702 и 316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     в т.ч. аренда офисов (БЦ «Сыганак», 701–702 + 316, 344,0 м² к оплате — ставка 13 500, коммунальные, 2 парковочных места; в 2026 — с 21.10, ≈2,35 мес.)</t>
-  </si>
-  <si>
-    <t>Справка по аренде — БЦ «Сыганак»: 701–702 (7 этаж) + 316 (3 этаж), к оплате 344,0 м² (312,7 + 10% МОП):</t>
-  </si>
-  <si>
     <t>Аренда с коммунальными и парковкой, ₸ в месяц без НДС</t>
   </si>
   <si>
-    <t>Против варианта 444,2 м² (зона 710 + восточное крыло, 6 296 700 ₸/мес без НДС) — разница, ₸ в месяц (минус — дешевле)</t>
-  </si>
-  <si>
     <t>Против ориентира 5 000 000 ₸/мес без НДС — разница, ₸ в месяц (минус — укладываемся)</t>
   </si>
   <si>
@@ -1723,10 +1687,148 @@
     <t>Оклады — из штатки 01.10.2026 (обновлённый должностной оклад); состав — по структуре 01.10.2026: 30 человек (Фонд с экспертной группой — 9, проектный офис — 21). Выход: с 21.10.2026 — 18, с 01.2027 — 1 (Ахантаева), с 02.2027 — 11 (в т.ч. экспертная группа и Абулхан). Строки с количеством 0 — аутсорс.</t>
   </si>
   <si>
-    <t>Проект от 07.10.2026 (v13). Штат — по структуре и штатке 01.10.2026: 30 человек (Фонд с экспертной группой — 9, проектный офис — 21); с 21.10.2026 — 18, с 01.2027 — 1 (Ахантаева), с 02.2027 — 11 (в т.ч. экспертная группа и Абулхан); аутсорс — 7 позиций, расчёт — на листе «Аутсорс», в бюджете. Аренда — БЦ «Сыганак», ул. Сыганак, 70: аппарат ЦАКФ — 701–702 (7 этаж, 119,7 м²), проектный офис — 316 (3 этаж, 193 м²); к оплате 344,0 м² (+10% общих зон), 2 платных парковочных места; в 2026 — с 21.10. Проекты и мероприятия — по статьям проектного офиса, однотипные объединены, — на листе «Проекты (вне бюджета)», в ИТОГО не входят. В оснащении — ламинатор, переплётчик, сетевые фильтры, удлинители, кабель-канал, стойка для ТВ. Суммы пересчитываются от листов «Параметры», «Штат», «Командировки», «Оснащение и офис», «Канцелярия», «Смета фото-видео».</t>
-  </si>
-  <si>
     <t>ВСЕГО за 2026-27 гг.:</t>
+  </si>
+  <si>
+    <t>Ставка аренды со скидкой, ₸ за 1 м² в месяц без НДС и без коммунальных (условия БЦ от 22.09.2026)</t>
+  </si>
+  <si>
+    <t>Парковка, ₸ за 1 место в месяц без НДС – 40 000, уточнено у БЦ</t>
+  </si>
+  <si>
+    <t>Аренда – БЦ «Сыганак», ул. Сыганак, 70, 7 этаж: 701–702 + зона 710</t>
+  </si>
+  <si>
+    <t>Площадь к оплате, м²: 701 (52,2) + 701а (21,4) + 701б (12,4) + 702 (33,7) = 119,7 по плану БЦ; зона 710 – 190,0 по экспликации БЦ; итого 309,7 полезной + 10% мест общего пользования</t>
+  </si>
+  <si>
+    <t>Коммунальные, ₸ в месяц без НДС: 743 ₸/м² × 309,7 м² полезной площади (без МОП); ориентир, уточнить у БЦ</t>
+  </si>
+  <si>
+    <t>Аренда офисов с коммунальными и парковкой, ₸ в месяц без НДС (БЦ «Сыганак», 7 этаж: 701–702 + зона 710 – расчёт ниже)</t>
+  </si>
+  <si>
+    <t>БЦ «Сыганак», 7 этаж: 701–702 (119,7 м²) + зона 710 (190,0) = 309,7 м² + 10% МОП = 340,7 м² × 13 500 ₸ + коммунальные 743 ₸/м² полезной (≈230 100) + парковка 2 × 40 000 = 4 909 152 ₸/мес без НДС (5 694 616 ₸ с НДС). Смета: D:\Аренда\Смета аренды — БЦ Сыганак, 701–702 + зона 710 (7 эт.) (проект 2026-10-08).xlsx. В 2026 – с 21.10 (≈2,35 мес.)</t>
+  </si>
+  <si>
+    <t>оценка; уточнить после осмотра помещений (701–702, 710)</t>
+  </si>
+  <si>
+    <t>Проект от 10.10.2026 (v15-1). Штат — по структуре и штатке 01.10.2026: 30 человек (Фонд с экспертной группой — 9, проектный офис — 21); с 21.10.2026 — 18, с 01.2027 — 1 (Ахантаева), с 02.2027 — 11 (в т.ч. экспертная группа и Абулхан); аутсорс — 7 позиций, расчёт — на листе «Аутсорс», в бюджете. Аренда – вариант 1: БЦ «Сыганак», ул. Сыганак, 70, 7 этаж: 701–702 (119,7 м²) и зона 710 (190,0 м²); к оплате 340,7 м² (+10% общих зон), 2 платных парковочных места; в 2026 – с 21.10. Проекты и мероприятия — по статьям проектного офиса, однотипные объединены, — на листе «Проекты (вне бюджета)», в ИТОГО не входят. В оснащении — ламинатор, переплётчик, сетевые фильтры, удлинители, кабель-канал, стойка для ТВ, источники бесперебойного питания (10 шт.). Суммы пересчитываются от листов «Параметры», «Штат», «Командировки», «Оснащение и офис», «Канцелярия», «Смета фото-видео».</t>
+  </si>
+  <si>
+    <t>6. Оснащение (разово): ноутбуки, мебель и стеллажи с их сборкой, МФУ А3 и 2 МФУ А4, ламинатор и переплётчик, удлинители (сетевые фильтры), ИБП (10 шт.), фото-видео, сеть</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     в т.ч. аренда офисов (БЦ «Сыганак», 7 этаж: 701–702 + зона 710, 340,7 м² к оплате – ставка 13 500, коммунальные, 2 парковочных места; в 2026 – с 21.10, ≈2,35 мес.)</t>
+  </si>
+  <si>
+    <t>Справка по аренде – вариант 1, БЦ «Сыганак», 7 этаж: 701–702 + зона 710:</t>
+  </si>
+  <si>
+    <t>Против варианта 2 – БЦ «Лазурный», 6 этаж (9 856 200 ₸/мес без НДС) – разница, ₸ в месяц (минус – дешевле)</t>
+  </si>
+  <si>
+    <t>Источник бесперебойного питания 1200 ВА / 650 Вт, линейно-интерактивный (APC Back-UPS BX1200MI-GR)</t>
+  </si>
+  <si>
+    <t>Kaspi.kz (Астана) на 10.10.2026 – 89 302 ₸ с НДС, в бюджете без НДС (÷1,16): https://kaspi.kz/shop/p/istochnik-bespereboinogo-pitanija-apc-by-schneider-electric-back-ups-bx1200mi-gr-101092827/ ; у b2bcompany.kz ИБП нет</t>
+  </si>
+  <si>
+    <t>Сравнение вариантов аренды: вариант 1 – БЦ «Сыганак» (701–702 + 710), вариант 2 – БЦ «Лазурный» (6 этаж)</t>
+  </si>
+  <si>
+    <t>Показатель</t>
+  </si>
+  <si>
+    <t>Вариант 1 – БЦ «Сыганак»</t>
+  </si>
+  <si>
+    <t>Вариант 2 – БЦ «Лазурный»</t>
+  </si>
+  <si>
+    <t>Помещения</t>
+  </si>
+  <si>
+    <t>7 этаж: 701, 701а, 701б, 702 + зона 710 (10 помещений)</t>
+  </si>
+  <si>
+    <t>6 этаж целиком: open space, 3 зала, кабинет, подсобные</t>
+  </si>
+  <si>
+    <t>Полезная площадь, м²</t>
+  </si>
+  <si>
+    <t>Площадь к оплате, м²</t>
+  </si>
+  <si>
+    <t>Полезной площади на 1 рабочее место (37 мест: 30 штат + 7 аутсорс), м²</t>
+  </si>
+  <si>
+    <t>Ставка, ₸ за м² в месяц без НДС</t>
+  </si>
+  <si>
+    <t>Коммунальные, ₸ в месяц без НДС</t>
+  </si>
+  <si>
+    <t>в ставке</t>
+  </si>
+  <si>
+    <t>Парковка, ₸ в месяц без НДС</t>
+  </si>
+  <si>
+    <t>5 мест, условия уточнить</t>
+  </si>
+  <si>
+    <t>Аренда в месяц без НДС, ₸</t>
+  </si>
+  <si>
+    <t>Аренда в месяц с НДС 16%, ₸</t>
+  </si>
+  <si>
+    <t>Аренда в год с НДС, ₸</t>
+  </si>
+  <si>
+    <t>Против ориентира 5 000 000 ₸/мес без НДС, ₸</t>
+  </si>
+  <si>
+    <t>Аренда в бюджете: октябрь–декабрь 2026 (с 21.10), ₸ без НДС</t>
+  </si>
+  <si>
+    <t>Аренда в бюджете: 2027, ₸ без НДС</t>
+  </si>
+  <si>
+    <t>Гарантийный депозит (1 месяц, возвратный), ₸</t>
+  </si>
+  <si>
+    <t>ИТОГО бюджета с НДС, октябрь–декабрь 2026, ₸</t>
+  </si>
+  <si>
+    <t>ИТОГО бюджета с НДС, 2027, ₸</t>
+  </si>
+  <si>
+    <t>ИТОГО бюджета с НДС, 3 мес. 2026 + 2027, ₸</t>
+  </si>
+  <si>
+    <t>Пояснения к сравнению:</t>
+  </si>
+  <si>
+    <t>1. Вариант 1 дешевле: аренда – на 4,9 млн ₸ в месяц без НДС; бюджет с НДС, резервом и депозитом – на 21,2 млн в 2026, на 75,7 млн в 2027, всего на 96,9 млн ₸.</t>
+  </si>
+  <si>
+    <t>2. Вариант 1 укладывается в ориентир 5 млн ₸/мес без НДС (запас ≈0,09 млн); вариант 2 – выше ориентира почти вдвое (+4,86 млн в месяц).</t>
+  </si>
+  <si>
+    <t>3. Вариант 1 – весь офис на одном 7 этаже, кабинеты под руководство уже есть (702, 701а, 710/3, 710/6), переговорная на 12. Площадь впритык: 8,4 м² полезной на место при норме ≈10; в 2026 (18 человек) – свободно, с 2027 (37 мест) – плотно, резерва под рост нет. Коммунальные и парковка – сверх ставки.</t>
+  </si>
+  <si>
+    <t>4. Вариант 2 – целый этаж, 12,7 м² полезной на место, запас под рост и под мероприятия (зал 93 м²); коммунальные, клининг и охрана – в ставке, 5 парковочных мест. Но платим и за центральный холл (коэффициент 1,4), кабинетов почти нет – под ГИД, заместителей, координатора и бухгалтерию нужны перегородки: в бюджете на ремонт в обоих вариантах 3 млн ₸, для «Лазурного» сумма – после осмотра и сметы.</t>
+  </si>
+  <si>
+    <t>5. Условия «Лазурного» по депозиту и стоимости парковки не известны – в расчёте депозит 1 месяц, парковка без оплаты. ИБП (10 шт., 0,8 млн ₸ без НДС) включены в оснащение в обоих вариантах.</t>
+  </si>
+  <si>
+    <t>Разница (2 – 1)</t>
   </si>
 </sst>
 </file>
@@ -1737,7 +1839,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.####"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1831,8 +1933,16 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1875,8 +1985,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9DDEB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1936,11 +2058,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2085,6 +2222,54 @@
     </xf>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2356,11 +2541,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.7109375" style="4" customWidth="1"/>
-    <col min="2" max="4" width="19.7109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="4" customWidth="1"/>
+    <col min="3" max="4" width="17.7109375" style="4" customWidth="1"/>
     <col min="5" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
@@ -2371,7 +2557,7 @@
     </row>
     <row r="2" spans="1:4" ht="210" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -2445,7 +2631,7 @@
     </row>
     <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="B9" s="49">
         <f>Аутсорс!K11</f>
@@ -2513,14 +2699,14 @@
     </row>
     <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>425</v>
+        <v>529</v>
       </c>
       <c r="B13" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I180,'Оснащение и офис'!A5:A180,"Оснащение")</f>
-        <v>41176218</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Оснащение")</f>
+        <v>41946058</v>
       </c>
       <c r="C13" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J180,'Оснащение и офис'!A5:A180,"Оснащение")</f>
+        <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Оснащение")</f>
         <v>0</v>
       </c>
       <c r="D13" s="50"/>
@@ -2530,33 +2716,33 @@
         <v>8</v>
       </c>
       <c r="B14" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I180,'Оснащение и офис'!A5:A180,"Офис")</f>
-        <v>22133074.967741936</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Офис")</f>
+        <v>21976663.496774193</v>
       </c>
       <c r="C14" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J180,'Оснащение и офис'!A5:A180,"Офис")</f>
-        <v>69498297</v>
+        <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Офис")</f>
+        <v>68938825.199999988</v>
       </c>
       <c r="D14" s="50">
         <f>C14/12</f>
-        <v>5791524.75</v>
+        <v>5744902.0999999987</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>444</v>
+        <v>530</v>
       </c>
       <c r="B15" s="51">
-        <f>'Оснащение и офис'!I38</f>
-        <v>11670050.217741936</v>
+        <f>'Оснащение и офис'!I39</f>
+        <v>11560261.396774193</v>
       </c>
       <c r="C15" s="51">
-        <f>'Оснащение и офис'!J38</f>
-        <v>59469297</v>
+        <f>'Оснащение и офис'!J39</f>
+        <v>58909825.199999996</v>
       </c>
       <c r="D15" s="51">
         <f>C15/12</f>
-        <v>4955774.75</v>
+        <v>4909152.0999999996</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2564,25 +2750,25 @@
         <v>337</v>
       </c>
       <c r="B16" s="51">
-        <f>'Оснащение и офис'!I39</f>
-        <v>4955774.75</v>
+        <f>'Оснащение и офис'!I40</f>
+        <v>4909152.0999999996</v>
       </c>
       <c r="C16" s="51">
-        <f>'Оснащение и офис'!J39</f>
+        <f>'Оснащение и офис'!J40</f>
         <v>0</v>
       </c>
       <c r="D16" s="51"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="B17" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I180,'Оснащение и офис'!A5:A180,"Цифровые")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Цифровые")</f>
         <v>820500</v>
       </c>
       <c r="C17" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J180,'Оснащение и офис'!A5:A180,"Цифровые")</f>
+        <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Цифровые")</f>
         <v>9282000</v>
       </c>
       <c r="D17" s="50">
@@ -2595,11 +2781,11 @@
         <v>369</v>
       </c>
       <c r="B18" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I180,'Оснащение и офис'!A5:A180,"Медиа")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Медиа")</f>
         <v>3325000</v>
       </c>
       <c r="C18" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J180,'Оснащение и офис'!A5:A180,"Медиа")</f>
+        <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Медиа")</f>
         <v>25300000</v>
       </c>
       <c r="D18" s="50">
@@ -2609,7 +2795,7 @@
     </row>
     <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="45" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="B19" s="52">
         <f>'Проекты (вне бюджета)'!G16</f>
@@ -2635,11 +2821,11 @@
         <v>9</v>
       </c>
       <c r="B20" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I180,'Оснащение и офис'!A5:A180,"Прочие")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Прочие")</f>
         <v>5300000</v>
       </c>
       <c r="C20" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J180,'Оснащение и офис'!A5:A180,"Прочие")</f>
+        <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Прочие")</f>
         <v>9400000</v>
       </c>
       <c r="D20" s="50">
@@ -2653,15 +2839,15 @@
       </c>
       <c r="B21" s="55">
         <f>B8+B9+B10+B11+B12+B13+B14+B17+B18+B20</f>
-        <v>178506118.58602151</v>
+        <v>179119547.11505377</v>
       </c>
       <c r="C21" s="55">
         <f>C8+C9+C10+C11+C12+C13+C14+C17+C18+C20</f>
-        <v>797536800.79166663</v>
+        <v>796977328.99166656</v>
       </c>
       <c r="D21" s="56">
         <f t="shared" si="0"/>
-        <v>66461400.065972216</v>
+        <v>66414777.41597221</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -2670,15 +2856,15 @@
       </c>
       <c r="B22" s="49">
         <f>B21*Резерв</f>
-        <v>17850611.858602151</v>
+        <v>17911954.71150538</v>
       </c>
       <c r="C22" s="49">
         <f>C21*Резерв</f>
-        <v>79753680.079166666</v>
+        <v>79697732.899166659</v>
       </c>
       <c r="D22" s="50">
         <f t="shared" si="0"/>
-        <v>6646140.0065972218</v>
+        <v>6641477.7415972212</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -2687,15 +2873,15 @@
       </c>
       <c r="B23" s="57">
         <f>B21+B22</f>
-        <v>196356730.44462365</v>
+        <v>197031501.82655916</v>
       </c>
       <c r="C23" s="57">
         <f>C21+C22</f>
-        <v>877290480.87083328</v>
+        <v>876675061.89083326</v>
       </c>
       <c r="D23" s="58">
         <f t="shared" si="0"/>
-        <v>73107540.072569445</v>
+        <v>73056255.157569438</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -2704,15 +2890,15 @@
       </c>
       <c r="B24" s="49">
         <f>B23*НДС</f>
-        <v>31417076.871139783</v>
+        <v>31525040.292249467</v>
       </c>
       <c r="C24" s="49">
         <f>C23*НДС</f>
-        <v>140366476.93933332</v>
+        <v>140268009.90253332</v>
       </c>
       <c r="D24" s="50">
         <f t="shared" si="0"/>
-        <v>11697206.41161111</v>
+        <v>11689000.82521111</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -2721,15 +2907,15 @@
       </c>
       <c r="B25" s="59">
         <f>B23+B24</f>
-        <v>227773807.31576344</v>
+        <v>228556542.11880863</v>
       </c>
       <c r="C25" s="60">
         <f>C23+C24</f>
-        <v>1017656957.8101666</v>
+        <v>1016943071.7933666</v>
       </c>
       <c r="D25" s="56">
         <f t="shared" si="0"/>
-        <v>84804746.484180555</v>
+        <v>84745255.982780546</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -2739,16 +2925,16 @@
       <c r="B26" s="61"/>
       <c r="C26" s="62">
         <f>B25+C25</f>
-        <v>1245430765.1259301</v>
+        <v>1245499613.9121752</v>
       </c>
       <c r="D26" s="48"/>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="40" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="C27" s="64">
         <f>B19+C19</f>
@@ -2776,66 +2962,66 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:2" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B34" s="49">
         <f>Аренда_мес</f>
-        <v>4955774.75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4909152.0999999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>316</v>
       </c>
       <c r="B35" s="55">
         <f>Аренда_с_НДС</f>
-        <v>5748698.71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5694616.4359999988</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>317</v>
       </c>
       <c r="B36" s="49">
         <f>Аренда_депозит</f>
-        <v>4955774.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>4909152.0999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>447</v>
+        <v>532</v>
       </c>
       <c r="B37" s="49">
-        <f>Аренда_мес-6296700</f>
-        <v>-1340925.25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <f>Аренда_мес-9856200</f>
+        <v>-4947047.9000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="B38" s="49">
         <f>Аренда_мес-5000000</f>
-        <v>-44225.25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>-90847.900000000373</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="B39" s="49">
         <f>(5000000-Коммун_мес-Парковка_мест*Парковка_цена)/Площадь_офиса</f>
-        <v>13628.572986016221</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13766.674200839523</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>342</v>
       </c>
@@ -2844,7 +3030,7 @@
         <v>360000</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>343</v>
       </c>
@@ -2853,7 +3039,7 @@
         <v>841000</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>318</v>
       </c>
@@ -2862,7 +3048,7 @@
         <v>240750</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>362</v>
       </c>
@@ -2871,7 +3057,324 @@
         <v>182213</v>
       </c>
     </row>
+    <row r="45" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="65" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="66" t="s">
+        <v>536</v>
+      </c>
+      <c r="B46" s="75" t="s">
+        <v>537</v>
+      </c>
+      <c r="C46" s="67" t="s">
+        <v>538</v>
+      </c>
+      <c r="D46" s="67" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A47" s="68" t="s">
+        <v>539</v>
+      </c>
+      <c r="B47" s="76" t="s">
+        <v>540</v>
+      </c>
+      <c r="C47" s="74" t="s">
+        <v>541</v>
+      </c>
+      <c r="D47" s="69"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="68" t="s">
+        <v>542</v>
+      </c>
+      <c r="B48" s="77">
+        <v>309.7</v>
+      </c>
+      <c r="C48" s="70">
+        <v>469.34</v>
+      </c>
+      <c r="D48" s="70">
+        <f>C48-B48</f>
+        <v>159.63999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="68" t="s">
+        <v>543</v>
+      </c>
+      <c r="B49" s="77">
+        <v>340.67</v>
+      </c>
+      <c r="C49" s="70">
+        <v>657.08</v>
+      </c>
+      <c r="D49" s="70">
+        <f>C49-B49</f>
+        <v>316.41000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="68" t="s">
+        <v>544</v>
+      </c>
+      <c r="B50" s="77">
+        <v>8.3702702702702698</v>
+      </c>
+      <c r="C50" s="70">
+        <v>12.684864864864901</v>
+      </c>
+      <c r="D50" s="70">
+        <f>C50-B50</f>
+        <v>4.3145945945946309</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="68" t="s">
+        <v>545</v>
+      </c>
+      <c r="B51" s="78">
+        <v>13500</v>
+      </c>
+      <c r="C51" s="71">
+        <v>15000</v>
+      </c>
+      <c r="D51" s="71">
+        <f>C51-B51</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="68" t="s">
+        <v>546</v>
+      </c>
+      <c r="B52" s="78">
+        <v>230107.1</v>
+      </c>
+      <c r="C52" s="71" t="s">
+        <v>547</v>
+      </c>
+      <c r="D52" s="71"/>
+    </row>
+    <row r="53" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="68" t="s">
+        <v>548</v>
+      </c>
+      <c r="B53" s="78">
+        <v>80000</v>
+      </c>
+      <c r="C53" s="71" t="s">
+        <v>549</v>
+      </c>
+      <c r="D53" s="71"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="68" t="s">
+        <v>550</v>
+      </c>
+      <c r="B54" s="78">
+        <v>4909152.0999999996</v>
+      </c>
+      <c r="C54" s="71">
+        <v>9856200</v>
+      </c>
+      <c r="D54" s="71">
+        <f t="shared" ref="D54:D63" si="1">C54-B54</f>
+        <v>4947047.9000000004</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="68" t="s">
+        <v>551</v>
+      </c>
+      <c r="B55" s="78">
+        <v>5694616.4359999998</v>
+      </c>
+      <c r="C55" s="71">
+        <v>11433192</v>
+      </c>
+      <c r="D55" s="71">
+        <f t="shared" si="1"/>
+        <v>5738575.5640000002</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="B56" s="78">
+        <v>68335397.231999993</v>
+      </c>
+      <c r="C56" s="71">
+        <v>137198304</v>
+      </c>
+      <c r="D56" s="71">
+        <f t="shared" si="1"/>
+        <v>68862906.768000007</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="68" t="s">
+        <v>553</v>
+      </c>
+      <c r="B57" s="78">
+        <v>-90847.900000000402</v>
+      </c>
+      <c r="C57" s="71">
+        <v>4856200</v>
+      </c>
+      <c r="D57" s="71">
+        <f t="shared" si="1"/>
+        <v>4947047.9000000004</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="68" t="s">
+        <v>554</v>
+      </c>
+      <c r="B58" s="78">
+        <v>11560261.396774201</v>
+      </c>
+      <c r="C58" s="71">
+        <v>23209761.290322602</v>
+      </c>
+      <c r="D58" s="71">
+        <f t="shared" si="1"/>
+        <v>11649499.893548401</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="68" t="s">
+        <v>555</v>
+      </c>
+      <c r="B59" s="78">
+        <v>58909825.200000003</v>
+      </c>
+      <c r="C59" s="71">
+        <v>118274400</v>
+      </c>
+      <c r="D59" s="71">
+        <f t="shared" si="1"/>
+        <v>59364574.799999997</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="68" t="s">
+        <v>556</v>
+      </c>
+      <c r="B60" s="78">
+        <v>4909152.0999999996</v>
+      </c>
+      <c r="C60" s="71">
+        <v>9856200</v>
+      </c>
+      <c r="D60" s="71">
+        <f t="shared" si="1"/>
+        <v>4947047.9000000004</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="72" t="s">
+        <v>557</v>
+      </c>
+      <c r="B61" s="79">
+        <v>228556542.11880901</v>
+      </c>
+      <c r="C61" s="73">
+        <v>249733737.103376</v>
+      </c>
+      <c r="D61" s="73">
+        <f t="shared" si="1"/>
+        <v>21177194.984566987</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="72" t="s">
+        <v>558</v>
+      </c>
+      <c r="B62" s="79">
+        <v>1016943071.79337</v>
+      </c>
+      <c r="C62" s="73">
+        <v>1092692269.2381699</v>
+      </c>
+      <c r="D62" s="73">
+        <f t="shared" si="1"/>
+        <v>75749197.4447999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="72" t="s">
+        <v>559</v>
+      </c>
+      <c r="B63" s="79">
+        <v>1245499613.9121799</v>
+      </c>
+      <c r="C63" s="73">
+        <v>1342426006.3415401</v>
+      </c>
+      <c r="D63" s="73">
+        <f t="shared" si="1"/>
+        <v>96926392.429360151</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="80" t="s">
+        <v>561</v>
+      </c>
+      <c r="B66" s="80"/>
+      <c r="C66" s="80"/>
+      <c r="D66" s="80"/>
+    </row>
+    <row r="67" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="80" t="s">
+        <v>562</v>
+      </c>
+      <c r="B67" s="80"/>
+      <c r="C67" s="80"/>
+      <c r="D67" s="80"/>
+    </row>
+    <row r="68" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="80" t="s">
+        <v>563</v>
+      </c>
+      <c r="B68" s="80"/>
+      <c r="C68" s="80"/>
+      <c r="D68" s="80"/>
+    </row>
+    <row r="69" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="80" t="s">
+        <v>564</v>
+      </c>
+      <c r="B69" s="80"/>
+      <c r="C69" s="80"/>
+      <c r="D69" s="80"/>
+    </row>
+    <row r="70" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="80" t="s">
+        <v>565</v>
+      </c>
+      <c r="B70" s="80"/>
+      <c r="C70" s="80"/>
+      <c r="D70" s="80"/>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -3245,10 +3748,10 @@
       </c>
       <c r="B34" s="11">
         <f>Площадь_офиса*Ставка_аренды_м2+Коммун_мес+Парковка_мест*Парковка_цена</f>
-        <v>4955774.75</v>
+        <v>4909152.0999999996</v>
       </c>
       <c r="C34" t="s">
-        <v>441</v>
+        <v>525</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3343,7 +3846,7 @@
     </row>
     <row r="47" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>435</v>
+        <v>522</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -3351,11 +3854,11 @@
         <v>254</v>
       </c>
       <c r="B48" s="16">
-        <f>ROUND((52.2+21.4+12.4+33.7+193)*1.1,2)</f>
-        <v>343.97</v>
+        <f>ROUND((52.2+21.4+12.4+33.7+190)*1.1,2)</f>
+        <v>340.67</v>
       </c>
       <c r="C48" t="s">
-        <v>436</v>
+        <v>523</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -3366,7 +3869,7 @@
         <v>13500</v>
       </c>
       <c r="C49" t="s">
-        <v>437</v>
+        <v>520</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -3374,11 +3877,11 @@
         <v>330</v>
       </c>
       <c r="B50" s="5">
-        <f>ROUND(300000/444.2,0)*Площадь_офиса</f>
-        <v>232179.75000000003</v>
+        <f>743*309.7</f>
+        <v>230107.1</v>
       </c>
       <c r="C50" t="s">
-        <v>438</v>
+        <v>524</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -3389,7 +3892,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -3400,7 +3903,7 @@
         <v>40000</v>
       </c>
       <c r="C52" t="s">
-        <v>440</v>
+        <v>521</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -3409,7 +3912,7 @@
       </c>
       <c r="B53" s="5">
         <f>Аренда_мес*(1+НДС)</f>
-        <v>5748698.71</v>
+        <v>5694616.4359999988</v>
       </c>
       <c r="C53" t="s">
         <v>259</v>
@@ -3421,7 +3924,7 @@
       </c>
       <c r="B54" s="5">
         <f>Аренда_мес*Депозит_мес</f>
-        <v>4955774.75</v>
+        <v>4909152.0999999996</v>
       </c>
       <c r="C54" t="s">
         <v>261</v>
@@ -3492,12 +3995,12 @@
   <sheetData>
     <row r="1" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3574,10 +4077,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>116</v>
@@ -3654,10 +4157,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>119</v>
@@ -3726,7 +4229,7 @@
         <v>25742720</v>
       </c>
       <c r="V6" s="20" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3734,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>412</v>
@@ -3817,7 +4320,7 @@
         <v>326</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>119</v>
@@ -3886,7 +4389,7 @@
         <v>25742720</v>
       </c>
       <c r="V8" s="20" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3900,7 +4403,7 @@
         <v>375</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="E9" s="24" t="s">
         <v>117</v>
@@ -4126,7 +4629,7 @@
         <v>17039733.333333332</v>
       </c>
       <c r="V11" s="24" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4206,7 +4709,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V12" s="24" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4286,7 +4789,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V13" s="24" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4294,13 +4797,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>117</v>
@@ -4366,7 +4869,7 @@
         <v>21958053.333333332</v>
       </c>
       <c r="V14" s="24" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4374,13 +4877,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>414</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>117</v>
@@ -4446,7 +4949,7 @@
         <v>13760853.333333334</v>
       </c>
       <c r="V15" s="24" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4454,13 +4957,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>413</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="E16" s="24" t="s">
         <v>117</v>
@@ -4526,7 +5029,7 @@
         <v>13760853.333333334</v>
       </c>
       <c r="V16" s="24" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4540,7 +5043,7 @@
         <v>384</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="E17" s="24" t="s">
         <v>117</v>
@@ -4606,7 +5109,7 @@
         <v>21958053.333333332</v>
       </c>
       <c r="V17" s="24" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4617,7 +5120,7 @@
         <v>383</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>386</v>
@@ -4686,7 +5189,7 @@
         <v>20377280</v>
       </c>
       <c r="V18" s="20" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4846,7 +5349,7 @@
         <v>17039733.333333332</v>
       </c>
       <c r="V20" s="24" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5166,7 +5669,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V24" s="24" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5246,7 +5749,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V25" s="24" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5326,7 +5829,7 @@
         <v>13760853.333333334</v>
       </c>
       <c r="V26" s="24" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5340,7 +5843,7 @@
         <v>375</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="E27" s="20" t="s">
         <v>117</v>
@@ -5417,7 +5920,7 @@
         <v>392</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="D28" s="29" t="s">
         <v>378</v>
@@ -5486,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="28" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5500,7 +6003,7 @@
         <v>396</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="E29" s="20" t="s">
         <v>117</v>
@@ -5726,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="28" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5806,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="28" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5886,7 +6389,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="28" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6126,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="28" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6134,7 +6637,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>121</v>
@@ -6214,7 +6717,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>122</v>
@@ -6294,13 +6797,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>117</v>
@@ -6366,7 +6869,7 @@
         <v>22165760</v>
       </c>
       <c r="V39" s="20" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6374,10 +6877,10 @@
         <v>36</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="D40" s="29" t="s">
         <v>325</v>
@@ -6446,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="28" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6454,10 +6957,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="D41" s="29" t="s">
         <v>325</v>
@@ -6526,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="28" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6590,7 +7093,7 @@
     </row>
     <row r="43" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="G43">
         <f>SUM(G8:G13)+SUM(G17:G36)</f>
@@ -6603,7 +7106,7 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="G44">
         <f>SUM(G5:G7)+SUM(G14:G16)+SUM(G37:G41)</f>
@@ -6640,7 +7143,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -6654,16 +7157,16 @@
         <v>99</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>104</v>
@@ -6686,13 +7189,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C4" s="35" t="s">
         <v>325</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="E4" s="36">
         <v>1000000</v>
@@ -6730,13 +7233,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>325</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="E5" s="36">
         <v>700000</v>
@@ -6774,13 +7277,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="E6" s="36">
         <v>1000000</v>
@@ -6818,13 +7321,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="E7" s="36">
         <v>1000000</v>
@@ -6862,13 +7365,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="E8" s="36">
         <v>700000</v>
@@ -6906,13 +7409,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="E9" s="36">
         <v>700000</v>
@@ -6950,13 +7453,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="E10" s="36">
         <v>700000</v>
@@ -6992,7 +7495,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="38"/>
       <c r="B11" s="38" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
@@ -7293,7 +7796,7 @@
     </row>
     <row r="11" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G9:G13)</f>
@@ -7327,7 +7830,7 @@
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="C12">
         <f>SUM(Штат!G17:G26)</f>
@@ -7361,7 +7864,7 @@
     </row>
     <row r="13" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="C13">
         <f>SUM(Штат!G14:G16)</f>
@@ -7395,7 +7898,7 @@
     </row>
     <row r="14" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C14">
         <f>SUM(Штат!G27:G28)</f>
@@ -7632,7 +8135,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7712,11 +8215,11 @@
         <v>144</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I37" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
+        <f t="shared" ref="I5:I38" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
         <v>11250000</v>
       </c>
       <c r="J5" s="5">
-        <f t="shared" ref="J5:J36" si="1">IF(F5="разово",IF(AND(G5&gt;3,G5&lt;=15),D5*E5,0),IF(F5="мес",D5*E5*MAX(0,MIN(12,16-MAX(G5,4))),D5*E5*MAX(0,MIN(12,16-MAX(G5,4)))/12))</f>
+        <f t="shared" ref="J5:J37" si="1">IF(F5="разово",IF(AND(G5&gt;3,G5&lt;=15),D5*E5,0),IF(F5="мес",D5*E5*MAX(0,MIN(12,16-MAX(G5,4))),D5*E5*MAX(0,MIN(12,16-MAX(G5,4)))/12))</f>
         <v>0</v>
       </c>
     </row>
@@ -7827,7 +8330,7 @@
         <v>140</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="C9" t="s">
         <v>148</v>
@@ -8336,7 +8839,7 @@
         <v>140</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C24" t="s">
         <v>142</v>
@@ -8355,7 +8858,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -8406,7 +8909,7 @@
         <v>140</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C26" t="s">
         <v>142</v>
@@ -8425,7 +8928,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -8441,7 +8944,7 @@
         <v>140</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C27" t="s">
         <v>142</v>
@@ -8460,7 +8963,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -8476,16 +8979,17 @@
         <v>140</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>156</v>
+        <v>533</v>
       </c>
       <c r="C28" t="s">
         <v>142</v>
       </c>
       <c r="D28" s="12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E28" s="13">
-        <v>450000</v>
+        <f>ROUND(89302/(1+НДС),0)</f>
+        <v>76984</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>143</v>
@@ -8494,14 +8998,14 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>428</v>
+        <v>534</v>
       </c>
       <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>450000</v>
+        <f t="shared" ref="I28" si="2">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
+        <v>769840</v>
       </c>
       <c r="J28" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J28" si="3">IF(F28="разово",IF(AND(G28&gt;3,G28&lt;=15),D28*E28,0),IF(F28="мес",D28*E28*MAX(0,MIN(12,16-MAX(G28,4))),D28*E28*MAX(0,MIN(12,16-MAX(G28,4)))/12))</f>
         <v>0</v>
       </c>
     </row>
@@ -8510,7 +9014,7 @@
         <v>140</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>426</v>
+        <v>156</v>
       </c>
       <c r="C29" t="s">
         <v>142</v>
@@ -8519,8 +9023,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="13">
-        <f>ROUND(57852/(1+НДС),0)</f>
-        <v>49872</v>
+        <v>450000</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>143</v>
@@ -8533,7 +9036,7 @@
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>49872</v>
+        <v>450000</v>
       </c>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
@@ -8545,16 +9048,17 @@
         <v>140</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>157</v>
+        <v>425</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D30" s="12">
         <v>1</v>
       </c>
       <c r="E30" s="13">
-        <v>300000</v>
+        <f>ROUND(57852/(1+НДС),0)</f>
+        <v>49872</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>143</v>
@@ -8563,11 +9067,11 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>158</v>
+        <v>426</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>49872</v>
       </c>
       <c r="J30" s="5">
         <f t="shared" si="1"/>
@@ -8579,7 +9083,7 @@
         <v>140</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C31" t="s">
         <v>148</v>
@@ -8588,7 +9092,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="13">
-        <v>800000</v>
+        <v>300000</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>143</v>
@@ -8597,11 +9101,11 @@
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>800000</v>
+        <v>300000</v>
       </c>
       <c r="J31" s="5">
         <f t="shared" si="1"/>
@@ -8613,16 +9117,16 @@
         <v>140</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D32" s="12">
         <v>1</v>
       </c>
       <c r="E32" s="13">
-        <v>700000</v>
+        <v>800000</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>143</v>
@@ -8630,77 +9134,79 @@
       <c r="G32" s="12">
         <v>1</v>
       </c>
-      <c r="H32" s="4"/>
+      <c r="H32" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
-        <v>700000</v>
+        <v>800000</v>
       </c>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>140</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" s="12">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13">
+        <v>700000</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G33" s="12">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>700000</v>
+      </c>
+      <c r="J33" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>162</v>
       </c>
-      <c r="D33" s="12">
-        <v>1</v>
-      </c>
-      <c r="E33" s="13">
+      <c r="D34" s="12">
+        <v>1</v>
+      </c>
+      <c r="E34" s="13">
         <f>'Смета фото-видео'!G35</f>
         <v>7062880</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F34" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G33" s="12">
-        <v>1</v>
-      </c>
-      <c r="H33" s="4" t="s">
+      <c r="G34" s="12">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I34" s="5">
         <f t="shared" si="0"/>
         <v>7062880</v>
-      </c>
-      <c r="J33" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>140</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C34" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" s="12">
-        <v>1</v>
-      </c>
-      <c r="E34" s="13">
-        <v>400000</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="G34" s="12">
-        <v>1</v>
-      </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>400000</v>
       </c>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
@@ -8712,7 +9218,7 @@
         <v>140</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C35" t="s">
         <v>148</v>
@@ -8721,7 +9227,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="13">
-        <v>150000</v>
+        <v>400000</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>143</v>
@@ -8732,7 +9238,7 @@
       <c r="H35" s="4"/>
       <c r="I35" s="5">
         <f t="shared" si="0"/>
-        <v>150000</v>
+        <v>400000</v>
       </c>
       <c r="J35" s="5">
         <f t="shared" si="1"/>
@@ -8744,7 +9250,7 @@
         <v>140</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C36" t="s">
         <v>148</v>
@@ -8753,7 +9259,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="13">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>143</v>
@@ -8764,7 +9270,7 @@
       <c r="H36" s="4"/>
       <c r="I36" s="5">
         <f t="shared" si="0"/>
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="J36" s="5">
         <f t="shared" si="1"/>
@@ -8776,7 +9282,7 @@
         <v>140</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
         <v>148</v>
@@ -8785,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="13">
-        <v>100000</v>
+        <v>400000</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>143</v>
@@ -8793,103 +9299,101 @@
       <c r="G37" s="12">
         <v>1</v>
       </c>
-      <c r="H37" s="4" t="s">
-        <v>443</v>
-      </c>
+      <c r="H37" s="4"/>
       <c r="I37" s="5">
         <f t="shared" si="0"/>
+        <v>400000</v>
+      </c>
+      <c r="J37" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="12">
+        <v>1</v>
+      </c>
+      <c r="E38" s="13">
         <v>100000</v>
       </c>
-      <c r="J37" s="5">
-        <f t="shared" ref="J37:J65" si="2">IF(F37="разово",IF(AND(G37&gt;3,G37&lt;=15),D37*E37,0),IF(F37="мес",D37*E37*MAX(0,MIN(12,16-MAX(G37,4))),D37*E37*MAX(0,MIN(12,16-MAX(G37,4)))/12))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>168</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C38" t="s">
-        <v>170</v>
-      </c>
-      <c r="D38" s="12">
-        <v>1</v>
-      </c>
-      <c r="E38" s="13">
-        <f>Аренда_мес</f>
-        <v>4955774.75</v>
-      </c>
       <c r="F38" s="12" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="G38" s="12">
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>442</v>
+        <v>527</v>
       </c>
       <c r="I38" s="5">
-        <f>D38*E38*Аренда_мес_2026</f>
-        <v>11670050.217741936</v>
+        <f t="shared" si="0"/>
+        <v>100000</v>
       </c>
       <c r="J38" s="5">
-        <f t="shared" si="2"/>
-        <v>59469297</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="J38:J66" si="4">IF(F38="разово",IF(AND(G38&gt;3,G38&lt;=15),D38*E38,0),IF(F38="мес",D38*E38*MAX(0,MIN(12,16-MAX(G38,4))),D38*E38*MAX(0,MIN(12,16-MAX(G38,4)))/12))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>168</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>335</v>
+        <v>169</v>
       </c>
       <c r="C39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D39" s="12">
         <v>1</v>
       </c>
       <c r="E39" s="13">
-        <f>Аренда_мес*Депозит_мес</f>
-        <v>4955774.75</v>
+        <f>Аренда_мес</f>
+        <v>4909152.0999999996</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="G39" s="12">
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>421</v>
+        <v>526</v>
       </c>
       <c r="I39" s="5">
-        <f t="shared" ref="I39:I65" si="3">IF(F39="разово",IF(G39&lt;=3,D39*E39,0),IF(F39="мес",D39*E39*MAX(0,4-G39),D39*E39*MAX(0,4-G39)/12))</f>
-        <v>4955774.75</v>
+        <f>D39*E39*Аренда_мес_2026</f>
+        <v>11560261.396774193</v>
       </c>
       <c r="J39" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>58909825.199999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>168</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>173</v>
+        <v>335</v>
       </c>
       <c r="C40" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D40" s="12">
         <v>1</v>
       </c>
       <c r="E40" s="13">
-        <v>3000000</v>
+        <f>Аренда_мес*Депозит_мес</f>
+        <v>4909152.0999999996</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>143</v>
@@ -8898,47 +9402,49 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>175</v>
+        <v>421</v>
       </c>
       <c r="I40" s="5">
-        <f t="shared" si="3"/>
-        <v>3000000</v>
+        <f t="shared" ref="I40:I66" si="5">IF(F40="разово",IF(G40&lt;=3,D40*E40,0),IF(F40="мес",D40*E40*MAX(0,4-G40),D40*E40*MAX(0,4-G40)/12))</f>
+        <v>4909152.0999999996</v>
       </c>
       <c r="J40" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>168</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C41" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D41" s="12">
         <v>1</v>
       </c>
       <c r="E41" s="13">
-        <v>50000</v>
+        <v>3000000</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
       </c>
-      <c r="H41" s="4"/>
+      <c r="H41" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="I41" s="5">
-        <f t="shared" si="3"/>
-        <v>150000</v>
+        <f t="shared" si="5"/>
+        <v>3000000</v>
       </c>
       <c r="J41" s="5">
-        <f t="shared" si="2"/>
-        <v>600000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8946,7 +9452,7 @@
         <v>168</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C42" t="s">
         <v>170</v>
@@ -8955,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="13">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>171</v>
@@ -8965,12 +9471,12 @@
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="5">
-        <f t="shared" si="3"/>
-        <v>180000</v>
+        <f t="shared" si="5"/>
+        <v>150000</v>
       </c>
       <c r="J42" s="5">
-        <f t="shared" si="2"/>
-        <v>720000</v>
+        <f t="shared" si="4"/>
+        <v>600000</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8978,7 +9484,7 @@
         <v>168</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C43" t="s">
         <v>170</v>
@@ -8987,7 +9493,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="13">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>171</v>
@@ -8997,12 +9503,12 @@
       </c>
       <c r="H43" s="4"/>
       <c r="I43" s="5">
-        <f t="shared" si="3"/>
-        <v>150000</v>
+        <f t="shared" si="5"/>
+        <v>180000</v>
       </c>
       <c r="J43" s="5">
-        <f t="shared" si="2"/>
-        <v>600000</v>
+        <f t="shared" si="4"/>
+        <v>720000</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9010,16 +9516,16 @@
         <v>168</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C44" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D44" s="12">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E44" s="13">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>171</v>
@@ -9027,16 +9533,14 @@
       <c r="G44" s="12">
         <v>1</v>
       </c>
-      <c r="H44" s="4" t="s">
-        <v>181</v>
-      </c>
+      <c r="H44" s="4"/>
       <c r="I44" s="5">
-        <f t="shared" si="3"/>
-        <v>375000</v>
+        <f t="shared" si="5"/>
+        <v>150000</v>
       </c>
       <c r="J44" s="5">
-        <f t="shared" si="2"/>
-        <v>1500000</v>
+        <f t="shared" si="4"/>
+        <v>600000</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9044,16 +9548,16 @@
         <v>168</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D45" s="12">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E45" s="13">
-        <v>60000</v>
+        <v>5000</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>171</v>
@@ -9061,14 +9565,16 @@
       <c r="G45" s="12">
         <v>1</v>
       </c>
-      <c r="H45" s="4"/>
+      <c r="H45" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="I45" s="5">
-        <f t="shared" si="3"/>
-        <v>180000</v>
+        <f t="shared" si="5"/>
+        <v>375000</v>
       </c>
       <c r="J45" s="5">
-        <f t="shared" si="2"/>
-        <v>720000</v>
+        <f t="shared" si="4"/>
+        <v>1500000</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9076,7 +9582,7 @@
         <v>168</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>315</v>
+        <v>182</v>
       </c>
       <c r="C46" t="s">
         <v>170</v>
@@ -9085,8 +9591,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="13">
-        <f>Канцелярия!F22</f>
-        <v>240750</v>
+        <v>60000</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>171</v>
@@ -9094,16 +9599,14 @@
       <c r="G46" s="12">
         <v>1</v>
       </c>
-      <c r="H46" s="4" t="s">
-        <v>336</v>
-      </c>
+      <c r="H46" s="4"/>
       <c r="I46" s="5">
-        <f t="shared" si="3"/>
-        <v>722250</v>
+        <f t="shared" si="5"/>
+        <v>180000</v>
       </c>
       <c r="J46" s="5">
-        <f t="shared" si="2"/>
-        <v>2889000</v>
+        <f t="shared" si="4"/>
+        <v>720000</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9111,16 +9614,17 @@
         <v>168</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>183</v>
+        <v>315</v>
       </c>
       <c r="C47" t="s">
         <v>170</v>
       </c>
       <c r="D47" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="13">
-        <v>200000</v>
+        <f>Канцелярия!F22</f>
+        <v>240750</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>171</v>
@@ -9129,15 +9633,15 @@
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>420</v>
+        <v>336</v>
       </c>
       <c r="I47" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>722250</v>
       </c>
       <c r="J47" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>2889000</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9145,16 +9649,16 @@
         <v>168</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C48" t="s">
         <v>170</v>
       </c>
       <c r="D48" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="13">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>171</v>
@@ -9162,14 +9666,16 @@
       <c r="G48" s="12">
         <v>1</v>
       </c>
-      <c r="H48" s="4"/>
+      <c r="H48" s="4" t="s">
+        <v>420</v>
+      </c>
       <c r="I48" s="5">
-        <f t="shared" si="3"/>
-        <v>450000</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="J48" s="5">
-        <f t="shared" si="2"/>
-        <v>1800000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9177,7 +9683,7 @@
         <v>168</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C49" t="s">
         <v>170</v>
@@ -9186,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="13">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>171</v>
@@ -9196,29 +9702,29 @@
       </c>
       <c r="H49" s="4"/>
       <c r="I49" s="5">
-        <f t="shared" si="3"/>
-        <v>300000</v>
+        <f t="shared" si="5"/>
+        <v>450000</v>
       </c>
       <c r="J49" s="5">
-        <f t="shared" si="2"/>
-        <v>1200000</v>
+        <f t="shared" si="4"/>
+        <v>1800000</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C50" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D50" s="12">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E50" s="13">
-        <v>7000</v>
+        <v>100000</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>171</v>
@@ -9226,16 +9732,14 @@
       <c r="G50" s="12">
         <v>1</v>
       </c>
-      <c r="H50" s="4" t="s">
-        <v>181</v>
-      </c>
+      <c r="H50" s="4"/>
       <c r="I50" s="5">
-        <f t="shared" si="3"/>
-        <v>525000</v>
+        <f t="shared" si="5"/>
+        <v>300000</v>
       </c>
       <c r="J50" s="5">
-        <f t="shared" si="2"/>
-        <v>2100000</v>
+        <f t="shared" si="4"/>
+        <v>1200000</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9243,16 +9747,16 @@
         <v>186</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C51" t="s">
         <v>188</v>
       </c>
       <c r="D51" s="12">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E51" s="13">
-        <v>7500</v>
+        <v>7000</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>171</v>
@@ -9260,14 +9764,16 @@
       <c r="G51" s="12">
         <v>1</v>
       </c>
-      <c r="H51" s="4"/>
+      <c r="H51" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="I51" s="5">
-        <f t="shared" si="3"/>
-        <v>67500</v>
+        <f t="shared" si="5"/>
+        <v>525000</v>
       </c>
       <c r="J51" s="5">
-        <f t="shared" si="2"/>
-        <v>270000</v>
+        <f t="shared" si="4"/>
+        <v>2100000</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9275,16 +9781,16 @@
         <v>186</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C52" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D52" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="13">
-        <v>30000</v>
+        <v>7500</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>171</v>
@@ -9292,16 +9798,14 @@
       <c r="G52" s="12">
         <v>1</v>
       </c>
-      <c r="H52" s="4" t="s">
-        <v>192</v>
-      </c>
+      <c r="H52" s="4"/>
       <c r="I52" s="5">
-        <f t="shared" si="3"/>
-        <v>180000</v>
+        <f t="shared" si="5"/>
+        <v>67500</v>
       </c>
       <c r="J52" s="5">
-        <f t="shared" si="2"/>
-        <v>720000</v>
+        <f t="shared" si="4"/>
+        <v>270000</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9309,7 +9813,7 @@
         <v>186</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C53" t="s">
         <v>191</v>
@@ -9318,7 +9822,7 @@
         <v>2</v>
       </c>
       <c r="E53" s="13">
-        <v>8000</v>
+        <v>30000</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>171</v>
@@ -9326,14 +9830,16 @@
       <c r="G53" s="12">
         <v>1</v>
       </c>
-      <c r="H53" s="4"/>
+      <c r="H53" s="4" t="s">
+        <v>192</v>
+      </c>
       <c r="I53" s="5">
-        <f t="shared" si="3"/>
-        <v>48000</v>
+        <f t="shared" si="5"/>
+        <v>180000</v>
       </c>
       <c r="J53" s="5">
-        <f t="shared" si="2"/>
-        <v>192000</v>
+        <f t="shared" si="4"/>
+        <v>720000</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9341,33 +9847,31 @@
         <v>186</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C54" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="D54" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="13">
-        <v>200000</v>
+        <v>8000</v>
       </c>
       <c r="F54" s="12" t="s">
         <v>171</v>
       </c>
       <c r="G54" s="12">
-        <v>4</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>195</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H54" s="4"/>
       <c r="I54" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>48000</v>
       </c>
       <c r="J54" s="5">
-        <f t="shared" si="2"/>
-        <v>2400000</v>
+        <f t="shared" si="4"/>
+        <v>192000</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9375,7 +9879,7 @@
         <v>186</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C55" t="s">
         <v>170</v>
@@ -9384,7 +9888,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="13">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="F55" s="12" t="s">
         <v>171</v>
@@ -9393,39 +9897,49 @@
         <v>4</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I55" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J55" s="5">
-        <f t="shared" si="2"/>
-        <v>3600000</v>
+        <f t="shared" si="4"/>
+        <v>2400000</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>526</v>
+        <v>196</v>
       </c>
       <c r="C56" t="s">
-        <v>366</v>
-      </c>
-      <c r="D56" s="12"/>
-      <c r="E56" s="13"/>
+        <v>170</v>
+      </c>
+      <c r="D56" s="12">
+        <v>1</v>
+      </c>
+      <c r="E56" s="13">
+        <v>300000</v>
+      </c>
       <c r="F56" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="G56" s="12"/>
-      <c r="H56" s="4"/>
+        <v>171</v>
+      </c>
+      <c r="G56" s="12">
+        <v>4</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>197</v>
+      </c>
       <c r="I56" s="5">
-        <v>2000000</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="J56" s="5">
-        <v>20000000</v>
+        <f t="shared" si="4"/>
+        <v>3600000</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9433,31 +9947,23 @@
         <v>198</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>199</v>
+        <v>514</v>
       </c>
       <c r="C57" t="s">
-        <v>200</v>
-      </c>
-      <c r="D57" s="12">
-        <v>1</v>
-      </c>
-      <c r="E57" s="13">
-        <v>5000000</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="D57" s="12"/>
+      <c r="E57" s="13"/>
       <c r="F57" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="G57" s="12">
-        <v>1</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="G57" s="12"/>
       <c r="H57" s="4"/>
       <c r="I57" s="5">
-        <f t="shared" si="3"/>
-        <v>1250000</v>
+        <v>2000000</v>
       </c>
       <c r="J57" s="5">
-        <f t="shared" si="2"/>
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9465,31 +9971,31 @@
         <v>198</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C58" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="D58" s="12">
         <v>1</v>
       </c>
       <c r="E58" s="13">
-        <v>25000</v>
+        <v>5000000</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="G58" s="12">
         <v>1</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="5">
-        <f t="shared" si="3"/>
-        <v>75000</v>
+        <f t="shared" si="5"/>
+        <v>1250000</v>
       </c>
       <c r="J58" s="5">
-        <f t="shared" si="2"/>
-        <v>300000</v>
+        <f t="shared" si="4"/>
+        <v>5000000</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9497,66 +10003,64 @@
         <v>198</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C59" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="D59" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="13">
-        <v>10000000</v>
+        <v>25000</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
       </c>
-      <c r="H59" s="4" t="s">
-        <v>364</v>
-      </c>
+      <c r="H59" s="4"/>
       <c r="I59" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>75000</v>
       </c>
       <c r="J59" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>300000</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C60" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D60" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="13">
-        <v>700000</v>
+        <v>10000000</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="G60" s="12">
         <v>1</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>206</v>
+        <v>364</v>
       </c>
       <c r="I60" s="5">
-        <f t="shared" si="3"/>
-        <v>700000</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="J60" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9565,31 +10069,33 @@
         <v>203</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C61" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D61" s="12">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E61" s="13">
-        <v>150000</v>
+        <v>700000</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
       </c>
-      <c r="H61" s="4"/>
+      <c r="H61" s="4" t="s">
+        <v>206</v>
+      </c>
       <c r="I61" s="5">
-        <f t="shared" si="3"/>
-        <v>937500</v>
+        <f t="shared" si="5"/>
+        <v>700000</v>
       </c>
       <c r="J61" s="5">
-        <f t="shared" si="2"/>
-        <v>3750000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9597,16 +10103,16 @@
         <v>203</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C62" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D62" s="12">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E62" s="13">
-        <v>2000000</v>
+        <v>150000</v>
       </c>
       <c r="F62" s="12" t="s">
         <v>200</v>
@@ -9616,12 +10122,12 @@
       </c>
       <c r="H62" s="4"/>
       <c r="I62" s="5">
-        <f t="shared" si="3"/>
-        <v>500000</v>
+        <f t="shared" si="5"/>
+        <v>937500</v>
       </c>
       <c r="J62" s="5">
-        <f t="shared" si="2"/>
-        <v>2000000</v>
+        <f t="shared" si="4"/>
+        <v>3750000</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9629,29 +10135,31 @@
         <v>203</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C63" t="s">
         <v>200</v>
       </c>
       <c r="D63" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="13">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>200</v>
       </c>
       <c r="G63" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="5">
-        <v>3000000</v>
+        <f t="shared" si="5"/>
+        <v>500000</v>
       </c>
       <c r="J63" s="5">
-        <v>3000000</v>
+        <f t="shared" si="4"/>
+        <v>2000000</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9659,31 +10167,29 @@
         <v>203</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C64" t="s">
         <v>200</v>
       </c>
       <c r="D64" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="13">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="F64" s="12" t="s">
         <v>200</v>
       </c>
       <c r="G64" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="5">
-        <f t="shared" si="3"/>
-        <v>125000</v>
+        <v>3000000</v>
       </c>
       <c r="J64" s="5">
-        <f t="shared" si="2"/>
-        <v>500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9691,7 +10197,7 @@
         <v>203</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C65" t="s">
         <v>200</v>
@@ -9700,7 +10206,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="13">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>200</v>
@@ -9710,11 +10216,43 @@
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
+        <v>125000</v>
+      </c>
+      <c r="J65" s="5">
+        <f t="shared" si="4"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>203</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C66" t="s">
+        <v>200</v>
+      </c>
+      <c r="D66" s="12">
+        <v>1</v>
+      </c>
+      <c r="E66" s="13">
+        <v>150000</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G66" s="12">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="5">
+        <f t="shared" si="5"/>
         <v>37500</v>
       </c>
-      <c r="J65" s="5">
-        <f t="shared" si="2"/>
+      <c r="J66" s="5">
+        <f t="shared" si="4"/>
         <v>150000</v>
       </c>
     </row>
@@ -9744,7 +10282,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -9778,10 +10316,10 @@
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="C5" t="s">
         <v>366</v>
@@ -9800,7 +10338,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>370</v>
@@ -9822,10 +10360,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="C7" t="s">
         <v>366</v>
@@ -9844,7 +10382,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>371</v>
@@ -9866,7 +10404,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>372</v>
@@ -9888,7 +10426,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>368</v>
@@ -9910,10 +10448,10 @@
     </row>
     <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C11" t="s">
         <v>366</v>
@@ -9932,7 +10470,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>367</v>
@@ -9954,7 +10492,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>373</v>
@@ -9976,7 +10514,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>365</v>
@@ -10002,7 +10540,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -10019,13 +10557,13 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>532</v>
-      </c>
-      <c r="G18" s="65">
+        <v>519</v>
+      </c>
+      <c r="G18" s="81">
         <f>G16+H16</f>
         <v>1743000000</v>
       </c>
-      <c r="H18" s="66"/>
+      <c r="H18" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10107,7 +10645,7 @@
         <v>21000</v>
       </c>
       <c r="G5" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" tabRatio="500" firstSheet="3" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Свод" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="566">
   <si>
     <t>Бюджет проектного офиса «Таза Қазақстан» (ЦАКФ) на октябрь–декабрь 2026 и 2027 год — СВОД, ₸</t>
   </si>
@@ -142,12 +142,6 @@
     <t>В среднем в месяц 2027</t>
   </si>
   <si>
-    <t>Штатная численность, чел.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  из них нанять (новые позиции), чел.</t>
-  </si>
-  <si>
     <t>4. ДМС и ОСНС штатных сотрудников</t>
   </si>
   <si>
@@ -1570,9 +1564,6 @@
     <t>Информационное сопровождение, в т.ч. презентация проектного офиса, пресс-мероприятия, мобильный брендинг</t>
   </si>
   <si>
-    <t>Проекты и мероприятия, не вошедшие в бюджет (по статьям проектного офиса), ₸ — в ИТОГО свода не входят</t>
-  </si>
-  <si>
     <t>10. Проекты и мероприятия по статьям проектного офиса (лист «Проекты (вне бюджета)») — в ИТОГО не входят</t>
   </si>
   <si>
@@ -1714,9 +1705,6 @@
     <t>оценка; уточнить после осмотра помещений (701–702, 710)</t>
   </si>
   <si>
-    <t>Проект от 10.10.2026 (v15-1). Штат — по структуре и штатке 01.10.2026: 30 человек (Фонд с экспертной группой — 9, проектный офис — 21); с 21.10.2026 — 18, с 01.2027 — 1 (Ахантаева), с 02.2027 — 11 (в т.ч. экспертная группа и Абулхан); аутсорс — 7 позиций, расчёт — на листе «Аутсорс», в бюджете. Аренда – вариант 1: БЦ «Сыганак», ул. Сыганак, 70, 7 этаж: 701–702 (119,7 м²) и зона 710 (190,0 м²); к оплате 340,7 м² (+10% общих зон), 2 платных парковочных места; в 2026 – с 21.10. Проекты и мероприятия — по статьям проектного офиса, однотипные объединены, — на листе «Проекты (вне бюджета)», в ИТОГО не входят. В оснащении — ламинатор, переплётчик, сетевые фильтры, удлинители, кабель-канал, стойка для ТВ, источники бесперебойного питания (10 шт.). Суммы пересчитываются от листов «Параметры», «Штат», «Командировки», «Оснащение и офис», «Канцелярия», «Смета фото-видео».</t>
-  </si>
-  <si>
     <t>6. Оснащение (разово): ноутбуки, мебель и стеллажи с их сборкой, МФУ А3 и 2 МФУ А4, ламинатор и переплётчик, удлинители (сетевые фильтры), ИБП (10 шт.), фото-видео, сеть</t>
   </si>
   <si>
@@ -1829,6 +1817,15 @@
   </si>
   <si>
     <t>Разница (2 – 1)</t>
+  </si>
+  <si>
+    <t>Проекты и мероприятия, не вошедшие в бюджет (по статьям проектного офиса), ₸ - в ИТОГО свода не входят</t>
+  </si>
+  <si>
+    <t>Штатная численность на конец периода, чел.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  из них нанять в периоде (новые позиции), чел.</t>
   </si>
 </sst>
 </file>
@@ -2077,7 +2074,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2268,6 +2265,9 @@
     <xf numFmtId="3" fontId="3" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2276,6 +2276,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2541,7 +2544,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.7109375" style="4" customWidth="1"/>
@@ -2555,825 +2558,824 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="210" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C3" s="43">
         <v>2027</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D3" s="44" t="s">
         <v>3</v>
       </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="B4" s="4">
+        <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!I5:I41,"&lt;=3")</f>
+        <v>18</v>
+      </c>
+      <c r="C4" s="4">
+        <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!I5:I41,"&lt;=15")</f>
+        <v>30</v>
+      </c>
+      <c r="D4" s="48"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>565</v>
       </c>
       <c r="B5" s="4">
-        <f>SUMIF(Штат!E5:E41,"штат",Штат!G5:G41)</f>
-        <v>30</v>
-      </c>
-      <c r="C5" s="4">
-        <f>B5</f>
-        <v>30</v>
+        <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!F5:F41,"новая",Штат!I5:I41,"&lt;=3")</f>
+        <v>14</v>
+      </c>
+      <c r="C5" s="84">
+        <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!F5:F41,"новая",Штат!I5:I41,"&gt;3")</f>
+        <v>12</v>
       </c>
       <c r="D5" s="48"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>327</v>
       </c>
       <c r="B6" s="4">
-        <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!F5:F41,"новая")</f>
-        <v>26</v>
-      </c>
-      <c r="D6" s="48"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B7" s="4">
+        <f>SUMPRODUCT((Штат!I8:I13&lt;=3)*Штат!G8:G13)+SUMPRODUCT((Штат!E17:E36="штат")*(Штат!I17:I36&lt;=3)*Штат!G17:G36)</f>
+        <v>12</v>
+      </c>
+      <c r="C6" s="4">
         <f>Штат!G43</f>
         <v>21</v>
       </c>
-      <c r="C7" s="4">
-        <f>B7</f>
-        <v>21</v>
-      </c>
-      <c r="D7" s="48"/>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B8" s="49">
+      <c r="D6" s="48"/>
+    </row>
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B7" s="49">
         <f>SUMIFS(Штат!N5:N41,Штат!E5:E41,"штат")</f>
         <v>58691747.741935484</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C7" s="49">
         <f>SUMIFS(Штат!O5:O41,Штат!E5:E41,"штат")</f>
         <v>419273990</v>
       </c>
+      <c r="D7" s="50">
+        <f>C7/12</f>
+        <v>34939499.166666664</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B8" s="49">
+        <f>Аутсорс!K11</f>
+        <v>15843354.83870968</v>
+      </c>
+      <c r="C8" s="49">
+        <f>Аутсорс!L11</f>
+        <v>80736000</v>
+      </c>
       <c r="D8" s="50">
         <f>C8/12</f>
-        <v>34939499.166666664</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+        <v>6728000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>505</v>
+        <v>417</v>
       </c>
       <c r="B9" s="49">
-        <f>Аутсорс!K11</f>
-        <v>15843354.83870968</v>
+        <f>Штат!P42</f>
+        <v>23115060</v>
       </c>
       <c r="C9" s="49">
-        <f>Аутсорс!L11</f>
-        <v>80736000</v>
+        <f>Штат!Q42</f>
+        <v>139757996.66666666</v>
       </c>
       <c r="D9" s="50">
         <f>C9/12</f>
-        <v>6728000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>11646499.722222222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>419</v>
+        <v>4</v>
       </c>
       <c r="B10" s="49">
-        <f>Штат!P42</f>
-        <v>23115060</v>
+        <f>Штат!R42</f>
+        <v>854387.09677419392</v>
       </c>
       <c r="C10" s="49">
-        <f>Штат!Q42</f>
-        <v>139757996.66666666</v>
+        <f>Штат!S42</f>
+        <v>6631000</v>
       </c>
       <c r="D10" s="50">
         <f>C10/12</f>
-        <v>11646499.722222222</v>
+        <v>552583.33333333337</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="49">
-        <f>Штат!R42</f>
-        <v>854387.09677419392</v>
+        <f>Командировки!I26</f>
+        <v>7246775.9408602165</v>
       </c>
       <c r="C11" s="49">
-        <f>Штат!S42</f>
-        <v>6631000</v>
+        <f>Командировки!J26</f>
+        <v>37657517.125</v>
       </c>
       <c r="D11" s="50">
         <f>C11/12</f>
-        <v>552583.33333333337</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3138126.4270833335</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>7</v>
+        <v>525</v>
       </c>
       <c r="B12" s="49">
-        <f>Командировки!I26</f>
-        <v>7246775.9408602165</v>
-      </c>
-      <c r="C12" s="49">
-        <f>Командировки!J26</f>
-        <v>37657517.125</v>
-      </c>
-      <c r="D12" s="50">
-        <f>C12/12</f>
-        <v>3138126.4270833335</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="B13" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Оснащение")</f>
         <v>41946058</v>
       </c>
-      <c r="C13" s="49">
+      <c r="C12" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Оснащение")</f>
         <v>0</v>
       </c>
-      <c r="D13" s="50"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="49">
+      <c r="D12" s="50"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Офис")</f>
         <v>21976663.496774193</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C13" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Офис")</f>
         <v>68938825.199999988</v>
       </c>
-      <c r="D14" s="50">
-        <f>C14/12</f>
+      <c r="D13" s="50">
+        <f>C13/12</f>
         <v>5744902.0999999987</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="B15" s="51">
+    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="B14" s="51">
         <f>'Оснащение и офис'!I39</f>
         <v>11560261.396774193</v>
       </c>
-      <c r="C15" s="51">
+      <c r="C14" s="51">
         <f>'Оснащение и офис'!J39</f>
         <v>58909825.199999996</v>
       </c>
-      <c r="D15" s="51">
-        <f>C15/12</f>
+      <c r="D14" s="51">
+        <f>C14/12</f>
         <v>4909152.0999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="B16" s="51">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B15" s="51">
         <f>'Оснащение и офис'!I40</f>
         <v>4909152.0999999996</v>
       </c>
-      <c r="C16" s="51">
+      <c r="C15" s="51">
         <f>'Оснащение и офис'!J40</f>
         <v>0</v>
       </c>
-      <c r="D16" s="51"/>
+      <c r="D15" s="51"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B16" s="49">
+        <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Цифровые")</f>
+        <v>820500</v>
+      </c>
+      <c r="C16" s="49">
+        <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Цифровые")</f>
+        <v>9282000</v>
+      </c>
+      <c r="D16" s="50">
+        <f t="shared" ref="D16:D24" si="0">C16/12</f>
+        <v>773500</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>506</v>
+        <v>367</v>
       </c>
       <c r="B17" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Цифровые")</f>
-        <v>820500</v>
-      </c>
-      <c r="C17" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Цифровые")</f>
-        <v>9282000</v>
-      </c>
-      <c r="D17" s="50">
-        <f t="shared" ref="D17:D25" si="0">C17/12</f>
-        <v>773500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="B18" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Медиа")</f>
         <v>3325000</v>
       </c>
-      <c r="C18" s="49">
+      <c r="C17" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Медиа")</f>
         <v>25300000</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D17" s="50">
         <f t="shared" si="0"/>
         <v>2108333.3333333335</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="45" t="s">
-        <v>481</v>
-      </c>
-      <c r="B19" s="52">
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="45" t="s">
+        <v>478</v>
+      </c>
+      <c r="B18" s="52">
         <f>'Проекты (вне бюджета)'!G16</f>
         <v>213000000</v>
       </c>
-      <c r="C19" s="52">
+      <c r="C18" s="52">
         <f>'Проекты (вне бюджета)'!H16</f>
         <v>1530000000</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D18" s="53">
         <f t="shared" si="0"/>
         <v>127500000</v>
       </c>
-      <c r="E19" s="46" t="s">
-        <v>422</v>
-      </c>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="49">
+      <c r="E18" s="46" t="s">
+        <v>420</v>
+      </c>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Прочие")</f>
         <v>5300000</v>
       </c>
-      <c r="C20" s="49">
+      <c r="C19" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Прочие")</f>
         <v>9400000</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D19" s="50">
         <f t="shared" si="0"/>
         <v>783333.33333333337</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="55">
-        <f>B8+B9+B10+B11+B12+B13+B14+B17+B18+B20</f>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="55">
+        <f>B7+B8+B9+B10+B11+B12+B13+B16+B17+B19</f>
         <v>179119547.11505377</v>
       </c>
-      <c r="C21" s="55">
-        <f>C8+C9+C10+C11+C12+C13+C14+C17+C18+C20</f>
+      <c r="C20" s="55">
+        <f>C7+C8+C9+C10+C11+C12+C13+C16+C17+C19</f>
         <v>796977328.99166656</v>
       </c>
-      <c r="D21" s="56">
+      <c r="D20" s="56">
         <f t="shared" si="0"/>
         <v>66414777.41597221</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B22" s="49">
-        <f>B21*Резерв</f>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B21" s="49">
+        <f>B20*Резерв</f>
         <v>17911954.71150538</v>
       </c>
-      <c r="C22" s="49">
-        <f>C21*Резерв</f>
+      <c r="C21" s="49">
+        <f>C20*Резерв</f>
         <v>79697732.899166659</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D21" s="50">
         <f t="shared" si="0"/>
         <v>6641477.7415972212</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="57">
-        <f>B21+B22</f>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="57">
+        <f>B20+B21</f>
         <v>197031501.82655916</v>
       </c>
-      <c r="C23" s="57">
-        <f>C21+C22</f>
+      <c r="C22" s="57">
+        <f>C20+C21</f>
         <v>876675061.89083326</v>
       </c>
-      <c r="D23" s="58">
+      <c r="D22" s="58">
         <f t="shared" si="0"/>
         <v>73056255.157569438</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="49">
-        <f>B23*НДС</f>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="49">
+        <f>B22*НДС</f>
         <v>31525040.292249467</v>
       </c>
-      <c r="C24" s="49">
-        <f>C23*НДС</f>
+      <c r="C23" s="49">
+        <f>C22*НДС</f>
         <v>140268009.90253332</v>
       </c>
-      <c r="D24" s="50">
+      <c r="D23" s="50">
         <f t="shared" si="0"/>
         <v>11689000.82521111</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="59">
-        <f>B23+B24</f>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="59">
+        <f>B22+B23</f>
         <v>228556542.11880863</v>
       </c>
-      <c r="C25" s="60">
-        <f>C23+C24</f>
+      <c r="C24" s="60">
+        <f>C22+C23</f>
         <v>1016943071.7933666</v>
       </c>
-      <c r="D25" s="56">
+      <c r="D24" s="56">
         <f t="shared" si="0"/>
         <v>84745255.982780546</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="B26" s="61"/>
-      <c r="C26" s="62">
-        <f>B25+C25</f>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" s="61"/>
+      <c r="C25" s="62">
+        <f>B24+C24</f>
         <v>1245499613.9121752</v>
       </c>
+      <c r="D25" s="48"/>
+    </row>
+    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
+        <v>479</v>
+      </c>
+      <c r="B26" s="63" t="s">
+        <v>514</v>
+      </c>
+      <c r="C26" s="64">
+        <f>B18+C18</f>
+        <v>1743000000</v>
+      </c>
       <c r="D26" s="48"/>
     </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="40" t="s">
-        <v>482</v>
-      </c>
-      <c r="B27" s="63" t="s">
-        <v>517</v>
-      </c>
-      <c r="C27" s="64">
-        <f>B19+C19</f>
-        <v>1743000000</v>
-      </c>
-      <c r="D27" s="48"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>14</v>
+      <c r="A28" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>531</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B33" s="49">
+        <f>Аренда_мес</f>
+        <v>4909152.0999999996</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="B34" s="49">
-        <f>Аренда_мес</f>
-        <v>4909152.0999999996</v>
+        <v>314</v>
+      </c>
+      <c r="B34" s="55">
+        <f>Аренда_с_НДС</f>
+        <v>5694616.4359999988</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B35" s="55">
-        <f>Аренда_с_НДС</f>
-        <v>5694616.4359999988</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B36" s="49">
+        <v>315</v>
+      </c>
+      <c r="B35" s="49">
         <f>Аренда_депозит</f>
         <v>4909152.0999999996</v>
       </c>
     </row>
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B36" s="49">
+        <f>Аренда_мес-9856200</f>
+        <v>-4947047.9000000004</v>
+      </c>
+    </row>
     <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>532</v>
+        <v>434</v>
       </c>
       <c r="B37" s="49">
-        <f>Аренда_мес-9856200</f>
-        <v>-4947047.9000000004</v>
+        <f>Аренда_мес-5000000</f>
+        <v>-90847.900000000373</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B38" s="49">
-        <f>Аренда_мес-5000000</f>
-        <v>-90847.900000000373</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="B39" s="49">
         <f>(5000000-Коммун_мес-Парковка_мест*Парковка_цена)/Площадь_офиса</f>
         <v>13766.674200839523</v>
       </c>
     </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B39" s="49">
+        <f>'Оснащение и офис'!I13</f>
+        <v>360000</v>
+      </c>
+    </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B40" s="49">
-        <f>'Оснащение и офис'!I13</f>
-        <v>360000</v>
+        <f>'Оснащение и офис'!E14</f>
+        <v>841000</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="B41" s="49">
-        <f>'Оснащение и офис'!E14</f>
-        <v>841000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B42" s="49">
         <f>Канцелярия!F22</f>
         <v>240750</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="B43" s="49">
+    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B42" s="49">
         <f>SUM('Оснащение и офис'!I20:I23)</f>
         <v>182213</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="65" t="s">
+    <row r="44" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="65" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="66" t="s">
+        <v>532</v>
+      </c>
+      <c r="B45" s="75" t="s">
+        <v>533</v>
+      </c>
+      <c r="C45" s="67" t="s">
+        <v>534</v>
+      </c>
+      <c r="D45" s="67" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A46" s="68" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="66" t="s">
+      <c r="B46" s="76" t="s">
         <v>536</v>
       </c>
-      <c r="B46" s="75" t="s">
+      <c r="C46" s="74" t="s">
         <v>537</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="D46" s="69"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="68" t="s">
         <v>538</v>
       </c>
-      <c r="D46" s="67" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A47" s="68" t="s">
-        <v>539</v>
-      </c>
-      <c r="B47" s="76" t="s">
-        <v>540</v>
-      </c>
-      <c r="C47" s="74" t="s">
-        <v>541</v>
-      </c>
-      <c r="D47" s="69"/>
+      <c r="B47" s="77">
+        <v>309.7</v>
+      </c>
+      <c r="C47" s="70">
+        <v>469.34</v>
+      </c>
+      <c r="D47" s="70">
+        <f>C47-B47</f>
+        <v>159.63999999999999</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="68" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B48" s="77">
-        <v>309.7</v>
+        <v>340.67</v>
       </c>
       <c r="C48" s="70">
-        <v>469.34</v>
+        <v>657.08</v>
       </c>
       <c r="D48" s="70">
         <f>C48-B48</f>
-        <v>159.63999999999999</v>
+        <v>316.41000000000003</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="68" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B49" s="77">
-        <v>340.67</v>
+        <v>8.3702702702702698</v>
       </c>
       <c r="C49" s="70">
-        <v>657.08</v>
+        <v>12.684864864864901</v>
       </c>
       <c r="D49" s="70">
         <f>C49-B49</f>
-        <v>316.41000000000003</v>
+        <v>4.3145945945946309</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="68" t="s">
-        <v>544</v>
-      </c>
-      <c r="B50" s="77">
-        <v>8.3702702702702698</v>
-      </c>
-      <c r="C50" s="70">
-        <v>12.684864864864901</v>
-      </c>
-      <c r="D50" s="70">
+        <v>541</v>
+      </c>
+      <c r="B50" s="78">
+        <v>13500</v>
+      </c>
+      <c r="C50" s="71">
+        <v>15000</v>
+      </c>
+      <c r="D50" s="71">
         <f>C50-B50</f>
-        <v>4.3145945945946309</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="68" t="s">
+        <v>542</v>
+      </c>
+      <c r="B51" s="78">
+        <v>230107.1</v>
+      </c>
+      <c r="C51" s="71" t="s">
+        <v>543</v>
+      </c>
+      <c r="D51" s="71"/>
+    </row>
+    <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="68" t="s">
+        <v>544</v>
+      </c>
+      <c r="B52" s="78">
+        <v>80000</v>
+      </c>
+      <c r="C52" s="71" t="s">
         <v>545</v>
       </c>
-      <c r="B51" s="78">
-        <v>13500</v>
-      </c>
-      <c r="C51" s="71">
-        <v>15000</v>
-      </c>
-      <c r="D51" s="71">
-        <f>C51-B51</f>
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="68" t="s">
+      <c r="D52" s="71"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="68" t="s">
         <v>546</v>
       </c>
-      <c r="B52" s="78">
-        <v>230107.1</v>
-      </c>
-      <c r="C52" s="71" t="s">
-        <v>547</v>
-      </c>
-      <c r="D52" s="71"/>
-    </row>
-    <row r="53" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="68" t="s">
-        <v>548</v>
-      </c>
       <c r="B53" s="78">
-        <v>80000</v>
-      </c>
-      <c r="C53" s="71" t="s">
-        <v>549</v>
-      </c>
-      <c r="D53" s="71"/>
+        <v>4909152.0999999996</v>
+      </c>
+      <c r="C53" s="71">
+        <v>9856200</v>
+      </c>
+      <c r="D53" s="71">
+        <f t="shared" ref="D53:D62" si="1">C53-B53</f>
+        <v>4947047.9000000004</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="68" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B54" s="78">
-        <v>4909152.0999999996</v>
+        <v>5694616.4359999998</v>
       </c>
       <c r="C54" s="71">
-        <v>9856200</v>
+        <v>11433192</v>
       </c>
       <c r="D54" s="71">
-        <f t="shared" ref="D54:D63" si="1">C54-B54</f>
-        <v>4947047.9000000004</v>
+        <f t="shared" si="1"/>
+        <v>5738575.5640000002</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="68" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B55" s="78">
-        <v>5694616.4359999998</v>
+        <v>68335397.231999993</v>
       </c>
       <c r="C55" s="71">
-        <v>11433192</v>
+        <v>137198304</v>
       </c>
       <c r="D55" s="71">
         <f t="shared" si="1"/>
-        <v>5738575.5640000002</v>
+        <v>68862906.768000007</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="68" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B56" s="78">
-        <v>68335397.231999993</v>
+        <v>-90847.900000000402</v>
       </c>
       <c r="C56" s="71">
-        <v>137198304</v>
+        <v>4856200</v>
       </c>
       <c r="D56" s="71">
         <f t="shared" si="1"/>
-        <v>68862906.768000007</v>
+        <v>4947047.9000000004</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="68" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B57" s="78">
-        <v>-90847.900000000402</v>
+        <v>11560261.396774201</v>
       </c>
       <c r="C57" s="71">
-        <v>4856200</v>
+        <v>23209761.290322602</v>
       </c>
       <c r="D57" s="71">
         <f t="shared" si="1"/>
-        <v>4947047.9000000004</v>
+        <v>11649499.893548401</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="68" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B58" s="78">
-        <v>11560261.396774201</v>
+        <v>58909825.200000003</v>
       </c>
       <c r="C58" s="71">
-        <v>23209761.290322602</v>
+        <v>118274400</v>
       </c>
       <c r="D58" s="71">
         <f t="shared" si="1"/>
-        <v>11649499.893548401</v>
+        <v>59364574.799999997</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="68" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B59" s="78">
-        <v>58909825.200000003</v>
+        <v>4909152.0999999996</v>
       </c>
       <c r="C59" s="71">
-        <v>118274400</v>
+        <v>9856200</v>
       </c>
       <c r="D59" s="71">
         <f t="shared" si="1"/>
-        <v>59364574.799999997</v>
+        <v>4947047.9000000004</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="68" t="s">
-        <v>556</v>
-      </c>
-      <c r="B60" s="78">
-        <v>4909152.0999999996</v>
-      </c>
-      <c r="C60" s="71">
-        <v>9856200</v>
-      </c>
-      <c r="D60" s="71">
+      <c r="A60" s="72" t="s">
+        <v>553</v>
+      </c>
+      <c r="B60" s="79">
+        <v>228556542.11880901</v>
+      </c>
+      <c r="C60" s="73">
+        <v>249733737.103376</v>
+      </c>
+      <c r="D60" s="73">
         <f t="shared" si="1"/>
-        <v>4947047.9000000004</v>
+        <v>21177194.984566987</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="72" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B61" s="79">
-        <v>228556542.11880901</v>
+        <v>1016943071.79337</v>
       </c>
       <c r="C61" s="73">
-        <v>249733737.103376</v>
+        <v>1092692269.2381699</v>
       </c>
       <c r="D61" s="73">
         <f t="shared" si="1"/>
-        <v>21177194.984566987</v>
+        <v>75749197.4447999</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="72" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B62" s="79">
-        <v>1016943071.79337</v>
+        <v>1245499613.9121799</v>
       </c>
       <c r="C62" s="73">
-        <v>1092692269.2381699</v>
+        <v>1342426006.3415401</v>
       </c>
       <c r="D62" s="73">
         <f t="shared" si="1"/>
-        <v>75749197.4447999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="72" t="s">
+        <v>96926392.429360151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="81" t="s">
+        <v>557</v>
+      </c>
+      <c r="B65" s="81"/>
+      <c r="C65" s="81"/>
+      <c r="D65" s="81"/>
+    </row>
+    <row r="66" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="81" t="s">
+        <v>558</v>
+      </c>
+      <c r="B66" s="81"/>
+      <c r="C66" s="81"/>
+      <c r="D66" s="81"/>
+    </row>
+    <row r="67" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="81" t="s">
         <v>559</v>
       </c>
-      <c r="B63" s="79">
-        <v>1245499613.9121799</v>
-      </c>
-      <c r="C63" s="73">
-        <v>1342426006.3415401</v>
-      </c>
-      <c r="D63" s="73">
-        <f t="shared" si="1"/>
-        <v>96926392.429360151</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
+      <c r="B67" s="81"/>
+      <c r="C67" s="81"/>
+      <c r="D67" s="81"/>
+    </row>
+    <row r="68" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="81" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="80" t="s">
+      <c r="B68" s="81"/>
+      <c r="C68" s="81"/>
+      <c r="D68" s="81"/>
+    </row>
+    <row r="69" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="81" t="s">
         <v>561</v>
       </c>
-      <c r="B66" s="80"/>
-      <c r="C66" s="80"/>
-      <c r="D66" s="80"/>
-    </row>
-    <row r="67" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="80" t="s">
-        <v>562</v>
-      </c>
-      <c r="B67" s="80"/>
-      <c r="C67" s="80"/>
-      <c r="D67" s="80"/>
-    </row>
-    <row r="68" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="80" t="s">
-        <v>563</v>
-      </c>
-      <c r="B68" s="80"/>
-      <c r="C68" s="80"/>
-      <c r="D68" s="80"/>
-    </row>
-    <row r="69" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="80" t="s">
-        <v>564</v>
-      </c>
-      <c r="B69" s="80"/>
-      <c r="C69" s="80"/>
-      <c r="D69" s="80"/>
-    </row>
-    <row r="70" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="80" t="s">
-        <v>565</v>
-      </c>
-      <c r="B70" s="80"/>
-      <c r="C70" s="80"/>
-      <c r="D70" s="80"/>
+      <c r="B69" s="81"/>
+      <c r="C69" s="81"/>
+      <c r="D69" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A66:D66"/>
     <mergeCell ref="A67:D67"/>
     <mergeCell ref="A68:D68"/>
     <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A70:D70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3392,7 +3394,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3400,574 +3402,574 @@
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" s="11">
         <v>85000</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="11">
         <v>4325</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" s="11">
         <v>0.06</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="11">
         <v>0.05</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" s="11">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="11">
         <v>0.03</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11">
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="11">
         <v>0.1</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" s="11">
         <v>0.02</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="11">
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="11">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="11">
         <v>200000</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="11">
         <v>28000</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" s="11">
         <v>530</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" s="11">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B20" s="11">
         <v>90000</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11">
         <v>30000</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B22" s="11">
         <v>15000</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" s="11">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B24" s="11">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11">
         <f>Авиа_РК+Отель_РК*Ночей_РК+Сут_РК*МРП*Дней_РК+Трансп_РК</f>
         <v>190950</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11">
         <f>Трансп_РК+Сут_РК*МРП</f>
         <v>23650</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11">
         <v>900</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11">
         <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B29" s="11">
         <v>150</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B30" s="11">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B31" s="11">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B32" s="11">
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B33" s="11">
         <f>(Авиа_межд+Отель_межд*Ночей_межд+Сут_межд*Дней_межд+Страх_межд)*Курс</f>
         <v>1219000</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B34" s="11">
         <f>Площадь_офиса*Ставка_аренды_м2+Коммун_мес+Парковка_мест*Парковка_цена</f>
         <v>4909152.0999999996</v>
       </c>
       <c r="C34" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B35" s="11">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B36" s="11">
         <v>0.1</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B37" s="11">
         <v>0.16</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B42">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B43">
         <f>МРП*(1+Индекс_МРП_2027)</f>
         <v>4627.75</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B44">
         <f>Авиа_РК+Отель_РК*Ночей_РК+Сут_РК*МРП_2027*Дней_РК+Трансп_РК</f>
         <v>192766.5</v>
       </c>
       <c r="C44" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B45">
         <f>Трансп_РК+Сут_РК*МРП_2027</f>
         <v>24255.5</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B48" s="16">
         <f>ROUND((52.2+21.4+12.4+33.7+190)*1.1,2)</f>
         <v>340.67</v>
       </c>
       <c r="C48" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B49" s="5">
         <v>13500</v>
       </c>
       <c r="C49" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B50" s="5">
         <f>743*309.7</f>
         <v>230107.1</v>
       </c>
       <c r="C50" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B51" s="5">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B52" s="5">
         <v>40000</v>
       </c>
       <c r="C52" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B53" s="5">
         <f>Аренда_мес*(1+НДС)</f>
         <v>5694616.4359999988</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B54" s="5">
         <f>Аренда_мес*Депозит_мес</f>
         <v>4909152.0999999996</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B55" s="19">
         <f>11/31+2</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C55" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B57" s="18">
         <v>0.1</v>
       </c>
       <c r="C57" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B58" s="19">
         <f>Аренда_мес_2026</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C58" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -3995,80 +3997,80 @@
   <sheetData>
     <row r="1" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="P4" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="R4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="W4" s="4"/>
     </row>
@@ -4077,19 +4079,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D5" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>116</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>118</v>
       </c>
       <c r="G5" s="20">
         <v>1</v>
@@ -4149,7 +4151,7 @@
         <v>29319680</v>
       </c>
       <c r="V5" s="20" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4157,19 +4159,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>438</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>440</v>
-      </c>
       <c r="D6" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G6" s="20">
         <v>1</v>
@@ -4229,7 +4231,7 @@
         <v>25742720</v>
       </c>
       <c r="V6" s="20" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4237,19 +4239,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G7" s="20">
         <v>1</v>
@@ -4309,7 +4311,7 @@
         <v>25742720</v>
       </c>
       <c r="V7" s="20" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4317,19 +4319,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G8" s="20">
         <v>1</v>
@@ -4389,7 +4391,7 @@
         <v>25742720</v>
       </c>
       <c r="V8" s="20" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4397,19 +4399,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G9" s="24">
         <v>1</v>
@@ -4469,7 +4471,7 @@
         <v>23954240</v>
       </c>
       <c r="V9" s="24" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4477,19 +4479,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G10" s="20">
         <v>1</v>
@@ -4549,7 +4551,7 @@
         <v>18588800</v>
       </c>
       <c r="V10" s="20" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4557,19 +4559,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G11" s="24">
         <v>1</v>
@@ -4629,7 +4631,7 @@
         <v>17039733.333333332</v>
       </c>
       <c r="V11" s="24" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4637,19 +4639,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G12" s="24">
         <v>1</v>
@@ -4709,7 +4711,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V12" s="24" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4717,19 +4719,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G13" s="24">
         <v>1</v>
@@ -4789,7 +4791,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V13" s="24" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4797,19 +4799,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>447</v>
+      </c>
+      <c r="D14" s="25" t="s">
         <v>448</v>
       </c>
-      <c r="C14" s="25" t="s">
-        <v>449</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>450</v>
-      </c>
       <c r="E14" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G14" s="24">
         <v>1</v>
@@ -4869,7 +4871,7 @@
         <v>21958053.333333332</v>
       </c>
       <c r="V14" s="24" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4877,19 +4879,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G15" s="24">
         <v>1</v>
@@ -4949,7 +4951,7 @@
         <v>13760853.333333334</v>
       </c>
       <c r="V15" s="24" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4957,19 +4959,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G16" s="24">
         <v>1</v>
@@ -5029,7 +5031,7 @@
         <v>13760853.333333334</v>
       </c>
       <c r="V16" s="24" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5037,19 +5039,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G17" s="24">
         <v>1</v>
@@ -5109,7 +5111,7 @@
         <v>21958053.333333332</v>
       </c>
       <c r="V17" s="24" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5117,19 +5119,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G18" s="20">
         <v>1</v>
@@ -5189,7 +5191,7 @@
         <v>20377280</v>
       </c>
       <c r="V18" s="20" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5197,19 +5199,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>385</v>
-      </c>
       <c r="D19" s="21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G19" s="20">
         <v>1</v>
@@ -5269,7 +5271,7 @@
         <v>18588800</v>
       </c>
       <c r="V19" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5277,19 +5279,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="24" t="s">
+        <v>381</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>385</v>
-      </c>
       <c r="D20" s="25" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G20" s="24">
         <v>1</v>
@@ -5349,7 +5351,7 @@
         <v>17039733.333333332</v>
       </c>
       <c r="V20" s="24" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5357,19 +5359,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>385</v>
-      </c>
       <c r="D21" s="21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G21" s="20">
         <v>1</v>
@@ -5429,7 +5431,7 @@
         <v>18588800</v>
       </c>
       <c r="V21" s="20" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5437,19 +5439,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G22" s="20">
         <v>1</v>
@@ -5509,7 +5511,7 @@
         <v>18588800</v>
       </c>
       <c r="V22" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5517,19 +5519,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G23" s="20">
         <v>1</v>
@@ -5589,7 +5591,7 @@
         <v>13223360</v>
       </c>
       <c r="V23" s="20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5597,19 +5599,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G24" s="24">
         <v>1</v>
@@ -5669,7 +5671,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V24" s="24" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5677,19 +5679,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G25" s="24">
         <v>1</v>
@@ -5749,7 +5751,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V25" s="24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5757,19 +5759,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F26" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G26" s="24">
         <v>1</v>
@@ -5829,7 +5831,7 @@
         <v>13760853.333333334</v>
       </c>
       <c r="V26" s="24" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5837,19 +5839,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G27" s="20">
         <v>1</v>
@@ -5909,7 +5911,7 @@
         <v>23954240</v>
       </c>
       <c r="V27" s="20" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5917,19 +5919,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>376</v>
+      </c>
+      <c r="E28" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="C28" s="29" t="s">
-        <v>462</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>378</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>394</v>
-      </c>
       <c r="F28" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G28" s="28">
         <v>0</v>
@@ -5989,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="28" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5997,19 +5999,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G29" s="20">
         <v>1</v>
@@ -6069,7 +6071,7 @@
         <v>23954240</v>
       </c>
       <c r="V29" s="20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6077,19 +6079,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G30" s="20">
         <v>1</v>
@@ -6149,7 +6151,7 @@
         <v>18588800</v>
       </c>
       <c r="V30" s="20" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6157,19 +6159,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G31" s="28">
         <v>0</v>
@@ -6229,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="28" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6237,19 +6239,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G32" s="28">
         <v>0</v>
@@ -6309,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="28" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6317,19 +6319,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G33" s="28">
         <v>0</v>
@@ -6389,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="28" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6397,19 +6399,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G34" s="20">
         <v>1</v>
@@ -6469,7 +6471,7 @@
         <v>18588800</v>
       </c>
       <c r="V34" s="20" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6477,19 +6479,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G35" s="20">
         <v>1</v>
@@ -6549,7 +6551,7 @@
         <v>13223360</v>
       </c>
       <c r="V35" s="20" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6557,19 +6559,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G36" s="28">
         <v>0</v>
@@ -6629,7 +6631,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="28" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6637,19 +6639,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G37" s="20">
         <v>1</v>
@@ -6709,7 +6711,7 @@
         <v>25742720</v>
       </c>
       <c r="V37" s="20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6717,19 +6719,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G38" s="20">
         <v>1</v>
@@ -6789,7 +6791,7 @@
         <v>13223360</v>
       </c>
       <c r="V38" s="20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6797,19 +6799,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G39" s="20">
         <v>1</v>
@@ -6869,7 +6871,7 @@
         <v>22165760</v>
       </c>
       <c r="V39" s="20" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6877,19 +6879,19 @@
         <v>36</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G40" s="28">
         <v>0</v>
@@ -6949,7 +6951,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="28" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6957,19 +6959,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G41" s="28">
         <v>0</v>
@@ -7029,14 +7031,14 @@
         <v>0</v>
       </c>
       <c r="V41" s="28" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D42" s="10"/>
       <c r="E42" s="10"/>
@@ -7093,7 +7095,7 @@
     </row>
     <row r="43" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G43">
         <f>SUM(G8:G13)+SUM(G17:G36)</f>
@@ -7106,7 +7108,7 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G44">
         <f>SUM(G5:G7)+SUM(G14:G16)+SUM(G37:G41)</f>
@@ -7143,42 +7145,42 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D3" s="33" t="s">
+        <v>481</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>482</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>483</v>
+      </c>
+      <c r="G3" s="33" t="s">
         <v>484</v>
       </c>
-      <c r="E3" s="33" t="s">
-        <v>485</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>486</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>487</v>
-      </c>
       <c r="H3" s="33" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I3" s="33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L3" s="33">
         <v>2027</v>
@@ -7189,13 +7191,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E4" s="36">
         <v>1000000</v>
@@ -7233,13 +7235,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E5" s="36">
         <v>700000</v>
@@ -7277,13 +7279,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E6" s="36">
         <v>1000000</v>
@@ -7321,13 +7323,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E7" s="36">
         <v>1000000</v>
@@ -7365,13 +7367,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C8" s="35" t="s">
+        <v>493</v>
+      </c>
+      <c r="D8" s="35" t="s">
         <v>496</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>499</v>
       </c>
       <c r="E8" s="36">
         <v>700000</v>
@@ -7409,13 +7411,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E9" s="36">
         <v>700000</v>
@@ -7453,13 +7455,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E10" s="36">
         <v>700000</v>
@@ -7495,7 +7497,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="38"/>
       <c r="B11" s="38" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
@@ -7544,41 +7546,41 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="J4" s="3">
         <v>2027</v>
@@ -7796,7 +7798,7 @@
     </row>
     <row r="11" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G9:G13)</f>
@@ -7830,7 +7832,7 @@
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C12">
         <f>SUM(Штат!G17:G26)</f>
@@ -7864,7 +7866,7 @@
     </row>
     <row r="13" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C13">
         <f>SUM(Штат!G14:G16)</f>
@@ -7898,7 +7900,7 @@
     </row>
     <row r="14" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C14">
         <f>SUM(Штат!G27:G28)</f>
@@ -7932,7 +7934,7 @@
     </row>
     <row r="15" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C15">
         <f>SUM(Штат!G29:G36)</f>
@@ -8106,7 +8108,7 @@
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -8149,41 +8151,41 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J4" s="3">
         <v>2027</v>
@@ -8191,13 +8193,13 @@
     </row>
     <row r="5" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" t="s">
         <v>140</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" t="s">
-        <v>142</v>
       </c>
       <c r="D5" s="12">
         <v>25</v>
@@ -8206,13 +8208,13 @@
         <v>450000</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G5" s="12">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I38" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -8225,13 +8227,13 @@
     </row>
     <row r="6" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" t="s">
         <v>140</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" t="s">
-        <v>142</v>
       </c>
       <c r="D6" s="12">
         <v>5</v>
@@ -8240,13 +8242,13 @@
         <v>900000</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G6" s="12">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -8259,13 +8261,13 @@
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D7" s="12">
         <v>15</v>
@@ -8274,13 +8276,13 @@
         <v>100000</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G7" s="12">
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
@@ -8293,13 +8295,13 @@
     </row>
     <row r="8" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D8" s="12">
         <v>19</v>
@@ -8308,13 +8310,13 @@
         <v>200000</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G8" s="12">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
@@ -8327,13 +8329,13 @@
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D9" s="12">
         <v>5</v>
@@ -8342,13 +8344,13 @@
         <v>500000</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G9" s="12">
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
@@ -8361,13 +8363,13 @@
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D10" s="12">
         <v>1</v>
@@ -8376,7 +8378,7 @@
         <v>800000</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G10" s="12">
         <v>1</v>
@@ -8393,13 +8395,13 @@
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D11" s="12">
         <v>1</v>
@@ -8408,7 +8410,7 @@
         <v>500000</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G11" s="12">
         <v>1</v>
@@ -8425,13 +8427,13 @@
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" s="12">
         <v>1</v>
@@ -8440,13 +8442,13 @@
         <v>450000</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G12" s="12">
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
@@ -8459,13 +8461,13 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" t="s">
         <v>140</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="C13" t="s">
-        <v>142</v>
       </c>
       <c r="D13" s="12">
         <v>6</v>
@@ -8474,13 +8476,13 @@
         <v>60000</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G13" s="12">
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
@@ -8493,13 +8495,13 @@
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D14" s="12">
         <v>1</v>
@@ -8509,13 +8511,13 @@
         <v>841000</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G14" s="12">
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
@@ -8528,13 +8530,13 @@
     </row>
     <row r="15" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C15" t="s">
         <v>140</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C15" t="s">
-        <v>142</v>
       </c>
       <c r="D15" s="12">
         <v>1</v>
@@ -8543,13 +8545,13 @@
         <v>2500000</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G15" s="12">
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
@@ -8562,13 +8564,13 @@
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
@@ -8577,7 +8579,7 @@
         <v>300000</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G16" s="12">
         <v>1</v>
@@ -8594,13 +8596,13 @@
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" t="s">
         <v>140</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C17" t="s">
-        <v>142</v>
       </c>
       <c r="D17" s="12">
         <v>2</v>
@@ -8609,13 +8611,13 @@
         <v>280000</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G17" s="12">
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
@@ -8628,13 +8630,13 @@
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C18" t="s">
         <v>140</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="C18" t="s">
-        <v>142</v>
       </c>
       <c r="D18" s="12">
         <v>4</v>
@@ -8643,13 +8645,13 @@
         <v>55000</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G18" s="12">
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
@@ -8662,13 +8664,13 @@
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D19" s="12">
         <v>1</v>
@@ -8677,13 +8679,13 @@
         <v>300000</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G19" s="12">
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
@@ -8696,13 +8698,13 @@
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C20" t="s">
         <v>140</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="C20" t="s">
-        <v>142</v>
       </c>
       <c r="D20" s="12">
         <v>1</v>
@@ -8712,13 +8714,13 @@
         <v>36500</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G20" s="12">
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
@@ -8731,13 +8733,13 @@
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C21" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D21" s="12">
         <v>1</v>
@@ -8747,13 +8749,13 @@
         <v>5172</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G21" s="12">
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
@@ -8766,13 +8768,13 @@
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C22" t="s">
         <v>140</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="C22" t="s">
-        <v>142</v>
       </c>
       <c r="D22" s="12">
         <v>1</v>
@@ -8782,13 +8784,13 @@
         <v>98558</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G22" s="12">
         <v>1</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
@@ -8801,13 +8803,13 @@
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D23" s="12">
         <v>1</v>
@@ -8817,13 +8819,13 @@
         <v>41983</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G23" s="12">
         <v>1</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
@@ -8836,13 +8838,13 @@
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C24" t="s">
         <v>140</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="C24" t="s">
-        <v>142</v>
       </c>
       <c r="D24" s="12">
         <v>31</v>
@@ -8852,13 +8854,13 @@
         <v>3550</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G24" s="12">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -8871,13 +8873,13 @@
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C25" t="s">
         <v>140</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="C25" t="s">
-        <v>142</v>
       </c>
       <c r="D25" s="12">
         <v>5</v>
@@ -8887,13 +8889,13 @@
         <v>5259</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G25" s="12">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -8906,13 +8908,13 @@
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C26" t="s">
         <v>140</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C26" t="s">
-        <v>142</v>
       </c>
       <c r="D26" s="12">
         <v>4</v>
@@ -8922,13 +8924,13 @@
         <v>6237</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G26" s="12">
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -8941,13 +8943,13 @@
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C27" t="s">
         <v>140</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="C27" t="s">
-        <v>142</v>
       </c>
       <c r="D27" s="12">
         <v>5</v>
@@ -8957,13 +8959,13 @@
         <v>7792</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G27" s="12">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -8976,13 +8978,13 @@
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="C28" t="s">
         <v>140</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="C28" t="s">
-        <v>142</v>
       </c>
       <c r="D28" s="12">
         <v>10</v>
@@ -8992,13 +8994,13 @@
         <v>76984</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G28" s="12">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="2">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -9011,13 +9013,13 @@
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" t="s">
         <v>140</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C29" t="s">
-        <v>142</v>
       </c>
       <c r="D29" s="12">
         <v>1</v>
@@ -9026,13 +9028,13 @@
         <v>450000</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -9045,13 +9047,13 @@
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C30" t="s">
         <v>140</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="C30" t="s">
-        <v>142</v>
       </c>
       <c r="D30" s="12">
         <v>1</v>
@@ -9061,13 +9063,13 @@
         <v>49872</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -9080,13 +9082,13 @@
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C31" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D31" s="12">
         <v>1</v>
@@ -9095,13 +9097,13 @@
         <v>300000</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G31" s="12">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
@@ -9114,13 +9116,13 @@
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C32" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D32" s="12">
         <v>1</v>
@@ -9129,13 +9131,13 @@
         <v>800000</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G32" s="12">
         <v>1</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
@@ -9148,13 +9150,13 @@
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C33" t="s">
         <v>140</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C33" t="s">
-        <v>142</v>
       </c>
       <c r="D33" s="12">
         <v>1</v>
@@ -9163,7 +9165,7 @@
         <v>700000</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G33" s="12">
         <v>1</v>
@@ -9180,13 +9182,13 @@
     </row>
     <row r="34" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C34" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D34" s="12">
         <v>1</v>
@@ -9196,13 +9198,13 @@
         <v>7062880</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -9215,13 +9217,13 @@
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C35" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D35" s="12">
         <v>1</v>
@@ -9230,7 +9232,7 @@
         <v>400000</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G35" s="12">
         <v>1</v>
@@ -9247,13 +9249,13 @@
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C36" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D36" s="12">
         <v>1</v>
@@ -9262,7 +9264,7 @@
         <v>150000</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G36" s="12">
         <v>1</v>
@@ -9279,13 +9281,13 @@
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D37" s="12">
         <v>1</v>
@@ -9294,7 +9296,7 @@
         <v>400000</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -9311,13 +9313,13 @@
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C38" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D38" s="12">
         <v>1</v>
@@ -9326,13 +9328,13 @@
         <v>100000</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G38" s="12">
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="0"/>
@@ -9345,13 +9347,13 @@
     </row>
     <row r="39" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" t="s">
         <v>168</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C39" t="s">
-        <v>170</v>
       </c>
       <c r="D39" s="12">
         <v>1</v>
@@ -9361,13 +9363,13 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G39" s="12">
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="I39" s="5">
         <f>D39*E39*Аренда_мес_2026</f>
@@ -9380,13 +9382,13 @@
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D40" s="12">
         <v>1</v>
@@ -9396,13 +9398,13 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G40" s="12">
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I40" s="5">
         <f t="shared" ref="I40:I66" si="5">IF(F40="разово",IF(G40&lt;=3,D40*E40,0),IF(F40="мес",D40*E40*MAX(0,4-G40),D40*E40*MAX(0,4-G40)/12))</f>
@@ -9415,13 +9417,13 @@
     </row>
     <row r="41" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C41" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D41" s="12">
         <v>1</v>
@@ -9430,13 +9432,13 @@
         <v>3000000</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" si="5"/>
@@ -9449,13 +9451,13 @@
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42" t="s">
         <v>168</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C42" t="s">
-        <v>170</v>
       </c>
       <c r="D42" s="12">
         <v>1</v>
@@ -9464,7 +9466,7 @@
         <v>50000</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G42" s="12">
         <v>1</v>
@@ -9481,13 +9483,13 @@
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>166</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C43" t="s">
         <v>168</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C43" t="s">
-        <v>170</v>
       </c>
       <c r="D43" s="12">
         <v>1</v>
@@ -9496,7 +9498,7 @@
         <v>60000</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G43" s="12">
         <v>1</v>
@@ -9513,13 +9515,13 @@
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44" t="s">
         <v>168</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C44" t="s">
-        <v>170</v>
       </c>
       <c r="D44" s="12">
         <v>1</v>
@@ -9528,7 +9530,7 @@
         <v>50000</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G44" s="12">
         <v>1</v>
@@ -9545,13 +9547,13 @@
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C45" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D45" s="12">
         <v>25</v>
@@ -9560,13 +9562,13 @@
         <v>5000</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G45" s="12">
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="5"/>
@@ -9579,13 +9581,13 @@
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C46" t="s">
         <v>168</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C46" t="s">
-        <v>170</v>
       </c>
       <c r="D46" s="12">
         <v>1</v>
@@ -9594,7 +9596,7 @@
         <v>60000</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G46" s="12">
         <v>1</v>
@@ -9611,13 +9613,13 @@
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C47" t="s">
         <v>168</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="C47" t="s">
-        <v>170</v>
       </c>
       <c r="D47" s="12">
         <v>1</v>
@@ -9627,13 +9629,13 @@
         <v>240750</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="5"/>
@@ -9646,13 +9648,13 @@
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>166</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C48" t="s">
         <v>168</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C48" t="s">
-        <v>170</v>
       </c>
       <c r="D48" s="12">
         <v>0</v>
@@ -9661,13 +9663,13 @@
         <v>200000</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="5"/>
@@ -9680,13 +9682,13 @@
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C49" t="s">
         <v>168</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C49" t="s">
-        <v>170</v>
       </c>
       <c r="D49" s="12">
         <v>1</v>
@@ -9695,7 +9697,7 @@
         <v>150000</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G49" s="12">
         <v>1</v>
@@ -9712,13 +9714,13 @@
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>166</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50" t="s">
         <v>168</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C50" t="s">
-        <v>170</v>
       </c>
       <c r="D50" s="12">
         <v>1</v>
@@ -9727,7 +9729,7 @@
         <v>100000</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G50" s="12">
         <v>1</v>
@@ -9744,13 +9746,13 @@
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>184</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C51" t="s">
         <v>186</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C51" t="s">
-        <v>188</v>
       </c>
       <c r="D51" s="12">
         <v>25</v>
@@ -9759,13 +9761,13 @@
         <v>7000</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G51" s="12">
         <v>1</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="5"/>
@@ -9778,13 +9780,13 @@
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>184</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C52" t="s">
         <v>186</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C52" t="s">
-        <v>188</v>
       </c>
       <c r="D52" s="12">
         <v>3</v>
@@ -9793,7 +9795,7 @@
         <v>7500</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -9810,13 +9812,13 @@
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C53" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D53" s="12">
         <v>2</v>
@@ -9825,13 +9827,13 @@
         <v>30000</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G53" s="12">
         <v>1</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="5"/>
@@ -9844,13 +9846,13 @@
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C54" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D54" s="12">
         <v>2</v>
@@ -9859,7 +9861,7 @@
         <v>8000</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -9876,13 +9878,13 @@
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D55" s="12">
         <v>1</v>
@@ -9891,13 +9893,13 @@
         <v>200000</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G55" s="12">
         <v>4</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I55" s="5">
         <f t="shared" si="5"/>
@@ -9910,13 +9912,13 @@
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C56" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D56" s="12">
         <v>1</v>
@@ -9925,13 +9927,13 @@
         <v>300000</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G56" s="12">
         <v>4</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I56" s="5">
         <f t="shared" si="5"/>
@@ -9944,18 +9946,18 @@
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C57" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="13"/>
       <c r="F57" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G57" s="12"/>
       <c r="H57" s="4"/>
@@ -9968,13 +9970,13 @@
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>196</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" t="s">
         <v>198</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C58" t="s">
-        <v>200</v>
       </c>
       <c r="D58" s="12">
         <v>1</v>
@@ -9983,7 +9985,7 @@
         <v>5000000</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G58" s="12">
         <v>1</v>
@@ -10000,13 +10002,13 @@
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C59" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D59" s="12">
         <v>1</v>
@@ -10015,7 +10017,7 @@
         <v>25000</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -10032,13 +10034,13 @@
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>196</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C60" t="s">
         <v>198</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C60" t="s">
-        <v>200</v>
       </c>
       <c r="D60" s="12">
         <v>0</v>
@@ -10047,13 +10049,13 @@
         <v>10000000</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G60" s="12">
         <v>1</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="5"/>
@@ -10066,13 +10068,13 @@
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C61" t="s">
         <v>203</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C61" t="s">
-        <v>205</v>
       </c>
       <c r="D61" s="12">
         <v>1</v>
@@ -10081,13 +10083,13 @@
         <v>700000</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I61" s="5">
         <f t="shared" si="5"/>
@@ -10100,13 +10102,13 @@
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C62" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D62" s="12">
         <v>25</v>
@@ -10115,7 +10117,7 @@
         <v>150000</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G62" s="12">
         <v>1</v>
@@ -10132,13 +10134,13 @@
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C63" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D63" s="12">
         <v>1</v>
@@ -10147,7 +10149,7 @@
         <v>2000000</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G63" s="12">
         <v>1</v>
@@ -10164,13 +10166,13 @@
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C64" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D64" s="12">
         <v>2</v>
@@ -10179,7 +10181,7 @@
         <v>3000000</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G64" s="12">
         <v>0</v>
@@ -10194,13 +10196,13 @@
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C65" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D65" s="12">
         <v>1</v>
@@ -10209,7 +10211,7 @@
         <v>500000</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -10226,13 +10228,13 @@
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C66" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D66" s="12">
         <v>1</v>
@@ -10241,7 +10243,7 @@
         <v>150000</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -10273,16 +10275,16 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="66.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" hidden="1" customWidth="1"/>
     <col min="7" max="8" width="14.7109375" customWidth="1"/>
     <col min="9" max="13" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>480</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -10290,44 +10292,44 @@
     </row>
     <row r="4" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H4" s="3">
+      <c r="G4" s="80" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="80">
         <v>2027</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
       <c r="F5" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G5" s="5">
         <v>6000000</v>
@@ -10338,18 +10340,18 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="13"/>
       <c r="F6" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G6" s="5">
         <v>2000000</v>
@@ -10360,18 +10362,18 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>474</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>478</v>
-      </c>
       <c r="C7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="13"/>
       <c r="F7" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G7" s="5">
         <v>10000000</v>
@@ -10382,18 +10384,18 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="13"/>
       <c r="F8" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -10404,18 +10406,18 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="13"/>
       <c r="F9" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -10426,18 +10428,18 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="13"/>
       <c r="F10" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -10448,18 +10450,18 @@
     </row>
     <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C11" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="13"/>
       <c r="F11" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G11" s="5">
         <v>30000000</v>
@@ -10470,18 +10472,18 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="13"/>
       <c r="F12" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G12" s="5">
         <v>15000000</v>
@@ -10492,18 +10494,18 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C13" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="13"/>
       <c r="F13" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G13" s="5">
         <v>50000000</v>
@@ -10514,18 +10516,18 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C14" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="13"/>
       <c r="F14" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G14" s="5">
         <v>100000000</v>
@@ -10540,7 +10542,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -10557,20 +10559,20 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="G18" s="81">
+        <v>516</v>
+      </c>
+      <c r="G18" s="82">
         <f>G16+H16</f>
         <v>1743000000</v>
       </c>
-      <c r="H18" s="82"/>
+      <c r="H18" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G18:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10593,46 +10595,46 @@
   <sheetData>
     <row r="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="E4" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>275</v>
-      </c>
       <c r="G4" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5" t="s">
         <v>276</v>
-      </c>
-      <c r="B5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C5" t="s">
-        <v>278</v>
       </c>
       <c r="D5" s="16">
         <v>7</v>
@@ -10645,18 +10647,18 @@
         <v>21000</v>
       </c>
       <c r="G5" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" t="s">
         <v>276</v>
-      </c>
-      <c r="B6" t="s">
-        <v>279</v>
-      </c>
-      <c r="C6" t="s">
-        <v>278</v>
       </c>
       <c r="D6" s="16">
         <v>0.5</v>
@@ -10669,18 +10671,18 @@
         <v>3250</v>
       </c>
       <c r="G6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D7" s="16">
         <v>1</v>
@@ -10693,18 +10695,18 @@
         <v>6000</v>
       </c>
       <c r="G7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8" s="16">
         <v>0.5</v>
@@ -10717,18 +10719,18 @@
         <v>2500</v>
       </c>
       <c r="G8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D9" s="16">
         <v>20</v>
@@ -10741,18 +10743,18 @@
         <v>24000</v>
       </c>
       <c r="G9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D10" s="16">
         <v>20</v>
@@ -10765,18 +10767,18 @@
         <v>18000</v>
       </c>
       <c r="G10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D11" s="16">
         <v>10</v>
@@ -10789,18 +10791,18 @@
         <v>15000</v>
       </c>
       <c r="G11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" s="16">
         <v>0.5</v>
@@ -10813,18 +10815,18 @@
         <v>4000</v>
       </c>
       <c r="G12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B13" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D13" s="16">
         <v>1</v>
@@ -10837,18 +10839,18 @@
         <v>10000</v>
       </c>
       <c r="G13" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D14" s="16">
         <v>0.5</v>
@@ -10863,13 +10865,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B15" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
@@ -10882,18 +10884,18 @@
         <v>12000</v>
       </c>
       <c r="G15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B16" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D16" s="16">
         <v>0.5</v>
@@ -10906,18 +10908,18 @@
         <v>4000</v>
       </c>
       <c r="G16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D17" s="16">
         <v>0.2</v>
@@ -10930,18 +10932,18 @@
         <v>5000</v>
       </c>
       <c r="G17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B18" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
@@ -10954,18 +10956,18 @@
         <v>35000</v>
       </c>
       <c r="G18" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D19" s="16">
         <v>0.2</v>
@@ -10980,13 +10982,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C20" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D20" s="16">
         <v>20</v>
@@ -10999,18 +11001,18 @@
         <v>36000</v>
       </c>
       <c r="G20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B21" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D21" s="16">
         <v>1</v>
@@ -11023,12 +11025,12 @@
         <v>40000</v>
       </c>
       <c r="G21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D22" s="41"/>
       <c r="E22" s="8"/>
@@ -11039,7 +11041,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="5"/>
@@ -11050,7 +11052,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -11084,40 +11086,40 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -11131,13 +11133,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C6">
         <v>5659</v>
       </c>
       <c r="D6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -11155,13 +11157,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C7">
         <v>2584</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -11179,13 +11181,13 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C8">
         <v>2534</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -11203,13 +11205,13 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C9">
         <v>6218</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -11227,13 +11229,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C10">
         <v>7045</v>
       </c>
       <c r="D10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -11251,13 +11253,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C11">
         <v>4240</v>
       </c>
       <c r="D11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -11275,13 +11277,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C12">
         <v>6976</v>
       </c>
       <c r="D12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -11299,13 +11301,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C13">
         <v>5729</v>
       </c>
       <c r="D13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -11323,13 +11325,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C14">
         <v>3288</v>
       </c>
       <c r="D14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -11347,13 +11349,13 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C15">
         <v>1756</v>
       </c>
       <c r="D15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -11371,13 +11373,13 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C16">
         <v>4400</v>
       </c>
       <c r="D16" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -11393,7 +11395,7 @@
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -11410,7 +11412,7 @@
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -11424,10 +11426,10 @@
         <v>2.1</v>
       </c>
       <c r="B20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D20" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -11445,10 +11447,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B21" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -11466,10 +11468,10 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B22" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D22" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -11487,10 +11489,10 @@
         <v>2.4</v>
       </c>
       <c r="B23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D23" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -11508,10 +11510,10 @@
         <v>2.5</v>
       </c>
       <c r="B24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D24" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -11529,10 +11531,10 @@
         <v>2.6</v>
       </c>
       <c r="B25" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E25">
         <v>12</v>
@@ -11548,7 +11550,7 @@
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -11565,7 +11567,7 @@
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -11579,10 +11581,10 @@
         <v>3.1</v>
       </c>
       <c r="B29" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D29" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -11600,10 +11602,10 @@
         <v>3.2</v>
       </c>
       <c r="B30" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D30" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -11621,10 +11623,10 @@
         <v>3.3</v>
       </c>
       <c r="B31" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D31" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -11642,10 +11644,10 @@
         <v>3.4</v>
       </c>
       <c r="B32" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D32" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -11661,7 +11663,7 @@
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -11679,7 +11681,7 @@
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
       <c r="B35" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="572">
   <si>
     <t>Бюджет проектного офиса «Таза Қазақстан» (ЦАКФ) на октябрь–декабрь 2026 и 2027 год — СВОД, ₸</t>
   </si>
@@ -142,9 +142,6 @@
     <t>В среднем в месяц 2027</t>
   </si>
   <si>
-    <t>5. Командировки (по РК, по макрорегионам, зарубежные)</t>
-  </si>
-  <si>
     <t>7. Офис: аренда, депозит, ремонт, хозрасходы, курьер, связь, уборка</t>
   </si>
   <si>
@@ -601,9 +598,6 @@
     <t>лист «Смета фото-видео»: КП 5 517 890 + аккумуляторы на год 970 000 + доп. оборудование 574 990</t>
   </si>
   <si>
-    <t>Бытовая техника (кулер, холодильник, микроволновка, кофемашина)</t>
-  </si>
-  <si>
     <t>Лицензии 1С на дополнительные рабочие места</t>
   </si>
   <si>
@@ -1838,6 +1832,18 @@
   </si>
   <si>
     <t>Реализация проектов, в т.ч. с молодёжью и волонтёрами</t>
+  </si>
+  <si>
+    <t>5. Командировки (по РК, по макрорегионам)</t>
+  </si>
+  <si>
+    <t>Бытовая техника (кулер для воды, холодильник, микроволновка, кофемашина)</t>
+  </si>
+  <si>
+    <t>Второй кулер для воды, напольный, нагрев и охлаждение (класс Midea MK-32H)</t>
+  </si>
+  <si>
+    <t>Второй кулер – для зоны 710 (первый – в комплекте бытовой техники). Kaspi.kz (Астана) на 10.10.2026 – 35 990 ₸ с НДС, в бюджете без НДС (÷1,16): https://kaspi.kz/shop/p/midea-mk-32h-belyi-25900012/</t>
   </si>
 </sst>
 </file>
@@ -2586,7 +2592,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B4" s="4">
         <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!I5:I41,"&lt;=3")</f>
@@ -2600,7 +2606,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B5" s="4">
         <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!F5:F41,"новая",Штат!I5:I41,"&lt;=3")</f>
@@ -2614,7 +2620,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B6" s="4">
         <f>SUMPRODUCT((Штат!I8:I13&lt;=3)*Штат!G8:G13)+SUMPRODUCT((Штат!E17:E36="штат")*(Штат!I17:I36&lt;=3)*Штат!G17:G36)</f>
@@ -2628,7 +2634,7 @@
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B7" s="49">
         <f>SUMIFS(Штат!N5:N41,Штат!E5:E41,"штат")</f>
@@ -2645,7 +2651,7 @@
     </row>
     <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B8" s="49">
         <f>Аутсорс!K11</f>
@@ -2662,7 +2668,7 @@
     </row>
     <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B9" s="49">
         <f>Штат!P42</f>
@@ -2679,7 +2685,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B10" s="49">
         <f>Штат!R42</f>
@@ -2696,62 +2702,62 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>4</v>
+        <v>568</v>
       </c>
       <c r="B11" s="49">
         <f>Командировки!I26</f>
-        <v>6158851.2096774196</v>
+        <v>3916750.4032258065</v>
       </c>
       <c r="C11" s="49">
         <f>Командировки!J26</f>
-        <v>37657517.125</v>
+        <v>32781517.125</v>
       </c>
       <c r="D11" s="50">
         <f>C11/12</f>
-        <v>3138126.4270833335</v>
+        <v>2731793.09375</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B12" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I183,'Оснащение и офис'!A5:A183,"Оснащение")</f>
-        <v>33792727</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I184,'Оснащение и офис'!A5:A184,"Оснащение")</f>
+        <v>33823753</v>
       </c>
       <c r="C12" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J183,'Оснащение и офис'!A5:A183,"Оснащение")</f>
+        <f>SUMIFS('Оснащение и офис'!J5:J184,'Оснащение и офис'!A5:A184,"Оснащение")</f>
         <v>5850000</v>
       </c>
       <c r="D12" s="50"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I183,'Оснащение и офис'!A5:A183,"Офис")</f>
-        <v>21976663.496774193</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I184,'Оснащение и офис'!A5:A184,"Офис")</f>
+        <v>21748663.496774193</v>
       </c>
       <c r="C13" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J183,'Оснащение и офис'!A5:A183,"Офис")</f>
-        <v>68938825.199999988</v>
+        <f>SUMIFS('Оснащение и офис'!J5:J184,'Оснащение и офис'!A5:A184,"Офис")</f>
+        <v>68026825.199999988</v>
       </c>
       <c r="D13" s="50">
         <f>C13/12</f>
-        <v>5744902.0999999987</v>
+        <v>5668902.0999999987</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B14" s="51">
-        <f>'Оснащение и офис'!I41</f>
+        <f>'Оснащение и офис'!I42</f>
         <v>11560261.396774193</v>
       </c>
       <c r="C14" s="51">
-        <f>'Оснащение и офис'!J41</f>
+        <f>'Оснащение и офис'!J42</f>
         <v>58909825.199999996</v>
       </c>
       <c r="D14" s="51">
@@ -2761,28 +2767,28 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B15" s="51">
-        <f>'Оснащение и офис'!I42</f>
+        <f>'Оснащение и офис'!I43</f>
         <v>4909152.0999999996</v>
       </c>
       <c r="C15" s="51">
-        <f>'Оснащение и офис'!J42</f>
+        <f>'Оснащение и офис'!J43</f>
         <v>0</v>
       </c>
       <c r="D15" s="51"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B16" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I183,'Оснащение и офис'!A5:A183,"Цифровые")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I184,'Оснащение и офис'!A5:A184,"Цифровые")</f>
         <v>820500</v>
       </c>
       <c r="C16" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J183,'Оснащение и офис'!A5:A183,"Цифровые")</f>
+        <f>SUMIFS('Оснащение и офис'!J5:J184,'Оснащение и офис'!A5:A184,"Цифровые")</f>
         <v>9282000</v>
       </c>
       <c r="D16" s="50">
@@ -2792,14 +2798,14 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B17" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I183,'Оснащение и офис'!A5:A183,"Медиа")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I184,'Оснащение и офис'!A5:A184,"Медиа")</f>
         <v>3325000</v>
       </c>
       <c r="C17" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J183,'Оснащение и офис'!A5:A183,"Медиа")</f>
+        <f>SUMIFS('Оснащение и офис'!J5:J184,'Оснащение и офис'!A5:A184,"Медиа")</f>
         <v>25300000</v>
       </c>
       <c r="D17" s="50">
@@ -2809,7 +2815,7 @@
     </row>
     <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="45" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B18" s="52">
         <f>'Проекты (вне бюджета)'!G16</f>
@@ -2824,7 +2830,7 @@
         <v>127500000</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F18" s="54"/>
       <c r="G18" s="54"/>
@@ -2832,14 +2838,14 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I183,'Оснащение и офис'!A5:A183,"Прочие")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I184,'Оснащение и офис'!A5:A184,"Прочие")</f>
         <v>2300000</v>
       </c>
       <c r="C19" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J183,'Оснащение и офис'!A5:A183,"Прочие")</f>
+        <f>SUMIFS('Оснащение и офис'!J5:J184,'Оснащение и офис'!A5:A184,"Прочие")</f>
         <v>9400000</v>
       </c>
       <c r="D19" s="50">
@@ -2849,106 +2855,106 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" s="55">
         <f>B7+B8+B9+B10+B11+B12+B13+B16+B17+B19</f>
-        <v>141737769.01827955</v>
+        <v>139298694.21182796</v>
       </c>
       <c r="C20" s="55">
         <f>C7+C8+C9+C10+C11+C12+C13+C16+C17+C19</f>
-        <v>802827328.99166656</v>
+        <v>797039328.99166656</v>
       </c>
       <c r="D20" s="56">
         <f t="shared" si="0"/>
-        <v>66902277.41597221</v>
+        <v>66419944.082638882</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B21" s="49">
         <f>B20*Резерв</f>
-        <v>14173776.901827956</v>
+        <v>13929869.421182796</v>
       </c>
       <c r="C21" s="49">
         <f>C20*Резерв</f>
-        <v>80282732.899166659</v>
+        <v>79703932.899166659</v>
       </c>
       <c r="D21" s="50">
         <f t="shared" si="0"/>
-        <v>6690227.7415972212</v>
+        <v>6641994.4082638882</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" s="57">
         <f>B20+B21</f>
-        <v>155911545.92010751</v>
+        <v>153228563.63301075</v>
       </c>
       <c r="C22" s="57">
         <f>C20+C21</f>
-        <v>883110061.89083326</v>
+        <v>876743261.89083326</v>
       </c>
       <c r="D22" s="58">
         <f t="shared" si="0"/>
-        <v>73592505.157569438</v>
+        <v>73061938.490902767</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" s="49">
         <f>B22*НДС</f>
-        <v>24945847.347217202</v>
+        <v>24516570.181281719</v>
       </c>
       <c r="C23" s="49">
         <f>C22*НДС</f>
-        <v>141297609.90253332</v>
+        <v>140278921.90253332</v>
       </c>
       <c r="D23" s="50">
         <f t="shared" si="0"/>
-        <v>11774800.82521111</v>
+        <v>11689910.158544444</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B24" s="59">
         <f>B22+B23</f>
-        <v>180857393.26732472</v>
+        <v>177745133.81429246</v>
       </c>
       <c r="C24" s="60">
         <f>C22+C23</f>
-        <v>1024407671.7933666</v>
+        <v>1017022183.7933666</v>
       </c>
       <c r="D24" s="56">
         <f t="shared" si="0"/>
-        <v>85367305.982780546</v>
+        <v>84751848.649447218</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B25" s="61"/>
       <c r="C25" s="62">
         <f>B24+C24</f>
-        <v>1205265065.0606914</v>
+        <v>1194767317.6076591</v>
       </c>
       <c r="D25" s="48"/>
     </row>
     <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="40" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C26" s="64">
         <f>B18+C18</f>
@@ -2958,32 +2964,32 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B33" s="49">
         <f>Аренда_мес</f>
@@ -2992,7 +2998,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B34" s="55">
         <f>Аренда_с_НДС</f>
@@ -3001,7 +3007,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B35" s="49">
         <f>Аренда_депозит</f>
@@ -3010,7 +3016,7 @@
     </row>
     <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B36" s="49">
         <f>Аренда_мес-9856200</f>
@@ -3019,7 +3025,7 @@
     </row>
     <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B37" s="49">
         <f>Аренда_мес-5000000</f>
@@ -3028,7 +3034,7 @@
     </row>
     <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B38" s="49">
         <f>(5000000-Коммун_мес-Парковка_мест*Парковка_цена)/Площадь_офиса</f>
@@ -3037,7 +3043,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B39" s="49">
         <f>'Оснащение и офис'!I15</f>
@@ -3046,7 +3052,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B40" s="49">
         <f>'Оснащение и офис'!E16</f>
@@ -3055,16 +3061,16 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B41" s="49">
         <f>Канцелярия!F22</f>
-        <v>240750</v>
+        <v>164750</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B42" s="49">
         <f>SUM('Оснащение и офис'!I22:I25)</f>
@@ -3073,38 +3079,38 @@
     </row>
     <row r="44" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A44" s="65" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="66" t="s">
+        <v>518</v>
+      </c>
+      <c r="B45" s="75" t="s">
+        <v>519</v>
+      </c>
+      <c r="C45" s="67" t="s">
         <v>520</v>
       </c>
-      <c r="B45" s="75" t="s">
-        <v>521</v>
-      </c>
-      <c r="C45" s="67" t="s">
-        <v>522</v>
-      </c>
       <c r="D45" s="67" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="68" t="s">
+        <v>521</v>
+      </c>
+      <c r="B46" s="76" t="s">
+        <v>522</v>
+      </c>
+      <c r="C46" s="74" t="s">
         <v>523</v>
-      </c>
-      <c r="B46" s="76" t="s">
-        <v>524</v>
-      </c>
-      <c r="C46" s="74" t="s">
-        <v>525</v>
       </c>
       <c r="D46" s="69"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="68" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B47" s="77">
         <v>309.7</v>
@@ -3119,7 +3125,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="68" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B48" s="77">
         <v>340.67</v>
@@ -3134,7 +3140,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="68" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B49" s="77">
         <v>8.3702702702702698</v>
@@ -3149,7 +3155,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="68" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B50" s="78">
         <v>13500</v>
@@ -3164,31 +3170,31 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="68" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B51" s="78">
         <v>230107.1</v>
       </c>
       <c r="C51" s="71" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D51" s="71"/>
     </row>
     <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="68" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B52" s="78">
         <v>80000</v>
       </c>
       <c r="C52" s="71" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D52" s="71"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="68" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B53" s="78">
         <v>4909152.0999999996</v>
@@ -3203,7 +3209,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="68" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B54" s="78">
         <v>5694616.4359999998</v>
@@ -3218,7 +3224,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="68" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B55" s="78">
         <v>68335397.231999993</v>
@@ -3233,7 +3239,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="68" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B56" s="78">
         <v>-90847.900000000402</v>
@@ -3248,7 +3254,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="68" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B57" s="78">
         <v>11560261.396774201</v>
@@ -3263,7 +3269,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="68" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B58" s="78">
         <v>58909825.200000003</v>
@@ -3278,7 +3284,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="68" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B59" s="78">
         <v>4909152.0999999996</v>
@@ -3293,13 +3299,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="72" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B60" s="79">
-        <v>180857393.26732472</v>
+        <v>177745133.81429246</v>
       </c>
       <c r="C60" s="73">
-        <v>202034588.2518917</v>
+        <v>198922328.79885945</v>
       </c>
       <c r="D60" s="73">
         <f t="shared" si="1"/>
@@ -3308,13 +3314,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="72" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B61" s="79">
-        <v>1024407671.7933666</v>
+        <v>1017022183.7933666</v>
       </c>
       <c r="C61" s="73">
-        <v>1100156869.2381663</v>
+        <v>1092771381.2381663</v>
       </c>
       <c r="D61" s="73">
         <f t="shared" si="1"/>
@@ -3323,13 +3329,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="72" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B62" s="79">
-        <v>1205265065.0606914</v>
+        <v>1194767317.6076591</v>
       </c>
       <c r="C62" s="73">
-        <v>1302191457.4900515</v>
+        <v>1291693710.0370193</v>
       </c>
       <c r="D62" s="73">
         <f t="shared" si="1"/>
@@ -3338,12 +3344,12 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="82" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B65" s="82"/>
       <c r="C65" s="82"/>
@@ -3351,7 +3357,7 @@
     </row>
     <row r="66" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="82" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B66" s="82"/>
       <c r="C66" s="82"/>
@@ -3359,7 +3365,7 @@
     </row>
     <row r="67" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="82" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B67" s="82"/>
       <c r="C67" s="82"/>
@@ -3367,7 +3373,7 @@
     </row>
     <row r="68" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="82" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B68" s="82"/>
       <c r="C68" s="82"/>
@@ -3375,7 +3381,7 @@
     </row>
     <row r="69" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="82" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B69" s="82"/>
       <c r="C69" s="82"/>
@@ -3406,7 +3412,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3414,574 +3420,574 @@
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="11">
         <v>85000</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="11">
         <v>4325</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="11">
         <v>0.06</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="11">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="11">
         <v>0.05</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="11">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="11">
         <v>0.03</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="11">
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="11">
         <v>0.1</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="11">
         <v>0.02</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="11">
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="11">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="11">
         <v>200000</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="11">
         <v>28000</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" s="11">
         <v>530</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="11">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="11">
         <v>90000</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="11">
         <v>30000</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="11">
         <v>15000</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" s="11">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" s="11">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" s="11">
         <f>Авиа_РК+Отель_РК*Ночей_РК+Сут_РК*МРП*Дней_РК+Трансп_РК</f>
         <v>190950</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26" s="11">
         <f>Трансп_РК+Сут_РК*МРП</f>
         <v>23650</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" s="11">
         <v>900</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B28" s="11">
         <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11">
         <v>150</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B31" s="11">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" s="11">
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B33" s="11">
         <f>(Авиа_межд+Отель_межд*Ночей_межд+Сут_межд*Дней_межд+Страх_межд)*Курс</f>
         <v>1219000</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B34" s="11">
         <f>Площадь_офиса*Ставка_аренды_м2+Коммун_мес+Парковка_мест*Парковка_цена</f>
         <v>4909152.0999999996</v>
       </c>
       <c r="C34" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B35" s="11">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B36" s="11">
         <v>0.1</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B37" s="11">
         <v>0.16</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B42">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B43">
         <f>МРП*(1+Индекс_МРП_2027)</f>
         <v>4627.75</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B44">
         <f>Авиа_РК+Отель_РК*Ночей_РК+Сут_РК*МРП_2027*Дней_РК+Трансп_РК</f>
         <v>192766.5</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B45">
         <f>Трансп_РК+Сут_РК*МРП_2027</f>
         <v>24255.5</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B48" s="16">
         <f>ROUND((52.2+21.4+12.4+33.7+190)*1.1,2)</f>
         <v>340.67</v>
       </c>
       <c r="C48" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B49" s="5">
         <v>13500</v>
       </c>
       <c r="C49" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B50" s="5">
         <f>743*309.7</f>
         <v>230107.1</v>
       </c>
       <c r="C50" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B51" s="5">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B52" s="5">
         <v>40000</v>
       </c>
       <c r="C52" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B53" s="5">
         <f>Аренда_мес*(1+НДС)</f>
         <v>5694616.4359999988</v>
       </c>
       <c r="C53" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B54" s="5">
         <f>Аренда_мес*Депозит_мес</f>
         <v>4909152.0999999996</v>
       </c>
       <c r="C54" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B55" s="19">
         <f>11/31+2</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C55" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B57" s="18">
         <v>0.1</v>
       </c>
       <c r="C57" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B58" s="19">
         <f>Аренда_мес_2026</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C58" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4009,80 +4015,80 @@
   <sheetData>
     <row r="1" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="L4" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="W4" s="4"/>
     </row>
@@ -4091,19 +4097,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D5" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="F5" s="20" t="s">
         <v>113</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>114</v>
       </c>
       <c r="G5" s="20">
         <v>1</v>
@@ -4147,23 +4153,23 @@
         <v>7272920.0000000009</v>
       </c>
       <c r="R5" s="22">
-        <f>IF(E5="штат",ОСНС*G5*L5/12,0)</f>
+        <f t="shared" ref="R5:R41" si="7">IF(E5="штат",ОСНС*G5*L5/12,0)</f>
         <v>7000</v>
       </c>
       <c r="S5" s="22">
-        <f t="shared" ref="S5:S34" si="7">IF(E5="штат",(ДМС+ОСНС)*G5*M5/12,0)</f>
+        <f t="shared" ref="S5:S34" si="8">IF(E5="штат",(ДМС+ОСНС)*G5*M5/12,0)</f>
         <v>228000</v>
       </c>
       <c r="T5" s="22">
-        <f t="shared" ref="T5:T34" si="8">N5+P5+R5</f>
+        <f t="shared" ref="T5:T34" si="9">N5+P5+R5</f>
         <v>5461690</v>
       </c>
       <c r="U5" s="22">
-        <f t="shared" ref="U5:U34" si="9">O5+Q5+S5</f>
+        <f t="shared" ref="U5:U34" si="10">O5+Q5+S5</f>
         <v>29319680</v>
       </c>
       <c r="V5" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4171,19 +4177,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="20" t="s">
+        <v>424</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>426</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>428</v>
-      </c>
       <c r="D6" s="21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E6" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>113</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>114</v>
       </c>
       <c r="G6" s="20">
         <v>1</v>
@@ -4227,23 +4233,23 @@
         <v>6378680.0000000009</v>
       </c>
       <c r="R6" s="22">
-        <f>IF(E6="штат",ОСНС*G6*L6/12,0)</f>
+        <f t="shared" si="7"/>
         <v>7000</v>
       </c>
       <c r="S6" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T6" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4791010</v>
       </c>
       <c r="U6" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>25742720</v>
       </c>
       <c r="V6" s="20" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4251,19 +4257,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E7" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" s="20" t="s">
         <v>113</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>114</v>
       </c>
       <c r="G7" s="20">
         <v>1</v>
@@ -4307,23 +4313,23 @@
         <v>6378680.0000000009</v>
       </c>
       <c r="R7" s="22">
-        <f>IF(E7="штат",ОСНС*G7*L7/12,0)</f>
+        <f t="shared" si="7"/>
         <v>7000</v>
       </c>
       <c r="S7" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T7" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4791010</v>
       </c>
       <c r="U7" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>25742720</v>
       </c>
       <c r="V7" s="20" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4331,19 +4337,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D8" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>115</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>116</v>
       </c>
       <c r="G8" s="20">
         <v>1</v>
@@ -4387,23 +4393,23 @@
         <v>6378680.0000000009</v>
       </c>
       <c r="R8" s="22">
-        <f>IF(E8="штат",ОСНС*G8*L8/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S8" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T8" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3760685.2688172045</v>
       </c>
       <c r="U8" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>25742720</v>
       </c>
       <c r="V8" s="20" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4411,19 +4417,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G9" s="24">
         <v>1</v>
@@ -4467,23 +4473,23 @@
         <v>5931560</v>
       </c>
       <c r="R9" s="26">
-        <f>IF(E9="штат",ОСНС*G9*L9/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S9" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T9" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U9" s="26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>23954240</v>
       </c>
       <c r="V9" s="24" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4491,19 +4497,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G10" s="20">
         <v>1</v>
@@ -4547,23 +4553,23 @@
         <v>4590200</v>
       </c>
       <c r="R10" s="22">
-        <f>IF(E10="штат",ОСНС*G10*L10/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S10" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T10" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="U10" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>18588800</v>
       </c>
       <c r="V10" s="20" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4571,19 +4577,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G11" s="24">
         <v>1</v>
@@ -4595,27 +4601,27 @@
         <v>5</v>
       </c>
       <c r="J11" s="26">
-        <f t="shared" ref="J11" si="10">IF(E11="штат",ROUND(Ставка_СН*H11*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H11+Ставка_СО*MIN(H11*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H11,Кап_ООСМС*МЗП),0),ROUND(H11*НДС,0))</f>
+        <f t="shared" ref="J11" si="11">IF(E11="штат",ROUND(Ставка_СН*H11*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H11+Ставка_СО*MIN(H11*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H11,Кап_ООСМС*МЗП),0),ROUND(H11*НДС,0))</f>
         <v>147550</v>
       </c>
       <c r="K11" s="26">
-        <f t="shared" ref="K11" si="11">G11*(H11+J11)</f>
+        <f t="shared" ref="K11" si="12">G11*(H11+J11)</f>
         <v>1147550</v>
       </c>
       <c r="L11" s="27">
-        <f t="shared" ref="L11" si="12">IF(AND(F11="новая",I11=1),Мес_2026_новые,MAX(0,4-I11))</f>
+        <f t="shared" ref="L11" si="13">IF(AND(F11="новая",I11=1),Мес_2026_новые,MAX(0,4-I11))</f>
         <v>0</v>
       </c>
       <c r="M11" s="24">
-        <f t="shared" ref="M11" si="13">MAX(0,MIN(12,16-MAX(I11,4)))</f>
+        <f t="shared" ref="M11" si="14">MAX(0,MIN(12,16-MAX(I11,4)))</f>
         <v>11</v>
       </c>
       <c r="N11" s="26">
-        <f t="shared" ref="N11" si="14">K11*L11</f>
+        <f t="shared" ref="N11" si="15">K11*L11</f>
         <v>0</v>
       </c>
       <c r="O11" s="26">
-        <f t="shared" ref="O11" si="15">K11*M11</f>
+        <f t="shared" ref="O11" si="16">K11*M11</f>
         <v>12623050</v>
       </c>
       <c r="P11" s="26">
@@ -4623,27 +4629,27 @@
         <v>0</v>
       </c>
       <c r="Q11" s="26">
-        <f t="shared" ref="Q11" si="16">IF(E11="штат",Премия_KPI*H11*(1+J11/H11)*G11*M11/12,0)</f>
+        <f t="shared" ref="Q11" si="17">IF(E11="штат",Премия_KPI*H11*(1+J11/H11)*G11*M11/12,0)</f>
         <v>4207683.333333333</v>
       </c>
       <c r="R11" s="26">
-        <f>IF(E11="штат",ОСНС*G11*L11/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S11" s="26">
-        <f t="shared" ref="S11" si="17">IF(E11="штат",(ДМС+ОСНС)*G11*M11/12,0)</f>
+        <f t="shared" ref="S11" si="18">IF(E11="штат",(ДМС+ОСНС)*G11*M11/12,0)</f>
         <v>209000</v>
       </c>
       <c r="T11" s="26">
-        <f t="shared" ref="T11" si="18">N11+P11+R11</f>
+        <f t="shared" ref="T11" si="19">N11+P11+R11</f>
         <v>0</v>
       </c>
       <c r="U11" s="26">
-        <f t="shared" ref="U11" si="19">O11+Q11+S11</f>
+        <f t="shared" ref="U11" si="20">O11+Q11+S11</f>
         <v>17039733.333333332</v>
       </c>
       <c r="V11" s="24" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4651,19 +4657,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G12" s="24">
         <v>1</v>
@@ -4707,23 +4713,23 @@
         <v>2978103.3333333326</v>
       </c>
       <c r="R12" s="26">
-        <f>IF(E12="штат",ОСНС*G12*L12/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S12" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>209000</v>
       </c>
       <c r="T12" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U12" s="26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12121413.333333332</v>
       </c>
       <c r="V12" s="24" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4731,19 +4737,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G13" s="24">
         <v>1</v>
@@ -4787,23 +4793,23 @@
         <v>2978103.3333333326</v>
       </c>
       <c r="R13" s="26">
-        <f>IF(E13="штат",ОСНС*G13*L13/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S13" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>209000</v>
       </c>
       <c r="T13" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U13" s="26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12121413.333333332</v>
       </c>
       <c r="V13" s="24" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4811,19 +4817,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>435</v>
+      </c>
+      <c r="D14" s="25" t="s">
         <v>436</v>
       </c>
-      <c r="C14" s="25" t="s">
-        <v>437</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>438</v>
-      </c>
       <c r="E14" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G14" s="24">
         <v>1</v>
@@ -4867,23 +4873,23 @@
         <v>5437263.333333333</v>
       </c>
       <c r="R14" s="26">
-        <f>IF(E14="штат",ОСНС*G14*L14/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S14" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>209000</v>
       </c>
       <c r="T14" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U14" s="26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21958053.333333332</v>
       </c>
       <c r="V14" s="24" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4891,19 +4897,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G15" s="24">
         <v>1</v>
@@ -4947,23 +4953,23 @@
         <v>3387963.3333333335</v>
       </c>
       <c r="R15" s="26">
-        <f>IF(E15="штат",ОСНС*G15*L15/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S15" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>209000</v>
       </c>
       <c r="T15" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U15" s="26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13760853.333333334</v>
       </c>
       <c r="V15" s="24" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4971,19 +4977,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G16" s="24">
         <v>1</v>
@@ -5027,23 +5033,23 @@
         <v>3387963.3333333335</v>
       </c>
       <c r="R16" s="26">
-        <f>IF(E16="штат",ОСНС*G16*L16/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S16" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>209000</v>
       </c>
       <c r="T16" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U16" s="26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13760853.333333334</v>
       </c>
       <c r="V16" s="24" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5051,19 +5057,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G17" s="24">
         <v>1</v>
@@ -5075,27 +5081,27 @@
         <v>5</v>
       </c>
       <c r="J17" s="26">
-        <f t="shared" ref="J17:J18" si="20">IF(E17="штат",ROUND(Ставка_СН*H17*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H17+Ставка_СО*MIN(H17*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H17,Кап_ООСМС*МЗП),0),ROUND(H17*НДС,0))</f>
+        <f t="shared" ref="J17:J18" si="21">IF(E17="штат",ROUND(Ставка_СН*H17*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H17+Ставка_СО*MIN(H17*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H17,Кап_ООСМС*МЗП),0),ROUND(H17*НДС,0))</f>
         <v>182890</v>
       </c>
       <c r="K17" s="26">
-        <f t="shared" ref="K17:K18" si="21">G17*(H17+J17)</f>
+        <f t="shared" ref="K17:K18" si="22">G17*(H17+J17)</f>
         <v>1482890</v>
       </c>
       <c r="L17" s="27">
-        <f t="shared" ref="L17:L18" si="22">IF(AND(F17="новая",I17=1),Мес_2026_новые,MAX(0,4-I17))</f>
+        <f t="shared" ref="L17:L18" si="23">IF(AND(F17="новая",I17=1),Мес_2026_новые,MAX(0,4-I17))</f>
         <v>0</v>
       </c>
       <c r="M17" s="24">
-        <f t="shared" ref="M17:M18" si="23">MAX(0,MIN(12,16-MAX(I17,4)))</f>
+        <f t="shared" ref="M17:M18" si="24">MAX(0,MIN(12,16-MAX(I17,4)))</f>
         <v>11</v>
       </c>
       <c r="N17" s="26">
-        <f t="shared" ref="N17:N18" si="24">K17*L17</f>
+        <f t="shared" ref="N17:N18" si="25">K17*L17</f>
         <v>0</v>
       </c>
       <c r="O17" s="26">
-        <f t="shared" ref="O17:O18" si="25">K17*M17</f>
+        <f t="shared" ref="O17:O18" si="26">K17*M17</f>
         <v>16311790</v>
       </c>
       <c r="P17" s="26">
@@ -5103,27 +5109,27 @@
         <v>0</v>
       </c>
       <c r="Q17" s="26">
-        <f t="shared" ref="Q17:Q18" si="26">IF(E17="штат",Премия_KPI*H17*(1+J17/H17)*G17*M17/12,0)</f>
+        <f t="shared" ref="Q17:Q18" si="27">IF(E17="штат",Премия_KPI*H17*(1+J17/H17)*G17*M17/12,0)</f>
         <v>5437263.333333333</v>
       </c>
       <c r="R17" s="26">
-        <f>IF(E17="штат",ОСНС*G17*L17/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S17" s="26">
-        <f t="shared" ref="S17:S18" si="27">IF(E17="штат",(ДМС+ОСНС)*G17*M17/12,0)</f>
+        <f t="shared" ref="S17:S18" si="28">IF(E17="штат",(ДМС+ОСНС)*G17*M17/12,0)</f>
         <v>209000</v>
       </c>
       <c r="T17" s="26">
-        <f t="shared" ref="T17:T18" si="28">N17+P17+R17</f>
+        <f t="shared" ref="T17:T18" si="29">N17+P17+R17</f>
         <v>0</v>
       </c>
       <c r="U17" s="26">
-        <f t="shared" ref="U17:U18" si="29">O17+Q17+S17</f>
+        <f t="shared" ref="U17:U18" si="30">O17+Q17+S17</f>
         <v>21958053.333333332</v>
       </c>
       <c r="V17" s="24" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5131,19 +5137,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G18" s="20">
         <v>1</v>
@@ -5155,27 +5161,27 @@
         <v>1</v>
       </c>
       <c r="J18" s="22">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>159330</v>
       </c>
       <c r="K18" s="22">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1259330</v>
       </c>
       <c r="L18" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.3548387096774195</v>
       </c>
       <c r="M18" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>12</v>
       </c>
       <c r="N18" s="22">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2965519.0322580645</v>
       </c>
       <c r="O18" s="22">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15111960</v>
       </c>
       <c r="P18" s="22">
@@ -5183,27 +5189,27 @@
         <v>0</v>
       </c>
       <c r="Q18" s="22">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5037320</v>
       </c>
       <c r="R18" s="22">
-        <f>IF(E18="штат",ОСНС*G18*L18/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S18" s="22">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>228000</v>
       </c>
       <c r="T18" s="22">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2971013.6559139783</v>
       </c>
       <c r="U18" s="22">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>20377280</v>
       </c>
       <c r="V18" s="20" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5211,19 +5217,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>377</v>
-      </c>
       <c r="D19" s="21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G19" s="20">
         <v>1</v>
@@ -5267,23 +5273,23 @@
         <v>4590200</v>
       </c>
       <c r="R19" s="22">
-        <f>IF(E19="штат",ОСНС*G19*L19/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S19" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T19" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="U19" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>18588800</v>
       </c>
       <c r="V19" s="20" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5291,19 +5297,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>377</v>
-      </c>
       <c r="D20" s="25" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G20" s="24">
         <v>1</v>
@@ -5347,23 +5353,23 @@
         <v>4207683.333333333</v>
       </c>
       <c r="R20" s="26">
-        <f>IF(E20="штат",ОСНС*G20*L20/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S20" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>209000</v>
       </c>
       <c r="T20" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U20" s="26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>17039733.333333332</v>
       </c>
       <c r="V20" s="24" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5371,19 +5377,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>377</v>
-      </c>
       <c r="D21" s="21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G21" s="20">
         <v>1</v>
@@ -5427,23 +5433,23 @@
         <v>4590200</v>
       </c>
       <c r="R21" s="22">
-        <f>IF(E21="штат",ОСНС*G21*L21/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S21" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T21" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="U21" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>18588800</v>
       </c>
       <c r="V21" s="20" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5451,19 +5457,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G22" s="20">
         <v>1</v>
@@ -5507,23 +5513,23 @@
         <v>4590200</v>
       </c>
       <c r="R22" s="22">
-        <f>IF(E22="штат",ОСНС*G22*L22/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S22" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T22" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="U22" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>18588800</v>
       </c>
       <c r="V22" s="20" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5531,19 +5537,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G23" s="20">
         <v>1</v>
@@ -5587,23 +5593,23 @@
         <v>3248839.9999999995</v>
       </c>
       <c r="R23" s="22">
-        <f>IF(E23="штат",ОСНС*G23*L23/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S23" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T23" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1918118.1720430108</v>
       </c>
       <c r="U23" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13223360</v>
       </c>
       <c r="V23" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5611,19 +5617,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G24" s="24">
         <v>1</v>
@@ -5667,23 +5673,23 @@
         <v>2978103.3333333326</v>
       </c>
       <c r="R24" s="26">
-        <f>IF(E24="штат",ОСНС*G24*L24/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S24" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>209000</v>
       </c>
       <c r="T24" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U24" s="26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12121413.333333332</v>
       </c>
       <c r="V24" s="24" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5691,19 +5697,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G25" s="24">
         <v>1</v>
@@ -5715,27 +5721,27 @@
         <v>5</v>
       </c>
       <c r="J25" s="26">
-        <f t="shared" ref="J25:J26" si="30">IF(E25="штат",ROUND(Ставка_СН*H25*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H25+Ставка_СО*MIN(H25*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H25,Кап_ООСМС*МЗП),0),ROUND(H25*НДС,0))</f>
+        <f t="shared" ref="J25:J26" si="31">IF(E25="штат",ROUND(Ставка_СН*H25*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H25+Ставка_СО*MIN(H25*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H25,Кап_ООСМС*МЗП),0),ROUND(H25*НДС,0))</f>
         <v>112210</v>
       </c>
       <c r="K25" s="26">
-        <f t="shared" ref="K25:K26" si="31">G25*(H25+J25)</f>
+        <f t="shared" ref="K25:K26" si="32">G25*(H25+J25)</f>
         <v>812210</v>
       </c>
       <c r="L25" s="27">
-        <f t="shared" ref="L25:L26" si="32">IF(AND(F25="новая",I25=1),Мес_2026_новые,MAX(0,4-I25))</f>
+        <f t="shared" ref="L25:L26" si="33">IF(AND(F25="новая",I25=1),Мес_2026_новые,MAX(0,4-I25))</f>
         <v>0</v>
       </c>
       <c r="M25" s="24">
-        <f t="shared" ref="M25:M26" si="33">MAX(0,MIN(12,16-MAX(I25,4)))</f>
+        <f t="shared" ref="M25:M26" si="34">MAX(0,MIN(12,16-MAX(I25,4)))</f>
         <v>11</v>
       </c>
       <c r="N25" s="26">
-        <f t="shared" ref="N25:N26" si="34">K25*L25</f>
+        <f t="shared" ref="N25:N26" si="35">K25*L25</f>
         <v>0</v>
       </c>
       <c r="O25" s="26">
-        <f t="shared" ref="O25:O26" si="35">K25*M25</f>
+        <f t="shared" ref="O25:O26" si="36">K25*M25</f>
         <v>8934310</v>
       </c>
       <c r="P25" s="26">
@@ -5743,27 +5749,27 @@
         <v>0</v>
       </c>
       <c r="Q25" s="26">
-        <f t="shared" ref="Q25:Q26" si="36">IF(E25="штат",Премия_KPI*H25*(1+J25/H25)*G25*M25/12,0)</f>
+        <f t="shared" ref="Q25:Q26" si="37">IF(E25="штат",Премия_KPI*H25*(1+J25/H25)*G25*M25/12,0)</f>
         <v>2978103.3333333326</v>
       </c>
       <c r="R25" s="26">
-        <f>IF(E25="штат",ОСНС*G25*L25/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S25" s="26">
-        <f t="shared" ref="S25:S26" si="37">IF(E25="штат",(ДМС+ОСНС)*G25*M25/12,0)</f>
+        <f t="shared" ref="S25:S26" si="38">IF(E25="штат",(ДМС+ОСНС)*G25*M25/12,0)</f>
         <v>209000</v>
       </c>
       <c r="T25" s="26">
-        <f t="shared" ref="T25:T26" si="38">N25+P25+R25</f>
+        <f t="shared" ref="T25:T26" si="39">N25+P25+R25</f>
         <v>0</v>
       </c>
       <c r="U25" s="26">
-        <f t="shared" ref="U25:U26" si="39">O25+Q25+S25</f>
+        <f t="shared" ref="U25:U26" si="40">O25+Q25+S25</f>
         <v>12121413.333333332</v>
       </c>
       <c r="V25" s="24" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5771,19 +5777,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F26" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G26" s="24">
         <v>1</v>
@@ -5795,27 +5801,27 @@
         <v>5</v>
       </c>
       <c r="J26" s="26">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>123990</v>
       </c>
       <c r="K26" s="26">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>923990</v>
       </c>
       <c r="L26" s="27">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M26" s="24">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11</v>
       </c>
       <c r="N26" s="26">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="O26" s="26">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>10163890</v>
       </c>
       <c r="P26" s="26">
@@ -5823,27 +5829,27 @@
         <v>0</v>
       </c>
       <c r="Q26" s="26">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>3387963.3333333335</v>
       </c>
       <c r="R26" s="26">
-        <f>IF(E26="штат",ОСНС*G26*L26/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S26" s="26">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>209000</v>
       </c>
       <c r="T26" s="26">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="U26" s="26">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>13760853.333333334</v>
       </c>
       <c r="V26" s="24" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5851,19 +5857,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G27" s="20">
         <v>1</v>
@@ -5875,27 +5881,27 @@
         <v>1</v>
       </c>
       <c r="J27" s="22">
-        <f t="shared" ref="J27" si="40">IF(E27="штат",ROUND(Ставка_СН*H27*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H27+Ставка_СО*MIN(H27*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H27,Кап_ООСМС*МЗП),0),ROUND(H27*НДС,0))</f>
+        <f t="shared" ref="J27" si="41">IF(E27="штат",ROUND(Ставка_СН*H27*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H27+Ставка_СО*MIN(H27*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H27,Кап_ООСМС*МЗП),0),ROUND(H27*НДС,0))</f>
         <v>182890</v>
       </c>
       <c r="K27" s="22">
-        <f t="shared" ref="K27" si="41">G27*(H27+J27)</f>
+        <f t="shared" ref="K27" si="42">G27*(H27+J27)</f>
         <v>1482890</v>
       </c>
       <c r="L27" s="23">
-        <f t="shared" ref="L27" si="42">IF(AND(F27="новая",I27=1),Мес_2026_новые,MAX(0,4-I27))</f>
+        <f t="shared" ref="L27" si="43">IF(AND(F27="новая",I27=1),Мес_2026_новые,MAX(0,4-I27))</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="M27" s="20">
-        <f t="shared" ref="M27" si="43">MAX(0,MIN(12,16-MAX(I27,4)))</f>
+        <f t="shared" ref="M27" si="44">MAX(0,MIN(12,16-MAX(I27,4)))</f>
         <v>12</v>
       </c>
       <c r="N27" s="22">
-        <f t="shared" ref="N27" si="44">K27*L27</f>
+        <f t="shared" ref="N27" si="45">K27*L27</f>
         <v>3491966.7741935486</v>
       </c>
       <c r="O27" s="22">
-        <f t="shared" ref="O27" si="45">K27*M27</f>
+        <f t="shared" ref="O27" si="46">K27*M27</f>
         <v>17794680</v>
       </c>
       <c r="P27" s="22">
@@ -5903,27 +5909,27 @@
         <v>0</v>
       </c>
       <c r="Q27" s="22">
-        <f t="shared" ref="Q27" si="46">IF(E27="штат",Премия_KPI*H27*(1+J27/H27)*G27*M27/12,0)</f>
+        <f t="shared" ref="Q27" si="47">IF(E27="штат",Премия_KPI*H27*(1+J27/H27)*G27*M27/12,0)</f>
         <v>5931560</v>
       </c>
       <c r="R27" s="22">
-        <f>IF(E27="штат",ОСНС*G27*L27/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S27" s="22">
-        <f t="shared" ref="S27" si="47">IF(E27="штат",(ДМС+ОСНС)*G27*M27/12,0)</f>
+        <f t="shared" ref="S27" si="48">IF(E27="штат",(ДМС+ОСНС)*G27*M27/12,0)</f>
         <v>228000</v>
       </c>
       <c r="T27" s="22">
-        <f t="shared" ref="T27" si="48">N27+P27+R27</f>
+        <f t="shared" ref="T27" si="49">N27+P27+R27</f>
         <v>3497461.3978494625</v>
       </c>
       <c r="U27" s="22">
-        <f t="shared" ref="U27" si="49">O27+Q27+S27</f>
+        <f t="shared" ref="U27" si="50">O27+Q27+S27</f>
         <v>23954240</v>
       </c>
       <c r="V27" s="20" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5931,19 +5937,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="28" t="s">
+        <v>382</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>448</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="E28" s="28" t="s">
         <v>384</v>
       </c>
-      <c r="C28" s="29" t="s">
-        <v>450</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>370</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>386</v>
-      </c>
       <c r="F28" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G28" s="28">
         <v>0</v>
@@ -5987,23 +5993,23 @@
         <v>0</v>
       </c>
       <c r="R28" s="30">
-        <f>IF(E28="штат",ОСНС*G28*L28/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S28" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T28" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U28" s="30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="V28" s="28" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6011,19 +6017,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G29" s="20">
         <v>1</v>
@@ -6067,23 +6073,23 @@
         <v>5931560</v>
       </c>
       <c r="R29" s="22">
-        <f>IF(E29="штат",ОСНС*G29*L29/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S29" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T29" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3497461.3978494625</v>
       </c>
       <c r="U29" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>23954240</v>
       </c>
       <c r="V29" s="20" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6091,19 +6097,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G30" s="20">
         <v>1</v>
@@ -6147,23 +6153,23 @@
         <v>4590200</v>
       </c>
       <c r="R30" s="22">
-        <f>IF(E30="штат",ОСНС*G30*L30/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S30" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T30" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="U30" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>18588800</v>
       </c>
       <c r="V30" s="20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6171,19 +6177,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G31" s="28">
         <v>0</v>
@@ -6227,23 +6233,23 @@
         <v>0</v>
       </c>
       <c r="R31" s="30">
-        <f>IF(E31="штат",ОСНС*G31*L31/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S31" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T31" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U31" s="30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="V31" s="28" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6251,19 +6257,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G32" s="28">
         <v>0</v>
@@ -6275,27 +6281,27 @@
         <v>2</v>
       </c>
       <c r="J32" s="30">
-        <f t="shared" ref="J32" si="50">IF(E32="штат",ROUND(Ставка_СН*H32*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H32+Ставка_СО*MIN(H32*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H32,Кап_ООСМС*МЗП),0),ROUND(H32*НДС,0))</f>
+        <f t="shared" ref="J32" si="51">IF(E32="штат",ROUND(Ставка_СН*H32*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H32+Ставка_СО*MIN(H32*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H32,Кап_ООСМС*МЗП),0),ROUND(H32*НДС,0))</f>
         <v>112000</v>
       </c>
       <c r="K32" s="30">
-        <f t="shared" ref="K32" si="51">G32*(H32+J32)</f>
+        <f t="shared" ref="K32" si="52">G32*(H32+J32)</f>
         <v>0</v>
       </c>
       <c r="L32" s="31">
-        <f t="shared" ref="L32" si="52">IF(AND(F32="новая",I32=1),Мес_2026_новые,MAX(0,4-I32))</f>
+        <f t="shared" ref="L32" si="53">IF(AND(F32="новая",I32=1),Мес_2026_новые,MAX(0,4-I32))</f>
         <v>2</v>
       </c>
       <c r="M32" s="28">
-        <f t="shared" ref="M32" si="53">MAX(0,MIN(12,16-MAX(I32,4)))</f>
+        <f t="shared" ref="M32" si="54">MAX(0,MIN(12,16-MAX(I32,4)))</f>
         <v>12</v>
       </c>
       <c r="N32" s="30">
-        <f t="shared" ref="N32" si="54">K32*L32</f>
+        <f t="shared" ref="N32" si="55">K32*L32</f>
         <v>0</v>
       </c>
       <c r="O32" s="30">
-        <f t="shared" ref="O32" si="55">K32*M32</f>
+        <f t="shared" ref="O32" si="56">K32*M32</f>
         <v>0</v>
       </c>
       <c r="P32" s="30">
@@ -6303,27 +6309,27 @@
         <v>0</v>
       </c>
       <c r="Q32" s="30">
-        <f t="shared" ref="Q32" si="56">IF(E32="штат",Премия_KPI*H32*(1+J32/H32)*G32*M32/12,0)</f>
+        <f t="shared" ref="Q32" si="57">IF(E32="штат",Премия_KPI*H32*(1+J32/H32)*G32*M32/12,0)</f>
         <v>0</v>
       </c>
       <c r="R32" s="30">
-        <f>IF(E32="штат",ОСНС*G32*L32/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S32" s="30">
-        <f t="shared" ref="S32" si="57">IF(E32="штат",(ДМС+ОСНС)*G32*M32/12,0)</f>
+        <f t="shared" ref="S32" si="58">IF(E32="штат",(ДМС+ОСНС)*G32*M32/12,0)</f>
         <v>0</v>
       </c>
       <c r="T32" s="30">
-        <f t="shared" ref="T32" si="58">N32+P32+R32</f>
+        <f t="shared" ref="T32" si="59">N32+P32+R32</f>
         <v>0</v>
       </c>
       <c r="U32" s="30">
-        <f t="shared" ref="U32" si="59">O32+Q32+S32</f>
+        <f t="shared" ref="U32" si="60">O32+Q32+S32</f>
         <v>0</v>
       </c>
       <c r="V32" s="28" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6331,19 +6337,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G33" s="28">
         <v>0</v>
@@ -6387,23 +6393,23 @@
         <v>0</v>
       </c>
       <c r="R33" s="30">
-        <f>IF(E33="штат",ОСНС*G33*L33/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S33" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T33" s="30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U33" s="30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="V33" s="28" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6411,19 +6417,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G34" s="20">
         <v>1</v>
@@ -6467,23 +6473,23 @@
         <v>4590200</v>
       </c>
       <c r="R34" s="22">
-        <f>IF(E34="штат",ОСНС*G34*L34/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S34" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228000</v>
       </c>
       <c r="T34" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="U34" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>18588800</v>
       </c>
       <c r="V34" s="20" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6491,19 +6497,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G35" s="20">
         <v>1</v>
@@ -6515,11 +6521,11 @@
         <v>1</v>
       </c>
       <c r="J35" s="22">
-        <f t="shared" ref="J35:J41" si="60">IF(E35="штат",ROUND(Ставка_СН*H35*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H35+Ставка_СО*MIN(H35*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H35,Кап_ООСМС*МЗП),0),ROUND(H35*НДС,0))</f>
+        <f t="shared" ref="J35:J41" si="61">IF(E35="штат",ROUND(Ставка_СН*H35*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H35+Ставка_СО*MIN(H35*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H35,Кап_ООСМС*МЗП),0),ROUND(H35*НДС,0))</f>
         <v>112210</v>
       </c>
       <c r="K35" s="22">
-        <f t="shared" ref="K35:K41" si="61">G35*(H35+J35)</f>
+        <f t="shared" ref="K35:K41" si="62">G35*(H35+J35)</f>
         <v>812210</v>
       </c>
       <c r="L35" s="23">
@@ -6527,15 +6533,15 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M35" s="20">
-        <f t="shared" ref="M35:M41" si="62">MAX(0,MIN(12,16-MAX(I35,4)))</f>
+        <f t="shared" ref="M35:M41" si="63">MAX(0,MIN(12,16-MAX(I35,4)))</f>
         <v>12</v>
       </c>
       <c r="N35" s="22">
-        <f t="shared" ref="N35:N41" si="63">K35*L35</f>
+        <f t="shared" ref="N35:N41" si="64">K35*L35</f>
         <v>1912623.548387097</v>
       </c>
       <c r="O35" s="22">
-        <f t="shared" ref="O35:O41" si="64">K35*M35</f>
+        <f t="shared" ref="O35:O41" si="65">K35*M35</f>
         <v>9746520</v>
       </c>
       <c r="P35" s="22">
@@ -6543,27 +6549,27 @@
         <v>0</v>
       </c>
       <c r="Q35" s="22">
-        <f t="shared" ref="Q35:Q41" si="65">IF(E35="штат",Премия_KPI*H35*(1+J35/H35)*G35*M35/12,0)</f>
+        <f t="shared" ref="Q35:Q41" si="66">IF(E35="штат",Премия_KPI*H35*(1+J35/H35)*G35*M35/12,0)</f>
         <v>3248839.9999999995</v>
       </c>
       <c r="R35" s="22">
-        <f>IF(E35="штат",ОСНС*G35*L35/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S35" s="22">
-        <f t="shared" ref="S35:S41" si="66">IF(E35="штат",(ДМС+ОСНС)*G35*M35/12,0)</f>
+        <f t="shared" ref="S35:S41" si="67">IF(E35="штат",(ДМС+ОСНС)*G35*M35/12,0)</f>
         <v>228000</v>
       </c>
       <c r="T35" s="22">
-        <f t="shared" ref="T35:T41" si="67">N35+P35+R35</f>
+        <f t="shared" ref="T35:T41" si="68">N35+P35+R35</f>
         <v>1918118.1720430108</v>
       </c>
       <c r="U35" s="22">
-        <f t="shared" ref="U35:U41" si="68">O35+Q35+S35</f>
+        <f t="shared" ref="U35:U41" si="69">O35+Q35+S35</f>
         <v>13223360</v>
       </c>
       <c r="V35" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6571,19 +6577,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G36" s="28">
         <v>0</v>
@@ -6595,11 +6601,11 @@
         <v>2</v>
       </c>
       <c r="J36" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>112000</v>
       </c>
       <c r="K36" s="30">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="L36" s="31">
@@ -6607,15 +6613,15 @@
         <v>2</v>
       </c>
       <c r="M36" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>12</v>
       </c>
       <c r="N36" s="30">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="O36" s="30">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="P36" s="30">
@@ -6623,27 +6629,27 @@
         <v>0</v>
       </c>
       <c r="Q36" s="30">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="R36" s="30">
-        <f>IF(E36="штат",ОСНС*G36*L36/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S36" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="T36" s="30">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="U36" s="30">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="V36" s="28" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6651,19 +6657,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E37" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" s="20" t="s">
         <v>113</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>114</v>
       </c>
       <c r="G37" s="20">
         <v>1</v>
@@ -6675,11 +6681,11 @@
         <v>1</v>
       </c>
       <c r="J37" s="22">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>194670</v>
       </c>
       <c r="K37" s="22">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1594670</v>
       </c>
       <c r="L37" s="23">
@@ -6687,15 +6693,15 @@
         <v>3</v>
       </c>
       <c r="M37" s="20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>12</v>
       </c>
       <c r="N37" s="22">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>4784010</v>
       </c>
       <c r="O37" s="22">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>19136040</v>
       </c>
       <c r="P37" s="22">
@@ -6703,27 +6709,27 @@
         <v>0</v>
       </c>
       <c r="Q37" s="22">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>6378680.0000000009</v>
       </c>
       <c r="R37" s="22">
-        <f>IF(E37="штат",ОСНС*G37*L37/12,0)</f>
+        <f t="shared" si="7"/>
         <v>7000</v>
       </c>
       <c r="S37" s="22">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>228000</v>
       </c>
       <c r="T37" s="22">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>4791010</v>
       </c>
       <c r="U37" s="22">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>25742720</v>
       </c>
       <c r="V37" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6731,19 +6737,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G38" s="20">
         <v>1</v>
@@ -6755,11 +6761,11 @@
         <v>1</v>
       </c>
       <c r="J38" s="22">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>112210</v>
       </c>
       <c r="K38" s="22">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>812210</v>
       </c>
       <c r="L38" s="23">
@@ -6767,15 +6773,15 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M38" s="20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>12</v>
       </c>
       <c r="N38" s="22">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1912623.548387097</v>
       </c>
       <c r="O38" s="22">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>9746520</v>
       </c>
       <c r="P38" s="22">
@@ -6783,27 +6789,27 @@
         <v>0</v>
       </c>
       <c r="Q38" s="22">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>3248839.9999999995</v>
       </c>
       <c r="R38" s="22">
-        <f>IF(E38="штат",ОСНС*G38*L38/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S38" s="22">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>228000</v>
       </c>
       <c r="T38" s="22">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>1918118.1720430108</v>
       </c>
       <c r="U38" s="22">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>13223360</v>
       </c>
       <c r="V38" s="20" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6811,19 +6817,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G39" s="20">
         <v>1</v>
@@ -6835,11 +6841,11 @@
         <v>1</v>
       </c>
       <c r="J39" s="22">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>171110</v>
       </c>
       <c r="K39" s="22">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>1371110</v>
       </c>
       <c r="L39" s="23">
@@ -6847,15 +6853,15 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M39" s="20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>12</v>
       </c>
       <c r="N39" s="22">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>3228742.9032258065</v>
       </c>
       <c r="O39" s="22">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>16453320</v>
       </c>
       <c r="P39" s="22">
@@ -6863,27 +6869,27 @@
         <v>0</v>
       </c>
       <c r="Q39" s="22">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>5484440</v>
       </c>
       <c r="R39" s="22">
-        <f>IF(E39="штат",ОСНС*G39*L39/12,0)</f>
+        <f t="shared" si="7"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="S39" s="22">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>228000</v>
       </c>
       <c r="T39" s="22">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>3234237.5268817204</v>
       </c>
       <c r="U39" s="22">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>22165760</v>
       </c>
       <c r="V39" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6891,19 +6897,19 @@
         <v>36</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G40" s="28">
         <v>0</v>
@@ -6915,11 +6921,11 @@
         <v>1</v>
       </c>
       <c r="J40" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>160000</v>
       </c>
       <c r="K40" s="30">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="L40" s="31">
@@ -6927,15 +6933,15 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M40" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>12</v>
       </c>
       <c r="N40" s="30">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="O40" s="30">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="P40" s="30">
@@ -6943,27 +6949,27 @@
         <v>0</v>
       </c>
       <c r="Q40" s="30">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="R40" s="30">
-        <f>IF(E40="штат",ОСНС*G40*L40/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S40" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="T40" s="30">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="U40" s="30">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="V40" s="28" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6971,19 +6977,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G41" s="28">
         <v>0</v>
@@ -6995,11 +7001,11 @@
         <v>1</v>
       </c>
       <c r="J41" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>112000</v>
       </c>
       <c r="K41" s="30">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="L41" s="31">
@@ -7007,15 +7013,15 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M41" s="28">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>12</v>
       </c>
       <c r="N41" s="30">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="O41" s="30">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="P41" s="30">
@@ -7023,34 +7029,34 @@
         <v>0</v>
       </c>
       <c r="Q41" s="30">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="R41" s="30">
-        <f>IF(E41="штат",ОСНС*G41*L41/12,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S41" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="T41" s="30">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="U41" s="30">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="V41" s="28" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D42" s="10"/>
       <c r="E42" s="10"/>
@@ -7076,38 +7082,38 @@
         <v>58691747.741935484</v>
       </c>
       <c r="O42" s="8">
-        <f t="shared" ref="O42:U42" si="69">SUM(O5:O41)</f>
+        <f t="shared" ref="O42:U42" si="70">SUM(O5:O41)</f>
         <v>419273990</v>
       </c>
       <c r="P42" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Q42" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>139757996.66666666</v>
       </c>
       <c r="R42" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>104924.73118279572</v>
       </c>
       <c r="S42" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>6631000</v>
       </c>
       <c r="T42" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>58796672.473118283</v>
       </c>
       <c r="U42" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>565662986.66666663</v>
       </c>
       <c r="V42" s="10"/>
     </row>
     <row r="43" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G43">
         <f>SUM(G8:G13)+SUM(G17:G36)</f>
@@ -7120,7 +7126,7 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G44">
         <f>SUM(G5:G7)+SUM(G14:G16)+SUM(G37:G41)</f>
@@ -7157,42 +7163,42 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="33" t="s">
+        <v>467</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="F3" s="33" t="s">
         <v>469</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="G3" s="33" t="s">
         <v>470</v>
       </c>
-      <c r="F3" s="33" t="s">
-        <v>471</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>472</v>
-      </c>
       <c r="H3" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I3" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="J3" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="J3" s="33" t="s">
-        <v>105</v>
-      </c>
       <c r="K3" s="33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L3" s="33">
         <v>2027</v>
@@ -7203,13 +7209,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E4" s="36">
         <v>1000000</v>
@@ -7247,13 +7253,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E5" s="36">
         <v>700000</v>
@@ -7291,13 +7297,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="35" t="s">
+        <v>475</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="D6" s="35" t="s">
         <v>477</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>478</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>479</v>
       </c>
       <c r="E6" s="36">
         <v>1000000</v>
@@ -7335,13 +7341,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="35" t="s">
+        <v>478</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>479</v>
+      </c>
+      <c r="D7" s="35" t="s">
         <v>480</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>481</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>482</v>
       </c>
       <c r="E7" s="36">
         <v>1000000</v>
@@ -7379,13 +7385,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E8" s="36">
         <v>700000</v>
@@ -7423,13 +7429,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E9" s="36">
         <v>700000</v>
@@ -7467,13 +7473,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E10" s="36">
         <v>700000</v>
@@ -7509,7 +7515,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="38"/>
       <c r="B11" s="38" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
@@ -7558,41 +7564,41 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="J4" s="3">
         <v>2027</v>
@@ -7614,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="19">
         <f>Штат!L5</f>
@@ -7625,12 +7631,12 @@
         <v>12</v>
       </c>
       <c r="I5" s="5">
-        <f>C5*(D5/12*G5*Поездка_РК+E5*G5*Поездка_местн)</f>
+        <f t="shared" ref="I5:I24" si="0">C5*(D5/12*G5*Поездка_РК+E5*G5*Поездка_местн)</f>
         <v>190950</v>
       </c>
       <c r="J5" s="5">
-        <f t="shared" ref="J5:J24" si="0">C5*(D5/12*H5*Поездка_РК_2027+E5*H5*Поездка_местн_2027+F5/12*H5*Поездка_межд)</f>
-        <v>1990066</v>
+        <f t="shared" ref="J5:J24" si="1">C5*(D5/12*H5*Поездка_РК_2027+E5*H5*Поездка_местн_2027+F5/12*H5*Поездка_межд)</f>
+        <v>771066</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7649,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="19">
         <f>Штат!L6</f>
@@ -7660,12 +7666,12 @@
         <v>12</v>
       </c>
       <c r="I6" s="5">
-        <f>C6*(D6/12*G6*Поездка_РК+E6*G6*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>286425</v>
       </c>
       <c r="J6" s="5">
-        <f t="shared" si="0"/>
-        <v>2375599</v>
+        <f t="shared" si="1"/>
+        <v>1156599</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7695,11 +7701,11 @@
         <v>12</v>
       </c>
       <c r="I7" s="5">
-        <f>C7*(D7/12*G7*Поездка_РК+E7*G7*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>95475</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>385533</v>
       </c>
     </row>
@@ -7730,11 +7736,11 @@
         <v>12</v>
       </c>
       <c r="I8" s="5">
-        <f>C8*(D8/12*G8*Поездка_РК+E8*G8*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7754,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="19">
         <f>Штат!L39</f>
@@ -7765,12 +7771,12 @@
         <v>12</v>
       </c>
       <c r="I9" s="5">
-        <f>C9*(D9/12*G9*Поездка_РК+E9*G9*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>37471.370967741932</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="0"/>
-        <v>1411766.5</v>
+        <f t="shared" si="1"/>
+        <v>192766.5</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7789,7 +7795,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="19">
         <f>Штат!L8</f>
@@ -7800,17 +7806,17 @@
         <v>12</v>
       </c>
       <c r="I10" s="5">
-        <f>C10*(D10/12*G10*Поездка_РК+E10*G10*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>374713.70967741939</v>
       </c>
       <c r="J10" s="5">
-        <f t="shared" si="0"/>
-        <v>3146665</v>
+        <f t="shared" si="1"/>
+        <v>1927665</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G9:G13)</f>
@@ -7834,17 +7840,17 @@
         <v>12</v>
       </c>
       <c r="I11" s="5">
-        <f>C11*(D11/12*G11*Поездка_РК+E11*G11*Поездка_местн)</f>
-        <v>1397449.5967741937</v>
+        <f>SUMPRODUCT((Штат!I9:I13&lt;=3)*Штат!G9:G13)*(D11/12*G11*Поездка_РК+E11*G11*Поездка_местн)</f>
+        <v>279489.91935483873</v>
       </c>
       <c r="J11" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7257487.5</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C12">
         <f>SUM(Штат!G17:G26)</f>
@@ -7868,17 +7874,17 @@
         <v>12</v>
       </c>
       <c r="I12" s="5">
-        <f>C12*(D12/12*G12*Поездка_РК+E12*G12*Поездка_местн)</f>
-        <v>2248282.2580645164</v>
+        <f>SUMPRODUCT((Штат!I17:I26&lt;=3)*Штат!G17:G26)*(D12/12*G12*Поездка_РК+E12*G12*Поездка_местн)</f>
+        <v>1124141.1290322582</v>
       </c>
       <c r="J12" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11565990</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C13">
         <f>SUM(Штат!G14:G16)</f>
@@ -7902,17 +7908,17 @@
         <v>11</v>
       </c>
       <c r="I13" s="5">
-        <f>C13*(D13/12*G13*Поездка_РК+E13*G13*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1590323.625</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C14">
         <f>SUM(Штат!G27:G28)</f>
@@ -7936,17 +7942,17 @@
         <v>12</v>
       </c>
       <c r="I14" s="5">
-        <f>C14*(D14/12*G14*Поездка_РК+E14*G14*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>37471.370967741932</v>
       </c>
       <c r="J14" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>192766.5</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C15">
         <f>SUM(Штат!G29:G36)</f>
@@ -7970,11 +7976,11 @@
         <v>12</v>
       </c>
       <c r="I15" s="5">
-        <f>C15*(D15/12*G15*Поездка_РК+E15*G15*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>1490612.9032258065</v>
       </c>
       <c r="J15" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7741320</v>
       </c>
     </row>
@@ -7984,11 +7990,11 @@
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
       <c r="I16" s="5">
-        <f>C16*(D16/12*G16*Поездка_РК+E16*G16*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J16" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7998,11 +8004,11 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
       <c r="I17" s="5">
-        <f>C17*(D17/12*G17*Поездка_РК+E17*G17*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J17" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8012,11 +8018,11 @@
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="I18" s="5">
-        <f>C18*(D18/12*G18*Поездка_РК+E18*G18*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J18" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8026,11 +8032,11 @@
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
       <c r="I19" s="5">
-        <f>C19*(D19/12*G19*Поездка_РК+E19*G19*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J19" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8040,11 +8046,11 @@
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
       <c r="I20" s="5">
-        <f>C20*(D20/12*G20*Поездка_РК+E20*G20*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J20" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8054,11 +8060,11 @@
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
       <c r="I21" s="5">
-        <f>C21*(D21/12*G21*Поездка_РК+E21*G21*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8068,11 +8074,11 @@
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
       <c r="I22" s="5">
-        <f>C22*(D22/12*G22*Поездка_РК+E22*G22*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J22" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8082,11 +8088,11 @@
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
       <c r="I23" s="5">
-        <f>C23*(D23/12*G23*Поездка_РК+E23*G23*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J23" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8096,11 +8102,11 @@
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
       <c r="I24" s="5">
-        <f>C24*(D24/12*G24*Поездка_РК+E24*G24*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J24" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -8120,7 +8126,7 @@
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -8131,11 +8137,11 @@
       <c r="H26" s="10"/>
       <c r="I26" s="8">
         <f>SUM(I5:I25)</f>
-        <v>6158851.2096774196</v>
+        <v>3916750.4032258065</v>
       </c>
       <c r="J26" s="8">
         <f>SUM(J5:J25)</f>
-        <v>37657517.125</v>
+        <v>32781517.125</v>
       </c>
     </row>
   </sheetData>
@@ -8149,7 +8155,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -8163,41 +8169,41 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J4" s="3">
         <v>2027</v>
@@ -8205,13 +8211,13 @@
     </row>
     <row r="5" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" t="s">
         <v>137</v>
-      </c>
-      <c r="C5" t="s">
-        <v>138</v>
       </c>
       <c r="D5" s="12">
         <v>12</v>
@@ -8220,32 +8226,32 @@
         <v>450000</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G5" s="12">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I40" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
+        <f t="shared" ref="I5:I41" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
         <v>5400000</v>
       </c>
       <c r="J5" s="5">
-        <f t="shared" ref="J5:J39" si="1">IF(F5="разово",IF(AND(G5&gt;3,G5&lt;=15),D5*E5,0),IF(F5="мес",D5*E5*MAX(0,MIN(12,16-MAX(G5,4))),D5*E5*MAX(0,MIN(12,16-MAX(G5,4)))/12))</f>
+        <f t="shared" ref="J5:J40" si="1">IF(F5="разово",IF(AND(G5&gt;3,G5&lt;=15),D5*E5,0),IF(F5="мес",D5*E5*MAX(0,MIN(12,16-MAX(G5,4))),D5*E5*MAX(0,MIN(12,16-MAX(G5,4)))/12))</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D6" s="12">
         <v>2</v>
@@ -8254,13 +8260,13 @@
         <v>900000</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G6" s="12">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -8273,13 +8279,13 @@
     </row>
     <row r="7" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D7" s="12">
         <v>11</v>
@@ -8288,13 +8294,13 @@
         <v>450000</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G7" s="12">
         <v>4</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" ref="I7:I8" si="2">IF(F7="разово",IF(G7&lt;=3,D7*E7,0),IF(F7="мес",D7*E7*MAX(0,4-G7),D7*E7*MAX(0,4-G7)/12))</f>
@@ -8307,13 +8313,13 @@
     </row>
     <row r="8" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D8" s="12">
         <v>1</v>
@@ -8322,13 +8328,13 @@
         <v>900000</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G8" s="12">
         <v>4</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
@@ -8341,13 +8347,13 @@
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" t="s">
         <v>141</v>
-      </c>
-      <c r="C9" t="s">
-        <v>142</v>
       </c>
       <c r="D9" s="12">
         <v>15</v>
@@ -8356,13 +8362,13 @@
         <v>100000</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G9" s="12">
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
@@ -8375,13 +8381,13 @@
     </row>
     <row r="10" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" t="s">
         <v>144</v>
-      </c>
-      <c r="C10" t="s">
-        <v>145</v>
       </c>
       <c r="D10" s="12">
         <v>19</v>
@@ -8390,13 +8396,13 @@
         <v>200000</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G10" s="12">
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
@@ -8409,13 +8415,13 @@
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D11" s="12">
         <v>5</v>
@@ -8424,13 +8430,13 @@
         <v>500000</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G11" s="12">
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
@@ -8443,13 +8449,13 @@
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" s="12">
         <v>1</v>
@@ -8458,7 +8464,7 @@
         <v>800000</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G12" s="12">
         <v>1</v>
@@ -8475,13 +8481,13 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D13" s="12">
         <v>1</v>
@@ -8490,7 +8496,7 @@
         <v>500000</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G13" s="12">
         <v>1</v>
@@ -8507,13 +8513,13 @@
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="12">
         <v>1</v>
@@ -8522,13 +8528,13 @@
         <v>450000</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G14" s="12">
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
@@ -8541,13 +8547,13 @@
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15" s="12">
         <v>6</v>
@@ -8556,13 +8562,13 @@
         <v>60000</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G15" s="12">
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
@@ -8575,13 +8581,13 @@
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
@@ -8591,13 +8597,13 @@
         <v>841000</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G16" s="12">
         <v>1</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
@@ -8610,13 +8616,13 @@
     </row>
     <row r="17" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D17" s="12">
         <v>1</v>
@@ -8625,13 +8631,13 @@
         <v>2500000</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G17" s="12">
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
@@ -8644,13 +8650,13 @@
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D18" s="12">
         <v>1</v>
@@ -8659,7 +8665,7 @@
         <v>300000</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G18" s="12">
         <v>1</v>
@@ -8676,13 +8682,13 @@
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D19" s="12">
         <v>2</v>
@@ -8691,13 +8697,13 @@
         <v>280000</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G19" s="12">
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
@@ -8710,13 +8716,13 @@
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D20" s="12">
         <v>4</v>
@@ -8725,13 +8731,13 @@
         <v>55000</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G20" s="12">
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
@@ -8744,13 +8750,13 @@
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D21" s="12">
         <v>1</v>
@@ -8759,13 +8765,13 @@
         <v>300000</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G21" s="12">
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
@@ -8778,13 +8784,13 @@
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D22" s="12">
         <v>1</v>
@@ -8794,13 +8800,13 @@
         <v>36500</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G22" s="12">
         <v>1</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
@@ -8813,13 +8819,13 @@
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C23" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D23" s="12">
         <v>1</v>
@@ -8829,13 +8835,13 @@
         <v>5172</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G23" s="12">
         <v>1</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
@@ -8848,13 +8854,13 @@
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D24" s="12">
         <v>1</v>
@@ -8864,13 +8870,13 @@
         <v>98558</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G24" s="12">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -8883,13 +8889,13 @@
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D25" s="12">
         <v>1</v>
@@ -8899,13 +8905,13 @@
         <v>41983</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G25" s="12">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -8918,13 +8924,13 @@
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D26" s="12">
         <v>31</v>
@@ -8934,13 +8940,13 @@
         <v>3550</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G26" s="12">
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -8953,13 +8959,13 @@
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D27" s="12">
         <v>5</v>
@@ -8969,13 +8975,13 @@
         <v>5259</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G27" s="12">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -8988,13 +8994,13 @@
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D28" s="12">
         <v>4</v>
@@ -9004,13 +9010,13 @@
         <v>6237</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G28" s="12">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="0"/>
@@ -9023,13 +9029,13 @@
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D29" s="12">
         <v>5</v>
@@ -9039,13 +9045,13 @@
         <v>7792</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -9058,13 +9064,13 @@
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" s="12">
         <v>10</v>
@@ -9074,13 +9080,13 @@
         <v>76984</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" ref="I30" si="4">IF(F30="разово",IF(G30&lt;=3,D30*E30,0),IF(F30="мес",D30*E30*MAX(0,4-G30),D30*E30*MAX(0,4-G30)/12))</f>
@@ -9093,13 +9099,13 @@
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31" s="12">
         <v>1</v>
@@ -9109,13 +9115,13 @@
         <v>853446</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G31" s="12">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
@@ -9128,13 +9134,13 @@
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D32" s="12">
         <v>1</v>
@@ -9144,13 +9150,13 @@
         <v>43095</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G32" s="12">
         <v>1</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
@@ -9163,13 +9169,13 @@
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D33" s="12">
         <v>1</v>
@@ -9178,13 +9184,13 @@
         <v>300000</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G33" s="12">
         <v>1</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="0"/>
@@ -9197,13 +9203,13 @@
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C34" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D34" s="12">
         <v>1</v>
@@ -9212,13 +9218,13 @@
         <v>800000</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -9231,13 +9237,13 @@
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D35" s="12">
         <v>1</v>
@@ -9246,7 +9252,7 @@
         <v>700000</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G35" s="12">
         <v>1</v>
@@ -9263,13 +9269,13 @@
     </row>
     <row r="36" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C36" t="s">
         <v>154</v>
-      </c>
-      <c r="C36" t="s">
-        <v>155</v>
       </c>
       <c r="D36" s="12">
         <v>1</v>
@@ -9279,13 +9285,13 @@
         <v>7062880</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G36" s="12">
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="0"/>
@@ -9298,13 +9304,13 @@
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>157</v>
+        <v>569</v>
       </c>
       <c r="C37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D37" s="12">
         <v>1</v>
@@ -9313,7 +9319,7 @@
         <v>400000</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -9330,54 +9336,57 @@
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>158</v>
+        <v>570</v>
       </c>
       <c r="C38" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D38" s="12">
         <v>1</v>
       </c>
       <c r="E38" s="13">
-        <v>150000</v>
+        <f>ROUND(35990/(1+НДС),0)</f>
+        <v>31026</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G38" s="12">
         <v>1</v>
       </c>
-      <c r="H38" s="4"/>
+      <c r="H38" s="4" t="s">
+        <v>571</v>
+      </c>
       <c r="I38" s="5">
-        <f t="shared" si="0"/>
-        <v>150000</v>
+        <f t="shared" ref="I38" si="6">IF(F38="разово",IF(G38&lt;=3,D38*E38,0),IF(F38="мес",D38*E38*MAX(0,4-G38),D38*E38*MAX(0,4-G38)/12))</f>
+        <v>31026</v>
       </c>
       <c r="J38" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J38" si="7">IF(F38="разово",IF(AND(G38&gt;3,G38&lt;=15),D38*E38,0),IF(F38="мес",D38*E38*MAX(0,MIN(12,16-MAX(G38,4))),D38*E38*MAX(0,MIN(12,16-MAX(G38,4)))/12))</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C39" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D39" s="12">
         <v>1</v>
       </c>
       <c r="E39" s="13">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G39" s="12">
         <v>1</v>
@@ -9385,7 +9394,7 @@
       <c r="H39" s="4"/>
       <c r="I39" s="5">
         <f t="shared" si="0"/>
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="J39" s="5">
         <f t="shared" si="1"/>
@@ -9394,948 +9403,980 @@
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D40" s="12">
         <v>1</v>
       </c>
       <c r="E40" s="13">
-        <v>100000</v>
+        <v>400000</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G40" s="12">
         <v>1</v>
       </c>
-      <c r="H40" s="4" t="s">
-        <v>512</v>
-      </c>
+      <c r="H40" s="4"/>
       <c r="I40" s="5">
         <f t="shared" si="0"/>
+        <v>400000</v>
+      </c>
+      <c r="J40" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" t="s">
+        <v>141</v>
+      </c>
+      <c r="D41" s="12">
+        <v>1</v>
+      </c>
+      <c r="E41" s="13">
         <v>100000</v>
       </c>
-      <c r="J40" s="5">
-        <f t="shared" ref="J40:J68" si="6">IF(F40="разово",IF(AND(G40&gt;3,G40&lt;=15),D40*E40,0),IF(F40="мес",D40*E40*MAX(0,MIN(12,16-MAX(G40,4))),D40*E40*MAX(0,MIN(12,16-MAX(G40,4)))/12))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="F41" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G41" s="12">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="I41" s="5">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="J41" s="5">
+        <f t="shared" ref="J41:J69" si="8">IF(F41="разово",IF(AND(G41&gt;3,G41&lt;=15),D41*E41,0),IF(F41="мес",D41*E41*MAX(0,MIN(12,16-MAX(G41,4))),D41*E41*MAX(0,MIN(12,16-MAX(G41,4)))/12))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>159</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C42" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C41" t="s">
-        <v>163</v>
-      </c>
-      <c r="D41" s="12">
-        <v>1</v>
-      </c>
-      <c r="E41" s="13">
+      <c r="D42" s="12">
+        <v>1</v>
+      </c>
+      <c r="E42" s="13">
         <f>Аренда_мес</f>
         <v>4909152.0999999996</v>
       </c>
-      <c r="F41" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="G41" s="12">
-        <v>1</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="I41" s="5">
-        <f>D41*E41*Аренда_мес_2026</f>
+      <c r="F42" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G42" s="12">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="I42" s="5">
+        <f>D42*E42*Аренда_мес_2026</f>
         <v>11560261.396774193</v>
       </c>
-      <c r="J41" s="5">
-        <f t="shared" si="6"/>
+      <c r="J42" s="5">
+        <f t="shared" si="8"/>
         <v>58909825.199999996</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>161</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C42" t="s">
-        <v>165</v>
-      </c>
-      <c r="D42" s="12">
-        <v>1</v>
-      </c>
-      <c r="E42" s="13">
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C43" t="s">
+        <v>163</v>
+      </c>
+      <c r="D43" s="12">
+        <v>1</v>
+      </c>
+      <c r="E43" s="13">
         <f>Аренда_мес*Депозит_мес</f>
         <v>4909152.0999999996</v>
       </c>
-      <c r="F42" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="G42" s="12">
-        <v>1</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="I42" s="5">
-        <f t="shared" ref="I42:I68" si="7">IF(F42="разово",IF(G42&lt;=3,D42*E42,0),IF(F42="мес",D42*E42*MAX(0,4-G42),D42*E42*MAX(0,4-G42)/12))</f>
+      <c r="F43" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G43" s="12">
+        <v>1</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="I43" s="5">
+        <f t="shared" ref="I43:I69" si="9">IF(F43="разово",IF(G43&lt;=3,D43*E43,0),IF(F43="мес",D43*E43*MAX(0,4-G43),D43*E43*MAX(0,4-G43)/12))</f>
         <v>4909152.0999999996</v>
       </c>
-      <c r="J42" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>161</v>
-      </c>
-      <c r="B43" s="4" t="s">
+      <c r="J43" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>159</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" s="12">
+        <v>1</v>
+      </c>
+      <c r="E44" s="13">
+        <v>3000000</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" s="12">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D43" s="12">
-        <v>1</v>
-      </c>
-      <c r="E43" s="13">
+      <c r="I44" s="5">
+        <f t="shared" si="9"/>
         <v>3000000</v>
       </c>
-      <c r="F43" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="G43" s="12">
-        <v>1</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="I43" s="5">
-        <f t="shared" si="7"/>
-        <v>3000000</v>
-      </c>
-      <c r="J43" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>161</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C44" t="s">
-        <v>163</v>
-      </c>
-      <c r="D44" s="12">
-        <v>1</v>
-      </c>
-      <c r="E44" s="13">
-        <v>50000</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="G44" s="12">
-        <v>1</v>
-      </c>
-      <c r="H44" s="4"/>
-      <c r="I44" s="5">
-        <f t="shared" si="7"/>
-        <v>150000</v>
-      </c>
       <c r="J44" s="5">
-        <f t="shared" si="6"/>
-        <v>600000</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" t="s">
         <v>161</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C45" t="s">
-        <v>163</v>
-      </c>
       <c r="D45" s="12">
         <v>1</v>
       </c>
       <c r="E45" s="13">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G45" s="12">
         <v>1</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="5">
-        <f t="shared" si="7"/>
-        <v>180000</v>
+        <f t="shared" si="9"/>
+        <v>150000</v>
       </c>
       <c r="J45" s="5">
-        <f t="shared" si="6"/>
-        <v>720000</v>
+        <f t="shared" si="8"/>
+        <v>600000</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>159</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" t="s">
         <v>161</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C46" t="s">
-        <v>163</v>
-      </c>
       <c r="D46" s="12">
         <v>1</v>
       </c>
       <c r="E46" s="13">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G46" s="12">
         <v>1</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="5">
-        <f t="shared" si="7"/>
-        <v>150000</v>
+        <f t="shared" si="9"/>
+        <v>180000</v>
       </c>
       <c r="J46" s="5">
-        <f t="shared" si="6"/>
-        <v>600000</v>
+        <f t="shared" si="8"/>
+        <v>720000</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>159</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" t="s">
         <v>161</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C47" t="s">
-        <v>173</v>
-      </c>
       <c r="D47" s="12">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E47" s="13">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>174</v>
-      </c>
+      <c r="H47" s="4"/>
       <c r="I47" s="5">
-        <f t="shared" si="7"/>
-        <v>375000</v>
+        <f t="shared" si="9"/>
+        <v>150000</v>
       </c>
       <c r="J47" s="5">
-        <f t="shared" si="6"/>
-        <v>1500000</v>
+        <f t="shared" si="8"/>
+        <v>600000</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C48" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="D48" s="12">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E48" s="13">
-        <v>60000</v>
+        <v>5000</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
       </c>
-      <c r="H48" s="4"/>
+      <c r="H48" s="4" t="s">
+        <v>172</v>
+      </c>
       <c r="I48" s="5">
-        <f t="shared" si="7"/>
-        <v>180000</v>
+        <f t="shared" si="9"/>
+        <v>375000</v>
       </c>
       <c r="J48" s="5">
-        <f t="shared" si="6"/>
-        <v>720000</v>
+        <f t="shared" si="8"/>
+        <v>1500000</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>159</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C49" t="s">
         <v>161</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C49" t="s">
-        <v>163</v>
-      </c>
       <c r="D49" s="12">
         <v>1</v>
       </c>
       <c r="E49" s="13">
-        <f>Канцелярия!F22</f>
-        <v>240750</v>
+        <v>60000</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G49" s="12">
         <v>1</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>328</v>
-      </c>
+      <c r="H49" s="4"/>
       <c r="I49" s="5">
-        <f t="shared" si="7"/>
-        <v>722250</v>
+        <f t="shared" si="9"/>
+        <v>180000</v>
       </c>
       <c r="J49" s="5">
-        <f t="shared" si="6"/>
-        <v>2889000</v>
+        <f t="shared" si="8"/>
+        <v>720000</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>159</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C50" t="s">
         <v>161</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C50" t="s">
-        <v>163</v>
-      </c>
       <c r="D50" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="13">
-        <v>200000</v>
+        <f>Канцелярия!F22</f>
+        <v>164750</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G50" s="12">
         <v>1</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>411</v>
+        <v>326</v>
       </c>
       <c r="I50" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>494250</v>
       </c>
       <c r="J50" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1977000</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>159</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C51" t="s">
         <v>161</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C51" t="s">
-        <v>163</v>
-      </c>
       <c r="D51" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="13">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G51" s="12">
         <v>1</v>
       </c>
-      <c r="H51" s="4"/>
+      <c r="H51" s="4" t="s">
+        <v>409</v>
+      </c>
       <c r="I51" s="5">
-        <f t="shared" si="7"/>
-        <v>450000</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="J51" s="5">
-        <f t="shared" si="6"/>
-        <v>1800000</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>159</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C52" t="s">
         <v>161</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C52" t="s">
-        <v>163</v>
-      </c>
       <c r="D52" s="12">
         <v>1</v>
       </c>
       <c r="E52" s="13">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="5">
-        <f t="shared" si="7"/>
-        <v>300000</v>
+        <f t="shared" si="9"/>
+        <v>450000</v>
       </c>
       <c r="J52" s="5">
-        <f t="shared" si="6"/>
-        <v>1200000</v>
+        <f t="shared" si="8"/>
+        <v>1800000</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C53" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="D53" s="12">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E53" s="13">
-        <v>7000</v>
+        <v>100000</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G53" s="12">
         <v>1</v>
       </c>
-      <c r="H53" s="4" t="s">
-        <v>174</v>
-      </c>
+      <c r="H53" s="4"/>
       <c r="I53" s="5">
-        <f t="shared" si="7"/>
-        <v>525000</v>
+        <f t="shared" si="9"/>
+        <v>300000</v>
       </c>
       <c r="J53" s="5">
-        <f t="shared" si="6"/>
-        <v>2100000</v>
+        <f t="shared" si="8"/>
+        <v>1200000</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>177</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" t="s">
         <v>179</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C54" t="s">
-        <v>181</v>
-      </c>
       <c r="D54" s="12">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E54" s="13">
-        <v>7500</v>
+        <v>7000</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
       </c>
-      <c r="H54" s="4"/>
+      <c r="H54" s="4" t="s">
+        <v>172</v>
+      </c>
       <c r="I54" s="5">
-        <f t="shared" si="7"/>
-        <v>67500</v>
+        <f t="shared" si="9"/>
+        <v>525000</v>
       </c>
       <c r="J54" s="5">
-        <f t="shared" si="6"/>
-        <v>270000</v>
+        <f t="shared" si="8"/>
+        <v>2100000</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>177</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C55" t="s">
         <v>179</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C55" t="s">
-        <v>184</v>
-      </c>
       <c r="D55" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" s="13">
-        <v>30000</v>
+        <v>7500</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G55" s="12">
         <v>1</v>
       </c>
-      <c r="H55" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="H55" s="4"/>
       <c r="I55" s="5">
-        <f t="shared" si="7"/>
-        <v>180000</v>
+        <f t="shared" si="9"/>
+        <v>67500</v>
       </c>
       <c r="J55" s="5">
-        <f t="shared" si="6"/>
-        <v>720000</v>
+        <f t="shared" si="8"/>
+        <v>270000</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C56" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D56" s="12">
         <v>2</v>
       </c>
       <c r="E56" s="13">
-        <v>8000</v>
+        <v>30000</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G56" s="12">
         <v>1</v>
       </c>
-      <c r="H56" s="4"/>
+      <c r="H56" s="4" t="s">
+        <v>183</v>
+      </c>
       <c r="I56" s="5">
-        <f t="shared" si="7"/>
-        <v>48000</v>
+        <f t="shared" si="9"/>
+        <v>180000</v>
       </c>
       <c r="J56" s="5">
-        <f t="shared" si="6"/>
-        <v>192000</v>
+        <f t="shared" si="8"/>
+        <v>720000</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C57" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="D57" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="13">
-        <v>200000</v>
+        <v>8000</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G57" s="12">
-        <v>4</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>188</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H57" s="4"/>
       <c r="I57" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>48000</v>
       </c>
       <c r="J57" s="5">
-        <f t="shared" si="6"/>
-        <v>2400000</v>
+        <f t="shared" si="8"/>
+        <v>192000</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C58" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D58" s="12">
         <v>1</v>
       </c>
       <c r="E58" s="13">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G58" s="12">
         <v>4</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I58" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J58" s="5">
-        <f t="shared" si="6"/>
-        <v>3600000</v>
+        <f t="shared" si="8"/>
+        <v>2400000</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>499</v>
+        <v>187</v>
       </c>
       <c r="C59" t="s">
-        <v>358</v>
-      </c>
-      <c r="D59" s="12"/>
-      <c r="E59" s="13"/>
+        <v>161</v>
+      </c>
+      <c r="D59" s="12">
+        <v>1</v>
+      </c>
+      <c r="E59" s="13">
+        <v>300000</v>
+      </c>
       <c r="F59" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="G59" s="12"/>
-      <c r="H59" s="4"/>
+        <v>162</v>
+      </c>
+      <c r="G59" s="12">
+        <v>4</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>188</v>
+      </c>
       <c r="I59" s="5">
-        <v>2000000</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="J59" s="5">
-        <v>20000000</v>
+        <f t="shared" si="8"/>
+        <v>3600000</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>192</v>
+        <v>497</v>
       </c>
       <c r="C60" t="s">
-        <v>193</v>
-      </c>
-      <c r="D60" s="12">
-        <v>1</v>
-      </c>
-      <c r="E60" s="13">
-        <v>5000000</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="D60" s="12"/>
+      <c r="E60" s="13"/>
       <c r="F60" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="G60" s="12">
-        <v>1</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="G60" s="12"/>
       <c r="H60" s="4"/>
       <c r="I60" s="5">
-        <f t="shared" si="7"/>
-        <v>1250000</v>
+        <v>2000000</v>
       </c>
       <c r="J60" s="5">
-        <f t="shared" si="6"/>
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C61" t="s">
         <v>191</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C61" t="s">
-        <v>163</v>
-      </c>
       <c r="D61" s="12">
         <v>1</v>
       </c>
       <c r="E61" s="13">
-        <v>25000</v>
+        <v>5000000</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="5">
-        <f t="shared" si="7"/>
-        <v>75000</v>
+        <f t="shared" si="9"/>
+        <v>1250000</v>
       </c>
       <c r="J61" s="5">
-        <f t="shared" si="6"/>
-        <v>300000</v>
+        <f t="shared" si="8"/>
+        <v>5000000</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="D62" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="13">
-        <v>10000000</v>
+        <v>25000</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="G62" s="12">
         <v>1</v>
       </c>
-      <c r="H62" s="4" t="s">
-        <v>356</v>
-      </c>
+      <c r="H62" s="4"/>
       <c r="I62" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>75000</v>
       </c>
       <c r="J62" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>300000</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C63" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D63" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="13">
-        <v>700000</v>
+        <v>10000000</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="G63" s="12">
         <v>1</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>199</v>
+        <v>354</v>
       </c>
       <c r="I63" s="5">
-        <f t="shared" si="7"/>
-        <v>700000</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="J63" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>194</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C64" t="s">
         <v>196</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C64" t="s">
-        <v>201</v>
-      </c>
       <c r="D64" s="12">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E64" s="13">
-        <v>150000</v>
+        <v>700000</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>193</v>
+        <v>138</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
       </c>
-      <c r="H64" s="4"/>
+      <c r="H64" s="4" t="s">
+        <v>197</v>
+      </c>
       <c r="I64" s="5">
-        <f t="shared" si="7"/>
-        <v>937500</v>
+        <f t="shared" si="9"/>
+        <v>700000</v>
       </c>
       <c r="J64" s="5">
-        <f t="shared" si="6"/>
-        <v>3750000</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C65" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D65" s="12">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E65" s="13">
-        <v>2000000</v>
+        <v>150000</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="5">
-        <f t="shared" si="7"/>
-        <v>500000</v>
+        <f t="shared" si="9"/>
+        <v>937500</v>
       </c>
       <c r="J65" s="5">
-        <f t="shared" si="6"/>
-        <v>2000000</v>
+        <f t="shared" si="8"/>
+        <v>3750000</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>563</v>
+        <v>200</v>
       </c>
       <c r="C66" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D66" s="12">
         <v>1</v>
       </c>
       <c r="E66" s="13">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G66" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="5">
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>500000</v>
       </c>
       <c r="J66" s="5">
-        <v>3000000</v>
+        <f t="shared" si="8"/>
+        <v>2000000</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>203</v>
+        <v>561</v>
       </c>
       <c r="C67" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D67" s="12">
         <v>1</v>
       </c>
       <c r="E67" s="13">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G67" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="5">
-        <f t="shared" si="7"/>
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="J67" s="5">
-        <f t="shared" si="6"/>
-        <v>500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C68" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D68" s="12">
         <v>1</v>
       </c>
       <c r="E68" s="13">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
+        <v>125000</v>
+      </c>
+      <c r="J68" s="5">
+        <f t="shared" si="8"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>194</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C69" t="s">
+        <v>191</v>
+      </c>
+      <c r="D69" s="12">
+        <v>1</v>
+      </c>
+      <c r="E69" s="13">
+        <v>150000</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="G69" s="12">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="5">
+        <f t="shared" si="9"/>
         <v>37500</v>
       </c>
-      <c r="J68" s="5">
-        <f t="shared" si="6"/>
+      <c r="J69" s="5">
+        <f t="shared" si="8"/>
         <v>150000</v>
       </c>
     </row>
@@ -10365,7 +10406,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -10373,25 +10414,25 @@
     </row>
     <row r="4" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="G4" s="80" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H4" s="80">
         <v>2027</v>
@@ -10399,18 +10440,18 @@
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
       <c r="F5" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G5" s="5">
         <v>6000000</v>
@@ -10421,18 +10462,18 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="13"/>
       <c r="F6" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G6" s="5">
         <v>2000000</v>
@@ -10443,18 +10484,18 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="13"/>
       <c r="F7" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G7" s="5">
         <v>10000000</v>
@@ -10465,18 +10506,18 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="13"/>
       <c r="F8" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -10487,18 +10528,18 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="13"/>
       <c r="F9" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -10509,18 +10550,18 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="13"/>
       <c r="F10" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -10531,18 +10572,18 @@
     </row>
     <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C11" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="13"/>
       <c r="F11" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G11" s="5">
         <v>30000000</v>
@@ -10553,18 +10594,18 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="13"/>
       <c r="F12" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G12" s="5">
         <v>15000000</v>
@@ -10575,18 +10616,18 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C13" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="13"/>
       <c r="F13" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G13" s="5">
         <v>50000000</v>
@@ -10597,18 +10638,18 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C14" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="13"/>
       <c r="F14" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G14" s="5">
         <v>30000000</v>
@@ -10623,7 +10664,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -10640,7 +10681,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G18" s="83">
         <f>G16+H16</f>
@@ -10676,46 +10717,46 @@
   <sheetData>
     <row r="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="E4" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>267</v>
-      </c>
       <c r="G4" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" t="s">
         <v>268</v>
-      </c>
-      <c r="B5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C5" t="s">
-        <v>270</v>
       </c>
       <c r="D5" s="16">
         <v>7</v>
@@ -10728,18 +10769,18 @@
         <v>21000</v>
       </c>
       <c r="G5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" t="s">
         <v>268</v>
-      </c>
-      <c r="B6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C6" t="s">
-        <v>270</v>
       </c>
       <c r="D6" s="16">
         <v>0.5</v>
@@ -10752,18 +10793,18 @@
         <v>3250</v>
       </c>
       <c r="G6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D7" s="16">
         <v>1</v>
@@ -10776,18 +10817,18 @@
         <v>6000</v>
       </c>
       <c r="G7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D8" s="16">
         <v>0.5</v>
@@ -10800,18 +10841,18 @@
         <v>2500</v>
       </c>
       <c r="G8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D9" s="16">
         <v>20</v>
@@ -10824,18 +10865,18 @@
         <v>24000</v>
       </c>
       <c r="G9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D10" s="16">
         <v>20</v>
@@ -10848,18 +10889,18 @@
         <v>18000</v>
       </c>
       <c r="G10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D11" s="16">
         <v>10</v>
@@ -10872,18 +10913,18 @@
         <v>15000</v>
       </c>
       <c r="G11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" s="16">
         <v>0.5</v>
@@ -10896,18 +10937,18 @@
         <v>4000</v>
       </c>
       <c r="G12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D13" s="16">
         <v>1</v>
@@ -10920,18 +10961,18 @@
         <v>10000</v>
       </c>
       <c r="G13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B14" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="16">
         <v>0.5</v>
@@ -10946,13 +10987,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
@@ -10965,18 +11006,18 @@
         <v>12000</v>
       </c>
       <c r="G15" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B16" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D16" s="16">
         <v>0.5</v>
@@ -10989,18 +11030,18 @@
         <v>4000</v>
       </c>
       <c r="G16" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B17" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D17" s="16">
         <v>0.2</v>
@@ -11013,18 +11054,18 @@
         <v>5000</v>
       </c>
       <c r="G17" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
@@ -11037,18 +11078,18 @@
         <v>35000</v>
       </c>
       <c r="G18" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B19" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D19" s="16">
         <v>0.2</v>
@@ -11063,83 +11104,83 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D20" s="16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E20" s="5">
         <v>1800</v>
       </c>
       <c r="F20" s="5">
         <f t="shared" si="0"/>
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B21" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D21" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5">
         <v>40000</v>
       </c>
       <c r="F21" s="5">
         <f t="shared" si="0"/>
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D22" s="41"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8">
         <f>SUM(F5:F21)</f>
-        <v>240750</v>
+        <v>164750</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5">
         <f>F22*12</f>
-        <v>2889000</v>
+        <v>1977000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5">
         <f>F22/20</f>
-        <v>12037.5</v>
+        <v>8237.5</v>
       </c>
     </row>
   </sheetData>
@@ -11167,40 +11208,40 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -11214,13 +11255,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C6">
         <v>5659</v>
       </c>
       <c r="D6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -11238,13 +11279,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C7">
         <v>2584</v>
       </c>
       <c r="D7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -11262,13 +11303,13 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C8">
         <v>2534</v>
       </c>
       <c r="D8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -11286,13 +11327,13 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C9">
         <v>6218</v>
       </c>
       <c r="D9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -11310,13 +11351,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C10">
         <v>7045</v>
       </c>
       <c r="D10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -11334,13 +11375,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C11">
         <v>4240</v>
       </c>
       <c r="D11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -11358,13 +11399,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C12">
         <v>6976</v>
       </c>
       <c r="D12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -11382,13 +11423,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C13">
         <v>5729</v>
       </c>
       <c r="D13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -11406,13 +11447,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C14">
         <v>3288</v>
       </c>
       <c r="D14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -11430,13 +11471,13 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C15">
         <v>1756</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -11454,13 +11495,13 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C16">
         <v>4400</v>
       </c>
       <c r="D16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -11476,7 +11517,7 @@
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -11493,7 +11534,7 @@
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -11507,10 +11548,10 @@
         <v>2.1</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -11528,10 +11569,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B21" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -11549,10 +11590,10 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B22" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D22" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -11570,10 +11611,10 @@
         <v>2.4</v>
       </c>
       <c r="B23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D23" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -11591,10 +11632,10 @@
         <v>2.5</v>
       </c>
       <c r="B24" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -11612,10 +11653,10 @@
         <v>2.6</v>
       </c>
       <c r="B25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D25" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E25">
         <v>12</v>
@@ -11631,7 +11672,7 @@
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -11648,7 +11689,7 @@
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -11662,10 +11703,10 @@
         <v>3.1</v>
       </c>
       <c r="B29" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D29" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -11683,10 +11724,10 @@
         <v>3.2</v>
       </c>
       <c r="B30" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D30" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -11704,10 +11745,10 @@
         <v>3.3</v>
       </c>
       <c r="B31" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D31" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -11725,10 +11766,10 @@
         <v>3.4</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D32" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -11744,7 +11785,7 @@
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -11762,7 +11803,7 @@
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
       <c r="B35" s="14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" tabRatio="500" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Свод" sheetId="1" r:id="rId1"/>
@@ -1843,7 +1843,7 @@
     <t>Второй кулер для воды, напольный, нагрев и охлаждение (класс Midea MK-32H)</t>
   </si>
   <si>
-    <t>Второй кулер – для зоны 710 (первый – в комплекте бытовой техники). Kaspi.kz (Астана) на 10.10.2026 – 35 990 ₸ с НДС, в бюджете без НДС (÷1,16): https://kaspi.kz/shop/p/midea-mk-32h-belyi-25900012/</t>
+    <t>Второй кулер – для переговорной зоны  (первый – в комплекте бытовой техники). Kaspi.kz (Астана) на 10.10.2026 – 35 990 ₸ с НДС, в бюджете без НДС (÷1,16): https://kaspi.kz/shop/p/midea-mk-32h-belyi-25900012/</t>
   </si>
 </sst>
 </file>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B12" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I184,'Оснащение и офис'!A5:A184,"Оснащение")</f>
-        <v>33823753</v>
+        <v>33059753</v>
       </c>
       <c r="C12" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J184,'Оснащение и офис'!A5:A184,"Оснащение")</f>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B20" s="55">
         <f>B7+B8+B9+B10+B11+B12+B13+B16+B17+B19</f>
-        <v>139298694.21182796</v>
+        <v>138534694.21182796</v>
       </c>
       <c r="C20" s="55">
         <f>C7+C8+C9+C10+C11+C12+C13+C16+C17+C19</f>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="B21" s="49">
         <f>B20*Резерв</f>
-        <v>13929869.421182796</v>
+        <v>13853469.421182796</v>
       </c>
       <c r="C21" s="49">
         <f>C20*Резерв</f>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="B22" s="57">
         <f>B20+B21</f>
-        <v>153228563.63301075</v>
+        <v>152388163.63301075</v>
       </c>
       <c r="C22" s="57">
         <f>C20+C21</f>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B23" s="49">
         <f>B22*НДС</f>
-        <v>24516570.181281719</v>
+        <v>24382106.181281719</v>
       </c>
       <c r="C23" s="49">
         <f>C22*НДС</f>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="B24" s="59">
         <f>B22+B23</f>
-        <v>177745133.81429246</v>
+        <v>176770269.81429246</v>
       </c>
       <c r="C24" s="60">
         <f>C22+C23</f>
@@ -2945,7 +2945,7 @@
       <c r="B25" s="61"/>
       <c r="C25" s="62">
         <f>B24+C24</f>
-        <v>1194767317.6076591</v>
+        <v>1193792453.6076591</v>
       </c>
       <c r="D25" s="48"/>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B39" s="49">
         <f>'Оснащение и офис'!I15</f>
-        <v>360000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="B40" s="49">
         <f>'Оснащение и офис'!E16</f>
-        <v>841000</v>
+        <v>817000</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -8356,7 +8356,7 @@
         <v>141</v>
       </c>
       <c r="D9" s="12">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E9" s="13">
         <v>100000</v>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
@@ -8556,7 +8556,7 @@
         <v>137</v>
       </c>
       <c r="D15" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15" s="13">
         <v>60000</v>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>360000</v>
+        <v>120000</v>
       </c>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="E16" s="13">
         <f>(D10*E10+D11*E11+D12*E12+D13*E13+D14*E14+D15*E15)*Сборка_мебели_проц</f>
-        <v>841000</v>
+        <v>817000</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>138</v>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>841000</v>
+        <v>817000</v>
       </c>
       <c r="J16" s="5">
         <f t="shared" si="1"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="539">
   <si>
     <t>Бюджет проектного офиса «Таза Қазақстан» (ЦАКФ) на октябрь–декабрь 2026 и 2027 год — СВОД, ₸</t>
   </si>
@@ -1672,109 +1672,10 @@
     <t>Справка по аренде – вариант 1, БЦ «Сыганак», 7 этаж: 701–702 + зона 710:</t>
   </si>
   <si>
-    <t>Против варианта 2 – БЦ «Лазурный», 6 этаж (9 856 200 ₸/мес без НДС) – разница, ₸ в месяц (минус – дешевле)</t>
-  </si>
-  <si>
     <t>Источник бесперебойного питания 1200 ВА / 650 Вт, линейно-интерактивный (APC Back-UPS BX1200MI-GR)</t>
   </si>
   <si>
     <t>Kaspi.kz (Астана) на 10.10.2026 – 89 302 ₸ с НДС, в бюджете без НДС (÷1,16): https://kaspi.kz/shop/p/istochnik-bespereboinogo-pitanija-apc-by-schneider-electric-back-ups-bx1200mi-gr-101092827/ ; у b2bcompany.kz ИБП нет</t>
-  </si>
-  <si>
-    <t>Сравнение вариантов аренды: вариант 1 – БЦ «Сыганак» (701–702 + 710), вариант 2 – БЦ «Лазурный» (6 этаж)</t>
-  </si>
-  <si>
-    <t>Показатель</t>
-  </si>
-  <si>
-    <t>Вариант 1 – БЦ «Сыганак»</t>
-  </si>
-  <si>
-    <t>Вариант 2 – БЦ «Лазурный»</t>
-  </si>
-  <si>
-    <t>Помещения</t>
-  </si>
-  <si>
-    <t>7 этаж: 701, 701а, 701б, 702 + зона 710 (10 помещений)</t>
-  </si>
-  <si>
-    <t>6 этаж целиком: open space, 3 зала, кабинет, подсобные</t>
-  </si>
-  <si>
-    <t>Полезная площадь, м²</t>
-  </si>
-  <si>
-    <t>Площадь к оплате, м²</t>
-  </si>
-  <si>
-    <t>Полезной площади на 1 рабочее место (37 мест: 30 штат + 7 аутсорс), м²</t>
-  </si>
-  <si>
-    <t>Ставка, ₸ за м² в месяц без НДС</t>
-  </si>
-  <si>
-    <t>Коммунальные, ₸ в месяц без НДС</t>
-  </si>
-  <si>
-    <t>в ставке</t>
-  </si>
-  <si>
-    <t>Парковка, ₸ в месяц без НДС</t>
-  </si>
-  <si>
-    <t>5 мест, условия уточнить</t>
-  </si>
-  <si>
-    <t>Аренда в месяц без НДС, ₸</t>
-  </si>
-  <si>
-    <t>Аренда в месяц с НДС 16%, ₸</t>
-  </si>
-  <si>
-    <t>Аренда в год с НДС, ₸</t>
-  </si>
-  <si>
-    <t>Против ориентира 5 000 000 ₸/мес без НДС, ₸</t>
-  </si>
-  <si>
-    <t>Аренда в бюджете: октябрь–декабрь 2026 (с 21.10), ₸ без НДС</t>
-  </si>
-  <si>
-    <t>Аренда в бюджете: 2027, ₸ без НДС</t>
-  </si>
-  <si>
-    <t>Гарантийный депозит (1 месяц, возвратный), ₸</t>
-  </si>
-  <si>
-    <t>ИТОГО бюджета с НДС, октябрь–декабрь 2026, ₸</t>
-  </si>
-  <si>
-    <t>ИТОГО бюджета с НДС, 2027, ₸</t>
-  </si>
-  <si>
-    <t>ИТОГО бюджета с НДС, 3 мес. 2026 + 2027, ₸</t>
-  </si>
-  <si>
-    <t>Пояснения к сравнению:</t>
-  </si>
-  <si>
-    <t>1. Вариант 1 дешевле: аренда – на 4,9 млн ₸ в месяц без НДС; бюджет с НДС, резервом и депозитом – на 21,2 млн в 2026, на 75,7 млн в 2027, всего на 96,9 млн ₸.</t>
-  </si>
-  <si>
-    <t>2. Вариант 1 укладывается в ориентир 5 млн ₸/мес без НДС (запас ≈0,09 млн); вариант 2 – выше ориентира почти вдвое (+4,86 млн в месяц).</t>
-  </si>
-  <si>
-    <t>3. Вариант 1 – весь офис на одном 7 этаже, кабинеты под руководство уже есть (702, 701а, 710/3, 710/6), переговорная на 12. Площадь впритык: 8,4 м² полезной на место при норме ≈10; в 2026 (18 человек) – свободно, с 2027 (37 мест) – плотно, резерва под рост нет. Коммунальные и парковка – сверх ставки.</t>
-  </si>
-  <si>
-    <t>4. Вариант 2 – целый этаж, 12,7 м² полезной на место, запас под рост и под мероприятия (зал 93 м²); коммунальные, клининг и охрана – в ставке, 5 парковочных мест. Но платим и за центральный холл (коэффициент 1,4), кабинетов почти нет – под ГИД, заместителей, координатора и бухгалтерию нужны перегородки: в бюджете на ремонт в обоих вариантах 3 млн ₸, для «Лазурного» сумма – после осмотра и сметы.</t>
-  </si>
-  <si>
-    <t>5. Условия «Лазурного» по депозиту и стоимости парковки не известны – в расчёте депозит 1 месяц, парковка без оплаты. ИБП (10 шт., 0,8 млн ₸ без НДС) включены в оснащение в обоих вариантах.</t>
-  </si>
-  <si>
-    <t>Разница (2 – 1)</t>
   </si>
   <si>
     <t>Проекты и мероприятия, не вошедшие в бюджет (по статьям проектного офиса), ₸ - в ИТОГО свода не входят</t>
@@ -1854,7 +1755,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.####"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1948,16 +1849,8 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2000,20 +1893,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9DDEB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2073,26 +1954,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2238,59 +2104,11 @@
     <xf numFmtId="3" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2562,7 +2380,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.7109375" style="4" customWidth="1"/>
@@ -2592,7 +2410,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>550</v>
+        <v>517</v>
       </c>
       <c r="B4" s="4">
         <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!I5:I41,"&lt;=3")</f>
@@ -2606,13 +2424,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>551</v>
+        <v>518</v>
       </c>
       <c r="B5" s="4">
         <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!F5:F41,"новая",Штат!I5:I41,"&lt;=3")</f>
         <v>14</v>
       </c>
-      <c r="C5" s="81">
+      <c r="C5" s="66">
         <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!F5:F41,"новая",Штат!I5:I41,"&gt;3")</f>
         <v>12</v>
       </c>
@@ -2668,7 +2486,7 @@
     </row>
     <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="B9" s="49">
         <f>Штат!P42</f>
@@ -2685,7 +2503,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>554</v>
+        <v>521</v>
       </c>
       <c r="B10" s="49">
         <f>Штат!R42</f>
@@ -2702,7 +2520,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="B11" s="49">
         <f>Командировки!I26</f>
@@ -2987,7 +2805,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>421</v>
       </c>
@@ -2996,7 +2814,7 @@
         <v>4909152.0999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>306</v>
       </c>
@@ -3005,7 +2823,7 @@
         <v>5694616.4359999988</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>307</v>
       </c>
@@ -3014,387 +2832,61 @@
         <v>4909152.0999999996</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>514</v>
+        <v>422</v>
       </c>
       <c r="B36" s="49">
-        <f>Аренда_мес-9856200</f>
-        <v>-4947047.9000000004</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="B37" s="49">
         <f>Аренда_мес-5000000</f>
         <v>-90847.900000000373</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+    <row r="37" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="B38" s="49">
+      <c r="B37" s="49">
         <f>(5000000-Коммун_мес-Парковка_мест*Парковка_цена)/Площадь_офиса</f>
         <v>13766.674200839523</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="B39" s="49">
+      <c r="B38" s="49">
         <f>'Оснащение и офис'!I15</f>
         <v>120000</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B40" s="49">
+      <c r="B39" s="49">
         <f>'Оснащение и офис'!E16</f>
         <v>817000</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="B41" s="49">
+      <c r="B40" s="49">
         <f>Канцелярия!F22</f>
         <v>164750</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+    <row r="41" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B42" s="49">
+      <c r="B41" s="49">
         <f>SUM('Оснащение и офис'!I22:I25)</f>
         <v>182213</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="65" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="66" t="s">
-        <v>518</v>
-      </c>
-      <c r="B45" s="75" t="s">
-        <v>519</v>
-      </c>
-      <c r="C45" s="67" t="s">
-        <v>520</v>
-      </c>
-      <c r="D45" s="67" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A46" s="68" t="s">
-        <v>521</v>
-      </c>
-      <c r="B46" s="76" t="s">
-        <v>522</v>
-      </c>
-      <c r="C46" s="74" t="s">
-        <v>523</v>
-      </c>
-      <c r="D46" s="69"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="68" t="s">
-        <v>524</v>
-      </c>
-      <c r="B47" s="77">
-        <v>309.7</v>
-      </c>
-      <c r="C47" s="70">
-        <v>469.34</v>
-      </c>
-      <c r="D47" s="70">
-        <f>C47-B47</f>
-        <v>159.63999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="68" t="s">
-        <v>525</v>
-      </c>
-      <c r="B48" s="77">
-        <v>340.67</v>
-      </c>
-      <c r="C48" s="70">
-        <v>657.08</v>
-      </c>
-      <c r="D48" s="70">
-        <f>C48-B48</f>
-        <v>316.41000000000003</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="68" t="s">
-        <v>526</v>
-      </c>
-      <c r="B49" s="77">
-        <v>8.3702702702702698</v>
-      </c>
-      <c r="C49" s="70">
-        <v>12.684864864864901</v>
-      </c>
-      <c r="D49" s="70">
-        <f>C49-B49</f>
-        <v>4.3145945945946309</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="68" t="s">
-        <v>527</v>
-      </c>
-      <c r="B50" s="78">
-        <v>13500</v>
-      </c>
-      <c r="C50" s="71">
-        <v>15000</v>
-      </c>
-      <c r="D50" s="71">
-        <f>C50-B50</f>
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="68" t="s">
-        <v>528</v>
-      </c>
-      <c r="B51" s="78">
-        <v>230107.1</v>
-      </c>
-      <c r="C51" s="71" t="s">
-        <v>529</v>
-      </c>
-      <c r="D51" s="71"/>
-    </row>
-    <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="68" t="s">
-        <v>530</v>
-      </c>
-      <c r="B52" s="78">
-        <v>80000</v>
-      </c>
-      <c r="C52" s="71" t="s">
-        <v>531</v>
-      </c>
-      <c r="D52" s="71"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="68" t="s">
-        <v>532</v>
-      </c>
-      <c r="B53" s="78">
-        <v>4909152.0999999996</v>
-      </c>
-      <c r="C53" s="71">
-        <v>9856200</v>
-      </c>
-      <c r="D53" s="71">
-        <f t="shared" ref="D53:D62" si="1">C53-B53</f>
-        <v>4947047.9000000004</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="68" t="s">
-        <v>533</v>
-      </c>
-      <c r="B54" s="78">
-        <v>5694616.4359999998</v>
-      </c>
-      <c r="C54" s="71">
-        <v>11433192</v>
-      </c>
-      <c r="D54" s="71">
-        <f t="shared" si="1"/>
-        <v>5738575.5640000002</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="68" t="s">
-        <v>534</v>
-      </c>
-      <c r="B55" s="78">
-        <v>68335397.231999993</v>
-      </c>
-      <c r="C55" s="71">
-        <v>137198304</v>
-      </c>
-      <c r="D55" s="71">
-        <f t="shared" si="1"/>
-        <v>68862906.768000007</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="68" t="s">
-        <v>535</v>
-      </c>
-      <c r="B56" s="78">
-        <v>-90847.900000000402</v>
-      </c>
-      <c r="C56" s="71">
-        <v>4856200</v>
-      </c>
-      <c r="D56" s="71">
-        <f t="shared" si="1"/>
-        <v>4947047.9000000004</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="68" t="s">
-        <v>536</v>
-      </c>
-      <c r="B57" s="78">
-        <v>11560261.396774201</v>
-      </c>
-      <c r="C57" s="71">
-        <v>23209761.290322602</v>
-      </c>
-      <c r="D57" s="71">
-        <f t="shared" si="1"/>
-        <v>11649499.893548401</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="68" t="s">
-        <v>537</v>
-      </c>
-      <c r="B58" s="78">
-        <v>58909825.200000003</v>
-      </c>
-      <c r="C58" s="71">
-        <v>118274400</v>
-      </c>
-      <c r="D58" s="71">
-        <f t="shared" si="1"/>
-        <v>59364574.799999997</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="68" t="s">
-        <v>538</v>
-      </c>
-      <c r="B59" s="78">
-        <v>4909152.0999999996</v>
-      </c>
-      <c r="C59" s="71">
-        <v>9856200</v>
-      </c>
-      <c r="D59" s="71">
-        <f t="shared" si="1"/>
-        <v>4947047.9000000004</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="72" t="s">
-        <v>539</v>
-      </c>
-      <c r="B60" s="79">
-        <v>177745133.81429246</v>
-      </c>
-      <c r="C60" s="73">
-        <v>198922328.79885945</v>
-      </c>
-      <c r="D60" s="73">
-        <f t="shared" si="1"/>
-        <v>21177194.984566987</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="72" t="s">
-        <v>540</v>
-      </c>
-      <c r="B61" s="79">
-        <v>1017022183.7933666</v>
-      </c>
-      <c r="C61" s="73">
-        <v>1092771381.2381663</v>
-      </c>
-      <c r="D61" s="73">
-        <f t="shared" si="1"/>
-        <v>75749197.444799781</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="72" t="s">
-        <v>541</v>
-      </c>
-      <c r="B62" s="79">
-        <v>1194767317.6076591</v>
-      </c>
-      <c r="C62" s="73">
-        <v>1291693710.0370193</v>
-      </c>
-      <c r="D62" s="73">
-        <f t="shared" si="1"/>
-        <v>96926392.429360151</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="82" t="s">
-        <v>543</v>
-      </c>
-      <c r="B65" s="82"/>
-      <c r="C65" s="82"/>
-      <c r="D65" s="82"/>
-    </row>
-    <row r="66" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="82" t="s">
-        <v>544</v>
-      </c>
-      <c r="B66" s="82"/>
-      <c r="C66" s="82"/>
-      <c r="D66" s="82"/>
-    </row>
-    <row r="67" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="82" t="s">
-        <v>545</v>
-      </c>
-      <c r="B67" s="82"/>
-      <c r="C67" s="82"/>
-      <c r="D67" s="82"/>
-    </row>
-    <row r="68" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="82" t="s">
-        <v>546</v>
-      </c>
-      <c r="B68" s="82"/>
-      <c r="C68" s="82"/>
-      <c r="D68" s="82"/>
-    </row>
-    <row r="69" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="82" t="s">
-        <v>547</v>
-      </c>
-      <c r="B69" s="82"/>
-      <c r="C69" s="82"/>
-      <c r="D69" s="82"/>
-    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -4076,7 +3568,7 @@
         <v>408</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>107</v>
@@ -8232,7 +7724,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I41" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -8266,7 +7758,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>556</v>
+        <v>523</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -8282,7 +7774,7 @@
         <v>135</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>557</v>
+        <v>524</v>
       </c>
       <c r="C7" t="s">
         <v>137</v>
@@ -8300,7 +7792,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" ref="I7:I8" si="2">IF(F7="разово",IF(G7&lt;=3,D7*E7,0),IF(F7="мес",D7*E7*MAX(0,4-G7),D7*E7*MAX(0,4-G7)/12))</f>
@@ -8316,7 +7808,7 @@
         <v>135</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="C8" t="s">
         <v>137</v>
@@ -8334,7 +7826,7 @@
         <v>4</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>560</v>
+        <v>527</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
@@ -9067,7 +8559,7 @@
         <v>135</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C30" t="s">
         <v>137</v>
@@ -9086,7 +8578,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" ref="I30" si="4">IF(F30="разово",IF(G30&lt;=3,D30*E30,0),IF(F30="мес",D30*E30*MAX(0,4-G30),D30*E30*MAX(0,4-G30)/12))</f>
@@ -9102,7 +8594,7 @@
         <v>135</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>562</v>
+        <v>529</v>
       </c>
       <c r="C31" t="s">
         <v>137</v>
@@ -9121,7 +8613,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>563</v>
+        <v>530</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
@@ -9137,7 +8629,7 @@
         <v>135</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>564</v>
+        <v>531</v>
       </c>
       <c r="C32" t="s">
         <v>137</v>
@@ -9156,7 +8648,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>565</v>
+        <v>532</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
@@ -9307,7 +8799,7 @@
         <v>135</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>569</v>
+        <v>536</v>
       </c>
       <c r="C37" t="s">
         <v>141</v>
@@ -9339,7 +8831,7 @@
         <v>135</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="C38" t="s">
         <v>137</v>
@@ -9358,7 +8850,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>571</v>
+        <v>538</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" ref="I38" si="6">IF(F38="разово",IF(G38&lt;=3,D38*E38,0),IF(F38="мес",D38*E38*MAX(0,4-G38),D38*E38*MAX(0,4-G38)/12))</f>
@@ -10291,7 +9783,7 @@
         <v>194</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>561</v>
+        <v>528</v>
       </c>
       <c r="C67" t="s">
         <v>191</v>
@@ -10406,7 +9898,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -10431,10 +9923,10 @@
       <c r="F4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="80" t="s">
+      <c r="G4" s="65" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="80">
+      <c r="H4" s="65">
         <v>2027</v>
       </c>
     </row>
@@ -10487,7 +9979,7 @@
         <v>462</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="C7" t="s">
         <v>356</v>
@@ -10575,7 +10067,7 @@
         <v>462</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>566</v>
+        <v>533</v>
       </c>
       <c r="C11" t="s">
         <v>356</v>
@@ -10683,11 +10175,11 @@
       <c r="B18" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="G18" s="83">
+      <c r="G18" s="67">
         <f>G16+H16</f>
         <v>1673000000</v>
       </c>
-      <c r="H18" s="84"/>
+      <c r="H18" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="413">
   <si>
     <t>Статья</t>
   </si>
@@ -456,9 +456,6 @@
     <t>Переговорная: стол + 12 стульев</t>
   </si>
   <si>
-    <t>Зона ресепшн (стойка, диван для посетителей)</t>
-  </si>
-  <si>
     <t>Конференц-камера и спикерфон</t>
   </si>
   <si>
@@ -471,24 +468,15 @@
     <t>Сетевой накопитель (NAS) с дисками — архив фото/видео и документов</t>
   </si>
   <si>
-    <t>Фото- и видеооборудование (КП PSP Digital), аккумуляторы на год, доп. оборудование</t>
-  </si>
-  <si>
     <t>смета</t>
   </si>
   <si>
-    <t>лист «Смета фото-видео»: КП 5 517 890 + аккумуляторы на год 970 000 + доп. оборудование 574 990</t>
-  </si>
-  <si>
     <t>Лицензии 1С на дополнительные рабочие места</t>
   </si>
   <si>
     <t>Вывеска и брендирование офиса</t>
   </si>
   <si>
-    <t>Пожарная безопасность и аптечки (огнетушители, знаки, аптечки)</t>
-  </si>
-  <si>
     <t>Офис</t>
   </si>
   <si>
@@ -504,15 +492,6 @@
     <t>депозит</t>
   </si>
   <si>
-    <t>Косметический ремонт помещения при заезде (покраска, свет, розетки, перегородки)</t>
-  </si>
-  <si>
-    <t>работы</t>
-  </si>
-  <si>
-    <t>оценка; уточнить после осмотра помещения</t>
-  </si>
-  <si>
     <t>Текущий мелкий ремонт и хозяйственные расходы</t>
   </si>
   <si>
@@ -522,21 +501,9 @@
     <t>Интернет (выделенный канал)</t>
   </si>
   <si>
-    <t>Корпоративная мобильная связь</t>
-  </si>
-  <si>
-    <t>SIM</t>
-  </si>
-  <si>
-    <t>на весь штат</t>
-  </si>
-  <si>
     <t>Обслуживание МФУ и расходники</t>
   </si>
   <si>
-    <t>Такси и транспорт по городу</t>
-  </si>
-  <si>
     <t>Представительские расходы (встречи, кофе-брейки)</t>
   </si>
   <si>
@@ -579,30 +546,6 @@
     <t>Прочие</t>
   </si>
   <si>
-    <t>Подбор персонала (hh.kz: публикации, доступ к базе резюме)</t>
-  </si>
-  <si>
-    <t>пакет</t>
-  </si>
-  <si>
-    <t>найм 21 человека</t>
-  </si>
-  <si>
-    <t>Обучение и повышение квалификации</t>
-  </si>
-  <si>
-    <t>чел.</t>
-  </si>
-  <si>
-    <t>Перевод материалов KZ/EN</t>
-  </si>
-  <si>
-    <t>Юридические и нотариальные расходы</t>
-  </si>
-  <si>
-    <t>Страхование оборудования (фото-видео, дрон, техника)</t>
-  </si>
-  <si>
     <t>Смета фото- и видеооборудования, ₸</t>
   </si>
   <si>
@@ -636,84 +579,36 @@
     <t>В наличии</t>
   </si>
   <si>
-    <t>Объектив Canon EF 70-200mm f/2.8L IS III USM</t>
-  </si>
-  <si>
-    <t>Нет в наличии</t>
-  </si>
-  <si>
     <t>Электронный стабилизатор DJI RS 4 Pro Combo</t>
   </si>
   <si>
-    <t>Дрон DJI Mini 5 Pro Fly More Combo Plus (RC 2)</t>
-  </si>
-  <si>
     <t>Карта памяти Sony 128GB SF-G Tough UHS-II SDXC 299Mb/s</t>
   </si>
   <si>
     <t>DJI Mic 3 2-Person Compact Digital Wireless Microphone System</t>
   </si>
   <si>
-    <t>Светодиодная панель Aputure MC Pro RGB LED Light Panel 8-Light Kit</t>
-  </si>
-  <si>
     <t>Монопод E-Image MA600+610FH</t>
   </si>
   <si>
     <t>Сумка для видеокамер E-Image OSCAR S50 (EB0925)</t>
   </si>
   <si>
-    <t>Телесуфлёр FeelWorld Portable TP2A</t>
-  </si>
-  <si>
     <t>Итого раздел 1</t>
   </si>
   <si>
-    <t>2. Аккумуляторы и элементы питания — на год</t>
-  </si>
-  <si>
     <t>Аккумулятор Canon BP-A30 для Canon EOS C70 — запасной</t>
   </si>
   <si>
     <t>ориентир</t>
   </si>
   <si>
-    <t>Зарядное устройство Canon CG-A20 (на 2 аккумулятора)</t>
-  </si>
-  <si>
-    <t>Батарейная рукоятка DJI RS BG70 для стабилизатора</t>
-  </si>
-  <si>
-    <t>ориентир (DJI $149)</t>
-  </si>
-  <si>
-    <t>Аккумулятор DJI Mini 5 Pro Intelligent Flight Battery Plus</t>
-  </si>
-  <si>
-    <t>ориентир (DJI $145)</t>
-  </si>
-  <si>
-    <t>Аккумуляторы Ni-MH AA/AAA (16 шт.) + зарядное</t>
-  </si>
-  <si>
-    <t>Батарейки одноразовые (AA, AAA, CR2032) — 5 000 ₸ в месяц × 12</t>
-  </si>
-  <si>
     <t>Итого раздел 2</t>
   </si>
   <si>
     <t>3. Дополнительное оборудование</t>
   </si>
   <si>
-    <t>Адаптер Canon Mount Adapter EF-EOS R (для объектива EF 70-200 на камере C70)</t>
-  </si>
-  <si>
-    <t>Вторая карта памяти Sony 128GB SF-G Tough (второй слот C70)</t>
-  </si>
-  <si>
-    <t>цена PSP</t>
-  </si>
-  <si>
     <t>Видеоштатив с видеоголовой</t>
   </si>
   <si>
@@ -774,12 +669,6 @@
     <t>второй комплект вслед за стартовым</t>
   </si>
   <si>
-    <t>Канцелярия, бумага и хозяйственные товары — расчёт в месяц, ₸</t>
-  </si>
-  <si>
-    <t>Офис 310,9 м², 20 сотрудников в офисе (25 в штате − 5 региональных координаторов). Итог переносится в лист «Оснащение и офис» (раздел «Офис»).</t>
-  </si>
-  <si>
     <t>Группа</t>
   </si>
   <si>
@@ -867,33 +756,9 @@
     <t>техника, пульты, микрофоны</t>
   </si>
   <si>
-    <t>Хозтовары</t>
-  </si>
-  <si>
-    <t>Бытовая химия и средства для уборки</t>
-  </si>
-  <si>
-    <t>сверх договора клининга</t>
-  </si>
-  <si>
-    <t>Санитарно-гигиенические товары (бумага, полотенца, мыло)</t>
-  </si>
-  <si>
-    <t>на 310,9 м², с/у и кухня</t>
-  </si>
-  <si>
-    <t>Мешки для мусора, перчатки, губки</t>
-  </si>
-  <si>
     <t>ИТОГО в месяц</t>
   </si>
   <si>
-    <t>На 1 сотрудника в офисе (20 чел.), в месяц</t>
-  </si>
-  <si>
-    <t>Канцелярия, бумага и хозтовары (расчёт — лист «Канцелярия»)</t>
-  </si>
-  <si>
     <t>Резерв на непредвиденные расходы (10%)</t>
   </si>
   <si>
@@ -933,9 +798,6 @@
     <t>Гарантийный депозит по аренде (1 месячная ставка, возвратный)</t>
   </si>
   <si>
-    <t>Бумага А4/А3, канцтовары на рабочие места, хозтовары и питьевая вода на офис</t>
-  </si>
-  <si>
     <t xml:space="preserve">     в т.ч. гарантийный депозит (1 месяц, возвратный)</t>
   </si>
   <si>
@@ -1095,15 +957,9 @@
     <t>Сетевые фильтры на общие зоны: 6 розеток, 5 м (Defender DFS 155)</t>
   </si>
   <si>
-    <t>Стол совещаний на 12 — 2 (ноутбуки участников), ТВ и ВКС — 1, МФУ и сетевое оборудование — 1, кухонная зона — 1. b2bcompany.kz на 30.09.2026 — 6 101 ₸ с НДС (код 51417), в бюджете без НДС (÷1,16): https://b2bcompany.kz/catalog/ofisnaya_tekhnika_i_aksessuary/elektrotovary/setevye_filtry/51417/</t>
-  </si>
-  <si>
     <t>Сетевые фильтры на рабочие места: 5 розеток, 3 м, с заземлением (Defender ES)</t>
   </si>
   <si>
-    <t>По 1 на рабочее место: 29 сотрудников + стол сисадмина + резерв/гостевое = 31. Ноутбук, монитор, зарядка телефона, лампа. Столы у стен и колонн — в розетку напрямую, островные блоки — в удлинитель блока (строка ниже). b2bcompany.kz на 30.09.2026 — 4 118 ₸ с НДС (код 9320), в бюджете без НДС (÷1,16): https://b2bcompany.kz/catalog/ofisnaya_tekhnika_i_aksessuary/elektrotovary/setevye_filtry/9320/</t>
-  </si>
-  <si>
     <t>Удлинители-магистрали 10 м, 3 розетки, с заземлением, ПВС 3×1 мм², 16 А (ЭРА U-3e-10m-3x1)</t>
   </si>
   <si>
@@ -1287,9 +1143,6 @@
     <t>БЦ «Сыганак», 7 этаж: 701–702 (119,7 м²) + зона 710 (190,0) = 309,7 м² + 10% МОП = 340,7 м² × 13 500 ₸ + коммунальные 743 ₸/м² полезной (≈230 100) + парковка 2 × 40 000 = 4 909 152 ₸/мес без НДС (5 694 616 ₸ с НДС). Смета: D:\Аренда\Смета аренды — БЦ Сыганак, 701–702 + зона 710 (7 эт.) (проект 2026-10-08).xlsx. В 2026 – с 21.10 (≈2,35 мес.)</t>
   </si>
   <si>
-    <t>оценка; уточнить после осмотра помещений (701–702, 710)</t>
-  </si>
-  <si>
     <t>Источник бесперебойного питания 1200 ВА / 650 Вт, линейно-интерактивный (APC Back-UPS BX1200MI-GR)</t>
   </si>
   <si>
@@ -1443,9 +1296,6 @@
     <t>5. Оснащение (разово): ноутбуки, мебель, МФУ, интерактивная панель, ИБП, фото-видео, сеть</t>
   </si>
   <si>
-    <t>6. Офис: аренда, депозит, ремонт, хозрасходы, курьер, связь</t>
-  </si>
-  <si>
     <t xml:space="preserve">     в т.ч. аренда офиса (БЦ «Сыганак», 7 этаж: 701–702 и зона 710), с 21.10</t>
   </si>
   <si>
@@ -1455,9 +1305,6 @@
     <t>8. Медиа: таргет, полиграфия, подписки</t>
   </si>
   <si>
-    <t>9. Прочие: подбор персонала, обучение, перевод, юруслуги, страхование</t>
-  </si>
-  <si>
     <t>Прямые затраты</t>
   </si>
   <si>
@@ -1468,6 +1315,51 @@
   </si>
   <si>
     <t>ВСЕГО (А + Б)</t>
+  </si>
+  <si>
+    <t>2. Аккумуляторы</t>
+  </si>
+  <si>
+    <t>Канцелярия и бумага – расчёт в месяц, ₸</t>
+  </si>
+  <si>
+    <t>Стойка ресепшн</t>
+  </si>
+  <si>
+    <t>По 1 на рабочее место новых сотрудников (14) и 2 у стола совещаний. b2bcompany.kz на 30.09.2026 – 4 118 ₸ с НДС (код 9320), в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>ТВ и ВКС – 1, МФУ и сетевое оборудование – 1, кухонная зона – 1. b2bcompany.kz на 30.09.2026 – 6 101 ₸ с НДС (код 51417), в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>Фото- и видеооборудование – базовый комплект (КП PSP Digital)</t>
+  </si>
+  <si>
+    <t>лист «Смета фото-видео»: камера, объектив 24-105, стабилизатор, микрофон, карта памяти, монопод, сумка, запасной аккумулятор, штатив, SSD</t>
+  </si>
+  <si>
+    <t>Аптечки</t>
+  </si>
+  <si>
+    <t>Канцелярия и бумага (расчёт – лист «Канцелярия»)</t>
+  </si>
+  <si>
+    <t>Бумага А4/А3, канцтовары на рабочие места</t>
+  </si>
+  <si>
+    <t>новые сотрудники 2026 года</t>
+  </si>
+  <si>
+    <t>Нотариальные расходы (доверенности, засвидетельствование копий)</t>
+  </si>
+  <si>
+    <t>Страхование фото- и видеооборудования</t>
+  </si>
+  <si>
+    <t>6. Офис: аренда, депозит, текущие хозрасходы, курьер, интернет, обслуживание МФУ, канцелярия, представительские</t>
+  </si>
+  <si>
+    <t>9. Прочие: нотариальные расходы, страхование фото- и видеооборудования</t>
   </si>
 </sst>
 </file>
@@ -1975,7 +1867,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>432</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1988,7 +1880,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>433</v>
+        <v>384</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E29,"штат",Штат!G5:G29)</f>
@@ -1997,7 +1889,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>434</v>
+        <v>385</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G31</f>
@@ -2006,7 +1898,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>435</v>
+        <v>386</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M29,Штат!E5:E29,"штат")</f>
@@ -2015,7 +1907,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>436</v>
+        <v>387</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -2024,7 +1916,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>437</v>
+        <v>388</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N30</f>
@@ -2033,7 +1925,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -2042,25 +1934,25 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>439</v>
+        <v>390</v>
       </c>
       <c r="B10" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I62,'Оснащение и офис'!A5:A62,"Оснащение")</f>
-        <v>33059753</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <f>SUMIFS('Оснащение и офис'!I5:I56,'Оснащение и офис'!A5:A56,"Оснащение")</f>
+        <v>29170035</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="B11" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I62,'Оснащение и офис'!A5:A62,"Офис")</f>
-        <v>21748663.496774193</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I56,'Оснащение и офис'!A5:A56,"Офис")</f>
+        <v>17523538.496774193</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="B12" s="40">
         <f>'Оснащение и офис'!I40</f>
@@ -2069,7 +1961,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="B13" s="40">
         <f>'Оснащение и офис'!I41</f>
@@ -2078,83 +1970,83 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
-        <v>442</v>
+        <v>392</v>
       </c>
       <c r="B14" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I62,'Оснащение и офис'!A5:A62,"Цифровые")</f>
-        <v>820500</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I56,'Оснащение и офис'!A5:A56,"Цифровые")</f>
+        <v>589500</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>443</v>
+        <v>393</v>
       </c>
       <c r="B15" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I62,'Оснащение и офис'!A5:A62,"Медиа")</f>
-        <v>3325000</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I56,'Оснащение и офис'!A5:A56,"Медиа")</f>
+        <v>2525000</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="B16" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I62,'Оснащение и офис'!A5:A62,"Прочие")</f>
-        <v>2300000</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I56,'Оснащение и офис'!A5:A56,"Прочие")</f>
+        <v>75000</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="B17" s="42">
         <f>B6+B7+B8+B9+B10+B11+B14+B15+B16</f>
-        <v>138401747.84086022</v>
+        <v>127030904.84086022</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="36" t="s">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="B18" s="38">
         <f>B17*Резерв</f>
-        <v>13840174.784086023</v>
+        <v>12703090.484086022</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="36" t="s">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="B19" s="38">
         <f>(B17+B18)*НДС</f>
-        <v>24358707.619991399</v>
+        <v>22357439.251991395</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="43" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
       <c r="B20" s="44">
         <f>B17+B18+B19</f>
-        <v>176600630.24493763</v>
+        <v>162091434.57693762</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="B21" s="42">
         <f>Проекты!G13</f>
-        <v>73399369.755062401</v>
+        <v>87908565.420000002</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="B22" s="46">
         <f>B20+B21</f>
-        <v>250000000.00000003</v>
+        <v>249999999.99693763</v>
       </c>
     </row>
   </sheetData>
@@ -2501,7 +2393,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C31" t="s">
-        <v>386</v>
+        <v>338</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2512,7 +2404,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2539,138 +2431,138 @@
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>429</v>
+        <v>380</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>430</v>
+        <v>381</v>
       </c>
     </row>
     <row r="40" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>383</v>
+        <v>335</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="B41" s="13">
         <f>ROUND((52.2+21.4+12.4+33.7+190)*1.1,2)</f>
         <v>340.67</v>
       </c>
       <c r="C41" t="s">
-        <v>384</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="B42" s="5">
         <v>13500</v>
       </c>
       <c r="C42" t="s">
-        <v>381</v>
+        <v>333</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>264</v>
+        <v>219</v>
       </c>
       <c r="B43" s="5">
         <f>743*309.7</f>
         <v>230107.1</v>
       </c>
       <c r="C43" t="s">
-        <v>385</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="B44" s="5">
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>331</v>
+        <v>283</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="B45" s="5">
         <v>40000</v>
       </c>
       <c r="C45" t="s">
-        <v>382</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <f>Аренда_мес*(1+НДС)</f>
         <v>5694616.4359999988</v>
       </c>
       <c r="C46" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B47" s="5">
         <f>Аренда_мес*Депозит_мес</f>
         <v>4909152.0999999996</v>
       </c>
       <c r="C47" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>276</v>
+        <v>230</v>
       </c>
       <c r="B48" s="15">
         <f>11/31+2</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C48" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>265</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>266</v>
+        <v>221</v>
       </c>
       <c r="B50" s="14">
         <v>0.1</v>
       </c>
       <c r="C50" t="s">
-        <v>267</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="B51" s="15">
         <f>Аренда_мес_2026</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C51" t="s">
-        <v>431</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -2698,7 +2590,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2730,7 +2622,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>404</v>
+        <v>355</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -2739,19 +2631,19 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>405</v>
+        <v>356</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>406</v>
+        <v>357</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -2760,10 +2652,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>333</v>
+        <v>285</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>79</v>
@@ -2796,19 +2688,19 @@
         <v>3</v>
       </c>
       <c r="M5" s="18">
-        <f>K5*L5</f>
+        <f t="shared" ref="M5:M29" si="3">K5*L5</f>
         <v>5454690</v>
       </c>
       <c r="N5" s="18">
-        <f>IF(E5="штат",ОСНС*G5*L5/12,0)</f>
+        <f t="shared" ref="N5:N29" si="4">IF(E5="штат",ОСНС*G5*L5/12,0)</f>
         <v>7000</v>
       </c>
       <c r="O5" s="18">
-        <f>M5+N5</f>
+        <f t="shared" ref="O5:O29" si="5">M5+N5</f>
         <v>5461690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>410</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2816,10 +2708,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>334</v>
+        <v>286</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -2852,19 +2744,19 @@
         <v>3</v>
       </c>
       <c r="M6" s="18">
-        <f>K6*L6</f>
+        <f t="shared" si="3"/>
         <v>4784010</v>
       </c>
       <c r="N6" s="18">
-        <f>IF(E6="штат",ОСНС*G6*L6/12,0)</f>
+        <f t="shared" si="4"/>
         <v>7000</v>
       </c>
       <c r="O6" s="18">
-        <f>M6+N6</f>
+        <f t="shared" si="5"/>
         <v>4791010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>411</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -2872,10 +2764,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>321</v>
+        <v>275</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>82</v>
@@ -2908,19 +2800,19 @@
         <v>3</v>
       </c>
       <c r="M7" s="18">
-        <f>K7*L7</f>
+        <f t="shared" si="3"/>
         <v>4784010</v>
       </c>
       <c r="N7" s="18">
-        <f>IF(E7="штат",ОСНС*G7*L7/12,0)</f>
+        <f t="shared" si="4"/>
         <v>7000</v>
       </c>
       <c r="O7" s="18">
-        <f>M7+N7</f>
+        <f t="shared" si="5"/>
         <v>4791010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>412</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2928,10 +2820,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2964,19 +2856,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M8" s="18">
-        <f>K8*L8</f>
+        <f t="shared" si="3"/>
         <v>3755190.6451612907</v>
       </c>
       <c r="N8" s="18">
-        <f>IF(E8="штат",ОСНС*G8*L8/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O8" s="18">
-        <f>M8+N8</f>
+        <f t="shared" si="5"/>
         <v>3760685.2688172045</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>413</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2984,13 +2876,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>80</v>
@@ -3020,19 +2912,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M9" s="18">
-        <f>K9*L9</f>
+        <f t="shared" si="3"/>
         <v>2702295.1612903229</v>
       </c>
       <c r="N9" s="18">
-        <f>IF(E9="штат",ОСНС*G9*L9/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O9" s="18">
-        <f>M9+N9</f>
+        <f t="shared" si="5"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>414</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3040,13 +2932,13 @@
         <v>14</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>80</v>
@@ -3064,31 +2956,31 @@
         <v>1</v>
       </c>
       <c r="J10" s="18">
-        <f t="shared" ref="J10" si="3">IF(E10="штат",ROUND(Ставка_СН*H10*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H10+Ставка_СО*MIN(H10*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H10,Кап_ООСМС*МЗП),0),ROUND(H10*НДС,0))</f>
+        <f t="shared" ref="J10" si="6">IF(E10="штат",ROUND(Ставка_СН*H10*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H10+Ставка_СО*MIN(H10*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H10,Кап_ООСМС*МЗП),0),ROUND(H10*НДС,0))</f>
         <v>159330</v>
       </c>
       <c r="K10" s="18">
-        <f t="shared" ref="K10" si="4">G10*(H10+J10)</f>
+        <f t="shared" ref="K10" si="7">G10*(H10+J10)</f>
         <v>1259330</v>
       </c>
       <c r="L10" s="19">
-        <f t="shared" ref="L10" si="5">IF(AND(F10="новая",I10=1),Мес_2026_новые,MAX(0,4-I10))</f>
+        <f t="shared" ref="L10" si="8">IF(AND(F10="новая",I10=1),Мес_2026_новые,MAX(0,4-I10))</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="M10" s="18">
-        <f>K10*L10</f>
+        <f t="shared" si="3"/>
         <v>2965519.0322580645</v>
       </c>
       <c r="N10" s="18">
-        <f>IF(E10="штат",ОСНС*G10*L10/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O10" s="18">
-        <f>M10+N10</f>
+        <f t="shared" si="5"/>
         <v>2971013.6559139783</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>339</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3096,13 +2988,13 @@
         <v>15</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>80</v>
@@ -3132,19 +3024,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M11" s="18">
-        <f>K11*L11</f>
+        <f t="shared" si="3"/>
         <v>2702295.1612903229</v>
       </c>
       <c r="N11" s="18">
-        <f>IF(E11="штат",ОСНС*G11*L11/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O11" s="18">
-        <f>M11+N11</f>
+        <f t="shared" si="5"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>415</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3152,13 +3044,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>80</v>
@@ -3188,19 +3080,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M12" s="18">
-        <f>K12*L12</f>
+        <f t="shared" si="3"/>
         <v>2702295.1612903229</v>
       </c>
       <c r="N12" s="18">
-        <f>IF(E12="штат",ОСНС*G12*L12/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O12" s="18">
-        <f>M12+N12</f>
+        <f t="shared" si="5"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>416</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3208,13 +3100,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>80</v>
@@ -3244,19 +3136,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M13" s="18">
-        <f>K13*L13</f>
+        <f t="shared" si="3"/>
         <v>2702295.1612903229</v>
       </c>
       <c r="N13" s="18">
-        <f>IF(E13="штат",ОСНС*G13*L13/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O13" s="18">
-        <f>M13+N13</f>
+        <f t="shared" si="5"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>417</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3264,13 +3156,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>80</v>
@@ -3300,19 +3192,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M14" s="18">
-        <f>K14*L14</f>
+        <f t="shared" si="3"/>
         <v>1912623.548387097</v>
       </c>
       <c r="N14" s="18">
-        <f>IF(E14="штат",ОСНС*G14*L14/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O14" s="18">
-        <f>M14+N14</f>
+        <f t="shared" si="5"/>
         <v>1918118.1720430108</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>418</v>
+        <v>369</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3320,13 +3212,13 @@
         <v>23</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>80</v>
@@ -3344,31 +3236,31 @@
         <v>1</v>
       </c>
       <c r="J15" s="18">
-        <f t="shared" ref="J15" si="6">IF(E15="штат",ROUND(Ставка_СН*H15*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H15+Ставка_СО*MIN(H15*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H15,Кап_ООСМС*МЗП),0),ROUND(H15*НДС,0))</f>
+        <f t="shared" ref="J15" si="9">IF(E15="штат",ROUND(Ставка_СН*H15*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H15+Ставка_СО*MIN(H15*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H15,Кап_ООСМС*МЗП),0),ROUND(H15*НДС,0))</f>
         <v>182890</v>
       </c>
       <c r="K15" s="18">
-        <f t="shared" ref="K15" si="7">G15*(H15+J15)</f>
+        <f t="shared" ref="K15" si="10">G15*(H15+J15)</f>
         <v>1482890</v>
       </c>
       <c r="L15" s="19">
-        <f t="shared" ref="L15" si="8">IF(AND(F15="новая",I15=1),Мес_2026_новые,MAX(0,4-I15))</f>
+        <f t="shared" ref="L15" si="11">IF(AND(F15="новая",I15=1),Мес_2026_новые,MAX(0,4-I15))</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="M15" s="18">
-        <f>K15*L15</f>
+        <f t="shared" si="3"/>
         <v>3491966.7741935486</v>
       </c>
       <c r="N15" s="18">
-        <f>IF(E15="штат",ОСНС*G15*L15/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O15" s="18">
-        <f>M15+N15</f>
+        <f t="shared" si="5"/>
         <v>3497461.3978494625</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>307</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3376,16 +3268,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>83</v>
@@ -3412,19 +3304,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M16" s="22">
-        <f>K16*L16</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N16" s="22">
-        <f>IF(E16="штат",ОСНС*G16*L16/12,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O16" s="22">
-        <f>M16+N16</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P16" s="21" t="s">
-        <v>371</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3432,13 +3324,13 @@
         <v>25</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>80</v>
@@ -3468,19 +3360,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M17" s="18">
-        <f>K17*L17</f>
+        <f t="shared" si="3"/>
         <v>3491966.7741935486</v>
       </c>
       <c r="N17" s="18">
-        <f>IF(E17="штат",ОСНС*G17*L17/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O17" s="18">
-        <f>M17+N17</f>
+        <f t="shared" si="5"/>
         <v>3497461.3978494625</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>419</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3488,13 +3380,13 @@
         <v>26</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>262</v>
+        <v>217</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>80</v>
@@ -3524,19 +3416,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M18" s="18">
-        <f>K18*L18</f>
+        <f t="shared" si="3"/>
         <v>2702295.1612903229</v>
       </c>
       <c r="N18" s="18">
-        <f>IF(E18="штат",ОСНС*G18*L18/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O18" s="18">
-        <f>M18+N18</f>
+        <f t="shared" si="5"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>420</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -3544,16 +3436,16 @@
         <v>27</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>316</v>
+        <v>270</v>
       </c>
       <c r="D19" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>262</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>308</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>83</v>
@@ -3580,19 +3472,19 @@
         <v>2</v>
       </c>
       <c r="M19" s="22">
-        <f>K19*L19</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N19" s="22">
-        <f>IF(E19="штат",ОСНС*G19*L19/12,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O19" s="22">
-        <f>M19+N19</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>372</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -3600,16 +3492,16 @@
         <v>28</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>317</v>
+        <v>271</v>
       </c>
       <c r="D20" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>262</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>308</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>83</v>
@@ -3624,31 +3516,31 @@
         <v>2</v>
       </c>
       <c r="J20" s="22">
-        <f t="shared" ref="J20" si="9">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
+        <f t="shared" ref="J20" si="12">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
         <v>112000</v>
       </c>
       <c r="K20" s="22">
-        <f t="shared" ref="K20" si="10">G20*(H20+J20)</f>
+        <f t="shared" ref="K20" si="13">G20*(H20+J20)</f>
         <v>0</v>
       </c>
       <c r="L20" s="23">
-        <f t="shared" ref="L20" si="11">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
+        <f t="shared" ref="L20" si="14">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
         <v>2</v>
       </c>
       <c r="M20" s="22">
-        <f>K20*L20</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N20" s="22">
-        <f>IF(E20="штат",ОСНС*G20*L20/12,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O20" s="22">
-        <f>M20+N20</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P20" s="21" t="s">
-        <v>373</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -3656,16 +3548,16 @@
         <v>29</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="D21" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="20" t="s">
         <v>262</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>308</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>83</v>
@@ -3692,19 +3584,19 @@
         <v>2</v>
       </c>
       <c r="M21" s="22">
-        <f>K21*L21</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N21" s="22">
-        <f>IF(E21="штат",ОСНС*G21*L21/12,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O21" s="22">
-        <f>M21+N21</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>374</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -3712,13 +3604,13 @@
         <v>30</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>312</v>
+        <v>266</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>262</v>
+        <v>217</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>80</v>
@@ -3748,19 +3640,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M22" s="18">
-        <f>K22*L22</f>
+        <f t="shared" si="3"/>
         <v>2702295.1612903229</v>
       </c>
       <c r="N22" s="18">
-        <f>IF(E22="штат",ОСНС*G22*L22/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O22" s="18">
-        <f>M22+N22</f>
+        <f t="shared" si="5"/>
         <v>2707789.7849462368</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>313</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -3768,13 +3660,13 @@
         <v>31</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>262</v>
+        <v>217</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>80</v>
@@ -3792,11 +3684,11 @@
         <v>1</v>
       </c>
       <c r="J23" s="18">
-        <f t="shared" ref="J23:J29" si="12">IF(E23="штат",ROUND(Ставка_СН*H23*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H23+Ставка_СО*MIN(H23*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H23,Кап_ООСМС*МЗП),0),ROUND(H23*НДС,0))</f>
+        <f t="shared" ref="J23:J29" si="15">IF(E23="штат",ROUND(Ставка_СН*H23*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H23+Ставка_СО*MIN(H23*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H23,Кап_ООСМС*МЗП),0),ROUND(H23*НДС,0))</f>
         <v>112210</v>
       </c>
       <c r="K23" s="18">
-        <f t="shared" ref="K23:K29" si="13">G23*(H23+J23)</f>
+        <f t="shared" ref="K23:K29" si="16">G23*(H23+J23)</f>
         <v>812210</v>
       </c>
       <c r="L23" s="19">
@@ -3804,19 +3696,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M23" s="18">
-        <f>K23*L23</f>
+        <f t="shared" si="3"/>
         <v>1912623.548387097</v>
       </c>
       <c r="N23" s="18">
-        <f>IF(E23="штат",ОСНС*G23*L23/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O23" s="18">
-        <f>M23+N23</f>
+        <f t="shared" si="5"/>
         <v>1918118.1720430108</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>315</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3824,16 +3716,16 @@
         <v>32</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
       <c r="D24" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>262</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>308</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>83</v>
@@ -3848,11 +3740,11 @@
         <v>2</v>
       </c>
       <c r="J24" s="22">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>112000</v>
       </c>
       <c r="K24" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L24" s="23">
@@ -3860,19 +3752,19 @@
         <v>2</v>
       </c>
       <c r="M24" s="22">
-        <f>K24*L24</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N24" s="22">
-        <f>IF(E24="штат",ОСНС*G24*L24/12,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O24" s="22">
-        <f>M24+N24</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>375</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -3880,7 +3772,7 @@
         <v>33</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>84</v>
@@ -3904,11 +3796,11 @@
         <v>1</v>
       </c>
       <c r="J25" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>194670</v>
       </c>
       <c r="K25" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1594670</v>
       </c>
       <c r="L25" s="19">
@@ -3916,19 +3808,19 @@
         <v>3</v>
       </c>
       <c r="M25" s="18">
-        <f>K25*L25</f>
+        <f t="shared" si="3"/>
         <v>4784010</v>
       </c>
       <c r="N25" s="18">
-        <f>IF(E25="штат",ОСНС*G25*L25/12,0)</f>
+        <f t="shared" si="4"/>
         <v>7000</v>
       </c>
       <c r="O25" s="18">
-        <f>M25+N25</f>
+        <f t="shared" si="5"/>
         <v>4791010</v>
       </c>
       <c r="P25" s="17" t="s">
-        <v>421</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3936,13 +3828,13 @@
         <v>34</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>85</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>258</v>
+        <v>213</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>80</v>
@@ -3960,11 +3852,11 @@
         <v>1</v>
       </c>
       <c r="J26" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>112210</v>
       </c>
       <c r="K26" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>812210</v>
       </c>
       <c r="L26" s="19">
@@ -3972,19 +3864,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M26" s="18">
-        <f>K26*L26</f>
+        <f t="shared" si="3"/>
         <v>1912623.548387097</v>
       </c>
       <c r="N26" s="18">
-        <f>IF(E26="штат",ОСНС*G26*L26/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O26" s="18">
-        <f>M26+N26</f>
+        <f t="shared" si="5"/>
         <v>1918118.1720430108</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>259</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3992,13 +3884,13 @@
         <v>35</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>337</v>
+        <v>289</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>80</v>
@@ -4016,11 +3908,11 @@
         <v>1</v>
       </c>
       <c r="J27" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>171110</v>
       </c>
       <c r="K27" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1371110</v>
       </c>
       <c r="L27" s="19">
@@ -4028,19 +3920,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M27" s="18">
-        <f>K27*L27</f>
+        <f t="shared" si="3"/>
         <v>3228742.9032258065</v>
       </c>
       <c r="N27" s="18">
-        <f>IF(E27="штат",ОСНС*G27*L27/12,0)</f>
+        <f t="shared" si="4"/>
         <v>5494.6236559139788</v>
       </c>
       <c r="O27" s="18">
-        <f>M27+N27</f>
+        <f t="shared" si="5"/>
         <v>3234237.5268817204</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>343</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4048,16 +3940,16 @@
         <v>36</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>344</v>
+        <v>296</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>83</v>
@@ -4072,11 +3964,11 @@
         <v>1</v>
       </c>
       <c r="J28" s="22">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>160000</v>
       </c>
       <c r="K28" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L28" s="23">
@@ -4084,19 +3976,19 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M28" s="22">
-        <f>K28*L28</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N28" s="22">
-        <f>IF(E28="штат",ОСНС*G28*L28/12,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O28" s="22">
-        <f>M28+N28</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P28" s="21" t="s">
-        <v>376</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4104,16 +3996,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>345</v>
+        <v>297</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>83</v>
@@ -4128,11 +4020,11 @@
         <v>1</v>
       </c>
       <c r="J29" s="22">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>112000</v>
       </c>
       <c r="K29" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L29" s="23">
@@ -4140,26 +4032,26 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="M29" s="22">
-        <f>K29*L29</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N29" s="22">
-        <f>IF(E29="штат",ОСНС*G29*L29/12,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O29" s="22">
-        <f>M29+N29</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>377</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
-        <v>407</v>
+        <v>358</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -4184,18 +4076,18 @@
         <v>58691747.741935484</v>
       </c>
       <c r="N30" s="6">
-        <f t="shared" ref="N30:O30" si="14">SUM(N5:N29)</f>
+        <f t="shared" ref="N30:O30" si="17">SUM(N5:N29)</f>
         <v>104924.73118279572</v>
       </c>
       <c r="O30" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>58796672.473118283</v>
       </c>
       <c r="P30" s="7"/>
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>408</v>
+        <v>359</v>
       </c>
       <c r="G31">
         <f>SUM(G8:G9)+SUM(G10:G24)</f>
@@ -4208,7 +4100,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>409</v>
+        <v>360</v>
       </c>
       <c r="G32">
         <f>G30-G31</f>
@@ -4245,7 +4137,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>422</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -4253,25 +4145,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>350</v>
+        <v>302</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>351</v>
+        <v>303</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>404</v>
+        <v>355</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -4285,13 +4177,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>354</v>
+        <v>306</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>355</v>
+        <v>307</v>
       </c>
       <c r="E4" s="28">
         <v>1000000</v>
@@ -4321,13 +4213,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>356</v>
+        <v>308</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>357</v>
+        <v>309</v>
       </c>
       <c r="E5" s="28">
         <v>700000</v>
@@ -4357,13 +4249,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>358</v>
+        <v>310</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>359</v>
+        <v>311</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -4393,13 +4285,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>363</v>
+        <v>315</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -4429,13 +4321,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>364</v>
+        <v>316</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>365</v>
+        <v>317</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -4465,13 +4357,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>366</v>
+        <v>318</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>367</v>
+        <v>319</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -4501,13 +4393,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>368</v>
+        <v>320</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>369</v>
+        <v>321</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -4535,7 +4427,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>370</v>
+        <v>322</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4579,12 +4471,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4684,7 +4576,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>401</v>
+        <v>352</v>
       </c>
       <c r="C8">
         <f>SUM(Штат!G9:G9)</f>
@@ -4707,7 +4599,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>402</v>
+        <v>353</v>
       </c>
       <c r="C9">
         <f>SUM(Штат!G10:G14)</f>
@@ -4730,7 +4622,7 @@
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>347</v>
+        <v>299</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G15:G16)</f>
@@ -4753,7 +4645,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>320</v>
+        <v>274</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G17:G24)</f>
@@ -4799,7 +4691,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4813,12 +4705,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>423</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>424</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4841,7 +4733,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>425</v>
+        <v>376</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -4873,7 +4765,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>426</v>
+        <v>377</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -4903,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -4975,7 +4867,7 @@
         <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -5033,7 +4925,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>111</v>
+        <v>400</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -5042,7 +4934,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="10">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>101</v>
@@ -5053,7 +4945,7 @@
       <c r="H11" s="4"/>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>500000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5061,7 +4953,7 @@
         <v>98</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="C12" t="s">
         <v>104</v>
@@ -5079,7 +4971,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
@@ -5091,7 +4983,7 @@
         <v>98</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>272</v>
+        <v>226</v>
       </c>
       <c r="C13" t="s">
         <v>100</v>
@@ -5109,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
@@ -5121,7 +5013,7 @@
         <v>98</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>268</v>
+        <v>223</v>
       </c>
       <c r="C14" t="s">
         <v>104</v>
@@ -5131,7 +5023,7 @@
       </c>
       <c r="E14" s="10">
         <f>(D8*E8+D9*E9+D10*E10+D11*E11+D12*E12+D13*E13)*Сборка_мебели_проц</f>
-        <v>817000</v>
+        <v>792000</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>101</v>
@@ -5140,11 +5032,11 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>817000</v>
+        <v>792000</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5152,7 +5044,7 @@
         <v>98</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
         <v>100</v>
@@ -5170,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
@@ -5182,7 +5074,7 @@
         <v>98</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="C16" t="s">
         <v>104</v>
@@ -5210,7 +5102,7 @@
         <v>98</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="C17" t="s">
         <v>100</v>
@@ -5228,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
@@ -5240,7 +5132,7 @@
         <v>98</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="C18" t="s">
         <v>100</v>
@@ -5258,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
@@ -5270,7 +5162,7 @@
         <v>98</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="C19" t="s">
         <v>104</v>
@@ -5288,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
@@ -5300,7 +5192,7 @@
         <v>98</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>283</v>
+        <v>237</v>
       </c>
       <c r="C20" t="s">
         <v>100</v>
@@ -5319,7 +5211,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
@@ -5331,10 +5223,10 @@
         <v>98</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="C21" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="D21" s="9">
         <v>1</v>
@@ -5350,7 +5242,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>287</v>
+        <v>241</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
@@ -5362,7 +5254,7 @@
         <v>98</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>288</v>
+        <v>242</v>
       </c>
       <c r="C22" t="s">
         <v>100</v>
@@ -5381,7 +5273,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
@@ -5393,7 +5285,7 @@
         <v>98</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>290</v>
+        <v>244</v>
       </c>
       <c r="C23" t="s">
         <v>104</v>
@@ -5412,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
@@ -5424,13 +5316,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>325</v>
+        <v>278</v>
       </c>
       <c r="C24" t="s">
         <v>100</v>
       </c>
       <c r="D24" s="9">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E24" s="10">
         <f>ROUND(4118/(1+НДС),0)</f>
@@ -5443,11 +5335,11 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>326</v>
+        <v>401</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>110050</v>
+        <v>56800</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5455,13 +5347,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="C25" t="s">
         <v>100</v>
       </c>
       <c r="D25" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="10">
         <f>ROUND(6101/(1+НДС),0)</f>
@@ -5474,11 +5366,11 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>324</v>
+        <v>402</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
-        <v>26295</v>
+        <v>15777</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5486,7 +5378,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
       <c r="C26" t="s">
         <v>100</v>
@@ -5505,7 +5397,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -5517,7 +5409,7 @@
         <v>98</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
       <c r="C27" t="s">
         <v>100</v>
@@ -5536,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -5548,7 +5440,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="C28" t="s">
         <v>100</v>
@@ -5567,7 +5459,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>390</v>
+        <v>341</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="1">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -5579,7 +5471,7 @@
         <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="C29" t="s">
         <v>100</v>
@@ -5598,7 +5490,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -5610,7 +5502,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
@@ -5629,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -5641,7 +5533,7 @@
         <v>98</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
         <v>104</v>
@@ -5659,7 +5551,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
@@ -5671,7 +5563,7 @@
         <v>98</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
@@ -5701,7 +5593,7 @@
         <v>98</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
         <v>100</v>
@@ -5729,17 +5621,17 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D34" s="9">
         <v>1</v>
       </c>
       <c r="E34" s="10">
-        <f>'Смета фото-видео'!G35</f>
-        <v>7062880</v>
+        <f>'Смета фото-видео'!G24</f>
+        <v>3591930</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>101</v>
@@ -5748,11 +5640,11 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>118</v>
+        <v>404</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
-        <v>7062880</v>
+        <v>3591930</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5760,7 +5652,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>398</v>
+        <v>349</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -5788,7 +5680,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
@@ -5807,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>400</v>
+        <v>351</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" ref="I36" si="2">IF(F36="разово",IF(G36&lt;=3,D36*E36,0),IF(F36="мес",D36*E36*MAX(0,4-G36),D36*E36*MAX(0,4-G36)/12))</f>
@@ -5819,7 +5711,7 @@
         <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
         <v>104</v>
@@ -5847,7 +5739,7 @@
         <v>98</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
         <v>104</v>
@@ -5875,16 +5767,16 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>121</v>
+        <v>405</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D39" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="10">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>101</v>
@@ -5892,23 +5784,21 @@
       <c r="G39" s="9">
         <v>1</v>
       </c>
-      <c r="H39" s="4" t="s">
-        <v>388</v>
-      </c>
+      <c r="H39" s="4"/>
       <c r="I39" s="5">
         <f t="shared" si="0"/>
-        <v>100000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D40" s="9">
         <v>1</v>
@@ -5918,13 +5808,13 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G40" s="9">
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>387</v>
+        <v>339</v>
       </c>
       <c r="I40" s="5">
         <f>D40*E40*Аренда_мес_2026</f>
@@ -5933,13 +5823,13 @@
     </row>
     <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C41" t="s">
         <v>122</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="C41" t="s">
-        <v>126</v>
       </c>
       <c r="D41" s="9">
         <v>1</v>
@@ -5955,61 +5845,59 @@
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>322</v>
+        <v>276</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" ref="I41:I62" si="3">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
+        <f t="shared" ref="I41:I56" si="3">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
         <v>4909152.0999999996</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D42" s="9">
         <v>1</v>
       </c>
       <c r="E42" s="10">
-        <v>3000000</v>
+        <v>50000</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G42" s="9">
         <v>1</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>129</v>
-      </c>
+      <c r="H42" s="4"/>
       <c r="I42" s="5">
         <f t="shared" si="3"/>
-        <v>3000000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D43" s="9">
         <v>1</v>
       </c>
       <c r="E43" s="10">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G43" s="9">
         <v>1</v>
@@ -6017,27 +5905,27 @@
       <c r="H43" s="4"/>
       <c r="I43" s="5">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D44" s="9">
         <v>1</v>
       </c>
       <c r="E44" s="10">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G44" s="9">
         <v>1</v>
@@ -6045,27 +5933,27 @@
       <c r="H44" s="4"/>
       <c r="I44" s="5">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D45" s="9">
         <v>1</v>
       </c>
       <c r="E45" s="10">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G45" s="9">
         <v>1</v>
@@ -6073,57 +5961,58 @@
       <c r="H45" s="4"/>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>133</v>
+        <v>406</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D46" s="9">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E46" s="10">
-        <v>5000</v>
+        <f>Канцелярия!F17</f>
+        <v>61375</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G46" s="9">
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>135</v>
+        <v>407</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
-        <v>375000</v>
+        <v>184125</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D47" s="9">
         <v>1</v>
       </c>
       <c r="E47" s="10">
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G47" s="9">
         <v>1</v>
@@ -6131,58 +6020,57 @@
       <c r="H47" s="4"/>
       <c r="I47" s="5">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>256</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D48" s="9">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E48" s="10">
-        <f>Канцелярия!F20</f>
-        <v>164750</v>
+        <v>7000</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G48" s="9">
         <v>1</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>270</v>
+        <v>408</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="3"/>
-        <v>494250</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D49" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" s="10">
-        <v>150000</v>
+        <v>7500</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G49" s="9">
         <v>1</v>
@@ -6190,143 +6078,134 @@
       <c r="H49" s="4"/>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
-        <v>450000</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D50" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="10">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G50" s="9">
         <v>1</v>
       </c>
-      <c r="H50" s="4"/>
+      <c r="H50" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="I50" s="5">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C51" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D51" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E51" s="10">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G51" s="9">
         <v>1</v>
       </c>
-      <c r="H51" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="H51" s="4"/>
       <c r="I51" s="5">
         <f t="shared" si="3"/>
-        <v>525000</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>142</v>
+        <v>330</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
-      </c>
-      <c r="D52" s="9">
-        <v>3</v>
-      </c>
-      <c r="E52" s="10">
-        <v>7500</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="D52" s="9"/>
+      <c r="E52" s="10"/>
       <c r="F52" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="G52" s="9">
-        <v>1</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="G52" s="9"/>
       <c r="H52" s="4"/>
       <c r="I52" s="5">
-        <f t="shared" si="3"/>
-        <v>67500</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="D53" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="10">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G53" s="9">
         <v>1</v>
       </c>
-      <c r="H53" s="4" t="s">
-        <v>145</v>
-      </c>
+      <c r="H53" s="4"/>
       <c r="I53" s="5">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>146</v>
-      </c>
       <c r="C54" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="D54" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="10">
-        <v>8000</v>
+        <v>25000</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G54" s="9">
         <v>1</v>
@@ -6334,48 +6213,55 @@
       <c r="H54" s="4"/>
       <c r="I54" s="5">
         <f t="shared" si="3"/>
-        <v>48000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="C55" t="s">
-        <v>294</v>
-      </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="10"/>
+        <v>104</v>
+      </c>
+      <c r="D55" s="9">
+        <v>1</v>
+      </c>
+      <c r="E55" s="10">
+        <v>50000</v>
+      </c>
       <c r="F55" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="G55" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="G55" s="9">
+        <v>1</v>
+      </c>
       <c r="H55" s="4"/>
       <c r="I55" s="5">
-        <v>2000000</v>
+        <f t="shared" si="3"/>
+        <v>50000</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>148</v>
+        <v>410</v>
       </c>
       <c r="C56" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D56" s="9">
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="G56" s="9">
         <v>1</v>
@@ -6383,177 +6269,7 @@
       <c r="H56" s="4"/>
       <c r="I56" s="5">
         <f t="shared" si="3"/>
-        <v>1250000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>147</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C57" t="s">
-        <v>124</v>
-      </c>
-      <c r="D57" s="9">
-        <v>1</v>
-      </c>
-      <c r="E57" s="10">
         <v>25000</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="G57" s="9">
-        <v>1</v>
-      </c>
-      <c r="H57" s="4"/>
-      <c r="I57" s="5">
-        <f t="shared" si="3"/>
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>151</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C58" t="s">
-        <v>153</v>
-      </c>
-      <c r="D58" s="9">
-        <v>1</v>
-      </c>
-      <c r="E58" s="10">
-        <v>700000</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G58" s="9">
-        <v>1</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="I58" s="5">
-        <f t="shared" si="3"/>
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>151</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D59" s="9">
-        <v>25</v>
-      </c>
-      <c r="E59" s="10">
-        <v>150000</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="G59" s="9">
-        <v>1</v>
-      </c>
-      <c r="H59" s="4"/>
-      <c r="I59" s="5">
-        <f t="shared" si="3"/>
-        <v>937500</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>151</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C60" t="s">
-        <v>149</v>
-      </c>
-      <c r="D60" s="9">
-        <v>1</v>
-      </c>
-      <c r="E60" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="G60" s="9">
-        <v>1</v>
-      </c>
-      <c r="H60" s="4"/>
-      <c r="I60" s="5">
-        <f t="shared" si="3"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C61" t="s">
-        <v>149</v>
-      </c>
-      <c r="D61" s="9">
-        <v>1</v>
-      </c>
-      <c r="E61" s="10">
-        <v>500000</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="G61" s="9">
-        <v>1</v>
-      </c>
-      <c r="H61" s="4"/>
-      <c r="I61" s="5">
-        <f t="shared" si="3"/>
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>151</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C62" t="s">
-        <v>149</v>
-      </c>
-      <c r="D62" s="9">
-        <v>1</v>
-      </c>
-      <c r="E62" s="10">
-        <v>150000</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="G62" s="9">
-        <v>1</v>
-      </c>
-      <c r="H62" s="4"/>
-      <c r="I62" s="5">
-        <f t="shared" si="3"/>
-        <v>37500</v>
       </c>
     </row>
   </sheetData>
@@ -6582,7 +6298,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>427</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6613,135 +6329,135 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C5" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
       <c r="F5" s="9" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="G5" s="5">
-        <v>3000000</v>
+        <v>3600000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>296</v>
+        <v>250</v>
       </c>
       <c r="C6" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
       <c r="F6" s="9" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="G6" s="5">
-        <v>1000000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>397</v>
-      </c>
       <c r="C7" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
       <c r="F7" s="9" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="G7" s="5">
-        <v>5100000</v>
+        <v>6100000</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="C8" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
       <c r="F8" s="9" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="G8" s="5">
-        <v>15300000</v>
+        <v>18400000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="C9" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
       <c r="F9" s="9" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="G9" s="5">
-        <v>7600000</v>
+        <v>9200000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>297</v>
+        <v>251</v>
       </c>
       <c r="C10" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
       <c r="F10" s="9" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="G10" s="5">
-        <v>26099369.755062401</v>
+        <v>31008565.420000002</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
       <c r="F11" s="9" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="G11" s="5">
-        <v>15300000</v>
+        <v>18400000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6749,7 +6465,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>428</v>
+        <v>379</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -6757,7 +6473,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="6">
         <f>SUM(G5:G11)</f>
-        <v>73399369.755062401</v>
+        <v>87908565.420000002</v>
       </c>
     </row>
   </sheetData>
@@ -6771,7 +6487,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -6785,32 +6501,27 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>218</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>94</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>97</v>
@@ -6818,378 +6529,298 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="B5" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="D5" s="13">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="E5" s="5">
         <v>3000</v>
       </c>
       <c r="F5" s="5">
-        <f t="shared" ref="F5:F19" si="0">D5*E5</f>
-        <v>21000</v>
+        <f t="shared" ref="F5:F16" si="0">D5*E5</f>
+        <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>379</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="B6" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="D6" s="13">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E6" s="5">
         <v>6500</v>
       </c>
       <c r="F6" s="5">
         <f t="shared" si="0"/>
-        <v>3250</v>
+        <v>1625</v>
       </c>
       <c r="G6" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="D7" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="5">
         <v>6000</v>
       </c>
       <c r="F7" s="5">
         <f t="shared" si="0"/>
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="G7" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="C8" t="s">
         <v>104</v>
       </c>
       <c r="D8" s="13">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E8" s="5">
         <v>5000</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>1250</v>
       </c>
       <c r="G8" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B9" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
       </c>
       <c r="D9" s="13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E9" s="5">
         <v>1200</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="G9" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
         <v>104</v>
       </c>
       <c r="D10" s="13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E10" s="5">
         <v>900</v>
       </c>
       <c r="F10" s="5">
         <f t="shared" si="0"/>
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="G10" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B11" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
       </c>
       <c r="D11" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E11" s="5">
         <v>1500</v>
       </c>
       <c r="F11" s="5">
         <f t="shared" si="0"/>
-        <v>15000</v>
+        <v>7500</v>
       </c>
       <c r="G11" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="C12" t="s">
         <v>104</v>
       </c>
       <c r="D12" s="13">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E12" s="5">
         <v>8000</v>
       </c>
       <c r="F12" s="5">
         <f t="shared" si="0"/>
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G12" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B13" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
         <v>104</v>
       </c>
       <c r="D13" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="5">
         <v>10000</v>
       </c>
       <c r="F13" s="5">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G13" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="C14" t="s">
         <v>104</v>
       </c>
       <c r="D14" s="13">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E14" s="5">
         <v>6000</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B15" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="C15" t="s">
         <v>104</v>
       </c>
       <c r="D15" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E15" s="5">
         <v>12000</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="0"/>
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="G15" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="C16" t="s">
         <v>104</v>
       </c>
       <c r="D16" s="13">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E16" s="5">
         <v>8000</v>
       </c>
       <c r="F16" s="5">
         <f t="shared" si="0"/>
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G16" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>248</v>
-      </c>
-      <c r="B17" t="s">
-        <v>249</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="E17" s="5">
-        <v>25000</v>
-      </c>
-      <c r="F17" s="5">
-        <f t="shared" si="0"/>
-        <v>5000</v>
-      </c>
-      <c r="G17" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>248</v>
-      </c>
-      <c r="B18" t="s">
-        <v>251</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="13">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5">
-        <v>35000</v>
-      </c>
-      <c r="F18" s="5">
-        <f t="shared" si="0"/>
-        <v>35000</v>
-      </c>
-      <c r="G18" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>248</v>
-      </c>
-      <c r="B19" t="s">
-        <v>253</v>
-      </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="E19" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F19" s="5">
-        <f t="shared" si="0"/>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6">
-        <f>SUM(F5:F19)</f>
-        <v>164750</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>255</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5">
-        <f>F20/20</f>
-        <v>8237.5</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" s="32"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6">
+        <f>SUM(F5:F16)</f>
+        <v>61375</v>
       </c>
     </row>
   </sheetData>
@@ -7203,7 +6834,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -7217,12 +6848,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7230,13 +6861,13 @@
         <v>66</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>72</v>
@@ -7245,12 +6876,12 @@
         <v>95</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -7264,13 +6895,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C6">
         <v>5659</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7279,7 +6910,7 @@
         <v>1669990</v>
       </c>
       <c r="G6" s="5">
-        <f t="shared" ref="G6:G16" si="0">E6*F6</f>
+        <f t="shared" ref="G6:G12" si="0">E6*F6</f>
         <v>1669990</v>
       </c>
     </row>
@@ -7288,13 +6919,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="C7">
         <v>2584</v>
       </c>
       <c r="D7" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -7309,232 +6940,186 @@
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="C8">
-        <v>2534</v>
+        <v>6218</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" s="5">
-        <v>1101990</v>
+        <v>479990</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="0"/>
-        <v>1101990</v>
+        <v>479990</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="C9">
-        <v>6218</v>
+        <v>4240</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" s="5">
-        <v>479990</v>
+        <v>104990</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>479990</v>
+        <v>104990</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="C10">
-        <v>7045</v>
+        <v>6976</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" s="5">
-        <v>638990</v>
+        <v>119990</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" si="0"/>
-        <v>638990</v>
+        <v>119990</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="C11">
-        <v>4240</v>
+        <v>3288</v>
       </c>
       <c r="D11" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" s="5">
-        <v>104990</v>
+        <v>58990</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="0"/>
-        <v>104990</v>
+        <v>58990</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C12">
-        <v>6976</v>
+        <v>1756</v>
       </c>
       <c r="D12" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" s="5">
-        <v>119990</v>
+        <v>31990</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="0"/>
-        <v>119990</v>
+        <v>31990</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>177</v>
-      </c>
-      <c r="C13">
-        <v>5729</v>
-      </c>
-      <c r="D13" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5">
-        <v>779990</v>
-      </c>
-      <c r="G13" s="5">
-        <f t="shared" si="0"/>
-        <v>779990</v>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6">
+        <f>SUM(G6:G12)</f>
+        <v>2951930</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14">
-        <v>3288</v>
-      </c>
-      <c r="D14" t="s">
-        <v>170</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5">
-        <v>58990</v>
-      </c>
-      <c r="G14" s="5">
-        <f t="shared" si="0"/>
-        <v>58990</v>
-      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>179</v>
-      </c>
-      <c r="C15">
-        <v>1756</v>
-      </c>
-      <c r="D15" t="s">
-        <v>170</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5">
-        <v>31990</v>
-      </c>
-      <c r="G15" s="5">
-        <f t="shared" si="0"/>
-        <v>31990</v>
-      </c>
+      <c r="A15" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>11</v>
+        <v>2.1</v>
       </c>
       <c r="B16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16">
-        <v>4400</v>
+        <v>158</v>
       </c>
       <c r="D16" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16" s="5">
-        <v>44990</v>
+        <v>240000</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" si="0"/>
-        <v>44990</v>
+        <f t="shared" ref="G16" si="1">E16*F16</f>
+        <v>240000</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6">
-        <f>SUM(G6:G16)</f>
-        <v>5517890</v>
+        <f>SUM(G16:G16)</f>
+        <v>240000</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7543,7 +7128,7 @@
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -7554,273 +7139,76 @@
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="B20" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="D20" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="5">
-        <v>240000</v>
+        <v>250000</v>
       </c>
       <c r="G20" s="5">
-        <f t="shared" ref="G20:G25" si="1">E20*F20</f>
-        <v>480000</v>
+        <f>E20*F20</f>
+        <v>250000</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2.2000000000000002</v>
+        <v>3.4</v>
       </c>
       <c r="B21" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="D21" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" s="5">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="1"/>
-        <v>200000</v>
+        <f>E21*F21</f>
+        <v>150000</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B22" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" t="s">
-        <v>187</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" s="5">
-        <v>95000</v>
-      </c>
-      <c r="G22" s="5">
-        <f t="shared" si="1"/>
-        <v>95000</v>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6">
+        <f>SUM(G20:G21)</f>
+        <v>400000</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2.4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>188</v>
-      </c>
-      <c r="D23" t="s">
-        <v>189</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" s="5">
-        <v>95000</v>
-      </c>
-      <c r="G23" s="5">
-        <f t="shared" si="1"/>
-        <v>95000</v>
-      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>2.5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" t="s">
-        <v>184</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5">
-        <v>40000</v>
-      </c>
-      <c r="G24" s="5">
-        <f t="shared" si="1"/>
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>2.6</v>
-      </c>
-      <c r="B25" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" t="s">
-        <v>184</v>
-      </c>
-      <c r="E25">
-        <v>12</v>
-      </c>
-      <c r="F25" s="5">
-        <v>5000</v>
-      </c>
-      <c r="G25" s="5">
-        <f t="shared" si="1"/>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6">
-        <f>SUM(G20:G25)</f>
-        <v>970000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-    </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>3.1</v>
-      </c>
-      <c r="B29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" t="s">
-        <v>184</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29" s="5">
-        <v>70000</v>
-      </c>
-      <c r="G29" s="5">
-        <f>E29*F29</f>
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>3.2</v>
-      </c>
-      <c r="B30" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" t="s">
-        <v>196</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30" s="5">
-        <v>104990</v>
-      </c>
-      <c r="G30" s="5">
-        <f>E30*F30</f>
-        <v>104990</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>3.3</v>
-      </c>
-      <c r="B31" t="s">
-        <v>197</v>
-      </c>
-      <c r="D31" t="s">
-        <v>184</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G31" s="5">
-        <f>E31*F31</f>
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>3.4</v>
-      </c>
-      <c r="B32" t="s">
-        <v>198</v>
-      </c>
-      <c r="D32" t="s">
-        <v>184</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32" s="5">
-        <v>150000</v>
-      </c>
-      <c r="G32" s="5">
-        <f>E32*F32</f>
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6">
-        <f>SUM(G29:G32)</f>
-        <v>574990</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12">
-        <f>G17+G26+G33</f>
-        <v>7062880</v>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12">
+        <f>G13+G17+G22</f>
+        <v>3591930</v>
       </c>
     </row>
   </sheetData>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="417">
   <si>
     <t>Статья</t>
   </si>
@@ -1320,9 +1320,6 @@
     <t>2. Аккумуляторы</t>
   </si>
   <si>
-    <t>Канцелярия и бумага – расчёт в месяц, ₸</t>
-  </si>
-  <si>
     <t>Стойка ресепшн</t>
   </si>
   <si>
@@ -1341,12 +1338,6 @@
     <t>Аптечки</t>
   </si>
   <si>
-    <t>Канцелярия и бумага (расчёт – лист «Канцелярия»)</t>
-  </si>
-  <si>
-    <t>Бумага А4/А3, канцтовары на рабочие места</t>
-  </si>
-  <si>
     <t>новые сотрудники 2026 года</t>
   </si>
   <si>
@@ -1360,6 +1351,27 @@
   </si>
   <si>
     <t>9. Прочие: нотариальные расходы, страхование фото- и видеооборудования</t>
+  </si>
+  <si>
+    <t>Разово при открытии офиса</t>
+  </si>
+  <si>
+    <t>ИТОГО разово</t>
+  </si>
+  <si>
+    <t>Канцелярия и бумага, ₸</t>
+  </si>
+  <si>
+    <t>Канцелярия и бумага – ежемесячно (лист «Канцелярия»)</t>
+  </si>
+  <si>
+    <t>Бумага А4/А3, бумага для флипчарта, ручки, блокноты</t>
+  </si>
+  <si>
+    <t>Канцелярские принадлежности при открытии офиса (лист «Канцелярия»)</t>
+  </si>
+  <si>
+    <t>Папки, конверты, скобы и скрепки, степлеры и дыроколы, архивные короба, батарейки и мелкая электрика</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1592,6 +1604,7 @@
     <xf numFmtId="3" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1937,17 +1950,17 @@
         <v>390</v>
       </c>
       <c r="B10" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I56,'Оснащение и офис'!A5:A56,"Оснащение")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
         <v>29170035</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B11" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I56,'Оснащение и офис'!A5:A56,"Офис")</f>
-        <v>17523538.496774193</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
+        <v>17530038.496774193</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1973,7 +1986,7 @@
         <v>392</v>
       </c>
       <c r="B14" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I56,'Оснащение и офис'!A5:A56,"Цифровые")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
         <v>589500</v>
       </c>
     </row>
@@ -1982,16 +1995,16 @@
         <v>393</v>
       </c>
       <c r="B15" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I56,'Оснащение и офис'!A5:A56,"Медиа")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
         <v>2525000</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B16" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I56,'Оснащение и офис'!A5:A56,"Прочие")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
         <v>75000</v>
       </c>
     </row>
@@ -2001,7 +2014,7 @@
       </c>
       <c r="B17" s="42">
         <f>B6+B7+B8+B9+B10+B11+B14+B15+B16</f>
-        <v>127030904.84086022</v>
+        <v>127037404.84086022</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2010,7 +2023,7 @@
       </c>
       <c r="B18" s="38">
         <f>B17*Резерв</f>
-        <v>12703090.484086022</v>
+        <v>12703740.484086022</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2019,7 +2032,7 @@
       </c>
       <c r="B19" s="38">
         <f>(B17+B18)*НДС</f>
-        <v>22357439.251991395</v>
+        <v>22358583.251991395</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2028,7 +2041,7 @@
       </c>
       <c r="B20" s="44">
         <f>B17+B18+B19</f>
-        <v>162091434.57693762</v>
+        <v>162099728.57693762</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2037,7 +2050,7 @@
       </c>
       <c r="B21" s="42">
         <f>Проекты!G13</f>
-        <v>87908565.420000002</v>
+        <v>87900271.420000002</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4691,7 +4704,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4925,7 +4938,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -5335,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -5366,7 +5379,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -5621,7 +5634,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -5640,7 +5653,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -5767,7 +5780,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -5848,7 +5861,7 @@
         <v>276</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" ref="I41:I56" si="3">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
+        <f t="shared" ref="I41:I57" si="3">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
         <v>4909152.0999999996</v>
       </c>
     </row>
@@ -5969,7 +5982,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -5978,8 +5991,8 @@
         <v>1</v>
       </c>
       <c r="E46" s="10">
-        <f>Канцелярия!F17</f>
-        <v>61375</v>
+        <f>Канцелярия!F11</f>
+        <v>37375</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>121</v>
@@ -5988,11 +6001,11 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
-        <v>184125</v>
+        <v>112125</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6000,57 +6013,58 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" s="9">
+        <v>1</v>
+      </c>
+      <c r="E47" s="10">
+        <f>Канцелярия!F20</f>
+        <v>78500</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" s="9">
+        <v>1</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="I47" s="5">
+        <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
+        <v>78500</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>120</v>
       </c>
-      <c r="D47" s="9">
-        <v>1</v>
-      </c>
-      <c r="E47" s="10">
+      <c r="D48" s="9">
+        <v>1</v>
+      </c>
+      <c r="E48" s="10">
         <v>100000</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F48" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G47" s="9">
-        <v>1</v>
-      </c>
-      <c r="H47" s="4"/>
-      <c r="I47" s="5">
+      <c r="G48" s="9">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4"/>
+      <c r="I48" s="5">
         <f t="shared" si="3"/>
         <v>300000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>128</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C48" t="s">
-        <v>130</v>
-      </c>
-      <c r="D48" s="9">
-        <v>14</v>
-      </c>
-      <c r="E48" s="10">
-        <v>7000</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G48" s="9">
-        <v>1</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="I48" s="5">
-        <f t="shared" si="3"/>
-        <v>294000</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6058,16 +6072,16 @@
         <v>128</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
         <v>130</v>
       </c>
       <c r="D49" s="9">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E49" s="10">
-        <v>7500</v>
+        <v>7000</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>121</v>
@@ -6075,10 +6089,12 @@
       <c r="G49" s="9">
         <v>1</v>
       </c>
-      <c r="H49" s="4"/>
+      <c r="H49" s="4" t="s">
+        <v>405</v>
+      </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
-        <v>67500</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6086,16 +6102,16 @@
         <v>128</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C50" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D50" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" s="10">
-        <v>30000</v>
+        <v>7500</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>121</v>
@@ -6103,12 +6119,10 @@
       <c r="G50" s="9">
         <v>1</v>
       </c>
-      <c r="H50" s="4" t="s">
-        <v>134</v>
-      </c>
+      <c r="H50" s="4"/>
       <c r="I50" s="5">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6116,7 +6130,7 @@
         <v>128</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C51" t="s">
         <v>133</v>
@@ -6125,7 +6139,7 @@
         <v>2</v>
       </c>
       <c r="E51" s="10">
-        <v>8000</v>
+        <v>30000</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>121</v>
@@ -6133,31 +6147,40 @@
       <c r="G51" s="9">
         <v>1</v>
       </c>
-      <c r="H51" s="4"/>
+      <c r="H51" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="I51" s="5">
         <f t="shared" si="3"/>
-        <v>48000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>330</v>
+        <v>135</v>
       </c>
       <c r="C52" t="s">
-        <v>248</v>
-      </c>
-      <c r="D52" s="9"/>
-      <c r="E52" s="10"/>
+        <v>133</v>
+      </c>
+      <c r="D52" s="9">
+        <v>2</v>
+      </c>
+      <c r="E52" s="10">
+        <v>8000</v>
+      </c>
       <c r="F52" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="G52" s="9"/>
+        <v>121</v>
+      </c>
+      <c r="G52" s="9">
+        <v>1</v>
+      </c>
       <c r="H52" s="4"/>
       <c r="I52" s="5">
-        <v>2000000</v>
+        <f t="shared" si="3"/>
+        <v>48000</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6165,27 +6188,20 @@
         <v>136</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>137</v>
+        <v>330</v>
       </c>
       <c r="C53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D53" s="9">
-        <v>1</v>
-      </c>
-      <c r="E53" s="10">
-        <v>150000</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="D53" s="9"/>
+      <c r="E53" s="10"/>
       <c r="F53" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G53" s="9">
-        <v>1</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="G53" s="9"/>
       <c r="H53" s="4"/>
       <c r="I53" s="5">
-        <f t="shared" si="3"/>
-        <v>450000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6193,7 +6209,7 @@
         <v>136</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C54" t="s">
         <v>120</v>
@@ -6202,7 +6218,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="10">
-        <v>25000</v>
+        <v>150000</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>121</v>
@@ -6213,27 +6229,27 @@
       <c r="H54" s="4"/>
       <c r="I54" s="5">
         <f t="shared" si="3"/>
-        <v>75000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>409</v>
+        <v>139</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D55" s="9">
         <v>1</v>
       </c>
       <c r="E55" s="10">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G55" s="9">
         <v>1</v>
@@ -6241,7 +6257,7 @@
       <c r="H55" s="4"/>
       <c r="I55" s="5">
         <f t="shared" si="3"/>
-        <v>50000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6249,25 +6265,53 @@
         <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="D56" s="9">
         <v>1</v>
       </c>
       <c r="E56" s="10">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="G56" s="9">
         <v>1</v>
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="5">
+        <f t="shared" si="3"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C57" t="s">
+        <v>138</v>
+      </c>
+      <c r="D57" s="9">
+        <v>1</v>
+      </c>
+      <c r="E57" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G57" s="9">
+        <v>1</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="5">
         <f t="shared" si="3"/>
         <v>25000</v>
       </c>
@@ -6438,7 +6482,7 @@
         <v>246</v>
       </c>
       <c r="G10" s="5">
-        <v>31008565.420000002</v>
+        <v>31000271.420000002</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6473,7 +6517,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="6">
         <f>SUM(G5:G11)</f>
-        <v>87908565.420000002</v>
+        <v>87900271.420000002</v>
       </c>
     </row>
   </sheetData>
@@ -6487,7 +6531,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -6501,7 +6545,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -6544,7 +6588,7 @@
         <v>3000</v>
       </c>
       <c r="F5" s="5">
-        <f t="shared" ref="F5:F16" si="0">D5*E5</f>
+        <f t="shared" ref="F5:F10" si="0">D5*E5</f>
         <v>10500</v>
       </c>
       <c r="G5" t="s">
@@ -6671,97 +6715,54 @@
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>196</v>
-      </c>
-      <c r="B11" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="13">
-        <v>5</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1500</v>
-      </c>
-      <c r="F11" s="5">
-        <f t="shared" si="0"/>
-        <v>7500</v>
-      </c>
-      <c r="G11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B12" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="E12" s="5">
-        <v>8000</v>
-      </c>
-      <c r="F12" s="5">
-        <f t="shared" si="0"/>
-        <v>2000</v>
-      </c>
-      <c r="G12" t="s">
-        <v>203</v>
+    <row r="11" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="32"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6">
+        <f>SUM(F5:F10)</f>
+        <v>37375</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>196</v>
-      </c>
-      <c r="B13" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F13" s="5">
-        <f t="shared" si="0"/>
-        <v>5000</v>
-      </c>
-      <c r="G13" t="s">
-        <v>205</v>
-      </c>
+      <c r="A13" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>196</v>
       </c>
       <c r="B14" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C14" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="13">
-        <v>0.25</v>
+      <c r="D14" s="47">
+        <v>15</v>
       </c>
       <c r="E14" s="5">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="F14" s="5">
-        <f t="shared" si="0"/>
-        <v>1500</v>
+        <f>D14*E14</f>
+        <v>22500</v>
+      </c>
+      <c r="G14" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6769,23 +6770,23 @@
         <v>196</v>
       </c>
       <c r="B15" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C15" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="13">
-        <v>0.5</v>
+      <c r="D15" s="47">
+        <v>1</v>
       </c>
       <c r="E15" s="5">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="F15" s="5">
-        <f t="shared" si="0"/>
-        <v>6000</v>
+        <f>D15*E15</f>
+        <v>8000</v>
       </c>
       <c r="G15" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6793,35 +6794,107 @@
         <v>196</v>
       </c>
       <c r="B16" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C16" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="13">
-        <v>0.25</v>
+      <c r="D16" s="47">
+        <v>1</v>
       </c>
       <c r="E16" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F16" s="5">
+        <f>D16*E16</f>
+        <v>10000</v>
+      </c>
+      <c r="G16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="47">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>6000</v>
+      </c>
+      <c r="F17" s="5">
+        <f>D17*E17</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="47">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5">
+        <v>12000</v>
+      </c>
+      <c r="F18" s="5">
+        <f>D18*E18</f>
+        <v>24000</v>
+      </c>
+      <c r="G18" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="47">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
         <v>8000</v>
       </c>
-      <c r="F16" s="5">
-        <f t="shared" si="0"/>
-        <v>2000</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="F19" s="5">
+        <f>D19*E19</f>
+        <v>8000</v>
+      </c>
+      <c r="G19" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="17" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6">
-        <f>SUM(F5:F16)</f>
-        <v>61375</v>
-      </c>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6">
+        <f>SUM(F14:F19)</f>
+        <v>78500</v>
+      </c>
+      <c r="G20" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="415">
   <si>
     <t>Статья</t>
   </si>
@@ -798,9 +798,6 @@
     <t>Гарантийный депозит по аренде (1 месячная ставка, возвратный)</t>
   </si>
   <si>
-    <t xml:space="preserve">     в т.ч. гарантийный депозит (1 месяц, возвратный)</t>
-  </si>
-  <si>
     <t>Стеллажи для складов и архивов (склад техники, архив документов, архив основного блока)</t>
   </si>
   <si>
@@ -1294,9 +1291,6 @@
   </si>
   <si>
     <t>5. Оснащение (разово): ноутбуки, мебель, МФУ, интерактивная панель, ИБП, фото-видео, сеть</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     в т.ч. аренда офиса (БЦ «Сыганак», 7 этаж: 701–702 и зона 710), с 21.10</t>
   </si>
   <si>
     <t>7. Цифровые инструменты</t>
@@ -1506,7 +1500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1578,12 +1572,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1869,7 +1857,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.7109375" style="4" customWidth="1"/>
@@ -1880,7 +1868,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1893,7 +1881,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E29,"штат",Штат!G5:G29)</f>
@@ -1902,7 +1890,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G31</f>
@@ -1911,7 +1899,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M29,Штат!E5:E29,"штат")</f>
@@ -1920,7 +1908,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -1929,7 +1917,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N30</f>
@@ -1938,7 +1926,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -1947,7 +1935,7 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
@@ -1956,7 +1944,7 @@
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
@@ -1964,75 +1952,75 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="B12" s="38">
+        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
+        <v>589500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
         <v>391</v>
       </c>
-      <c r="B12" s="40">
-        <f>'Оснащение и офис'!I40</f>
-        <v>11560261.396774193</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
-        <v>225</v>
-      </c>
-      <c r="B13" s="40">
-        <f>'Оснащение и офис'!I41</f>
-        <v>4909152.0999999996</v>
+      <c r="B13" s="38">
+        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
+        <v>2525000</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
+        <v>407</v>
+      </c>
+      <c r="B14" s="38">
+        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="39" t="s">
         <v>392</v>
       </c>
-      <c r="B14" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
-        <v>589500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
-        <v>393</v>
-      </c>
-      <c r="B15" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
-        <v>2525000</v>
+      <c r="B15" s="40">
+        <f>B6+B7+B8+B9+B10+B11+B12+B13+B14</f>
+        <v>127037404.84086022</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>409</v>
+        <v>212</v>
       </c>
       <c r="B16" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
-        <v>75000</v>
+        <f>B15*Резерв</f>
+        <v>12703740.484086022</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="B17" s="38">
+        <f>(B15+B16)*НДС</f>
+        <v>22358583.251991395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
+        <v>393</v>
+      </c>
+      <c r="B18" s="42">
+        <f>B15+B16+B17</f>
+        <v>162099728.57693762</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
         <v>394</v>
       </c>
-      <c r="B17" s="42">
-        <f>B6+B7+B8+B9+B10+B11+B14+B15+B16</f>
-        <v>127037404.84086022</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="36" t="s">
-        <v>212</v>
-      </c>
-      <c r="B18" s="38">
-        <f>B17*Резерв</f>
-        <v>12703740.484086022</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
-        <v>304</v>
-      </c>
-      <c r="B19" s="38">
-        <f>(B17+B18)*НДС</f>
-        <v>22358583.251991395</v>
+      <c r="B19" s="40">
+        <f>Проекты!G13</f>
+        <v>87900271.420000002</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2040,25 +2028,7 @@
         <v>395</v>
       </c>
       <c r="B20" s="44">
-        <f>B17+B18+B19</f>
-        <v>162099728.57693762</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="s">
-        <v>396</v>
-      </c>
-      <c r="B21" s="42">
-        <f>Проекты!G13</f>
-        <v>87900271.420000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="45" t="s">
-        <v>397</v>
-      </c>
-      <c r="B22" s="46">
-        <f>B20+B21</f>
+        <f>B18+B19</f>
         <v>249999999.99693763</v>
       </c>
     </row>
@@ -2406,7 +2376,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C31" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2417,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2444,17 +2414,17 @@
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="40" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2466,7 +2436,7 @@
         <v>340.67</v>
       </c>
       <c r="C41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2477,7 +2447,7 @@
         <v>13500</v>
       </c>
       <c r="C42" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2489,7 +2459,7 @@
         <v>230107.1</v>
       </c>
       <c r="C43" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2500,7 +2470,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2511,7 +2481,7 @@
         <v>40000</v>
       </c>
       <c r="C45" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2540,14 +2510,14 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B48" s="15">
         <f>11/31+2</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2568,14 +2538,14 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B51" s="15">
         <f>Аренда_мес_2026</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C51" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -2603,7 +2573,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2635,7 +2605,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -2644,19 +2614,19 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -2665,10 +2635,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>284</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>285</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>79</v>
@@ -2713,7 +2683,7 @@
         <v>5461690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2721,10 +2691,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -2769,7 +2739,7 @@
         <v>4791010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -2777,10 +2747,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>82</v>
@@ -2825,7 +2795,7 @@
         <v>4791010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2836,7 +2806,7 @@
         <v>216</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2881,7 +2851,7 @@
         <v>3760685.2688172045</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2889,13 +2859,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C9" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>254</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>255</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>80</v>
@@ -2937,7 +2907,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2945,13 +2915,13 @@
         <v>14</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>80</v>
@@ -2993,7 +2963,7 @@
         <v>2971013.6559139783</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3001,13 +2971,13 @@
         <v>15</v>
       </c>
       <c r="B11" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="D11" s="17" t="s">
         <v>257</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>258</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>80</v>
@@ -3049,7 +3019,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3057,13 +3027,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="D12" s="17" t="s">
         <v>257</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>258</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>80</v>
@@ -3105,7 +3075,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3113,13 +3083,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>80</v>
@@ -3161,7 +3131,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3169,13 +3139,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>80</v>
@@ -3217,7 +3187,7 @@
         <v>1918118.1720430108</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3225,13 +3195,13 @@
         <v>23</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>80</v>
@@ -3273,7 +3243,7 @@
         <v>3497461.3978494625</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3281,16 +3251,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>83</v>
@@ -3329,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3337,13 +3307,13 @@
         <v>25</v>
       </c>
       <c r="B17" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>264</v>
-      </c>
       <c r="D17" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>80</v>
@@ -3385,7 +3355,7 @@
         <v>3497461.3978494625</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3393,10 +3363,10 @@
         <v>26</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>217</v>
@@ -3441,7 +3411,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -3449,16 +3419,16 @@
         <v>27</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>217</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>83</v>
@@ -3497,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -3505,16 +3475,16 @@
         <v>28</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>217</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>83</v>
@@ -3553,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -3561,16 +3531,16 @@
         <v>29</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>217</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>83</v>
@@ -3609,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -3617,10 +3587,10 @@
         <v>30</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>217</v>
@@ -3665,7 +3635,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -3673,10 +3643,10 @@
         <v>31</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>217</v>
@@ -3721,7 +3691,7 @@
         <v>1918118.1720430108</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3729,16 +3699,16 @@
         <v>32</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D24" s="21" t="s">
         <v>217</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>83</v>
@@ -3777,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -3785,7 +3755,7 @@
         <v>33</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>84</v>
@@ -3833,7 +3803,7 @@
         <v>4791010</v>
       </c>
       <c r="P25" s="17" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3841,7 +3811,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>85</v>
@@ -3897,13 +3867,13 @@
         <v>35</v>
       </c>
       <c r="B27" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C27" s="17" t="s">
-        <v>294</v>
-      </c>
       <c r="D27" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>80</v>
@@ -3945,7 +3915,7 @@
         <v>3234237.5268817204</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3953,16 +3923,16 @@
         <v>36</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>215</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>83</v>
@@ -4001,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4009,16 +3979,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>215</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>83</v>
@@ -4057,14 +4027,14 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -4100,7 +4070,7 @@
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G31">
         <f>SUM(G8:G9)+SUM(G10:G24)</f>
@@ -4113,7 +4083,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G32">
         <f>G30-G31</f>
@@ -4150,7 +4120,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -4164,19 +4134,19 @@
         <v>69</v>
       </c>
       <c r="D3" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="F3" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="G3" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="G3" s="25" t="s">
-        <v>305</v>
-      </c>
       <c r="H3" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -4190,13 +4160,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>215</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E4" s="28">
         <v>1000000</v>
@@ -4226,13 +4196,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>215</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E5" s="28">
         <v>700000</v>
@@ -4262,13 +4232,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>310</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="D6" s="27" t="s">
         <v>311</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>312</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -4298,13 +4268,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="D7" s="27" t="s">
         <v>314</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>315</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -4334,13 +4304,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="27" t="s">
         <v>316</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>314</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>317</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -4370,13 +4340,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>318</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>314</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>319</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -4406,13 +4376,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>320</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>314</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>321</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -4440,7 +4410,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4484,7 +4454,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4589,7 +4559,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C8">
         <f>SUM(Штат!G9:G9)</f>
@@ -4612,7 +4582,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C9">
         <f>SUM(Штат!G10:G14)</f>
@@ -4635,7 +4605,7 @@
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G15:G16)</f>
@@ -4658,7 +4628,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G17:G24)</f>
@@ -4718,12 +4688,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4746,7 +4716,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -4778,7 +4748,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -4808,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -4880,7 +4850,7 @@
         <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -4938,7 +4908,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -4966,7 +4936,7 @@
         <v>98</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C12" t="s">
         <v>104</v>
@@ -4984,7 +4954,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
@@ -4996,7 +4966,7 @@
         <v>98</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C13" t="s">
         <v>100</v>
@@ -5014,7 +4984,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
@@ -5045,7 +5015,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
@@ -5133,7 +5103,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
@@ -5205,7 +5175,7 @@
         <v>98</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C20" t="s">
         <v>100</v>
@@ -5224,7 +5194,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
@@ -5236,10 +5206,10 @@
         <v>98</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C21" t="s">
         <v>239</v>
-      </c>
-      <c r="C21" t="s">
-        <v>240</v>
       </c>
       <c r="D21" s="9">
         <v>1</v>
@@ -5255,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
@@ -5267,7 +5237,7 @@
         <v>98</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C22" t="s">
         <v>100</v>
@@ -5286,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
@@ -5298,7 +5268,7 @@
         <v>98</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C23" t="s">
         <v>104</v>
@@ -5317,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
@@ -5329,7 +5299,7 @@
         <v>98</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C24" t="s">
         <v>100</v>
@@ -5348,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -5360,7 +5330,7 @@
         <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C25" t="s">
         <v>100</v>
@@ -5379,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -5391,7 +5361,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C26" t="s">
         <v>100</v>
@@ -5410,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -5422,7 +5392,7 @@
         <v>98</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C27" t="s">
         <v>100</v>
@@ -5441,7 +5411,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -5453,7 +5423,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C28" t="s">
         <v>100</v>
@@ -5472,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="1">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -5484,7 +5454,7 @@
         <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C29" t="s">
         <v>100</v>
@@ -5503,7 +5473,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -5515,7 +5485,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
@@ -5534,7 +5504,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -5634,7 +5604,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -5653,7 +5623,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -5665,7 +5635,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -5693,7 +5663,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
@@ -5712,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" ref="I36" si="2">IF(F36="разово",IF(G36&lt;=3,D36*E36,0),IF(F36="мес",D36*E36*MAX(0,4-G36),D36*E36*MAX(0,4-G36)/12))</f>
@@ -5780,7 +5750,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -5827,7 +5797,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I40" s="5">
         <f>D40*E40*Аренда_мес_2026</f>
@@ -5858,7 +5828,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" ref="I41:I57" si="3">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
@@ -5982,7 +5952,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -6001,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -6013,7 +5983,7 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -6032,7 +6002,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
@@ -6090,7 +6060,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -6188,15 +6158,15 @@
         <v>136</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C53" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="10"/>
       <c r="F53" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G53" s="9"/>
       <c r="H53" s="4"/>
@@ -6265,7 +6235,7 @@
         <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C56" t="s">
         <v>104</v>
@@ -6293,7 +6263,7 @@
         <v>140</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -6342,7 +6312,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6373,18 +6343,18 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>301</v>
-      </c>
       <c r="C5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
       <c r="F5" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G5" s="5">
         <v>3600000</v>
@@ -6392,18 +6362,18 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
       <c r="F6" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G6" s="5">
         <v>1200000</v>
@@ -6411,18 +6381,18 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
       <c r="F7" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G7" s="5">
         <v>6100000</v>
@@ -6430,18 +6400,18 @@
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
       <c r="F8" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G8" s="5">
         <v>18400000</v>
@@ -6449,18 +6419,18 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
       <c r="F9" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G9" s="5">
         <v>9200000</v>
@@ -6468,18 +6438,18 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
       <c r="F10" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G10" s="5">
         <v>31000271.420000002</v>
@@ -6487,18 +6457,18 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" t="s">
         <v>247</v>
-      </c>
-      <c r="C11" t="s">
-        <v>248</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
       <c r="F11" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G11" s="5">
         <v>18400000</v>
@@ -6509,7 +6479,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -6545,7 +6515,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -6592,7 +6562,7 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6728,7 +6698,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6751,14 +6721,14 @@
       <c r="C14" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="45">
         <v>15</v>
       </c>
       <c r="E14" s="5">
         <v>1500</v>
       </c>
       <c r="F14" s="5">
-        <f>D14*E14</f>
+        <f t="shared" ref="F14:F19" si="1">D14*E14</f>
         <v>22500</v>
       </c>
       <c r="G14" t="s">
@@ -6775,14 +6745,14 @@
       <c r="C15" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="45">
         <v>1</v>
       </c>
       <c r="E15" s="5">
         <v>8000</v>
       </c>
       <c r="F15" s="5">
-        <f>D15*E15</f>
+        <f t="shared" si="1"/>
         <v>8000</v>
       </c>
       <c r="G15" t="s">
@@ -6799,14 +6769,14 @@
       <c r="C16" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="45">
         <v>1</v>
       </c>
       <c r="E16" s="5">
         <v>10000</v>
       </c>
       <c r="F16" s="5">
-        <f>D16*E16</f>
+        <f t="shared" si="1"/>
         <v>10000</v>
       </c>
       <c r="G16" t="s">
@@ -6823,14 +6793,14 @@
       <c r="C17" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="45">
         <v>1</v>
       </c>
       <c r="E17" s="5">
         <v>6000</v>
       </c>
       <c r="F17" s="5">
-        <f>D17*E17</f>
+        <f t="shared" si="1"/>
         <v>6000</v>
       </c>
     </row>
@@ -6844,14 +6814,14 @@
       <c r="C18" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="47">
+      <c r="D18" s="45">
         <v>2</v>
       </c>
       <c r="E18" s="5">
         <v>12000</v>
       </c>
       <c r="F18" s="5">
-        <f>D18*E18</f>
+        <f t="shared" si="1"/>
         <v>24000</v>
       </c>
       <c r="G18" t="s">
@@ -6868,14 +6838,14 @@
       <c r="C19" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="47">
+      <c r="D19" s="45">
         <v>1</v>
       </c>
       <c r="E19" s="5">
         <v>8000</v>
       </c>
       <c r="F19" s="5">
-        <f>D19*E19</f>
+        <f t="shared" si="1"/>
         <v>8000</v>
       </c>
       <c r="G19" t="s">
@@ -6885,7 +6855,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -7151,7 +7121,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="414">
   <si>
     <t>Статья</t>
   </si>
@@ -759,9 +759,6 @@
     <t>ИТОГО в месяц</t>
   </si>
   <si>
-    <t>Резерв на непредвиденные расходы (10%)</t>
-  </si>
-  <si>
     <t>Финансовому директору</t>
   </si>
   <si>
@@ -1344,9 +1341,6 @@
     <t>6. Офис: аренда, депозит, текущие хозрасходы, курьер, интернет, обслуживание МФУ, канцелярия, представительские</t>
   </si>
   <si>
-    <t>9. Прочие: нотариальные расходы, страхование фото- и видеооборудования</t>
-  </si>
-  <si>
     <t>Разово при открытии офиса</t>
   </si>
   <si>
@@ -1366,6 +1360,9 @@
   </si>
   <si>
     <t>Папки, конверты, скобы и скрепки, степлеры и дыроколы, архивные короба, батарейки и мелкая электрика</t>
+  </si>
+  <si>
+    <t>Непредвиденные расходы: резерв 10% и прочие (нотариальные расходы, страхование фото- и видеооборудования)</t>
   </si>
 </sst>
 </file>
@@ -1857,7 +1854,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.7109375" style="4" customWidth="1"/>
@@ -1868,7 +1865,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1881,7 +1878,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E29,"штат",Штат!G5:G29)</f>
@@ -1890,7 +1887,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G31</f>
@@ -1899,7 +1896,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M29,Штат!E5:E29,"штат")</f>
@@ -1908,7 +1905,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -1917,7 +1914,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N30</f>
@@ -1926,7 +1923,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -1935,7 +1932,7 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
@@ -1944,7 +1941,7 @@
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
@@ -1953,7 +1950,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
@@ -1962,7 +1959,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
@@ -1970,65 +1967,56 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
-        <v>407</v>
-      </c>
-      <c r="B14" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="39" t="s">
-        <v>392</v>
-      </c>
-      <c r="B15" s="40">
-        <f>B6+B7+B8+B9+B10+B11+B12+B13+B14</f>
-        <v>127037404.84086022</v>
+      <c r="A14" s="39" t="s">
+        <v>391</v>
+      </c>
+      <c r="B14" s="40">
+        <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
+        <v>126962404.84086022</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="B15" s="38">
+        <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
+        <v>12771240.484086022</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>212</v>
+        <v>302</v>
       </c>
       <c r="B16" s="38">
-        <f>B15*Резерв</f>
-        <v>12703740.484086022</v>
+        <f>(B14+B15)*НДС</f>
+        <v>22357383.251991395</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B17" s="38">
-        <f>(B15+B16)*НДС</f>
-        <v>22358583.251991395</v>
+      <c r="A17" s="41" t="s">
+        <v>392</v>
+      </c>
+      <c r="B17" s="42">
+        <f>B14+B15+B16</f>
+        <v>162091028.57693762</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="39" t="s">
         <v>393</v>
       </c>
-      <c r="B18" s="42">
-        <f>B15+B16+B17</f>
-        <v>162099728.57693762</v>
+      <c r="B18" s="40">
+        <f>Проекты!G13</f>
+        <v>87908971.420000002</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="43" t="s">
         <v>394</v>
       </c>
-      <c r="B19" s="40">
-        <f>Проекты!G13</f>
-        <v>87900271.420000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
-        <v>395</v>
-      </c>
-      <c r="B20" s="44">
-        <f>B18+B19</f>
+      <c r="B19" s="44">
+        <f>B17+B18</f>
         <v>249999999.99693763</v>
       </c>
     </row>
@@ -2376,7 +2364,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C31" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2387,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2414,17 +2402,17 @@
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="40" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2436,7 +2424,7 @@
         <v>340.67</v>
       </c>
       <c r="C41" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2447,19 +2435,19 @@
         <v>13500</v>
       </c>
       <c r="C42" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B43" s="5">
         <f>743*309.7</f>
         <v>230107.1</v>
       </c>
       <c r="C43" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2470,7 +2458,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2481,7 +2469,7 @@
         <v>40000</v>
       </c>
       <c r="C45" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2510,42 +2498,42 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B48" s="15">
         <f>11/31+2</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C48" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B50" s="14">
         <v>0.1</v>
       </c>
       <c r="C50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B51" s="15">
         <f>Аренда_мес_2026</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C51" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -2573,7 +2561,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2605,7 +2593,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -2614,19 +2602,19 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -2635,10 +2623,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>283</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>284</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>79</v>
@@ -2683,7 +2671,7 @@
         <v>5461690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2691,10 +2679,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -2739,7 +2727,7 @@
         <v>4791010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -2747,10 +2735,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>82</v>
@@ -2795,7 +2783,7 @@
         <v>4791010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2803,10 +2791,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2851,7 +2839,7 @@
         <v>3760685.2688172045</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2859,13 +2847,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C9" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>253</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>254</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>80</v>
@@ -2907,7 +2895,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2915,13 +2903,13 @@
         <v>14</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>80</v>
@@ -2963,7 +2951,7 @@
         <v>2971013.6559139783</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -2971,13 +2959,13 @@
         <v>15</v>
       </c>
       <c r="B11" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="D11" s="17" t="s">
         <v>256</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>257</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>80</v>
@@ -3019,7 +3007,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3027,13 +3015,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="D12" s="17" t="s">
         <v>256</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>257</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>80</v>
@@ -3075,7 +3063,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3083,13 +3071,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>80</v>
@@ -3131,7 +3119,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3139,13 +3127,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>80</v>
@@ -3187,7 +3175,7 @@
         <v>1918118.1720430108</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3195,13 +3183,13 @@
         <v>23</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>80</v>
@@ -3243,7 +3231,7 @@
         <v>3497461.3978494625</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3251,16 +3239,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>83</v>
@@ -3299,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3307,13 +3295,13 @@
         <v>25</v>
       </c>
       <c r="B17" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>263</v>
-      </c>
       <c r="D17" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>80</v>
@@ -3355,7 +3343,7 @@
         <v>3497461.3978494625</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3363,13 +3351,13 @@
         <v>26</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>80</v>
@@ -3411,7 +3399,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -3419,16 +3407,16 @@
         <v>27</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>83</v>
@@ -3467,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -3475,16 +3463,16 @@
         <v>28</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>83</v>
@@ -3523,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -3531,16 +3519,16 @@
         <v>29</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>83</v>
@@ -3579,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -3587,13 +3575,13 @@
         <v>30</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>80</v>
@@ -3635,7 +3623,7 @@
         <v>2707789.7849462368</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -3643,13 +3631,13 @@
         <v>31</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>80</v>
@@ -3691,7 +3679,7 @@
         <v>1918118.1720430108</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3699,16 +3687,16 @@
         <v>32</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>83</v>
@@ -3747,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -3755,7 +3743,7 @@
         <v>33</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>84</v>
@@ -3803,7 +3791,7 @@
         <v>4791010</v>
       </c>
       <c r="P25" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3811,13 +3799,13 @@
         <v>34</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>85</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>80</v>
@@ -3859,7 +3847,7 @@
         <v>1918118.1720430108</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3867,13 +3855,13 @@
         <v>35</v>
       </c>
       <c r="B27" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="C27" s="17" t="s">
-        <v>293</v>
-      </c>
       <c r="D27" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>80</v>
@@ -3915,7 +3903,7 @@
         <v>3234237.5268817204</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3923,16 +3911,16 @@
         <v>36</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>83</v>
@@ -3971,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3979,16 +3967,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>83</v>
@@ -4027,14 +4015,14 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -4070,7 +4058,7 @@
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G31">
         <f>SUM(G8:G9)+SUM(G10:G24)</f>
@@ -4083,7 +4071,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G32">
         <f>G30-G31</f>
@@ -4120,7 +4108,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -4134,19 +4122,19 @@
         <v>69</v>
       </c>
       <c r="D3" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>301</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="F3" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="G3" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="G3" s="25" t="s">
-        <v>304</v>
-      </c>
       <c r="H3" s="25" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -4160,13 +4148,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="27" t="s">
         <v>305</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>306</v>
       </c>
       <c r="E4" s="28">
         <v>1000000</v>
@@ -4196,13 +4184,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>307</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>308</v>
       </c>
       <c r="E5" s="28">
         <v>700000</v>
@@ -4232,13 +4220,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="D6" s="27" t="s">
         <v>310</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>311</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -4268,13 +4256,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="D7" s="27" t="s">
         <v>313</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>314</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -4304,13 +4292,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="D8" s="27" t="s">
         <v>315</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>316</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -4340,13 +4328,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>317</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>318</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -4376,13 +4364,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>319</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>320</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -4410,7 +4398,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4454,12 +4442,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4559,7 +4547,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C8">
         <f>SUM(Штат!G9:G9)</f>
@@ -4582,7 +4570,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C9">
         <f>SUM(Штат!G10:G14)</f>
@@ -4605,7 +4593,7 @@
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G15:G16)</f>
@@ -4628,7 +4616,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G17:G24)</f>
@@ -4688,12 +4676,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4716,7 +4704,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -4748,7 +4736,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -4778,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -4850,7 +4838,7 @@
         <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -4908,7 +4896,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -4936,7 +4924,7 @@
         <v>98</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C12" t="s">
         <v>104</v>
@@ -4954,7 +4942,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
@@ -4966,7 +4954,7 @@
         <v>98</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C13" t="s">
         <v>100</v>
@@ -4984,7 +4972,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
@@ -4996,7 +4984,7 @@
         <v>98</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C14" t="s">
         <v>104</v>
@@ -5015,7 +5003,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
@@ -5103,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
@@ -5175,7 +5163,7 @@
         <v>98</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C20" t="s">
         <v>100</v>
@@ -5194,7 +5182,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
@@ -5206,10 +5194,10 @@
         <v>98</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C21" t="s">
         <v>238</v>
-      </c>
-      <c r="C21" t="s">
-        <v>239</v>
       </c>
       <c r="D21" s="9">
         <v>1</v>
@@ -5225,7 +5213,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
@@ -5237,7 +5225,7 @@
         <v>98</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C22" t="s">
         <v>100</v>
@@ -5256,7 +5244,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
@@ -5268,7 +5256,7 @@
         <v>98</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C23" t="s">
         <v>104</v>
@@ -5287,7 +5275,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
@@ -5299,7 +5287,7 @@
         <v>98</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C24" t="s">
         <v>100</v>
@@ -5318,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -5330,7 +5318,7 @@
         <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C25" t="s">
         <v>100</v>
@@ -5349,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -5361,7 +5349,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C26" t="s">
         <v>100</v>
@@ -5380,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -5392,7 +5380,7 @@
         <v>98</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C27" t="s">
         <v>100</v>
@@ -5411,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -5423,7 +5411,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C28" t="s">
         <v>100</v>
@@ -5442,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="1">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -5454,7 +5442,7 @@
         <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C29" t="s">
         <v>100</v>
@@ -5473,7 +5461,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -5485,7 +5473,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
@@ -5504,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -5604,7 +5592,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -5623,7 +5611,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -5635,7 +5623,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -5663,7 +5651,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
@@ -5682,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" ref="I36" si="2">IF(F36="разово",IF(G36&lt;=3,D36*E36,0),IF(F36="мес",D36*E36*MAX(0,4-G36),D36*E36*MAX(0,4-G36)/12))</f>
@@ -5750,7 +5738,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -5797,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I40" s="5">
         <f>D40*E40*Аренда_мес_2026</f>
@@ -5809,7 +5797,7 @@
         <v>118</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C41" t="s">
         <v>122</v>
@@ -5828,7 +5816,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" ref="I41:I57" si="3">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
@@ -5952,7 +5940,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -5971,7 +5959,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -5983,7 +5971,7 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -6002,7 +5990,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
@@ -6060,7 +6048,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -6158,15 +6146,15 @@
         <v>136</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C53" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="10"/>
       <c r="F53" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G53" s="9"/>
       <c r="H53" s="4"/>
@@ -6235,7 +6223,7 @@
         <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C56" t="s">
         <v>104</v>
@@ -6263,7 +6251,7 @@
         <v>140</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -6312,7 +6300,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6343,18 +6331,18 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>300</v>
-      </c>
       <c r="C5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
       <c r="F5" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G5" s="5">
         <v>3600000</v>
@@ -6362,18 +6350,18 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
       <c r="F6" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G6" s="5">
         <v>1200000</v>
@@ -6381,18 +6369,18 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
       <c r="F7" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G7" s="5">
         <v>6100000</v>
@@ -6400,18 +6388,18 @@
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
       <c r="F8" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G8" s="5">
         <v>18400000</v>
@@ -6419,18 +6407,18 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
       <c r="F9" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G9" s="5">
         <v>9200000</v>
@@ -6438,37 +6426,37 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
       <c r="F10" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G10" s="5">
-        <v>31000271.420000002</v>
+        <v>31008971.420000002</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" t="s">
         <v>246</v>
-      </c>
-      <c r="C11" t="s">
-        <v>247</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
       <c r="F11" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G11" s="5">
         <v>18400000</v>
@@ -6479,7 +6467,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -6487,7 +6475,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="6">
         <f>SUM(G5:G11)</f>
-        <v>87900271.420000002</v>
+        <v>87908971.420000002</v>
       </c>
     </row>
   </sheetData>
@@ -6515,7 +6503,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -6562,7 +6550,7 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6698,7 +6686,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6855,7 +6843,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -7121,7 +7109,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -23,47 +23,48 @@
     <sheet name="Смета фото-видео" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="Авиа_межд">Параметры!$B$24</definedName>
-    <definedName name="Авиа_РК">Параметры!$B$17</definedName>
-    <definedName name="Аренда_депозит">Параметры!$B$47</definedName>
-    <definedName name="Аренда_мес">Параметры!$B$31</definedName>
-    <definedName name="Аренда_мес_2026">Параметры!$B$48</definedName>
-    <definedName name="Аренда_с_НДС">Параметры!$B$46</definedName>
-    <definedName name="Депозит_мес">Параметры!$B$32</definedName>
-    <definedName name="Дней_межд">Параметры!$B$27</definedName>
-    <definedName name="Дней_РК">Параметры!$B$20</definedName>
+    <definedName name="Авиа_межд">Параметры!$B$25</definedName>
+    <definedName name="Авиа_РК">Параметры!$B$18</definedName>
+    <definedName name="Аренда_депозит">Параметры!$B$48</definedName>
+    <definedName name="Аренда_мес">Параметры!$B$32</definedName>
+    <definedName name="Аренда_мес_2026">Параметры!$B$49</definedName>
+    <definedName name="Аренда_с_НДС">Параметры!$B$47</definedName>
+    <definedName name="Депозит_мес">Параметры!$B$33</definedName>
+    <definedName name="Дней_межд">Параметры!$B$28</definedName>
+    <definedName name="Дней_РК">Параметры!$B$21</definedName>
     <definedName name="Кап_ООСМС">Параметры!$B$11</definedName>
     <definedName name="Кап_СО">Параметры!$B$9</definedName>
-    <definedName name="Коммун_мес">Параметры!$B$43</definedName>
-    <definedName name="Курс">Параметры!$B$15</definedName>
-    <definedName name="Мес_2026_новые">Параметры!$B$51</definedName>
+    <definedName name="Коммун_мес">Параметры!$B$44</definedName>
+    <definedName name="Курс">Параметры!$B$16</definedName>
+    <definedName name="Мес_2026_новые">Параметры!$B$52</definedName>
     <definedName name="МЗП">Параметры!$B$4</definedName>
     <definedName name="МРП">Параметры!$B$5</definedName>
-    <definedName name="НДС">Параметры!$B$34</definedName>
-    <definedName name="Ночей_межд">Параметры!$B$28</definedName>
-    <definedName name="Ночей_РК">Параметры!$B$21</definedName>
+    <definedName name="НДС">Параметры!$B$35</definedName>
+    <definedName name="Ночей_межд">Параметры!$B$29</definedName>
+    <definedName name="Ночей_РК">Параметры!$B$22</definedName>
     <definedName name="ОСНС">Параметры!$B$14</definedName>
-    <definedName name="Отель_межд">Параметры!$B$25</definedName>
-    <definedName name="Отель_РК">Параметры!$B$18</definedName>
-    <definedName name="Парковка_мест">Параметры!$B$44</definedName>
-    <definedName name="Парковка_цена">Параметры!$B$45</definedName>
-    <definedName name="Площадь_офиса">Параметры!$B$41</definedName>
-    <definedName name="Поездка_межд">Параметры!$B$30</definedName>
-    <definedName name="Поездка_местн">Параметры!$B$23</definedName>
-    <definedName name="Поездка_РК">Параметры!$B$22</definedName>
-    <definedName name="Резерв">Параметры!$B$33</definedName>
-    <definedName name="Сборка_мебели_проц">Параметры!$B$50</definedName>
-    <definedName name="Ставка_аренды_м2">Параметры!$B$42</definedName>
+    <definedName name="ОСНС_полис">Параметры!$B$15</definedName>
+    <definedName name="Отель_межд">Параметры!$B$26</definedName>
+    <definedName name="Отель_РК">Параметры!$B$19</definedName>
+    <definedName name="Парковка_мест">Параметры!$B$45</definedName>
+    <definedName name="Парковка_цена">Параметры!$B$46</definedName>
+    <definedName name="Площадь_офиса">Параметры!$B$42</definedName>
+    <definedName name="Поездка_межд">Параметры!$B$31</definedName>
+    <definedName name="Поездка_местн">Параметры!$B$24</definedName>
+    <definedName name="Поездка_РК">Параметры!$B$23</definedName>
+    <definedName name="Резерв">Параметры!$B$34</definedName>
+    <definedName name="Сборка_мебели_проц">Параметры!$B$51</definedName>
+    <definedName name="Ставка_аренды_м2">Параметры!$B$43</definedName>
     <definedName name="Ставка_ВОСМС">Параметры!$B$13</definedName>
     <definedName name="Ставка_ООСМС">Параметры!$B$10</definedName>
     <definedName name="Ставка_ОПВ">Параметры!$B$12</definedName>
     <definedName name="Ставка_ОПВР">Параметры!$B$7</definedName>
     <definedName name="Ставка_СН">Параметры!$B$6</definedName>
     <definedName name="Ставка_СО">Параметры!$B$8</definedName>
-    <definedName name="Страх_межд">Параметры!$B$29</definedName>
-    <definedName name="Сут_межд">Параметры!$B$26</definedName>
-    <definedName name="Сут_РК">Параметры!$B$16</definedName>
-    <definedName name="Трансп_РК">Параметры!$B$19</definedName>
+    <definedName name="Страх_межд">Параметры!$B$30</definedName>
+    <definedName name="Сут_межд">Параметры!$B$27</definedName>
+    <definedName name="Сут_РК">Параметры!$B$17</definedName>
+    <definedName name="Трансп_РК">Параметры!$B$20</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -92,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0">
+    <comment ref="B17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -104,7 +105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B33" authorId="0" shapeId="0">
+    <comment ref="B34" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -121,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="416">
   <si>
     <t>Статья</t>
   </si>
@@ -1185,9 +1186,6 @@
     <t>Старт (1 – октябрь, 2 – ноябрь, 3 – декабрь)</t>
   </si>
   <si>
-    <t>ОСНС окт–дек 2026</t>
-  </si>
-  <si>
     <t>Функционал и опыт</t>
   </si>
   <si>
@@ -1281,9 +1279,6 @@
     <t>2. Аутсорс-услуги: юрист МФЦА, сис.админ, разработчик, режиссёр, копирайтер, дизайнер, менеджер по креаторам (с НДС исполнителя)</t>
   </si>
   <si>
-    <t>3. ОСНС штатных сотрудников</t>
-  </si>
-  <si>
     <t>4. Командировки по РК</t>
   </si>
   <si>
@@ -1363,6 +1358,18 @@
   </si>
   <si>
     <t>Непредвиденные расходы: резерв 10% и прочие (нотариальные расходы, страхование фото- и видеооборудования)</t>
+  </si>
+  <si>
+    <t>ОСНС_полис</t>
+  </si>
+  <si>
+    <t>Годовой полис ОСНС на новых сотрудников 2026 года, ₸ (оценка: тариф 0,29% от годового ФОТ)</t>
+  </si>
+  <si>
+    <t>ОСНС (годовой полис новым сотрудникам)</t>
+  </si>
+  <si>
+    <t>3. ОСНС: годовой полис на новых сотрудников</t>
   </si>
 </sst>
 </file>
@@ -1865,7 +1872,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1878,7 +1885,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E29,"штат",Штат!G5:G29)</f>
@@ -1887,7 +1894,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G31</f>
@@ -1896,7 +1903,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M29,Штат!E5:E29,"штат")</f>
@@ -1905,7 +1912,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -1914,16 +1921,16 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N30</f>
-        <v>104924.73118279572</v>
+        <v>500000.00000000017</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -1932,7 +1939,7 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
@@ -1941,7 +1948,7 @@
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
@@ -1950,7 +1957,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
@@ -1959,7 +1966,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
@@ -1968,20 +1975,20 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>126962404.84086022</v>
+        <v>127357480.10967742</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
-        <v>12771240.484086022</v>
+        <v>12810748.010967743</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1990,34 +1997,34 @@
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>22357383.251991395</v>
+        <v>22426916.499303225</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>162091028.57693762</v>
+        <v>162595144.61994839</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
-        <v>87908971.420000002</v>
+        <v>87404855.379999995</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>249999999.99693763</v>
+        <v>249999999.99994838</v>
       </c>
     </row>
   </sheetData>
@@ -2028,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2178,362 +2185,373 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>412</v>
       </c>
       <c r="B15" s="8">
-        <v>530</v>
+        <v>500000</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B16" s="8">
-        <v>2</v>
+        <v>530</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B17" s="8">
-        <v>90000</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B18" s="8">
-        <v>30000</v>
+        <v>90000</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B19" s="8">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B20" s="8">
-        <v>3</v>
+        <v>15000</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="8">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B23" s="8">
         <f>Авиа_РК+Отель_РК*Ночей_РК+Сут_РК*МРП*Дней_РК+Трансп_РК</f>
         <v>190950</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B24" s="8">
         <f>Трансп_РК+Сут_РК*МРП</f>
         <v>23650</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="8">
-        <v>900</v>
-      </c>
-      <c r="C24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B25" s="8">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" s="8">
         <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B27" s="8">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29" s="8">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="8">
+        <v>50</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B31" s="8">
         <f>(Авиа_межд+Отель_межд*Ночей_межд+Сут_межд*Дней_межд+Страх_межд)*Курс</f>
         <v>1219000</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B32" s="8">
         <f>Площадь_офиса*Ставка_аренды_м2+Коммун_мес+Парковка_мест*Парковка_цена</f>
         <v>4909152.0999999996</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>336</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="8">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B33" s="8">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B35" s="8">
         <v>0.16</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>166</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B42" s="13">
         <f>ROUND((52.2+21.4+12.4+33.7+190)*1.1,2)</f>
         <v>340.67</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>334</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>167</v>
-      </c>
-      <c r="B42" s="5">
-        <v>13500</v>
-      </c>
-      <c r="C42" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="5">
+        <v>13500</v>
+      </c>
+      <c r="C43" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>218</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B44" s="5">
         <f>743*309.7</f>
         <v>230107.1</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C44" t="s">
         <v>335</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>168</v>
-      </c>
-      <c r="B44" s="5">
-        <v>2</v>
-      </c>
-      <c r="C44" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B45" s="5">
-        <v>40000</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>169</v>
+      </c>
+      <c r="B46" s="5">
+        <v>40000</v>
+      </c>
+      <c r="C46" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>170</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B47" s="5">
         <f>Аренда_мес*(1+НДС)</f>
         <v>5694616.4359999988</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>172</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B48" s="5">
         <f>Аренда_мес*Депозит_мес</f>
         <v>4909152.0999999996</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>228</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B49" s="15">
         <f>11/31+2</f>
         <v>2.3548387096774195</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
         <v>219</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>220</v>
-      </c>
-      <c r="B50" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="C50" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>230</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B52" s="15">
         <f>Аренда_мес_2026</f>
         <v>2.3548387096774195</v>
       </c>
-      <c r="C51" t="s">
-        <v>380</v>
+      <c r="C52" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -2608,13 +2626,13 @@
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -2663,15 +2681,15 @@
         <v>5454690</v>
       </c>
       <c r="N5" s="18">
-        <f t="shared" ref="N5:N29" si="4">IF(E5="штат",ОСНС*G5*L5/12,0)</f>
-        <v>7000</v>
+        <f>IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
       </c>
       <c r="O5" s="18">
-        <f t="shared" ref="O5:O29" si="5">M5+N5</f>
-        <v>5461690</v>
+        <f t="shared" ref="O5:O29" si="4">M5+N5</f>
+        <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2719,15 +2737,15 @@
         <v>4784010</v>
       </c>
       <c r="N6" s="18">
+        <f>IF(AND(E6="штат",F6="новая"),ОСНС_полис*G6/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="18">
         <f t="shared" si="4"/>
-        <v>7000</v>
-      </c>
-      <c r="O6" s="18">
-        <f t="shared" si="5"/>
-        <v>4791010</v>
+        <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -2775,15 +2793,15 @@
         <v>4784010</v>
       </c>
       <c r="N7" s="18">
+        <f>IF(AND(E7="штат",F7="новая"),ОСНС_полис*G7/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="18">
         <f t="shared" si="4"/>
-        <v>7000</v>
-      </c>
-      <c r="O7" s="18">
-        <f t="shared" si="5"/>
-        <v>4791010</v>
+        <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2831,15 +2849,15 @@
         <v>3755190.6451612907</v>
       </c>
       <c r="N8" s="18">
+        <f>IF(AND(E8="штат",F8="новая"),ОСНС_полис*G8/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O8" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O8" s="18">
-        <f t="shared" si="5"/>
-        <v>3760685.2688172045</v>
+        <v>3790904.9308755766</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2887,15 +2905,15 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N9" s="18">
+        <f>IF(AND(E9="штат",F9="новая"),ОСНС_полис*G9/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O9" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O9" s="18">
-        <f t="shared" si="5"/>
-        <v>2707789.7849462368</v>
+        <v>2738009.4470046088</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2927,15 +2945,15 @@
         <v>1</v>
       </c>
       <c r="J10" s="18">
-        <f t="shared" ref="J10" si="6">IF(E10="штат",ROUND(Ставка_СН*H10*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H10+Ставка_СО*MIN(H10*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H10,Кап_ООСМС*МЗП),0),ROUND(H10*НДС,0))</f>
+        <f t="shared" ref="J10" si="5">IF(E10="штат",ROUND(Ставка_СН*H10*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H10+Ставка_СО*MIN(H10*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H10,Кап_ООСМС*МЗП),0),ROUND(H10*НДС,0))</f>
         <v>159330</v>
       </c>
       <c r="K10" s="18">
-        <f t="shared" ref="K10" si="7">G10*(H10+J10)</f>
+        <f t="shared" ref="K10" si="6">G10*(H10+J10)</f>
         <v>1259330</v>
       </c>
       <c r="L10" s="19">
-        <f t="shared" ref="L10" si="8">IF(AND(F10="новая",I10=1),Мес_2026_новые,MAX(0,4-I10))</f>
+        <f t="shared" ref="L10" si="7">IF(AND(F10="новая",I10=1),Мес_2026_новые,MAX(0,4-I10))</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="M10" s="18">
@@ -2943,12 +2961,12 @@
         <v>2965519.0322580645</v>
       </c>
       <c r="N10" s="18">
+        <f>IF(AND(E10="штат",F10="новая"),ОСНС_полис*G10/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O10" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O10" s="18">
-        <f t="shared" si="5"/>
-        <v>2971013.6559139783</v>
+        <v>3001233.3179723504</v>
       </c>
       <c r="P10" s="17" t="s">
         <v>289</v>
@@ -2999,15 +3017,15 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N11" s="18">
+        <f>IF(AND(E11="штат",F11="новая"),ОСНС_полис*G11/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O11" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O11" s="18">
-        <f t="shared" si="5"/>
-        <v>2707789.7849462368</v>
+        <v>2738009.4470046088</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3055,15 +3073,15 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N12" s="18">
+        <f>IF(AND(E12="штат",F12="новая"),ОСНС_полис*G12/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O12" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O12" s="18">
-        <f t="shared" si="5"/>
-        <v>2707789.7849462368</v>
+        <v>2738009.4470046088</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3111,15 +3129,15 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N13" s="18">
+        <f>IF(AND(E13="штат",F13="новая"),ОСНС_полис*G13/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O13" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O13" s="18">
-        <f t="shared" si="5"/>
-        <v>2707789.7849462368</v>
+        <v>2738009.4470046088</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3167,15 +3185,15 @@
         <v>1912623.548387097</v>
       </c>
       <c r="N14" s="18">
+        <f>IF(AND(E14="штат",F14="новая"),ОСНС_полис*G14/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O14" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O14" s="18">
-        <f t="shared" si="5"/>
-        <v>1918118.1720430108</v>
+        <v>1948337.8341013826</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3207,15 +3225,15 @@
         <v>1</v>
       </c>
       <c r="J15" s="18">
-        <f t="shared" ref="J15" si="9">IF(E15="штат",ROUND(Ставка_СН*H15*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H15+Ставка_СО*MIN(H15*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H15,Кап_ООСМС*МЗП),0),ROUND(H15*НДС,0))</f>
+        <f t="shared" ref="J15" si="8">IF(E15="штат",ROUND(Ставка_СН*H15*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H15+Ставка_СО*MIN(H15*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H15,Кап_ООСМС*МЗП),0),ROUND(H15*НДС,0))</f>
         <v>182890</v>
       </c>
       <c r="K15" s="18">
-        <f t="shared" ref="K15" si="10">G15*(H15+J15)</f>
+        <f t="shared" ref="K15" si="9">G15*(H15+J15)</f>
         <v>1482890</v>
       </c>
       <c r="L15" s="19">
-        <f t="shared" ref="L15" si="11">IF(AND(F15="новая",I15=1),Мес_2026_новые,MAX(0,4-I15))</f>
+        <f t="shared" ref="L15" si="10">IF(AND(F15="новая",I15=1),Мес_2026_новые,MAX(0,4-I15))</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="M15" s="18">
@@ -3223,12 +3241,12 @@
         <v>3491966.7741935486</v>
       </c>
       <c r="N15" s="18">
+        <f>IF(AND(E15="штат",F15="новая"),ОСНС_полис*G15/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O15" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O15" s="18">
-        <f t="shared" si="5"/>
-        <v>3497461.3978494625</v>
+        <v>3527681.0599078345</v>
       </c>
       <c r="P15" s="17" t="s">
         <v>259</v>
@@ -3279,11 +3297,11 @@
         <v>0</v>
       </c>
       <c r="N16" s="22">
+        <f>IF(AND(E16="штат",F16="новая"),ОСНС_полис*G16/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P16" s="21" t="s">
@@ -3335,15 +3353,15 @@
         <v>3491966.7741935486</v>
       </c>
       <c r="N17" s="18">
+        <f>IF(AND(E17="штат",F17="новая"),ОСНС_полис*G17/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O17" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O17" s="18">
-        <f t="shared" si="5"/>
-        <v>3497461.3978494625</v>
+        <v>3527681.0599078345</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3391,15 +3409,15 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N18" s="18">
+        <f>IF(AND(E18="штат",F18="новая"),ОСНС_полис*G18/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O18" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O18" s="18">
-        <f t="shared" si="5"/>
-        <v>2707789.7849462368</v>
+        <v>2738009.4470046088</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -3447,11 +3465,11 @@
         <v>0</v>
       </c>
       <c r="N19" s="22">
+        <f>IF(AND(E19="штат",F19="новая"),ОСНС_полис*G19/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P19" s="21" t="s">
@@ -3487,15 +3505,15 @@
         <v>2</v>
       </c>
       <c r="J20" s="22">
-        <f t="shared" ref="J20" si="12">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
+        <f t="shared" ref="J20" si="11">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
         <v>112000</v>
       </c>
       <c r="K20" s="22">
-        <f t="shared" ref="K20" si="13">G20*(H20+J20)</f>
+        <f t="shared" ref="K20" si="12">G20*(H20+J20)</f>
         <v>0</v>
       </c>
       <c r="L20" s="23">
-        <f t="shared" ref="L20" si="14">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
+        <f t="shared" ref="L20" si="13">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
         <v>2</v>
       </c>
       <c r="M20" s="22">
@@ -3503,11 +3521,11 @@
         <v>0</v>
       </c>
       <c r="N20" s="22">
+        <f>IF(AND(E20="штат",F20="новая"),ОСНС_полис*G20/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P20" s="21" t="s">
@@ -3559,11 +3577,11 @@
         <v>0</v>
       </c>
       <c r="N21" s="22">
+        <f>IF(AND(E21="штат",F21="новая"),ОСНС_полис*G21/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
@@ -3615,12 +3633,12 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N22" s="18">
+        <f>IF(AND(E22="штат",F22="новая"),ОСНС_полис*G22/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O22" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O22" s="18">
-        <f t="shared" si="5"/>
-        <v>2707789.7849462368</v>
+        <v>2738009.4470046088</v>
       </c>
       <c r="P22" s="17" t="s">
         <v>265</v>
@@ -3655,11 +3673,11 @@
         <v>1</v>
       </c>
       <c r="J23" s="18">
-        <f t="shared" ref="J23:J29" si="15">IF(E23="штат",ROUND(Ставка_СН*H23*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H23+Ставка_СО*MIN(H23*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H23,Кап_ООСМС*МЗП),0),ROUND(H23*НДС,0))</f>
+        <f t="shared" ref="J23:J29" si="14">IF(E23="штат",ROUND(Ставка_СН*H23*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H23+Ставка_СО*MIN(H23*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H23,Кап_ООСМС*МЗП),0),ROUND(H23*НДС,0))</f>
         <v>112210</v>
       </c>
       <c r="K23" s="18">
-        <f t="shared" ref="K23:K29" si="16">G23*(H23+J23)</f>
+        <f t="shared" ref="K23:K29" si="15">G23*(H23+J23)</f>
         <v>812210</v>
       </c>
       <c r="L23" s="19">
@@ -3671,12 +3689,12 @@
         <v>1912623.548387097</v>
       </c>
       <c r="N23" s="18">
+        <f>IF(AND(E23="штат",F23="новая"),ОСНС_полис*G23/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O23" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O23" s="18">
-        <f t="shared" si="5"/>
-        <v>1918118.1720430108</v>
+        <v>1948337.8341013826</v>
       </c>
       <c r="P23" s="17" t="s">
         <v>267</v>
@@ -3711,11 +3729,11 @@
         <v>2</v>
       </c>
       <c r="J24" s="22">
+        <f t="shared" si="14"/>
+        <v>112000</v>
+      </c>
+      <c r="K24" s="22">
         <f t="shared" si="15"/>
-        <v>112000</v>
-      </c>
-      <c r="K24" s="22">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L24" s="23">
@@ -3727,11 +3745,11 @@
         <v>0</v>
       </c>
       <c r="N24" s="22">
+        <f>IF(AND(E24="штат",F24="новая"),ОСНС_полис*G24/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
@@ -3767,11 +3785,11 @@
         <v>1</v>
       </c>
       <c r="J25" s="18">
+        <f t="shared" si="14"/>
+        <v>194670</v>
+      </c>
+      <c r="K25" s="18">
         <f t="shared" si="15"/>
-        <v>194670</v>
-      </c>
-      <c r="K25" s="18">
-        <f t="shared" si="16"/>
         <v>1594670</v>
       </c>
       <c r="L25" s="19">
@@ -3783,15 +3801,15 @@
         <v>4784010</v>
       </c>
       <c r="N25" s="18">
+        <f>IF(AND(E25="штат",F25="новая"),ОСНС_полис*G25/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="18">
         <f t="shared" si="4"/>
-        <v>7000</v>
-      </c>
-      <c r="O25" s="18">
-        <f t="shared" si="5"/>
-        <v>4791010</v>
+        <v>4784010</v>
       </c>
       <c r="P25" s="17" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3823,11 +3841,11 @@
         <v>1</v>
       </c>
       <c r="J26" s="18">
+        <f t="shared" si="14"/>
+        <v>112210</v>
+      </c>
+      <c r="K26" s="18">
         <f t="shared" si="15"/>
-        <v>112210</v>
-      </c>
-      <c r="K26" s="18">
-        <f t="shared" si="16"/>
         <v>812210</v>
       </c>
       <c r="L26" s="19">
@@ -3839,12 +3857,12 @@
         <v>1912623.548387097</v>
       </c>
       <c r="N26" s="18">
+        <f>IF(AND(E26="штат",F26="новая"),ОСНС_полис*G26/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O26" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O26" s="18">
-        <f t="shared" si="5"/>
-        <v>1918118.1720430108</v>
+        <v>1948337.8341013826</v>
       </c>
       <c r="P26" s="17" t="s">
         <v>213</v>
@@ -3879,11 +3897,11 @@
         <v>1</v>
       </c>
       <c r="J27" s="18">
+        <f t="shared" si="14"/>
+        <v>171110</v>
+      </c>
+      <c r="K27" s="18">
         <f t="shared" si="15"/>
-        <v>171110</v>
-      </c>
-      <c r="K27" s="18">
-        <f t="shared" si="16"/>
         <v>1371110</v>
       </c>
       <c r="L27" s="19">
@@ -3895,12 +3913,12 @@
         <v>3228742.9032258065</v>
       </c>
       <c r="N27" s="18">
+        <f>IF(AND(E27="штат",F27="новая"),ОСНС_полис*G27/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>35714.285714285717</v>
+      </c>
+      <c r="O27" s="18">
         <f t="shared" si="4"/>
-        <v>5494.6236559139788</v>
-      </c>
-      <c r="O27" s="18">
-        <f t="shared" si="5"/>
-        <v>3234237.5268817204</v>
+        <v>3264457.1889400925</v>
       </c>
       <c r="P27" s="17" t="s">
         <v>293</v>
@@ -3935,11 +3953,11 @@
         <v>1</v>
       </c>
       <c r="J28" s="22">
+        <f t="shared" si="14"/>
+        <v>160000</v>
+      </c>
+      <c r="K28" s="22">
         <f t="shared" si="15"/>
-        <v>160000</v>
-      </c>
-      <c r="K28" s="22">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L28" s="23">
@@ -3951,11 +3969,11 @@
         <v>0</v>
       </c>
       <c r="N28" s="22">
+        <f>IF(AND(E28="штат",F28="новая"),ОСНС_полис*G28/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P28" s="21" t="s">
@@ -3991,11 +4009,11 @@
         <v>1</v>
       </c>
       <c r="J29" s="22">
+        <f t="shared" si="14"/>
+        <v>112000</v>
+      </c>
+      <c r="K29" s="22">
         <f t="shared" si="15"/>
-        <v>112000</v>
-      </c>
-      <c r="K29" s="22">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L29" s="23">
@@ -4007,11 +4025,11 @@
         <v>0</v>
       </c>
       <c r="N29" s="22">
+        <f>IF(AND(E29="штат",F29="новая"),ОСНС_полис*G29/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
@@ -4022,7 +4040,7 @@
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -4047,18 +4065,18 @@
         <v>58691747.741935484</v>
       </c>
       <c r="N30" s="6">
-        <f t="shared" ref="N30:O30" si="17">SUM(N5:N29)</f>
-        <v>104924.73118279572</v>
+        <f t="shared" ref="N30:O30" si="16">SUM(N5:N29)</f>
+        <v>500000.00000000017</v>
       </c>
       <c r="O30" s="6">
-        <f t="shared" si="17"/>
-        <v>58796672.473118283</v>
+        <f t="shared" si="16"/>
+        <v>59191747.741935477</v>
       </c>
       <c r="P30" s="7"/>
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G31">
         <f>SUM(G8:G9)+SUM(G10:G24)</f>
@@ -4071,7 +4089,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G32">
         <f>G30-G31</f>
@@ -4108,7 +4126,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -4676,12 +4694,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4704,7 +4722,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -4736,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -4896,7 +4914,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -5306,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -5337,7 +5355,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -5592,7 +5610,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -5611,7 +5629,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -5738,7 +5756,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -5940,7 +5958,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -5959,7 +5977,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -5971,7 +5989,7 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -5990,7 +6008,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
@@ -6048,7 +6066,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -6223,7 +6241,7 @@
         <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C56" t="s">
         <v>104</v>
@@ -6251,7 +6269,7 @@
         <v>140</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -6300,7 +6318,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6440,7 +6458,7 @@
         <v>244</v>
       </c>
       <c r="G10" s="5">
-        <v>31008971.420000002</v>
+        <v>30504855.379999999</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6467,7 +6485,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -6475,7 +6493,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="6">
         <f>SUM(G5:G11)</f>
-        <v>87908971.420000002</v>
+        <v>87404855.379999995</v>
       </c>
     </row>
   </sheetData>
@@ -6503,7 +6521,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -6686,7 +6704,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6843,7 +6861,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -7109,7 +7127,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -1357,9 +1357,6 @@
     <t>Папки, конверты, скобы и скрепки, степлеры и дыроколы, архивные короба, батарейки и мелкая электрика</t>
   </si>
   <si>
-    <t>Непредвиденные расходы: резерв 10% и прочие (нотариальные расходы, страхование фото- и видеооборудования)</t>
-  </si>
-  <si>
     <t>ОСНС_полис</t>
   </si>
   <si>
@@ -1370,6 +1367,9 @@
   </si>
   <si>
     <t>3. ОСНС: годовой полис на новых сотрудников</t>
+  </si>
+  <si>
+    <t>Непредвиденные расходы: резерв 10% и прочие (страхование фото- и видеооборудования, нотариус, переводы и т.п.)</t>
   </si>
 </sst>
 </file>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N30</f>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
@@ -2185,13 +2185,13 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B15" s="8">
         <v>500000</v>
       </c>
       <c r="C15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2626,7 +2626,7 @@
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
@@ -2681,11 +2681,11 @@
         <v>5454690</v>
       </c>
       <c r="N5" s="18">
-        <f>IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" ref="N5:N29" si="4">IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
         <v>0</v>
       </c>
       <c r="O5" s="18">
-        <f t="shared" ref="O5:O29" si="4">M5+N5</f>
+        <f t="shared" ref="O5:O29" si="5">M5+N5</f>
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
@@ -2737,11 +2737,11 @@
         <v>4784010</v>
       </c>
       <c r="N6" s="18">
-        <f>IF(AND(E6="штат",F6="новая"),ОСНС_полис*G6/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O6" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
@@ -2793,11 +2793,11 @@
         <v>4784010</v>
       </c>
       <c r="N7" s="18">
-        <f>IF(AND(E7="штат",F7="новая"),ОСНС_полис*G7/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O7" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
@@ -2849,11 +2849,11 @@
         <v>3755190.6451612907</v>
       </c>
       <c r="N8" s="18">
-        <f>IF(AND(E8="штат",F8="новая"),ОСНС_полис*G8/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O8" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3790904.9308755766</v>
       </c>
       <c r="P8" s="17" t="s">
@@ -2905,11 +2905,11 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N9" s="18">
-        <f>IF(AND(E9="штат",F9="новая"),ОСНС_полис*G9/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O9" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2738009.4470046088</v>
       </c>
       <c r="P9" s="17" t="s">
@@ -2945,15 +2945,15 @@
         <v>1</v>
       </c>
       <c r="J10" s="18">
-        <f t="shared" ref="J10" si="5">IF(E10="штат",ROUND(Ставка_СН*H10*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H10+Ставка_СО*MIN(H10*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H10,Кап_ООСМС*МЗП),0),ROUND(H10*НДС,0))</f>
+        <f t="shared" ref="J10" si="6">IF(E10="штат",ROUND(Ставка_СН*H10*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H10+Ставка_СО*MIN(H10*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H10,Кап_ООСМС*МЗП),0),ROUND(H10*НДС,0))</f>
         <v>159330</v>
       </c>
       <c r="K10" s="18">
-        <f t="shared" ref="K10" si="6">G10*(H10+J10)</f>
+        <f t="shared" ref="K10" si="7">G10*(H10+J10)</f>
         <v>1259330</v>
       </c>
       <c r="L10" s="19">
-        <f t="shared" ref="L10" si="7">IF(AND(F10="новая",I10=1),Мес_2026_новые,MAX(0,4-I10))</f>
+        <f t="shared" ref="L10" si="8">IF(AND(F10="новая",I10=1),Мес_2026_новые,MAX(0,4-I10))</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="M10" s="18">
@@ -2961,11 +2961,11 @@
         <v>2965519.0322580645</v>
       </c>
       <c r="N10" s="18">
-        <f>IF(AND(E10="штат",F10="новая"),ОСНС_полис*G10/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O10" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3001233.3179723504</v>
       </c>
       <c r="P10" s="17" t="s">
@@ -3017,11 +3017,11 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N11" s="18">
-        <f>IF(AND(E11="штат",F11="новая"),ОСНС_полис*G11/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O11" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2738009.4470046088</v>
       </c>
       <c r="P11" s="17" t="s">
@@ -3073,11 +3073,11 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N12" s="18">
-        <f>IF(AND(E12="штат",F12="новая"),ОСНС_полис*G12/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O12" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2738009.4470046088</v>
       </c>
       <c r="P12" s="17" t="s">
@@ -3129,11 +3129,11 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N13" s="18">
-        <f>IF(AND(E13="штат",F13="новая"),ОСНС_полис*G13/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O13" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2738009.4470046088</v>
       </c>
       <c r="P13" s="17" t="s">
@@ -3185,11 +3185,11 @@
         <v>1912623.548387097</v>
       </c>
       <c r="N14" s="18">
-        <f>IF(AND(E14="штат",F14="новая"),ОСНС_полис*G14/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O14" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1948337.8341013826</v>
       </c>
       <c r="P14" s="17" t="s">
@@ -3225,15 +3225,15 @@
         <v>1</v>
       </c>
       <c r="J15" s="18">
-        <f t="shared" ref="J15" si="8">IF(E15="штат",ROUND(Ставка_СН*H15*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H15+Ставка_СО*MIN(H15*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H15,Кап_ООСМС*МЗП),0),ROUND(H15*НДС,0))</f>
+        <f t="shared" ref="J15" si="9">IF(E15="штат",ROUND(Ставка_СН*H15*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H15+Ставка_СО*MIN(H15*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H15,Кап_ООСМС*МЗП),0),ROUND(H15*НДС,0))</f>
         <v>182890</v>
       </c>
       <c r="K15" s="18">
-        <f t="shared" ref="K15" si="9">G15*(H15+J15)</f>
+        <f t="shared" ref="K15" si="10">G15*(H15+J15)</f>
         <v>1482890</v>
       </c>
       <c r="L15" s="19">
-        <f t="shared" ref="L15" si="10">IF(AND(F15="новая",I15=1),Мес_2026_новые,MAX(0,4-I15))</f>
+        <f t="shared" ref="L15" si="11">IF(AND(F15="новая",I15=1),Мес_2026_новые,MAX(0,4-I15))</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="M15" s="18">
@@ -3241,11 +3241,11 @@
         <v>3491966.7741935486</v>
       </c>
       <c r="N15" s="18">
-        <f>IF(AND(E15="штат",F15="новая"),ОСНС_полис*G15/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O15" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3527681.0599078345</v>
       </c>
       <c r="P15" s="17" t="s">
@@ -3297,11 +3297,11 @@
         <v>0</v>
       </c>
       <c r="N16" s="22">
-        <f>IF(AND(E16="штат",F16="новая"),ОСНС_полис*G16/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O16" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P16" s="21" t="s">
@@ -3353,11 +3353,11 @@
         <v>3491966.7741935486</v>
       </c>
       <c r="N17" s="18">
-        <f>IF(AND(E17="штат",F17="новая"),ОСНС_полис*G17/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O17" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3527681.0599078345</v>
       </c>
       <c r="P17" s="17" t="s">
@@ -3409,11 +3409,11 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N18" s="18">
-        <f>IF(AND(E18="штат",F18="новая"),ОСНС_полис*G18/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O18" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2738009.4470046088</v>
       </c>
       <c r="P18" s="17" t="s">
@@ -3465,11 +3465,11 @@
         <v>0</v>
       </c>
       <c r="N19" s="22">
-        <f>IF(AND(E19="штат",F19="новая"),ОСНС_полис*G19/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O19" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P19" s="21" t="s">
@@ -3505,15 +3505,15 @@
         <v>2</v>
       </c>
       <c r="J20" s="22">
-        <f t="shared" ref="J20" si="11">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
+        <f t="shared" ref="J20" si="12">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
         <v>112000</v>
       </c>
       <c r="K20" s="22">
-        <f t="shared" ref="K20" si="12">G20*(H20+J20)</f>
+        <f t="shared" ref="K20" si="13">G20*(H20+J20)</f>
         <v>0</v>
       </c>
       <c r="L20" s="23">
-        <f t="shared" ref="L20" si="13">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
+        <f t="shared" ref="L20" si="14">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
         <v>2</v>
       </c>
       <c r="M20" s="22">
@@ -3521,11 +3521,11 @@
         <v>0</v>
       </c>
       <c r="N20" s="22">
-        <f>IF(AND(E20="штат",F20="новая"),ОСНС_полис*G20/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O20" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P20" s="21" t="s">
@@ -3577,11 +3577,11 @@
         <v>0</v>
       </c>
       <c r="N21" s="22">
-        <f>IF(AND(E21="штат",F21="новая"),ОСНС_полис*G21/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O21" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
@@ -3633,11 +3633,11 @@
         <v>2702295.1612903229</v>
       </c>
       <c r="N22" s="18">
-        <f>IF(AND(E22="штат",F22="новая"),ОСНС_полис*G22/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O22" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2738009.4470046088</v>
       </c>
       <c r="P22" s="17" t="s">
@@ -3673,11 +3673,11 @@
         <v>1</v>
       </c>
       <c r="J23" s="18">
-        <f t="shared" ref="J23:J29" si="14">IF(E23="штат",ROUND(Ставка_СН*H23*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H23+Ставка_СО*MIN(H23*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H23,Кап_ООСМС*МЗП),0),ROUND(H23*НДС,0))</f>
+        <f t="shared" ref="J23:J29" si="15">IF(E23="штат",ROUND(Ставка_СН*H23*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H23+Ставка_СО*MIN(H23*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H23,Кап_ООСМС*МЗП),0),ROUND(H23*НДС,0))</f>
         <v>112210</v>
       </c>
       <c r="K23" s="18">
-        <f t="shared" ref="K23:K29" si="15">G23*(H23+J23)</f>
+        <f t="shared" ref="K23:K29" si="16">G23*(H23+J23)</f>
         <v>812210</v>
       </c>
       <c r="L23" s="19">
@@ -3689,11 +3689,11 @@
         <v>1912623.548387097</v>
       </c>
       <c r="N23" s="18">
-        <f>IF(AND(E23="штат",F23="новая"),ОСНС_полис*G23/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O23" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1948337.8341013826</v>
       </c>
       <c r="P23" s="17" t="s">
@@ -3729,11 +3729,11 @@
         <v>2</v>
       </c>
       <c r="J24" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>112000</v>
       </c>
       <c r="K24" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L24" s="23">
@@ -3745,11 +3745,11 @@
         <v>0</v>
       </c>
       <c r="N24" s="22">
-        <f>IF(AND(E24="штат",F24="новая"),ОСНС_полис*G24/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O24" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
@@ -3785,11 +3785,11 @@
         <v>1</v>
       </c>
       <c r="J25" s="18">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>194670</v>
       </c>
       <c r="K25" s="18">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1594670</v>
       </c>
       <c r="L25" s="19">
@@ -3801,11 +3801,11 @@
         <v>4784010</v>
       </c>
       <c r="N25" s="18">
-        <f>IF(AND(E25="штат",F25="новая"),ОСНС_полис*G25/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O25" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4784010</v>
       </c>
       <c r="P25" s="17" t="s">
@@ -3841,11 +3841,11 @@
         <v>1</v>
       </c>
       <c r="J26" s="18">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>112210</v>
       </c>
       <c r="K26" s="18">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>812210</v>
       </c>
       <c r="L26" s="19">
@@ -3857,11 +3857,11 @@
         <v>1912623.548387097</v>
       </c>
       <c r="N26" s="18">
-        <f>IF(AND(E26="штат",F26="новая"),ОСНС_полис*G26/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O26" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1948337.8341013826</v>
       </c>
       <c r="P26" s="17" t="s">
@@ -3897,11 +3897,11 @@
         <v>1</v>
       </c>
       <c r="J27" s="18">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>171110</v>
       </c>
       <c r="K27" s="18">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1371110</v>
       </c>
       <c r="L27" s="19">
@@ -3913,11 +3913,11 @@
         <v>3228742.9032258065</v>
       </c>
       <c r="N27" s="18">
-        <f>IF(AND(E27="штат",F27="новая"),ОСНС_полис*G27/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>35714.285714285717</v>
       </c>
       <c r="O27" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3264457.1889400925</v>
       </c>
       <c r="P27" s="17" t="s">
@@ -3953,11 +3953,11 @@
         <v>1</v>
       </c>
       <c r="J28" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>160000</v>
       </c>
       <c r="K28" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L28" s="23">
@@ -3969,11 +3969,11 @@
         <v>0</v>
       </c>
       <c r="N28" s="22">
-        <f>IF(AND(E28="штат",F28="новая"),ОСНС_полис*G28/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O28" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P28" s="21" t="s">
@@ -4009,11 +4009,11 @@
         <v>1</v>
       </c>
       <c r="J29" s="22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>112000</v>
       </c>
       <c r="K29" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L29" s="23">
@@ -4025,11 +4025,11 @@
         <v>0</v>
       </c>
       <c r="N29" s="22">
-        <f>IF(AND(E29="штат",F29="новая"),ОСНС_полис*G29/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O29" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
@@ -4065,11 +4065,11 @@
         <v>58691747.741935484</v>
       </c>
       <c r="N30" s="6">
-        <f t="shared" ref="N30:O30" si="16">SUM(N5:N29)</f>
+        <f t="shared" ref="N30:O30" si="17">SUM(N5:N29)</f>
         <v>500000.00000000017</v>
       </c>
       <c r="O30" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>59191747.741935477</v>
       </c>
       <c r="P30" s="7"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Свод" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="417">
   <si>
     <t>Статья</t>
   </si>
@@ -976,18 +976,12 @@
     <t>Главный исполнительный директор (ГИД)</t>
   </si>
   <si>
-    <t>Заместитель ГИД (стратегия, проекты)</t>
-  </si>
-  <si>
     <t>Национальный координатор проектного офиса</t>
   </si>
   <si>
     <t>Национальному координатору</t>
   </si>
   <si>
-    <t>Заместителю ГИД (стратегия, проекты)</t>
-  </si>
-  <si>
     <t>Заместитель директора (МЭПР, ЦГО, регионы)</t>
   </si>
   <si>
@@ -1000,12 +994,6 @@
     <t>Административный персонал</t>
   </si>
   <si>
-    <t>Менеджер международных проектов</t>
-  </si>
-  <si>
-    <t>Международные проекты Фонда</t>
-  </si>
-  <si>
     <t>Юрист (МФЦА) — аутсорс</t>
   </si>
   <si>
@@ -1201,12 +1189,6 @@
     <t>[Қаражан Е.Н.] Общее руководство Фондом и проектным офисом, соглашение с МЭПР, отчётность перед органами Фонда. Опыт: к.э.н. (PhD), MSc LSE («Болашақ»), Chevening; ГИД ЦАКФ с 02.2025 (Региональный экологический саммит 2026); председатель Правления ИЭИ, советник Министра национальной экономики, консультант АБР, директор по устойчивому развитию ФНБ «Самрук-Қазына».</t>
   </si>
   <si>
-    <t>[Кононец А.В.] Стратегия и портфель проектов Фонда, партнёрства; экспертная группа; курация проектного управления. Опыт: 20 лет в медиа и госкоммуникациях – руководитель пресс-службы, советник министра труда и социальной защиты, главный редактор Total.kz; в ЦАКФ с 07.2025.</t>
-  </si>
-  <si>
-    <t>[Темирбеков М.Е.] Наём, закупки, офис, договоры с поставщиками. Опыт: международные экономические отношения (диплом с отличием); акиматы Костанайской области и Астаны; руководитель аппарата холдинга (3 000+ сотрудников); проекты МЗ РК и Всемирного банка; в ЦАКФ с 02.2025, член Управляющего совета.</t>
-  </si>
-  <si>
     <t>[Серикжанова А.] Руководство проектным офисом, календарь мероприятий, работа с акиматами и госорганами. Опыт: PhD по политологии.</t>
   </si>
   <si>
@@ -1264,9 +1246,6 @@
     <t>Месяцев 2026 для новых сотрудников (зарплата, отчисления): приём одновременно с заездом в офис — с 21.10.2026, ≈2,35 мес. Действующие — 3 мес.</t>
   </si>
   <si>
-    <t>Бюджет проектного офиса «Таза Қазақстан» (ЦАКФ) на октябрь–декабрь 2026 года, ₸</t>
-  </si>
-  <si>
     <t>Штатная численность, чел.</t>
   </si>
   <si>
@@ -1370,6 +1349,30 @@
   </si>
   <si>
     <t>Непредвиденные расходы: резерв 10% и прочие (страхование фото- и видеооборудования, нотариус, переводы и т.п.)</t>
+  </si>
+  <si>
+    <t>Бюджет ЦАКФ на октябрь–декабрь 2026 года, ₸</t>
+  </si>
+  <si>
+    <t>Международные и страновые проекты Фонда</t>
+  </si>
+  <si>
+    <t>[Темирбеков М.Е.] Наём, закупки, офис, договоры с поставщиками. Опыт: международные экономические отношения (диплом с отличием); акиматы Костанайской области и Астаны; руководитель аппарата холдинга (3 000+ сотрудников); проекты МЗ РК и Всемирного банка; руководитель в общественных организациях, структур в квазигоссекторе; в ЦАКФ с 02.2025, член Управляющего совета.</t>
+  </si>
+  <si>
+    <t>Заместитель ГИД по стратегии и проектам</t>
+  </si>
+  <si>
+    <t>Проектный офис для Центральной Азии по изменению климата и зеленой энергетике</t>
+  </si>
+  <si>
+    <t>Менеджер проектов</t>
+  </si>
+  <si>
+    <t>Руководителю Проектного офиса для Центральной Азии</t>
+  </si>
+  <si>
+    <t>[Кононец А.В.] Стратегия и портфель проектов Фонда, партнёрства; Проектный офис для Центральной Азии; курация проектного управления. Опыт: 20 лет в медиа и госкоммуникациях – руководитель пресс-службы, советник министра труда и социальной защиты, главный редактор Казправды, Total.kz и др.; в ЦАКФ с 07.2025.</t>
   </si>
 </sst>
 </file>
@@ -1870,9 +1873,9 @@
     <col min="5" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="34.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>380</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1885,7 +1888,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E29,"штат",Штат!G5:G29)</f>
@@ -1894,7 +1897,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G31</f>
@@ -1903,7 +1906,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M29,Штат!E5:E29,"штат")</f>
@@ -1912,7 +1915,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -1921,7 +1924,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N30</f>
@@ -1930,7 +1933,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -1939,7 +1942,7 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
@@ -1948,7 +1951,7 @@
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
@@ -1957,7 +1960,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
@@ -1966,7 +1969,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
@@ -1975,7 +1978,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
@@ -1984,7 +1987,7 @@
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
@@ -1993,7 +1996,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
@@ -2002,7 +2005,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
@@ -2011,7 +2014,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
@@ -2020,7 +2023,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
@@ -2185,13 +2188,13 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B15" s="8">
         <v>500000</v>
       </c>
       <c r="C15" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2382,7 +2385,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2420,17 +2423,17 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2442,7 +2445,7 @@
         <v>340.67</v>
       </c>
       <c r="C42" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2453,7 +2456,7 @@
         <v>13500</v>
       </c>
       <c r="C43" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2465,7 +2468,7 @@
         <v>230107.1</v>
       </c>
       <c r="C44" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2487,7 +2490,7 @@
         <v>40000</v>
       </c>
       <c r="C46" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2551,7 +2554,7 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="C52" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -2579,7 +2582,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2611,7 +2614,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -2626,13 +2629,13 @@
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -2689,7 +2692,7 @@
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2700,7 +2703,7 @@
         <v>282</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>284</v>
+        <v>412</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -2745,10 +2748,10 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>3</v>
       </c>
@@ -2801,7 +2804,7 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>360</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2812,7 +2815,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2857,7 +2860,7 @@
         <v>3790904.9308755766</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2913,7 +2916,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2924,7 +2927,7 @@
         <v>254</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>256</v>
@@ -2969,7 +2972,7 @@
         <v>3001233.3179723504</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3025,7 +3028,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3081,7 +3084,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3137,7 +3140,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" x14ac:dyDescent="0.25">
@@ -3193,7 +3196,7 @@
         <v>1948337.8341013826</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3207,7 +3210,7 @@
         <v>251</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>80</v>
@@ -3260,7 +3263,7 @@
         <v>258</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>253</v>
@@ -3305,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="21" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3319,7 +3322,7 @@
         <v>262</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>80</v>
@@ -3361,7 +3364,7 @@
         <v>3527681.0599078345</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3417,7 +3420,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -3473,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -3529,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="21" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -3585,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -3753,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -3761,7 +3764,7 @@
         <v>33</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>84</v>
@@ -3809,7 +3812,7 @@
         <v>4784010</v>
       </c>
       <c r="P25" s="17" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3817,7 +3820,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>85</v>
@@ -3868,18 +3871,18 @@
         <v>213</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>35</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>291</v>
+        <v>413</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>292</v>
+        <v>414</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>287</v>
+        <v>415</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>80</v>
@@ -3921,7 +3924,7 @@
         <v>3264457.1889400925</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>293</v>
+        <v>410</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3929,10 +3932,10 @@
         <v>36</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>214</v>
@@ -3977,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="21" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3985,10 +3988,10 @@
         <v>37</v>
       </c>
       <c r="B29" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="C29" s="21" t="s">
         <v>291</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>295</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>214</v>
@@ -4033,14 +4036,14 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -4076,7 +4079,7 @@
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G31">
         <f>SUM(G8:G9)+SUM(G10:G24)</f>
@@ -4089,7 +4092,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G32">
         <f>G30-G31</f>
@@ -4126,7 +4129,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -4140,19 +4143,19 @@
         <v>69</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -4166,13 +4169,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E4" s="28">
         <v>1000000</v>
@@ -4202,13 +4205,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E5" s="28">
         <v>700000</v>
@@ -4238,13 +4241,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -4274,13 +4277,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -4310,13 +4313,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -4346,13 +4349,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -4382,13 +4385,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -4416,7 +4419,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4460,7 +4463,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4518,7 +4521,7 @@
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="str">
         <f>Штат!C6</f>
-        <v>Заместитель ГИД (стратегия, проекты)</v>
+        <v>Заместитель ГИД по стратегии и проектам</v>
       </c>
       <c r="C6">
         <f>Штат!G6</f>
@@ -4565,7 +4568,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C8">
         <f>SUM(Штат!G9:G9)</f>
@@ -4588,7 +4591,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C9">
         <f>SUM(Штат!G10:G14)</f>
@@ -4611,7 +4614,7 @@
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G15:G16)</f>
@@ -4694,12 +4697,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4722,7 +4725,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -4754,7 +4757,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -4784,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -4856,7 +4859,7 @@
         <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -4914,7 +4917,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -5324,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -5355,7 +5358,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -5429,7 +5432,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C28" t="s">
         <v>100</v>
@@ -5448,7 +5451,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="1">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -5460,7 +5463,7 @@
         <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C29" t="s">
         <v>100</v>
@@ -5479,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -5491,7 +5494,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
@@ -5510,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -5610,7 +5613,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -5629,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -5641,7 +5644,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -5669,7 +5672,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
@@ -5688,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" ref="I36" si="2">IF(F36="разово",IF(G36&lt;=3,D36*E36,0),IF(F36="мес",D36*E36*MAX(0,4-G36),D36*E36*MAX(0,4-G36)/12))</f>
@@ -5756,7 +5759,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -5803,7 +5806,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="I40" s="5">
         <f>D40*E40*Аренда_мес_2026</f>
@@ -5958,7 +5961,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -5977,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -5989,7 +5992,7 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -6008,7 +6011,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
@@ -6066,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -6164,7 +6167,7 @@
         <v>136</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C53" t="s">
         <v>246</v>
@@ -6241,7 +6244,7 @@
         <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C56" t="s">
         <v>104</v>
@@ -6269,7 +6272,7 @@
         <v>140</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -6318,7 +6321,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6349,10 +6352,10 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C5" t="s">
         <v>246</v>
@@ -6368,7 +6371,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>248</v>
@@ -6387,10 +6390,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C7" t="s">
         <v>246</v>
@@ -6406,10 +6409,10 @@
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C8" t="s">
         <v>246</v>
@@ -6425,7 +6428,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>247</v>
@@ -6444,7 +6447,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>249</v>
@@ -6463,7 +6466,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>245</v>
@@ -6485,7 +6488,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -6521,7 +6524,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -6568,7 +6571,7 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6704,7 +6707,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6861,7 +6864,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -7127,7 +7130,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -901,9 +901,6 @@
     <t>Департамент цифрового развития</t>
   </si>
   <si>
-    <t>[Тастан] Платформа TAZA.KZ, цифровой мониторинг, работа с подрядчиком платформы</t>
-  </si>
-  <si>
     <t>аутсорс</t>
   </si>
   <si>
@@ -976,9 +973,6 @@
     <t>Главный исполнительный директор (ГИД)</t>
   </si>
   <si>
-    <t>Национальный координатор проектного офиса</t>
-  </si>
-  <si>
     <t>Национальному координатору</t>
   </si>
   <si>
@@ -1189,30 +1183,12 @@
     <t>[Қаражан Е.Н.] Общее руководство Фондом и проектным офисом, соглашение с МЭПР, отчётность перед органами Фонда. Опыт: к.э.н. (PhD), MSc LSE («Болашақ»), Chevening; ГИД ЦАКФ с 02.2025 (Региональный экологический саммит 2026); председатель Правления ИЭИ, советник Министра национальной экономики, консультант АБР, директор по устойчивому развитию ФНБ «Самрук-Қазына».</t>
   </si>
   <si>
-    <t>[Серикжанова А.] Руководство проектным офисом, календарь мероприятий, работа с акиматами и госорганами. Опыт: PhD по политологии.</t>
-  </si>
-  <si>
     <t>[Тленчиева Ш.] Исследования восприятия акции, опросы. Опыт: PhD по социологии.</t>
   </si>
   <si>
-    <t>[Қуандық Ж.] Ведение проектов, координация регионов. Опыт: PhD-кандидат (государственное и местное управление); член Президентского молодёжного кадрового резерва.</t>
-  </si>
-  <si>
-    <t>[Жандилдаев Б.] Координация регионов, взаимодействие с госорганами и общественными организациями. Опыт: магистр; управление проектами, региональная координация, взаимодействие с государственными и общественными организациями.</t>
-  </si>
-  <si>
-    <t>[Шербаева Б.] Ведение проектов календаря, планы и отчёты, взаимодействие с акиматами. Опыт: магистр; управление республиканскими и региональными проектами.</t>
-  </si>
-  <si>
-    <t>[Абенов А.] Аналитическое сопровождение проектов, методические материалы. Опыт: аналитическое сопровождение государственных программ, разработка методических материалов.</t>
-  </si>
-  <si>
     <t>[Сундетбай С.] Коммуникационная стратегия, медиаплан, работа со СМИ. Опыт: коммуникации, медиа и PR.</t>
   </si>
   <si>
-    <t>[Талғат А.] Пресс-служба, тексты и материалы для СМИ. Опыт: PR- и контент-стратегии, управление брендами, digital-контент.</t>
-  </si>
-  <si>
     <t>[Оразбаева М.К.] Бюджет проекта, раздельный учёт, работа со спонсорами, финансовая отчётность, налоги. Опыт: 30+ лет в финансах, бухгалтерском и налоговом учёте – главный бухгалтер АО «Международный аэропорт Нурсултан Назарбаев», аудит BDO Qazaqstan (МФЦА); профессиональный бухгалтер РК, ДипИФР ACCA, налоговый консультант.</t>
   </si>
   <si>
@@ -1373,6 +1349,30 @@
   </si>
   <si>
     <t>[Кононец А.В.] Стратегия и портфель проектов Фонда, партнёрства; Проектный офис для Центральной Азии; курация проектного управления. Опыт: 20 лет в медиа и госкоммуникациях – руководитель пресс-службы, советник министра труда и социальной защиты, главный редактор Казправды, Total.kz и др.; в ЦАКФ с 07.2025.</t>
+  </si>
+  <si>
+    <t>[Серикжанова А.Т.] Руководитель проектного офиса: руководство командой, календарь мероприятий, работа с акиматами и госорганами. Опыт: директор Департамента развития талантов, образовательных программ и экспертного сопровождения КФ «Фонд развития креативных индустрий»; PhD, постдокторантура «Политология» (ЕНУ им. Л.Н. Гумилёва), магистр права LLM (РУДН), магистр юридических наук (КазНУ им. аль-Фараби).</t>
+  </si>
+  <si>
+    <t>Руководитель проектного офиса «Таза Қазақстан»</t>
+  </si>
+  <si>
+    <t>[Қуандық Ж.Б.] Проектный менеджер: ведение проектов, координация регионов, молодёжные проекты. Опыт: президент благотворительного фонда «Dauletten», основатель портала для молодёжи jastar.online; КазНУ им. аль-Фараби – бакалавр «Государственное и местное управление», MBA, докторантура (PhD).</t>
+  </si>
+  <si>
+    <t>[Жандилдаев Б.Б.] Проектный менеджер: координация регионов, взаимодействие с госорганами и общественными организациями. Опыт: исполнительный директор ОЮЛ «Конгресс молодежи Казахстана»; бакалавр «Государственное и местное управление» (КазУТБ), «Финансы» (Тұран-Астана), магистр юриспруденции («Синергия»).</t>
+  </si>
+  <si>
+    <t>[Шербаева Б.Б.] Проектный менеджер: ведение проектов календаря, планы и отчёты, взаимодействие с акиматами. Опыт: председатель ОСО «За будущее Казахстана»; бакалавр «Профессиональное обучение», магистр «Казахский язык и литература» (Казахский национальный женский педагогический университет).</t>
+  </si>
+  <si>
+    <t>[Абенов А.Д.] Аналитик: аналитическое сопровождение проектов, методические материалы, отчётность. Опыт: руководитель управления развития кадров и документооборота АО «Центр международных программ»; бакалавр «Метрология, стандартизация и сертификация» (Карагандинский экономический университет).</t>
+  </si>
+  <si>
+    <t>[Тастан Н.Е.] IT-специалист: платформа TAZA.KZ, цифровой мониторинг, информационная безопасность, работа с подрядчиком платформы. Опыт: советник председателя по информационной безопасности НАО «ННПЦ Тіл-Қазына»; бакалавр «Вычислительная техника и программное обеспечение» (ЕНУ им. Л.Н. Гумилёва), магистр юриспруденции.</t>
+  </si>
+  <si>
+    <t>[Талғат А.Т.] PR-менеджер: пресс-служба, тексты и материалы для СМИ и соцсетей. Опыт: ведущий специалист КФ «Фонд развития креативных индустрий»; бакалавр журналистики (ЕНУ им. Л.Н. Гумилёва).</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1875,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1888,7 +1888,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E29,"штат",Штат!G5:G29)</f>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G31</f>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M29,Штат!E5:E29,"штат")</f>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N30</f>
@@ -1933,7 +1933,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
@@ -2188,13 +2188,13 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B15" s="8">
         <v>500000</v>
       </c>
       <c r="C15" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2385,7 +2385,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2423,17 +2423,17 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2445,7 +2445,7 @@
         <v>340.67</v>
       </c>
       <c r="C42" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2456,7 +2456,7 @@
         <v>13500</v>
       </c>
       <c r="C43" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2468,7 +2468,7 @@
         <v>230107.1</v>
       </c>
       <c r="C44" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2479,7 +2479,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2490,7 +2490,7 @@
         <v>40000</v>
       </c>
       <c r="C46" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2554,7 +2554,7 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="C52" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -2582,7 +2582,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2614,7 +2614,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -2629,13 +2629,13 @@
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -2644,10 +2644,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>282</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>283</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>79</v>
@@ -2692,7 +2692,7 @@
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2700,10 +2700,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -2748,7 +2748,7 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2756,10 +2756,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>82</v>
@@ -2804,10 +2804,10 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>4</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>284</v>
+        <v>410</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2860,7 +2860,7 @@
         <v>3790904.9308755766</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>355</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2916,7 +2916,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2927,7 +2927,7 @@
         <v>254</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>256</v>
@@ -2972,10 +2972,10 @@
         <v>3001233.3179723504</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>15</v>
       </c>
@@ -3028,10 +3028,10 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>17</v>
       </c>
@@ -3084,10 +3084,10 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>18</v>
       </c>
@@ -3140,10 +3140,10 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>19</v>
       </c>
@@ -3196,10 +3196,10 @@
         <v>1948337.8341013826</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>23</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>251</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>80</v>
@@ -3252,7 +3252,7 @@
         <v>3527681.0599078345</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>259</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3263,13 +3263,13 @@
         <v>258</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>253</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>83</v>
@@ -3308,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3316,13 +3316,13 @@
         <v>25</v>
       </c>
       <c r="B17" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>262</v>
-      </c>
       <c r="D17" s="17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>80</v>
@@ -3364,18 +3364,18 @@
         <v>3527681.0599078345</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>26</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>216</v>
@@ -3420,7 +3420,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>362</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -3428,16 +3428,16 @@
         <v>27</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>83</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -3484,16 +3484,16 @@
         <v>28</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>83</v>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="21" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -3540,16 +3540,16 @@
         <v>29</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>83</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -3596,10 +3596,10 @@
         <v>30</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>216</v>
@@ -3644,7 +3644,7 @@
         <v>2738009.4470046088</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -3652,10 +3652,10 @@
         <v>31</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>216</v>
@@ -3700,7 +3700,7 @@
         <v>1948337.8341013826</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3708,16 +3708,16 @@
         <v>32</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D24" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>83</v>
@@ -3756,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -3764,7 +3764,7 @@
         <v>33</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>84</v>
@@ -3812,7 +3812,7 @@
         <v>4784010</v>
       </c>
       <c r="P25" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3820,7 +3820,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>85</v>
@@ -3876,13 +3876,13 @@
         <v>35</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>80</v>
@@ -3924,7 +3924,7 @@
         <v>3264457.1889400925</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3932,16 +3932,16 @@
         <v>36</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>214</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>83</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="21" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3988,16 +3988,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="C29" s="21" t="s">
         <v>289</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>291</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>214</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>83</v>
@@ -4036,14 +4036,14 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -4077,9 +4077,9 @@
       </c>
       <c r="P30" s="7"/>
     </row>
-    <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G31">
         <f>SUM(G8:G9)+SUM(G10:G24)</f>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G32">
         <f>G30-G31</f>
@@ -4129,7 +4129,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -4143,19 +4143,19 @@
         <v>69</v>
       </c>
       <c r="D3" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="F3" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="G3" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="F3" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>299</v>
-      </c>
       <c r="H3" s="25" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -4169,13 +4169,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E4" s="28">
         <v>1000000</v>
@@ -4205,13 +4205,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E5" s="28">
         <v>700000</v>
@@ -4241,13 +4241,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>304</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>306</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -4277,13 +4277,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>307</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>308</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>309</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -4313,13 +4313,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -4349,13 +4349,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -4385,13 +4385,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -4419,7 +4419,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4463,7 +4463,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4545,7 +4545,7 @@
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="str">
         <f>Штат!C8</f>
-        <v>Национальный координатор проектного офиса</v>
+        <v>Руководитель проектного офиса «Таза Қазақстан»</v>
       </c>
       <c r="C7">
         <f>Штат!G8</f>
@@ -4568,7 +4568,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C8">
         <f>SUM(Штат!G9:G9)</f>
@@ -4591,7 +4591,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C9">
         <f>SUM(Штат!G10:G14)</f>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G15:G16)</f>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G17:G24)</f>
@@ -4697,12 +4697,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4725,7 +4725,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -4757,7 +4757,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -4787,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -4859,7 +4859,7 @@
         <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -4917,7 +4917,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -5308,7 +5308,7 @@
         <v>98</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C24" t="s">
         <v>100</v>
@@ -5327,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -5339,7 +5339,7 @@
         <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C25" t="s">
         <v>100</v>
@@ -5358,7 +5358,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -5370,7 +5370,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C26" t="s">
         <v>100</v>
@@ -5389,7 +5389,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -5401,7 +5401,7 @@
         <v>98</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C27" t="s">
         <v>100</v>
@@ -5420,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -5432,7 +5432,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C28" t="s">
         <v>100</v>
@@ -5451,7 +5451,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="1">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -5463,7 +5463,7 @@
         <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C29" t="s">
         <v>100</v>
@@ -5482,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -5494,7 +5494,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
@@ -5513,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -5613,7 +5613,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -5644,7 +5644,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -5672,7 +5672,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
@@ -5691,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" ref="I36" si="2">IF(F36="разово",IF(G36&lt;=3,D36*E36,0),IF(F36="мес",D36*E36*MAX(0,4-G36),D36*E36*MAX(0,4-G36)/12))</f>
@@ -5759,7 +5759,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -5806,7 +5806,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I40" s="5">
         <f>D40*E40*Аренда_мес_2026</f>
@@ -5837,7 +5837,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" ref="I41:I57" si="3">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
@@ -5961,7 +5961,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -5980,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -5992,7 +5992,7 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -6011,7 +6011,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
@@ -6069,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -6167,7 +6167,7 @@
         <v>136</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C53" t="s">
         <v>246</v>
@@ -6244,7 +6244,7 @@
         <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C56" t="s">
         <v>104</v>
@@ -6272,7 +6272,7 @@
         <v>140</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -6321,7 +6321,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6352,10 +6352,10 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C5" t="s">
         <v>246</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>248</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C7" t="s">
         <v>246</v>
@@ -6409,10 +6409,10 @@
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C8" t="s">
         <v>246</v>
@@ -6428,7 +6428,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>247</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>249</v>
@@ -6466,7 +6466,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>245</v>
@@ -6488,7 +6488,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -6524,7 +6524,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -6571,7 +6571,7 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6707,7 +6707,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6864,7 +6864,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -7130,7 +7130,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -1351,28 +1351,28 @@
     <t>[Кононец А.В.] Стратегия и портфель проектов Фонда, партнёрства; Проектный офис для Центральной Азии; курация проектного управления. Опыт: 20 лет в медиа и госкоммуникациях – руководитель пресс-службы, советник министра труда и социальной защиты, главный редактор Казправды, Total.kz и др.; в ЦАКФ с 07.2025.</t>
   </si>
   <si>
-    <t>[Серикжанова А.Т.] Руководитель проектного офиса: руководство командой, календарь мероприятий, работа с акиматами и госорганами. Опыт: директор Департамента развития талантов, образовательных программ и экспертного сопровождения КФ «Фонд развития креативных индустрий»; PhD, постдокторантура «Политология» (ЕНУ им. Л.Н. Гумилёва), магистр права LLM (РУДН), магистр юридических наук (КазНУ им. аль-Фараби).</t>
-  </si>
-  <si>
     <t>Руководитель проектного офиса «Таза Қазақстан»</t>
   </si>
   <si>
-    <t>[Қуандық Ж.Б.] Проектный менеджер: ведение проектов, координация регионов, молодёжные проекты. Опыт: президент благотворительного фонда «Dauletten», основатель портала для молодёжи jastar.online; КазНУ им. аль-Фараби – бакалавр «Государственное и местное управление», MBA, докторантура (PhD).</t>
-  </si>
-  <si>
-    <t>[Жандилдаев Б.Б.] Проектный менеджер: координация регионов, взаимодействие с госорганами и общественными организациями. Опыт: исполнительный директор ОЮЛ «Конгресс молодежи Казахстана»; бакалавр «Государственное и местное управление» (КазУТБ), «Финансы» (Тұран-Астана), магистр юриспруденции («Синергия»).</t>
-  </si>
-  <si>
-    <t>[Шербаева Б.Б.] Проектный менеджер: ведение проектов календаря, планы и отчёты, взаимодействие с акиматами. Опыт: председатель ОСО «За будущее Казахстана»; бакалавр «Профессиональное обучение», магистр «Казахский язык и литература» (Казахский национальный женский педагогический университет).</t>
-  </si>
-  <si>
-    <t>[Абенов А.Д.] Аналитик: аналитическое сопровождение проектов, методические материалы, отчётность. Опыт: руководитель управления развития кадров и документооборота АО «Центр международных программ»; бакалавр «Метрология, стандартизация и сертификация» (Карагандинский экономический университет).</t>
-  </si>
-  <si>
-    <t>[Тастан Н.Е.] IT-специалист: платформа TAZA.KZ, цифровой мониторинг, информационная безопасность, работа с подрядчиком платформы. Опыт: советник председателя по информационной безопасности НАО «ННПЦ Тіл-Қазына»; бакалавр «Вычислительная техника и программное обеспечение» (ЕНУ им. Л.Н. Гумилёва), магистр юриспруденции.</t>
-  </si>
-  <si>
-    <t>[Талғат А.Т.] PR-менеджер: пресс-служба, тексты и материалы для СМИ и соцсетей. Опыт: ведущий специалист КФ «Фонд развития креативных индустрий»; бакалавр журналистики (ЕНУ им. Л.Н. Гумилёва).</t>
+    <t>[Серикжанова Айгерим] Руководитель проектного офиса: руководство командой, календарь мероприятий, работа с акиматами и госорганами. Опыт: директор Департамента развития талантов, образовательных программ и экспертного сопровождения КФ «Фонд развития креативных индустрий»; PhD, постдокторантура «Политология» (ЕНУ им. Л.Н. Гумилёва), магистр права LLM (РУДН), магистр юридических наук (КазНУ им. аль-Фараби).</t>
+  </si>
+  <si>
+    <t>[Қуандық Жасұлан] Проектный менеджер: ведение проектов, координация регионов, молодёжные проекты. Опыт: президент благотворительного фонда «Dauletten», основатель портала для молодёжи jastar.online; КазНУ им. аль-Фараби – бакалавр «Государственное и местное управление», MBA, докторантура (PhD).</t>
+  </si>
+  <si>
+    <t>[Жандилдаев Бакдаулет] Проектный менеджер: координация регионов, взаимодействие с госорганами и общественными организациями. Опыт: исполнительный директор ОЮЛ «Конгресс молодежи Казахстана»; бакалавр «Государственное и местное управление» (КазУТБ), «Финансы» (Тұран-Астана), магистр юриспруденции («Синергия»).</t>
+  </si>
+  <si>
+    <t>[Шербаева Бибинур] Проектный менеджер: ведение проектов календаря, планы и отчёты, взаимодействие с акиматами. Опыт: председатель ОСО «За будущее Казахстана»; бакалавр «Профессиональное обучение», магистр «Казахский язык и литература» (Казахский национальный женский педагогический университет).</t>
+  </si>
+  <si>
+    <t>[Абенов Алибек] Аналитик: аналитическое сопровождение проектов, методические материалы, отчётность. Опыт: руководитель управления развития кадров и документооборота АО «Центр международных программ»; бакалавр «Метрология, стандартизация и сертификация» (Карагандинский экономический университет).</t>
+  </si>
+  <si>
+    <t>[Тастан Нұрбол] IT-специалист: платформа TAZA.KZ, цифровой мониторинг, информационная безопасность, работа с подрядчиком платформы. Опыт: советник председателя по информационной безопасности НАО «ННПЦ Тіл-Қазына»; бакалавр «Вычислительная техника и программное обеспечение» (ЕНУ им. Л.Н. Гумилёва), магистр юриспруденции.</t>
+  </si>
+  <si>
+    <t>[Талғат Айман] PR-менеджер: пресс-служба, тексты и материалы для СМИ и соцсетей. Опыт: ведущий специалист КФ «Фонд развития креативных индустрий»; бакалавр журналистики (ЕНУ им. Л.Н. Гумилёва).</t>
   </si>
 </sst>
 </file>
@@ -2815,7 +2815,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2860,7 +2860,7 @@
         <v>3790904.9308755766</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3143,7 +3143,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>19</v>
       </c>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Свод" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="425">
   <si>
     <t>Статья</t>
   </si>
@@ -916,9 +916,6 @@
     <t>Ведущий специалист — фотограф, рилсмейкер</t>
   </si>
   <si>
-    <t>[Жумабай] Фотосъёмка, короткие видео</t>
-  </si>
-  <si>
     <t>Ведущий специалист — менеджер по блогерам</t>
   </si>
   <si>
@@ -931,15 +928,9 @@
     <t>Копирайтер — аутсорс</t>
   </si>
   <si>
-    <t>Дизайнер — аутсорс</t>
-  </si>
-  <si>
     <t>Менеджер по креаторам и креативным проектам — аутсорс</t>
   </si>
   <si>
-    <t>Группа «Коммуникация и креатив» (4 чел.): съёмки и освещение мероприятий в регионах</t>
-  </si>
-  <si>
     <t>Заместитель ГИД (адм.-хоз. вопросы, закупки, кадры, проекты)</t>
   </si>
   <si>
@@ -1054,12 +1045,6 @@
     <t>Тексты для соцсетей, сайта, СМИ</t>
   </si>
   <si>
-    <t>Дизайнер</t>
-  </si>
-  <si>
-    <t>Визуалы, инфографика, макеты</t>
-  </si>
-  <si>
     <t>Менеджер по креаторам и креативным проектам</t>
   </si>
   <si>
@@ -1078,9 +1063,6 @@
     <t>[аутсорс] Тексты для соцсетей, сайта, СМИ</t>
   </si>
   <si>
-    <t>[аутсорс] Визуалы, инфографика, макеты</t>
-  </si>
-  <si>
     <t>[аутсорс] Работа с креаторами, креативные проекты</t>
   </si>
   <si>
@@ -1156,12 +1138,6 @@
     <t>Второй кулер – для переговорной зоны  (первый – в комплекте бытовой техники). Kaspi.kz (Астана) на 10.10.2026 – 35 990 ₸ с НДС, в бюджете без НДС (÷1,16): https://kaspi.kz/shop/p/midea-mk-32h-belyi-25900012/</t>
   </si>
   <si>
-    <t>Департамент социологических исследований и аналитики (1 чел.)</t>
-  </si>
-  <si>
-    <t>Департамент проектного управления и региональной координации (5 чел.)</t>
-  </si>
-  <si>
     <t>Командировки по РК на октябрь–декабрь 2026 года, ₸</t>
   </si>
   <si>
@@ -1186,9 +1162,6 @@
     <t>[Тленчиева Ш.] Исследования восприятия акции, опросы. Опыт: PhD по социологии.</t>
   </si>
   <si>
-    <t>[Сундетбай С.] Коммуникационная стратегия, медиаплан, работа со СМИ. Опыт: коммуникации, медиа и PR.</t>
-  </si>
-  <si>
     <t>[Оразбаева М.К.] Бюджет проекта, раздельный учёт, работа со спонсорами, финансовая отчётность, налоги. Опыт: 30+ лет в финансах, бухгалтерском и налоговом учёте – главный бухгалтер АО «Международный аэропорт Нурсултан Назарбаев», аудит BDO Qazaqstan (МФЦА); профессиональный бухгалтер РК, ДипИФР ACCA, налоговый консультант.</t>
   </si>
   <si>
@@ -1204,9 +1177,6 @@
     <t>Старт (1 – октябрь)</t>
   </si>
   <si>
-    <t>новые сотрудники (14) без 2 производительных; 4 действующих – со своей техникой; аутсорс – со своей</t>
-  </si>
-  <si>
     <t>Первоочередные проекты на октябрь–декабрь 2026 года, ₸</t>
   </si>
   <si>
@@ -1231,9 +1201,6 @@
     <t>1. Персонал: оклады и отчисления работодателя (СН, ОПВР, СО, ООСМС)</t>
   </si>
   <si>
-    <t>2. Аутсорс-услуги: юрист МФЦА, сис.админ, разработчик, режиссёр, копирайтер, дизайнер, менеджер по креаторам (с НДС исполнителя)</t>
-  </si>
-  <si>
     <t>4. Командировки по РК</t>
   </si>
   <si>
@@ -1264,9 +1231,6 @@
     <t>Стойка ресепшн</t>
   </si>
   <si>
-    <t>По 1 на рабочее место новых сотрудников (14) и 2 у стола совещаний. b2bcompany.kz на 30.09.2026 – 4 118 ₸ с НДС (код 9320), в бюджете без НДС (÷1,16)</t>
-  </si>
-  <si>
     <t>ТВ и ВКС – 1, МФУ и сетевое оборудование – 1, кухонная зона – 1. b2bcompany.kz на 30.09.2026 – 6 101 ₸ с НДС (код 51417), в бюджете без НДС (÷1,16)</t>
   </si>
   <si>
@@ -1315,9 +1279,6 @@
     <t>ОСНС_полис</t>
   </si>
   <si>
-    <t>Годовой полис ОСНС на новых сотрудников 2026 года, ₸ (оценка: тариф 0,29% от годового ФОТ)</t>
-  </si>
-  <si>
     <t>ОСНС (годовой полис новым сотрудникам)</t>
   </si>
   <si>
@@ -1366,13 +1327,76 @@
     <t>[Шербаева Бибинур] Проектный менеджер: ведение проектов календаря, планы и отчёты, взаимодействие с акиматами. Опыт: председатель ОСО «За будущее Казахстана»; бакалавр «Профессиональное обучение», магистр «Казахский язык и литература» (Казахский национальный женский педагогический университет).</t>
   </si>
   <si>
-    <t>[Абенов Алибек] Аналитик: аналитическое сопровождение проектов, методические материалы, отчётность. Опыт: руководитель управления развития кадров и документооборота АО «Центр международных программ»; бакалавр «Метрология, стандартизация и сертификация» (Карагандинский экономический университет).</t>
-  </si>
-  <si>
     <t>[Тастан Нұрбол] IT-специалист: платформа TAZA.KZ, цифровой мониторинг, информационная безопасность, работа с подрядчиком платформы. Опыт: советник председателя по информационной безопасности НАО «ННПЦ Тіл-Қазына»; бакалавр «Вычислительная техника и программное обеспечение» (ЕНУ им. Л.Н. Гумилёва), магистр юриспруденции.</t>
   </si>
   <si>
     <t>[Талғат Айман] PR-менеджер: пресс-служба, тексты и материалы для СМИ и соцсетей. Опыт: ведущий специалист КФ «Фонд развития креативных индустрий»; бакалавр журналистики (ЕНУ им. Л.Н. Гумилёва).</t>
+  </si>
+  <si>
+    <t>[Сағынұлы С.] Коммуникационная стратегия, медиаплан, работа со СМИ</t>
+  </si>
+  <si>
+    <t>[Жумабай Б.] Фотосъёмка, короткие видео</t>
+  </si>
+  <si>
+    <t>Ведущий специалист — дизайнер</t>
+  </si>
+  <si>
+    <t>[Найла] Визуалы, инфографика, макеты, фирменный стиль</t>
+  </si>
+  <si>
+    <t>[Тулесова А.] Ведение проектов и закреплённых регионов, мониторинг мероприятий, отчётность</t>
+  </si>
+  <si>
+    <t>[Арманов Р.] Ведение проектов и закреплённых регионов, мониторинг мероприятий (с декабря 2026)</t>
+  </si>
+  <si>
+    <t>[Мирам А.] Ведение проектов и закреплённых регионов, сбор данных (с декабря 2026)</t>
+  </si>
+  <si>
+    <t>[Өміртай А.] Руководитель департамента социологии: программа исследований, методология измерения поведения, ежегодный доклад</t>
+  </si>
+  <si>
+    <t>Главный специалист — аналитик</t>
+  </si>
+  <si>
+    <t>[Абенов Алибек] Аналитик: большие данные, дашборды, расчёт KPI, аналитическое сопровождение проектов. Опыт: руководитель управления развития кадров и документооборота АО «Центр международных программ»; бакалавр «Метрология, стандартизация и сертификация» (Карагандинский экономический университет).</t>
+  </si>
+  <si>
+    <t>Социолог — аутсорс</t>
+  </si>
+  <si>
+    <t>[Нурканат А.] Социолог (аутсорс): опросы, полевые работы, обработка данных</t>
+  </si>
+  <si>
+    <t>Социолог (Нурканат А.)</t>
+  </si>
+  <si>
+    <t>Руководителю департамента социологии</t>
+  </si>
+  <si>
+    <t>Опросы и полевые работы, обработка данных</t>
+  </si>
+  <si>
+    <t>Департамент социологических исследований и аналитики (3 чел.)</t>
+  </si>
+  <si>
+    <t>Департамент проектного управления и региональной координации (7 чел., из них 2 – с декабря)</t>
+  </si>
+  <si>
+    <t>Группа «Коммуникация и креатив» (5 чел.): съёмки и освещение мероприятий в регионах</t>
+  </si>
+  <si>
+    <t>новые сотрудники (19) без 2 производительных; 4 действующих – со своей техникой; аутсорс – со своей</t>
+  </si>
+  <si>
+    <t>По 1 на рабочее место новых сотрудников (19) и 2 у стола совещаний. b2bcompany.kz на 30.09.2026 – 4 118 ₸ с НДС (код 9320), в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>Годовой полис ОСНС на новых сотрудников 2026 года: 0,29% от их годового ФОТ (тариф по КП сентября 2026), ₸</t>
+  </si>
+  <si>
+    <t>2. Аутсорс-услуги: юрист МФЦА, сис.админ, разработчик, режиссёр, копирайтер, социолог, менеджер по креаторам (с НДС исполнителя)</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1899,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1888,70 +1912,70 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B4" s="37">
-        <f>SUMIF(Штат!E5:E29,"штат",Штат!G5:G29)</f>
-        <v>18</v>
+        <f>SUMIF(Штат!E5:E34,"штат",Штат!G5:G34)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B5" s="37">
-        <f>Штат!G31</f>
-        <v>12</v>
+        <f>Штат!G36</f>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B6" s="38">
-        <f>SUMIFS(Штат!M5:M29,Штат!E5:E29,"штат")</f>
-        <v>58691747.741935484</v>
+        <f>SUMIFS(Штат!M5:M34,Штат!E5:E34,"штат")</f>
+        <v>68758393.225806445</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>369</v>
+        <v>424</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
-        <v>14567354.838709679</v>
+        <v>14855483.870967744</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="B8" s="38">
-        <f>Штат!N30</f>
-        <v>500000.00000000017</v>
+        <f>Штат!N35</f>
+        <v>665000</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
-        <v>3783804.032258065</v>
+        <v>4906387.0967741935</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
-        <v>29170035</v>
+        <v>31437785</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
@@ -1960,16 +1984,16 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
-        <v>589500</v>
+        <v>694500</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
@@ -1978,56 +2002,56 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>127357480.10967742</v>
+        <v>141372587.69032258</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
-        <v>12810748.010967743</v>
+        <v>14212258.769032259</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>22426916.499303225</v>
+        <v>24893575.433496777</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>162595144.61994839</v>
+        <v>180478421.89285162</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
-        <v>87404855.379999995</v>
+        <v>69521578.109999999</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>249999999.99994838</v>
+        <v>250000000.00285161</v>
       </c>
     </row>
   </sheetData>
@@ -2188,13 +2212,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="B15" s="8">
-        <v>500000</v>
+        <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$34,Штат!$E$5:$E$34,"штат",Штат!$F$5:$F$34,"новая"),-3)</f>
+        <v>665000</v>
       </c>
       <c r="C15" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2385,7 +2410,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2423,17 +2448,17 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2445,7 +2470,7 @@
         <v>340.67</v>
       </c>
       <c r="C42" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2456,7 +2481,7 @@
         <v>13500</v>
       </c>
       <c r="C43" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2468,7 +2493,7 @@
         <v>230107.1</v>
       </c>
       <c r="C44" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2479,7 +2504,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2490,7 +2515,7 @@
         <v>40000</v>
       </c>
       <c r="C46" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2554,7 +2579,7 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="C52" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -2569,7 +2594,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -2582,7 +2607,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2614,7 +2639,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -2629,13 +2654,13 @@
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -2644,10 +2669,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>79</v>
@@ -2668,31 +2693,31 @@
         <v>1</v>
       </c>
       <c r="J5" s="18">
-        <f t="shared" ref="J5:J22" si="0">IF(E5="штат",ROUND(Ставка_СН*H5*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H5+Ставка_СО*MIN(H5*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H5,Кап_ООСМС*МЗП),0),ROUND(H5*НДС,0))</f>
+        <f t="shared" ref="J5:J27" si="0">IF(E5="штат",ROUND(Ставка_СН*H5*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H5+Ставка_СО*MIN(H5*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H5,Кап_ООСМС*МЗП),0),ROUND(H5*НДС,0))</f>
         <v>218230</v>
       </c>
       <c r="K5" s="18">
-        <f t="shared" ref="K5:K22" si="1">G5*(H5+J5)</f>
+        <f t="shared" ref="K5:K27" si="1">G5*(H5+J5)</f>
         <v>1818230</v>
       </c>
       <c r="L5" s="19">
-        <f t="shared" ref="L5:L29" si="2">IF(AND(F5="новая",I5=1),Мес_2026_новые,MAX(0,4-I5))</f>
+        <f t="shared" ref="L5:L34" si="2">IF(AND(F5="новая",I5=1),Мес_2026_новые,MAX(0,4-I5))</f>
         <v>3</v>
       </c>
       <c r="M5" s="18">
-        <f t="shared" ref="M5:M29" si="3">K5*L5</f>
+        <f t="shared" ref="M5:M34" si="3">K5*L5</f>
         <v>5454690</v>
       </c>
       <c r="N5" s="18">
-        <f t="shared" ref="N5:N29" si="4">IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$29,"штат",$F$5:$F$29,"новая"),0)</f>
+        <f t="shared" ref="N5:N34" si="4">IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$34,"штат",$F$5:$F$34,"новая"),0)</f>
         <v>0</v>
       </c>
       <c r="O5" s="18">
-        <f t="shared" ref="O5:O29" si="5">M5+N5</f>
+        <f t="shared" ref="O5:O34" si="5">M5+N5</f>
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2700,10 +2725,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -2748,7 +2773,7 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2756,10 +2781,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>82</v>
@@ -2804,7 +2829,7 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2815,7 +2840,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2853,14 +2878,14 @@
       </c>
       <c r="N8" s="18">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
+        <v>35000</v>
       </c>
       <c r="O8" s="18">
         <f t="shared" si="5"/>
-        <v>3790904.9308755766</v>
+        <v>3790190.6451612907</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2871,10 +2896,10 @@
         <v>250</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>80</v>
@@ -2886,51 +2911,51 @@
         <v>1</v>
       </c>
       <c r="H9" s="18">
-        <v>1000000</v>
+        <v>1300000</v>
       </c>
       <c r="I9" s="16">
         <v>1</v>
       </c>
       <c r="J9" s="18">
-        <f t="shared" si="0"/>
-        <v>147550</v>
+        <f t="shared" ref="J9:J11" si="6">IF(E9="штат",ROUND(Ставка_СН*H9*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H9+Ставка_СО*MIN(H9*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H9,Кап_ООСМС*МЗП),0),ROUND(H9*НДС,0))</f>
+        <v>182890</v>
       </c>
       <c r="K9" s="18">
-        <f t="shared" si="1"/>
-        <v>1147550</v>
+        <f t="shared" ref="K9:K11" si="7">G9*(H9+J9)</f>
+        <v>1482890</v>
       </c>
       <c r="L9" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="L9:L11" si="8">IF(AND(F9="новая",I9=1),Мес_2026_новые,MAX(0,4-I9))</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="M9" s="18">
-        <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
+        <f t="shared" ref="M9:M11" si="9">K9*L9</f>
+        <v>3491966.7741935486</v>
       </c>
       <c r="N9" s="18">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
+        <v>35000</v>
       </c>
       <c r="O9" s="18">
-        <f t="shared" si="5"/>
-        <v>2738009.4470046088</v>
+        <f t="shared" ref="O9:O11" si="10">M9+N9</f>
+        <v>3526966.7741935486</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>284</v>
+        <v>411</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>80</v>
@@ -2942,107 +2967,107 @@
         <v>1</v>
       </c>
       <c r="H10" s="18">
-        <v>1100000</v>
+        <v>1000000</v>
       </c>
       <c r="I10" s="16">
         <v>1</v>
       </c>
       <c r="J10" s="18">
-        <f t="shared" ref="J10" si="6">IF(E10="штат",ROUND(Ставка_СН*H10*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H10+Ставка_СО*MIN(H10*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H10,Кап_ООСМС*МЗП),0),ROUND(H10*НДС,0))</f>
-        <v>159330</v>
+        <f t="shared" si="6"/>
+        <v>147550</v>
       </c>
       <c r="K10" s="18">
-        <f t="shared" ref="K10" si="7">G10*(H10+J10)</f>
-        <v>1259330</v>
+        <f t="shared" si="7"/>
+        <v>1147550</v>
       </c>
       <c r="L10" s="19">
-        <f t="shared" ref="L10" si="8">IF(AND(F10="новая",I10=1),Мес_2026_новые,MAX(0,4-I10))</f>
+        <f t="shared" si="8"/>
         <v>2.3548387096774195</v>
       </c>
       <c r="M10" s="18">
-        <f t="shared" si="3"/>
-        <v>2965519.0322580645</v>
+        <f t="shared" si="9"/>
+        <v>2702295.1612903229</v>
       </c>
       <c r="N10" s="18">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
+        <v>35000</v>
       </c>
       <c r="O10" s="18">
-        <f t="shared" si="5"/>
-        <v>3001233.3179723504</v>
+        <f t="shared" si="10"/>
+        <v>2737295.1612903229</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
-        <v>15</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="16" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="20">
+        <v>6</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="16">
-        <v>1</v>
-      </c>
-      <c r="H11" s="18">
-        <v>1000000</v>
-      </c>
-      <c r="I11" s="16">
-        <v>1</v>
-      </c>
-      <c r="J11" s="18">
-        <f t="shared" si="0"/>
-        <v>147550</v>
-      </c>
-      <c r="K11" s="18">
-        <f t="shared" si="1"/>
-        <v>1147550</v>
-      </c>
-      <c r="L11" s="19">
-        <f t="shared" si="2"/>
+      <c r="G11" s="20">
+        <v>0</v>
+      </c>
+      <c r="H11" s="22">
+        <v>700000</v>
+      </c>
+      <c r="I11" s="20">
+        <v>1</v>
+      </c>
+      <c r="J11" s="22">
+        <f t="shared" si="6"/>
+        <v>112000</v>
+      </c>
+      <c r="K11" s="22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="23">
+        <f t="shared" si="8"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M11" s="18">
-        <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
-      </c>
-      <c r="N11" s="18">
+      <c r="M11" s="22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="22">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
-      </c>
-      <c r="O11" s="18">
-        <f t="shared" si="5"/>
-        <v>2738009.4470046088</v>
-      </c>
-      <c r="P11" s="17" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="O11" s="22">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="21" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>80</v>
@@ -3077,25 +3102,25 @@
       </c>
       <c r="N12" s="18">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
+        <v>35000</v>
       </c>
       <c r="O12" s="18">
         <f t="shared" si="5"/>
-        <v>2738009.4470046088</v>
+        <v>2737295.1612903229</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>254</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>256</v>
@@ -3110,74 +3135,74 @@
         <v>1</v>
       </c>
       <c r="H13" s="18">
+        <v>1100000</v>
+      </c>
+      <c r="I13" s="16">
+        <v>1</v>
+      </c>
+      <c r="J13" s="18">
+        <f t="shared" ref="J13" si="11">IF(E13="штат",ROUND(Ставка_СН*H13*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H13+Ставка_СО*MIN(H13*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H13,Кап_ООСМС*МЗП),0),ROUND(H13*НДС,0))</f>
+        <v>159330</v>
+      </c>
+      <c r="K13" s="18">
+        <f t="shared" ref="K13" si="12">G13*(H13+J13)</f>
+        <v>1259330</v>
+      </c>
+      <c r="L13" s="19">
+        <f t="shared" ref="L13" si="13">IF(AND(F13="новая",I13=1),Мес_2026_новые,MAX(0,4-I13))</f>
+        <v>2.3548387096774195</v>
+      </c>
+      <c r="M13" s="18">
+        <f t="shared" si="3"/>
+        <v>2965519.0322580645</v>
+      </c>
+      <c r="N13" s="18">
+        <f t="shared" si="4"/>
+        <v>35000</v>
+      </c>
+      <c r="O13" s="18">
+        <f t="shared" si="5"/>
+        <v>3000519.0322580645</v>
+      </c>
+      <c r="P13" s="17" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>15</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="16">
+        <v>1</v>
+      </c>
+      <c r="H14" s="18">
         <v>1000000</v>
       </c>
-      <c r="I13" s="16">
-        <v>1</v>
-      </c>
-      <c r="J13" s="18">
+      <c r="I14" s="16">
+        <v>1</v>
+      </c>
+      <c r="J14" s="18">
         <f t="shared" si="0"/>
         <v>147550</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K14" s="18">
         <f t="shared" si="1"/>
         <v>1147550</v>
-      </c>
-      <c r="L13" s="19">
-        <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
-      </c>
-      <c r="M13" s="18">
-        <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
-      </c>
-      <c r="N13" s="18">
-        <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
-      </c>
-      <c r="O13" s="18">
-        <f t="shared" si="5"/>
-        <v>2738009.4470046088</v>
-      </c>
-      <c r="P13" s="17" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
-        <v>19</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="16">
-        <v>1</v>
-      </c>
-      <c r="H14" s="18">
-        <v>700000</v>
-      </c>
-      <c r="I14" s="16">
-        <v>1</v>
-      </c>
-      <c r="J14" s="18">
-        <f t="shared" si="0"/>
-        <v>112210</v>
-      </c>
-      <c r="K14" s="18">
-        <f t="shared" si="1"/>
-        <v>812210</v>
       </c>
       <c r="L14" s="19">
         <f t="shared" si="2"/>
@@ -3185,32 +3210,32 @@
       </c>
       <c r="M14" s="18">
         <f t="shared" si="3"/>
-        <v>1912623.548387097</v>
+        <v>2702295.1612903229</v>
       </c>
       <c r="N14" s="18">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
+        <v>35000</v>
       </c>
       <c r="O14" s="18">
         <f t="shared" si="5"/>
-        <v>1948337.8341013826</v>
+        <v>2737295.1612903229</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>80</v>
@@ -3222,350 +3247,350 @@
         <v>1</v>
       </c>
       <c r="H15" s="18">
-        <v>1300000</v>
+        <v>1000000</v>
       </c>
       <c r="I15" s="16">
         <v>1</v>
       </c>
       <c r="J15" s="18">
-        <f t="shared" ref="J15" si="9">IF(E15="штат",ROUND(Ставка_СН*H15*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H15+Ставка_СО*MIN(H15*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H15,Кап_ООСМС*МЗП),0),ROUND(H15*НДС,0))</f>
-        <v>182890</v>
+        <f t="shared" si="0"/>
+        <v>147550</v>
       </c>
       <c r="K15" s="18">
-        <f t="shared" ref="K15" si="10">G15*(H15+J15)</f>
-        <v>1482890</v>
+        <f t="shared" si="1"/>
+        <v>1147550</v>
       </c>
       <c r="L15" s="19">
-        <f t="shared" ref="L15" si="11">IF(AND(F15="новая",I15=1),Мес_2026_новые,MAX(0,4-I15))</f>
+        <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
       <c r="M15" s="18">
         <f t="shared" si="3"/>
-        <v>3491966.7741935486</v>
+        <v>2702295.1612903229</v>
       </c>
       <c r="N15" s="18">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
+        <v>35000</v>
       </c>
       <c r="O15" s="18">
         <f t="shared" si="5"/>
-        <v>3527681.0599078345</v>
+        <v>2737295.1612903229</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>18</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="18">
+        <v>1000000</v>
+      </c>
+      <c r="I16" s="16">
+        <v>1</v>
+      </c>
+      <c r="J16" s="18">
+        <f t="shared" si="0"/>
+        <v>147550</v>
+      </c>
+      <c r="K16" s="18">
+        <f t="shared" si="1"/>
+        <v>1147550</v>
+      </c>
+      <c r="L16" s="19">
+        <f t="shared" si="2"/>
+        <v>2.3548387096774195</v>
+      </c>
+      <c r="M16" s="18">
+        <f t="shared" si="3"/>
+        <v>2702295.1612903229</v>
+      </c>
+      <c r="N16" s="18">
+        <f t="shared" si="4"/>
+        <v>35000</v>
+      </c>
+      <c r="O16" s="18">
+        <f t="shared" si="5"/>
+        <v>2737295.1612903229</v>
+      </c>
+      <c r="P16" s="17" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>19</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="16">
+        <v>1</v>
+      </c>
+      <c r="H17" s="18">
+        <v>1000000</v>
+      </c>
+      <c r="I17" s="16">
+        <v>3</v>
+      </c>
+      <c r="J17" s="18">
+        <f t="shared" ref="J17:J18" si="14">IF(E17="штат",ROUND(Ставка_СН*H17*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H17+Ставка_СО*MIN(H17*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H17,Кап_ООСМС*МЗП),0),ROUND(H17*НДС,0))</f>
+        <v>147550</v>
+      </c>
+      <c r="K17" s="18">
+        <f t="shared" ref="K17:K18" si="15">G17*(H17+J17)</f>
+        <v>1147550</v>
+      </c>
+      <c r="L17" s="19">
+        <f t="shared" ref="L17:L18" si="16">IF(AND(F17="новая",I17=1),Мес_2026_новые,MAX(0,4-I17))</f>
+        <v>1</v>
+      </c>
+      <c r="M17" s="18">
+        <f t="shared" ref="M17:M18" si="17">K17*L17</f>
+        <v>1147550</v>
+      </c>
+      <c r="N17" s="18">
+        <f t="shared" si="4"/>
+        <v>35000</v>
+      </c>
+      <c r="O17" s="18">
+        <f t="shared" ref="O17:O18" si="18">M17+N17</f>
+        <v>1182550</v>
+      </c>
+      <c r="P17" s="17" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>19</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="16">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18">
+        <v>700000</v>
+      </c>
+      <c r="I18" s="16">
+        <v>3</v>
+      </c>
+      <c r="J18" s="18">
+        <f t="shared" si="14"/>
+        <v>112210</v>
+      </c>
+      <c r="K18" s="18">
+        <f t="shared" si="15"/>
+        <v>812210</v>
+      </c>
+      <c r="L18" s="19">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="M18" s="18">
+        <f t="shared" si="17"/>
+        <v>812210</v>
+      </c>
+      <c r="N18" s="18">
+        <f t="shared" si="4"/>
+        <v>35000</v>
+      </c>
+      <c r="O18" s="18">
+        <f t="shared" si="18"/>
+        <v>847210</v>
+      </c>
+      <c r="P18" s="17" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>19</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="16">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18">
+        <v>700000</v>
+      </c>
+      <c r="I19" s="16">
+        <v>1</v>
+      </c>
+      <c r="J19" s="18">
+        <f t="shared" si="0"/>
+        <v>112210</v>
+      </c>
+      <c r="K19" s="18">
+        <f t="shared" si="1"/>
+        <v>812210</v>
+      </c>
+      <c r="L19" s="19">
+        <f t="shared" si="2"/>
+        <v>2.3548387096774195</v>
+      </c>
+      <c r="M19" s="18">
+        <f t="shared" si="3"/>
+        <v>1912623.548387097</v>
+      </c>
+      <c r="N19" s="18">
+        <f t="shared" si="4"/>
+        <v>35000</v>
+      </c>
+      <c r="O19" s="18">
+        <f t="shared" si="5"/>
+        <v>1947623.548387097</v>
+      </c>
+      <c r="P19" s="17" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>23</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="16">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18">
+        <v>1300000</v>
+      </c>
+      <c r="I20" s="16">
+        <v>1</v>
+      </c>
+      <c r="J20" s="18">
+        <f t="shared" ref="J20" si="19">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
+        <v>182890</v>
+      </c>
+      <c r="K20" s="18">
+        <f t="shared" ref="K20" si="20">G20*(H20+J20)</f>
+        <v>1482890</v>
+      </c>
+      <c r="L20" s="19">
+        <f t="shared" ref="L20" si="21">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
+        <v>2.3548387096774195</v>
+      </c>
+      <c r="M20" s="18">
+        <f t="shared" si="3"/>
+        <v>3491966.7741935486</v>
+      </c>
+      <c r="N20" s="18">
+        <f t="shared" si="4"/>
+        <v>35000</v>
+      </c>
+      <c r="O20" s="18">
+        <f t="shared" si="5"/>
+        <v>3526966.7741935486</v>
+      </c>
+      <c r="P20" s="17" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="20">
         <v>24</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B21" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="D16" s="21" t="s">
+      <c r="C21" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="D21" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E21" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F21" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G21" s="20">
         <v>0</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H21" s="22">
         <v>1000000</v>
       </c>
-      <c r="I16" s="20">
-        <v>1</v>
-      </c>
-      <c r="J16" s="22">
+      <c r="I21" s="20">
+        <v>1</v>
+      </c>
+      <c r="J21" s="22">
         <f t="shared" si="0"/>
         <v>160000</v>
-      </c>
-      <c r="K16" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="23">
-        <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
-      </c>
-      <c r="M16" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="22">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="21" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
-        <v>25</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="16">
-        <v>1</v>
-      </c>
-      <c r="H17" s="18">
-        <v>1300000</v>
-      </c>
-      <c r="I17" s="16">
-        <v>1</v>
-      </c>
-      <c r="J17" s="18">
-        <f t="shared" si="0"/>
-        <v>182890</v>
-      </c>
-      <c r="K17" s="18">
-        <f t="shared" si="1"/>
-        <v>1482890</v>
-      </c>
-      <c r="L17" s="19">
-        <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
-      </c>
-      <c r="M17" s="18">
-        <f t="shared" si="3"/>
-        <v>3491966.7741935486</v>
-      </c>
-      <c r="N17" s="18">
-        <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
-      </c>
-      <c r="O17" s="18">
-        <f t="shared" si="5"/>
-        <v>3527681.0599078345</v>
-      </c>
-      <c r="P17" s="17" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
-        <v>26</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="16">
-        <v>1</v>
-      </c>
-      <c r="H18" s="18">
-        <v>1000000</v>
-      </c>
-      <c r="I18" s="16">
-        <v>1</v>
-      </c>
-      <c r="J18" s="18">
-        <f t="shared" si="0"/>
-        <v>147550</v>
-      </c>
-      <c r="K18" s="18">
-        <f t="shared" si="1"/>
-        <v>1147550</v>
-      </c>
-      <c r="L18" s="19">
-        <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
-      </c>
-      <c r="M18" s="18">
-        <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
-      </c>
-      <c r="N18" s="18">
-        <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
-      </c>
-      <c r="O18" s="18">
-        <f t="shared" si="5"/>
-        <v>2738009.4470046088</v>
-      </c>
-      <c r="P18" s="17" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="20">
-        <v>27</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="20">
-        <v>0</v>
-      </c>
-      <c r="H19" s="22">
-        <v>1000000</v>
-      </c>
-      <c r="I19" s="20">
-        <v>2</v>
-      </c>
-      <c r="J19" s="22">
-        <f t="shared" si="0"/>
-        <v>160000</v>
-      </c>
-      <c r="K19" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="23">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="M19" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="22">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="21" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="20">
-        <v>28</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="20">
-        <v>0</v>
-      </c>
-      <c r="H20" s="22">
-        <v>700000</v>
-      </c>
-      <c r="I20" s="20">
-        <v>2</v>
-      </c>
-      <c r="J20" s="22">
-        <f t="shared" ref="J20" si="12">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
-        <v>112000</v>
-      </c>
-      <c r="K20" s="22">
-        <f t="shared" ref="K20" si="13">G20*(H20+J20)</f>
-        <v>0</v>
-      </c>
-      <c r="L20" s="23">
-        <f t="shared" ref="L20" si="14">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
-        <v>2</v>
-      </c>
-      <c r="M20" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="22">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="21" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="20">
-        <v>29</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G21" s="20">
-        <v>0</v>
-      </c>
-      <c r="H21" s="22">
-        <v>700000</v>
-      </c>
-      <c r="I21" s="20">
-        <v>2</v>
-      </c>
-      <c r="J21" s="22">
-        <f t="shared" si="0"/>
-        <v>112000</v>
       </c>
       <c r="K21" s="22">
         <f t="shared" si="1"/>
@@ -3573,7 +3598,7 @@
       </c>
       <c r="L21" s="23">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>2.3548387096774195</v>
       </c>
       <c r="M21" s="22">
         <f t="shared" si="3"/>
@@ -3588,21 +3613,21 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>260</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>80</v>
@@ -3614,18 +3639,18 @@
         <v>1</v>
       </c>
       <c r="H22" s="18">
-        <v>1000000</v>
+        <v>1300000</v>
       </c>
       <c r="I22" s="16">
         <v>1</v>
       </c>
       <c r="J22" s="18">
         <f t="shared" si="0"/>
-        <v>147550</v>
+        <v>182890</v>
       </c>
       <c r="K22" s="18">
         <f t="shared" si="1"/>
-        <v>1147550</v>
+        <v>1482890</v>
       </c>
       <c r="L22" s="19">
         <f t="shared" si="2"/>
@@ -3633,29 +3658,29 @@
       </c>
       <c r="M22" s="18">
         <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
+        <v>3491966.7741935486</v>
       </c>
       <c r="N22" s="18">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
+        <v>35000</v>
       </c>
       <c r="O22" s="18">
         <f t="shared" si="5"/>
-        <v>2738009.4470046088</v>
+        <v>3526966.7741935486</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>260</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>216</v>
@@ -3670,18 +3695,18 @@
         <v>1</v>
       </c>
       <c r="H23" s="18">
-        <v>700000</v>
+        <v>1000000</v>
       </c>
       <c r="I23" s="16">
         <v>1</v>
       </c>
       <c r="J23" s="18">
-        <f t="shared" ref="J23:J29" si="15">IF(E23="штат",ROUND(Ставка_СН*H23*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H23+Ставка_СО*MIN(H23*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H23,Кап_ООСМС*МЗП),0),ROUND(H23*НДС,0))</f>
-        <v>112210</v>
+        <f t="shared" si="0"/>
+        <v>147550</v>
       </c>
       <c r="K23" s="18">
-        <f t="shared" ref="K23:K29" si="16">G23*(H23+J23)</f>
-        <v>812210</v>
+        <f t="shared" si="1"/>
+        <v>1147550</v>
       </c>
       <c r="L23" s="19">
         <f t="shared" si="2"/>
@@ -3689,29 +3714,29 @@
       </c>
       <c r="M23" s="18">
         <f t="shared" si="3"/>
-        <v>1912623.548387097</v>
+        <v>2702295.1612903229</v>
       </c>
       <c r="N23" s="18">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
+        <v>35000</v>
       </c>
       <c r="O23" s="18">
         <f t="shared" si="5"/>
-        <v>1948337.8341013826</v>
+        <v>2737295.1612903229</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="20">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B24" s="20" t="s">
         <v>260</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D24" s="21" t="s">
         <v>216</v>
@@ -3726,17 +3751,17 @@
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>700000</v>
+        <v>1000000</v>
       </c>
       <c r="I24" s="20">
         <v>2</v>
       </c>
       <c r="J24" s="22">
-        <f t="shared" si="15"/>
-        <v>112000</v>
+        <f t="shared" si="0"/>
+        <v>160000</v>
       </c>
       <c r="K24" s="22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L24" s="23">
@@ -3756,77 +3781,77 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="75" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
-        <v>33</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G25" s="16">
-        <v>1</v>
-      </c>
-      <c r="H25" s="18">
-        <v>1400000</v>
-      </c>
-      <c r="I25" s="16">
-        <v>1</v>
-      </c>
-      <c r="J25" s="18">
-        <f t="shared" si="15"/>
-        <v>194670</v>
-      </c>
-      <c r="K25" s="18">
-        <f t="shared" si="16"/>
-        <v>1594670</v>
-      </c>
-      <c r="L25" s="19">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="M25" s="18">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="20">
+        <v>28</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="20">
+        <v>0</v>
+      </c>
+      <c r="H25" s="22">
+        <v>700000</v>
+      </c>
+      <c r="I25" s="20">
+        <v>2</v>
+      </c>
+      <c r="J25" s="22">
+        <f t="shared" ref="J25" si="22">IF(E25="штат",ROUND(Ставка_СН*H25*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H25+Ставка_СО*MIN(H25*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H25,Кап_ООСМС*МЗП),0),ROUND(H25*НДС,0))</f>
+        <v>112000</v>
+      </c>
+      <c r="K25" s="22">
+        <f t="shared" ref="K25" si="23">G25*(H25+J25)</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="23">
+        <f t="shared" ref="L25" si="24">IF(AND(F25="новая",I25=1),Мес_2026_новые,MAX(0,4-I25))</f>
+        <v>2</v>
+      </c>
+      <c r="M25" s="22">
         <f t="shared" si="3"/>
-        <v>4784010</v>
-      </c>
-      <c r="N25" s="18">
+        <v>0</v>
+      </c>
+      <c r="N25" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O25" s="18">
+      <c r="O25" s="22">
         <f t="shared" si="5"/>
-        <v>4784010</v>
-      </c>
-      <c r="P25" s="17" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="P25" s="21" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>85</v>
+        <v>405</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>80</v>
@@ -3844,11 +3869,11 @@
         <v>1</v>
       </c>
       <c r="J26" s="18">
-        <f t="shared" si="15"/>
+        <f t="shared" si="0"/>
         <v>112210</v>
       </c>
       <c r="K26" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="1"/>
         <v>812210</v>
       </c>
       <c r="L26" s="19">
@@ -3861,28 +3886,28 @@
       </c>
       <c r="N26" s="18">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
+        <v>35000</v>
       </c>
       <c r="O26" s="18">
         <f t="shared" si="5"/>
-        <v>1948337.8341013826</v>
+        <v>1947623.548387097</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>405</v>
+        <v>260</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>406</v>
+        <v>263</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>407</v>
+        <v>216</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>80</v>
@@ -3894,18 +3919,18 @@
         <v>1</v>
       </c>
       <c r="H27" s="18">
-        <v>1200000</v>
+        <v>1000000</v>
       </c>
       <c r="I27" s="16">
         <v>1</v>
       </c>
       <c r="J27" s="18">
-        <f t="shared" si="15"/>
-        <v>171110</v>
+        <f t="shared" si="0"/>
+        <v>147550</v>
       </c>
       <c r="K27" s="18">
-        <f t="shared" si="16"/>
-        <v>1371110</v>
+        <f t="shared" si="1"/>
+        <v>1147550</v>
       </c>
       <c r="L27" s="19">
         <f t="shared" si="2"/>
@@ -3913,88 +3938,88 @@
       </c>
       <c r="M27" s="18">
         <f t="shared" si="3"/>
-        <v>3228742.9032258065</v>
+        <v>2702295.1612903229</v>
       </c>
       <c r="N27" s="18">
         <f t="shared" si="4"/>
-        <v>35714.285714285717</v>
+        <v>35000</v>
       </c>
       <c r="O27" s="18">
         <f t="shared" si="5"/>
-        <v>3264457.1889400925</v>
+        <v>2737295.1612903229</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="20">
-        <v>36</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="F28" s="20" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="16">
+        <v>31</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="20">
-        <v>0</v>
-      </c>
-      <c r="H28" s="22">
-        <v>1000000</v>
-      </c>
-      <c r="I28" s="20">
-        <v>1</v>
-      </c>
-      <c r="J28" s="22">
-        <f t="shared" si="15"/>
-        <v>160000</v>
-      </c>
-      <c r="K28" s="22">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="23">
+      <c r="G28" s="16">
+        <v>1</v>
+      </c>
+      <c r="H28" s="18">
+        <v>700000</v>
+      </c>
+      <c r="I28" s="16">
+        <v>1</v>
+      </c>
+      <c r="J28" s="18">
+        <f t="shared" ref="J28:J34" si="25">IF(E28="штат",ROUND(Ставка_СН*H28*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H28+Ставка_СО*MIN(H28*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H28,Кап_ООСМС*МЗП),0),ROUND(H28*НДС,0))</f>
+        <v>112210</v>
+      </c>
+      <c r="K28" s="18">
+        <f t="shared" ref="K28:K34" si="26">G28*(H28+J28)</f>
+        <v>812210</v>
+      </c>
+      <c r="L28" s="19">
         <f t="shared" si="2"/>
         <v>2.3548387096774195</v>
       </c>
-      <c r="M28" s="22">
+      <c r="M28" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="22">
+        <v>1912623.548387097</v>
+      </c>
+      <c r="N28" s="18">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="22">
+        <v>35000</v>
+      </c>
+      <c r="O28" s="18">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P28" s="21" t="s">
-        <v>320</v>
+        <v>1947623.548387097</v>
+      </c>
+      <c r="P28" s="17" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="20">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E29" s="20" t="s">
         <v>259</v>
@@ -4009,19 +4034,19 @@
         <v>700000</v>
       </c>
       <c r="I29" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>112000</v>
       </c>
       <c r="K29" s="22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="L29" s="23">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M29" s="22">
         <f t="shared" si="3"/>
@@ -4036,70 +4061,350 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7">
-        <f>SUM(G5:G29)</f>
-        <v>18</v>
-      </c>
-      <c r="H30" s="6">
-        <f>SUMPRODUCT(G5:G29,H5:H29)</f>
-        <v>20200000</v>
-      </c>
-      <c r="I30" s="7"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6">
-        <f>SUM(K5:K29)</f>
-        <v>23115060</v>
-      </c>
-      <c r="L30" s="7"/>
-      <c r="M30" s="6">
-        <f>SUM(M5:M29)</f>
-        <v>58691747.741935484</v>
-      </c>
-      <c r="N30" s="6">
-        <f t="shared" ref="N30:O30" si="17">SUM(N5:N29)</f>
-        <v>500000.00000000017</v>
-      </c>
-      <c r="O30" s="6">
-        <f t="shared" si="17"/>
-        <v>59191747.741935477</v>
-      </c>
-      <c r="P30" s="7"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
-        <v>350</v>
-      </c>
-      <c r="G31">
-        <f>SUM(G8:G9)+SUM(G10:G24)</f>
-        <v>12</v>
-      </c>
-      <c r="H31" s="5">
-        <f>SUMPRODUCT(G8:G9,H8:H9)+SUMPRODUCT(G10:G24,H10:H24)</f>
-        <v>12500000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C32" t="s">
-        <v>351</v>
-      </c>
-      <c r="G32">
-        <f>G30-G31</f>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A30" s="16">
+        <v>33</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="16">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18">
+        <v>1400000</v>
+      </c>
+      <c r="I30" s="16">
+        <v>1</v>
+      </c>
+      <c r="J30" s="18">
+        <f t="shared" si="25"/>
+        <v>194670</v>
+      </c>
+      <c r="K30" s="18">
+        <f t="shared" si="26"/>
+        <v>1594670</v>
+      </c>
+      <c r="L30" s="19">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="M30" s="18">
+        <f t="shared" si="3"/>
+        <v>4784010</v>
+      </c>
+      <c r="N30" s="18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="18">
+        <f t="shared" si="5"/>
+        <v>4784010</v>
+      </c>
+      <c r="P30" s="17" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="16">
+        <v>34</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G31" s="16">
+        <v>1</v>
+      </c>
+      <c r="H31" s="18">
+        <v>700000</v>
+      </c>
+      <c r="I31" s="16">
+        <v>1</v>
+      </c>
+      <c r="J31" s="18">
+        <f t="shared" si="25"/>
+        <v>112210</v>
+      </c>
+      <c r="K31" s="18">
+        <f t="shared" si="26"/>
+        <v>812210</v>
+      </c>
+      <c r="L31" s="19">
+        <f t="shared" si="2"/>
+        <v>2.3548387096774195</v>
+      </c>
+      <c r="M31" s="18">
+        <f t="shared" si="3"/>
+        <v>1912623.548387097</v>
+      </c>
+      <c r="N31" s="18">
+        <f t="shared" si="4"/>
+        <v>35000</v>
+      </c>
+      <c r="O31" s="18">
+        <f t="shared" si="5"/>
+        <v>1947623.548387097</v>
+      </c>
+      <c r="P31" s="17" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="16">
+        <v>35</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" s="16">
+        <v>1</v>
+      </c>
+      <c r="H32" s="18">
+        <v>1200000</v>
+      </c>
+      <c r="I32" s="16">
+        <v>1</v>
+      </c>
+      <c r="J32" s="18">
+        <f t="shared" si="25"/>
+        <v>171110</v>
+      </c>
+      <c r="K32" s="18">
+        <f t="shared" si="26"/>
+        <v>1371110</v>
+      </c>
+      <c r="L32" s="19">
+        <f t="shared" si="2"/>
+        <v>2.3548387096774195</v>
+      </c>
+      <c r="M32" s="18">
+        <f t="shared" si="3"/>
+        <v>3228742.9032258065</v>
+      </c>
+      <c r="N32" s="18">
+        <f t="shared" si="4"/>
+        <v>35000</v>
+      </c>
+      <c r="O32" s="18">
+        <f t="shared" si="5"/>
+        <v>3263742.9032258065</v>
+      </c>
+      <c r="P32" s="17" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="20">
+        <v>36</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" s="20">
+        <v>0</v>
+      </c>
+      <c r="H33" s="22">
+        <v>1000000</v>
+      </c>
+      <c r="I33" s="20">
+        <v>1</v>
+      </c>
+      <c r="J33" s="22">
+        <f t="shared" si="25"/>
+        <v>160000</v>
+      </c>
+      <c r="K33" s="22">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="23">
+        <f t="shared" si="2"/>
+        <v>2.3548387096774195</v>
+      </c>
+      <c r="M33" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P33" s="21" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="20">
+        <v>37</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G34" s="20">
+        <v>0</v>
+      </c>
+      <c r="H34" s="22">
+        <v>700000</v>
+      </c>
+      <c r="I34" s="20">
+        <v>1</v>
+      </c>
+      <c r="J34" s="22">
+        <f t="shared" si="25"/>
+        <v>112000</v>
+      </c>
+      <c r="K34" s="22">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="23">
+        <f t="shared" si="2"/>
+        <v>2.3548387096774195</v>
+      </c>
+      <c r="M34" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N34" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O34" s="22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P34" s="21" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7">
+        <f>SUM(G5:G34)</f>
+        <v>23</v>
+      </c>
+      <c r="H35" s="6">
+        <f>SUMPRODUCT(G5:G34,H5:H34)</f>
+        <v>24900000</v>
+      </c>
+      <c r="I35" s="7"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6">
+        <f>SUM(K5:K34)</f>
+        <v>28517470</v>
+      </c>
+      <c r="L35" s="7"/>
+      <c r="M35" s="6">
+        <f>SUM(M5:M34)</f>
+        <v>68758393.225806445</v>
+      </c>
+      <c r="N35" s="6">
+        <f t="shared" ref="N35:O35" si="27">SUM(N5:N34)</f>
+        <v>665000</v>
+      </c>
+      <c r="O35" s="6">
+        <f t="shared" si="27"/>
+        <v>69423393.225806445</v>
+      </c>
+      <c r="P35" s="7"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>342</v>
+      </c>
+      <c r="G36">
+        <f>SUM(G8:G12)+SUM(G13:G29)</f>
+        <v>17</v>
+      </c>
+      <c r="H36" s="5">
+        <f>SUMPRODUCT(G8:G12,H8:H12)+SUMPRODUCT(G13:G29,H13:H29)</f>
+        <v>17200000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>343</v>
+      </c>
+      <c r="G37">
+        <f>G35-G36</f>
         <v>6</v>
       </c>
-      <c r="H32" s="5">
-        <f>H30-H31</f>
+      <c r="H37" s="5">
+        <f>H35-H36</f>
         <v>7700000</v>
       </c>
     </row>
@@ -4129,7 +4434,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -4143,19 +4448,19 @@
         <v>69</v>
       </c>
       <c r="D3" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="G3" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="E3" s="25" t="s">
-        <v>295</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>297</v>
-      </c>
       <c r="H3" s="25" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -4169,13 +4474,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E4" s="28">
         <v>1000000</v>
@@ -4205,13 +4510,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E5" s="28">
         <v>700000</v>
@@ -4241,13 +4546,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -4277,13 +4582,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -4313,13 +4618,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C8" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="D8" s="27" t="s">
         <v>306</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>309</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -4344,18 +4649,18 @@
         <v>1624000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>310</v>
+        <v>415</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>306</v>
+        <v>416</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>311</v>
+        <v>417</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -4369,15 +4674,15 @@
         <v>812000</v>
       </c>
       <c r="H9" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="29">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>2.3548387096774195</v>
       </c>
       <c r="J9" s="28">
         <f t="shared" si="3"/>
-        <v>1624000</v>
+        <v>1912129.0322580647</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -4385,13 +4690,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -4419,7 +4724,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4439,7 +4744,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="31">
         <f>SUM(J4:J10)</f>
-        <v>14567354.838709679</v>
+        <v>14855483.870967744</v>
       </c>
     </row>
   </sheetData>
@@ -4463,7 +4768,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4514,7 +4819,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="5">
-        <f>C5*(D5/12*F5*Поездка_РК+E5*F5*Поездка_местн)</f>
+        <f t="shared" ref="G5:G11" si="0">C5*(D5/12*F5*Поездка_РК+E5*F5*Поездка_местн)</f>
         <v>190950</v>
       </c>
     </row>
@@ -4538,7 +4843,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="5">
-        <f>C6*(D6/12*F6*Поездка_РК+E6*F6*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>286425</v>
       </c>
     </row>
@@ -4562,17 +4867,17 @@
         <v>2.3548387096774195</v>
       </c>
       <c r="G7" s="5">
-        <f>C7*(D7/12*F7*Поездка_РК+E7*F7*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>374713.70967741939</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>344</v>
+        <v>418</v>
       </c>
       <c r="C8">
-        <f>SUM(Штат!G9:G9)</f>
-        <v>1</v>
+        <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")</f>
+        <v>3</v>
       </c>
       <c r="D8" s="9">
         <v>3</v>
@@ -4581,21 +4886,21 @@
         <v>3</v>
       </c>
       <c r="F8" s="15">
-        <f>Штат!L9</f>
+        <f>IF(C8&gt;0,SUMIFS(Штат!$L$5:$L$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")/C8,0)</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="G8" s="5">
-        <f>SUMPRODUCT((Штат!I9:I9&lt;=3)*Штат!G9:G9)*(D8/12*F8*Поездка_РК+E8*F8*Поездка_местн)</f>
-        <v>279489.91935483873</v>
+        <f t="shared" si="0"/>
+        <v>838469.75806451612</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>345</v>
+        <v>419</v>
       </c>
       <c r="C9">
-        <f>SUM(Штат!G10:G14)</f>
-        <v>5</v>
+        <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")</f>
+        <v>7</v>
       </c>
       <c r="D9" s="9">
         <v>6</v>
@@ -4604,20 +4909,20 @@
         <v>0</v>
       </c>
       <c r="F9" s="15">
-        <f>Штат!L11</f>
-        <v>2.3548387096774195</v>
+        <f>IF(C9&gt;0,SUMIFS(Штат!$L$5:$L$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")/C9,0)</f>
+        <v>1.9677419354838712</v>
       </c>
       <c r="G9" s="5">
-        <f>SUMPRODUCT((Штат!I10:I14&lt;=3)*Штат!G10:G14)*(D9/12*F9*Поездка_РК+E9*F9*Поездка_местн)</f>
-        <v>1124141.1290322582</v>
+        <f t="shared" si="0"/>
+        <v>1315091.1290322582</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C10">
-        <f>SUM(Штат!G15:G16)</f>
+        <f>SUM(Штат!G20:G21)</f>
         <v>1</v>
       </c>
       <c r="D10" s="9">
@@ -4627,21 +4932,21 @@
         <v>0</v>
       </c>
       <c r="F10" s="15">
-        <f>Штат!L15</f>
+        <f>Штат!L20</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="G10" s="5">
-        <f>C10*(D10/12*F10*Поездка_РК+E10*F10*Поездка_местн)</f>
+        <f t="shared" si="0"/>
         <v>37471.370967741932</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>271</v>
+        <v>420</v>
       </c>
       <c r="C11">
-        <f>SUM(Штат!G17:G24)</f>
-        <v>4</v>
+        <f>SUM(Штат!G22:G29)</f>
+        <v>5</v>
       </c>
       <c r="D11" s="9">
         <v>4</v>
@@ -4650,12 +4955,12 @@
         <v>4</v>
       </c>
       <c r="F11" s="15">
-        <f>Штат!L17</f>
+        <f>Штат!L22</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="G11" s="5">
-        <f>C11*(D11/12*F11*Поездка_РК+E11*F11*Поездка_местн)</f>
-        <v>1490612.9032258065</v>
+        <f t="shared" si="0"/>
+        <v>1863266.1290322582</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4669,7 +4974,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="6">
         <f>SUM(G5:G11)</f>
-        <v>3783804.032258065</v>
+        <v>4906387.0967741935</v>
       </c>
     </row>
   </sheetData>
@@ -4697,12 +5002,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4725,7 +5030,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -4745,7 +5050,7 @@
         <v>100</v>
       </c>
       <c r="D5" s="9">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E5" s="10">
         <v>450000</v>
@@ -4757,11 +5062,11 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>360</v>
+        <v>421</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
-        <v>5400000</v>
+        <v>7650000</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4787,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -4859,7 +5164,7 @@
         <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -4917,7 +5222,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -5308,13 +5613,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C24" t="s">
         <v>100</v>
       </c>
       <c r="D24" s="9">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E24" s="10">
         <f>ROUND(4118/(1+НДС),0)</f>
@@ -5327,11 +5632,11 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>56800</v>
+        <v>74550</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5339,7 +5644,7 @@
         <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C25" t="s">
         <v>100</v>
@@ -5358,7 +5663,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -5370,7 +5675,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C26" t="s">
         <v>100</v>
@@ -5389,7 +5694,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -5401,7 +5706,7 @@
         <v>98</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C27" t="s">
         <v>100</v>
@@ -5420,7 +5725,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -5432,7 +5737,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C28" t="s">
         <v>100</v>
@@ -5451,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="1">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -5463,7 +5768,7 @@
         <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C29" t="s">
         <v>100</v>
@@ -5482,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -5494,7 +5799,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
@@ -5513,7 +5818,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -5613,7 +5918,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -5632,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -5644,7 +5949,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -5672,7 +5977,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
@@ -5691,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" ref="I36" si="2">IF(F36="разово",IF(G36&lt;=3,D36*E36,0),IF(F36="мес",D36*E36*MAX(0,4-G36),D36*E36*MAX(0,4-G36)/12))</f>
@@ -5759,7 +6064,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -5806,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="I40" s="5">
         <f>D40*E40*Аренда_мес_2026</f>
@@ -5837,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" ref="I41:I57" si="3">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
@@ -5961,7 +6266,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -5980,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -5992,7 +6297,7 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -6011,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
@@ -6057,7 +6362,7 @@
         <v>130</v>
       </c>
       <c r="D49" s="9">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E49" s="10">
         <v>7000</v>
@@ -6069,11 +6374,11 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
-        <v>294000</v>
+        <v>399000</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6167,7 +6472,7 @@
         <v>136</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C53" t="s">
         <v>246</v>
@@ -6244,7 +6549,7 @@
         <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="C56" t="s">
         <v>104</v>
@@ -6272,7 +6577,7 @@
         <v>140</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -6321,7 +6626,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6352,10 +6657,10 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C5" t="s">
         <v>246</v>
@@ -6366,12 +6671,12 @@
         <v>244</v>
       </c>
       <c r="G5" s="5">
-        <v>3600000</v>
+        <v>2900000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>248</v>
@@ -6385,15 +6690,15 @@
         <v>244</v>
       </c>
       <c r="G6" s="5">
-        <v>1200000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C7" t="s">
         <v>246</v>
@@ -6404,15 +6709,15 @@
         <v>244</v>
       </c>
       <c r="G7" s="5">
-        <v>6100000</v>
+        <v>4800000</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C8" t="s">
         <v>246</v>
@@ -6423,12 +6728,12 @@
         <v>244</v>
       </c>
       <c r="G8" s="5">
-        <v>18400000</v>
+        <v>14500000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>247</v>
@@ -6442,12 +6747,12 @@
         <v>244</v>
       </c>
       <c r="G9" s="5">
-        <v>9200000</v>
+        <v>7200000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>249</v>
@@ -6461,12 +6766,12 @@
         <v>244</v>
       </c>
       <c r="G10" s="5">
-        <v>30504855.379999999</v>
+        <v>24721578.109999999</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>245</v>
@@ -6480,7 +6785,7 @@
         <v>244</v>
       </c>
       <c r="G11" s="5">
-        <v>18400000</v>
+        <v>14500000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6488,7 +6793,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -6496,7 +6801,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="6">
         <f>SUM(G5:G11)</f>
-        <v>87404855.379999995</v>
+        <v>69521578.109999999</v>
       </c>
     </row>
   </sheetData>
@@ -6524,7 +6829,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -6571,7 +6876,7 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6707,7 +7012,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -6864,7 +7169,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -7130,7 +7435,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -1237,9 +1237,6 @@
     <t>Фото- и видеооборудование – базовый комплект (КП PSP Digital)</t>
   </si>
   <si>
-    <t>лист «Смета фото-видео»: камера, объектив 24-105, стабилизатор, микрофон, карта памяти, монопод, сумка, запасной аккумулятор, штатив, SSD</t>
-  </si>
-  <si>
     <t>Аптечки</t>
   </si>
   <si>
@@ -1397,6 +1394,9 @@
   </si>
   <si>
     <t>2. Аутсорс-услуги: юрист МФЦА, сис.админ, разработчик, режиссёр, копирайтер, социолог, менеджер по креаторам (с НДС исполнителя)</t>
+  </si>
+  <si>
+    <t>лист «Смета фото-видео»: в 2026 году – только внешние SSD 2 ТБ для исходников, 2 шт.</t>
   </si>
 </sst>
 </file>
@@ -1899,7 +1899,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1939,7 +1939,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -1948,7 +1948,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N35</f>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
-        <v>31437785</v>
+        <v>28145855</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>141372587.69032258</v>
+        <v>138080657.69032258</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
-        <v>14212258.769032259</v>
+        <v>13883065.769032259</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>24893575.433496777</v>
+        <v>24314195.753496777</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>180478421.89285162</v>
+        <v>176277919.21285161</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
-        <v>69521578.109999999</v>
+        <v>87404855.379999995</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>250000000.00285161</v>
+        <v>263682774.59285161</v>
       </c>
     </row>
   </sheetData>
@@ -2212,14 +2212,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$34,Штат!$E$5:$E$34,"штат",Штат!$F$5:$F$34,"новая"),-3)</f>
         <v>665000</v>
       </c>
       <c r="C15" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2654,7 +2654,7 @@
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
@@ -2728,7 +2728,7 @@
         <v>278</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -2773,7 +2773,7 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2829,7 +2829,7 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2840,7 +2840,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2885,7 +2885,7 @@
         <v>3790190.6451612907</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2941,7 +2941,7 @@
         <v>3526966.7741935486</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2952,7 +2952,7 @@
         <v>250</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>253</v>
@@ -2997,7 +2997,7 @@
         <v>2737295.1612903229</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3008,7 +3008,7 @@
         <v>250</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>253</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3221,7 +3221,7 @@
         <v>2737295.1612903229</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -3277,7 +3277,7 @@
         <v>2737295.1612903229</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3333,7 +3333,7 @@
         <v>2737295.1612903229</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3389,7 +3389,7 @@
         <v>1182550</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3445,7 +3445,7 @@
         <v>847210</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3501,7 +3501,7 @@
         <v>1947623.548387097</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -3557,7 +3557,7 @@
         <v>3526966.7741935486</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3669,7 +3669,7 @@
         <v>3526966.7741935486</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -3725,7 +3725,7 @@
         <v>2737295.1612903229</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -3848,7 +3848,7 @@
         <v>260</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>216</v>
@@ -3893,7 +3893,7 @@
         <v>1947623.548387097</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -3949,7 +3949,7 @@
         <v>2737295.1612903229</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -4181,13 +4181,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="D32" s="17" t="s">
         <v>393</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>394</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>80</v>
@@ -4229,7 +4229,7 @@
         <v>3263742.9032258065</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4654,13 +4654,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>415</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="D9" s="27" t="s">
         <v>416</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>417</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")</f>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")</f>
@@ -4942,7 +4942,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -5062,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="E34" s="10">
         <f>'Смета фото-видео'!G24</f>
-        <v>3591930</v>
+        <v>300000</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>101</v>
@@ -5937,11 +5937,11 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>371</v>
+        <v>424</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
-        <v>3591930</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6064,7 +6064,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -6266,7 +6266,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -6285,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -6297,7 +6297,7 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -6316,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
@@ -6374,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -6549,7 +6549,7 @@
         <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C56" t="s">
         <v>104</v>
@@ -6577,7 +6577,7 @@
         <v>140</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -6671,7 +6671,7 @@
         <v>244</v>
       </c>
       <c r="G5" s="5">
-        <v>2900000</v>
+        <v>3600000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6690,7 +6690,7 @@
         <v>244</v>
       </c>
       <c r="G6" s="5">
-        <v>900000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6709,7 +6709,7 @@
         <v>244</v>
       </c>
       <c r="G7" s="5">
-        <v>4800000</v>
+        <v>6100000</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -6728,7 +6728,7 @@
         <v>244</v>
       </c>
       <c r="G8" s="5">
-        <v>14500000</v>
+        <v>18400000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6747,7 +6747,7 @@
         <v>244</v>
       </c>
       <c r="G9" s="5">
-        <v>7200000</v>
+        <v>9200000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6766,7 +6766,7 @@
         <v>244</v>
       </c>
       <c r="G10" s="5">
-        <v>24721578.109999999</v>
+        <v>30504855.379999999</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6785,7 +6785,7 @@
         <v>244</v>
       </c>
       <c r="G11" s="5">
-        <v>14500000</v>
+        <v>18400000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6801,7 +6801,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="6">
         <f>SUM(G5:G11)</f>
-        <v>69521578.109999999</v>
+        <v>87404855.379999995</v>
       </c>
     </row>
   </sheetData>
@@ -6829,7 +6829,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -7012,7 +7012,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -7169,7 +7169,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -7261,14 +7261,14 @@
         <v>149</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5">
         <v>1669990</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" ref="G6:G12" si="0">E6*F6</f>
-        <v>1669990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7285,14 +7285,14 @@
         <v>151</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5">
         <v>485990</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="0"/>
-        <v>485990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7309,14 +7309,14 @@
         <v>151</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5">
         <v>479990</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="0"/>
-        <v>479990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7333,14 +7333,14 @@
         <v>151</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5">
         <v>104990</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>104990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7357,14 +7357,14 @@
         <v>151</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5">
         <v>119990</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" si="0"/>
-        <v>119990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7381,14 +7381,14 @@
         <v>151</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="5">
         <v>58990</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="0"/>
-        <v>58990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7405,14 +7405,14 @@
         <v>151</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="5">
         <v>31990</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="0"/>
-        <v>31990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7426,7 +7426,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="6">
         <f>SUM(G6:G12)</f>
-        <v>2951930</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7455,14 +7455,14 @@
         <v>159</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5">
         <v>240000</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" ref="G16" si="1">E16*F16</f>
-        <v>240000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7476,7 +7476,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="6">
         <f>SUM(G16:G16)</f>
-        <v>240000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7505,14 +7505,14 @@
         <v>159</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5">
         <v>250000</v>
       </c>
       <c r="G20" s="5">
         <f>E20*F20</f>
-        <v>250000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7526,14 +7526,14 @@
         <v>159</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="5">
         <v>150000</v>
       </c>
       <c r="G21" s="5">
         <f>E21*F21</f>
-        <v>150000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7547,7 +7547,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="6">
         <f>SUM(G20:G21)</f>
-        <v>400000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7565,7 +7565,7 @@
       <c r="F24" s="12"/>
       <c r="G24" s="12">
         <f>G13+G17+G22</f>
-        <v>3591930</v>
+        <v>300000</v>
       </c>
     </row>
   </sheetData>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -817,9 +817,6 @@
     <t>Мес_2026_новые</t>
   </si>
   <si>
-    <t>Мес. 2026 (новые — с 21.10)</t>
-  </si>
-  <si>
     <t>Гарантийный депозит по аренде, в месячных ставках (возвратный) — допущение 1 месяц, условия запрошены у БЦ</t>
   </si>
   <si>
@@ -1189,9 +1186,6 @@
     <t>Старт позиции/расхода: 1 – октябрь, 2 – ноябрь, 3 – декабрь 2026.</t>
   </si>
   <si>
-    <t>Месяцев 2026 для новых сотрудников (зарплата, отчисления): приём одновременно с заездом в офис — с 21.10.2026, ≈2,35 мес. Действующие — 3 мес.</t>
-  </si>
-  <si>
     <t>Штатная численность, чел.</t>
   </si>
   <si>
@@ -1397,6 +1391,12 @@
   </si>
   <si>
     <t>лист «Смета фото-видео»: в 2026 году – только внешние SSD 2 ТБ для исходников, 2 шт.</t>
+  </si>
+  <si>
+    <t>Месяцев 2026 для новых сотрудников (зарплата, отчисления): приём с 01.11.2026, 2 мес. Действующие – 3 мес. Аренда – с 21.10.2026 (Аренда_мес_2026)</t>
+  </si>
+  <si>
+    <t>Мес. 2026 (новые – с 01.11)</t>
   </si>
 </sst>
 </file>
@@ -1899,7 +1899,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1912,7 +1912,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E34,"штат",Штат!G5:G34)</f>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G36</f>
@@ -1930,25 +1930,25 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M34,Штат!E5:E34,"штат")</f>
-        <v>68758393.225806445</v>
+        <v>61677420</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
-        <v>14855483.870967744</v>
+        <v>13456000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N35</f>
@@ -1957,16 +1957,16 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
-        <v>4906387.0967741935</v>
+        <v>4267775</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
@@ -1975,70 +1975,70 @@
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
-        <v>17530038.496774193</v>
+        <v>17202663.496774193</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
-        <v>694500</v>
+        <v>463000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
-        <v>2525000</v>
+        <v>2350000</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>138080657.69032258</v>
+        <v>128227713.4967742</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
-        <v>13883065.769032259</v>
+        <v>12889438.016344087</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>24314195.753496777</v>
+        <v>22578744.242098927</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>176277919.21285161</v>
+        <v>163695895.75521722</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
@@ -2047,11 +2047,11 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>263682774.59285161</v>
+        <v>251100751.13521722</v>
       </c>
     </row>
   </sheetData>
@@ -2212,14 +2212,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$34,Штат!$E$5:$E$34,"штат",Штат!$F$5:$F$34,"новая"),-3)</f>
         <v>665000</v>
       </c>
       <c r="C15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2410,7 +2410,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2421,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2448,17 +2448,17 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2470,7 +2470,7 @@
         <v>340.67</v>
       </c>
       <c r="C42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2481,7 +2481,7 @@
         <v>13500</v>
       </c>
       <c r="C43" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2493,7 +2493,7 @@
         <v>230107.1</v>
       </c>
       <c r="C44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2504,7 +2504,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2515,7 +2515,7 @@
         <v>40000</v>
       </c>
       <c r="C46" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2575,11 +2575,10 @@
         <v>230</v>
       </c>
       <c r="B52" s="15">
-        <f>Аренда_мес_2026</f>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>355</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -2607,7 +2606,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2639,7 +2638,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -2648,19 +2647,19 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>231</v>
+        <v>424</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -2669,10 +2668,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>278</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>279</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>79</v>
@@ -2717,7 +2716,7 @@
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2725,10 +2724,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -2773,7 +2772,7 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2781,10 +2780,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>82</v>
@@ -2829,7 +2828,7 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2840,7 +2839,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2858,7 +2857,7 @@
         <v>1400000</v>
       </c>
       <c r="I8" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="18">
         <f t="shared" si="0"/>
@@ -2870,11 +2869,11 @@
       </c>
       <c r="L8" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M8" s="18">
         <f t="shared" si="3"/>
-        <v>3755190.6451612907</v>
+        <v>3189340</v>
       </c>
       <c r="N8" s="18">
         <f t="shared" si="4"/>
@@ -2882,10 +2881,10 @@
       </c>
       <c r="O8" s="18">
         <f t="shared" si="5"/>
-        <v>3790190.6451612907</v>
+        <v>3224340</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2893,13 +2892,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>251</v>
-      </c>
       <c r="D9" s="17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>80</v>
@@ -2914,7 +2913,7 @@
         <v>1300000</v>
       </c>
       <c r="I9" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="18">
         <f t="shared" ref="J9:J11" si="6">IF(E9="штат",ROUND(Ставка_СН*H9*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H9+Ставка_СО*MIN(H9*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H9,Кап_ООСМС*МЗП),0),ROUND(H9*НДС,0))</f>
@@ -2926,11 +2925,11 @@
       </c>
       <c r="L9" s="19">
         <f t="shared" ref="L9:L11" si="8">IF(AND(F9="новая",I9=1),Мес_2026_новые,MAX(0,4-I9))</f>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M9" s="18">
         <f t="shared" ref="M9:M11" si="9">K9*L9</f>
-        <v>3491966.7741935486</v>
+        <v>2965780</v>
       </c>
       <c r="N9" s="18">
         <f t="shared" si="4"/>
@@ -2938,10 +2937,10 @@
       </c>
       <c r="O9" s="18">
         <f t="shared" ref="O9:O11" si="10">M9+N9</f>
-        <v>3526966.7741935486</v>
+        <v>3000780</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2949,13 +2948,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>80</v>
@@ -2970,7 +2969,7 @@
         <v>1000000</v>
       </c>
       <c r="I10" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="18">
         <f t="shared" si="6"/>
@@ -2982,11 +2981,11 @@
       </c>
       <c r="L10" s="19">
         <f t="shared" si="8"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M10" s="18">
         <f t="shared" si="9"/>
-        <v>2702295.1612903229</v>
+        <v>2295100</v>
       </c>
       <c r="N10" s="18">
         <f t="shared" si="4"/>
@@ -2994,10 +2993,10 @@
       </c>
       <c r="O10" s="18">
         <f t="shared" si="10"/>
-        <v>2737295.1612903229</v>
+        <v>2330100</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3005,16 +3004,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>83</v>
@@ -3026,7 +3025,7 @@
         <v>700000</v>
       </c>
       <c r="I11" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="22">
         <f t="shared" si="6"/>
@@ -3038,7 +3037,7 @@
       </c>
       <c r="L11" s="23">
         <f t="shared" si="8"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M11" s="22">
         <f t="shared" si="9"/>
@@ -3053,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3061,13 +3060,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C12" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>252</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>253</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>80</v>
@@ -3082,7 +3081,7 @@
         <v>1000000</v>
       </c>
       <c r="I12" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="18">
         <f t="shared" si="0"/>
@@ -3094,11 +3093,11 @@
       </c>
       <c r="L12" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M12" s="18">
         <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
+        <v>2295100</v>
       </c>
       <c r="N12" s="18">
         <f t="shared" si="4"/>
@@ -3106,10 +3105,10 @@
       </c>
       <c r="O12" s="18">
         <f t="shared" si="5"/>
-        <v>2737295.1612903229</v>
+        <v>2330100</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3117,13 +3116,13 @@
         <v>14</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>80</v>
@@ -3138,7 +3137,7 @@
         <v>1100000</v>
       </c>
       <c r="I13" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="18">
         <f t="shared" ref="J13" si="11">IF(E13="штат",ROUND(Ставка_СН*H13*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H13+Ставка_СО*MIN(H13*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H13,Кап_ООСМС*МЗП),0),ROUND(H13*НДС,0))</f>
@@ -3150,11 +3149,11 @@
       </c>
       <c r="L13" s="19">
         <f t="shared" ref="L13" si="13">IF(AND(F13="новая",I13=1),Мес_2026_новые,MAX(0,4-I13))</f>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M13" s="18">
         <f t="shared" si="3"/>
-        <v>2965519.0322580645</v>
+        <v>2518660</v>
       </c>
       <c r="N13" s="18">
         <f t="shared" si="4"/>
@@ -3162,10 +3161,10 @@
       </c>
       <c r="O13" s="18">
         <f t="shared" si="5"/>
-        <v>3000519.0322580645</v>
+        <v>2553660</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3173,13 +3172,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="17" t="s">
         <v>255</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>256</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>80</v>
@@ -3194,7 +3193,7 @@
         <v>1000000</v>
       </c>
       <c r="I14" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="18">
         <f t="shared" si="0"/>
@@ -3206,11 +3205,11 @@
       </c>
       <c r="L14" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M14" s="18">
         <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
+        <v>2295100</v>
       </c>
       <c r="N14" s="18">
         <f t="shared" si="4"/>
@@ -3218,10 +3217,10 @@
       </c>
       <c r="O14" s="18">
         <f t="shared" si="5"/>
-        <v>2737295.1612903229</v>
+        <v>2330100</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -3229,13 +3228,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="D15" s="17" t="s">
         <v>255</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>256</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>80</v>
@@ -3250,7 +3249,7 @@
         <v>1000000</v>
       </c>
       <c r="I15" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="18">
         <f t="shared" si="0"/>
@@ -3262,11 +3261,11 @@
       </c>
       <c r="L15" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M15" s="18">
         <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
+        <v>2295100</v>
       </c>
       <c r="N15" s="18">
         <f t="shared" si="4"/>
@@ -3274,10 +3273,10 @@
       </c>
       <c r="O15" s="18">
         <f t="shared" si="5"/>
-        <v>2737295.1612903229</v>
+        <v>2330100</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3285,13 +3284,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>80</v>
@@ -3306,7 +3305,7 @@
         <v>1000000</v>
       </c>
       <c r="I16" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="18">
         <f t="shared" si="0"/>
@@ -3318,11 +3317,11 @@
       </c>
       <c r="L16" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M16" s="18">
         <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
+        <v>2295100</v>
       </c>
       <c r="N16" s="18">
         <f t="shared" si="4"/>
@@ -3330,10 +3329,10 @@
       </c>
       <c r="O16" s="18">
         <f t="shared" si="5"/>
-        <v>2737295.1612903229</v>
+        <v>2330100</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3341,13 +3340,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="D17" s="17" t="s">
         <v>255</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>256</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>80</v>
@@ -3389,7 +3388,7 @@
         <v>1182550</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3397,13 +3396,13 @@
         <v>19</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>80</v>
@@ -3445,7 +3444,7 @@
         <v>847210</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3453,13 +3452,13 @@
         <v>19</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>80</v>
@@ -3474,7 +3473,7 @@
         <v>700000</v>
       </c>
       <c r="I19" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="18">
         <f t="shared" si="0"/>
@@ -3486,11 +3485,11 @@
       </c>
       <c r="L19" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M19" s="18">
         <f t="shared" si="3"/>
-        <v>1912623.548387097</v>
+        <v>1624420</v>
       </c>
       <c r="N19" s="18">
         <f t="shared" si="4"/>
@@ -3498,10 +3497,10 @@
       </c>
       <c r="O19" s="18">
         <f t="shared" si="5"/>
-        <v>1947623.548387097</v>
+        <v>1659420</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -3509,13 +3508,13 @@
         <v>23</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>80</v>
@@ -3530,7 +3529,7 @@
         <v>1300000</v>
       </c>
       <c r="I20" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="18">
         <f t="shared" ref="J20" si="19">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
@@ -3542,11 +3541,11 @@
       </c>
       <c r="L20" s="19">
         <f t="shared" ref="L20" si="21">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M20" s="18">
         <f t="shared" si="3"/>
-        <v>3491966.7741935486</v>
+        <v>2965780</v>
       </c>
       <c r="N20" s="18">
         <f t="shared" si="4"/>
@@ -3554,10 +3553,10 @@
       </c>
       <c r="O20" s="18">
         <f t="shared" si="5"/>
-        <v>3526966.7741935486</v>
+        <v>3000780</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3565,16 +3564,16 @@
         <v>24</v>
       </c>
       <c r="B21" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="E21" s="20" t="s">
         <v>258</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>259</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>83</v>
@@ -3586,7 +3585,7 @@
         <v>1000000</v>
       </c>
       <c r="I21" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="22">
         <f t="shared" si="0"/>
@@ -3598,7 +3597,7 @@
       </c>
       <c r="L21" s="23">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M21" s="22">
         <f t="shared" si="3"/>
@@ -3613,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3621,13 +3620,13 @@
         <v>25</v>
       </c>
       <c r="B22" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="C22" s="17" t="s">
-        <v>261</v>
-      </c>
       <c r="D22" s="17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>80</v>
@@ -3642,7 +3641,7 @@
         <v>1300000</v>
       </c>
       <c r="I22" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="18">
         <f t="shared" si="0"/>
@@ -3654,11 +3653,11 @@
       </c>
       <c r="L22" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M22" s="18">
         <f t="shared" si="3"/>
-        <v>3491966.7741935486</v>
+        <v>2965780</v>
       </c>
       <c r="N22" s="18">
         <f t="shared" si="4"/>
@@ -3666,10 +3665,10 @@
       </c>
       <c r="O22" s="18">
         <f t="shared" si="5"/>
-        <v>3526966.7741935486</v>
+        <v>3000780</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -3677,10 +3676,10 @@
         <v>26</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>216</v>
@@ -3698,7 +3697,7 @@
         <v>1000000</v>
       </c>
       <c r="I23" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="18">
         <f t="shared" si="0"/>
@@ -3710,11 +3709,11 @@
       </c>
       <c r="L23" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M23" s="18">
         <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
+        <v>2295100</v>
       </c>
       <c r="N23" s="18">
         <f t="shared" si="4"/>
@@ -3722,10 +3721,10 @@
       </c>
       <c r="O23" s="18">
         <f t="shared" si="5"/>
-        <v>2737295.1612903229</v>
+        <v>2330100</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -3733,16 +3732,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>83</v>
@@ -3781,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -3789,16 +3788,16 @@
         <v>28</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>83</v>
@@ -3837,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -3845,10 +3844,10 @@
         <v>29</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>216</v>
@@ -3866,7 +3865,7 @@
         <v>700000</v>
       </c>
       <c r="I26" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="18">
         <f t="shared" si="0"/>
@@ -3878,11 +3877,11 @@
       </c>
       <c r="L26" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M26" s="18">
         <f t="shared" si="3"/>
-        <v>1912623.548387097</v>
+        <v>1624420</v>
       </c>
       <c r="N26" s="18">
         <f t="shared" si="4"/>
@@ -3890,10 +3889,10 @@
       </c>
       <c r="O26" s="18">
         <f t="shared" si="5"/>
-        <v>1947623.548387097</v>
+        <v>1659420</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -3901,10 +3900,10 @@
         <v>30</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>216</v>
@@ -3922,7 +3921,7 @@
         <v>1000000</v>
       </c>
       <c r="I27" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="18">
         <f t="shared" si="0"/>
@@ -3934,11 +3933,11 @@
       </c>
       <c r="L27" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M27" s="18">
         <f t="shared" si="3"/>
-        <v>2702295.1612903229</v>
+        <v>2295100</v>
       </c>
       <c r="N27" s="18">
         <f t="shared" si="4"/>
@@ -3946,10 +3945,10 @@
       </c>
       <c r="O27" s="18">
         <f t="shared" si="5"/>
-        <v>2737295.1612903229</v>
+        <v>2330100</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -3957,10 +3956,10 @@
         <v>31</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>216</v>
@@ -3978,7 +3977,7 @@
         <v>700000</v>
       </c>
       <c r="I28" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="18">
         <f t="shared" ref="J28:J34" si="25">IF(E28="штат",ROUND(Ставка_СН*H28*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H28+Ставка_СО*MIN(H28*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H28,Кап_ООСМС*МЗП),0),ROUND(H28*НДС,0))</f>
@@ -3990,11 +3989,11 @@
       </c>
       <c r="L28" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M28" s="18">
         <f t="shared" si="3"/>
-        <v>1912623.548387097</v>
+        <v>1624420</v>
       </c>
       <c r="N28" s="18">
         <f t="shared" si="4"/>
@@ -4002,10 +4001,10 @@
       </c>
       <c r="O28" s="18">
         <f t="shared" si="5"/>
-        <v>1947623.548387097</v>
+        <v>1659420</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4013,16 +4012,16 @@
         <v>32</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>83</v>
@@ -4061,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -4069,7 +4068,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>84</v>
@@ -4117,7 +4116,7 @@
         <v>4784010</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4125,7 +4124,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>85</v>
@@ -4146,7 +4145,7 @@
         <v>700000</v>
       </c>
       <c r="I31" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="18">
         <f t="shared" si="25"/>
@@ -4158,11 +4157,11 @@
       </c>
       <c r="L31" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M31" s="18">
         <f t="shared" si="3"/>
-        <v>1912623.548387097</v>
+        <v>1624420</v>
       </c>
       <c r="N31" s="18">
         <f t="shared" si="4"/>
@@ -4170,7 +4169,7 @@
       </c>
       <c r="O31" s="18">
         <f t="shared" si="5"/>
-        <v>1947623.548387097</v>
+        <v>1659420</v>
       </c>
       <c r="P31" s="17" t="s">
         <v>213</v>
@@ -4181,13 +4180,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>391</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>393</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>80</v>
@@ -4202,7 +4201,7 @@
         <v>1200000</v>
       </c>
       <c r="I32" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="18">
         <f t="shared" si="25"/>
@@ -4214,11 +4213,11 @@
       </c>
       <c r="L32" s="19">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M32" s="18">
         <f t="shared" si="3"/>
-        <v>3228742.9032258065</v>
+        <v>2742220</v>
       </c>
       <c r="N32" s="18">
         <f t="shared" si="4"/>
@@ -4226,10 +4225,10 @@
       </c>
       <c r="O32" s="18">
         <f t="shared" si="5"/>
-        <v>3263742.9032258065</v>
+        <v>2777220</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4237,16 +4236,16 @@
         <v>36</v>
       </c>
       <c r="B33" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>284</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>285</v>
       </c>
       <c r="D33" s="21" t="s">
         <v>214</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F33" s="20" t="s">
         <v>83</v>
@@ -4258,7 +4257,7 @@
         <v>1000000</v>
       </c>
       <c r="I33" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="22">
         <f t="shared" si="25"/>
@@ -4270,7 +4269,7 @@
       </c>
       <c r="L33" s="23">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M33" s="22">
         <f t="shared" si="3"/>
@@ -4285,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4293,16 +4292,16 @@
         <v>37</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D34" s="21" t="s">
         <v>214</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>83</v>
@@ -4314,7 +4313,7 @@
         <v>700000</v>
       </c>
       <c r="I34" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="22">
         <f t="shared" si="25"/>
@@ -4326,7 +4325,7 @@
       </c>
       <c r="L34" s="23">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="M34" s="22">
         <f t="shared" si="3"/>
@@ -4341,14 +4340,14 @@
         <v>0</v>
       </c>
       <c r="P34" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -4370,7 +4369,7 @@
       <c r="L35" s="7"/>
       <c r="M35" s="6">
         <f>SUM(M5:M34)</f>
-        <v>68758393.225806445</v>
+        <v>61677420</v>
       </c>
       <c r="N35" s="6">
         <f t="shared" ref="N35:O35" si="27">SUM(N5:N34)</f>
@@ -4378,13 +4377,13 @@
       </c>
       <c r="O35" s="6">
         <f t="shared" si="27"/>
-        <v>69423393.225806445</v>
+        <v>62342420</v>
       </c>
       <c r="P35" s="7"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G36">
         <f>SUM(G8:G12)+SUM(G13:G29)</f>
@@ -4397,7 +4396,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G37">
         <f>G35-G36</f>
@@ -4434,7 +4433,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -4448,19 +4447,19 @@
         <v>69</v>
       </c>
       <c r="D3" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>291</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="F3" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="G3" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="G3" s="25" t="s">
-        <v>294</v>
-      </c>
       <c r="H3" s="25" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -4474,13 +4473,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E4" s="28">
         <v>1000000</v>
@@ -4494,15 +4493,15 @@
         <v>1160000</v>
       </c>
       <c r="H4" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="29">
         <f t="shared" ref="I4:I10" si="2">IF(H4=1,Мес_2026_новые,MAX(0,4-H4))</f>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="J4" s="28">
         <f t="shared" ref="J4:J10" si="3">G4*I4</f>
-        <v>2731612.9032258065</v>
+        <v>2320000</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -4510,13 +4509,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E5" s="28">
         <v>700000</v>
@@ -4530,15 +4529,15 @@
         <v>812000</v>
       </c>
       <c r="H5" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="29">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="J5" s="28">
         <f t="shared" si="3"/>
-        <v>1912129.0322580647</v>
+        <v>1624000</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -4546,13 +4545,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="D6" s="27" t="s">
         <v>300</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>301</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -4566,15 +4565,15 @@
         <v>1160000</v>
       </c>
       <c r="H6" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="29">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="J6" s="28">
         <f t="shared" si="3"/>
-        <v>2731612.9032258065</v>
+        <v>2320000</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -4582,13 +4581,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>302</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="D7" s="27" t="s">
         <v>303</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>304</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -4618,13 +4617,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="D8" s="27" t="s">
         <v>305</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>306</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -4654,13 +4653,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>412</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>414</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>415</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>416</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -4674,15 +4673,15 @@
         <v>812000</v>
       </c>
       <c r="H9" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="29">
         <f t="shared" si="2"/>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="J9" s="28">
         <f t="shared" si="3"/>
-        <v>1912129.0322580647</v>
+        <v>1624000</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -4690,13 +4689,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>307</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>308</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -4724,7 +4723,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4744,7 +4743,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="31">
         <f>SUM(J4:J10)</f>
-        <v>14855483.870967744</v>
+        <v>13456000</v>
       </c>
     </row>
   </sheetData>
@@ -4768,7 +4767,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4864,16 +4863,16 @@
       </c>
       <c r="F7" s="15">
         <f>Штат!L8</f>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="0"/>
-        <v>374713.70967741939</v>
+        <v>318250</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")</f>
@@ -4887,16 +4886,16 @@
       </c>
       <c r="F8" s="15">
         <f>IF(C8&gt;0,SUMIFS(Штат!$L$5:$L$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")/C8,0)</f>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="0"/>
-        <v>838469.75806451612</v>
+        <v>712125</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")</f>
@@ -4910,16 +4909,16 @@
       </c>
       <c r="F9" s="15">
         <f>IF(C9&gt;0,SUMIFS(Штат!$L$5:$L$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")/C9,0)</f>
-        <v>1.9677419354838712</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>1315091.1290322582</v>
+        <v>1145699.9999999998</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G20:G21)</f>
@@ -4933,16 +4932,16 @@
       </c>
       <c r="F10" s="15">
         <f>Штат!L20</f>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" si="0"/>
-        <v>37471.370967741932</v>
+        <v>31825</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -4956,11 +4955,11 @@
       </c>
       <c r="F11" s="15">
         <f>Штат!L22</f>
-        <v>2.3548387096774195</v>
+        <v>2</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="0"/>
-        <v>1863266.1290322582</v>
+        <v>1582500</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4974,7 +4973,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="6">
         <f>SUM(G5:G11)</f>
-        <v>4906387.0967741935</v>
+        <v>4267775</v>
       </c>
     </row>
   </sheetData>
@@ -5002,12 +5001,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5030,7 +5029,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -5062,7 +5061,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -5092,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -5164,7 +5163,7 @@
         <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -5222,7 +5221,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -5298,7 +5297,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
@@ -5417,7 +5416,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
@@ -5489,7 +5488,7 @@
         <v>98</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C20" t="s">
         <v>100</v>
@@ -5508,7 +5507,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
@@ -5520,10 +5519,10 @@
         <v>98</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C21" t="s">
         <v>237</v>
-      </c>
-      <c r="C21" t="s">
-        <v>238</v>
       </c>
       <c r="D21" s="9">
         <v>1</v>
@@ -5539,7 +5538,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
@@ -5551,7 +5550,7 @@
         <v>98</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C22" t="s">
         <v>100</v>
@@ -5570,7 +5569,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
@@ -5582,7 +5581,7 @@
         <v>98</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C23" t="s">
         <v>104</v>
@@ -5601,7 +5600,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
@@ -5613,7 +5612,7 @@
         <v>98</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C24" t="s">
         <v>100</v>
@@ -5632,7 +5631,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -5644,7 +5643,7 @@
         <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C25" t="s">
         <v>100</v>
@@ -5663,7 +5662,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -5675,7 +5674,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C26" t="s">
         <v>100</v>
@@ -5694,7 +5693,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -5706,7 +5705,7 @@
         <v>98</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C27" t="s">
         <v>100</v>
@@ -5725,7 +5724,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -5737,7 +5736,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C28" t="s">
         <v>100</v>
@@ -5756,7 +5755,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="1">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -5768,7 +5767,7 @@
         <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C29" t="s">
         <v>100</v>
@@ -5787,7 +5786,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -5799,7 +5798,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
@@ -5818,7 +5817,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -5918,7 +5917,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -5937,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -5949,7 +5948,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -5977,7 +5976,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
@@ -5996,7 +5995,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" ref="I36" si="2">IF(F36="разово",IF(G36&lt;=3,D36*E36,0),IF(F36="мес",D36*E36*MAX(0,4-G36),D36*E36*MAX(0,4-G36)/12))</f>
@@ -6064,7 +6063,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -6111,7 +6110,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I40" s="5">
         <f>D40*E40*Аренда_мес_2026</f>
@@ -6142,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" ref="I41:I57" si="3">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
@@ -6169,12 +6168,12 @@
         <v>121</v>
       </c>
       <c r="G42" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="5">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6197,12 +6196,12 @@
         <v>121</v>
       </c>
       <c r="G43" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="4"/>
       <c r="I43" s="5">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6225,12 +6224,12 @@
         <v>121</v>
       </c>
       <c r="G44" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="4"/>
       <c r="I44" s="5">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6253,12 +6252,12 @@
         <v>121</v>
       </c>
       <c r="G45" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
-        <v>90000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6266,7 +6265,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -6282,14 +6281,14 @@
         <v>121</v>
       </c>
       <c r="G46" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
-        <v>112125</v>
+        <v>74750</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6297,7 +6296,7 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -6316,7 +6315,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
@@ -6343,12 +6342,12 @@
         <v>121</v>
       </c>
       <c r="G48" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="5">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6371,14 +6370,14 @@
         <v>121</v>
       </c>
       <c r="G49" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
-        <v>399000</v>
+        <v>266000</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6401,12 +6400,12 @@
         <v>121</v>
       </c>
       <c r="G50" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="5">
         <f t="shared" si="3"/>
-        <v>67500</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6429,14 +6428,14 @@
         <v>121</v>
       </c>
       <c r="G51" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>134</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6459,12 +6458,12 @@
         <v>121</v>
       </c>
       <c r="G52" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="5">
         <f t="shared" si="3"/>
-        <v>48000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6472,15 +6471,15 @@
         <v>136</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C53" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="10"/>
       <c r="F53" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G53" s="9"/>
       <c r="H53" s="4"/>
@@ -6508,12 +6507,12 @@
         <v>121</v>
       </c>
       <c r="G54" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="5">
         <f t="shared" si="3"/>
-        <v>450000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6536,12 +6535,12 @@
         <v>121</v>
       </c>
       <c r="G55" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="5">
         <f t="shared" si="3"/>
-        <v>75000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6549,7 +6548,7 @@
         <v>140</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C56" t="s">
         <v>104</v>
@@ -6577,7 +6576,7 @@
         <v>140</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -6592,12 +6591,12 @@
         <v>138</v>
       </c>
       <c r="G57" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="5">
         <f t="shared" si="3"/>
-        <v>25000</v>
+        <v>16666.666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -6626,7 +6625,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6657,18 +6656,18 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>290</v>
-      </c>
       <c r="C5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
       <c r="F5" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G5" s="5">
         <v>3600000</v>
@@ -6676,18 +6675,18 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
       <c r="F6" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G6" s="5">
         <v>1200000</v>
@@ -6695,18 +6694,18 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
       <c r="F7" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G7" s="5">
         <v>6100000</v>
@@ -6714,18 +6713,18 @@
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
       <c r="F8" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G8" s="5">
         <v>18400000</v>
@@ -6733,18 +6732,18 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
       <c r="F9" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G9" s="5">
         <v>9200000</v>
@@ -6752,18 +6751,18 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
       <c r="F10" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G10" s="5">
         <v>30504855.379999999</v>
@@ -6771,18 +6770,18 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" t="s">
         <v>245</v>
-      </c>
-      <c r="C11" t="s">
-        <v>246</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
       <c r="F11" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G11" s="5">
         <v>18400000</v>
@@ -6793,7 +6792,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -6829,7 +6828,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -6876,7 +6875,7 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7012,7 +7011,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -7169,7 +7168,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -7435,7 +7434,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="431">
   <si>
     <t>Статья</t>
   </si>
@@ -1397,6 +1397,24 @@
   </si>
   <si>
     <t>Мес. 2026 (новые – с 01.11)</t>
+  </si>
+  <si>
+    <t>Стул офисный для посетителей</t>
+  </si>
+  <si>
+    <t>Дополнение № 1 в план закупок, поз. 81: цена zeta.kz (Астана) 11 425 ₸ с НДС за стул «Изо»; в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>Жалюзи вертикальные тканевые (зона 710)</t>
+  </si>
+  <si>
+    <t>Дополнение № 1, поз. 82: 1 комплект на окна зоны 710 с установкой – 428 736 ₸ с НДС; в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>Декоративное растение напольное в высоком кашпо</t>
+  </si>
+  <si>
+    <t>Дополнение № 1, поз. 83: kaspi.kz (Астана) – дерево 25 974 + кашпо 4 727 = 30 701 ₸ с НДС; в бюджете без НДС (÷1,16)</t>
   </si>
 </sst>
 </file>
@@ -1969,8 +1987,8 @@
         <v>358</v>
       </c>
       <c r="B10" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Оснащение")</f>
-        <v>28145855</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Оснащение")</f>
+        <v>28742588</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1978,7 +1996,7 @@
         <v>373</v>
       </c>
       <c r="B11" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Офис")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Офис")</f>
         <v>17202663.496774193</v>
       </c>
     </row>
@@ -1987,7 +2005,7 @@
         <v>359</v>
       </c>
       <c r="B12" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Цифровые")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Цифровые")</f>
         <v>463000</v>
       </c>
     </row>
@@ -1996,7 +2014,7 @@
         <v>360</v>
       </c>
       <c r="B13" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Медиа")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Медиа")</f>
         <v>2350000</v>
       </c>
     </row>
@@ -2006,7 +2024,7 @@
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>128227713.4967742</v>
+        <v>128824446.4967742</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2014,8 +2032,8 @@
         <v>384</v>
       </c>
       <c r="B15" s="38">
-        <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I57,'Оснащение и офис'!A5:A57,"Прочие")</f>
-        <v>12889438.016344087</v>
+        <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Прочие")</f>
+        <v>12949111.316344086</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2024,7 +2042,7 @@
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>22578744.242098927</v>
+        <v>22683769.250098925</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2033,7 +2051,7 @@
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>163695895.75521722</v>
+        <v>164457327.06321719</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2051,7 +2069,7 @@
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>251100751.13521722</v>
+        <v>251862182.44321719</v>
       </c>
     </row>
   </sheetData>
@@ -4987,7 +5005,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5064,7 +5082,7 @@
         <v>418</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I39" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
+        <f t="shared" ref="I5:I42" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
         <v>7650000</v>
       </c>
     </row>
@@ -6007,16 +6025,17 @@
         <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>116</v>
+        <v>425</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D37" s="9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E37" s="10">
-        <v>150000</v>
+        <f>ROUND(11425/(1+НДС),0)</f>
+        <v>9849</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>101</v>
@@ -6024,10 +6043,12 @@
       <c r="G37" s="9">
         <v>1</v>
       </c>
-      <c r="H37" s="4"/>
+      <c r="H37" s="4" t="s">
+        <v>426</v>
+      </c>
       <c r="I37" s="5">
-        <f t="shared" si="0"/>
-        <v>150000</v>
+        <f t="shared" ref="I37:I39" si="3">IF(F37="разово",IF(G37&lt;=3,D37*E37,0),IF(F37="мес",D37*E37*MAX(0,4-G37),D37*E37*MAX(0,4-G37)/12))</f>
+        <v>147735</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6035,7 +6056,7 @@
         <v>98</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>117</v>
+        <v>427</v>
       </c>
       <c r="C38" t="s">
         <v>104</v>
@@ -6044,7 +6065,8 @@
         <v>1</v>
       </c>
       <c r="E38" s="10">
-        <v>400000</v>
+        <f>ROUND(428736/(1+НДС),0)</f>
+        <v>369600</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>101</v>
@@ -6052,10 +6074,12 @@
       <c r="G38" s="9">
         <v>1</v>
       </c>
-      <c r="H38" s="4"/>
+      <c r="H38" s="4" t="s">
+        <v>428</v>
+      </c>
       <c r="I38" s="5">
-        <f t="shared" si="0"/>
-        <v>400000</v>
+        <f t="shared" si="3"/>
+        <v>369600</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6063,16 +6087,17 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
       </c>
       <c r="D39" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="10">
-        <v>10000</v>
+        <f>ROUND(30701/(1+НДС),0)</f>
+        <v>26466</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>101</v>
@@ -6080,128 +6105,127 @@
       <c r="G39" s="9">
         <v>1</v>
       </c>
-      <c r="H39" s="4"/>
+      <c r="H39" s="4" t="s">
+        <v>430</v>
+      </c>
       <c r="I39" s="5">
+        <f t="shared" si="3"/>
+        <v>79398</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="9">
+        <v>1</v>
+      </c>
+      <c r="E40" s="10">
+        <v>150000</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" s="9">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="5">
+        <f t="shared" si="0"/>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="9">
+        <v>1</v>
+      </c>
+      <c r="E41" s="10">
+        <v>400000</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41" s="9">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="5">
+        <f t="shared" si="0"/>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C42" t="s">
+        <v>100</v>
+      </c>
+      <c r="D42" s="9">
+        <v>2</v>
+      </c>
+      <c r="E42" s="10">
+        <v>10000</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" s="9">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="5">
         <f t="shared" si="0"/>
         <v>20000</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="43" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B43" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C43" t="s">
         <v>120</v>
       </c>
-      <c r="D40" s="9">
-        <v>1</v>
-      </c>
-      <c r="E40" s="10">
+      <c r="D43" s="9">
+        <v>1</v>
+      </c>
+      <c r="E43" s="10">
         <f>Аренда_мес</f>
         <v>4909152.0999999996</v>
       </c>
-      <c r="F40" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G40" s="9">
-        <v>1</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="I40" s="5">
-        <f>D40*E40*Аренда_мес_2026</f>
-        <v>11560261.396774193</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>118</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C41" t="s">
-        <v>122</v>
-      </c>
-      <c r="D41" s="9">
-        <v>1</v>
-      </c>
-      <c r="E41" s="10">
-        <f>Аренда_мес*Депозит_мес</f>
-        <v>4909152.0999999996</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G41" s="9">
-        <v>1</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="I41" s="5">
-        <f t="shared" ref="I41:I57" si="3">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
-        <v>4909152.0999999996</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>118</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" s="9">
-        <v>1</v>
-      </c>
-      <c r="E42" s="10">
-        <v>50000</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G42" s="9">
-        <v>2</v>
-      </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="5">
-        <f t="shared" si="3"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>118</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" s="9">
-        <v>1</v>
-      </c>
-      <c r="E43" s="10">
-        <v>60000</v>
-      </c>
       <c r="F43" s="9" t="s">
         <v>121</v>
       </c>
       <c r="G43" s="9">
-        <v>2</v>
-      </c>
-      <c r="H43" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>324</v>
+      </c>
       <c r="I43" s="5">
-        <f t="shared" si="3"/>
-        <v>120000</v>
+        <f>D43*E43*Аренда_мес_2026</f>
+        <v>11560261.396774193</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6209,27 +6233,30 @@
         <v>118</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>125</v>
+        <v>223</v>
       </c>
       <c r="C44" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D44" s="9">
         <v>1</v>
       </c>
       <c r="E44" s="10">
-        <v>50000</v>
+        <f>Аренда_мес*Депозит_мес</f>
+        <v>4909152.0999999996</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="G44" s="9">
-        <v>2</v>
-      </c>
-      <c r="H44" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="I44" s="5">
-        <f t="shared" si="3"/>
-        <v>100000</v>
+        <f t="shared" ref="I44:I60" si="4">IF(F44="разово",IF(G44&lt;=3,D44*E44,0),IF(F44="мес",D44*E44*MAX(0,4-G44),D44*E44*MAX(0,4-G44)/12))</f>
+        <v>4909152.0999999996</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6237,7 +6264,7 @@
         <v>118</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C45" t="s">
         <v>120</v>
@@ -6246,7 +6273,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="10">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>121</v>
@@ -6256,8 +6283,8 @@
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="5">
-        <f t="shared" si="3"/>
-        <v>60000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6265,7 +6292,7 @@
         <v>118</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>377</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
         <v>120</v>
@@ -6274,8 +6301,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="10">
-        <f>Канцелярия!F11</f>
-        <v>37375</v>
+        <v>60000</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>121</v>
@@ -6283,12 +6309,10 @@
       <c r="G46" s="9">
         <v>2</v>
       </c>
-      <c r="H46" s="4" t="s">
-        <v>378</v>
-      </c>
+      <c r="H46" s="4"/>
       <c r="I46" s="5">
-        <f t="shared" si="3"/>
-        <v>74750</v>
+        <f t="shared" si="4"/>
+        <v>120000</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6296,30 +6320,27 @@
         <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>379</v>
+        <v>125</v>
       </c>
       <c r="C47" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D47" s="9">
         <v>1</v>
       </c>
       <c r="E47" s="10">
-        <f>Канцелярия!F20</f>
-        <v>78500</v>
+        <v>50000</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G47" s="9">
-        <v>1</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>380</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H47" s="4"/>
       <c r="I47" s="5">
-        <f t="shared" ref="I47" si="4">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
-        <v>78500</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6327,7 +6348,7 @@
         <v>118</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C48" t="s">
         <v>120</v>
@@ -6336,7 +6357,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="10">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>121</v>
@@ -6346,25 +6367,26 @@
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="5">
-        <f t="shared" si="3"/>
-        <v>200000</v>
+        <f t="shared" si="4"/>
+        <v>60000</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>129</v>
+        <v>377</v>
       </c>
       <c r="C49" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D49" s="9">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E49" s="10">
-        <v>7000</v>
+        <f>Канцелярия!F11</f>
+        <v>37375</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>121</v>
@@ -6373,56 +6395,59 @@
         <v>2</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="I49" s="5">
-        <f t="shared" si="3"/>
-        <v>266000</v>
+        <f t="shared" si="4"/>
+        <v>74750</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>131</v>
+        <v>379</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="D50" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" s="10">
-        <v>7500</v>
+        <f>Канцелярия!F20</f>
+        <v>78500</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="G50" s="9">
-        <v>2</v>
-      </c>
-      <c r="H50" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>380</v>
+      </c>
       <c r="I50" s="5">
-        <f t="shared" si="3"/>
-        <v>45000</v>
+        <f t="shared" ref="I50" si="5">IF(F50="разово",IF(G50&lt;=3,D50*E50,0),IF(F50="мес",D50*E50*MAX(0,4-G50),D50*E50*MAX(0,4-G50)/12))</f>
+        <v>78500</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C51" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D51" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="10">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>121</v>
@@ -6430,12 +6455,10 @@
       <c r="G51" s="9">
         <v>2</v>
       </c>
-      <c r="H51" s="4" t="s">
-        <v>134</v>
-      </c>
+      <c r="H51" s="4"/>
       <c r="I51" s="5">
-        <f t="shared" si="3"/>
-        <v>120000</v>
+        <f t="shared" si="4"/>
+        <v>200000</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6443,16 +6466,16 @@
         <v>128</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D52" s="9">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E52" s="10">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>121</v>
@@ -6460,48 +6483,57 @@
       <c r="G52" s="9">
         <v>2</v>
       </c>
-      <c r="H52" s="4"/>
+      <c r="H52" s="4" t="s">
+        <v>370</v>
+      </c>
       <c r="I52" s="5">
-        <f t="shared" si="3"/>
-        <v>32000</v>
+        <f t="shared" si="4"/>
+        <v>266000</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>315</v>
+        <v>131</v>
       </c>
       <c r="C53" t="s">
-        <v>245</v>
-      </c>
-      <c r="D53" s="9"/>
-      <c r="E53" s="10"/>
+        <v>130</v>
+      </c>
+      <c r="D53" s="9">
+        <v>3</v>
+      </c>
+      <c r="E53" s="10">
+        <v>7500</v>
+      </c>
       <c r="F53" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="G53" s="9"/>
+        <v>121</v>
+      </c>
+      <c r="G53" s="9">
+        <v>2</v>
+      </c>
       <c r="H53" s="4"/>
       <c r="I53" s="5">
-        <v>2000000</v>
+        <f t="shared" si="4"/>
+        <v>45000</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D54" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="10">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>121</v>
@@ -6509,27 +6541,29 @@
       <c r="G54" s="9">
         <v>2</v>
       </c>
-      <c r="H54" s="4"/>
+      <c r="H54" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="I54" s="5">
-        <f t="shared" si="3"/>
-        <v>300000</v>
+        <f t="shared" si="4"/>
+        <v>120000</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D55" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="10">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>121</v>
@@ -6539,63 +6573,140 @@
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="5">
-        <f t="shared" si="3"/>
-        <v>50000</v>
+        <f t="shared" si="4"/>
+        <v>32000</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>371</v>
+        <v>315</v>
       </c>
       <c r="C56" t="s">
-        <v>104</v>
-      </c>
-      <c r="D56" s="9">
-        <v>1</v>
-      </c>
-      <c r="E56" s="10">
-        <v>50000</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="D56" s="9"/>
+      <c r="E56" s="10"/>
       <c r="F56" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G56" s="9">
-        <v>1</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="G56" s="9"/>
       <c r="H56" s="4"/>
       <c r="I56" s="5">
-        <f t="shared" si="3"/>
-        <v>50000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>372</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="D57" s="9">
         <v>1</v>
       </c>
       <c r="E57" s="10">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="G57" s="9">
         <v>2</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>136</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="9">
+        <v>1</v>
+      </c>
+      <c r="E58" s="10">
+        <v>25000</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G58" s="9">
+        <v>2</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="5">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C59" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="9">
+        <v>1</v>
+      </c>
+      <c r="E59" s="10">
+        <v>50000</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G59" s="9">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="5">
+        <f t="shared" si="4"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C60" t="s">
+        <v>138</v>
+      </c>
+      <c r="D60" s="9">
+        <v>1</v>
+      </c>
+      <c r="E60" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G60" s="9">
+        <v>2</v>
+      </c>
+      <c r="H60" s="4"/>
+      <c r="I60" s="5">
+        <f t="shared" si="4"/>
         <v>16666.666666666668</v>
       </c>
     </row>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="432">
   <si>
     <t>Статья</t>
   </si>
@@ -1415,6 +1415,9 @@
   </si>
   <si>
     <t>Дополнение № 1, поз. 83: kaspi.kz (Астана) – дерево 25 974 + кашпо 4 727 = 30 701 ₸ с НДС; в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>Мес. 2026 (поездки – с ноября)</t>
   </si>
 </sst>
 </file>
@@ -1979,7 +1982,7 @@
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
-        <v>4267775</v>
+        <v>4108650</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2024,7 +2027,7 @@
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>128824446.4967742</v>
+        <v>128665321.4967742</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2033,7 +2036,7 @@
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Прочие")</f>
-        <v>12949111.316344086</v>
+        <v>12933198.816344086</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2042,7 +2045,7 @@
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>22683769.250098925</v>
+        <v>22655763.250098925</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2051,7 +2054,7 @@
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>164457327.06321719</v>
+        <v>164254283.56321719</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2069,7 +2072,7 @@
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>251862182.44321719</v>
+        <v>251659138.94321719</v>
       </c>
     </row>
   </sheetData>
@@ -4810,7 +4813,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>76</v>
+        <v>431</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>91</v>
@@ -4832,12 +4835,12 @@
         <v>0</v>
       </c>
       <c r="F5" s="15">
-        <f>Штат!L5</f>
-        <v>3</v>
+        <f>MIN(2,Штат!L5)</f>
+        <v>2</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" ref="G5:G11" si="0">C5*(D5/12*F5*Поездка_РК+E5*F5*Поездка_местн)</f>
-        <v>190950</v>
+        <v>127300</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4856,12 +4859,12 @@
         <v>0</v>
       </c>
       <c r="F6" s="15">
-        <f>Штат!L6</f>
-        <v>3</v>
+        <f>MIN(2,Штат!L6)</f>
+        <v>2</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="0"/>
-        <v>286425</v>
+        <v>190950</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4880,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="15">
-        <f>Штат!L8</f>
+        <f>MIN(2,Штат!L8)</f>
         <v>2</v>
       </c>
       <c r="G7" s="5">
@@ -4903,7 +4906,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="15">
-        <f>IF(C8&gt;0,SUMIFS(Штат!$L$5:$L$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")/C8,0)</f>
+        <f>MIN(2,IF(C8&gt;0,SUMIFS(Штат!$L$5:$L$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")/C8,0))</f>
         <v>2</v>
       </c>
       <c r="G8" s="5">
@@ -4926,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="15">
-        <f>IF(C9&gt;0,SUMIFS(Штат!$L$5:$L$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")/C9,0)</f>
+        <f>MIN(2,IF(C9&gt;0,SUMIFS(Штат!$L$5:$L$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")/C9,0))</f>
         <v>1.7142857142857142</v>
       </c>
       <c r="G9" s="5">
@@ -4949,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="15">
-        <f>Штат!L20</f>
+        <f>MIN(2,Штат!L20)</f>
         <v>2</v>
       </c>
       <c r="G10" s="5">
@@ -4972,7 +4975,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="15">
-        <f>Штат!L22</f>
+        <f>MIN(2,Штат!L22)</f>
         <v>2</v>
       </c>
       <c r="G11" s="5">
@@ -4991,7 +4994,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="6">
         <f>SUM(G5:G11)</f>
-        <v>4267775</v>
+        <v>4108650</v>
       </c>
     </row>
   </sheetData>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -19,51 +19,312 @@
     <sheet name="Командировки" sheetId="4" r:id="rId5"/>
     <sheet name="Оснащение и офис" sheetId="5" r:id="rId6"/>
     <sheet name="Проекты" sheetId="8" r:id="rId7"/>
-    <sheet name="Канцелярия" sheetId="7" r:id="rId8"/>
-    <sheet name="Смета фото-видео" sheetId="6" r:id="rId9"/>
+    <sheet name="Taza talqy" sheetId="10" r:id="rId8"/>
+    <sheet name="Презентация офисе" sheetId="11" r:id="rId9"/>
+    <sheet name="креативные проекты" sheetId="12" r:id="rId10"/>
+    <sheet name="Информ сопровождение" sheetId="13" r:id="rId11"/>
+    <sheet name="Соц исследования" sheetId="14" r:id="rId12"/>
+    <sheet name="Разработка платформы" sheetId="15" r:id="rId13"/>
+    <sheet name="Канцелярия" sheetId="7" r:id="rId14"/>
+    <sheet name="Смета фото-видео" sheetId="6" r:id="rId15"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId16"/>
+  </externalReferences>
   <definedNames>
+    <definedName name="Авиа_межд" localSheetId="7">#REF!</definedName>
+    <definedName name="Авиа_межд" localSheetId="10">#REF!</definedName>
+    <definedName name="Авиа_межд" localSheetId="9">#REF!</definedName>
+    <definedName name="Авиа_межд" localSheetId="8">#REF!</definedName>
+    <definedName name="Авиа_межд" localSheetId="12">#REF!</definedName>
+    <definedName name="Авиа_межд" localSheetId="11">#REF!</definedName>
     <definedName name="Авиа_межд">Параметры!$B$25</definedName>
+    <definedName name="Авиа_РК" localSheetId="7">#REF!</definedName>
+    <definedName name="Авиа_РК" localSheetId="10">#REF!</definedName>
+    <definedName name="Авиа_РК" localSheetId="9">#REF!</definedName>
+    <definedName name="Авиа_РК" localSheetId="8">#REF!</definedName>
+    <definedName name="Авиа_РК" localSheetId="12">#REF!</definedName>
+    <definedName name="Авиа_РК" localSheetId="11">#REF!</definedName>
     <definedName name="Авиа_РК">Параметры!$B$18</definedName>
+    <definedName name="Аренда_депозит" localSheetId="7">#REF!</definedName>
+    <definedName name="Аренда_депозит" localSheetId="10">#REF!</definedName>
+    <definedName name="Аренда_депозит" localSheetId="9">#REF!</definedName>
+    <definedName name="Аренда_депозит" localSheetId="8">#REF!</definedName>
+    <definedName name="Аренда_депозит" localSheetId="12">#REF!</definedName>
+    <definedName name="Аренда_депозит" localSheetId="11">#REF!</definedName>
     <definedName name="Аренда_депозит">Параметры!$B$48</definedName>
+    <definedName name="Аренда_мес" localSheetId="7">#REF!</definedName>
+    <definedName name="Аренда_мес" localSheetId="10">#REF!</definedName>
+    <definedName name="Аренда_мес" localSheetId="9">#REF!</definedName>
+    <definedName name="Аренда_мес" localSheetId="8">#REF!</definedName>
+    <definedName name="Аренда_мес" localSheetId="12">#REF!</definedName>
+    <definedName name="Аренда_мес" localSheetId="11">#REF!</definedName>
     <definedName name="Аренда_мес">Параметры!$B$32</definedName>
+    <definedName name="Аренда_мес_2026" localSheetId="7">#REF!</definedName>
+    <definedName name="Аренда_мес_2026" localSheetId="10">#REF!</definedName>
+    <definedName name="Аренда_мес_2026" localSheetId="9">#REF!</definedName>
+    <definedName name="Аренда_мес_2026" localSheetId="8">#REF!</definedName>
+    <definedName name="Аренда_мес_2026" localSheetId="12">#REF!</definedName>
+    <definedName name="Аренда_мес_2026" localSheetId="11">#REF!</definedName>
     <definedName name="Аренда_мес_2026">Параметры!$B$49</definedName>
+    <definedName name="Аренда_с_НДС" localSheetId="7">#REF!</definedName>
+    <definedName name="Аренда_с_НДС" localSheetId="10">#REF!</definedName>
+    <definedName name="Аренда_с_НДС" localSheetId="9">#REF!</definedName>
+    <definedName name="Аренда_с_НДС" localSheetId="8">#REF!</definedName>
+    <definedName name="Аренда_с_НДС" localSheetId="12">#REF!</definedName>
+    <definedName name="Аренда_с_НДС" localSheetId="11">#REF!</definedName>
     <definedName name="Аренда_с_НДС">Параметры!$B$47</definedName>
+    <definedName name="Депозит_мес" localSheetId="7">#REF!</definedName>
+    <definedName name="Депозит_мес" localSheetId="10">#REF!</definedName>
+    <definedName name="Депозит_мес" localSheetId="9">#REF!</definedName>
+    <definedName name="Депозит_мес" localSheetId="8">#REF!</definedName>
+    <definedName name="Депозит_мес" localSheetId="12">#REF!</definedName>
+    <definedName name="Депозит_мес" localSheetId="11">#REF!</definedName>
     <definedName name="Депозит_мес">Параметры!$B$33</definedName>
+    <definedName name="Дней_межд" localSheetId="7">#REF!</definedName>
+    <definedName name="Дней_межд" localSheetId="10">#REF!</definedName>
+    <definedName name="Дней_межд" localSheetId="9">#REF!</definedName>
+    <definedName name="Дней_межд" localSheetId="8">#REF!</definedName>
+    <definedName name="Дней_межд" localSheetId="12">#REF!</definedName>
+    <definedName name="Дней_межд" localSheetId="11">#REF!</definedName>
     <definedName name="Дней_межд">Параметры!$B$28</definedName>
+    <definedName name="Дней_РК" localSheetId="7">#REF!</definedName>
+    <definedName name="Дней_РК" localSheetId="10">#REF!</definedName>
+    <definedName name="Дней_РК" localSheetId="9">#REF!</definedName>
+    <definedName name="Дней_РК" localSheetId="8">#REF!</definedName>
+    <definedName name="Дней_РК" localSheetId="12">#REF!</definedName>
+    <definedName name="Дней_РК" localSheetId="11">#REF!</definedName>
     <definedName name="Дней_РК">Параметры!$B$21</definedName>
+    <definedName name="Кап_ООСМС" localSheetId="7">#REF!</definedName>
+    <definedName name="Кап_ООСМС" localSheetId="10">#REF!</definedName>
+    <definedName name="Кап_ООСМС" localSheetId="9">#REF!</definedName>
+    <definedName name="Кап_ООСМС" localSheetId="8">#REF!</definedName>
+    <definedName name="Кап_ООСМС" localSheetId="12">#REF!</definedName>
+    <definedName name="Кап_ООСМС" localSheetId="11">#REF!</definedName>
     <definedName name="Кап_ООСМС">Параметры!$B$11</definedName>
+    <definedName name="Кап_СО" localSheetId="7">#REF!</definedName>
+    <definedName name="Кап_СО" localSheetId="10">#REF!</definedName>
+    <definedName name="Кап_СО" localSheetId="9">#REF!</definedName>
+    <definedName name="Кап_СО" localSheetId="8">#REF!</definedName>
+    <definedName name="Кап_СО" localSheetId="12">#REF!</definedName>
+    <definedName name="Кап_СО" localSheetId="11">#REF!</definedName>
     <definedName name="Кап_СО">Параметры!$B$9</definedName>
+    <definedName name="Коммун_мес" localSheetId="7">#REF!</definedName>
+    <definedName name="Коммун_мес" localSheetId="10">#REF!</definedName>
+    <definedName name="Коммун_мес" localSheetId="9">#REF!</definedName>
+    <definedName name="Коммун_мес" localSheetId="8">#REF!</definedName>
+    <definedName name="Коммун_мес" localSheetId="12">#REF!</definedName>
+    <definedName name="Коммун_мес" localSheetId="11">#REF!</definedName>
     <definedName name="Коммун_мес">Параметры!$B$44</definedName>
+    <definedName name="Курс" localSheetId="7">#REF!</definedName>
+    <definedName name="Курс" localSheetId="10">#REF!</definedName>
+    <definedName name="Курс" localSheetId="9">#REF!</definedName>
+    <definedName name="Курс" localSheetId="8">#REF!</definedName>
+    <definedName name="Курс" localSheetId="12">#REF!</definedName>
+    <definedName name="Курс" localSheetId="11">#REF!</definedName>
     <definedName name="Курс">Параметры!$B$16</definedName>
+    <definedName name="Мес_2026_новые" localSheetId="7">#REF!</definedName>
+    <definedName name="Мес_2026_новые" localSheetId="10">#REF!</definedName>
+    <definedName name="Мес_2026_новые" localSheetId="9">#REF!</definedName>
+    <definedName name="Мес_2026_новые" localSheetId="8">#REF!</definedName>
+    <definedName name="Мес_2026_новые" localSheetId="12">#REF!</definedName>
+    <definedName name="Мес_2026_новые" localSheetId="11">#REF!</definedName>
     <definedName name="Мес_2026_новые">Параметры!$B$52</definedName>
+    <definedName name="МЗП" localSheetId="7">#REF!</definedName>
+    <definedName name="МЗП" localSheetId="10">#REF!</definedName>
+    <definedName name="МЗП" localSheetId="9">#REF!</definedName>
+    <definedName name="МЗП" localSheetId="8">#REF!</definedName>
+    <definedName name="МЗП" localSheetId="12">#REF!</definedName>
+    <definedName name="МЗП" localSheetId="11">#REF!</definedName>
     <definedName name="МЗП">Параметры!$B$4</definedName>
+    <definedName name="МРП" localSheetId="7">#REF!</definedName>
+    <definedName name="МРП" localSheetId="10">#REF!</definedName>
+    <definedName name="МРП" localSheetId="9">#REF!</definedName>
+    <definedName name="МРП" localSheetId="8">#REF!</definedName>
+    <definedName name="МРП" localSheetId="12">#REF!</definedName>
+    <definedName name="МРП" localSheetId="11">#REF!</definedName>
     <definedName name="МРП">Параметры!$B$5</definedName>
+    <definedName name="НДС" localSheetId="7">#REF!</definedName>
+    <definedName name="НДС" localSheetId="10">#REF!</definedName>
+    <definedName name="НДС" localSheetId="9">#REF!</definedName>
+    <definedName name="НДС" localSheetId="8">#REF!</definedName>
+    <definedName name="НДС" localSheetId="12">#REF!</definedName>
+    <definedName name="НДС" localSheetId="11">#REF!</definedName>
     <definedName name="НДС">Параметры!$B$35</definedName>
+    <definedName name="Ночей_межд" localSheetId="7">#REF!</definedName>
+    <definedName name="Ночей_межд" localSheetId="10">#REF!</definedName>
+    <definedName name="Ночей_межд" localSheetId="9">#REF!</definedName>
+    <definedName name="Ночей_межд" localSheetId="8">#REF!</definedName>
+    <definedName name="Ночей_межд" localSheetId="12">#REF!</definedName>
+    <definedName name="Ночей_межд" localSheetId="11">#REF!</definedName>
     <definedName name="Ночей_межд">Параметры!$B$29</definedName>
+    <definedName name="Ночей_РК" localSheetId="7">#REF!</definedName>
+    <definedName name="Ночей_РК" localSheetId="10">#REF!</definedName>
+    <definedName name="Ночей_РК" localSheetId="9">#REF!</definedName>
+    <definedName name="Ночей_РК" localSheetId="8">#REF!</definedName>
+    <definedName name="Ночей_РК" localSheetId="12">#REF!</definedName>
+    <definedName name="Ночей_РК" localSheetId="11">#REF!</definedName>
     <definedName name="Ночей_РК">Параметры!$B$22</definedName>
+    <definedName name="ОСНС" localSheetId="7">#REF!</definedName>
+    <definedName name="ОСНС" localSheetId="10">#REF!</definedName>
+    <definedName name="ОСНС" localSheetId="9">#REF!</definedName>
+    <definedName name="ОСНС" localSheetId="8">#REF!</definedName>
+    <definedName name="ОСНС" localSheetId="12">#REF!</definedName>
+    <definedName name="ОСНС" localSheetId="11">#REF!</definedName>
     <definedName name="ОСНС">Параметры!$B$14</definedName>
+    <definedName name="ОСНС_полис" localSheetId="7">#REF!</definedName>
+    <definedName name="ОСНС_полис" localSheetId="10">#REF!</definedName>
+    <definedName name="ОСНС_полис" localSheetId="9">#REF!</definedName>
+    <definedName name="ОСНС_полис" localSheetId="8">#REF!</definedName>
+    <definedName name="ОСНС_полис" localSheetId="12">#REF!</definedName>
+    <definedName name="ОСНС_полис" localSheetId="11">#REF!</definedName>
     <definedName name="ОСНС_полис">Параметры!$B$15</definedName>
+    <definedName name="Отель_межд" localSheetId="7">#REF!</definedName>
+    <definedName name="Отель_межд" localSheetId="10">#REF!</definedName>
+    <definedName name="Отель_межд" localSheetId="9">#REF!</definedName>
+    <definedName name="Отель_межд" localSheetId="8">#REF!</definedName>
+    <definedName name="Отель_межд" localSheetId="12">#REF!</definedName>
+    <definedName name="Отель_межд" localSheetId="11">#REF!</definedName>
     <definedName name="Отель_межд">Параметры!$B$26</definedName>
+    <definedName name="Отель_РК" localSheetId="7">#REF!</definedName>
+    <definedName name="Отель_РК" localSheetId="10">#REF!</definedName>
+    <definedName name="Отель_РК" localSheetId="9">#REF!</definedName>
+    <definedName name="Отель_РК" localSheetId="8">#REF!</definedName>
+    <definedName name="Отель_РК" localSheetId="12">#REF!</definedName>
+    <definedName name="Отель_РК" localSheetId="11">#REF!</definedName>
     <definedName name="Отель_РК">Параметры!$B$19</definedName>
+    <definedName name="Парковка_мест" localSheetId="7">#REF!</definedName>
+    <definedName name="Парковка_мест" localSheetId="10">#REF!</definedName>
+    <definedName name="Парковка_мест" localSheetId="9">#REF!</definedName>
+    <definedName name="Парковка_мест" localSheetId="8">#REF!</definedName>
+    <definedName name="Парковка_мест" localSheetId="12">#REF!</definedName>
+    <definedName name="Парковка_мест" localSheetId="11">#REF!</definedName>
     <definedName name="Парковка_мест">Параметры!$B$45</definedName>
+    <definedName name="Парковка_цена" localSheetId="7">#REF!</definedName>
+    <definedName name="Парковка_цена" localSheetId="10">#REF!</definedName>
+    <definedName name="Парковка_цена" localSheetId="9">#REF!</definedName>
+    <definedName name="Парковка_цена" localSheetId="8">#REF!</definedName>
+    <definedName name="Парковка_цена" localSheetId="12">#REF!</definedName>
+    <definedName name="Парковка_цена" localSheetId="11">#REF!</definedName>
     <definedName name="Парковка_цена">Параметры!$B$46</definedName>
+    <definedName name="Площадь_офиса" localSheetId="7">#REF!</definedName>
+    <definedName name="Площадь_офиса" localSheetId="10">#REF!</definedName>
+    <definedName name="Площадь_офиса" localSheetId="9">#REF!</definedName>
+    <definedName name="Площадь_офиса" localSheetId="8">#REF!</definedName>
+    <definedName name="Площадь_офиса" localSheetId="12">#REF!</definedName>
+    <definedName name="Площадь_офиса" localSheetId="11">#REF!</definedName>
     <definedName name="Площадь_офиса">Параметры!$B$42</definedName>
+    <definedName name="Поездка_межд" localSheetId="7">#REF!</definedName>
+    <definedName name="Поездка_межд" localSheetId="10">#REF!</definedName>
+    <definedName name="Поездка_межд" localSheetId="9">#REF!</definedName>
+    <definedName name="Поездка_межд" localSheetId="8">#REF!</definedName>
+    <definedName name="Поездка_межд" localSheetId="12">#REF!</definedName>
+    <definedName name="Поездка_межд" localSheetId="11">#REF!</definedName>
     <definedName name="Поездка_межд">Параметры!$B$31</definedName>
+    <definedName name="Поездка_местн" localSheetId="7">#REF!</definedName>
+    <definedName name="Поездка_местн" localSheetId="10">#REF!</definedName>
+    <definedName name="Поездка_местн" localSheetId="9">#REF!</definedName>
+    <definedName name="Поездка_местн" localSheetId="8">#REF!</definedName>
+    <definedName name="Поездка_местн" localSheetId="12">#REF!</definedName>
+    <definedName name="Поездка_местн" localSheetId="11">#REF!</definedName>
     <definedName name="Поездка_местн">Параметры!$B$24</definedName>
+    <definedName name="Поездка_РК" localSheetId="7">#REF!</definedName>
+    <definedName name="Поездка_РК" localSheetId="10">#REF!</definedName>
+    <definedName name="Поездка_РК" localSheetId="9">#REF!</definedName>
+    <definedName name="Поездка_РК" localSheetId="8">#REF!</definedName>
+    <definedName name="Поездка_РК" localSheetId="12">#REF!</definedName>
+    <definedName name="Поездка_РК" localSheetId="11">#REF!</definedName>
     <definedName name="Поездка_РК">Параметры!$B$23</definedName>
+    <definedName name="Резерв" localSheetId="7">#REF!</definedName>
+    <definedName name="Резерв" localSheetId="10">#REF!</definedName>
+    <definedName name="Резерв" localSheetId="9">#REF!</definedName>
+    <definedName name="Резерв" localSheetId="8">#REF!</definedName>
+    <definedName name="Резерв" localSheetId="12">#REF!</definedName>
+    <definedName name="Резерв" localSheetId="11">#REF!</definedName>
     <definedName name="Резерв">Параметры!$B$34</definedName>
+    <definedName name="Сборка_мебели_проц" localSheetId="7">#REF!</definedName>
+    <definedName name="Сборка_мебели_проц" localSheetId="10">#REF!</definedName>
+    <definedName name="Сборка_мебели_проц" localSheetId="9">#REF!</definedName>
+    <definedName name="Сборка_мебели_проц" localSheetId="8">#REF!</definedName>
+    <definedName name="Сборка_мебели_проц" localSheetId="12">#REF!</definedName>
+    <definedName name="Сборка_мебели_проц" localSheetId="11">#REF!</definedName>
     <definedName name="Сборка_мебели_проц">Параметры!$B$51</definedName>
+    <definedName name="Ставка_аренды_м2" localSheetId="7">#REF!</definedName>
+    <definedName name="Ставка_аренды_м2" localSheetId="10">#REF!</definedName>
+    <definedName name="Ставка_аренды_м2" localSheetId="9">#REF!</definedName>
+    <definedName name="Ставка_аренды_м2" localSheetId="8">#REF!</definedName>
+    <definedName name="Ставка_аренды_м2" localSheetId="12">#REF!</definedName>
+    <definedName name="Ставка_аренды_м2" localSheetId="11">#REF!</definedName>
     <definedName name="Ставка_аренды_м2">Параметры!$B$43</definedName>
+    <definedName name="Ставка_ВОСМС" localSheetId="7">#REF!</definedName>
+    <definedName name="Ставка_ВОСМС" localSheetId="10">#REF!</definedName>
+    <definedName name="Ставка_ВОСМС" localSheetId="9">#REF!</definedName>
+    <definedName name="Ставка_ВОСМС" localSheetId="8">#REF!</definedName>
+    <definedName name="Ставка_ВОСМС" localSheetId="12">#REF!</definedName>
+    <definedName name="Ставка_ВОСМС" localSheetId="11">#REF!</definedName>
     <definedName name="Ставка_ВОСМС">Параметры!$B$13</definedName>
+    <definedName name="Ставка_ООСМС" localSheetId="7">#REF!</definedName>
+    <definedName name="Ставка_ООСМС" localSheetId="10">#REF!</definedName>
+    <definedName name="Ставка_ООСМС" localSheetId="9">#REF!</definedName>
+    <definedName name="Ставка_ООСМС" localSheetId="8">#REF!</definedName>
+    <definedName name="Ставка_ООСМС" localSheetId="12">#REF!</definedName>
+    <definedName name="Ставка_ООСМС" localSheetId="11">#REF!</definedName>
     <definedName name="Ставка_ООСМС">Параметры!$B$10</definedName>
+    <definedName name="Ставка_ОПВ" localSheetId="7">#REF!</definedName>
+    <definedName name="Ставка_ОПВ" localSheetId="10">#REF!</definedName>
+    <definedName name="Ставка_ОПВ" localSheetId="9">#REF!</definedName>
+    <definedName name="Ставка_ОПВ" localSheetId="8">#REF!</definedName>
+    <definedName name="Ставка_ОПВ" localSheetId="12">#REF!</definedName>
+    <definedName name="Ставка_ОПВ" localSheetId="11">#REF!</definedName>
     <definedName name="Ставка_ОПВ">Параметры!$B$12</definedName>
+    <definedName name="Ставка_ОПВР" localSheetId="7">#REF!</definedName>
+    <definedName name="Ставка_ОПВР" localSheetId="10">#REF!</definedName>
+    <definedName name="Ставка_ОПВР" localSheetId="9">#REF!</definedName>
+    <definedName name="Ставка_ОПВР" localSheetId="8">#REF!</definedName>
+    <definedName name="Ставка_ОПВР" localSheetId="12">#REF!</definedName>
+    <definedName name="Ставка_ОПВР" localSheetId="11">#REF!</definedName>
     <definedName name="Ставка_ОПВР">Параметры!$B$7</definedName>
+    <definedName name="Ставка_СН" localSheetId="7">#REF!</definedName>
+    <definedName name="Ставка_СН" localSheetId="10">#REF!</definedName>
+    <definedName name="Ставка_СН" localSheetId="9">#REF!</definedName>
+    <definedName name="Ставка_СН" localSheetId="8">#REF!</definedName>
+    <definedName name="Ставка_СН" localSheetId="12">#REF!</definedName>
+    <definedName name="Ставка_СН" localSheetId="11">#REF!</definedName>
     <definedName name="Ставка_СН">Параметры!$B$6</definedName>
+    <definedName name="Ставка_СО" localSheetId="7">#REF!</definedName>
+    <definedName name="Ставка_СО" localSheetId="10">#REF!</definedName>
+    <definedName name="Ставка_СО" localSheetId="9">#REF!</definedName>
+    <definedName name="Ставка_СО" localSheetId="8">#REF!</definedName>
+    <definedName name="Ставка_СО" localSheetId="12">#REF!</definedName>
+    <definedName name="Ставка_СО" localSheetId="11">#REF!</definedName>
     <definedName name="Ставка_СО">Параметры!$B$8</definedName>
+    <definedName name="Страх_межд" localSheetId="7">#REF!</definedName>
+    <definedName name="Страх_межд" localSheetId="10">#REF!</definedName>
+    <definedName name="Страх_межд" localSheetId="9">#REF!</definedName>
+    <definedName name="Страх_межд" localSheetId="8">#REF!</definedName>
+    <definedName name="Страх_межд" localSheetId="12">#REF!</definedName>
+    <definedName name="Страх_межд" localSheetId="11">#REF!</definedName>
     <definedName name="Страх_межд">Параметры!$B$30</definedName>
+    <definedName name="Сут_межд" localSheetId="7">#REF!</definedName>
+    <definedName name="Сут_межд" localSheetId="10">#REF!</definedName>
+    <definedName name="Сут_межд" localSheetId="9">#REF!</definedName>
+    <definedName name="Сут_межд" localSheetId="8">#REF!</definedName>
+    <definedName name="Сут_межд" localSheetId="12">#REF!</definedName>
+    <definedName name="Сут_межд" localSheetId="11">#REF!</definedName>
     <definedName name="Сут_межд">Параметры!$B$27</definedName>
+    <definedName name="Сут_РК" localSheetId="7">#REF!</definedName>
+    <definedName name="Сут_РК" localSheetId="10">#REF!</definedName>
+    <definedName name="Сут_РК" localSheetId="9">#REF!</definedName>
+    <definedName name="Сут_РК" localSheetId="8">#REF!</definedName>
+    <definedName name="Сут_РК" localSheetId="12">#REF!</definedName>
+    <definedName name="Сут_РК" localSheetId="11">#REF!</definedName>
     <definedName name="Сут_РК">Параметры!$B$17</definedName>
+    <definedName name="Трансп_РК" localSheetId="7">#REF!</definedName>
+    <definedName name="Трансп_РК" localSheetId="10">#REF!</definedName>
+    <definedName name="Трансп_РК" localSheetId="9">#REF!</definedName>
+    <definedName name="Трансп_РК" localSheetId="8">#REF!</definedName>
+    <definedName name="Трансп_РК" localSheetId="12">#REF!</definedName>
+    <definedName name="Трансп_РК" localSheetId="11">#REF!</definedName>
     <definedName name="Трансп_РК">Параметры!$B$20</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -122,7 +383,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="485">
   <si>
     <t>Статья</t>
   </si>
@@ -856,18 +1117,9 @@
     <t>по ПО</t>
   </si>
   <si>
-    <t>Разработка и техническое сопровождение цифровой платформы</t>
-  </si>
-  <si>
     <t>сумма</t>
   </si>
   <si>
-    <t>Привлечение инфлюенсеров</t>
-  </si>
-  <si>
-    <t>Реализация проекта «TAZA OI»</t>
-  </si>
-  <si>
     <t>Реализация специальных / креативных проектов</t>
   </si>
   <si>
@@ -991,9 +1243,6 @@
     <t>Проекты</t>
   </si>
   <si>
-    <t>Реализация проекта «TAZA TALQY» (проведение встреч в регионах), в т.ч. круглые столы и семинары для акиматов</t>
-  </si>
-  <si>
     <t>Функции</t>
   </si>
   <si>
@@ -1120,12 +1369,6 @@
     <t>Панель – на передвижной стойке у стола совещаний. Kaspi.kz (Астана) на 10.10.2026 – 49 990 ₸ с НДС, в бюджете без НДС (÷1,16): https://kaspi.kz/shop/p/napol-naja-stoika-dlja-televizora-ava-1500-32-75-na-koljosikah-chjornaja-178402637/</t>
   </si>
   <si>
-    <t>Информационное сопровождение, в т.ч. пресс-мероприятия, мобильный брендинг</t>
-  </si>
-  <si>
-    <t>Реализация проектов, в т.ч. с молодёжью и волонтёрами</t>
-  </si>
-  <si>
     <t>Бытовая техника (кулер для воды, холодильник, микроволновка, кофемашина)</t>
   </si>
   <si>
@@ -1418,23 +1661,233 @@
   </si>
   <si>
     <t>Мес. 2026 (поездки – с ноября)</t>
+  </si>
+  <si>
+    <t>Смета расходов по реализации проекта «TAZA TALQY» 
+(в 6 регионах:ноябрь-январь)</t>
+  </si>
+  <si>
+    <t>Статьи затрат</t>
+  </si>
+  <si>
+    <t>Единица измерения</t>
+  </si>
+  <si>
+    <t>Количество</t>
+  </si>
+  <si>
+    <t>Сумма за единицу, тенге</t>
+  </si>
+  <si>
+    <t>Общая сумма, тыс.тенге</t>
+  </si>
+  <si>
+    <t>Всего расходов</t>
+  </si>
+  <si>
+    <t>1.</t>
+  </si>
+  <si>
+    <t>Проезд организаоторов и спикеров (туда и обратно) 4 человек*6 региона</t>
+  </si>
+  <si>
+    <t>человек</t>
+  </si>
+  <si>
+    <t>2.</t>
+  </si>
+  <si>
+    <t>Услуга по проживанию в гостинице 4 человек*8 региона*2 ночь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">услуга </t>
+  </si>
+  <si>
+    <t>3.</t>
+  </si>
+  <si>
+    <t>Услуга по фото и видеосъёмке мероприятия</t>
+  </si>
+  <si>
+    <t>4.</t>
+  </si>
+  <si>
+    <t>Продвижение в соцсетях (привлечение инфлюенсеров)</t>
+  </si>
+  <si>
+    <t>5.</t>
+  </si>
+  <si>
+    <t>Амбассадор-модератор проекта</t>
+  </si>
+  <si>
+    <t>6.</t>
+  </si>
+  <si>
+    <t>Обед/ужин спикеров</t>
+  </si>
+  <si>
+    <t>ИТОГО без НДС</t>
+  </si>
+  <si>
+    <t>Всего расходов с НДС</t>
+  </si>
+  <si>
+    <r>
+      <t>Смета расходов по проведению презентации/старта работы Проектного офиса 
+(Астана, на 100 человек, нояб</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>рь</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Аренда площадки</t>
+  </si>
+  <si>
+    <t>день</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аренда оборудования, ЛЭД, колонки и усилитель (комплект),световое оборудование,кликер, доставка, монтаж, микрофоны,  петличные микрофоны для спикеров </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Видеозапись и фото мероприятия </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Декорации и оформление фотозоны (фотозона размером 3м*6м с установкой, арт-зона с демонтажом и доставкой) </t>
+  </si>
+  <si>
+    <t>услуга</t>
+  </si>
+  <si>
+    <t>Печатная продукция (TAZA KIT: стикерпаки, букмарк, Карточка «5 привычек чистоты» и др.)</t>
+  </si>
+  <si>
+    <t>штук</t>
+  </si>
+  <si>
+    <t>Услуга по организации кофе-брейка (100 участников* 8 500 тг)</t>
+  </si>
+  <si>
+    <t>Фотобудка (3 часа, classic)</t>
+  </si>
+  <si>
+    <t>7.</t>
+  </si>
+  <si>
+    <t>Ведущий</t>
+  </si>
+  <si>
+    <t>Смета расходов по реализации  специальных / креативных проектов (ноябрь-январь)</t>
+  </si>
+  <si>
+    <t>YouTube-проект «Taza niet»</t>
+  </si>
+  <si>
+    <t>выпуск</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Совместный проект с амбассадором ByDastan </t>
+  </si>
+  <si>
+    <t>проект</t>
+  </si>
+  <si>
+    <t>Совместный проект с амбассадором Алия Ашим</t>
+  </si>
+  <si>
+    <t>Информационное сопровождение проектов и деятельности (ноябрь-январь)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продвижение проекта Таза пакет в соцсетях (привлечение инфлюенсеров) </t>
+  </si>
+  <si>
+    <t>Изготовление видеороликов (ИИ ролики, промо, отчетные, интервью/подкаст в студии: съемки, монтаж, продвижение)</t>
+  </si>
+  <si>
+    <t>Изготовление печатной продукции (бомберы, кепки, жилетки и др)</t>
+  </si>
+  <si>
+    <t>Ведение специальных инстаграм/тикток/тредс страниц (3 страницы*3 месяца)</t>
+  </si>
+  <si>
+    <t>Проект "Менің таза әдетім" c UGC блогерами (4 блогера*4 публикаций*2 месяца)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продвижение проекта Taza team в соцсетях (привлечение инфлюенсеров) </t>
+  </si>
+  <si>
+    <t>Изготовление маскота Tazabek (ростовая кукла)</t>
+  </si>
+  <si>
+    <t>Проведение социологического исследования (ноябрь-декабрь)</t>
+  </si>
+  <si>
+    <t>Проведение комплексного социологического исследования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналитическая обработка результатов и подготовка итогового отчёта </t>
+  </si>
+  <si>
+    <t>Разработка цифровой платформы (ноябрь-декабрь)</t>
+  </si>
+  <si>
+    <t>Первый этап разработки цифровой платформы</t>
+  </si>
+  <si>
+    <t>Реализация проекта «TAZA TALQY» (проведение встреч в регионах с жителями, молодежью)</t>
+  </si>
+  <si>
+    <t>Презентация / запуск деятельности Проектного офиса</t>
+  </si>
+  <si>
+    <t>Информационное сопровождение проектов и деятельности</t>
+  </si>
+  <si>
+    <t>Проведение социологического исследования</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.####"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1465,8 +1918,61 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1506,6 +2012,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1549,27 +2061,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1586,7 +2101,7 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1601,20 +2116,20 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1626,28 +2141,122 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 12 2 2" xfId="1"/>
+    <cellStyle name="Обычный 3 2 2 3 2" xfId="3"/>
+    <cellStyle name="Обычный 5 3 2 3" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1728,6 +2337,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Проекты"/>
+      <sheetName val="Taza talqy"/>
+      <sheetName val="Презентация офисе"/>
+      <sheetName val="креативные проекты"/>
+      <sheetName val="Информ сопровождение"/>
+      <sheetName val="Соц исследования"/>
+      <sheetName val="Разработка платформы"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1920,7 +2554,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1933,7 +2567,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E34,"штат",Штат!G5:G34)</f>
@@ -1942,7 +2576,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G36</f>
@@ -1951,7 +2585,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M34,Штат!E5:E34,"штат")</f>
@@ -1960,7 +2594,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -1969,7 +2603,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N35</f>
@@ -1978,7 +2612,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -1987,7 +2621,7 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Оснащение")</f>
@@ -1996,7 +2630,7 @@
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Офис")</f>
@@ -2005,7 +2639,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Цифровые")</f>
@@ -2014,7 +2648,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Медиа")</f>
@@ -2023,7 +2657,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
@@ -2032,7 +2666,7 @@
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Прочие")</f>
@@ -2041,7 +2675,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
@@ -2050,7 +2684,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
@@ -2059,25 +2693,1544 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
-        <v>87404855.379999995</v>
+        <v>87234320</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>251659138.94321719</v>
+        <v>251488603.56321719</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="48"/>
+    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="48" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>462</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+    </row>
+    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>430</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="53"/>
+      <c r="B4" s="50" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55">
+        <f>F8</f>
+        <v>14900000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="53" t="s">
+        <v>433</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>463</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>464</v>
+      </c>
+      <c r="D5" s="57">
+        <v>4</v>
+      </c>
+      <c r="E5" s="58">
+        <v>1100000</v>
+      </c>
+      <c r="F5" s="58">
+        <f>E5*D5</f>
+        <v>4400000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="53" t="s">
+        <v>436</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>465</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>466</v>
+      </c>
+      <c r="D6" s="57">
+        <v>1</v>
+      </c>
+      <c r="E6" s="58">
+        <v>6500000</v>
+      </c>
+      <c r="F6" s="58">
+        <f>E6*D6</f>
+        <v>6500000</v>
+      </c>
+      <c r="G6" s="60"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="53" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>467</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>466</v>
+      </c>
+      <c r="D7" s="57">
+        <v>1</v>
+      </c>
+      <c r="E7" s="58">
+        <v>4000000</v>
+      </c>
+      <c r="F7" s="58">
+        <f>E7*D7</f>
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="53"/>
+      <c r="B8" s="61" t="s">
+        <v>447</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="55">
+        <f>SUM(F5:F7)</f>
+        <v>14900000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="53"/>
+      <c r="B9" s="62" t="s">
+        <v>448</v>
+      </c>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="65">
+        <f>F8*1.16</f>
+        <v>17284000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F14" s="74"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E15" s="75"/>
+      <c r="F15" s="74"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="72"/>
+    </row>
+    <row r="17" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="60"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="H17" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="48"/>
+    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" style="48" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>468</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+    </row>
+    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>430</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="53"/>
+      <c r="B4" s="50" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55">
+        <f>F12</f>
+        <v>20200000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="53" t="s">
+        <v>433</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>469</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="D5" s="57">
+        <v>6</v>
+      </c>
+      <c r="E5" s="58">
+        <v>400000</v>
+      </c>
+      <c r="F5" s="58">
+        <f>E5*D5</f>
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="53" t="s">
+        <v>436</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>470</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>464</v>
+      </c>
+      <c r="D6" s="57">
+        <v>1</v>
+      </c>
+      <c r="E6" s="58">
+        <v>3500000</v>
+      </c>
+      <c r="F6" s="58">
+        <f>E6*D6</f>
+        <v>3500000</v>
+      </c>
+      <c r="G6" s="60"/>
+    </row>
+    <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="53" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>471</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="D7" s="57">
+        <v>1</v>
+      </c>
+      <c r="E7" s="58">
+        <v>1500000</v>
+      </c>
+      <c r="F7" s="58">
+        <f>E7*D7</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="53" t="s">
+        <v>441</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>472</v>
+      </c>
+      <c r="C8" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="D8" s="57">
+        <v>9</v>
+      </c>
+      <c r="E8" s="58">
+        <v>800000</v>
+      </c>
+      <c r="F8" s="58">
+        <f>D8*E8</f>
+        <v>7200000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="53" t="s">
+        <v>443</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>473</v>
+      </c>
+      <c r="C9" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="D9" s="76">
+        <v>32</v>
+      </c>
+      <c r="E9" s="58">
+        <v>100000</v>
+      </c>
+      <c r="F9" s="58">
+        <f>D9*E9</f>
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>474</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="D10" s="57">
+        <v>3</v>
+      </c>
+      <c r="E10" s="58">
+        <v>400000</v>
+      </c>
+      <c r="F10" s="58">
+        <f>E10*D10</f>
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>475</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>457</v>
+      </c>
+      <c r="D11" s="57">
+        <v>3</v>
+      </c>
+      <c r="E11" s="58">
+        <v>400000</v>
+      </c>
+      <c r="F11" s="58">
+        <f>E11*D11</f>
+        <v>1200000</v>
+      </c>
+      <c r="G11" s="75"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="53"/>
+      <c r="B12" s="61" t="s">
+        <v>447</v>
+      </c>
+      <c r="C12" s="51"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="55">
+        <f>SUM(F5:F11)</f>
+        <v>20200000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="53"/>
+      <c r="B13" s="62" t="s">
+        <v>448</v>
+      </c>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="65">
+        <f>F12*1.16</f>
+        <v>23432000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H17" s="72"/>
+    </row>
+    <row r="18" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="60"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="74"/>
+      <c r="H18" s="73"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E19" s="75"/>
+      <c r="F19" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="48"/>
+    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="48" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+    </row>
+    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>430</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="53"/>
+      <c r="B4" s="50" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55">
+        <f>F7</f>
+        <v>11300000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="53" t="s">
+        <v>433</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>477</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="D5" s="57">
+        <v>1</v>
+      </c>
+      <c r="E5" s="58">
+        <v>10000000</v>
+      </c>
+      <c r="F5" s="58">
+        <f>E5*D5</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="53" t="s">
+        <v>436</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>478</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>464</v>
+      </c>
+      <c r="D6" s="57">
+        <v>1</v>
+      </c>
+      <c r="E6" s="58">
+        <v>1300000</v>
+      </c>
+      <c r="F6" s="58">
+        <f>E6*D6</f>
+        <v>1300000</v>
+      </c>
+      <c r="G6" s="60"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="53"/>
+      <c r="B7" s="61" t="s">
+        <v>447</v>
+      </c>
+      <c r="C7" s="51"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="55">
+        <f>F6+F5</f>
+        <v>11300000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="53"/>
+      <c r="B8" s="62" t="s">
+        <v>448</v>
+      </c>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="65">
+        <f>F7*1.16</f>
+        <v>13108000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F13" s="74"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E14" s="75"/>
+      <c r="F14" s="74"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="72"/>
+    </row>
+    <row r="17" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="60"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="H17" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="48"/>
+    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="48" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="48"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>479</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+    </row>
+    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>430</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="53"/>
+      <c r="B4" s="50" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55">
+        <f>F6</f>
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="53" t="s">
+        <v>433</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>480</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="D5" s="57">
+        <v>1</v>
+      </c>
+      <c r="E5" s="58">
+        <v>14000000</v>
+      </c>
+      <c r="F5" s="58">
+        <f>E5*D5</f>
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="53"/>
+      <c r="B6" s="61" t="s">
+        <v>447</v>
+      </c>
+      <c r="C6" s="51"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="55">
+        <f>F5</f>
+        <v>14000000</v>
+      </c>
+      <c r="G6" s="60"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="53"/>
+      <c r="B7" s="62" t="s">
+        <v>448</v>
+      </c>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="65">
+        <f>F6*1.16</f>
+        <v>16239999.999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F12" s="74"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E13" s="75"/>
+      <c r="F13" s="74"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="72"/>
+    </row>
+    <row r="17" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="60"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="H17" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="62.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="48.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3000</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" ref="F5:F10" si="0">D5*E5</f>
+        <v>10500</v>
+      </c>
+      <c r="G5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="5">
+        <v>6500</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
+        <v>1625</v>
+      </c>
+      <c r="G6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="5">
+        <v>6000</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="G7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="5">
+        <v>5000</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="G8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="13">
+        <v>10</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1200</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="G9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="13">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5">
+        <v>900</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>9000</v>
+      </c>
+      <c r="G10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="32"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6">
+        <f>SUM(F5:F10)</f>
+        <v>37375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="45">
+        <v>15</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1500</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" ref="F14:F19" si="1">D14*E14</f>
+        <v>22500</v>
+      </c>
+      <c r="G14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="45">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>8000</v>
+      </c>
+      <c r="F15" s="5">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+      <c r="G15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="45">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="G16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="45">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>6000</v>
+      </c>
+      <c r="F17" s="5">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="45">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5">
+        <v>12000</v>
+      </c>
+      <c r="F18" s="5">
+        <f t="shared" si="1"/>
+        <v>24000</v>
+      </c>
+      <c r="G18" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="45">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
+        <v>8000</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+      <c r="G19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6">
+        <f>SUM(F14:F19)</f>
+        <v>78500</v>
+      </c>
+      <c r="G20" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="69" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="62.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6">
+        <v>5659</v>
+      </c>
+      <c r="D6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1669990</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" ref="G6:G12" si="0">E6*F6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7">
+        <v>2584</v>
+      </c>
+      <c r="D7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>485990</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8">
+        <v>6218</v>
+      </c>
+      <c r="D8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>479990</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9">
+        <v>4240</v>
+      </c>
+      <c r="D9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>104990</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10">
+        <v>6976</v>
+      </c>
+      <c r="D10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>119990</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11">
+        <v>3288</v>
+      </c>
+      <c r="D11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>58990</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12">
+        <v>1756</v>
+      </c>
+      <c r="D12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>31990</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6">
+        <f>SUM(G6:G12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2.1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>240000</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" ref="G16" si="1">E16*F16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6">
+        <f>SUM(G16:G16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>3.3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G20" s="5">
+        <f>E20*F20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>3.4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" s="5">
+        <v>150000</v>
+      </c>
+      <c r="G21" s="5">
+        <f>E21*F21</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6">
+        <f>SUM(G20:G21)</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12">
+        <f>G13+G17+G22</f>
+        <v>300000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -2233,14 +4386,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$34,Штат!$E$5:$E$34,"штат",Штат!$F$5:$F$34,"новая"),-3)</f>
         <v>665000</v>
       </c>
       <c r="C15" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2431,7 +4584,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2469,17 +4622,17 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2491,7 +4644,7 @@
         <v>340.67</v>
       </c>
       <c r="C42" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2502,7 +4655,7 @@
         <v>13500</v>
       </c>
       <c r="C43" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2514,7 +4667,7 @@
         <v>230107.1</v>
       </c>
       <c r="C44" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2525,7 +4678,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2536,7 +4689,7 @@
         <v>40000</v>
       </c>
       <c r="C46" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2599,7 +4752,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -2627,7 +4780,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2659,7 +4812,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -2668,19 +4821,19 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -2689,10 +4842,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>79</v>
@@ -2737,7 +4890,7 @@
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2745,10 +4898,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -2793,7 +4946,7 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2801,10 +4954,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>82</v>
@@ -2849,7 +5002,7 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2860,7 +5013,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -2905,7 +5058,7 @@
         <v>3224340</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -2913,13 +5066,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>80</v>
@@ -2961,7 +5114,7 @@
         <v>3000780</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -2969,13 +5122,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>249</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>252</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>80</v>
@@ -3017,7 +5170,7 @@
         <v>2330100</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3025,16 +5178,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>252</v>
-      </c>
       <c r="E11" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>83</v>
@@ -3073,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3081,13 +5234,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>249</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>252</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>80</v>
@@ -3129,7 +5282,7 @@
         <v>2330100</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -3137,13 +5290,13 @@
         <v>14</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>80</v>
@@ -3185,7 +5338,7 @@
         <v>2553660</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3193,13 +5346,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>80</v>
@@ -3241,7 +5394,7 @@
         <v>2330100</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -3249,13 +5402,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>80</v>
@@ -3297,7 +5450,7 @@
         <v>2330100</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -3305,13 +5458,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>256</v>
-      </c>
       <c r="D16" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>80</v>
@@ -3353,7 +5506,7 @@
         <v>2330100</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3361,13 +5514,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>80</v>
@@ -3409,7 +5562,7 @@
         <v>1182550</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3417,13 +5570,13 @@
         <v>19</v>
       </c>
       <c r="B18" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="C18" s="17" t="s">
-        <v>256</v>
-      </c>
       <c r="D18" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>80</v>
@@ -3465,7 +5618,7 @@
         <v>847210</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3473,13 +5626,13 @@
         <v>19</v>
       </c>
       <c r="B19" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>256</v>
-      </c>
       <c r="D19" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>80</v>
@@ -3521,7 +5674,7 @@
         <v>1659420</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -3529,13 +5682,13 @@
         <v>23</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>80</v>
@@ -3577,7 +5730,7 @@
         <v>3000780</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3585,16 +5738,16 @@
         <v>24</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>83</v>
@@ -3633,7 +5786,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -3641,13 +5794,13 @@
         <v>25</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>80</v>
@@ -3689,7 +5842,7 @@
         <v>3000780</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -3697,10 +5850,10 @@
         <v>26</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>216</v>
@@ -3745,7 +5898,7 @@
         <v>2330100</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -3753,16 +5906,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D24" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>83</v>
@@ -3801,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -3809,16 +5962,16 @@
         <v>28</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>83</v>
@@ -3857,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -3865,10 +6018,10 @@
         <v>29</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>216</v>
@@ -3913,7 +6066,7 @@
         <v>1659420</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -3921,10 +6074,10 @@
         <v>30</v>
       </c>
       <c r="B27" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>259</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>262</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>216</v>
@@ -3969,7 +6122,7 @@
         <v>2330100</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -3977,10 +6130,10 @@
         <v>31</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>216</v>
@@ -4025,7 +6178,7 @@
         <v>1659420</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4033,16 +6186,16 @@
         <v>32</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>216</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>83</v>
@@ -4081,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -4089,7 +6242,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>84</v>
@@ -4137,7 +6290,7 @@
         <v>4784010</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4145,7 +6298,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>85</v>
@@ -4201,13 +6354,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>80</v>
@@ -4249,7 +6402,7 @@
         <v>2777220</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4257,16 +6410,16 @@
         <v>36</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D33" s="21" t="s">
         <v>214</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F33" s="20" t="s">
         <v>83</v>
@@ -4305,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="21" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -4313,16 +6466,16 @@
         <v>37</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D34" s="21" t="s">
         <v>214</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>83</v>
@@ -4361,14 +6514,14 @@
         <v>0</v>
       </c>
       <c r="P34" s="21" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -4404,7 +6557,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="G36">
         <f>SUM(G8:G12)+SUM(G13:G29)</f>
@@ -4417,7 +6570,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="G37">
         <f>G35-G36</f>
@@ -4454,7 +6607,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -4468,19 +6621,19 @@
         <v>69</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -4494,13 +6647,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E4" s="28">
         <v>1000000</v>
@@ -4530,13 +6683,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E5" s="28">
         <v>700000</v>
@@ -4566,13 +6719,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -4602,13 +6755,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -4638,13 +6791,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -4674,13 +6827,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -4710,13 +6863,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -4744,7 +6897,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4788,7 +6941,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4813,7 +6966,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>91</v>
@@ -4893,7 +7046,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")</f>
@@ -4916,7 +7069,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")</f>
@@ -4939,7 +7092,7 @@
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G20:G21)</f>
@@ -4962,7 +7115,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -5022,12 +7175,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5050,7 +7203,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -5082,7 +7235,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I42" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -5112,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -5184,7 +7337,7 @@
         <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -5242,7 +7395,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -5633,7 +7786,7 @@
         <v>98</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C24" t="s">
         <v>100</v>
@@ -5652,7 +7805,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -5664,7 +7817,7 @@
         <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C25" t="s">
         <v>100</v>
@@ -5683,7 +7836,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -5695,7 +7848,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C26" t="s">
         <v>100</v>
@@ -5714,7 +7867,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -5726,7 +7879,7 @@
         <v>98</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C27" t="s">
         <v>100</v>
@@ -5745,7 +7898,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -5757,7 +7910,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C28" t="s">
         <v>100</v>
@@ -5776,7 +7929,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="1">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -5788,7 +7941,7 @@
         <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C29" t="s">
         <v>100</v>
@@ -5807,7 +7960,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -5819,7 +7972,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
@@ -5838,7 +7991,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -5938,7 +8091,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -5957,7 +8110,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -5969,7 +8122,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -5997,7 +8150,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
@@ -6016,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" ref="I36" si="2">IF(F36="разово",IF(G36&lt;=3,D36*E36,0),IF(F36="мес",D36*E36*MAX(0,4-G36),D36*E36*MAX(0,4-G36)/12))</f>
@@ -6028,7 +8181,7 @@
         <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C37" t="s">
         <v>100</v>
@@ -6047,7 +8200,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" ref="I37:I39" si="3">IF(F37="разово",IF(G37&lt;=3,D37*E37,0),IF(F37="мес",D37*E37*MAX(0,4-G37),D37*E37*MAX(0,4-G37)/12))</f>
@@ -6059,7 +8212,7 @@
         <v>98</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C38" t="s">
         <v>104</v>
@@ -6078,7 +8231,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="3"/>
@@ -6090,7 +8243,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -6109,7 +8262,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="3"/>
@@ -6177,7 +8330,7 @@
         <v>98</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C42" t="s">
         <v>100</v>
@@ -6224,7 +8377,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I43" s="5">
         <f>D43*E43*Аренда_мес_2026</f>
@@ -6255,7 +8408,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" ref="I44:I60" si="4">IF(F44="разово",IF(G44&lt;=3,D44*E44,0),IF(F44="мес",D44*E44*MAX(0,4-G44),D44*E44*MAX(0,4-G44)/12))</f>
@@ -6379,7 +8532,7 @@
         <v>118</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C49" t="s">
         <v>120</v>
@@ -6398,7 +8551,7 @@
         <v>2</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="4"/>
@@ -6410,7 +8563,7 @@
         <v>118</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
@@ -6429,7 +8582,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" ref="I50" si="5">IF(F50="разово",IF(G50&lt;=3,D50*E50,0),IF(F50="мес",D50*E50*MAX(0,4-G50),D50*E50*MAX(0,4-G50)/12))</f>
@@ -6487,7 +8640,7 @@
         <v>2</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="I52" s="5">
         <f t="shared" si="4"/>
@@ -6585,10 +8738,10 @@
         <v>136</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C56" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="10"/>
@@ -6662,7 +8815,7 @@
         <v>140</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C59" t="s">
         <v>104</v>
@@ -6690,7 +8843,7 @@
         <v>140</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C60" t="s">
         <v>138</v>
@@ -6739,7 +8892,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6770,13 +8923,13 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>289</v>
+        <v>481</v>
       </c>
       <c r="C5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
@@ -6784,18 +8937,19 @@
         <v>243</v>
       </c>
       <c r="G5" s="5">
-        <v>3600000</v>
+        <f>'Taza talqy'!F12</f>
+        <v>10755520</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>247</v>
+        <v>482</v>
       </c>
       <c r="C6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
@@ -6803,18 +8957,19 @@
         <v>243</v>
       </c>
       <c r="G6" s="5">
-        <v>1200000</v>
+        <f>'Презентация офисе'!F15</f>
+        <v>6414800</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>333</v>
+        <v>245</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
@@ -6822,18 +8977,19 @@
         <v>243</v>
       </c>
       <c r="G7" s="5">
-        <v>6100000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <f>'креативные проекты'!F9</f>
+        <v>17284000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>332</v>
+        <v>483</v>
       </c>
       <c r="C8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
@@ -6841,18 +8997,19 @@
         <v>243</v>
       </c>
       <c r="G8" s="5">
-        <v>18400000</v>
+        <f>'Информ сопровождение'!F13</f>
+        <v>23432000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>246</v>
+        <v>484</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
@@ -6860,18 +9017,19 @@
         <v>243</v>
       </c>
       <c r="G9" s="5">
-        <v>9200000</v>
+        <f>'Соц исследования'!F8</f>
+        <v>13108000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>248</v>
+        <v>480</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
@@ -6879,34 +9037,23 @@
         <v>243</v>
       </c>
       <c r="G10" s="5">
-        <v>30504855.379999999</v>
+        <f>'Разработка платформы'!F7</f>
+        <v>16239999.999999998</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="C11" t="s">
-        <v>245</v>
-      </c>
+      <c r="B11" s="4"/>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="G11" s="5">
-        <v>18400000</v>
-      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -6914,7 +9061,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="6">
         <f>SUM(G5:G11)</f>
-        <v>87404855.379999995</v>
+        <v>87234320</v>
       </c>
     </row>
   </sheetData>
@@ -6925,764 +9072,575 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="62.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="48.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="48"/>
+    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="48" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="13">
-        <v>3.5</v>
-      </c>
-      <c r="E5" s="5">
-        <v>3000</v>
-      </c>
-      <c r="F5" s="5">
-        <f t="shared" ref="F5:F10" si="0">D5*E5</f>
-        <v>10500</v>
-      </c>
-      <c r="G5" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="E6" s="5">
-        <v>6500</v>
-      </c>
-      <c r="F6" s="5">
+    <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>426</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+    </row>
+    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>430</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="53"/>
+      <c r="B4" s="50" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55">
+        <f>F11</f>
+        <v>9272000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="53" t="s">
+        <v>433</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>434</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>435</v>
+      </c>
+      <c r="D5" s="57">
+        <v>56</v>
+      </c>
+      <c r="E5" s="58">
+        <v>30000</v>
+      </c>
+      <c r="F5" s="58">
+        <f t="shared" ref="F5:F10" si="0">E5*D5</f>
+        <v>1680000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="53" t="s">
+        <v>436</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>437</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>438</v>
+      </c>
+      <c r="D6" s="57">
+        <v>56</v>
+      </c>
+      <c r="E6" s="58">
+        <v>25000</v>
+      </c>
+      <c r="F6" s="58">
         <f t="shared" si="0"/>
-        <v>1625</v>
-      </c>
-      <c r="G6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D7" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="5">
-        <v>6000</v>
-      </c>
-      <c r="F7" s="5">
+        <v>1400000</v>
+      </c>
+      <c r="G6" s="60"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="53" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>440</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>438</v>
+      </c>
+      <c r="D7" s="57">
+        <v>6</v>
+      </c>
+      <c r="E7" s="58">
+        <v>100000</v>
+      </c>
+      <c r="F7" s="58">
         <f t="shared" si="0"/>
-        <v>3000</v>
-      </c>
-      <c r="G7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" t="s">
-        <v>194</v>
-      </c>
-      <c r="C8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="E8" s="5">
-        <v>5000</v>
-      </c>
-      <c r="F8" s="5">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="53" t="s">
+        <v>441</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>442</v>
+      </c>
+      <c r="C8" s="57" t="s">
+        <v>438</v>
+      </c>
+      <c r="D8" s="57">
+        <v>6</v>
+      </c>
+      <c r="E8" s="58">
+        <v>400000</v>
+      </c>
+      <c r="F8" s="58">
         <f t="shared" si="0"/>
-        <v>1250</v>
-      </c>
-      <c r="G8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D9" s="13">
-        <v>10</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1200</v>
-      </c>
-      <c r="F9" s="5">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="53" t="s">
+        <v>443</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>444</v>
+      </c>
+      <c r="C9" s="57" t="s">
+        <v>438</v>
+      </c>
+      <c r="D9" s="57">
+        <v>6</v>
+      </c>
+      <c r="E9" s="58">
+        <v>500000</v>
+      </c>
+      <c r="F9" s="58">
         <f t="shared" si="0"/>
-        <v>12000</v>
-      </c>
-      <c r="G9" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B10" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="13">
-        <v>10</v>
-      </c>
-      <c r="E10" s="5">
-        <v>900</v>
-      </c>
-      <c r="F10" s="5">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>446</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>438</v>
+      </c>
+      <c r="D10" s="57">
+        <v>48</v>
+      </c>
+      <c r="E10" s="58">
+        <v>4000</v>
+      </c>
+      <c r="F10" s="58">
         <f t="shared" si="0"/>
-        <v>9000</v>
-      </c>
-      <c r="G10" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6">
+        <v>192000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="53"/>
+      <c r="B11" s="61" t="s">
+        <v>447</v>
+      </c>
+      <c r="C11" s="51"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="55">
         <f>SUM(F5:F10)</f>
-        <v>37375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>196</v>
-      </c>
-      <c r="B14" t="s">
-        <v>200</v>
-      </c>
-      <c r="C14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" s="45">
-        <v>15</v>
-      </c>
-      <c r="E14" s="5">
-        <v>1500</v>
-      </c>
-      <c r="F14" s="5">
-        <f t="shared" ref="F14:F19" si="1">D14*E14</f>
-        <v>22500</v>
-      </c>
-      <c r="G14" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>196</v>
-      </c>
-      <c r="B15" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" s="45">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5">
-        <v>8000</v>
-      </c>
-      <c r="F15" s="5">
-        <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-      <c r="G15" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="45">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F16" s="5">
-        <f t="shared" si="1"/>
-        <v>10000</v>
-      </c>
-      <c r="G16" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>196</v>
-      </c>
-      <c r="B17" t="s">
-        <v>206</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="45">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5">
-        <v>6000</v>
-      </c>
-      <c r="F17" s="5">
-        <f t="shared" si="1"/>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>196</v>
-      </c>
-      <c r="B18" t="s">
-        <v>207</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="45">
-        <v>2</v>
-      </c>
-      <c r="E18" s="5">
-        <v>12000</v>
-      </c>
-      <c r="F18" s="5">
-        <f t="shared" si="1"/>
-        <v>24000</v>
-      </c>
-      <c r="G18" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>196</v>
-      </c>
-      <c r="B19" t="s">
-        <v>209</v>
-      </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="45">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5">
-        <v>8000</v>
-      </c>
-      <c r="F19" s="5">
-        <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-      <c r="G19" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6">
-        <f>SUM(F14:F19)</f>
-        <v>78500</v>
-      </c>
-      <c r="G20" s="7"/>
+        <v>9272000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="53"/>
+      <c r="B12" s="62" t="s">
+        <v>448</v>
+      </c>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="65">
+        <f>F11*1.16</f>
+        <v>10755520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="66"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="68"/>
+      <c r="B15" s="69"/>
+      <c r="F15" s="70"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="71"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="69"/>
+      <c r="F17" s="70"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H18" s="72"/>
+    </row>
+    <row r="19" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="60"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="H19" s="73"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F22" s="74"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E23" s="75"/>
+      <c r="F23" s="74"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:L1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="69" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="62.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="48"/>
+    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="48" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+    </row>
+    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6">
-        <v>5659</v>
-      </c>
-      <c r="D6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1669990</v>
-      </c>
-      <c r="G6" s="5">
-        <f t="shared" ref="G6:G12" si="0">E6*F6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7">
-        <v>2584</v>
-      </c>
-      <c r="D7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <v>485990</v>
-      </c>
-      <c r="G7" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="B3" s="50" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" s="52" t="s">
+        <v>430</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="53"/>
+      <c r="B4" s="50" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55">
+        <f>F14</f>
+        <v>5530000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="53" t="s">
+        <v>433</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>450</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>451</v>
+      </c>
+      <c r="D5" s="57">
+        <v>1</v>
+      </c>
+      <c r="E5" s="58">
+        <v>500000</v>
+      </c>
+      <c r="F5" s="58">
+        <f>E5*D5</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="53" t="s">
+        <v>436</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>452</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>451</v>
+      </c>
+      <c r="D6" s="57">
+        <v>1</v>
+      </c>
+      <c r="E6" s="58">
+        <v>1500000</v>
+      </c>
+      <c r="F6" s="58">
+        <f>E6*D6</f>
+        <v>1500000</v>
+      </c>
+      <c r="G6" s="60"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="53" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>453</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>451</v>
+      </c>
+      <c r="D7" s="57">
+        <v>1</v>
+      </c>
+      <c r="E7" s="58">
+        <v>100000</v>
+      </c>
+      <c r="F7" s="58">
+        <f>E7*D7</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="53" t="s">
+        <v>441</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>454</v>
+      </c>
+      <c r="C8" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="D8" s="57">
+        <v>1</v>
+      </c>
+      <c r="E8" s="58">
+        <v>500000</v>
+      </c>
+      <c r="F8" s="58">
+        <f>D8*E8</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="53" t="s">
+        <v>443</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>456</v>
+      </c>
+      <c r="C9" s="57" t="s">
+        <v>457</v>
+      </c>
+      <c r="D9" s="76">
+        <v>100</v>
+      </c>
+      <c r="E9" s="58">
+        <v>3000</v>
+      </c>
+      <c r="F9" s="58">
+        <f>D9*E9</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>458</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>457</v>
+      </c>
+      <c r="D10" s="76">
+        <v>100</v>
+      </c>
+      <c r="E10" s="58">
+        <v>7000</v>
+      </c>
+      <c r="F10" s="58">
+        <f>D10*E10</f>
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="53"/>
+      <c r="B11" s="59" t="s">
+        <v>459</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>457</v>
+      </c>
+      <c r="D11" s="76">
+        <v>1</v>
+      </c>
+      <c r="E11" s="58">
+        <v>130000</v>
+      </c>
+      <c r="F11" s="58">
+        <f>D11*E11</f>
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>442</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="D12" s="57">
         <v>4</v>
       </c>
-      <c r="B8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8">
-        <v>6218</v>
-      </c>
-      <c r="D8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
-        <v>479990</v>
-      </c>
-      <c r="G8" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9">
-        <v>4240</v>
-      </c>
-      <c r="D9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
-        <v>104990</v>
-      </c>
-      <c r="G9" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10">
-        <v>6976</v>
-      </c>
-      <c r="D10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
-        <v>119990</v>
-      </c>
-      <c r="G10" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11">
-        <v>3288</v>
-      </c>
-      <c r="D11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
-        <v>58990</v>
-      </c>
-      <c r="G11" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12">
-        <v>1756</v>
-      </c>
-      <c r="D12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
-        <v>31990</v>
-      </c>
-      <c r="G12" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6">
-        <f>SUM(G6:G12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2.1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D16" t="s">
-        <v>159</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5">
-        <v>240000</v>
-      </c>
-      <c r="G16" s="5">
-        <f t="shared" ref="G16" si="1">E16*F16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6">
-        <f>SUM(G16:G16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>3.3</v>
-      </c>
-      <c r="B20" t="s">
-        <v>162</v>
-      </c>
-      <c r="D20" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G20" s="5">
-        <f>E20*F20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>3.4</v>
-      </c>
-      <c r="B21" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21" s="5">
-        <v>150000</v>
-      </c>
-      <c r="G21" s="5">
-        <f>E21*F21</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6">
-        <f>SUM(G20:G21)</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12">
-        <f>G13+G17+G22</f>
-        <v>300000</v>
-      </c>
+      <c r="E12" s="58">
+        <v>400000</v>
+      </c>
+      <c r="F12" s="58">
+        <f>D12*E12</f>
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="B13" s="77" t="s">
+        <v>461</v>
+      </c>
+      <c r="C13" s="78" t="s">
+        <v>435</v>
+      </c>
+      <c r="D13" s="78">
+        <v>1</v>
+      </c>
+      <c r="E13" s="79">
+        <v>200000</v>
+      </c>
+      <c r="F13" s="80">
+        <f>E13*D13</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="53"/>
+      <c r="B14" s="61" t="s">
+        <v>447</v>
+      </c>
+      <c r="C14" s="51"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="55">
+        <f>SUM(F5:F13)</f>
+        <v>5530000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="53"/>
+      <c r="B15" s="62" t="s">
+        <v>448</v>
+      </c>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="65">
+        <f>F14*1.16</f>
+        <v>6414800</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="72"/>
+    </row>
+    <row r="17" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="60"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="H17" s="73"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F20" s="74"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E21" s="75"/>
+      <c r="F21" s="74"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -28,9 +28,6 @@
     <sheet name="Канцелярия" sheetId="7" r:id="rId14"/>
     <sheet name="Смета фото-видео" sheetId="6" r:id="rId15"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId16"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Авиа_межд" localSheetId="7">#REF!</definedName>
     <definedName name="Авиа_межд" localSheetId="10">#REF!</definedName>
@@ -1255,15 +1252,9 @@
     <t>В мес. с НДС</t>
   </si>
   <si>
-    <t>Юрист (МФЦА)</t>
-  </si>
-  <si>
     <t>Договоры и соглашения, право МФЦА, сопровождение закупок и кадровых документов</t>
   </si>
   <si>
-    <t>Администратор (сис.админ)</t>
-  </si>
-  <si>
     <t>ИТ-инфраструктура, сеть и техника; делопроизводство, хоз. администрирование, ассистирование</t>
   </si>
   <si>
@@ -1531,9 +1522,6 @@
     <t>[Темирбеков М.Е.] Наём, закупки, офис, договоры с поставщиками. Опыт: международные экономические отношения (диплом с отличием); акиматы Костанайской области и Астаны; руководитель аппарата холдинга (3 000+ сотрудников); проекты МЗ РК и Всемирного банка; руководитель в общественных организациях, структур в квазигоссекторе; в ЦАКФ с 02.2025, член Управляющего совета.</t>
   </si>
   <si>
-    <t>Заместитель ГИД по стратегии и проектам</t>
-  </si>
-  <si>
     <t>Проектный офис для Центральной Азии по изменению климата и зеленой энергетике</t>
   </si>
   <si>
@@ -1541,9 +1529,6 @@
   </si>
   <si>
     <t>Руководителю Проектного офиса для Центральной Азии</t>
-  </si>
-  <si>
-    <t>[Кононец А.В.] Стратегия и портфель проектов Фонда, партнёрства; Проектный офис для Центральной Азии; курация проектного управления. Опыт: 20 лет в медиа и госкоммуникациях – руководитель пресс-службы, советник министра труда и социальной защиты, главный редактор Казправды, Total.kz и др.; в ЦАКФ с 07.2025.</t>
   </si>
   <si>
     <t>Руководитель проектного офиса «Таза Қазақстан»</t>
@@ -1862,6 +1847,18 @@
   </si>
   <si>
     <t>Проведение социологического исследования</t>
+  </si>
+  <si>
+    <t>Советник ГИД по стратегии и науке</t>
+  </si>
+  <si>
+    <t>[Кононец А.В.] Стратегия и научное направление Фонда, аналитические и экспертные материалы, международные партнёры; поручения ГИД. Опыт: 20 лет в медиа и госкоммуникациях – руководитель пресс-службы, советник министра труда и социальной защиты, главный редактор Казправды, Total.kz и др.; в ЦАКФ с 07.2025.</t>
+  </si>
+  <si>
+    <t>Юрист (МФЦА), на руки 700 000</t>
+  </si>
+  <si>
+    <t>Администратор (сис.админ), на руки 350 000</t>
   </si>
 </sst>
 </file>
@@ -2160,10 +2157,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2251,6 +2244,10 @@
     <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2337,31 +2334,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Проекты"/>
-      <sheetName val="Taza talqy"/>
-      <sheetName val="Презентация офисе"/>
-      <sheetName val="креативные проекты"/>
-      <sheetName val="Информ сопровождение"/>
-      <sheetName val="Соц исследования"/>
-      <sheetName val="Разработка платформы"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2554,7 +2526,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2567,16 +2539,16 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E34,"штат",Штат!G5:G34)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G36</f>
@@ -2585,34 +2557,34 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M34,Штат!E5:E34,"штат")</f>
-        <v>61677420</v>
+        <v>58935200</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
-        <v>13456000</v>
+        <v>12098200</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N35</f>
-        <v>665000</v>
+        <v>623368.42105263157</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -2621,7 +2593,7 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Оснащение")</f>
@@ -2630,7 +2602,7 @@
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Офис")</f>
@@ -2639,7 +2611,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Цифровые")</f>
@@ -2648,7 +2620,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Медиа")</f>
@@ -2657,20 +2629,20 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>128665321.4967742</v>
+        <v>124523669.91782683</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Прочие")</f>
-        <v>12933198.816344086</v>
+        <v>12519033.65844935</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2679,21 +2651,21 @@
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>22655763.250098925</v>
+        <v>21926832.572204191</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>164254283.56321719</v>
+        <v>158969536.14848039</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
@@ -2702,11 +2674,11 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>251488603.56321719</v>
+        <v>246203856.14848039</v>
       </c>
     </row>
   </sheetData>
@@ -2720,174 +2692,174 @@
   <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
-    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="48"/>
-    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="48" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="48"/>
+    <col min="1" max="1" width="5.28515625" style="58" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="46" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="46"/>
+    <col min="5" max="5" width="12.42578125" style="46" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="46" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="46" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>462</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="A1" s="79" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="48" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>425</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>426</v>
+      </c>
+      <c r="F3" s="50" t="s">
         <v>427</v>
       </c>
-      <c r="C3" s="51" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="48" t="s">
         <v>428</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>429</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="53"/>
-      <c r="B4" s="50" t="s">
-        <v>432</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55">
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53">
         <f>F8</f>
         <v>14900000</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="53" t="s">
-        <v>433</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>463</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>464</v>
-      </c>
-      <c r="D5" s="57">
+      <c r="A5" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>459</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>460</v>
+      </c>
+      <c r="D5" s="55">
         <v>4</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="56">
         <v>1100000</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="56">
         <f>E5*D5</f>
         <v>4400000</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>465</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>466</v>
-      </c>
-      <c r="D6" s="57">
-        <v>1</v>
-      </c>
-      <c r="E6" s="58">
+      <c r="A6" s="51" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>461</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>462</v>
+      </c>
+      <c r="D6" s="55">
+        <v>1</v>
+      </c>
+      <c r="E6" s="56">
         <v>6500000</v>
       </c>
-      <c r="F6" s="58">
+      <c r="F6" s="56">
         <f>E6*D6</f>
         <v>6500000</v>
       </c>
-      <c r="G6" s="60"/>
+      <c r="G6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
-        <v>439</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>467</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>466</v>
-      </c>
-      <c r="D7" s="57">
-        <v>1</v>
-      </c>
-      <c r="E7" s="58">
+      <c r="A7" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>463</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>462</v>
+      </c>
+      <c r="D7" s="55">
+        <v>1</v>
+      </c>
+      <c r="E7" s="56">
         <v>4000000</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="56">
         <f>E7*D7</f>
         <v>4000000</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="53"/>
-      <c r="B8" s="61" t="s">
-        <v>447</v>
-      </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="55">
+      <c r="A8" s="51"/>
+      <c r="B8" s="59" t="s">
+        <v>443</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="53">
         <f>SUM(F5:F7)</f>
         <v>14900000</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="53"/>
-      <c r="B9" s="62" t="s">
-        <v>448</v>
-      </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="65">
+      <c r="A9" s="51"/>
+      <c r="B9" s="60" t="s">
+        <v>444</v>
+      </c>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="63">
         <f>F8*1.16</f>
         <v>17284000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F14" s="74"/>
+      <c r="F14" s="72"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E15" s="75"/>
-      <c r="F15" s="74"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="72"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H16" s="72"/>
-    </row>
-    <row r="17" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="H17" s="73"/>
+      <c r="H16" s="70"/>
+    </row>
+    <row r="17" spans="1:8" s="65" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="58"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="H17" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2904,256 +2876,256 @@
   <dimension ref="A1:L19"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
-    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="48"/>
-    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" style="48" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="48"/>
+    <col min="1" max="1" width="5.28515625" style="58" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="46" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="46"/>
+    <col min="5" max="5" width="12.42578125" style="46" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="46" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" style="46" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>468</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="A1" s="79" t="s">
+        <v>464</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="48" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>425</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>426</v>
+      </c>
+      <c r="F3" s="50" t="s">
         <v>427</v>
       </c>
-      <c r="C3" s="51" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="48" t="s">
         <v>428</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>429</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="53"/>
-      <c r="B4" s="50" t="s">
-        <v>432</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55">
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53">
         <f>F12</f>
         <v>20200000</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="53" t="s">
-        <v>433</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>469</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="D5" s="57">
+      <c r="A5" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>465</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="D5" s="55">
         <v>6</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="56">
         <v>400000</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="56">
         <f>E5*D5</f>
         <v>2400000</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>470</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>464</v>
-      </c>
-      <c r="D6" s="57">
-        <v>1</v>
-      </c>
-      <c r="E6" s="58">
+      <c r="A6" s="51" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>466</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>460</v>
+      </c>
+      <c r="D6" s="55">
+        <v>1</v>
+      </c>
+      <c r="E6" s="56">
         <v>3500000</v>
       </c>
-      <c r="F6" s="58">
+      <c r="F6" s="56">
         <f>E6*D6</f>
         <v>3500000</v>
       </c>
-      <c r="G6" s="60"/>
+      <c r="G6" s="58"/>
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
-        <v>439</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>471</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="D7" s="57">
-        <v>1</v>
-      </c>
-      <c r="E7" s="58">
+      <c r="A7" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>467</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="D7" s="55">
+        <v>1</v>
+      </c>
+      <c r="E7" s="56">
         <v>1500000</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="56">
         <f>E7*D7</f>
         <v>1500000</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
-        <v>441</v>
-      </c>
-      <c r="B8" s="59" t="s">
-        <v>472</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="D8" s="57">
+      <c r="A8" s="51" t="s">
+        <v>437</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>468</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="D8" s="55">
         <v>9</v>
       </c>
-      <c r="E8" s="58">
+      <c r="E8" s="56">
         <v>800000</v>
       </c>
-      <c r="F8" s="58">
+      <c r="F8" s="56">
         <f>D8*E8</f>
         <v>7200000</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="53" t="s">
-        <v>443</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>473</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="D9" s="76">
+      <c r="A9" s="51" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>469</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="D9" s="74">
         <v>32</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="56">
         <v>100000</v>
       </c>
-      <c r="F9" s="58">
+      <c r="F9" s="56">
         <f>D9*E9</f>
         <v>3200000</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="53" t="s">
-        <v>445</v>
-      </c>
-      <c r="B10" s="59" t="s">
-        <v>474</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="D10" s="57">
+      <c r="A10" s="51" t="s">
+        <v>441</v>
+      </c>
+      <c r="B10" s="57" t="s">
+        <v>470</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="D10" s="55">
         <v>3</v>
       </c>
-      <c r="E10" s="58">
+      <c r="E10" s="56">
         <v>400000</v>
       </c>
-      <c r="F10" s="58">
+      <c r="F10" s="56">
         <f>E10*D10</f>
         <v>1200000</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="53" t="s">
-        <v>460</v>
-      </c>
-      <c r="B11" s="59" t="s">
-        <v>475</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>457</v>
-      </c>
-      <c r="D11" s="57">
+      <c r="A11" s="51" t="s">
+        <v>456</v>
+      </c>
+      <c r="B11" s="57" t="s">
+        <v>471</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>453</v>
+      </c>
+      <c r="D11" s="55">
         <v>3</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="56">
         <v>400000</v>
       </c>
-      <c r="F11" s="58">
+      <c r="F11" s="56">
         <f>E11*D11</f>
         <v>1200000</v>
       </c>
-      <c r="G11" s="75"/>
+      <c r="G11" s="73"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="53"/>
-      <c r="B12" s="61" t="s">
-        <v>447</v>
-      </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="55">
+      <c r="A12" s="51"/>
+      <c r="B12" s="59" t="s">
+        <v>443</v>
+      </c>
+      <c r="C12" s="49"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="53">
         <f>SUM(F5:F11)</f>
         <v>20200000</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="53"/>
-      <c r="B13" s="62" t="s">
-        <v>448</v>
-      </c>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="65">
+      <c r="A13" s="51"/>
+      <c r="B13" s="60" t="s">
+        <v>444</v>
+      </c>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="63">
         <f>F12*1.16</f>
         <v>23432000</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H17" s="72"/>
-    </row>
-    <row r="18" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="60"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="74"/>
-      <c r="H18" s="73"/>
+      <c r="H17" s="70"/>
+    </row>
+    <row r="18" spans="1:8" s="65" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="58"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="72"/>
+      <c r="H18" s="71"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E19" s="75"/>
-      <c r="F19" s="74"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3170,153 +3142,153 @@
   <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
-    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="48"/>
-    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="48" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="48"/>
+    <col min="1" max="1" width="5.28515625" style="58" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="46" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="46"/>
+    <col min="5" max="5" width="12.42578125" style="46" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="46" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="46" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>476</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="A1" s="79" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="48" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>425</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>426</v>
+      </c>
+      <c r="F3" s="50" t="s">
         <v>427</v>
       </c>
-      <c r="C3" s="51" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="48" t="s">
         <v>428</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>429</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="53"/>
-      <c r="B4" s="50" t="s">
-        <v>432</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55">
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53">
         <f>F7</f>
         <v>11300000</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="53" t="s">
-        <v>433</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>477</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="D5" s="57">
-        <v>1</v>
-      </c>
-      <c r="E5" s="58">
+      <c r="A5" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>473</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="D5" s="55">
+        <v>1</v>
+      </c>
+      <c r="E5" s="56">
         <v>10000000</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="56">
         <f>E5*D5</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>478</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>464</v>
-      </c>
-      <c r="D6" s="57">
-        <v>1</v>
-      </c>
-      <c r="E6" s="58">
+      <c r="A6" s="51" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>474</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>460</v>
+      </c>
+      <c r="D6" s="55">
+        <v>1</v>
+      </c>
+      <c r="E6" s="56">
         <v>1300000</v>
       </c>
-      <c r="F6" s="58">
+      <c r="F6" s="56">
         <f>E6*D6</f>
         <v>1300000</v>
       </c>
-      <c r="G6" s="60"/>
+      <c r="G6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="53"/>
-      <c r="B7" s="61" t="s">
-        <v>447</v>
-      </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="55">
+      <c r="A7" s="51"/>
+      <c r="B7" s="59" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="53">
         <f>F6+F5</f>
         <v>11300000</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="53"/>
-      <c r="B8" s="62" t="s">
-        <v>448</v>
-      </c>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="65">
+      <c r="A8" s="51"/>
+      <c r="B8" s="60" t="s">
+        <v>444</v>
+      </c>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="63">
         <f>F7*1.16</f>
         <v>13108000</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F13" s="74"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E14" s="75"/>
-      <c r="F14" s="74"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="72"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H16" s="72"/>
-    </row>
-    <row r="17" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="H17" s="73"/>
+      <c r="H16" s="70"/>
+    </row>
+    <row r="17" spans="1:8" s="65" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="58"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="H17" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3333,132 +3305,132 @@
   <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
-    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="48"/>
-    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="48" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="48"/>
+    <col min="1" max="1" width="5.28515625" style="58" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="46" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="46"/>
+    <col min="5" max="5" width="12.42578125" style="46" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="46" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="46" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>479</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="A1" s="79" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="48" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>425</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>426</v>
+      </c>
+      <c r="F3" s="50" t="s">
         <v>427</v>
       </c>
-      <c r="C3" s="51" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="48" t="s">
         <v>428</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>429</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="53"/>
-      <c r="B4" s="50" t="s">
-        <v>432</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55">
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53">
         <f>F6</f>
         <v>14000000</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="53" t="s">
-        <v>433</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>480</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="D5" s="57">
-        <v>1</v>
-      </c>
-      <c r="E5" s="58">
+      <c r="A5" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>476</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="D5" s="55">
+        <v>1</v>
+      </c>
+      <c r="E5" s="56">
         <v>14000000</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="56">
         <f>E5*D5</f>
         <v>14000000</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="53"/>
-      <c r="B6" s="61" t="s">
-        <v>447</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="55">
+      <c r="A6" s="51"/>
+      <c r="B6" s="59" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="49"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="53">
         <f>F5</f>
         <v>14000000</v>
       </c>
-      <c r="G6" s="60"/>
+      <c r="G6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="53"/>
-      <c r="B7" s="62" t="s">
-        <v>448</v>
-      </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65">
+      <c r="A7" s="51"/>
+      <c r="B7" s="60" t="s">
+        <v>444</v>
+      </c>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="63">
         <f>F6*1.16</f>
         <v>16239999.999999998</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F12" s="74"/>
+      <c r="F12" s="72"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E13" s="75"/>
-      <c r="F13" s="74"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H16" s="72"/>
-    </row>
-    <row r="17" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="H17" s="73"/>
+      <c r="H16" s="70"/>
+    </row>
+    <row r="17" spans="1:8" s="65" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="58"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="H17" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3489,7 +3461,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -3536,7 +3508,7 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3672,7 +3644,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3829,7 +3801,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -4095,7 +4067,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -4386,14 +4358,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$34,Штат!$E$5:$E$34,"штат",Штат!$F$5:$F$34,"новая"),-3)</f>
-        <v>665000</v>
+        <v>658000</v>
       </c>
       <c r="C15" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4584,7 +4556,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4622,17 +4594,17 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -4644,7 +4616,7 @@
         <v>340.67</v>
       </c>
       <c r="C42" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -4655,7 +4627,7 @@
         <v>13500</v>
       </c>
       <c r="C43" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -4667,7 +4639,7 @@
         <v>230107.1</v>
       </c>
       <c r="C44" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -4689,7 +4661,7 @@
         <v>40000</v>
       </c>
       <c r="C46" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -4752,7 +4724,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -4812,7 +4784,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -4821,19 +4793,19 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -4890,7 +4862,7 @@
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -4901,7 +4873,7 @@
         <v>274</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>382</v>
+        <v>481</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -4946,7 +4918,7 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>386</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -5002,7 +4974,7 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -5013,7 +4985,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -5051,14 +5023,14 @@
       </c>
       <c r="N8" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O8" s="18">
         <f t="shared" si="5"/>
-        <v>3224340</v>
+        <v>3223971.5789473685</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5107,14 +5079,14 @@
       </c>
       <c r="N9" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O9" s="18">
         <f t="shared" ref="O9:O11" si="10">M9+N9</f>
-        <v>3000780</v>
+        <v>3000411.5789473685</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5125,7 +5097,7 @@
         <v>246</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>249</v>
@@ -5163,14 +5135,14 @@
       </c>
       <c r="N10" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O10" s="18">
         <f t="shared" si="10"/>
-        <v>2330100</v>
+        <v>2329731.5789473685</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5181,7 +5153,7 @@
         <v>246</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>249</v>
@@ -5226,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5275,14 +5247,14 @@
       </c>
       <c r="N12" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O12" s="18">
         <f t="shared" si="5"/>
-        <v>2330100</v>
+        <v>2329731.5789473685</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5331,11 +5303,11 @@
       </c>
       <c r="N13" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O13" s="18">
         <f t="shared" si="5"/>
-        <v>2553660</v>
+        <v>2553291.5789473685</v>
       </c>
       <c r="P13" s="17" t="s">
         <v>278</v>
@@ -5387,14 +5359,14 @@
       </c>
       <c r="N14" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O14" s="18">
         <f t="shared" si="5"/>
-        <v>2330100</v>
+        <v>2329731.5789473685</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -5443,14 +5415,14 @@
       </c>
       <c r="N15" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O15" s="18">
         <f t="shared" si="5"/>
-        <v>2330100</v>
+        <v>2329731.5789473685</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5499,14 +5471,14 @@
       </c>
       <c r="N16" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O16" s="18">
         <f t="shared" si="5"/>
-        <v>2330100</v>
+        <v>2329731.5789473685</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5555,14 +5527,14 @@
       </c>
       <c r="N17" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O17" s="18">
         <f t="shared" ref="O17:O18" si="18">M17+N17</f>
-        <v>1182550</v>
+        <v>1182181.5789473683</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5611,14 +5583,14 @@
       </c>
       <c r="N18" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O18" s="18">
         <f t="shared" si="18"/>
-        <v>847210</v>
+        <v>846841.57894736843</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5667,14 +5639,14 @@
       </c>
       <c r="N19" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O19" s="18">
         <f t="shared" si="5"/>
-        <v>1659420</v>
+        <v>1659051.5789473683</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -5723,14 +5695,14 @@
       </c>
       <c r="N20" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O20" s="18">
         <f t="shared" si="5"/>
-        <v>3000780</v>
+        <v>3000411.5789473685</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5786,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5835,14 +5807,14 @@
       </c>
       <c r="N22" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O22" s="18">
         <f t="shared" si="5"/>
-        <v>3000780</v>
+        <v>3000411.5789473685</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -5891,14 +5863,14 @@
       </c>
       <c r="N23" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O23" s="18">
         <f t="shared" si="5"/>
-        <v>2330100</v>
+        <v>2329731.5789473685</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -5954,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -6010,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -6021,7 +5993,7 @@
         <v>256</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>216</v>
@@ -6059,14 +6031,14 @@
       </c>
       <c r="N26" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O26" s="18">
         <f t="shared" si="5"/>
-        <v>1659420</v>
+        <v>1659051.5789473683</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -6115,14 +6087,14 @@
       </c>
       <c r="N27" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O27" s="18">
         <f t="shared" si="5"/>
-        <v>2330100</v>
+        <v>2329731.5789473685</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -6171,11 +6143,11 @@
       </c>
       <c r="N28" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O28" s="18">
         <f t="shared" si="5"/>
-        <v>1659420</v>
+        <v>1659051.5789473683</v>
       </c>
       <c r="P28" s="17" t="s">
         <v>261</v>
@@ -6234,7 +6206,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -6290,7 +6262,7 @@
         <v>4784010</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6339,11 +6311,11 @@
       </c>
       <c r="N31" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>34631.57894736842</v>
       </c>
       <c r="O31" s="18">
         <f t="shared" si="5"/>
-        <v>1659420</v>
+        <v>1659051.5789473683</v>
       </c>
       <c r="P31" s="17" t="s">
         <v>213</v>
@@ -6354,13 +6326,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>80</v>
@@ -6369,21 +6341,21 @@
         <v>83</v>
       </c>
       <c r="G32" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="18">
-        <v>1200000</v>
+        <v>1000000</v>
       </c>
       <c r="I32" s="16">
         <v>2</v>
       </c>
       <c r="J32" s="18">
         <f t="shared" si="25"/>
-        <v>171110</v>
+        <v>147550</v>
       </c>
       <c r="K32" s="18">
         <f t="shared" si="26"/>
-        <v>1371110</v>
+        <v>0</v>
       </c>
       <c r="L32" s="19">
         <f t="shared" si="2"/>
@@ -6391,18 +6363,18 @@
       </c>
       <c r="M32" s="18">
         <f t="shared" si="3"/>
-        <v>2742220</v>
+        <v>0</v>
       </c>
       <c r="N32" s="18">
         <f t="shared" si="4"/>
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="O32" s="18">
         <f t="shared" si="5"/>
-        <v>2777220</v>
+        <v>0</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6428,14 +6400,14 @@
         <v>0</v>
       </c>
       <c r="H33" s="22">
-        <v>1000000</v>
+        <v>867500</v>
       </c>
       <c r="I33" s="20">
         <v>2</v>
       </c>
       <c r="J33" s="22">
         <f t="shared" si="25"/>
-        <v>160000</v>
+        <v>138800</v>
       </c>
       <c r="K33" s="22">
         <f t="shared" si="26"/>
@@ -6458,7 +6430,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="21" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6484,14 +6456,14 @@
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>700000</v>
+        <v>425600</v>
       </c>
       <c r="I34" s="20">
         <v>2</v>
       </c>
       <c r="J34" s="22">
         <f t="shared" si="25"/>
-        <v>112000</v>
+        <v>68096</v>
       </c>
       <c r="K34" s="22">
         <f t="shared" si="26"/>
@@ -6514,50 +6486,50 @@
         <v>0</v>
       </c>
       <c r="P34" s="21" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7">
         <f>SUM(G5:G34)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H35" s="6">
         <f>SUMPRODUCT(G5:G34,H5:H34)</f>
-        <v>24900000</v>
+        <v>23700000</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="6"/>
       <c r="K35" s="6">
         <f>SUM(K5:K34)</f>
-        <v>28517470</v>
+        <v>27146360</v>
       </c>
       <c r="L35" s="7"/>
       <c r="M35" s="6">
         <f>SUM(M5:M34)</f>
-        <v>61677420</v>
+        <v>58935200</v>
       </c>
       <c r="N35" s="6">
         <f t="shared" ref="N35:O35" si="27">SUM(N5:N34)</f>
-        <v>665000</v>
+        <v>623368.42105263157</v>
       </c>
       <c r="O35" s="6">
         <f t="shared" si="27"/>
-        <v>62342420</v>
+        <v>59558568.421052605</v>
       </c>
       <c r="P35" s="7"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G36">
         <f>SUM(G8:G12)+SUM(G13:G29)</f>
@@ -6570,15 +6542,15 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G37">
         <f>G35-G36</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H37" s="5">
         <f>H35-H36</f>
-        <v>7700000</v>
+        <v>6500000</v>
       </c>
     </row>
   </sheetData>
@@ -6607,7 +6579,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -6633,7 +6605,7 @@
         <v>289</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -6647,35 +6619,34 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>290</v>
+        <v>483</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E4" s="28">
-        <v>1000000</v>
+        <v>867500</v>
       </c>
       <c r="F4" s="28">
-        <f t="shared" ref="F4:F10" si="0">E4*НДС</f>
-        <v>160000</v>
+        <v>0</v>
       </c>
       <c r="G4" s="28">
-        <f t="shared" ref="G4:G10" si="1">E4+F4</f>
-        <v>1160000</v>
+        <f t="shared" ref="G4:G10" si="0">E4+F4</f>
+        <v>867500</v>
       </c>
       <c r="H4" s="26">
         <v>2</v>
       </c>
       <c r="I4" s="29">
-        <f t="shared" ref="I4:I10" si="2">IF(H4=1,Мес_2026_новые,MAX(0,4-H4))</f>
+        <f t="shared" ref="I4:I10" si="1">IF(H4=1,Мес_2026_новые,MAX(0,4-H4))</f>
         <v>2</v>
       </c>
       <c r="J4" s="28">
-        <f t="shared" ref="J4:J10" si="3">G4*I4</f>
-        <v>2320000</v>
+        <f t="shared" ref="J4:J10" si="2">G4*I4</f>
+        <v>1735000</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -6683,35 +6654,34 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>292</v>
+        <v>484</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>214</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E5" s="28">
-        <v>700000</v>
+        <v>425600</v>
       </c>
       <c r="F5" s="28">
+        <v>0</v>
+      </c>
+      <c r="G5" s="28">
         <f t="shared" si="0"/>
-        <v>112000</v>
-      </c>
-      <c r="G5" s="28">
-        <f t="shared" si="1"/>
-        <v>812000</v>
+        <v>425600</v>
       </c>
       <c r="H5" s="26">
         <v>2</v>
       </c>
       <c r="I5" s="29">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J5" s="28">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="J5" s="28">
-        <f t="shared" si="3"/>
-        <v>1624000</v>
+        <v>851200</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -6719,34 +6689,34 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>294</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>296</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
       </c>
       <c r="F6" s="28">
+        <f t="shared" ref="F4:F10" si="3">E6*НДС</f>
+        <v>160000</v>
+      </c>
+      <c r="G6" s="28">
         <f t="shared" si="0"/>
-        <v>160000</v>
-      </c>
-      <c r="G6" s="28">
-        <f t="shared" si="1"/>
         <v>1160000</v>
       </c>
       <c r="H6" s="26">
         <v>2</v>
       </c>
       <c r="I6" s="29">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J6" s="28">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="J6" s="28">
-        <f t="shared" si="3"/>
         <v>2320000</v>
       </c>
     </row>
@@ -6755,34 +6725,34 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>297</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>299</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
       </c>
       <c r="F7" s="28">
+        <f t="shared" si="3"/>
+        <v>160000</v>
+      </c>
+      <c r="G7" s="28">
         <f t="shared" si="0"/>
-        <v>160000</v>
-      </c>
-      <c r="G7" s="28">
-        <f t="shared" si="1"/>
         <v>1160000</v>
       </c>
       <c r="H7" s="26">
         <v>2</v>
       </c>
       <c r="I7" s="29">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J7" s="28">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="J7" s="28">
-        <f t="shared" si="3"/>
         <v>2320000</v>
       </c>
     </row>
@@ -6791,34 +6761,34 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
       </c>
       <c r="F8" s="28">
+        <f t="shared" si="3"/>
+        <v>112000</v>
+      </c>
+      <c r="G8" s="28">
         <f t="shared" si="0"/>
-        <v>112000</v>
-      </c>
-      <c r="G8" s="28">
-        <f t="shared" si="1"/>
         <v>812000</v>
       </c>
       <c r="H8" s="26">
         <v>2</v>
       </c>
       <c r="I8" s="29">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J8" s="28">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="J8" s="28">
-        <f t="shared" si="3"/>
         <v>1624000</v>
       </c>
     </row>
@@ -6827,34 +6797,34 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
       </c>
       <c r="F9" s="28">
+        <f t="shared" si="3"/>
+        <v>112000</v>
+      </c>
+      <c r="G9" s="28">
         <f t="shared" si="0"/>
-        <v>112000</v>
-      </c>
-      <c r="G9" s="28">
-        <f t="shared" si="1"/>
         <v>812000</v>
       </c>
       <c r="H9" s="26">
         <v>2</v>
       </c>
       <c r="I9" s="29">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J9" s="28">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="J9" s="28">
-        <f t="shared" si="3"/>
         <v>1624000</v>
       </c>
     </row>
@@ -6863,61 +6833,61 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
       </c>
       <c r="F10" s="28">
+        <f t="shared" si="3"/>
+        <v>112000</v>
+      </c>
+      <c r="G10" s="28">
         <f t="shared" si="0"/>
-        <v>112000</v>
-      </c>
-      <c r="G10" s="28">
-        <f t="shared" si="1"/>
         <v>812000</v>
       </c>
       <c r="H10" s="26">
         <v>2</v>
       </c>
       <c r="I10" s="29">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J10" s="28">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="J10" s="28">
-        <f t="shared" si="3"/>
         <v>1624000</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
       <c r="E11" s="31">
         <f>SUM(E4:E10)</f>
-        <v>5800000</v>
+        <v>5393100</v>
       </c>
       <c r="F11" s="31">
         <f>SUM(F4:F10)</f>
-        <v>928000</v>
+        <v>656000</v>
       </c>
       <c r="G11" s="31">
         <f>SUM(G4:G10)</f>
-        <v>6728000</v>
+        <v>6049100</v>
       </c>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
       <c r="J11" s="31">
         <f>SUM(J4:J10)</f>
-        <v>13456000</v>
+        <v>12098200</v>
       </c>
     </row>
   </sheetData>
@@ -6941,7 +6911,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6966,7 +6936,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>91</v>
@@ -6999,7 +6969,7 @@
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="str">
         <f>Штат!C6</f>
-        <v>Заместитель ГИД по стратегии и проектам</v>
+        <v>Советник ГИД по стратегии и науке</v>
       </c>
       <c r="C6">
         <f>Штат!G6</f>
@@ -7046,7 +7016,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")</f>
@@ -7069,7 +7039,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")</f>
@@ -7115,7 +7085,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -7175,12 +7145,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7203,7 +7173,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -7235,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I42" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -7265,7 +7235,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -7337,7 +7307,7 @@
         <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -7395,7 +7365,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -7805,7 +7775,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -7836,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -7910,7 +7880,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C28" t="s">
         <v>100</v>
@@ -7929,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="1">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -7941,7 +7911,7 @@
         <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C29" t="s">
         <v>100</v>
@@ -7960,7 +7930,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -7972,7 +7942,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
@@ -7991,7 +7961,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -8091,7 +8061,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -8110,7 +8080,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -8122,7 +8092,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
@@ -8150,7 +8120,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
@@ -8169,7 +8139,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" ref="I36" si="2">IF(F36="разово",IF(G36&lt;=3,D36*E36,0),IF(F36="мес",D36*E36*MAX(0,4-G36),D36*E36*MAX(0,4-G36)/12))</f>
@@ -8181,7 +8151,7 @@
         <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C37" t="s">
         <v>100</v>
@@ -8200,7 +8170,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" ref="I37:I39" si="3">IF(F37="разово",IF(G37&lt;=3,D37*E37,0),IF(F37="мес",D37*E37*MAX(0,4-G37),D37*E37*MAX(0,4-G37)/12))</f>
@@ -8212,7 +8182,7 @@
         <v>98</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C38" t="s">
         <v>104</v>
@@ -8231,7 +8201,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="3"/>
@@ -8243,7 +8213,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -8262,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="3"/>
@@ -8330,7 +8300,7 @@
         <v>98</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C42" t="s">
         <v>100</v>
@@ -8377,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I43" s="5">
         <f>D43*E43*Аренда_мес_2026</f>
@@ -8532,7 +8502,7 @@
         <v>118</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C49" t="s">
         <v>120</v>
@@ -8551,7 +8521,7 @@
         <v>2</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="4"/>
@@ -8563,7 +8533,7 @@
         <v>118</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
@@ -8582,7 +8552,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" ref="I50" si="5">IF(F50="разово",IF(G50&lt;=3,D50*E50,0),IF(F50="мес",D50*E50*MAX(0,4-G50),D50*E50*MAX(0,4-G50)/12))</f>
@@ -8640,7 +8610,7 @@
         <v>2</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I52" s="5">
         <f t="shared" si="4"/>
@@ -8738,7 +8708,7 @@
         <v>136</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C56" t="s">
         <v>244</v>
@@ -8815,7 +8785,7 @@
         <v>140</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C59" t="s">
         <v>104</v>
@@ -8843,7 +8813,7 @@
         <v>140</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C60" t="s">
         <v>138</v>
@@ -8892,7 +8862,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -8926,7 +8896,7 @@
         <v>285</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C5" t="s">
         <v>244</v>
@@ -8946,7 +8916,7 @@
         <v>285</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C6" t="s">
         <v>244</v>
@@ -8986,7 +8956,7 @@
         <v>285</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C8" t="s">
         <v>244</v>
@@ -9006,7 +8976,7 @@
         <v>285</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C9" t="s">
         <v>244</v>
@@ -9026,7 +8996,7 @@
         <v>285</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C10" t="s">
         <v>244</v>
@@ -9053,7 +9023,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -9075,257 +9045,257 @@
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
-    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="48"/>
-    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="48" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="48"/>
+    <col min="1" max="1" width="5.28515625" style="58" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="46" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="46"/>
+    <col min="5" max="5" width="12.42578125" style="46" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="46" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="46" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="79" t="s">
+        <v>422</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+    </row>
+    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>425</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>426</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-    </row>
-    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>427</v>
       </c>
-      <c r="C3" s="51" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="48" t="s">
         <v>428</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>429</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="53"/>
-      <c r="B4" s="50" t="s">
-        <v>432</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55">
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53">
         <f>F11</f>
         <v>9272000</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="53" t="s">
-        <v>433</v>
-      </c>
-      <c r="B5" s="56" t="s">
-        <v>434</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>435</v>
-      </c>
-      <c r="D5" s="57">
+      <c r="A5" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>430</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>431</v>
+      </c>
+      <c r="D5" s="55">
         <v>56</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="56">
         <v>30000</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="56">
         <f t="shared" ref="F5:F10" si="0">E5*D5</f>
         <v>1680000</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>437</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>438</v>
-      </c>
-      <c r="D6" s="57">
+      <c r="A6" s="51" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>434</v>
+      </c>
+      <c r="D6" s="55">
         <v>56</v>
       </c>
-      <c r="E6" s="58">
+      <c r="E6" s="56">
         <v>25000</v>
       </c>
-      <c r="F6" s="58">
+      <c r="F6" s="56">
         <f t="shared" si="0"/>
         <v>1400000</v>
       </c>
-      <c r="G6" s="60"/>
+      <c r="G6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
-        <v>439</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>440</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>438</v>
-      </c>
-      <c r="D7" s="57">
+      <c r="A7" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>436</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>434</v>
+      </c>
+      <c r="D7" s="55">
         <v>6</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="56">
         <v>100000</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="56">
         <f t="shared" si="0"/>
         <v>600000</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
-        <v>441</v>
-      </c>
-      <c r="B8" s="59" t="s">
-        <v>442</v>
-      </c>
-      <c r="C8" s="57" t="s">
+      <c r="A8" s="51" t="s">
+        <v>437</v>
+      </c>
+      <c r="B8" s="57" t="s">
         <v>438</v>
       </c>
-      <c r="D8" s="57">
+      <c r="C8" s="55" t="s">
+        <v>434</v>
+      </c>
+      <c r="D8" s="55">
         <v>6</v>
       </c>
-      <c r="E8" s="58">
+      <c r="E8" s="56">
         <v>400000</v>
       </c>
-      <c r="F8" s="58">
+      <c r="F8" s="56">
         <f t="shared" si="0"/>
         <v>2400000</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="53" t="s">
-        <v>443</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>444</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>438</v>
-      </c>
-      <c r="D9" s="57">
+      <c r="A9" s="51" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>440</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>434</v>
+      </c>
+      <c r="D9" s="55">
         <v>6</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="56">
         <v>500000</v>
       </c>
-      <c r="F9" s="58">
+      <c r="F9" s="56">
         <f t="shared" si="0"/>
         <v>3000000</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="53" t="s">
-        <v>445</v>
-      </c>
-      <c r="B10" s="59" t="s">
-        <v>446</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>438</v>
-      </c>
-      <c r="D10" s="57">
+      <c r="A10" s="51" t="s">
+        <v>441</v>
+      </c>
+      <c r="B10" s="57" t="s">
+        <v>442</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>434</v>
+      </c>
+      <c r="D10" s="55">
         <v>48</v>
       </c>
-      <c r="E10" s="58">
+      <c r="E10" s="56">
         <v>4000</v>
       </c>
-      <c r="F10" s="58">
+      <c r="F10" s="56">
         <f t="shared" si="0"/>
         <v>192000</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="53"/>
-      <c r="B11" s="61" t="s">
-        <v>447</v>
-      </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="55">
+      <c r="A11" s="51"/>
+      <c r="B11" s="59" t="s">
+        <v>443</v>
+      </c>
+      <c r="C11" s="49"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="53">
         <f>SUM(F5:F10)</f>
         <v>9272000</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="53"/>
-      <c r="B12" s="62" t="s">
-        <v>448</v>
-      </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="65">
+      <c r="A12" s="51"/>
+      <c r="B12" s="60" t="s">
+        <v>444</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="63">
         <f>F11*1.16</f>
         <v>10755520</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="66"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
+      <c r="A14" s="64"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="68"/>
-      <c r="B15" s="69"/>
-      <c r="F15" s="70"/>
+      <c r="A15" s="66"/>
+      <c r="B15" s="67"/>
+      <c r="F15" s="68"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="71"/>
+      <c r="A16" s="69"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="69"/>
-      <c r="F17" s="70"/>
+      <c r="B17" s="67"/>
+      <c r="F17" s="68"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H18" s="72"/>
-    </row>
-    <row r="19" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="60"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="H19" s="73"/>
+      <c r="H18" s="70"/>
+    </row>
+    <row r="19" spans="1:8" s="65" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="58"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="H19" s="71"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F22" s="74"/>
+      <c r="F22" s="72"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E23" s="75"/>
-      <c r="F23" s="74"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9342,298 +9312,298 @@
   <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="60" customWidth="1"/>
-    <col min="2" max="2" width="52.85546875" style="48" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="48" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="48"/>
-    <col min="5" max="5" width="12.42578125" style="48" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="48" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="48" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="48"/>
+    <col min="1" max="1" width="5.28515625" style="58" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="46" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="46"/>
+    <col min="5" max="5" width="12.42578125" style="46" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="46" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="46" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>449</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="A1" s="79" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="48" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>425</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>426</v>
+      </c>
+      <c r="F3" s="50" t="s">
         <v>427</v>
       </c>
-      <c r="C3" s="51" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="48" t="s">
         <v>428</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>429</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="53"/>
-      <c r="B4" s="50" t="s">
-        <v>432</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55">
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53">
         <f>F14</f>
         <v>5530000</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="53" t="s">
-        <v>433</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>450</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>451</v>
-      </c>
-      <c r="D5" s="57">
-        <v>1</v>
-      </c>
-      <c r="E5" s="58">
+      <c r="A5" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>446</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="D5" s="55">
+        <v>1</v>
+      </c>
+      <c r="E5" s="56">
         <v>500000</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="56">
         <f>E5*D5</f>
         <v>500000</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>452</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>451</v>
-      </c>
-      <c r="D6" s="57">
-        <v>1</v>
-      </c>
-      <c r="E6" s="58">
+      <c r="A6" s="51" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>448</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="D6" s="55">
+        <v>1</v>
+      </c>
+      <c r="E6" s="56">
         <v>1500000</v>
       </c>
-      <c r="F6" s="58">
+      <c r="F6" s="56">
         <f>E6*D6</f>
         <v>1500000</v>
       </c>
-      <c r="G6" s="60"/>
+      <c r="G6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
-        <v>439</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>453</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>451</v>
-      </c>
-      <c r="D7" s="57">
-        <v>1</v>
-      </c>
-      <c r="E7" s="58">
+      <c r="A7" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>449</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="D7" s="55">
+        <v>1</v>
+      </c>
+      <c r="E7" s="56">
         <v>100000</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="56">
         <f>E7*D7</f>
         <v>100000</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
-        <v>441</v>
-      </c>
-      <c r="B8" s="59" t="s">
-        <v>454</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="D8" s="57">
-        <v>1</v>
-      </c>
-      <c r="E8" s="58">
+      <c r="A8" s="51" t="s">
+        <v>437</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>450</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="D8" s="55">
+        <v>1</v>
+      </c>
+      <c r="E8" s="56">
         <v>500000</v>
       </c>
-      <c r="F8" s="58">
+      <c r="F8" s="56">
         <f>D8*E8</f>
         <v>500000</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="53" t="s">
-        <v>443</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>456</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>457</v>
-      </c>
-      <c r="D9" s="76">
+      <c r="A9" s="51" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>452</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>453</v>
+      </c>
+      <c r="D9" s="74">
         <v>100</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="56">
         <v>3000</v>
       </c>
-      <c r="F9" s="58">
+      <c r="F9" s="56">
         <f>D9*E9</f>
         <v>300000</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="53" t="s">
-        <v>445</v>
-      </c>
-      <c r="B10" s="59" t="s">
-        <v>458</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>457</v>
-      </c>
-      <c r="D10" s="76">
+      <c r="A10" s="51" t="s">
+        <v>441</v>
+      </c>
+      <c r="B10" s="57" t="s">
+        <v>454</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>453</v>
+      </c>
+      <c r="D10" s="74">
         <v>100</v>
       </c>
-      <c r="E10" s="58">
+      <c r="E10" s="56">
         <v>7000</v>
       </c>
-      <c r="F10" s="58">
+      <c r="F10" s="56">
         <f>D10*E10</f>
         <v>700000</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="53"/>
-      <c r="B11" s="59" t="s">
-        <v>459</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>457</v>
-      </c>
-      <c r="D11" s="76">
-        <v>1</v>
-      </c>
-      <c r="E11" s="58">
+      <c r="A11" s="51"/>
+      <c r="B11" s="57" t="s">
+        <v>455</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>453</v>
+      </c>
+      <c r="D11" s="74">
+        <v>1</v>
+      </c>
+      <c r="E11" s="56">
         <v>130000</v>
       </c>
-      <c r="F11" s="58">
+      <c r="F11" s="56">
         <f>D11*E11</f>
         <v>130000</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="53" t="s">
-        <v>445</v>
-      </c>
-      <c r="B12" s="59" t="s">
-        <v>442</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="D12" s="57">
+      <c r="A12" s="51" t="s">
+        <v>441</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>438</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>451</v>
+      </c>
+      <c r="D12" s="55">
         <v>4</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="56">
         <v>400000</v>
       </c>
-      <c r="F12" s="58">
+      <c r="F12" s="56">
         <f>D12*E12</f>
         <v>1600000</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="53" t="s">
-        <v>460</v>
-      </c>
-      <c r="B13" s="77" t="s">
-        <v>461</v>
-      </c>
-      <c r="C13" s="78" t="s">
-        <v>435</v>
-      </c>
-      <c r="D13" s="78">
-        <v>1</v>
-      </c>
-      <c r="E13" s="79">
+      <c r="A13" s="51" t="s">
+        <v>456</v>
+      </c>
+      <c r="B13" s="75" t="s">
+        <v>457</v>
+      </c>
+      <c r="C13" s="76" t="s">
+        <v>431</v>
+      </c>
+      <c r="D13" s="76">
+        <v>1</v>
+      </c>
+      <c r="E13" s="77">
         <v>200000</v>
       </c>
-      <c r="F13" s="80">
+      <c r="F13" s="78">
         <f>E13*D13</f>
         <v>200000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="53"/>
-      <c r="B14" s="61" t="s">
-        <v>447</v>
-      </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="55">
+      <c r="A14" s="51"/>
+      <c r="B14" s="59" t="s">
+        <v>443</v>
+      </c>
+      <c r="C14" s="49"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="53">
         <f>SUM(F5:F13)</f>
         <v>5530000</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="53"/>
-      <c r="B15" s="62" t="s">
-        <v>448</v>
-      </c>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="65">
+      <c r="A15" s="51"/>
+      <c r="B15" s="60" t="s">
+        <v>444</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="63">
         <f>F14*1.16</f>
         <v>6414800</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H16" s="72"/>
-    </row>
-    <row r="17" spans="1:8" s="67" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="H17" s="73"/>
+      <c r="H16" s="70"/>
+    </row>
+    <row r="17" spans="1:8" s="65" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="58"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="H17" s="71"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F20" s="74"/>
+      <c r="F20" s="72"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E21" s="75"/>
-      <c r="F21" s="74"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -1387,9 +1387,6 @@
     <t xml:space="preserve">  в т.ч. Фонд</t>
   </si>
   <si>
-    <t>[Қаражан Е.Н.] Общее руководство Фондом и проектным офисом, соглашение с МЭПР, отчётность перед органами Фонда. Опыт: к.э.н. (PhD), MSc LSE («Болашақ»), Chevening; ГИД ЦАКФ с 02.2025 (Региональный экологический саммит 2026); председатель Правления ИЭИ, советник Министра национальной экономики, консультант АБР, директор по устойчивому развитию ФНБ «Самрук-Қазына».</t>
-  </si>
-  <si>
     <t>[Тленчиева Ш.] Исследования восприятия акции, опросы. Опыт: PhD по социологии.</t>
   </si>
   <si>
@@ -1526,9 +1523,6 @@
   </si>
   <si>
     <t>Менеджер проектов</t>
-  </si>
-  <si>
-    <t>Руководителю Проектного офиса для Центральной Азии</t>
   </si>
   <si>
     <t>Руководитель проектного офиса «Таза Қазақстан»</t>
@@ -1859,6 +1853,12 @@
   </si>
   <si>
     <t>Администратор (сис.админ), на руки 350 000</t>
+  </si>
+  <si>
+    <t>ГИД (Руководитель Проектного офиса для Центральной Азии)</t>
+  </si>
+  <si>
+    <t>[Қаражан Е.Н.] Общее руководство Фондом и проектным офисом, руководство Проектным офисом для Центральной Азии, соглашение с МЭПР, отчётность перед органами Фонда. Опыт: к.э.н. (PhD), MSc LSE («Болашақ»), Chevening; ГИД ЦАКФ с 02.2025 (Региональный экологический саммит 2026); председатель Правления ИЭИ, советник Министра национальной экономики, консультант АБР, директор по устойчивому развитию ФНБ «Самрук-Қазына».</t>
   </si>
 </sst>
 </file>
@@ -2526,7 +2526,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2539,7 +2539,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E34,"штат",Штат!G5:G34)</f>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G36</f>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M34,Штат!E5:E34,"штат")</f>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -2575,7 +2575,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N35</f>
@@ -2584,7 +2584,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -2593,7 +2593,7 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Оснащение")</f>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Офис")</f>
@@ -2611,7 +2611,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Цифровые")</f>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Медиа")</f>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Прочие")</f>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
@@ -2665,7 +2665,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
@@ -2705,7 +2705,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -2724,25 +2724,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>421</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>422</v>
+      </c>
+      <c r="D3" s="49" t="s">
         <v>423</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>425</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>426</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2754,13 +2754,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -2775,13 +2775,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -2797,13 +2797,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -2819,7 +2819,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="59" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="55"/>
@@ -2832,7 +2832,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51"/>
       <c r="B9" s="60" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
@@ -2889,7 +2889,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -2908,25 +2908,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>421</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>422</v>
+      </c>
+      <c r="D3" s="49" t="s">
         <v>423</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>425</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>426</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2938,13 +2938,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D5" s="55">
         <v>6</v>
@@ -2959,13 +2959,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -2981,13 +2981,13 @@
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3002,13 +3002,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D8" s="55">
         <v>9</v>
@@ -3023,13 +3023,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D9" s="74">
         <v>32</v>
@@ -3044,13 +3044,13 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D10" s="55">
         <v>3</v>
@@ -3065,13 +3065,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D11" s="55">
         <v>3</v>
@@ -3088,7 +3088,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="59" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="55"/>
@@ -3101,7 +3101,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
@@ -3155,7 +3155,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -3174,25 +3174,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>421</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>422</v>
+      </c>
+      <c r="D3" s="49" t="s">
         <v>423</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>425</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>426</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3204,13 +3204,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3225,13 +3225,13 @@
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3248,7 +3248,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="59" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="55"/>
@@ -3261,7 +3261,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="60" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -3318,7 +3318,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -3337,25 +3337,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>421</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>422</v>
+      </c>
+      <c r="D3" s="49" t="s">
         <v>423</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>425</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>426</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3367,13 +3367,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3389,7 +3389,7 @@
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51"/>
       <c r="B6" s="59" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="55"/>
@@ -3403,7 +3403,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="60" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
@@ -3461,7 +3461,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -3644,7 +3644,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3801,7 +3801,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -4358,14 +4358,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$34,Штат!$E$5:$E$34,"штат",Штат!$F$5:$F$34,"новая"),-3)</f>
         <v>658000</v>
       </c>
       <c r="C15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4594,12 +4594,12 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -4724,7 +4724,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -4793,13 +4793,13 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>1</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>335</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -4873,7 +4873,7 @@
         <v>274</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -4918,7 +4918,7 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -4974,7 +4974,7 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -4985,7 +4985,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -5030,7 +5030,7 @@
         <v>3223971.5789473685</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5086,7 +5086,7 @@
         <v>3000411.5789473685</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5097,7 +5097,7 @@
         <v>246</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>249</v>
@@ -5142,7 +5142,7 @@
         <v>2329731.5789473685</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5153,7 +5153,7 @@
         <v>246</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>249</v>
@@ -5198,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5254,7 +5254,7 @@
         <v>2329731.5789473685</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5366,7 +5366,7 @@
         <v>2329731.5789473685</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -5422,7 +5422,7 @@
         <v>2329731.5789473685</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5478,7 +5478,7 @@
         <v>2329731.5789473685</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5534,7 +5534,7 @@
         <v>1182181.5789473683</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5590,7 +5590,7 @@
         <v>846841.57894736843</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5646,7 +5646,7 @@
         <v>1659051.5789473683</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -5702,7 +5702,7 @@
         <v>3000411.5789473685</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5814,7 +5814,7 @@
         <v>3000411.5789473685</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -5870,7 +5870,7 @@
         <v>2329731.5789473685</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -5993,7 +5993,7 @@
         <v>256</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>216</v>
@@ -6038,7 +6038,7 @@
         <v>1659051.5789473683</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -6094,7 +6094,7 @@
         <v>2329731.5789473685</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -6262,7 +6262,7 @@
         <v>4784010</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6326,13 +6326,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="C32" s="17" t="s">
-        <v>381</v>
-      </c>
       <c r="D32" s="17" t="s">
-        <v>382</v>
+        <v>483</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>80</v>
@@ -6374,7 +6374,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6579,7 +6579,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>214</v>
@@ -6654,7 +6654,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>214</v>
@@ -6701,7 +6701,7 @@
         <v>1000000</v>
       </c>
       <c r="F6" s="28">
-        <f t="shared" ref="F4:F10" si="3">E6*НДС</f>
+        <f t="shared" ref="F6:F10" si="3">E6*НДС</f>
         <v>160000</v>
       </c>
       <c r="G6" s="28">
@@ -6797,13 +6797,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>400</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>402</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>403</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>404</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -6936,7 +6936,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>91</v>
@@ -7016,7 +7016,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")</f>
@@ -7039,7 +7039,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")</f>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -7145,12 +7145,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7173,7 +7173,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -7205,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I42" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -7365,7 +7365,7 @@
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
@@ -7775,7 +7775,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -7806,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -8061,7 +8061,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -8080,7 +8080,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -8151,7 +8151,7 @@
         <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C37" t="s">
         <v>100</v>
@@ -8170,7 +8170,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" ref="I37:I39" si="3">IF(F37="разово",IF(G37&lt;=3,D37*E37,0),IF(F37="мес",D37*E37*MAX(0,4-G37),D37*E37*MAX(0,4-G37)/12))</f>
@@ -8182,7 +8182,7 @@
         <v>98</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C38" t="s">
         <v>104</v>
@@ -8201,7 +8201,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="3"/>
@@ -8213,7 +8213,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -8232,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="3"/>
@@ -8300,7 +8300,7 @@
         <v>98</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C42" t="s">
         <v>100</v>
@@ -8502,7 +8502,7 @@
         <v>118</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C49" t="s">
         <v>120</v>
@@ -8521,7 +8521,7 @@
         <v>2</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="4"/>
@@ -8533,7 +8533,7 @@
         <v>118</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
@@ -8552,7 +8552,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" ref="I50" si="5">IF(F50="разово",IF(G50&lt;=3,D50*E50,0),IF(F50="мес",D50*E50*MAX(0,4-G50),D50*E50*MAX(0,4-G50)/12))</f>
@@ -8610,7 +8610,7 @@
         <v>2</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I52" s="5">
         <f t="shared" si="4"/>
@@ -8785,7 +8785,7 @@
         <v>140</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C59" t="s">
         <v>104</v>
@@ -8813,7 +8813,7 @@
         <v>140</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C60" t="s">
         <v>138</v>
@@ -8862,7 +8862,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -8896,7 +8896,7 @@
         <v>285</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C5" t="s">
         <v>244</v>
@@ -8916,7 +8916,7 @@
         <v>285</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C6" t="s">
         <v>244</v>
@@ -8956,7 +8956,7 @@
         <v>285</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C8" t="s">
         <v>244</v>
@@ -8976,7 +8976,7 @@
         <v>285</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C9" t="s">
         <v>244</v>
@@ -8996,7 +8996,7 @@
         <v>285</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C10" t="s">
         <v>244</v>
@@ -9023,7 +9023,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -9058,7 +9058,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -9077,25 +9077,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>421</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>422</v>
+      </c>
+      <c r="D3" s="49" t="s">
         <v>423</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>425</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>426</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -9107,13 +9107,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>428</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>429</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>430</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>431</v>
       </c>
       <c r="D5" s="55">
         <v>56</v>
@@ -9128,13 +9128,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
+        <v>430</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>431</v>
+      </c>
+      <c r="C6" s="55" t="s">
         <v>432</v>
-      </c>
-      <c r="B6" s="57" t="s">
-        <v>433</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>434</v>
       </c>
       <c r="D6" s="55">
         <v>56</v>
@@ -9150,13 +9150,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D7" s="55">
         <v>6</v>
@@ -9171,13 +9171,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D8" s="55">
         <v>6</v>
@@ -9192,13 +9192,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D9" s="55">
         <v>6</v>
@@ -9213,13 +9213,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D10" s="55">
         <v>48</v>
@@ -9235,7 +9235,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="59" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="55"/>
@@ -9248,7 +9248,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="60" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>
@@ -9325,7 +9325,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -9344,25 +9344,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>421</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>422</v>
+      </c>
+      <c r="D3" s="49" t="s">
         <v>423</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>425</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>426</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -9374,13 +9374,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -9395,13 +9395,13 @@
     </row>
     <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -9417,13 +9417,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -9438,13 +9438,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D8" s="55">
         <v>1</v>
@@ -9459,13 +9459,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D9" s="74">
         <v>100</v>
@@ -9480,13 +9480,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D10" s="74">
         <v>100</v>
@@ -9502,10 +9502,10 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="57" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D11" s="74">
         <v>1</v>
@@ -9520,13 +9520,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D12" s="55">
         <v>4</v>
@@ -9541,13 +9541,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B13" s="75" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D13" s="76">
         <v>1</v>
@@ -9563,7 +9563,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="51"/>
       <c r="B14" s="59" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="55"/>
@@ -9576,7 +9576,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -380,7 +380,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="489">
   <si>
     <t>Статья</t>
   </si>
@@ -1859,6 +1859,18 @@
   </si>
   <si>
     <t>[Қаражан Е.Н.] Общее руководство Фондом и проектным офисом, руководство Проектным офисом для Центральной Азии, соглашение с МЭПР, отчётность перед органами Фонда. Опыт: к.э.н. (PhD), MSc LSE («Болашақ»), Chevening; ГИД ЦАКФ с 02.2025 (Региональный экологический саммит 2026); председатель Правления ИЭИ, советник Министра национальной экономики, консультант АБР, директор по устойчивому развитию ФНБ «Самрук-Қазына».</t>
+  </si>
+  <si>
+    <t>Эксперт-эколог</t>
+  </si>
+  <si>
+    <t>[Загирова Анастасия] Экологическая экспертиза, данные о состоянии окружающей среды, методические материалы</t>
+  </si>
+  <si>
+    <t>Эксперт</t>
+  </si>
+  <si>
+    <t>[Абулхан А.] Молодёжь, волонтёры, НПО, школы и вузы; экспертиза молодёжных и общественных проектов</t>
   </si>
 </sst>
 </file>
@@ -2064,7 +2076,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2244,6 +2256,7 @@
     <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -2542,8 +2555,8 @@
         <v>345</v>
       </c>
       <c r="B4" s="37">
-        <f>SUMIF(Штат!E5:E34,"штат",Штат!G5:G34)</f>
-        <v>22</v>
+        <f>SUMIF(Штат!E5:E36,"штат",Штат!G5:G36)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2551,7 +2564,7 @@
         <v>346</v>
       </c>
       <c r="B5" s="37">
-        <f>Штат!G36</f>
+        <f>Штат!G38</f>
         <v>17</v>
       </c>
     </row>
@@ -2560,8 +2573,8 @@
         <v>347</v>
       </c>
       <c r="B6" s="38">
-        <f>SUMIFS(Штат!M5:M34,Штат!E5:E34,"штат")</f>
-        <v>58935200</v>
+        <f>SUMIFS(Штат!M5:M36,Штат!E5:E36,"штат")</f>
+        <v>61795688</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2578,8 +2591,8 @@
         <v>374</v>
       </c>
       <c r="B8" s="38">
-        <f>Штат!N35</f>
-        <v>623368.42105263157</v>
+        <f>Штат!N37</f>
+        <v>667619.04761904769</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2597,7 +2610,7 @@
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Оснащение")</f>
-        <v>28742588</v>
+        <v>22439688</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2615,7 +2628,7 @@
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Цифровые")</f>
-        <v>463000</v>
+        <v>491000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2633,7 +2646,7 @@
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>124523669.91782683</v>
+        <v>121153508.54439324</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2642,7 +2655,7 @@
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Прочие")</f>
-        <v>12519033.65844935</v>
+        <v>12182017.521105992</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2651,7 +2664,7 @@
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>21926832.572204191</v>
+        <v>21333684.170479879</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2660,7 +2673,7 @@
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>158969536.14848039</v>
+        <v>154669210.23597911</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2678,7 +2691,7 @@
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>246203856.14848039</v>
+        <v>241903530.23597911</v>
       </c>
     </row>
   </sheetData>
@@ -2704,20 +2717,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>456</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
@@ -2888,20 +2901,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>462</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
@@ -3154,20 +3167,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>470</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
@@ -3317,20 +3330,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>473</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
@@ -4361,8 +4374,8 @@
         <v>372</v>
       </c>
       <c r="B15" s="8">
-        <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$34,Штат!$E$5:$E$34,"штат",Штат!$F$5:$F$34,"новая"),-3)</f>
-        <v>658000</v>
+        <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$36,Штат!$E$5:$E$36,"штат",Штат!$F$5:$F$36,"новая"),-3)</f>
+        <v>701000</v>
       </c>
       <c r="C15" t="s">
         <v>408</v>
@@ -4739,7 +4752,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -4846,19 +4859,19 @@
         <v>1818230</v>
       </c>
       <c r="L5" s="19">
-        <f t="shared" ref="L5:L34" si="2">IF(AND(F5="новая",I5=1),Мес_2026_новые,MAX(0,4-I5))</f>
+        <f t="shared" ref="L5:L36" si="2">IF(AND(F5="новая",I5=1),Мес_2026_новые,MAX(0,4-I5))</f>
         <v>3</v>
       </c>
       <c r="M5" s="18">
-        <f t="shared" ref="M5:M34" si="3">K5*L5</f>
+        <f t="shared" ref="M5:M36" si="3">K5*L5</f>
         <v>5454690</v>
       </c>
       <c r="N5" s="18">
-        <f t="shared" ref="N5:N34" si="4">IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$34,"штат",$F$5:$F$34,"новая"),0)</f>
+        <f>IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
         <v>0</v>
       </c>
       <c r="O5" s="18">
-        <f t="shared" ref="O5:O34" si="5">M5+N5</f>
+        <f t="shared" ref="O5:O36" si="4">M5+N5</f>
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
@@ -4910,11 +4923,11 @@
         <v>4784010</v>
       </c>
       <c r="N6" s="18">
+        <f>IF(AND(E6="штат",F6="новая"),ОСНС_полис*G6/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="18">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O6" s="18">
-        <f t="shared" si="5"/>
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
@@ -4966,11 +4979,11 @@
         <v>4784010</v>
       </c>
       <c r="N7" s="18">
+        <f>IF(AND(E7="штат",F7="новая"),ОСНС_полис*G7/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="18">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O7" s="18">
-        <f t="shared" si="5"/>
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
@@ -5022,12 +5035,12 @@
         <v>3189340</v>
       </c>
       <c r="N8" s="18">
+        <f>IF(AND(E8="штат",F8="новая"),ОСНС_полис*G8/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O8" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O8" s="18">
-        <f t="shared" si="5"/>
-        <v>3223971.5789473685</v>
+        <v>3222720.9523809524</v>
       </c>
       <c r="P8" s="17" t="s">
         <v>382</v>
@@ -5062,28 +5075,28 @@
         <v>2</v>
       </c>
       <c r="J9" s="18">
-        <f t="shared" ref="J9:J11" si="6">IF(E9="штат",ROUND(Ставка_СН*H9*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H9+Ставка_СО*MIN(H9*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H9,Кап_ООСМС*МЗП),0),ROUND(H9*НДС,0))</f>
+        <f t="shared" ref="J9:J11" si="5">IF(E9="штат",ROUND(Ставка_СН*H9*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H9+Ставка_СО*MIN(H9*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H9,Кап_ООСМС*МЗП),0),ROUND(H9*НДС,0))</f>
         <v>182890</v>
       </c>
       <c r="K9" s="18">
-        <f t="shared" ref="K9:K11" si="7">G9*(H9+J9)</f>
+        <f t="shared" ref="K9:K11" si="6">G9*(H9+J9)</f>
         <v>1482890</v>
       </c>
       <c r="L9" s="19">
-        <f t="shared" ref="L9:L11" si="8">IF(AND(F9="новая",I9=1),Мес_2026_новые,MAX(0,4-I9))</f>
+        <f t="shared" ref="L9:L11" si="7">IF(AND(F9="новая",I9=1),Мес_2026_новые,MAX(0,4-I9))</f>
         <v>2</v>
       </c>
       <c r="M9" s="18">
-        <f t="shared" ref="M9:M11" si="9">K9*L9</f>
+        <f t="shared" ref="M9:M11" si="8">K9*L9</f>
         <v>2965780</v>
       </c>
       <c r="N9" s="18">
-        <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
+        <f>IF(AND(E9="штат",F9="новая"),ОСНС_полис*G9/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
       </c>
       <c r="O9" s="18">
-        <f t="shared" ref="O9:O11" si="10">M9+N9</f>
-        <v>3000411.5789473685</v>
+        <f t="shared" ref="O9:O11" si="9">M9+N9</f>
+        <v>2999160.9523809524</v>
       </c>
       <c r="P9" s="17" t="s">
         <v>395</v>
@@ -5118,28 +5131,28 @@
         <v>2</v>
       </c>
       <c r="J10" s="18">
+        <f t="shared" si="5"/>
+        <v>147550</v>
+      </c>
+      <c r="K10" s="18">
         <f t="shared" si="6"/>
-        <v>147550</v>
-      </c>
-      <c r="K10" s="18">
+        <v>1147550</v>
+      </c>
+      <c r="L10" s="19">
         <f t="shared" si="7"/>
-        <v>1147550</v>
-      </c>
-      <c r="L10" s="19">
+        <v>2</v>
+      </c>
+      <c r="M10" s="18">
         <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="M10" s="18">
+        <v>2295100</v>
+      </c>
+      <c r="N10" s="18">
+        <f>IF(AND(E10="штат",F10="новая"),ОСНС_полис*G10/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O10" s="18">
         <f t="shared" si="9"/>
-        <v>2295100</v>
-      </c>
-      <c r="N10" s="18">
-        <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O10" s="18">
-        <f t="shared" si="10"/>
-        <v>2329731.5789473685</v>
+        <v>2328480.9523809524</v>
       </c>
       <c r="P10" s="17" t="s">
         <v>397</v>
@@ -5174,27 +5187,27 @@
         <v>2</v>
       </c>
       <c r="J11" s="22">
+        <f t="shared" si="5"/>
+        <v>112000</v>
+      </c>
+      <c r="K11" s="22">
         <f t="shared" si="6"/>
-        <v>112000</v>
-      </c>
-      <c r="K11" s="22">
+        <v>0</v>
+      </c>
+      <c r="L11" s="23">
         <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="M11" s="22">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L11" s="23">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="M11" s="22">
+      <c r="N11" s="22">
+        <f>IF(AND(E11="штат",F11="новая"),ОСНС_полис*G11/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="22">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="22">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="22">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
@@ -5246,12 +5259,12 @@
         <v>2295100</v>
       </c>
       <c r="N12" s="18">
+        <f>IF(AND(E12="штат",F12="новая"),ОСНС_полис*G12/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O12" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O12" s="18">
-        <f t="shared" si="5"/>
-        <v>2329731.5789473685</v>
+        <v>2328480.9523809524</v>
       </c>
       <c r="P12" s="17" t="s">
         <v>335</v>
@@ -5286,15 +5299,15 @@
         <v>2</v>
       </c>
       <c r="J13" s="18">
-        <f t="shared" ref="J13" si="11">IF(E13="штат",ROUND(Ставка_СН*H13*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H13+Ставка_СО*MIN(H13*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H13,Кап_ООСМС*МЗП),0),ROUND(H13*НДС,0))</f>
+        <f t="shared" ref="J13" si="10">IF(E13="штат",ROUND(Ставка_СН*H13*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H13+Ставка_СО*MIN(H13*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H13,Кап_ООСМС*МЗП),0),ROUND(H13*НДС,0))</f>
         <v>159330</v>
       </c>
       <c r="K13" s="18">
-        <f t="shared" ref="K13" si="12">G13*(H13+J13)</f>
+        <f t="shared" ref="K13" si="11">G13*(H13+J13)</f>
         <v>1259330</v>
       </c>
       <c r="L13" s="19">
-        <f t="shared" ref="L13" si="13">IF(AND(F13="новая",I13=1),Мес_2026_новые,MAX(0,4-I13))</f>
+        <f t="shared" ref="L13" si="12">IF(AND(F13="новая",I13=1),Мес_2026_новые,MAX(0,4-I13))</f>
         <v>2</v>
       </c>
       <c r="M13" s="18">
@@ -5302,12 +5315,12 @@
         <v>2518660</v>
       </c>
       <c r="N13" s="18">
+        <f>IF(AND(E13="штат",F13="новая"),ОСНС_полис*G13/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O13" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O13" s="18">
-        <f t="shared" si="5"/>
-        <v>2553291.5789473685</v>
+        <v>2552040.9523809524</v>
       </c>
       <c r="P13" s="17" t="s">
         <v>278</v>
@@ -5358,12 +5371,12 @@
         <v>2295100</v>
       </c>
       <c r="N14" s="18">
+        <f>IF(AND(E14="штат",F14="новая"),ОСНС_полис*G14/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O14" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O14" s="18">
-        <f t="shared" si="5"/>
-        <v>2329731.5789473685</v>
+        <v>2328480.9523809524</v>
       </c>
       <c r="P14" s="17" t="s">
         <v>383</v>
@@ -5414,12 +5427,12 @@
         <v>2295100</v>
       </c>
       <c r="N15" s="18">
+        <f>IF(AND(E15="штат",F15="новая"),ОСНС_полис*G15/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O15" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O15" s="18">
-        <f t="shared" si="5"/>
-        <v>2329731.5789473685</v>
+        <v>2328480.9523809524</v>
       </c>
       <c r="P15" s="17" t="s">
         <v>384</v>
@@ -5470,12 +5483,12 @@
         <v>2295100</v>
       </c>
       <c r="N16" s="18">
+        <f>IF(AND(E16="штат",F16="новая"),ОСНС_полис*G16/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O16" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O16" s="18">
-        <f t="shared" si="5"/>
-        <v>2329731.5789473685</v>
+        <v>2328480.9523809524</v>
       </c>
       <c r="P16" s="17" t="s">
         <v>385</v>
@@ -5510,28 +5523,28 @@
         <v>3</v>
       </c>
       <c r="J17" s="18">
-        <f t="shared" ref="J17:J18" si="14">IF(E17="штат",ROUND(Ставка_СН*H17*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H17+Ставка_СО*MIN(H17*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H17,Кап_ООСМС*МЗП),0),ROUND(H17*НДС,0))</f>
+        <f t="shared" ref="J17:J18" si="13">IF(E17="штат",ROUND(Ставка_СН*H17*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H17+Ставка_СО*MIN(H17*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H17,Кап_ООСМС*МЗП),0),ROUND(H17*НДС,0))</f>
         <v>147550</v>
       </c>
       <c r="K17" s="18">
-        <f t="shared" ref="K17:K18" si="15">G17*(H17+J17)</f>
+        <f t="shared" ref="K17:K18" si="14">G17*(H17+J17)</f>
         <v>1147550</v>
       </c>
       <c r="L17" s="19">
-        <f t="shared" ref="L17:L18" si="16">IF(AND(F17="новая",I17=1),Мес_2026_новые,MAX(0,4-I17))</f>
+        <f t="shared" ref="L17:L18" si="15">IF(AND(F17="новая",I17=1),Мес_2026_новые,MAX(0,4-I17))</f>
         <v>1</v>
       </c>
       <c r="M17" s="18">
-        <f t="shared" ref="M17:M18" si="17">K17*L17</f>
+        <f t="shared" ref="M17:M18" si="16">K17*L17</f>
         <v>1147550</v>
       </c>
       <c r="N17" s="18">
-        <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
+        <f>IF(AND(E17="штат",F17="новая"),ОСНС_полис*G17/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
       </c>
       <c r="O17" s="18">
-        <f t="shared" ref="O17:O18" si="18">M17+N17</f>
-        <v>1182181.5789473683</v>
+        <f t="shared" ref="O17:O18" si="17">M17+N17</f>
+        <v>1180930.9523809524</v>
       </c>
       <c r="P17" s="17" t="s">
         <v>393</v>
@@ -5566,28 +5579,28 @@
         <v>3</v>
       </c>
       <c r="J18" s="18">
+        <f t="shared" si="13"/>
+        <v>112210</v>
+      </c>
+      <c r="K18" s="18">
         <f t="shared" si="14"/>
-        <v>112210</v>
-      </c>
-      <c r="K18" s="18">
+        <v>812210</v>
+      </c>
+      <c r="L18" s="19">
         <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="M18" s="18">
+        <f t="shared" si="16"/>
         <v>812210</v>
       </c>
-      <c r="L18" s="19">
-        <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="M18" s="18">
+      <c r="N18" s="18">
+        <f>IF(AND(E18="штат",F18="новая"),ОСНС_полис*G18/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O18" s="18">
         <f t="shared" si="17"/>
-        <v>812210</v>
-      </c>
-      <c r="N18" s="18">
-        <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O18" s="18">
-        <f t="shared" si="18"/>
-        <v>846841.57894736843</v>
+        <v>845590.95238095243</v>
       </c>
       <c r="P18" s="17" t="s">
         <v>394</v>
@@ -5638,12 +5651,12 @@
         <v>1624420</v>
       </c>
       <c r="N19" s="18">
+        <f>IF(AND(E19="штат",F19="новая"),ОСНС_полис*G19/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O19" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O19" s="18">
-        <f t="shared" si="5"/>
-        <v>1659051.5789473683</v>
+        <v>1657800.9523809524</v>
       </c>
       <c r="P19" s="17" t="s">
         <v>392</v>
@@ -5678,15 +5691,15 @@
         <v>2</v>
       </c>
       <c r="J20" s="18">
-        <f t="shared" ref="J20" si="19">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
+        <f t="shared" ref="J20" si="18">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
         <v>182890</v>
       </c>
       <c r="K20" s="18">
-        <f t="shared" ref="K20" si="20">G20*(H20+J20)</f>
+        <f t="shared" ref="K20" si="19">G20*(H20+J20)</f>
         <v>1482890</v>
       </c>
       <c r="L20" s="19">
-        <f t="shared" ref="L20" si="21">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
+        <f t="shared" ref="L20" si="20">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
         <v>2</v>
       </c>
       <c r="M20" s="18">
@@ -5694,12 +5707,12 @@
         <v>2965780</v>
       </c>
       <c r="N20" s="18">
+        <f>IF(AND(E20="штат",F20="новая"),ОСНС_полис*G20/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O20" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O20" s="18">
-        <f t="shared" si="5"/>
-        <v>3000411.5789473685</v>
+        <v>2999160.9523809524</v>
       </c>
       <c r="P20" s="17" t="s">
         <v>386</v>
@@ -5750,11 +5763,11 @@
         <v>0</v>
       </c>
       <c r="N21" s="22">
+        <f>IF(AND(E21="штат",F21="новая"),ОСНС_полис*G21/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
@@ -5806,12 +5819,12 @@
         <v>2965780</v>
       </c>
       <c r="N22" s="18">
+        <f>IF(AND(E22="штат",F22="новая"),ОСНС_полис*G22/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O22" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O22" s="18">
-        <f t="shared" si="5"/>
-        <v>3000411.5789473685</v>
+        <v>2999160.9523809524</v>
       </c>
       <c r="P22" s="17" t="s">
         <v>388</v>
@@ -5862,12 +5875,12 @@
         <v>2295100</v>
       </c>
       <c r="N23" s="18">
+        <f>IF(AND(E23="штат",F23="новая"),ОСНС_полис*G23/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O23" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O23" s="18">
-        <f t="shared" si="5"/>
-        <v>2329731.5789473685</v>
+        <v>2328480.9523809524</v>
       </c>
       <c r="P23" s="17" t="s">
         <v>387</v>
@@ -5918,11 +5931,11 @@
         <v>0</v>
       </c>
       <c r="N24" s="22">
+        <f>IF(AND(E24="штат",F24="новая"),ОСНС_полис*G24/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
@@ -5958,15 +5971,15 @@
         <v>2</v>
       </c>
       <c r="J25" s="22">
-        <f t="shared" ref="J25" si="22">IF(E25="штат",ROUND(Ставка_СН*H25*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H25+Ставка_СО*MIN(H25*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H25,Кап_ООСМС*МЗП),0),ROUND(H25*НДС,0))</f>
+        <f t="shared" ref="J25" si="21">IF(E25="штат",ROUND(Ставка_СН*H25*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H25+Ставка_СО*MIN(H25*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H25,Кап_ООСМС*МЗП),0),ROUND(H25*НДС,0))</f>
         <v>112000</v>
       </c>
       <c r="K25" s="22">
-        <f t="shared" ref="K25" si="23">G25*(H25+J25)</f>
+        <f t="shared" ref="K25" si="22">G25*(H25+J25)</f>
         <v>0</v>
       </c>
       <c r="L25" s="23">
-        <f t="shared" ref="L25" si="24">IF(AND(F25="новая",I25=1),Мес_2026_новые,MAX(0,4-I25))</f>
+        <f t="shared" ref="L25" si="23">IF(AND(F25="новая",I25=1),Мес_2026_новые,MAX(0,4-I25))</f>
         <v>2</v>
       </c>
       <c r="M25" s="22">
@@ -5974,11 +5987,11 @@
         <v>0</v>
       </c>
       <c r="N25" s="22">
+        <f>IF(AND(E25="штат",F25="новая"),ОСНС_полис*G25/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P25" s="21" t="s">
@@ -6030,12 +6043,12 @@
         <v>1624420</v>
       </c>
       <c r="N26" s="18">
+        <f>IF(AND(E26="штат",F26="новая"),ОСНС_полис*G26/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O26" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O26" s="18">
-        <f t="shared" si="5"/>
-        <v>1659051.5789473683</v>
+        <v>1657800.9523809524</v>
       </c>
       <c r="P26" s="17" t="s">
         <v>391</v>
@@ -6086,12 +6099,12 @@
         <v>2295100</v>
       </c>
       <c r="N27" s="18">
+        <f>IF(AND(E27="штат",F27="новая"),ОСНС_полис*G27/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O27" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O27" s="18">
-        <f t="shared" si="5"/>
-        <v>2329731.5789473685</v>
+        <v>2328480.9523809524</v>
       </c>
       <c r="P27" s="17" t="s">
         <v>389</v>
@@ -6126,11 +6139,11 @@
         <v>2</v>
       </c>
       <c r="J28" s="18">
-        <f t="shared" ref="J28:J34" si="25">IF(E28="штат",ROUND(Ставка_СН*H28*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H28+Ставка_СО*MIN(H28*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H28,Кап_ООСМС*МЗП),0),ROUND(H28*НДС,0))</f>
+        <f t="shared" ref="J28:J36" si="24">IF(E28="штат",ROUND(Ставка_СН*H28*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H28+Ставка_СО*MIN(H28*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H28,Кап_ООСМС*МЗП),0),ROUND(H28*НДС,0))</f>
         <v>112210</v>
       </c>
       <c r="K28" s="18">
-        <f t="shared" ref="K28:K34" si="26">G28*(H28+J28)</f>
+        <f t="shared" ref="K28:K36" si="25">G28*(H28+J28)</f>
         <v>812210</v>
       </c>
       <c r="L28" s="19">
@@ -6142,12 +6155,12 @@
         <v>1624420</v>
       </c>
       <c r="N28" s="18">
+        <f>IF(AND(E28="штат",F28="новая"),ОСНС_полис*G28/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O28" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O28" s="18">
-        <f t="shared" si="5"/>
-        <v>1659051.5789473683</v>
+        <v>1657800.9523809524</v>
       </c>
       <c r="P28" s="17" t="s">
         <v>261</v>
@@ -6182,11 +6195,11 @@
         <v>2</v>
       </c>
       <c r="J29" s="22">
+        <f t="shared" si="24"/>
+        <v>112000</v>
+      </c>
+      <c r="K29" s="22">
         <f t="shared" si="25"/>
-        <v>112000</v>
-      </c>
-      <c r="K29" s="22">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="L29" s="23">
@@ -6198,11 +6211,11 @@
         <v>0</v>
       </c>
       <c r="N29" s="22">
+        <f>IF(AND(E29="штат",F29="новая"),ОСНС_полис*G29/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="22">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="22">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
@@ -6238,11 +6251,11 @@
         <v>1</v>
       </c>
       <c r="J30" s="18">
+        <f t="shared" si="24"/>
+        <v>194670</v>
+      </c>
+      <c r="K30" s="18">
         <f t="shared" si="25"/>
-        <v>194670</v>
-      </c>
-      <c r="K30" s="18">
-        <f t="shared" si="26"/>
         <v>1594670</v>
       </c>
       <c r="L30" s="19">
@@ -6254,11 +6267,11 @@
         <v>4784010</v>
       </c>
       <c r="N30" s="18">
+        <f>IF(AND(E30="штат",F30="новая"),ОСНС_полис*G30/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="18">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="18">
-        <f t="shared" si="5"/>
         <v>4784010</v>
       </c>
       <c r="P30" s="17" t="s">
@@ -6294,11 +6307,11 @@
         <v>2</v>
       </c>
       <c r="J31" s="18">
+        <f t="shared" si="24"/>
+        <v>112210</v>
+      </c>
+      <c r="K31" s="18">
         <f t="shared" si="25"/>
-        <v>112210</v>
-      </c>
-      <c r="K31" s="18">
-        <f t="shared" si="26"/>
         <v>812210</v>
       </c>
       <c r="L31" s="19">
@@ -6310,12 +6323,12 @@
         <v>1624420</v>
       </c>
       <c r="N31" s="18">
+        <f>IF(AND(E31="штат",F31="новая"),ОСНС_полис*G31/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O31" s="18">
         <f t="shared" si="4"/>
-        <v>34631.57894736842</v>
-      </c>
-      <c r="O31" s="18">
-        <f t="shared" si="5"/>
-        <v>1659051.5789473683</v>
+        <v>1657800.9523809524</v>
       </c>
       <c r="P31" s="17" t="s">
         <v>213</v>
@@ -6350,11 +6363,11 @@
         <v>2</v>
       </c>
       <c r="J32" s="18">
+        <f t="shared" si="24"/>
+        <v>147550</v>
+      </c>
+      <c r="K32" s="18">
         <f t="shared" si="25"/>
-        <v>147550</v>
-      </c>
-      <c r="K32" s="18">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="L32" s="19">
@@ -6366,191 +6379,303 @@
         <v>0</v>
       </c>
       <c r="N32" s="18">
+        <f>IF(AND(E32="штат",F32="новая"),ОСНС_полис*G32/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O32" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O32" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="P32" s="17" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="20">
+    <row r="33" spans="1:16" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="16">
+        <v>35</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" s="16">
+        <v>1</v>
+      </c>
+      <c r="H33" s="18">
+        <v>615000</v>
+      </c>
+      <c r="I33" s="16">
+        <v>2</v>
+      </c>
+      <c r="J33" s="18">
+        <f t="shared" ref="J33" si="26">IF(E33="штат",ROUND(Ставка_СН*H33*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H33+Ставка_СО*MIN(H33*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H33,Кап_ООСМС*МЗП),0),ROUND(H33*НДС,0))</f>
+        <v>100122</v>
+      </c>
+      <c r="K33" s="18">
+        <f t="shared" ref="K33" si="27">G33*(H33+J33)</f>
+        <v>715122</v>
+      </c>
+      <c r="L33" s="19">
+        <f t="shared" ref="L33" si="28">IF(AND(F33="новая",I33=1),Мес_2026_новые,MAX(0,4-I33))</f>
+        <v>2</v>
+      </c>
+      <c r="M33" s="18">
+        <f t="shared" ref="M33" si="29">K33*L33</f>
+        <v>1430244</v>
+      </c>
+      <c r="N33" s="18">
+        <f>IF(AND(E33="штат",F33="новая"),ОСНС_полис*G33/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O33" s="18">
+        <f t="shared" ref="O33" si="30">M33+N33</f>
+        <v>1463624.9523809524</v>
+      </c>
+      <c r="P33" s="17" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="16">
+        <v>35</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G34" s="16">
+        <v>1</v>
+      </c>
+      <c r="H34" s="18">
+        <v>615000</v>
+      </c>
+      <c r="I34" s="16">
+        <v>2</v>
+      </c>
+      <c r="J34" s="18">
+        <f t="shared" ref="J34" si="31">IF(E34="штат",ROUND(Ставка_СН*H34*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H34+Ставка_СО*MIN(H34*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H34,Кап_ООСМС*МЗП),0),ROUND(H34*НДС,0))</f>
+        <v>100122</v>
+      </c>
+      <c r="K34" s="18">
+        <f t="shared" ref="K34" si="32">G34*(H34+J34)</f>
+        <v>715122</v>
+      </c>
+      <c r="L34" s="19">
+        <f t="shared" ref="L34" si="33">IF(AND(F34="новая",I34=1),Мес_2026_новые,MAX(0,4-I34))</f>
+        <v>2</v>
+      </c>
+      <c r="M34" s="18">
+        <f t="shared" ref="M34" si="34">K34*L34</f>
+        <v>1430244</v>
+      </c>
+      <c r="N34" s="18">
+        <f>IF(AND(E34="штат",F34="новая"),ОСНС_полис*G34/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>33380.952380952382</v>
+      </c>
+      <c r="O34" s="18">
+        <f t="shared" ref="O34" si="35">M34+N34</f>
+        <v>1463624.9523809524</v>
+      </c>
+      <c r="P34" s="17" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="20">
         <v>36</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="B35" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C35" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D35" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E35" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F35" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G35" s="20">
         <v>0</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H35" s="22">
         <v>867500</v>
       </c>
-      <c r="I33" s="20">
-        <v>2</v>
-      </c>
-      <c r="J33" s="22">
+      <c r="I35" s="20">
+        <v>2</v>
+      </c>
+      <c r="J35" s="22">
+        <f t="shared" si="24"/>
+        <v>138800</v>
+      </c>
+      <c r="K35" s="22">
         <f t="shared" si="25"/>
-        <v>138800</v>
-      </c>
-      <c r="K33" s="22">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="L33" s="23">
+      <c r="L35" s="23">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="M33" s="22">
+      <c r="M35" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N33" s="22">
+      <c r="N35" s="22">
+        <f>IF(AND(E35="штат",F35="новая"),ОСНС_полис*G35/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O35" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O33" s="22">
-        <f t="shared" si="5"/>
+      <c r="P35" s="21" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="20">
+        <v>37</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G36" s="20">
         <v>0</v>
       </c>
-      <c r="P33" s="21" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="20">
-        <v>37</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G34" s="20">
+      <c r="H36" s="22">
+        <v>425600</v>
+      </c>
+      <c r="I36" s="20">
+        <v>2</v>
+      </c>
+      <c r="J36" s="22">
+        <f t="shared" si="24"/>
+        <v>68096</v>
+      </c>
+      <c r="K36" s="22">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="H34" s="22">
-        <v>425600</v>
-      </c>
-      <c r="I34" s="20">
-        <v>2</v>
-      </c>
-      <c r="J34" s="22">
-        <f t="shared" si="25"/>
-        <v>68096</v>
-      </c>
-      <c r="K34" s="22">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="23">
+      <c r="L36" s="23">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="M34" s="22">
+      <c r="M36" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N34" s="22">
+      <c r="N36" s="22">
+        <f>IF(AND(E36="штат",F36="новая"),ОСНС_полис*G36/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O36" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O34" s="22">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P34" s="21" t="s">
+      <c r="P36" s="21" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7" t="s">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7">
-        <f>SUM(G5:G34)</f>
-        <v>22</v>
-      </c>
-      <c r="H35" s="6">
-        <f>SUMPRODUCT(G5:G34,H5:H34)</f>
-        <v>23700000</v>
-      </c>
-      <c r="I35" s="7"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6">
-        <f>SUM(K5:K34)</f>
-        <v>27146360</v>
-      </c>
-      <c r="L35" s="7"/>
-      <c r="M35" s="6">
-        <f>SUM(M5:M34)</f>
-        <v>58935200</v>
-      </c>
-      <c r="N35" s="6">
-        <f t="shared" ref="N35:O35" si="27">SUM(N5:N34)</f>
-        <v>623368.42105263157</v>
-      </c>
-      <c r="O35" s="6">
-        <f t="shared" si="27"/>
-        <v>59558568.421052605</v>
-      </c>
-      <c r="P35" s="7"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C36" t="s">
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7">
+        <f>SUM(G5:G36)</f>
+        <v>24</v>
+      </c>
+      <c r="H37" s="6">
+        <f>SUMPRODUCT(G5:G36,H5:H36)</f>
+        <v>24930000</v>
+      </c>
+      <c r="I37" s="7"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6">
+        <f>SUM(K5:K36)</f>
+        <v>28576604</v>
+      </c>
+      <c r="L37" s="7"/>
+      <c r="M37" s="6">
+        <f>SUM(M5:M36)</f>
+        <v>61795688</v>
+      </c>
+      <c r="N37" s="6">
+        <f t="shared" ref="N37:O37" si="36">SUM(N5:N36)</f>
+        <v>667619.04761904769</v>
+      </c>
+      <c r="O37" s="6">
+        <f t="shared" si="36"/>
+        <v>62463307.047619075</v>
+      </c>
+      <c r="P37" s="7"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
         <v>333</v>
       </c>
-      <c r="G36">
+      <c r="G38">
         <f>SUM(G8:G12)+SUM(G13:G29)</f>
         <v>17</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H38" s="5">
         <f>SUMPRODUCT(G8:G12,H8:H12)+SUMPRODUCT(G13:G29,H13:H29)</f>
         <v>17200000</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C37" t="s">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
         <v>334</v>
       </c>
-      <c r="G37">
-        <f>G35-G36</f>
-        <v>5</v>
-      </c>
-      <c r="H37" s="5">
-        <f>H35-H36</f>
-        <v>6500000</v>
+      <c r="G39">
+        <f>G37-G38</f>
+        <v>7</v>
+      </c>
+      <c r="H39" s="5">
+        <f>H37-H38</f>
+        <v>7730000</v>
       </c>
     </row>
   </sheetData>
@@ -7019,7 +7144,7 @@
         <v>403</v>
       </c>
       <c r="C8">
-        <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")</f>
+        <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")</f>
         <v>3</v>
       </c>
       <c r="D8" s="9">
@@ -7029,7 +7154,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="15">
-        <f>MIN(2,IF(C8&gt;0,SUMIFS(Штат!$L$5:$L$34,Штат!$B$5:$B$34,"Департамент социологических*",Штат!$E$5:$E$34,"штат")/C8,0))</f>
+        <f>MIN(2,IF(C8&gt;0,SUMIFS(Штат!$L$5:$L$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")/C8,0))</f>
         <v>2</v>
       </c>
       <c r="G8" s="5">
@@ -7042,7 +7167,7 @@
         <v>404</v>
       </c>
       <c r="C9">
-        <f>SUMIFS(Штат!$G$5:$G$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")</f>
+        <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
         <v>7</v>
       </c>
       <c r="D9" s="9">
@@ -7052,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="15">
-        <f>MIN(2,IF(C9&gt;0,SUMIFS(Штат!$L$5:$L$34,Штат!$B$5:$B$34,"Департамент проектного управления*",Штат!$E$5:$E$34,"штат")/C9,0))</f>
+        <f>MIN(2,IF(C9&gt;0,SUMIFS(Штат!$L$5:$L$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")/C9,0))</f>
         <v>1.7142857142857142</v>
       </c>
       <c r="G9" s="5">
@@ -7193,7 +7318,7 @@
         <v>100</v>
       </c>
       <c r="D5" s="9">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E5" s="10">
         <v>450000</v>
@@ -7209,7 +7334,7 @@
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I42" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
-        <v>7650000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7223,7 +7348,7 @@
         <v>100</v>
       </c>
       <c r="D6" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="10">
         <v>900000</v>
@@ -7239,7 +7364,7 @@
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
-        <v>1800000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7283,7 +7408,7 @@
         <v>107</v>
       </c>
       <c r="D8" s="9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E8" s="10">
         <v>200000</v>
@@ -7299,7 +7424,7 @@
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>3800000</v>
+        <v>4200000</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7463,7 +7588,7 @@
       </c>
       <c r="E14" s="10">
         <f>(D8*E8+D9*E9+D10*E10+D11*E11+D12*E12+D13*E13)*Сборка_мебели_проц</f>
-        <v>792000</v>
+        <v>832000</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>101</v>
@@ -7476,7 +7601,7 @@
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>792000</v>
+        <v>832000</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7762,7 +7887,7 @@
         <v>100</v>
       </c>
       <c r="D24" s="9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E24" s="10">
         <f>ROUND(4118/(1+НДС),0)</f>
@@ -7779,7 +7904,7 @@
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>74550</v>
+        <v>81650</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8598,7 +8723,7 @@
         <v>130</v>
       </c>
       <c r="D52" s="9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E52" s="10">
         <v>7000</v>
@@ -8614,7 +8739,7 @@
       </c>
       <c r="I52" s="5">
         <f t="shared" si="4"/>
-        <v>266000</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9057,20 +9182,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>420</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
@@ -9324,20 +9449,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>443</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -380,7 +380,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="488">
   <si>
     <t>Статья</t>
   </si>
@@ -1520,9 +1520,6 @@
   </si>
   <si>
     <t>Проектный офис для Центральной Азии по изменению климата и зеленой энергетике</t>
-  </si>
-  <si>
-    <t>Менеджер проектов</t>
   </si>
   <si>
     <t>Руководитель проектного офиса «Таза Қазақстан»</t>
@@ -1861,16 +1858,16 @@
     <t>[Қаражан Е.Н.] Общее руководство Фондом и проектным офисом, руководство Проектным офисом для Центральной Азии, соглашение с МЭПР, отчётность перед органами Фонда. Опыт: к.э.н. (PhD), MSc LSE («Болашақ»), Chevening; ГИД ЦАКФ с 02.2025 (Региональный экологический саммит 2026); председатель Правления ИЭИ, советник Министра национальной экономики, консультант АБР, директор по устойчивому развитию ФНБ «Самрук-Қазына».</t>
   </si>
   <si>
-    <t>Эксперт-эколог</t>
-  </si>
-  <si>
     <t>[Загирова Анастасия] Экологическая экспертиза, данные о состоянии окружающей среды, методические материалы</t>
   </si>
   <si>
-    <t>Эксперт</t>
-  </si>
-  <si>
     <t>[Абулхан А.] Молодёжь, волонтёры, НПО, школы и вузы; экспертиза молодёжных и общественных проектов</t>
+  </si>
+  <si>
+    <t>Заместитель руководителя ПО для ЦА</t>
+  </si>
+  <si>
+    <t>Менеджер проектов – эколог</t>
   </si>
 </sst>
 </file>
@@ -2579,7 +2576,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -2718,7 +2715,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -2737,25 +2734,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>420</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>422</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>423</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>424</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2767,13 +2764,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>457</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>458</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -2788,13 +2785,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B6" s="57" t="s">
+        <v>458</v>
+      </c>
+      <c r="C6" s="55" t="s">
         <v>459</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>460</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -2810,13 +2807,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -2832,7 +2829,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="59" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="55"/>
@@ -2845,7 +2842,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51"/>
       <c r="B9" s="60" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
@@ -2902,7 +2899,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -2921,25 +2918,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>420</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>422</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>423</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>424</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2951,13 +2948,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D5" s="55">
         <v>6</v>
@@ -2972,13 +2969,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -2994,13 +2991,13 @@
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3015,13 +3012,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D8" s="55">
         <v>9</v>
@@ -3036,13 +3033,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D9" s="74">
         <v>32</v>
@@ -3057,13 +3054,13 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D10" s="55">
         <v>3</v>
@@ -3078,13 +3075,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D11" s="55">
         <v>3</v>
@@ -3101,7 +3098,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="59" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="55"/>
@@ -3114,7 +3111,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
@@ -3168,7 +3165,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -3187,25 +3184,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>420</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>422</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>423</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>424</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3217,13 +3214,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3238,13 +3235,13 @@
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3261,7 +3258,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="59" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="55"/>
@@ -3274,7 +3271,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="60" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -3331,7 +3328,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -3350,25 +3347,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>420</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>422</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>423</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>424</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3380,13 +3377,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3402,7 +3399,7 @@
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51"/>
       <c r="B6" s="59" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="55"/>
@@ -3416,7 +3413,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="60" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
@@ -4378,7 +4375,7 @@
         <v>701000</v>
       </c>
       <c r="C15" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4737,7 +4734,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -4806,7 +4803,7 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
@@ -4867,15 +4864,15 @@
         <v>5454690</v>
       </c>
       <c r="N5" s="18">
-        <f>IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" ref="N5:N36" si="4">IF(AND(E5="штат",F5="новая"),ОСНС_полис*G5/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
         <v>0</v>
       </c>
       <c r="O5" s="18">
-        <f t="shared" ref="O5:O36" si="4">M5+N5</f>
+        <f t="shared" ref="O5:O36" si="5">M5+N5</f>
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -4886,7 +4883,7 @@
         <v>274</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -4923,15 +4920,15 @@
         <v>4784010</v>
       </c>
       <c r="N6" s="18">
-        <f>IF(AND(E6="штат",F6="новая"),ОСНС_полис*G6/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O6" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -4979,11 +4976,11 @@
         <v>4784010</v>
       </c>
       <c r="N7" s="18">
-        <f>IF(AND(E7="штат",F7="новая"),ОСНС_полис*G7/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O7" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
@@ -4998,7 +4995,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -5035,15 +5032,15 @@
         <v>3189340</v>
       </c>
       <c r="N8" s="18">
-        <f>IF(AND(E8="штат",F8="новая"),ОСНС_полис*G8/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O8" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3222720.9523809524</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5075,31 +5072,31 @@
         <v>2</v>
       </c>
       <c r="J9" s="18">
-        <f t="shared" ref="J9:J11" si="5">IF(E9="штат",ROUND(Ставка_СН*H9*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H9+Ставка_СО*MIN(H9*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H9,Кап_ООСМС*МЗП),0),ROUND(H9*НДС,0))</f>
+        <f t="shared" ref="J9:J11" si="6">IF(E9="штат",ROUND(Ставка_СН*H9*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H9+Ставка_СО*MIN(H9*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H9,Кап_ООСМС*МЗП),0),ROUND(H9*НДС,0))</f>
         <v>182890</v>
       </c>
       <c r="K9" s="18">
-        <f t="shared" ref="K9:K11" si="6">G9*(H9+J9)</f>
+        <f t="shared" ref="K9:K11" si="7">G9*(H9+J9)</f>
         <v>1482890</v>
       </c>
       <c r="L9" s="19">
-        <f t="shared" ref="L9:L11" si="7">IF(AND(F9="новая",I9=1),Мес_2026_новые,MAX(0,4-I9))</f>
+        <f t="shared" ref="L9:L11" si="8">IF(AND(F9="новая",I9=1),Мес_2026_новые,MAX(0,4-I9))</f>
         <v>2</v>
       </c>
       <c r="M9" s="18">
-        <f t="shared" ref="M9:M11" si="8">K9*L9</f>
+        <f t="shared" ref="M9:M11" si="9">K9*L9</f>
         <v>2965780</v>
       </c>
       <c r="N9" s="18">
-        <f>IF(AND(E9="штат",F9="новая"),ОСНС_полис*G9/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O9" s="18">
-        <f t="shared" ref="O9:O11" si="9">M9+N9</f>
+        <f t="shared" ref="O9:O11" si="10">M9+N9</f>
         <v>2999160.9523809524</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5110,7 +5107,7 @@
         <v>246</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>249</v>
@@ -5131,31 +5128,31 @@
         <v>2</v>
       </c>
       <c r="J10" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>147550</v>
       </c>
       <c r="K10" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1147550</v>
       </c>
       <c r="L10" s="19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="M10" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2295100</v>
       </c>
       <c r="N10" s="18">
-        <f>IF(AND(E10="штат",F10="новая"),ОСНС_полис*G10/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O10" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2328480.9523809524</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5166,7 +5163,7 @@
         <v>246</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>249</v>
@@ -5187,31 +5184,31 @@
         <v>2</v>
       </c>
       <c r="J11" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>112000</v>
       </c>
       <c r="K11" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L11" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="M11" s="22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="22">
-        <f>IF(AND(E11="штат",F11="новая"),ОСНС_полис*G11/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
+      <c r="N11" s="22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="22">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="P11" s="21" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5259,11 +5256,11 @@
         <v>2295100</v>
       </c>
       <c r="N12" s="18">
-        <f>IF(AND(E12="штат",F12="новая"),ОСНС_полис*G12/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O12" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2328480.9523809524</v>
       </c>
       <c r="P12" s="17" t="s">
@@ -5299,15 +5296,15 @@
         <v>2</v>
       </c>
       <c r="J13" s="18">
-        <f t="shared" ref="J13" si="10">IF(E13="штат",ROUND(Ставка_СН*H13*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H13+Ставка_СО*MIN(H13*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H13,Кап_ООСМС*МЗП),0),ROUND(H13*НДС,0))</f>
+        <f t="shared" ref="J13" si="11">IF(E13="штат",ROUND(Ставка_СН*H13*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H13+Ставка_СО*MIN(H13*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H13,Кап_ООСМС*МЗП),0),ROUND(H13*НДС,0))</f>
         <v>159330</v>
       </c>
       <c r="K13" s="18">
-        <f t="shared" ref="K13" si="11">G13*(H13+J13)</f>
+        <f t="shared" ref="K13" si="12">G13*(H13+J13)</f>
         <v>1259330</v>
       </c>
       <c r="L13" s="19">
-        <f t="shared" ref="L13" si="12">IF(AND(F13="новая",I13=1),Мес_2026_новые,MAX(0,4-I13))</f>
+        <f t="shared" ref="L13" si="13">IF(AND(F13="новая",I13=1),Мес_2026_новые,MAX(0,4-I13))</f>
         <v>2</v>
       </c>
       <c r="M13" s="18">
@@ -5315,11 +5312,11 @@
         <v>2518660</v>
       </c>
       <c r="N13" s="18">
-        <f>IF(AND(E13="штат",F13="новая"),ОСНС_полис*G13/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O13" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2552040.9523809524</v>
       </c>
       <c r="P13" s="17" t="s">
@@ -5371,15 +5368,15 @@
         <v>2295100</v>
       </c>
       <c r="N14" s="18">
-        <f>IF(AND(E14="штат",F14="новая"),ОСНС_полис*G14/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O14" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2328480.9523809524</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -5427,15 +5424,15 @@
         <v>2295100</v>
       </c>
       <c r="N15" s="18">
-        <f>IF(AND(E15="штат",F15="новая"),ОСНС_полис*G15/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O15" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2328480.9523809524</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5483,15 +5480,15 @@
         <v>2295100</v>
       </c>
       <c r="N16" s="18">
-        <f>IF(AND(E16="штат",F16="новая"),ОСНС_полис*G16/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O16" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2328480.9523809524</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5523,31 +5520,31 @@
         <v>3</v>
       </c>
       <c r="J17" s="18">
-        <f t="shared" ref="J17:J18" si="13">IF(E17="штат",ROUND(Ставка_СН*H17*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H17+Ставка_СО*MIN(H17*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H17,Кап_ООСМС*МЗП),0),ROUND(H17*НДС,0))</f>
+        <f t="shared" ref="J17:J18" si="14">IF(E17="штат",ROUND(Ставка_СН*H17*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H17+Ставка_СО*MIN(H17*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H17,Кап_ООСМС*МЗП),0),ROUND(H17*НДС,0))</f>
         <v>147550</v>
       </c>
       <c r="K17" s="18">
-        <f t="shared" ref="K17:K18" si="14">G17*(H17+J17)</f>
+        <f t="shared" ref="K17:K18" si="15">G17*(H17+J17)</f>
         <v>1147550</v>
       </c>
       <c r="L17" s="19">
-        <f t="shared" ref="L17:L18" si="15">IF(AND(F17="новая",I17=1),Мес_2026_новые,MAX(0,4-I17))</f>
+        <f t="shared" ref="L17:L18" si="16">IF(AND(F17="новая",I17=1),Мес_2026_новые,MAX(0,4-I17))</f>
         <v>1</v>
       </c>
       <c r="M17" s="18">
-        <f t="shared" ref="M17:M18" si="16">K17*L17</f>
+        <f t="shared" ref="M17:M18" si="17">K17*L17</f>
         <v>1147550</v>
       </c>
       <c r="N17" s="18">
-        <f>IF(AND(E17="штат",F17="новая"),ОСНС_полис*G17/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O17" s="18">
-        <f t="shared" ref="O17:O18" si="17">M17+N17</f>
+        <f t="shared" ref="O17:O18" si="18">M17+N17</f>
         <v>1180930.9523809524</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5579,31 +5576,31 @@
         <v>3</v>
       </c>
       <c r="J18" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>112210</v>
       </c>
       <c r="K18" s="18">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>812210</v>
       </c>
       <c r="L18" s="19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="M18" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>812210</v>
       </c>
       <c r="N18" s="18">
-        <f>IF(AND(E18="штат",F18="новая"),ОСНС_полис*G18/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O18" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>845590.95238095243</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5651,15 +5648,15 @@
         <v>1624420</v>
       </c>
       <c r="N19" s="18">
-        <f>IF(AND(E19="штат",F19="новая"),ОСНС_полис*G19/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O19" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1657800.9523809524</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -5691,15 +5688,15 @@
         <v>2</v>
       </c>
       <c r="J20" s="18">
-        <f t="shared" ref="J20" si="18">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
+        <f t="shared" ref="J20" si="19">IF(E20="штат",ROUND(Ставка_СН*H20*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H20+Ставка_СО*MIN(H20*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H20,Кап_ООСМС*МЗП),0),ROUND(H20*НДС,0))</f>
         <v>182890</v>
       </c>
       <c r="K20" s="18">
-        <f t="shared" ref="K20" si="19">G20*(H20+J20)</f>
+        <f t="shared" ref="K20" si="20">G20*(H20+J20)</f>
         <v>1482890</v>
       </c>
       <c r="L20" s="19">
-        <f t="shared" ref="L20" si="20">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
+        <f t="shared" ref="L20" si="21">IF(AND(F20="новая",I20=1),Мес_2026_новые,MAX(0,4-I20))</f>
         <v>2</v>
       </c>
       <c r="M20" s="18">
@@ -5707,15 +5704,15 @@
         <v>2965780</v>
       </c>
       <c r="N20" s="18">
-        <f>IF(AND(E20="штат",F20="новая"),ОСНС_полис*G20/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O20" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2999160.9523809524</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5763,11 +5760,11 @@
         <v>0</v>
       </c>
       <c r="N21" s="22">
-        <f>IF(AND(E21="штат",F21="новая"),ОСНС_полис*G21/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O21" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
@@ -5819,15 +5816,15 @@
         <v>2965780</v>
       </c>
       <c r="N22" s="18">
-        <f>IF(AND(E22="штат",F22="новая"),ОСНС_полис*G22/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O22" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2999160.9523809524</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -5875,15 +5872,15 @@
         <v>2295100</v>
       </c>
       <c r="N23" s="18">
-        <f>IF(AND(E23="штат",F23="новая"),ОСНС_полис*G23/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O23" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2328480.9523809524</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -5931,11 +5928,11 @@
         <v>0</v>
       </c>
       <c r="N24" s="22">
-        <f>IF(AND(E24="штат",F24="новая"),ОСНС_полис*G24/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O24" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
@@ -5971,15 +5968,15 @@
         <v>2</v>
       </c>
       <c r="J25" s="22">
-        <f t="shared" ref="J25" si="21">IF(E25="штат",ROUND(Ставка_СН*H25*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H25+Ставка_СО*MIN(H25*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H25,Кап_ООСМС*МЗП),0),ROUND(H25*НДС,0))</f>
+        <f t="shared" ref="J25" si="22">IF(E25="штат",ROUND(Ставка_СН*H25*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H25+Ставка_СО*MIN(H25*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H25,Кап_ООСМС*МЗП),0),ROUND(H25*НДС,0))</f>
         <v>112000</v>
       </c>
       <c r="K25" s="22">
-        <f t="shared" ref="K25" si="22">G25*(H25+J25)</f>
+        <f t="shared" ref="K25" si="23">G25*(H25+J25)</f>
         <v>0</v>
       </c>
       <c r="L25" s="23">
-        <f t="shared" ref="L25" si="23">IF(AND(F25="новая",I25=1),Мес_2026_новые,MAX(0,4-I25))</f>
+        <f t="shared" ref="L25" si="24">IF(AND(F25="новая",I25=1),Мес_2026_новые,MAX(0,4-I25))</f>
         <v>2</v>
       </c>
       <c r="M25" s="22">
@@ -5987,11 +5984,11 @@
         <v>0</v>
       </c>
       <c r="N25" s="22">
-        <f>IF(AND(E25="штат",F25="новая"),ОСНС_полис*G25/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O25" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P25" s="21" t="s">
@@ -6006,7 +6003,7 @@
         <v>256</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>216</v>
@@ -6043,15 +6040,15 @@
         <v>1624420</v>
       </c>
       <c r="N26" s="18">
-        <f>IF(AND(E26="штат",F26="новая"),ОСНС_полис*G26/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O26" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1657800.9523809524</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -6099,15 +6096,15 @@
         <v>2295100</v>
       </c>
       <c r="N27" s="18">
-        <f>IF(AND(E27="штат",F27="новая"),ОСНС_полис*G27/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O27" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2328480.9523809524</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -6139,11 +6136,11 @@
         <v>2</v>
       </c>
       <c r="J28" s="18">
-        <f t="shared" ref="J28:J36" si="24">IF(E28="штат",ROUND(Ставка_СН*H28*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H28+Ставка_СО*MIN(H28*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H28,Кап_ООСМС*МЗП),0),ROUND(H28*НДС,0))</f>
+        <f t="shared" ref="J28:J36" si="25">IF(E28="штат",ROUND(Ставка_СН*H28*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H28+Ставка_СО*MIN(H28*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H28,Кап_ООСМС*МЗП),0),ROUND(H28*НДС,0))</f>
         <v>112210</v>
       </c>
       <c r="K28" s="18">
-        <f t="shared" ref="K28:K36" si="25">G28*(H28+J28)</f>
+        <f t="shared" ref="K28:K36" si="26">G28*(H28+J28)</f>
         <v>812210</v>
       </c>
       <c r="L28" s="19">
@@ -6155,11 +6152,11 @@
         <v>1624420</v>
       </c>
       <c r="N28" s="18">
-        <f>IF(AND(E28="штат",F28="новая"),ОСНС_полис*G28/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O28" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1657800.9523809524</v>
       </c>
       <c r="P28" s="17" t="s">
@@ -6195,11 +6192,11 @@
         <v>2</v>
       </c>
       <c r="J29" s="22">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>112000</v>
       </c>
       <c r="K29" s="22">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="L29" s="23">
@@ -6211,11 +6208,11 @@
         <v>0</v>
       </c>
       <c r="N29" s="22">
-        <f>IF(AND(E29="штат",F29="новая"),ОСНС_полис*G29/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O29" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
@@ -6251,11 +6248,11 @@
         <v>1</v>
       </c>
       <c r="J30" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>194670</v>
       </c>
       <c r="K30" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1594670</v>
       </c>
       <c r="L30" s="19">
@@ -6267,11 +6264,11 @@
         <v>4784010</v>
       </c>
       <c r="N30" s="18">
-        <f>IF(AND(E30="штат",F30="новая"),ОСНС_полис*G30/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O30" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4784010</v>
       </c>
       <c r="P30" s="17" t="s">
@@ -6307,11 +6304,11 @@
         <v>2</v>
       </c>
       <c r="J31" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>112210</v>
       </c>
       <c r="K31" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>812210</v>
       </c>
       <c r="L31" s="19">
@@ -6323,11 +6320,11 @@
         <v>1624420</v>
       </c>
       <c r="N31" s="18">
-        <f>IF(AND(E31="штат",F31="новая"),ОСНС_полис*G31/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O31" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1657800.9523809524</v>
       </c>
       <c r="P31" s="17" t="s">
@@ -6342,10 +6339,10 @@
         <v>379</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>380</v>
+        <v>486</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>80</v>
@@ -6363,11 +6360,11 @@
         <v>2</v>
       </c>
       <c r="J32" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>147550</v>
       </c>
       <c r="K32" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="L32" s="19">
@@ -6379,11 +6376,11 @@
         <v>0</v>
       </c>
       <c r="N32" s="18">
-        <f>IF(AND(E32="штат",F32="новая"),ОСНС_полис*G32/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O32" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P32" s="17" t="s">
@@ -6398,10 +6395,10 @@
         <v>379</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>80</v>
@@ -6419,31 +6416,31 @@
         <v>2</v>
       </c>
       <c r="J33" s="18">
-        <f t="shared" ref="J33" si="26">IF(E33="штат",ROUND(Ставка_СН*H33*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H33+Ставка_СО*MIN(H33*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H33,Кап_ООСМС*МЗП),0),ROUND(H33*НДС,0))</f>
+        <f t="shared" ref="J33" si="27">IF(E33="штат",ROUND(Ставка_СН*H33*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H33+Ставка_СО*MIN(H33*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H33,Кап_ООСМС*МЗП),0),ROUND(H33*НДС,0))</f>
         <v>100122</v>
       </c>
       <c r="K33" s="18">
-        <f t="shared" ref="K33" si="27">G33*(H33+J33)</f>
+        <f t="shared" ref="K33" si="28">G33*(H33+J33)</f>
         <v>715122</v>
       </c>
       <c r="L33" s="19">
-        <f t="shared" ref="L33" si="28">IF(AND(F33="новая",I33=1),Мес_2026_новые,MAX(0,4-I33))</f>
+        <f t="shared" ref="L33" si="29">IF(AND(F33="новая",I33=1),Мес_2026_новые,MAX(0,4-I33))</f>
         <v>2</v>
       </c>
       <c r="M33" s="18">
-        <f t="shared" ref="M33" si="29">K33*L33</f>
+        <f t="shared" ref="M33" si="30">K33*L33</f>
         <v>1430244</v>
       </c>
       <c r="N33" s="18">
-        <f>IF(AND(E33="штат",F33="новая"),ОСНС_полис*G33/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O33" s="18">
-        <f t="shared" ref="O33" si="30">M33+N33</f>
+        <f t="shared" ref="O33" si="31">M33+N33</f>
         <v>1463624.9523809524</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="34" spans="1:16" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6457,7 +6454,7 @@
         <v>487</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>80</v>
@@ -6475,31 +6472,31 @@
         <v>2</v>
       </c>
       <c r="J34" s="18">
-        <f t="shared" ref="J34" si="31">IF(E34="штат",ROUND(Ставка_СН*H34*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H34+Ставка_СО*MIN(H34*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H34,Кап_ООСМС*МЗП),0),ROUND(H34*НДС,0))</f>
+        <f t="shared" ref="J34" si="32">IF(E34="штат",ROUND(Ставка_СН*H34*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H34+Ставка_СО*MIN(H34*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H34,Кап_ООСМС*МЗП),0),ROUND(H34*НДС,0))</f>
         <v>100122</v>
       </c>
       <c r="K34" s="18">
-        <f t="shared" ref="K34" si="32">G34*(H34+J34)</f>
+        <f t="shared" ref="K34" si="33">G34*(H34+J34)</f>
         <v>715122</v>
       </c>
       <c r="L34" s="19">
-        <f t="shared" ref="L34" si="33">IF(AND(F34="новая",I34=1),Мес_2026_новые,MAX(0,4-I34))</f>
+        <f t="shared" ref="L34" si="34">IF(AND(F34="новая",I34=1),Мес_2026_новые,MAX(0,4-I34))</f>
         <v>2</v>
       </c>
       <c r="M34" s="18">
-        <f t="shared" ref="M34" si="34">K34*L34</f>
+        <f t="shared" ref="M34" si="35">K34*L34</f>
         <v>1430244</v>
       </c>
       <c r="N34" s="18">
-        <f>IF(AND(E34="штат",F34="новая"),ОСНС_полис*G34/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>33380.952380952382</v>
       </c>
       <c r="O34" s="18">
-        <f t="shared" ref="O34" si="35">M34+N34</f>
+        <f t="shared" ref="O34" si="36">M34+N34</f>
         <v>1463624.9523809524</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6531,11 +6528,11 @@
         <v>2</v>
       </c>
       <c r="J35" s="22">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>138800</v>
       </c>
       <c r="K35" s="22">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="L35" s="23">
@@ -6547,11 +6544,11 @@
         <v>0</v>
       </c>
       <c r="N35" s="22">
-        <f>IF(AND(E35="штат",F35="новая"),ОСНС_полис*G35/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O35" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P35" s="21" t="s">
@@ -6587,11 +6584,11 @@
         <v>2</v>
       </c>
       <c r="J36" s="22">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>68096</v>
       </c>
       <c r="K36" s="22">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="L36" s="23">
@@ -6603,11 +6600,11 @@
         <v>0</v>
       </c>
       <c r="N36" s="22">
-        <f>IF(AND(E36="штат",F36="новая"),ОСНС_полис*G36/COUNTIFS($E$5:$E$36,"штат",$F$5:$F$36,"новая"),0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O36" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P36" s="21" t="s">
@@ -6643,11 +6640,11 @@
         <v>61795688</v>
       </c>
       <c r="N37" s="6">
-        <f t="shared" ref="N37:O37" si="36">SUM(N5:N36)</f>
+        <f t="shared" ref="N37:O37" si="37">SUM(N5:N36)</f>
         <v>667619.04761904769</v>
       </c>
       <c r="O37" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>62463307.047619075</v>
       </c>
       <c r="P37" s="7"/>
@@ -6744,7 +6741,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>214</v>
@@ -6779,7 +6776,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>214</v>
@@ -6922,13 +6919,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>400</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="D9" s="27" t="s">
         <v>401</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>402</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -7061,7 +7058,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>91</v>
@@ -7141,7 +7138,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")</f>
@@ -7164,7 +7161,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
@@ -7210,7 +7207,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -7330,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I42" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -7900,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -8205,7 +8202,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -8276,7 +8273,7 @@
         <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C37" t="s">
         <v>100</v>
@@ -8295,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" ref="I37:I39" si="3">IF(F37="разово",IF(G37&lt;=3,D37*E37,0),IF(F37="мес",D37*E37*MAX(0,4-G37),D37*E37*MAX(0,4-G37)/12))</f>
@@ -8307,7 +8304,7 @@
         <v>98</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C38" t="s">
         <v>104</v>
@@ -8326,7 +8323,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="3"/>
@@ -8338,7 +8335,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -8357,7 +8354,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="3"/>
@@ -9021,7 +9018,7 @@
         <v>285</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C5" t="s">
         <v>244</v>
@@ -9041,7 +9038,7 @@
         <v>285</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C6" t="s">
         <v>244</v>
@@ -9081,7 +9078,7 @@
         <v>285</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C8" t="s">
         <v>244</v>
@@ -9101,7 +9098,7 @@
         <v>285</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C9" t="s">
         <v>244</v>
@@ -9121,7 +9118,7 @@
         <v>285</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C10" t="s">
         <v>244</v>
@@ -9183,7 +9180,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -9202,25 +9199,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>420</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>422</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>423</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>424</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -9232,13 +9229,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
+        <v>426</v>
+      </c>
+      <c r="B5" s="54" t="s">
         <v>427</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="C5" s="55" t="s">
         <v>428</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>429</v>
       </c>
       <c r="D5" s="55">
         <v>56</v>
@@ -9253,13 +9250,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" s="57" t="s">
         <v>430</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="C6" s="55" t="s">
         <v>431</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>432</v>
       </c>
       <c r="D6" s="55">
         <v>56</v>
@@ -9275,13 +9272,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
+        <v>432</v>
+      </c>
+      <c r="B7" s="57" t="s">
         <v>433</v>
       </c>
-      <c r="B7" s="57" t="s">
-        <v>434</v>
-      </c>
       <c r="C7" s="55" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D7" s="55">
         <v>6</v>
@@ -9296,13 +9293,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="B8" s="57" t="s">
         <v>435</v>
       </c>
-      <c r="B8" s="57" t="s">
-        <v>436</v>
-      </c>
       <c r="C8" s="55" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D8" s="55">
         <v>6</v>
@@ -9317,13 +9314,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
+        <v>436</v>
+      </c>
+      <c r="B9" s="57" t="s">
         <v>437</v>
       </c>
-      <c r="B9" s="57" t="s">
-        <v>438</v>
-      </c>
       <c r="C9" s="55" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D9" s="55">
         <v>6</v>
@@ -9338,13 +9335,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
+        <v>438</v>
+      </c>
+      <c r="B10" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="B10" s="57" t="s">
-        <v>440</v>
-      </c>
       <c r="C10" s="55" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D10" s="55">
         <v>48</v>
@@ -9360,7 +9357,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="59" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="55"/>
@@ -9373,7 +9370,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="60" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>
@@ -9450,7 +9447,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -9469,25 +9466,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>420</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>422</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>423</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>424</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -9499,13 +9496,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>443</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>444</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>445</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -9520,13 +9517,13 @@
     </row>
     <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -9542,13 +9539,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -9563,13 +9560,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B8" s="57" t="s">
+        <v>447</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>448</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>449</v>
       </c>
       <c r="D8" s="55">
         <v>1</v>
@@ -9584,13 +9581,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B9" s="57" t="s">
+        <v>449</v>
+      </c>
+      <c r="C9" s="55" t="s">
         <v>450</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>451</v>
       </c>
       <c r="D9" s="74">
         <v>100</v>
@@ -9605,13 +9602,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D10" s="74">
         <v>100</v>
@@ -9627,10 +9624,10 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="57" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D11" s="74">
         <v>1</v>
@@ -9645,13 +9642,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D12" s="55">
         <v>4</v>
@@ -9666,13 +9663,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51" t="s">
+        <v>453</v>
+      </c>
+      <c r="B13" s="75" t="s">
         <v>454</v>
       </c>
-      <c r="B13" s="75" t="s">
-        <v>455</v>
-      </c>
       <c r="C13" s="76" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D13" s="76">
         <v>1</v>
@@ -9688,7 +9685,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="51"/>
       <c r="B14" s="59" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="55"/>
@@ -9701,7 +9698,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -1558,12 +1558,6 @@
     <t>[Тулесова А.] Ведение проектов и закреплённых регионов, мониторинг мероприятий, отчётность</t>
   </si>
   <si>
-    <t>[Арманов Р.] Ведение проектов и закреплённых регионов, мониторинг мероприятий (с декабря 2026)</t>
-  </si>
-  <si>
-    <t>[Мирам А.] Ведение проектов и закреплённых регионов, сбор данных (с декабря 2026)</t>
-  </si>
-  <si>
     <t>[Өміртай А.] Руководитель департамента социологии: программа исследований, методология измерения поведения, ежегодный доклад</t>
   </si>
   <si>
@@ -1589,9 +1583,6 @@
   </si>
   <si>
     <t>Департамент социологических исследований и аналитики (3 чел.)</t>
-  </si>
-  <si>
-    <t>Департамент проектного управления и региональной координации (7 чел., из них 2 – с декабря)</t>
   </si>
   <si>
     <t>Группа «Коммуникация и креатив» (5 чел.): съёмки и освещение мероприятий в регионах</t>
@@ -1868,6 +1859,15 @@
   </si>
   <si>
     <t>Менеджер проектов – эколог</t>
+  </si>
+  <si>
+    <t>[Арманов Р.] Ведение проектов и закреплённых регионов, мониторинг мероприятий</t>
+  </si>
+  <si>
+    <t>[Мирам А.] Ведение проектов и закреплённых регионов, сбор данных</t>
+  </si>
+  <si>
+    <t>Департамент проектного управления и региональной координации (5 чел.)</t>
   </si>
 </sst>
 </file>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E36,"штат",Штат!G5:G36)</f>
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B5" s="37">
         <f>Штат!G38</f>
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M36,Штат!E5:E36,"штат")</f>
-        <v>61795688</v>
+        <v>58353038</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B8" s="38">
         <f>Штат!N37</f>
-        <v>667619.04761904769</v>
+        <v>600857.14285714284</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
-        <v>4108650</v>
+        <v>3799012.5</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="B10" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Оснащение")</f>
-        <v>22439688</v>
+        <v>21992588</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Цифровые")</f>
-        <v>491000</v>
+        <v>463000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>121153508.54439324</v>
+        <v>116859359.13963135</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Прочие")</f>
-        <v>12182017.521105992</v>
+        <v>11752602.580629801</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>21333684.170479879</v>
+        <v>20577913.875241783</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>154669210.23597911</v>
+        <v>149189875.59550291</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>241903530.23597911</v>
+        <v>236424195.59550291</v>
       </c>
     </row>
   </sheetData>
@@ -2715,7 +2715,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -2734,25 +2734,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>421</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>422</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2764,13 +2764,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -2785,13 +2785,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -2829,7 +2829,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="59" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="55"/>
@@ -2842,7 +2842,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51"/>
       <c r="B9" s="60" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
@@ -2899,7 +2899,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -2918,25 +2918,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>421</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>422</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2948,13 +2948,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D5" s="55">
         <v>6</v>
@@ -2969,13 +2969,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -2991,13 +2991,13 @@
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3012,13 +3012,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D8" s="55">
         <v>9</v>
@@ -3033,13 +3033,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D9" s="74">
         <v>32</v>
@@ -3054,13 +3054,13 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D10" s="55">
         <v>3</v>
@@ -3075,13 +3075,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D11" s="55">
         <v>3</v>
@@ -3098,7 +3098,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="59" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="55"/>
@@ -3111,7 +3111,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
@@ -3165,7 +3165,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -3184,25 +3184,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>421</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>422</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3214,13 +3214,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3235,13 +3235,13 @@
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="59" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="55"/>
@@ -3271,7 +3271,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="60" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -3328,7 +3328,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -3347,25 +3347,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>421</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>422</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3377,13 +3377,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3399,7 +3399,7 @@
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51"/>
       <c r="B6" s="59" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="55"/>
@@ -3413,7 +3413,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="60" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
@@ -4375,7 +4375,7 @@
         <v>701000</v>
       </c>
       <c r="C15" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4734,7 +4734,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -4803,7 +4803,7 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
@@ -4872,7 +4872,7 @@
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -4883,7 +4883,7 @@
         <v>274</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -4928,7 +4928,7 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -5069,7 +5069,7 @@
         <v>1300000</v>
       </c>
       <c r="I9" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="18">
         <f t="shared" ref="J9:J11" si="6">IF(E9="штат",ROUND(Ставка_СН*H9*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H9+Ставка_СО*MIN(H9*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H9,Кап_ООСМС*МЗП),0),ROUND(H9*НДС,0))</f>
@@ -5081,11 +5081,11 @@
       </c>
       <c r="L9" s="19">
         <f t="shared" ref="L9:L11" si="8">IF(AND(F9="новая",I9=1),Мес_2026_новые,MAX(0,4-I9))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="18">
         <f t="shared" ref="M9:M11" si="9">K9*L9</f>
-        <v>2965780</v>
+        <v>1482890</v>
       </c>
       <c r="N9" s="18">
         <f t="shared" si="4"/>
@@ -5093,10 +5093,10 @@
       </c>
       <c r="O9" s="18">
         <f t="shared" ref="O9:O11" si="10">M9+N9</f>
-        <v>2999160.9523809524</v>
+        <v>1516270.9523809524</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5107,7 +5107,7 @@
         <v>246</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>249</v>
@@ -5152,7 +5152,7 @@
         <v>2328480.9523809524</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5163,7 +5163,7 @@
         <v>246</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>249</v>
@@ -5208,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5511,7 +5511,7 @@
         <v>83</v>
       </c>
       <c r="G17" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="18">
         <v>1000000</v>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="K17" s="18">
         <f t="shared" ref="K17:K18" si="15">G17*(H17+J17)</f>
-        <v>1147550</v>
+        <v>0</v>
       </c>
       <c r="L17" s="19">
         <f t="shared" ref="L17:L18" si="16">IF(AND(F17="новая",I17=1),Мес_2026_новые,MAX(0,4-I17))</f>
@@ -5533,18 +5533,18 @@
       </c>
       <c r="M17" s="18">
         <f t="shared" ref="M17:M18" si="17">K17*L17</f>
-        <v>1147550</v>
+        <v>0</v>
       </c>
       <c r="N17" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>0</v>
       </c>
       <c r="O17" s="18">
         <f t="shared" ref="O17:O18" si="18">M17+N17</f>
-        <v>1180930.9523809524</v>
+        <v>0</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>392</v>
+        <v>485</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5567,7 +5567,7 @@
         <v>83</v>
       </c>
       <c r="G18" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="18">
         <v>700000</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="K18" s="18">
         <f t="shared" si="15"/>
-        <v>812210</v>
+        <v>0</v>
       </c>
       <c r="L18" s="19">
         <f t="shared" si="16"/>
@@ -5589,18 +5589,18 @@
       </c>
       <c r="M18" s="18">
         <f t="shared" si="17"/>
-        <v>812210</v>
+        <v>0</v>
       </c>
       <c r="N18" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>0</v>
       </c>
       <c r="O18" s="18">
         <f t="shared" si="18"/>
-        <v>845590.95238095243</v>
+        <v>0</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>393</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6339,10 +6339,10 @@
         <v>379</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>80</v>
@@ -6395,10 +6395,10 @@
         <v>379</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>80</v>
@@ -6440,7 +6440,7 @@
         <v>1463624.9523809524</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="34" spans="1:16" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6451,10 +6451,10 @@
         <v>379</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>80</v>
@@ -6496,7 +6496,7 @@
         <v>1463624.9523809524</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6622,30 +6622,30 @@
       <c r="F37" s="7"/>
       <c r="G37" s="7">
         <f>SUM(G5:G36)</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H37" s="6">
         <f>SUMPRODUCT(G5:G36,H5:H36)</f>
-        <v>24930000</v>
+        <v>23230000</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6">
         <f>SUM(K5:K36)</f>
-        <v>28576604</v>
+        <v>26616844</v>
       </c>
       <c r="L37" s="7"/>
       <c r="M37" s="6">
         <f>SUM(M5:M36)</f>
-        <v>61795688</v>
+        <v>58353038</v>
       </c>
       <c r="N37" s="6">
         <f t="shared" ref="N37:O37" si="37">SUM(N5:N36)</f>
-        <v>667619.04761904769</v>
+        <v>600857.14285714284</v>
       </c>
       <c r="O37" s="6">
         <f t="shared" si="37"/>
-        <v>62463307.047619075</v>
+        <v>58953895.142857164</v>
       </c>
       <c r="P37" s="7"/>
     </row>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="G38">
         <f>SUM(G8:G12)+SUM(G13:G29)</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H38" s="5">
         <f>SUMPRODUCT(G8:G12,H8:H12)+SUMPRODUCT(G13:G29,H13:H29)</f>
-        <v>17200000</v>
+        <v>15500000</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -6741,7 +6741,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>214</v>
@@ -6776,7 +6776,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>214</v>
@@ -6919,13 +6919,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>397</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>398</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>399</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>400</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>401</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -7058,7 +7058,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>91</v>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")</f>
@@ -7152,20 +7152,20 @@
       </c>
       <c r="F8" s="15">
         <f>MIN(2,IF(C8&gt;0,SUMIFS(Штат!$L$5:$L$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")/C8,0))</f>
-        <v>2</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="0"/>
-        <v>712125</v>
+        <v>593437.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>403</v>
+        <v>487</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" s="9">
         <v>6</v>
@@ -7175,11 +7175,11 @@
       </c>
       <c r="F9" s="15">
         <f>MIN(2,IF(C9&gt;0,SUMIFS(Штат!$L$5:$L$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")/C9,0))</f>
-        <v>1.7142857142857142</v>
+        <v>2</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>1145699.9999999998</v>
+        <v>954750</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7207,7 +7207,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -7239,7 +7239,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="6">
         <f>SUM(G5:G11)</f>
-        <v>4108650</v>
+        <v>3799012.5</v>
       </c>
     </row>
   </sheetData>
@@ -7327,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I42" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -7405,7 +7405,7 @@
         <v>107</v>
       </c>
       <c r="D8" s="9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8" s="10">
         <v>200000</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>4200000</v>
+        <v>3800000</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="E14" s="10">
         <f>(D8*E8+D9*E9+D10*E10+D11*E11+D12*E12+D13*E13)*Сборка_мебели_проц</f>
-        <v>832000</v>
+        <v>792000</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>101</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>832000</v>
+        <v>792000</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7884,7 +7884,7 @@
         <v>100</v>
       </c>
       <c r="D24" s="9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E24" s="10">
         <f>ROUND(4118/(1+НДС),0)</f>
@@ -7897,11 +7897,11 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
-        <v>81650</v>
+        <v>74550</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8202,7 +8202,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -8273,7 +8273,7 @@
         <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C37" t="s">
         <v>100</v>
@@ -8292,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" ref="I37:I39" si="3">IF(F37="разово",IF(G37&lt;=3,D37*E37,0),IF(F37="мес",D37*E37*MAX(0,4-G37),D37*E37*MAX(0,4-G37)/12))</f>
@@ -8304,7 +8304,7 @@
         <v>98</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C38" t="s">
         <v>104</v>
@@ -8323,7 +8323,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="3"/>
@@ -8335,7 +8335,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -8354,7 +8354,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="3"/>
@@ -8720,7 +8720,7 @@
         <v>130</v>
       </c>
       <c r="D52" s="9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E52" s="10">
         <v>7000</v>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="I52" s="5">
         <f t="shared" si="4"/>
-        <v>294000</v>
+        <v>266000</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9018,7 +9018,7 @@
         <v>285</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C5" t="s">
         <v>244</v>
@@ -9038,7 +9038,7 @@
         <v>285</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C6" t="s">
         <v>244</v>
@@ -9078,7 +9078,7 @@
         <v>285</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C8" t="s">
         <v>244</v>
@@ -9098,7 +9098,7 @@
         <v>285</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C9" t="s">
         <v>244</v>
@@ -9118,7 +9118,7 @@
         <v>285</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C10" t="s">
         <v>244</v>
@@ -9180,7 +9180,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -9199,25 +9199,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>421</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>422</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -9229,13 +9229,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D5" s="55">
         <v>56</v>
@@ -9250,13 +9250,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D6" s="55">
         <v>56</v>
@@ -9272,13 +9272,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D7" s="55">
         <v>6</v>
@@ -9293,13 +9293,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D8" s="55">
         <v>6</v>
@@ -9314,13 +9314,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D9" s="55">
         <v>6</v>
@@ -9335,13 +9335,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D10" s="55">
         <v>48</v>
@@ -9357,7 +9357,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="59" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="55"/>
@@ -9370,7 +9370,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="60" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>
@@ -9447,7 +9447,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="80" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -9466,25 +9466,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>421</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>422</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -9496,13 +9496,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -9517,13 +9517,13 @@
     </row>
     <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -9539,13 +9539,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -9560,13 +9560,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D8" s="55">
         <v>1</v>
@@ -9581,13 +9581,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D9" s="74">
         <v>100</v>
@@ -9602,13 +9602,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D10" s="74">
         <v>100</v>
@@ -9624,10 +9624,10 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="57" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D11" s="74">
         <v>1</v>
@@ -9642,13 +9642,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D12" s="55">
         <v>4</v>
@@ -9663,13 +9663,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B13" s="75" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D13" s="76">
         <v>1</v>
@@ -9685,7 +9685,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="51"/>
       <c r="B14" s="59" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="55"/>
@@ -9698,7 +9698,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M36,Штат!E5:E36,"штат")</f>
-        <v>58353038</v>
+        <v>59188510</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B8" s="38">
         <f>Штат!N37</f>
-        <v>600857.14285714284</v>
+        <v>611142.85714285716</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>116859359.13963135</v>
+        <v>117705116.85391705</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B15" s="38">
         <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Прочие")</f>
-        <v>11752602.580629801</v>
+        <v>11837178.352058372</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>20577913.875241783</v>
+        <v>20726767.232956067</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>149189875.59550291</v>
+        <v>150269062.43893147</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>236424195.59550291</v>
+        <v>237503382.43893147</v>
       </c>
     </row>
   </sheetData>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$36,Штат!$E$5:$E$36,"штат",Штат!$F$5:$F$36,"новая"),-3)</f>
-        <v>701000</v>
+        <v>713000</v>
       </c>
       <c r="C15" t="s">
         <v>404</v>
@@ -5033,11 +5033,11 @@
       </c>
       <c r="N8" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O8" s="18">
         <f t="shared" si="5"/>
-        <v>3222720.9523809524</v>
+        <v>3223292.3809523811</v>
       </c>
       <c r="P8" s="17" t="s">
         <v>381</v>
@@ -5089,11 +5089,11 @@
       </c>
       <c r="N9" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O9" s="18">
         <f t="shared" ref="O9:O11" si="10">M9+N9</f>
-        <v>1516270.9523809524</v>
+        <v>1516842.3809523811</v>
       </c>
       <c r="P9" s="17" t="s">
         <v>392</v>
@@ -5145,11 +5145,11 @@
       </c>
       <c r="N10" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O10" s="18">
         <f t="shared" si="10"/>
-        <v>2328480.9523809524</v>
+        <v>2329052.3809523811</v>
       </c>
       <c r="P10" s="17" t="s">
         <v>394</v>
@@ -5257,11 +5257,11 @@
       </c>
       <c r="N12" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O12" s="18">
         <f t="shared" si="5"/>
-        <v>2328480.9523809524</v>
+        <v>2329052.3809523811</v>
       </c>
       <c r="P12" s="17" t="s">
         <v>335</v>
@@ -5313,11 +5313,11 @@
       </c>
       <c r="N13" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O13" s="18">
         <f t="shared" si="5"/>
-        <v>2552040.9523809524</v>
+        <v>2552612.3809523811</v>
       </c>
       <c r="P13" s="17" t="s">
         <v>278</v>
@@ -5369,11 +5369,11 @@
       </c>
       <c r="N14" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O14" s="18">
         <f t="shared" si="5"/>
-        <v>2328480.9523809524</v>
+        <v>2329052.3809523811</v>
       </c>
       <c r="P14" s="17" t="s">
         <v>382</v>
@@ -5425,11 +5425,11 @@
       </c>
       <c r="N15" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O15" s="18">
         <f t="shared" si="5"/>
-        <v>2328480.9523809524</v>
+        <v>2329052.3809523811</v>
       </c>
       <c r="P15" s="17" t="s">
         <v>383</v>
@@ -5481,11 +5481,11 @@
       </c>
       <c r="N16" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O16" s="18">
         <f t="shared" si="5"/>
-        <v>2328480.9523809524</v>
+        <v>2329052.3809523811</v>
       </c>
       <c r="P16" s="17" t="s">
         <v>384</v>
@@ -5649,11 +5649,11 @@
       </c>
       <c r="N19" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O19" s="18">
         <f t="shared" si="5"/>
-        <v>1657800.9523809524</v>
+        <v>1658372.3809523811</v>
       </c>
       <c r="P19" s="17" t="s">
         <v>391</v>
@@ -5705,11 +5705,11 @@
       </c>
       <c r="N20" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O20" s="18">
         <f t="shared" si="5"/>
-        <v>2999160.9523809524</v>
+        <v>2999732.3809523811</v>
       </c>
       <c r="P20" s="17" t="s">
         <v>385</v>
@@ -5817,11 +5817,11 @@
       </c>
       <c r="N22" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O22" s="18">
         <f t="shared" si="5"/>
-        <v>2999160.9523809524</v>
+        <v>2999732.3809523811</v>
       </c>
       <c r="P22" s="17" t="s">
         <v>387</v>
@@ -5873,11 +5873,11 @@
       </c>
       <c r="N23" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O23" s="18">
         <f t="shared" si="5"/>
-        <v>2328480.9523809524</v>
+        <v>2329052.3809523811</v>
       </c>
       <c r="P23" s="17" t="s">
         <v>386</v>
@@ -6041,11 +6041,11 @@
       </c>
       <c r="N26" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O26" s="18">
         <f t="shared" si="5"/>
-        <v>1657800.9523809524</v>
+        <v>1658372.3809523811</v>
       </c>
       <c r="P26" s="17" t="s">
         <v>390</v>
@@ -6097,11 +6097,11 @@
       </c>
       <c r="N27" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O27" s="18">
         <f t="shared" si="5"/>
-        <v>2328480.9523809524</v>
+        <v>2329052.3809523811</v>
       </c>
       <c r="P27" s="17" t="s">
         <v>388</v>
@@ -6153,11 +6153,11 @@
       </c>
       <c r="N28" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O28" s="18">
         <f t="shared" si="5"/>
-        <v>1657800.9523809524</v>
+        <v>1658372.3809523811</v>
       </c>
       <c r="P28" s="17" t="s">
         <v>261</v>
@@ -6321,11 +6321,11 @@
       </c>
       <c r="N31" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O31" s="18">
         <f t="shared" si="5"/>
-        <v>1657800.9523809524</v>
+        <v>1658372.3809523811</v>
       </c>
       <c r="P31" s="17" t="s">
         <v>213</v>
@@ -6410,18 +6410,18 @@
         <v>1</v>
       </c>
       <c r="H33" s="18">
-        <v>615000</v>
+        <v>800000</v>
       </c>
       <c r="I33" s="16">
         <v>2</v>
       </c>
       <c r="J33" s="18">
         <f t="shared" ref="J33" si="27">IF(E33="штат",ROUND(Ставка_СН*H33*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H33+Ставка_СО*MIN(H33*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H33,Кап_ООСМС*МЗП),0),ROUND(H33*НДС,0))</f>
-        <v>100122</v>
+        <v>123990</v>
       </c>
       <c r="K33" s="18">
         <f t="shared" ref="K33" si="28">G33*(H33+J33)</f>
-        <v>715122</v>
+        <v>923990</v>
       </c>
       <c r="L33" s="19">
         <f t="shared" ref="L33" si="29">IF(AND(F33="новая",I33=1),Мес_2026_новые,MAX(0,4-I33))</f>
@@ -6429,15 +6429,15 @@
       </c>
       <c r="M33" s="18">
         <f t="shared" ref="M33" si="30">K33*L33</f>
-        <v>1430244</v>
+        <v>1847980</v>
       </c>
       <c r="N33" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O33" s="18">
         <f t="shared" ref="O33" si="31">M33+N33</f>
-        <v>1463624.9523809524</v>
+        <v>1881932.3809523811</v>
       </c>
       <c r="P33" s="17" t="s">
         <v>481</v>
@@ -6466,18 +6466,18 @@
         <v>1</v>
       </c>
       <c r="H34" s="18">
-        <v>615000</v>
+        <v>800000</v>
       </c>
       <c r="I34" s="16">
         <v>2</v>
       </c>
       <c r="J34" s="18">
         <f t="shared" ref="J34" si="32">IF(E34="штат",ROUND(Ставка_СН*H34*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*H34+Ставка_СО*MIN(H34*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(H34,Кап_ООСМС*МЗП),0),ROUND(H34*НДС,0))</f>
-        <v>100122</v>
+        <v>123990</v>
       </c>
       <c r="K34" s="18">
         <f t="shared" ref="K34" si="33">G34*(H34+J34)</f>
-        <v>715122</v>
+        <v>923990</v>
       </c>
       <c r="L34" s="19">
         <f t="shared" ref="L34" si="34">IF(AND(F34="новая",I34=1),Мес_2026_новые,MAX(0,4-I34))</f>
@@ -6485,15 +6485,15 @@
       </c>
       <c r="M34" s="18">
         <f t="shared" ref="M34" si="35">K34*L34</f>
-        <v>1430244</v>
+        <v>1847980</v>
       </c>
       <c r="N34" s="18">
         <f t="shared" si="4"/>
-        <v>33380.952380952382</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O34" s="18">
         <f t="shared" ref="O34" si="36">M34+N34</f>
-        <v>1463624.9523809524</v>
+        <v>1881932.3809523811</v>
       </c>
       <c r="P34" s="17" t="s">
         <v>482</v>
@@ -6626,26 +6626,26 @@
       </c>
       <c r="H37" s="6">
         <f>SUMPRODUCT(G5:G36,H5:H36)</f>
-        <v>23230000</v>
+        <v>23600000</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6">
         <f>SUM(K5:K36)</f>
-        <v>26616844</v>
+        <v>27034580</v>
       </c>
       <c r="L37" s="7"/>
       <c r="M37" s="6">
         <f>SUM(M5:M36)</f>
-        <v>58353038</v>
+        <v>59188510</v>
       </c>
       <c r="N37" s="6">
         <f t="shared" ref="N37:O37" si="37">SUM(N5:N36)</f>
-        <v>600857.14285714284</v>
+        <v>611142.85714285716</v>
       </c>
       <c r="O37" s="6">
         <f t="shared" si="37"/>
-        <v>58953895.142857164</v>
+        <v>59799652.857142851</v>
       </c>
       <c r="P37" s="7"/>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="H39" s="5">
         <f>H37-H38</f>
-        <v>7730000</v>
+        <v>8100000</v>
       </c>
     </row>
   </sheetData>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -380,7 +380,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="508">
   <si>
     <t>Статья</t>
   </si>
@@ -700,15 +700,6 @@
     <t>новые сотрудники в офисе (рег. координаторы — удалённо)</t>
   </si>
   <si>
-    <t>Рабочее место: стол, кресло, тумба</t>
-  </si>
-  <si>
-    <t>место</t>
-  </si>
-  <si>
-    <t>16 сотрудников в open space + 3 гостевых (продакшн-группа, координаторы в приезд)</t>
-  </si>
-  <si>
     <t>новый офис</t>
   </si>
   <si>
@@ -1057,12 +1048,6 @@
     <t>Стеллажи для складов и архивов (склад техники, архив документов, архив основного блока)</t>
   </si>
   <si>
-    <t>Шкафы для документов и сейф</t>
-  </si>
-  <si>
-    <t>Сейф офисный для документов и печатей входит в этот комплект</t>
-  </si>
-  <si>
     <t>Сборка и занос: рабочие места, кабинеты руководства, переговорная, ресепшн, шкафы и сейф, стеллажи. Ориентир 10% от стоимости мебели и стеллажей (лист «Параметры»), уточнить в КП</t>
   </si>
   <si>
@@ -1315,9 +1300,6 @@
     <t>≈3 500 страниц в месяц</t>
   </si>
   <si>
-    <t>Мебель кабинетов руководства (ГИД, 2 заместителя, Нац.коорд., финдир)</t>
-  </si>
-  <si>
     <t>Ставка аренды со скидкой, ₸ за 1 м² в месяц без НДС и без коммунальных (условия БЦ от 22.09.2026)</t>
   </si>
   <si>
@@ -1607,12 +1589,6 @@
   </si>
   <si>
     <t>Мес. 2026 (новые – с 01.11)</t>
-  </si>
-  <si>
-    <t>Стул офисный для посетителей</t>
-  </si>
-  <si>
-    <t>Дополнение № 1 в план закупок, поз. 81: цена zeta.kz (Астана) 11 425 ₸ с НДС за стул «Изо»; в бюджете без НДС (÷1,16)</t>
   </si>
   <si>
     <t>Жалюзи вертикальные тканевые (зона 710)</t>
@@ -1868,6 +1844,90 @@
   </si>
   <si>
     <t>Департамент проектного управления и региональной координации (5 чел.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шкафы для документов </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шка-картотека офисный для документов и печатей входит </t>
+  </si>
+  <si>
+    <t>Стол рабочий с подкатной тумбой (ZETA Лофт, 140×70×77,7 см, ЛДСП, каркас металл, тумба на колёсах с 3 ящиками)</t>
+  </si>
+  <si>
+    <t>Решение 23.10.2026. Kaspi.kz, продавец ZETA, код товара 138600603 – 80 861 ₸ с НДС, в бюджете без НДС (÷1,16). 20 рабочих мест. Тумба входит в комплект стола</t>
+  </si>
+  <si>
+    <t>Кресло рабочее (МИ-6 Z, спинка-сетка, подлокотники, крестовина с колёсами, регулировка высоты, нагрузка 120 кг)</t>
+  </si>
+  <si>
+    <t>Решение 23.10.2026. Kaspi.kz, продавец ZETA, код товара 105723720 – 17 110 ₸ с НДС, в бюджете без НДС (÷1,16). У «ZETA Астана» со склада в Астане – 17 950 ₸</t>
+  </si>
+  <si>
+    <t>Стул офисный для посетителей (ZETA СМ-6 серый, каркас металл, обивка гобелен, нагрузка 100 кг)</t>
+  </si>
+  <si>
+    <t>Решение 23.10.2026: серый вместо чёрного. Kaspi.kz, продавец ZETA, код товара 100872340 – 7 400 ₸ с НДС, в бюджете без НДС (÷1,16). У «ZETA Астана» со склада в Астане – 7 455 ₸</t>
+  </si>
+  <si>
+    <t>Кресло руководителя (ZETA Гермес, высокая спинка, механизм качания, подлокотники, нагрузка 120 кг)</t>
+  </si>
+  <si>
+    <t>Решение 23.10.2026: заместителю ГИД, финансовому директору, национальному координатору и советнику. Kaspi.kz, код товара 101065129, продавец RUH MARKET – 70 900 ₸ с НДС (+1 995 ₸ доставка), в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>Кресло Главного исполнительного директора (ZETA мод. 2338, экокожа, высокая спинка, нагрузка 120 кг)</t>
+  </si>
+  <si>
+    <t>Решение 23.10.2026: кресло ГИД. Kaspi.kz, код товара 129848350, продавец ZETA ПОЗИТИВ – 114 460 ₸ с НДС (+1 995 ₸ доставка), в бюджете без НДС (÷1,16). Страна производства – Китай</t>
+  </si>
+  <si>
+    <t>Стол руководителя (ZETA Тейлор, 140×70×75 см, светло-серый)</t>
+  </si>
+  <si>
+    <t>Кабинеты: ГИД, заместитель ГИД, национальный координатор, финансовый директор, советник. Kaspi.kz, код товара 146093286 – 67 576 ₸ с НДС, в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>Шкаф для документов в кабинет руководителя (ZETA СТЖ 11 / Кул-123, 80×38,5×201 см)</t>
+  </si>
+  <si>
+    <t>Kaspi.kz, код товара 130663491 – 41 990 ₸ с НДС, в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>Тумба подкатная в кабинет руководителя, 3 ящика</t>
+  </si>
+  <si>
+    <t>ОЦЕНКА: подкатной тумбы ZETA на Kaspi.kz нет, цену запросить у ZETA (zeta.kz, Астана) вместе с остальной мебелью</t>
+  </si>
+  <si>
+    <t>Шкаф-гардероб в кабинет руководителя</t>
+  </si>
+  <si>
+    <t>ОЦЕНКА: офисного шкафа-гардероба ZETA на Kaspi.kz нет, цену запросить у ZETA (zeta.kz, Астана)</t>
+  </si>
+  <si>
+    <t>Стул представительский (ZETA Shugyla, 87×55×57 см, металл, обивка велюр, бежевый)</t>
+  </si>
+  <si>
+    <t>Решение 23.10.2026. Kaspi.kz, код товара 148942187, продавец ZETA – 26 905 ₸ с НДС, доставка бесплатно, в бюджете без НДС (÷1,16). Место размещения уточнить</t>
+  </si>
+  <si>
+    <t>Кухонный гарнитур ZETA Денвер, 200×215×60 см, ЛДСП, серый / бежевый</t>
+  </si>
+  <si>
+    <t>Решение 23.10.2026: вариант 2 подборки. Kaspi.kz, код товара 119304315, продавец ZETA – 102 898 ₸ с НДС, в бюджете без НДС (÷1,16). Верхние 200×71,6×29,6, нижние 200×84,6×44,2, столешница 200×60. Мойка и смеситель – отдельной строкой</t>
+  </si>
+  <si>
+    <t>Мойка врезная HALI со смесителем, 60×45×22 см, нерж. сталь 3 мм, графит</t>
+  </si>
+  <si>
+    <t>Kaspi.kz, код товара 141384274 – 36 990 ₸ с НДС, в бюджете без НДС (÷1,16). В комплекте: мойка, смеситель, сифон, перелив, дозатор, коландер, сетка, решётка для сушки</t>
+  </si>
+  <si>
+    <t>Врезка мойки, подключение воды и канализации на кухонной зоне</t>
+  </si>
+  <si>
+    <t>ОЦЕНКА: цену запросить вместе с гарнитуром. Сборка самого гарнитура входит в строку «Сборка, доставка и подъём мебели» (10%)</t>
   </si>
 </sst>
 </file>
@@ -2073,7 +2133,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2253,6 +2313,13 @@
     <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -2536,7 +2603,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2549,7 +2616,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E36,"штат",Штат!G5:G36)</f>
@@ -2558,7 +2625,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G38</f>
@@ -2567,7 +2634,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M36,Штат!E5:E36,"штат")</f>
@@ -2576,7 +2643,7 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B7" s="38">
         <f>Аутсорс!J11</f>
@@ -2585,7 +2652,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B8" s="38">
         <f>Штат!N37</f>
@@ -2594,7 +2661,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B9" s="38">
         <f>Командировки!G12</f>
@@ -2603,79 +2670,79 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B10" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Оснащение")</f>
-        <v>21992588</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I70,'Оснащение и офис'!A5:A70,"Оснащение")</f>
+        <v>14358335.6</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B11" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Офис")</f>
-        <v>17202663.496774193</v>
+        <f>SUMIFS('Оснащение и офис'!I5:I70,'Оснащение и офис'!A5:A70,"Офис")</f>
+        <v>17053163.496774193</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B12" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Цифровые")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I70,'Оснащение и офис'!A5:A70,"Цифровые")</f>
         <v>463000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B13" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Медиа")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I70,'Оснащение и офис'!A5:A70,"Медиа")</f>
         <v>2350000</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B14" s="40">
         <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>117705116.85391705</v>
+        <v>109921364.45391704</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B15" s="38">
-        <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I60,'Оснащение и офис'!A5:A60,"Прочие")</f>
-        <v>11837178.352058372</v>
+        <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I70,'Оснащение и офис'!A5:A70,"Прочие")</f>
+        <v>11042136.445391705</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B16" s="38">
         <f>(B14+B15)*НДС</f>
-        <v>20726767.232956067</v>
+        <v>19354160.143889397</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B17" s="42">
         <f>B14+B15+B16</f>
-        <v>150269062.43893147</v>
+        <v>140317661.04319814</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B18" s="40">
         <f>Проекты!G13</f>
@@ -2684,11 +2751,11 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B19" s="44">
         <f>B17+B18</f>
-        <v>237503382.43893147</v>
+        <v>227551981.04319814</v>
       </c>
     </row>
   </sheetData>
@@ -2714,45 +2781,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
-        <v>452</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
+      <c r="A1" s="87" t="s">
+        <v>444</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2764,13 +2831,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -2785,13 +2852,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -2807,13 +2874,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -2829,7 +2896,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="59" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="55"/>
@@ -2842,7 +2909,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51"/>
       <c r="B9" s="60" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
@@ -2898,45 +2965,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
-        <v>458</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
+      <c r="A1" s="87" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2948,13 +3015,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D5" s="55">
         <v>6</v>
@@ -2969,13 +3036,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -2991,13 +3058,13 @@
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3012,13 +3079,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D8" s="55">
         <v>9</v>
@@ -3033,13 +3100,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D9" s="74">
         <v>32</v>
@@ -3054,13 +3121,13 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D10" s="55">
         <v>3</v>
@@ -3075,13 +3142,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="D11" s="55">
         <v>3</v>
@@ -3098,7 +3165,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="59" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="55"/>
@@ -3111,7 +3178,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
@@ -3164,45 +3231,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
-        <v>466</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
+      <c r="A1" s="87" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3214,13 +3281,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3235,13 +3302,13 @@
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3258,7 +3325,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="59" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="55"/>
@@ -3271,7 +3338,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="60" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -3327,45 +3394,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
-        <v>469</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
+      <c r="A1" s="87" t="s">
+        <v>461</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3377,13 +3444,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3399,7 +3466,7 @@
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51"/>
       <c r="B6" s="59" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="55"/>
@@ -3413,7 +3480,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="60" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
@@ -3471,27 +3538,27 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>94</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>97</v>
@@ -3499,13 +3566,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D5" s="13">
         <v>3.5</v>
@@ -3518,18 +3585,18 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" t="s">
         <v>186</v>
       </c>
-      <c r="B6" t="s">
-        <v>189</v>
-      </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D6" s="13">
         <v>0.25</v>
@@ -3542,18 +3609,18 @@
         <v>1625</v>
       </c>
       <c r="G6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D7" s="13">
         <v>0.5</v>
@@ -3566,63 +3633,63 @@
         <v>3000</v>
       </c>
       <c r="G7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
         <v>104</v>
       </c>
       <c r="D8" s="13">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5">
         <v>5000</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" si="0"/>
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
       </c>
       <c r="D9" s="13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5">
         <v>1200</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" t="s">
         <v>196</v>
-      </c>
-      <c r="B10" t="s">
-        <v>199</v>
       </c>
       <c r="C10" t="s">
         <v>104</v>
@@ -3638,23 +3705,23 @@
         <v>9000</v>
       </c>
       <c r="G10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6">
         <f>SUM(F5:F10)</f>
-        <v>37375</v>
+        <v>24125</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3663,133 +3730,125 @@
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B14" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C14" t="s">
         <v>104</v>
       </c>
       <c r="D14" s="45">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E14" s="5">
         <v>1500</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" ref="F14:F19" si="1">D14*E14</f>
-        <v>22500</v>
+        <v>7500</v>
       </c>
       <c r="G14" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C15" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="45">
-        <v>1</v>
-      </c>
+      <c r="D15" s="45"/>
       <c r="E15" s="5">
         <v>8000</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="1"/>
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C16" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="45">
-        <v>1</v>
-      </c>
+      <c r="D16" s="45"/>
       <c r="E16" s="5">
         <v>10000</v>
       </c>
       <c r="F16" s="5">
         <f t="shared" si="1"/>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C17" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="45">
-        <v>1</v>
-      </c>
+      <c r="D17" s="45"/>
       <c r="E17" s="5">
         <v>6000</v>
       </c>
       <c r="F17" s="5">
         <f t="shared" si="1"/>
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C18" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="45">
-        <v>2</v>
-      </c>
+      <c r="D18" s="45"/>
       <c r="E18" s="5">
         <v>12000</v>
       </c>
       <c r="F18" s="5">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C19" t="s">
         <v>104</v>
@@ -3805,20 +3864,20 @@
         <v>8000</v>
       </c>
       <c r="G19" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6">
         <f>SUM(F14:F19)</f>
-        <v>78500</v>
+        <v>15500</v>
       </c>
       <c r="G20" s="7"/>
     </row>
@@ -3847,12 +3906,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3860,13 +3919,13 @@
         <v>66</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>72</v>
@@ -3875,12 +3934,12 @@
         <v>95</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -3894,13 +3953,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C6">
         <v>5659</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -3918,13 +3977,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C7">
         <v>2584</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3942,13 +4001,13 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C8">
         <v>6218</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -3966,13 +4025,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9">
         <v>4240</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -3990,13 +4049,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C10">
         <v>6976</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -4014,13 +4073,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C11">
         <v>3288</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4038,13 +4097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C12">
         <v>1756</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4060,7 +4119,7 @@
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -4077,7 +4136,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -4091,10 +4150,10 @@
         <v>2.1</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4110,7 +4169,7 @@
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -4127,7 +4186,7 @@
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -4141,10 +4200,10 @@
         <v>3.3</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4162,10 +4221,10 @@
         <v>3.4</v>
       </c>
       <c r="B21" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -4181,7 +4240,7 @@
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -4199,7 +4258,7 @@
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
@@ -4368,14 +4427,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$36,Штат!$E$5:$E$36,"штат",Штат!$F$5:$F$36,"новая"),-3)</f>
         <v>713000</v>
       </c>
       <c r="C15" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4566,7 +4625,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4577,7 +4636,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4604,137 +4663,137 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B42" s="13">
         <f>ROUND((52.2+21.4+12.4+33.7+190)*1.1,2)</f>
         <v>340.67</v>
       </c>
       <c r="C42" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B43" s="5">
         <v>13500</v>
       </c>
       <c r="C43" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B44" s="5">
         <f>743*309.7</f>
         <v>230107.1</v>
       </c>
       <c r="C44" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B45" s="5">
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>40000</v>
       </c>
       <c r="C46" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B47" s="5">
         <f>Аренда_мес*(1+НДС)</f>
         <v>5694616.4359999988</v>
       </c>
       <c r="C47" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <f>Аренда_мес*Депозит_мес</f>
         <v>4909152.0999999996</v>
       </c>
       <c r="C48" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B49" s="15">
         <f>11/31+2</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C49" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B51" s="14">
         <v>0.1</v>
       </c>
       <c r="C51" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B52" s="15">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -4762,7 +4821,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4794,7 +4853,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -4803,19 +4862,19 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
@@ -4824,10 +4883,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>79</v>
@@ -4872,7 +4931,7 @@
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -4880,10 +4939,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -4928,7 +4987,7 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -4936,10 +4995,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>82</v>
@@ -4984,7 +5043,7 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -4992,10 +5051,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -5040,7 +5099,7 @@
         <v>3223292.3809523811</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5048,13 +5107,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>80</v>
@@ -5096,7 +5155,7 @@
         <v>1516842.3809523811</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5104,13 +5163,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>80</v>
@@ -5152,7 +5211,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5160,16 +5219,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>83</v>
@@ -5208,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5216,13 +5275,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>80</v>
@@ -5264,7 +5323,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5272,13 +5331,13 @@
         <v>14</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>80</v>
@@ -5320,7 +5379,7 @@
         <v>2552612.3809523811</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5328,13 +5387,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>80</v>
@@ -5376,7 +5435,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -5384,13 +5443,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>80</v>
@@ -5432,7 +5491,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5440,13 +5499,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>80</v>
@@ -5488,7 +5547,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5496,13 +5555,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>80</v>
@@ -5544,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5552,13 +5611,13 @@
         <v>19</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>80</v>
@@ -5600,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5608,13 +5667,13 @@
         <v>19</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>80</v>
@@ -5656,7 +5715,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -5664,13 +5723,13 @@
         <v>23</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>80</v>
@@ -5712,7 +5771,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5720,16 +5779,16 @@
         <v>24</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>83</v>
@@ -5768,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -5776,13 +5835,13 @@
         <v>25</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>80</v>
@@ -5824,7 +5883,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -5832,13 +5891,13 @@
         <v>26</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>80</v>
@@ -5880,7 +5939,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -5888,16 +5947,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>83</v>
@@ -5936,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -5944,16 +6003,16 @@
         <v>28</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>83</v>
@@ -5992,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -6000,13 +6059,13 @@
         <v>29</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>80</v>
@@ -6048,7 +6107,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -6056,13 +6115,13 @@
         <v>30</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>80</v>
@@ -6104,7 +6163,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -6112,13 +6171,13 @@
         <v>31</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>80</v>
@@ -6160,7 +6219,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6168,16 +6227,16 @@
         <v>32</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>83</v>
@@ -6216,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -6224,7 +6283,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>84</v>
@@ -6272,7 +6331,7 @@
         <v>4784010</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6280,13 +6339,13 @@
         <v>34</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>85</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>80</v>
@@ -6328,7 +6387,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P31" s="17" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="45" x14ac:dyDescent="0.25">
@@ -6336,13 +6395,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>80</v>
@@ -6384,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="33" spans="1:16" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6392,13 +6451,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>80</v>
@@ -6440,7 +6499,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
     <row r="34" spans="1:16" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -6448,13 +6507,13 @@
         <v>35</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>80</v>
@@ -6496,7 +6555,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6504,16 +6563,16 @@
         <v>36</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>83</v>
@@ -6552,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="21" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -6560,16 +6619,16 @@
         <v>37</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>83</v>
@@ -6608,14 +6667,14 @@
         <v>0</v>
       </c>
       <c r="P36" s="21" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -6651,7 +6710,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G38">
         <f>SUM(G8:G12)+SUM(G13:G29)</f>
@@ -6664,7 +6723,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G39">
         <f>G37-G38</f>
@@ -6701,7 +6760,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -6709,25 +6768,25 @@
         <v>66</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -6741,13 +6800,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E4" s="28">
         <v>867500</v>
@@ -6776,13 +6835,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E5" s="28">
         <v>425600</v>
@@ -6811,13 +6870,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -6847,13 +6906,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -6883,13 +6942,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -6919,13 +6978,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -6955,13 +7014,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C10" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>296</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>301</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -6989,7 +7048,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -7033,12 +7092,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7058,7 +7117,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>91</v>
@@ -7138,7 +7197,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")</f>
@@ -7161,7 +7220,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
@@ -7184,7 +7243,7 @@
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G20:G21)</f>
@@ -7207,7 +7266,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -7253,7 +7312,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7267,12 +7326,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7295,7 +7354,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -7327,10 +7386,10 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I42" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
+        <f t="shared" ref="I5:I52" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
         <v>1800000</v>
       </c>
     </row>
@@ -7357,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -7399,16 +7458,17 @@
         <v>98</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>106</v>
+        <v>482</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D8" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="10">
-        <v>200000</v>
+        <f>ROUND(80861/(1+НДС),0)</f>
+        <v>69708</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>101</v>
@@ -7417,28 +7477,29 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>108</v>
+        <v>483</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>3800000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>1394160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="80" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="80" t="s">
         <v>98</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="C9" t="s">
-        <v>104</v>
+        <v>484</v>
+      </c>
+      <c r="C9" s="80" t="s">
+        <v>100</v>
       </c>
       <c r="D9" s="9">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E9" s="10">
-        <v>500000</v>
+        <f>ROUND(17110/(1+НДС),0)</f>
+        <v>14750</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>101</v>
@@ -7447,28 +7508,29 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>109</v>
+        <v>485</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <f t="shared" ref="I9" si="1">IF(F9="разово",IF(G9&lt;=3,D9*E9,0),IF(F9="мес",D9*E9*MAX(0,4-G9),D9*E9*MAX(0,4-G9)/12))</f>
+        <v>383500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="81" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="81" t="s">
         <v>98</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" t="s">
-        <v>104</v>
+        <v>488</v>
+      </c>
+      <c r="C10" s="81" t="s">
+        <v>100</v>
       </c>
       <c r="D10" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10" s="10">
-        <v>800000</v>
+        <f>ROUND(70900/(1+НДС),0)</f>
+        <v>61121</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>101</v>
@@ -7476,27 +7538,30 @@
       <c r="G10" s="9">
         <v>1</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>489</v>
+      </c>
       <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <f t="shared" ref="I10" si="2">IF(F10="разово",IF(G10&lt;=3,D10*E10,0),IF(F10="мес",D10*E10*MAX(0,4-G10),D10*E10*MAX(0,4-G10)/12))</f>
+        <v>244484</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="82" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="82" t="s">
         <v>98</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
+        <v>490</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>100</v>
       </c>
       <c r="D11" s="9">
         <v>1</v>
       </c>
       <c r="E11" s="10">
-        <v>250000</v>
+        <f>ROUND(114460/(1+НДС),0)</f>
+        <v>98672</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>101</v>
@@ -7504,10 +7569,12 @@
       <c r="G11" s="9">
         <v>1</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>491</v>
+      </c>
       <c r="I11" s="5">
-        <f t="shared" si="0"/>
-        <v>250000</v>
+        <f t="shared" ref="I11" si="3">IF(F11="разово",IF(G11&lt;=3,D11*E11,0),IF(F11="мес",D11*E11*MAX(0,4-G11),D11*E11*MAX(0,4-G11)/12))</f>
+        <v>98672</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7515,16 +7582,17 @@
         <v>98</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>225</v>
+        <v>492</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D12" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E12" s="10">
-        <v>450000</v>
+        <f>ROUND(67576/(1+НДС),0)</f>
+        <v>58255</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>101</v>
@@ -7533,28 +7601,29 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>226</v>
+        <v>493</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+        <v>291275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="83" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="84" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" t="s">
+        <v>494</v>
+      </c>
+      <c r="C13" s="84" t="s">
         <v>100</v>
       </c>
       <c r="D13" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E13" s="10">
-        <v>60000</v>
+        <f>ROUND(41990/(1+НДС),0)</f>
+        <v>36198</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>101</v>
@@ -7563,29 +7632,29 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>232</v>
+        <v>495</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+        <f>IF(F13="разово",IF(G13&lt;=3,D13*E13,0),IF(F13="мес",D13*E13*MAX(0,4-G13),D13*E13*MAX(0,4-G13)/12))</f>
+        <v>180990</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="83" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="84" t="s">
         <v>98</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C14" t="s">
-        <v>104</v>
+        <v>496</v>
+      </c>
+      <c r="C14" s="84" t="s">
+        <v>100</v>
       </c>
       <c r="D14" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" s="10">
-        <f>(D8*E8+D9*E9+D10*E10+D11*E11+D12*E12+D13*E13)*Сборка_мебели_проц</f>
-        <v>792000</v>
+        <f>ROUND(35000/(1+НДС),0)</f>
+        <v>30172</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>101</v>
@@ -7594,28 +7663,29 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>227</v>
+        <v>497</v>
       </c>
       <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>792000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+        <f>IF(F14="разово",IF(G14&lt;=3,D14*E14,0),IF(F14="мес",D14*E14*MAX(0,4-G14),D14*E14*MAX(0,4-G14)/12))</f>
+        <v>150860</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="83" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="83" t="s">
         <v>98</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15" t="s">
+        <v>498</v>
+      </c>
+      <c r="C15" s="83" t="s">
         <v>100</v>
       </c>
       <c r="D15" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15" s="10">
-        <v>2500000</v>
+        <f>ROUND(60000/(1+НДС),0)</f>
+        <v>51724</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>101</v>
@@ -7624,28 +7694,29 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>175</v>
+        <v>499</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+        <f t="shared" ref="I15" si="4">IF(F15="разово",IF(G15&lt;=3,D15*E15,0),IF(F15="мес",D15*E15*MAX(0,4-G15),D15*E15*MAX(0,4-G15)/12))</f>
+        <v>258620</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="85" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="85" t="s">
         <v>98</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" t="s">
-        <v>104</v>
+        <v>500</v>
+      </c>
+      <c r="C16" s="85" t="s">
+        <v>100</v>
       </c>
       <c r="D16" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="10">
-        <v>300000</v>
+        <f>ROUND(26905/(1+НДС),0)</f>
+        <v>23194</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>101</v>
@@ -7653,27 +7724,30 @@
       <c r="G16" s="9">
         <v>1</v>
       </c>
-      <c r="H16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>501</v>
+      </c>
       <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+        <f>IF(F16="разово",IF(G16&lt;=3,D16*E16,0),IF(F16="мес",D16*E16*MAX(0,4-G16),D16*E16*MAX(0,4-G16)/12))</f>
+        <v>69582</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="86" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="86" t="s">
         <v>98</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C17" t="s">
-        <v>100</v>
+        <v>502</v>
+      </c>
+      <c r="C17" s="86" t="s">
+        <v>104</v>
       </c>
       <c r="D17" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="10">
-        <v>280000</v>
+        <f>ROUND(102898/(1+НДС),0)</f>
+        <v>88705</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>101</v>
@@ -7682,28 +7756,29 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>233</v>
+        <v>503</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>560000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+        <f>IF(F17="разово",IF(G17&lt;=3,D17*E17,0),IF(F17="мес",D17*E17*MAX(0,4-G17),D17*E17*MAX(0,4-G17)/12))</f>
+        <v>88705</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="86" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="86" t="s">
         <v>98</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C18" t="s">
-        <v>100</v>
+        <v>504</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>104</v>
       </c>
       <c r="D18" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="10">
-        <v>55000</v>
+        <f>ROUND(36990/(1+НДС),0)</f>
+        <v>31888</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>101</v>
@@ -7712,11 +7787,11 @@
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>179</v>
+        <v>505</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>220000</v>
+        <f>IF(F18="разово",IF(G18&lt;=3,D18*E18,0),IF(F18="мес",D18*E18*MAX(0,4-G18),D18*E18*MAX(0,4-G18)/12))</f>
+        <v>31888</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7724,16 +7799,16 @@
         <v>98</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
         <v>104</v>
       </c>
       <c r="D19" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="10">
-        <v>300000</v>
+        <v>800000</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>101</v>
@@ -7741,12 +7816,10 @@
       <c r="G19" s="9">
         <v>1</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>181</v>
-      </c>
+      <c r="H19" s="4"/>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7754,17 +7827,16 @@
         <v>98</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>234</v>
+        <v>351</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="10">
-        <f>ROUND(42340/(1+НДС),0)</f>
-        <v>36500</v>
+        <v>250000</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>101</v>
@@ -7772,12 +7844,10 @@
       <c r="G20" s="9">
         <v>1</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>235</v>
-      </c>
+      <c r="H20" s="4"/>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
-        <v>36500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7785,17 +7855,16 @@
         <v>98</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>236</v>
+        <v>480</v>
       </c>
       <c r="C21" t="s">
-        <v>237</v>
+        <v>104</v>
       </c>
       <c r="D21" s="9">
         <v>1</v>
       </c>
       <c r="E21" s="10">
-        <f>ROUND(6000/(1+НДС),0)</f>
-        <v>5172</v>
+        <v>100000</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>101</v>
@@ -7804,11 +7873,11 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>238</v>
+        <v>481</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>5172</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7816,17 +7885,16 @@
         <v>98</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="C22" t="s">
         <v>100</v>
       </c>
       <c r="D22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="10">
-        <f>ROUND(114327/(1+НДС),0)</f>
-        <v>98558</v>
+        <v>60000</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>101</v>
@@ -7835,11 +7903,11 @@
         <v>1</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
-        <v>98558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7847,7 +7915,7 @@
         <v>98</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="C23" t="s">
         <v>104</v>
@@ -7856,8 +7924,8 @@
         <v>1</v>
       </c>
       <c r="E23" s="10">
-        <f>ROUND((100*55+100*68+100*26+100*37+100*57+100*244)/(1+НДС),0)</f>
-        <v>41983</v>
+        <f>SUMPRODUCT(D8:D22,E8:E22)*Сборка_мебели_проц</f>
+        <v>329273.60000000003</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>101</v>
@@ -7866,29 +7934,29 @@
         <v>1</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
-        <v>41983</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+        <v>329273.60000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="86" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="86" t="s">
         <v>98</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="C24" t="s">
-        <v>100</v>
+        <v>506</v>
+      </c>
+      <c r="C24" s="86" t="s">
+        <v>104</v>
       </c>
       <c r="D24" s="9">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E24" s="10">
-        <f>ROUND(4118/(1+НДС),0)</f>
-        <v>3550</v>
+        <f>ROUND(25000/(1+НДС),0)</f>
+        <v>21552</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>101</v>
@@ -7897,29 +7965,28 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>403</v>
+        <v>507</v>
       </c>
       <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>74550</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <f>IF(F24="разово",IF(G24&lt;=3,D24*E24,0),IF(F24="мес",D24*E24*MAX(0,4-G24),D24*E24*MAX(0,4-G24)/12))</f>
+        <v>21552</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>267</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
         <v>100</v>
       </c>
       <c r="D25" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="10">
-        <f>ROUND(6101/(1+НДС),0)</f>
-        <v>5259</v>
+        <v>2500000</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>101</v>
@@ -7928,11 +7995,11 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>358</v>
+        <v>172</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
-        <v>15777</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7940,17 +8007,16 @@
         <v>98</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>269</v>
+        <v>173</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D26" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26" s="10">
-        <f>ROUND(7235/(1+НДС),0)</f>
-        <v>6237</v>
+        <v>300000</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>101</v>
@@ -7958,12 +8024,10 @@
       <c r="G26" s="9">
         <v>1</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>270</v>
-      </c>
+      <c r="H26" s="4"/>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
-        <v>24948</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7971,17 +8035,16 @@
         <v>98</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>271</v>
+        <v>174</v>
       </c>
       <c r="C27" t="s">
         <v>100</v>
       </c>
       <c r="D27" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="10">
-        <f>ROUND(9039/(1+НДС),0)</f>
-        <v>7792</v>
+        <v>280000</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>101</v>
@@ -7990,11 +8053,11 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
-        <v>38960</v>
+        <v>560000</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8002,17 +8065,16 @@
         <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>319</v>
+        <v>175</v>
       </c>
       <c r="C28" t="s">
         <v>100</v>
       </c>
       <c r="D28" s="9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E28" s="10">
-        <f>ROUND(89302/(1+НДС),0)</f>
-        <v>76984</v>
+        <v>55000</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>101</v>
@@ -8021,11 +8083,11 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>320</v>
+        <v>176</v>
       </c>
       <c r="I28" s="5">
-        <f t="shared" ref="I28" si="1">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
-        <v>769840</v>
+        <f t="shared" si="0"/>
+        <v>220000</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8033,17 +8095,16 @@
         <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>322</v>
+        <v>177</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D29" s="9">
         <v>1</v>
       </c>
       <c r="E29" s="10">
-        <f>ROUND(989997/(1+НДС),0)</f>
-        <v>853446</v>
+        <v>300000</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>101</v>
@@ -8052,11 +8113,11 @@
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>323</v>
+        <v>178</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
-        <v>853446</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8064,17 +8125,15 @@
         <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>324</v>
+        <v>229</v>
       </c>
       <c r="C30" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="9">
-        <v>1</v>
-      </c>
+      <c r="D30" s="9"/>
       <c r="E30" s="10">
-        <f>ROUND(49990/(1+НДС),0)</f>
-        <v>43095</v>
+        <f>ROUND(42340/(1+НДС),0)</f>
+        <v>36500</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>101</v>
@@ -8083,11 +8142,11 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
-        <v>43095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8095,16 +8154,15 @@
         <v>98</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D31" s="9">
-        <v>1</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="D31" s="9"/>
       <c r="E31" s="10">
-        <v>300000</v>
+        <f>ROUND(6000/(1+НДС),0)</f>
+        <v>5172</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>101</v>
@@ -8113,11 +8171,11 @@
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8125,16 +8183,15 @@
         <v>98</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>113</v>
+        <v>234</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="9">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D32" s="9"/>
       <c r="E32" s="10">
-        <v>800000</v>
+        <f>ROUND(114327/(1+НДС),0)</f>
+        <v>98558</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>101</v>
@@ -8143,11 +8200,11 @@
         <v>1</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>109</v>
+        <v>235</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
-        <v>800000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8155,16 +8212,15 @@
         <v>98</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>114</v>
+        <v>236</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" s="9">
-        <v>1</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D33" s="9"/>
       <c r="E33" s="10">
-        <v>700000</v>
+        <f>ROUND((100*55+100*68+100*26+100*37+100*57+100*244)/(1+НДС),0)</f>
+        <v>41983</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>101</v>
@@ -8172,28 +8228,30 @@
       <c r="G33" s="9">
         <v>1</v>
       </c>
-      <c r="H33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>237</v>
+      </c>
       <c r="I33" s="5">
         <f t="shared" si="0"/>
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>359</v>
+        <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D34" s="9">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E34" s="10">
-        <f>'Смета фото-видео'!G24</f>
-        <v>300000</v>
+        <f>ROUND(4118/(1+НДС),0)</f>
+        <v>3550</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>101</v>
@@ -8202,11 +8260,11 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>74550</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8214,16 +8272,17 @@
         <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>326</v>
+        <v>262</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D35" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35" s="10">
-        <v>400000</v>
+        <f>ROUND(6101/(1+НДС),0)</f>
+        <v>5259</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>101</v>
@@ -8231,10 +8290,12 @@
       <c r="G35" s="9">
         <v>1</v>
       </c>
-      <c r="H35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>352</v>
+      </c>
       <c r="I35" s="5">
         <f t="shared" si="0"/>
-        <v>400000</v>
+        <v>15777</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8242,17 +8303,17 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>327</v>
+        <v>264</v>
       </c>
       <c r="C36" t="s">
         <v>100</v>
       </c>
       <c r="D36" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E36" s="10">
-        <f>ROUND(35990/(1+НДС),0)</f>
-        <v>31026</v>
+        <f>ROUND(7235/(1+НДС),0)</f>
+        <v>6237</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>101</v>
@@ -8261,11 +8322,11 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>328</v>
+        <v>265</v>
       </c>
       <c r="I36" s="5">
-        <f t="shared" ref="I36" si="2">IF(F36="разово",IF(G36&lt;=3,D36*E36,0),IF(F36="мес",D36*E36*MAX(0,4-G36),D36*E36*MAX(0,4-G36)/12))</f>
-        <v>31026</v>
+        <f t="shared" si="0"/>
+        <v>24948</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8273,17 +8334,17 @@
         <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>409</v>
+        <v>266</v>
       </c>
       <c r="C37" t="s">
         <v>100</v>
       </c>
       <c r="D37" s="9">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E37" s="10">
-        <f>ROUND(11425/(1+НДС),0)</f>
-        <v>9849</v>
+        <f>ROUND(9039/(1+НДС),0)</f>
+        <v>7792</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>101</v>
@@ -8292,11 +8353,11 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>410</v>
+        <v>267</v>
       </c>
       <c r="I37" s="5">
-        <f t="shared" ref="I37:I39" si="3">IF(F37="разово",IF(G37&lt;=3,D37*E37,0),IF(F37="мес",D37*E37*MAX(0,4-G37),D37*E37*MAX(0,4-G37)/12))</f>
-        <v>147735</v>
+        <f t="shared" si="0"/>
+        <v>38960</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8304,17 +8365,17 @@
         <v>98</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>411</v>
+        <v>313</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D38" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E38" s="10">
-        <f>ROUND(428736/(1+НДС),0)</f>
-        <v>369600</v>
+        <f>ROUND(89302/(1+НДС),0)</f>
+        <v>76984</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>101</v>
@@ -8323,11 +8384,11 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>412</v>
+        <v>314</v>
       </c>
       <c r="I38" s="5">
-        <f t="shared" si="3"/>
-        <v>369600</v>
+        <f t="shared" ref="I38" si="5">IF(F38="разово",IF(G38&lt;=3,D38*E38,0),IF(F38="мес",D38*E38*MAX(0,4-G38),D38*E38*MAX(0,4-G38)/12))</f>
+        <v>769840</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8335,17 +8396,17 @@
         <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>413</v>
+        <v>316</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
       </c>
       <c r="D39" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E39" s="10">
-        <f>ROUND(30701/(1+НДС),0)</f>
-        <v>26466</v>
+        <f>ROUND(989997/(1+НДС),0)</f>
+        <v>853446</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>101</v>
@@ -8354,11 +8415,11 @@
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="I39" s="5">
-        <f t="shared" si="3"/>
-        <v>79398</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8366,16 +8427,17 @@
         <v>98</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>116</v>
+        <v>318</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D40" s="9">
         <v>1</v>
       </c>
       <c r="E40" s="10">
-        <v>150000</v>
+        <f>ROUND(49990/(1+НДС),0)</f>
+        <v>43095</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>101</v>
@@ -8383,10 +8445,12 @@
       <c r="G40" s="9">
         <v>1</v>
       </c>
-      <c r="H40" s="4"/>
+      <c r="H40" s="4" t="s">
+        <v>319</v>
+      </c>
       <c r="I40" s="5">
         <f t="shared" si="0"/>
-        <v>150000</v>
+        <v>43095</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8394,7 +8458,7 @@
         <v>98</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
@@ -8403,7 +8467,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="10">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>101</v>
@@ -8411,10 +8475,12 @@
       <c r="G41" s="9">
         <v>1</v>
       </c>
-      <c r="H41" s="4"/>
+      <c r="H41" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="I41" s="5">
         <f t="shared" si="0"/>
-        <v>400000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8422,16 +8488,16 @@
         <v>98</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>360</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D42" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="10">
-        <v>10000</v>
+        <v>800000</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>101</v>
@@ -8439,523 +8505,818 @@
       <c r="G42" s="9">
         <v>1</v>
       </c>
-      <c r="H42" s="4"/>
+      <c r="H42" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="I42" s="5">
         <f t="shared" si="0"/>
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D43" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="10">
+        <v>700000</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" s="9">
+        <v>1</v>
+      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C44" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" s="9">
+        <v>1</v>
+      </c>
+      <c r="E44" s="10">
+        <f>'Смета фото-видео'!G24</f>
+        <v>300000</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G44" s="9">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="I44" s="5">
+        <f t="shared" si="0"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C45" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="9">
+        <v>1</v>
+      </c>
+      <c r="E45" s="10">
+        <v>400000</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" s="9">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4"/>
+      <c r="I45" s="5">
+        <f t="shared" si="0"/>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" s="9">
+        <v>1</v>
+      </c>
+      <c r="E46" s="10">
+        <f>ROUND(35990/(1+НДС),0)</f>
+        <v>31026</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" s="9">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="I46" s="5">
+        <f t="shared" ref="I46" si="6">IF(F46="разово",IF(G46&lt;=3,D46*E46,0),IF(F46="мес",D46*E46*MAX(0,4-G46),D46*E46*MAX(0,4-G46)/12))</f>
+        <v>31026</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C47" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="9">
+        <v>20</v>
+      </c>
+      <c r="E47" s="10">
+        <f>ROUND(7400/(1+НДС),0)</f>
+        <v>6379</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" s="9">
+        <v>1</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="I47" s="5">
+        <f t="shared" ref="I47:I49" si="7">IF(F47="разово",IF(G47&lt;=3,D47*E47,0),IF(F47="мес",D47*E47*MAX(0,4-G47),D47*E47*MAX(0,4-G47)/12))</f>
+        <v>127580</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>98</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" s="9">
+        <v>1</v>
+      </c>
+      <c r="E48" s="10">
+        <f>ROUND(428736/(1+НДС),0)</f>
+        <v>369600</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G48" s="9">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="I48" s="5">
+        <f t="shared" si="7"/>
+        <v>369600</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" s="9">
+        <v>3</v>
+      </c>
+      <c r="E49" s="10">
+        <f>ROUND(30701/(1+НДС),0)</f>
+        <v>26466</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G49" s="9">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="I49" s="5">
+        <f t="shared" si="7"/>
+        <v>79398</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="9">
+        <v>1</v>
+      </c>
+      <c r="E50" s="10">
+        <v>150000</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G50" s="9">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="5">
+        <f t="shared" si="0"/>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" s="9">
+        <v>1</v>
+      </c>
+      <c r="E51" s="10">
+        <v>400000</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G51" s="9">
+        <v>1</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="5">
+        <f t="shared" si="0"/>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C52" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" s="9">
+        <v>1</v>
+      </c>
+      <c r="E52" s="10">
+        <v>10000</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G52" s="9">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="5">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D53" s="9">
+        <v>1</v>
+      </c>
+      <c r="E53" s="10">
         <f>Аренда_мес</f>
         <v>4909152.0999999996</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G43" s="9">
-        <v>1</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="I43" s="5">
-        <f>D43*E43*Аренда_мес_2026</f>
+      <c r="F53" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G53" s="9">
+        <v>1</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="I53" s="5">
+        <f>D53*E53*Аренда_мес_2026</f>
         <v>11560261.396774193</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>118</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C44" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" s="9">
-        <v>1</v>
-      </c>
-      <c r="E44" s="10">
+    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C54" t="s">
+        <v>119</v>
+      </c>
+      <c r="D54" s="9">
+        <v>1</v>
+      </c>
+      <c r="E54" s="10">
         <f>Аренда_мес*Депозит_мес</f>
         <v>4909152.0999999996</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F54" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G44" s="9">
-        <v>1</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="I44" s="5">
-        <f t="shared" ref="I44:I60" si="4">IF(F44="разово",IF(G44&lt;=3,D44*E44,0),IF(F44="мес",D44*E44*MAX(0,4-G44),D44*E44*MAX(0,4-G44)/12))</f>
+      <c r="G54" s="9">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I54" s="5">
+        <f t="shared" ref="I54:I70" si="8">IF(F54="разово",IF(G54&lt;=3,D54*E54,0),IF(F54="мес",D54*E54*MAX(0,4-G54),D54*E54*MAX(0,4-G54)/12))</f>
         <v>4909152.0999999996</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>118</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C45" t="s">
-        <v>120</v>
-      </c>
-      <c r="D45" s="9">
-        <v>1</v>
-      </c>
-      <c r="E45" s="10">
-        <v>50000</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G45" s="9">
-        <v>2</v>
-      </c>
-      <c r="H45" s="4"/>
-      <c r="I45" s="5">
-        <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>118</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C46" t="s">
-        <v>120</v>
-      </c>
-      <c r="D46" s="9">
-        <v>1</v>
-      </c>
-      <c r="E46" s="10">
-        <v>60000</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G46" s="9">
-        <v>2</v>
-      </c>
-      <c r="H46" s="4"/>
-      <c r="I46" s="5">
-        <f t="shared" si="4"/>
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>118</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C47" t="s">
-        <v>120</v>
-      </c>
-      <c r="D47" s="9">
-        <v>1</v>
-      </c>
-      <c r="E47" s="10">
-        <v>50000</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G47" s="9">
-        <v>2</v>
-      </c>
-      <c r="H47" s="4"/>
-      <c r="I47" s="5">
-        <f t="shared" si="4"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>118</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C48" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" s="9">
-        <v>1</v>
-      </c>
-      <c r="E48" s="10">
-        <v>30000</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G48" s="9">
-        <v>2</v>
-      </c>
-      <c r="H48" s="4"/>
-      <c r="I48" s="5">
-        <f t="shared" si="4"/>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>118</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="C49" t="s">
-        <v>120</v>
-      </c>
-      <c r="D49" s="9">
-        <v>1</v>
-      </c>
-      <c r="E49" s="10">
-        <f>Канцелярия!F11</f>
-        <v>37375</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G49" s="9">
-        <v>2</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="I49" s="5">
-        <f t="shared" si="4"/>
-        <v>74750</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>118</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="C50" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" s="9">
-        <v>1</v>
-      </c>
-      <c r="E50" s="10">
-        <f>Канцелярия!F20</f>
-        <v>78500</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G50" s="9">
-        <v>1</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="I50" s="5">
-        <f t="shared" ref="I50" si="5">IF(F50="разово",IF(G50&lt;=3,D50*E50,0),IF(F50="мес",D50*E50*MAX(0,4-G50),D50*E50*MAX(0,4-G50)/12))</f>
-        <v>78500</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>118</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C51" t="s">
-        <v>120</v>
-      </c>
-      <c r="D51" s="9">
-        <v>1</v>
-      </c>
-      <c r="E51" s="10">
-        <v>100000</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G51" s="9">
-        <v>2</v>
-      </c>
-      <c r="H51" s="4"/>
-      <c r="I51" s="5">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>128</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C52" t="s">
-        <v>130</v>
-      </c>
-      <c r="D52" s="9">
-        <v>19</v>
-      </c>
-      <c r="E52" s="10">
-        <v>7000</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G52" s="9">
-        <v>2</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="I52" s="5">
-        <f t="shared" si="4"/>
-        <v>266000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>128</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C53" t="s">
-        <v>130</v>
-      </c>
-      <c r="D53" s="9">
-        <v>3</v>
-      </c>
-      <c r="E53" s="10">
-        <v>7500</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G53" s="9">
-        <v>2</v>
-      </c>
-      <c r="H53" s="4"/>
-      <c r="I53" s="5">
-        <f t="shared" si="4"/>
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>128</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C54" t="s">
-        <v>133</v>
-      </c>
-      <c r="D54" s="9">
-        <v>2</v>
-      </c>
-      <c r="E54" s="10">
-        <v>30000</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G54" s="9">
-        <v>2</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I54" s="5">
-        <f t="shared" si="4"/>
-        <v>120000</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D55" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="10">
-        <v>8000</v>
+        <v>50000</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G55" s="9">
         <v>2</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="5">
-        <f t="shared" si="4"/>
-        <v>32000</v>
+        <f t="shared" si="8"/>
+        <v>100000</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>309</v>
+        <v>121</v>
       </c>
       <c r="C56" t="s">
-        <v>244</v>
-      </c>
-      <c r="D56" s="9"/>
-      <c r="E56" s="10"/>
+        <v>117</v>
+      </c>
+      <c r="D56" s="9">
+        <v>1</v>
+      </c>
+      <c r="E56" s="10">
+        <v>30000</v>
+      </c>
       <c r="F56" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="G56" s="9"/>
+        <v>118</v>
+      </c>
+      <c r="G56" s="9">
+        <v>2</v>
+      </c>
       <c r="H56" s="4"/>
       <c r="I56" s="5">
-        <v>2000000</v>
+        <f t="shared" si="8"/>
+        <v>60000</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C57" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D57" s="9">
         <v>1</v>
       </c>
       <c r="E57" s="10">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G57" s="9">
         <v>2</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="5">
-        <f t="shared" si="4"/>
-        <v>300000</v>
+        <f t="shared" si="8"/>
+        <v>100000</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D58" s="9">
         <v>1</v>
       </c>
       <c r="E58" s="10">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G58" s="9">
         <v>2</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="5">
-        <f t="shared" si="4"/>
-        <v>50000</v>
+        <f t="shared" si="8"/>
+        <v>60000</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D59" s="9">
         <v>1</v>
       </c>
       <c r="E59" s="10">
-        <v>50000</v>
+        <f>Канцелярия!F11</f>
+        <v>24125</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="G59" s="9">
-        <v>1</v>
-      </c>
-      <c r="H59" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>363</v>
+      </c>
       <c r="I59" s="5">
-        <f t="shared" si="4"/>
-        <v>50000</v>
+        <f t="shared" si="8"/>
+        <v>48250</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="D60" s="9">
         <v>1</v>
       </c>
       <c r="E60" s="10">
+        <f>Канцелярия!F20</f>
+        <v>15500</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G60" s="9">
+        <v>1</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="I60" s="5">
+        <f t="shared" ref="I60" si="9">IF(F60="разово",IF(G60&lt;=3,D60*E60,0),IF(F60="мес",D60*E60*MAX(0,4-G60),D60*E60*MAX(0,4-G60)/12))</f>
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61" s="9">
+        <v>1</v>
+      </c>
+      <c r="E61" s="10">
         <v>100000</v>
       </c>
-      <c r="F60" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="G60" s="9">
+      <c r="F61" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G61" s="9">
         <v>2</v>
       </c>
-      <c r="H60" s="4"/>
-      <c r="I60" s="5">
-        <f t="shared" si="4"/>
-        <v>16666.666666666668</v>
+      <c r="H61" s="4"/>
+      <c r="I61" s="5">
+        <f t="shared" si="8"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" t="s">
+        <v>127</v>
+      </c>
+      <c r="D62" s="9">
+        <v>19</v>
+      </c>
+      <c r="E62" s="10">
+        <v>7000</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G62" s="9">
+        <v>2</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="I62" s="5">
+        <f t="shared" si="8"/>
+        <v>266000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>125</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C63" t="s">
+        <v>127</v>
+      </c>
+      <c r="D63" s="9">
+        <v>3</v>
+      </c>
+      <c r="E63" s="10">
+        <v>7500</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G63" s="9">
+        <v>2</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="5">
+        <f t="shared" si="8"/>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" s="9">
+        <v>2</v>
+      </c>
+      <c r="E64" s="10">
+        <v>30000</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G64" s="9">
+        <v>2</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I64" s="5">
+        <f t="shared" si="8"/>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>125</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" t="s">
+        <v>130</v>
+      </c>
+      <c r="D65" s="9">
+        <v>2</v>
+      </c>
+      <c r="E65" s="10">
+        <v>8000</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G65" s="9">
+        <v>2</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="5">
+        <f t="shared" si="8"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C66" t="s">
+        <v>239</v>
+      </c>
+      <c r="D66" s="9"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="G66" s="9"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="5">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" t="s">
+        <v>117</v>
+      </c>
+      <c r="D67" s="9">
+        <v>1</v>
+      </c>
+      <c r="E67" s="10">
+        <v>150000</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G67" s="9">
+        <v>2</v>
+      </c>
+      <c r="H67" s="4"/>
+      <c r="I67" s="5">
+        <f t="shared" si="8"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D68" s="9">
+        <v>1</v>
+      </c>
+      <c r="E68" s="10">
+        <v>25000</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G68" s="9">
+        <v>2</v>
+      </c>
+      <c r="H68" s="4"/>
+      <c r="I68" s="5">
+        <f t="shared" si="8"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C69" t="s">
+        <v>104</v>
+      </c>
+      <c r="D69" s="9">
+        <v>1</v>
+      </c>
+      <c r="E69" s="10">
+        <v>50000</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G69" s="9">
+        <v>1</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="5">
+        <f t="shared" si="8"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C70" t="s">
+        <v>135</v>
+      </c>
+      <c r="D70" s="9"/>
+      <c r="E70" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G70" s="9">
+        <v>2</v>
+      </c>
+      <c r="H70" s="4"/>
+      <c r="I70" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8984,7 +9345,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -9015,18 +9376,18 @@
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C5" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
       <c r="F5" s="9" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G5" s="5">
         <f>'Taza talqy'!F12</f>
@@ -9035,18 +9396,18 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
       <c r="F6" s="9" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G6" s="5">
         <f>'Презентация офисе'!F15</f>
@@ -9055,18 +9416,18 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
       <c r="F7" s="9" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G7" s="5">
         <f>'креативные проекты'!F9</f>
@@ -9075,18 +9436,18 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C8" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
       <c r="F8" s="9" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G8" s="5">
         <f>'Информ сопровождение'!F13</f>
@@ -9095,18 +9456,18 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C9" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
       <c r="F9" s="9" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G9" s="5">
         <f>'Соц исследования'!F8</f>
@@ -9115,18 +9476,18 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C10" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
       <c r="F10" s="9" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G10" s="5">
         <f>'Разработка платформы'!F7</f>
@@ -9145,7 +9506,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -9179,45 +9540,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
-        <v>416</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
+      <c r="A1" s="87" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -9229,13 +9590,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="D5" s="55">
         <v>56</v>
@@ -9250,13 +9611,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="D6" s="55">
         <v>56</v>
@@ -9272,13 +9633,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="D7" s="55">
         <v>6</v>
@@ -9293,13 +9654,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="D8" s="55">
         <v>6</v>
@@ -9314,13 +9675,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="D9" s="55">
         <v>6</v>
@@ -9335,13 +9696,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="D10" s="55">
         <v>48</v>
@@ -9357,7 +9718,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="59" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="55"/>
@@ -9370,7 +9731,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="60" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>
@@ -9446,45 +9807,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
-        <v>439</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
+      <c r="A1" s="87" t="s">
+        <v>431</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -9496,13 +9857,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -9517,13 +9878,13 @@
     </row>
     <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -9539,13 +9900,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -9560,13 +9921,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D8" s="55">
         <v>1</v>
@@ -9581,13 +9942,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="D9" s="74">
         <v>100</v>
@@ -9602,13 +9963,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="D10" s="74">
         <v>100</v>
@@ -9624,10 +9985,10 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="57" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="D11" s="74">
         <v>1</v>
@@ -9642,13 +10003,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D12" s="55">
         <v>4</v>
@@ -9663,13 +10024,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B13" s="75" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="D13" s="76">
         <v>1</v>
@@ -9685,7 +10046,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="51"/>
       <c r="B14" s="59" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="55"/>
@@ -9698,7 +10059,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>

--- a/TAZA/_документы/Бюджет ТАЗА.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА.xlsx
@@ -380,7 +380,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="517">
   <si>
     <t>Статья</t>
   </si>
@@ -1195,9 +1195,6 @@
     <t>Главный исполнительный директор (ГИД)</t>
   </si>
   <si>
-    <t>Национальному координатору</t>
-  </si>
-  <si>
     <t>Заместитель директора (МЭПР, ЦГО, регионы)</t>
   </si>
   <si>
@@ -1334,12 +1331,6 @@
   </si>
   <si>
     <t>Вместо ТВ 65". Совещания, презентации, ВКС, работа со схемами. Kaspi.kz (Астана) на 10.10.2026 – 989 997 ₸ с НДС, в бюджете без НДС (÷1,16): https://kaspi.kz/shop/p/iiyama-te7515a-b2ag-75-djuim-177664336/</t>
-  </si>
-  <si>
-    <t>Мобильная стойка на колёсах для панели 32–75″ (AVA-1500)</t>
-  </si>
-  <si>
-    <t>Панель – на передвижной стойке у стола совещаний. Kaspi.kz (Астана) на 10.10.2026 – 49 990 ₸ с НДС, в бюджете без НДС (÷1,16): https://kaspi.kz/shop/p/napol-naja-stoika-dlja-televizora-ava-1500-32-75-na-koljosikah-chjornaja-178402637/</t>
   </si>
   <si>
     <t>Бытовая техника (кулер для воды, холодильник, микроволновка, кофемашина)</t>
@@ -1864,18 +1855,9 @@
     <t>Решение 23.10.2026. Kaspi.kz, продавец ZETA, код товара 105723720 – 17 110 ₸ с НДС, в бюджете без НДС (÷1,16). У «ZETA Астана» со склада в Астане – 17 950 ₸</t>
   </si>
   <si>
-    <t>Стул офисный для посетителей (ZETA СМ-6 серый, каркас металл, обивка гобелен, нагрузка 100 кг)</t>
-  </si>
-  <si>
-    <t>Решение 23.10.2026: серый вместо чёрного. Kaspi.kz, продавец ZETA, код товара 100872340 – 7 400 ₸ с НДС, в бюджете без НДС (÷1,16). У «ZETA Астана» со склада в Астане – 7 455 ₸</t>
-  </si>
-  <si>
     <t>Кресло руководителя (ZETA Гермес, высокая спинка, механизм качания, подлокотники, нагрузка 120 кг)</t>
   </si>
   <si>
-    <t>Решение 23.10.2026: заместителю ГИД, финансовому директору, национальному координатору и советнику. Kaspi.kz, код товара 101065129, продавец RUH MARKET – 70 900 ₸ с НДС (+1 995 ₸ доставка), в бюджете без НДС (÷1,16)</t>
-  </si>
-  <si>
     <t>Кресло Главного исполнительного директора (ZETA мод. 2338, экокожа, высокая спинка, нагрузка 120 кг)</t>
   </si>
   <si>
@@ -1885,9 +1867,6 @@
     <t>Стол руководителя (ZETA Тейлор, 140×70×75 см, светло-серый)</t>
   </si>
   <si>
-    <t>Кабинеты: ГИД, заместитель ГИД, национальный координатор, финансовый директор, советник. Kaspi.kz, код товара 146093286 – 67 576 ₸ с НДС, в бюджете без НДС (÷1,16)</t>
-  </si>
-  <si>
     <t>Шкаф для документов в кабинет руководителя (ZETA СТЖ 11 / Кул-123, 80×38,5×201 см)</t>
   </si>
   <si>
@@ -1928,6 +1907,54 @@
   </si>
   <si>
     <t>ОЦЕНКА: цену запросить вместе с гарнитуром. Сборка самого гарнитура входит в строку «Сборка, доставка и подъём мебели» (10%)</t>
+  </si>
+  <si>
+    <t>Стул офисный для посетителей (ZETA СМ 6 серый, скруглённая спинка, каркас металл, обивка рогожка)</t>
+  </si>
+  <si>
+    <t>Решение 24.10.2026: вариант со скруглённой спинкой и обивкой рогожка. Kaspi.kz, код товара 178424287, продавец ZETA ПОЗИТИВ – 7 595 ₸ с НДС, доставка бесплатно, в бюджете без НДС (÷1,16). Нагрузка в карточке не указана – в ТС требовать не менее 100 кг</t>
+  </si>
+  <si>
+    <t>Мобильная стойка на колёсах под ТВ 40″ (Onkron TS1351, сталь SPCC, нагрузка 45,5 кг, 32–65″)</t>
+  </si>
+  <si>
+    <t>Решение 24.10.2026: интерактивная панель 75″ обнулена, поэтому стойка SK-200 под неё не нужна. Остаётся одна лёгкая стойка под имеющийся ТВ ≈40″. Kaspi.kz – 56 990 ₸ с НДС, в бюджете без НДС (÷1,16). Заменила AVA-1500 (49 990, нагрузка 40 кг)</t>
+  </si>
+  <si>
+    <t>Комплект мебели кабинета ГИД (ZETA Атлант МДФ КУЛ: стол, приставной стол, 2 тумбы, шкаф, стеллаж – 6 предметов)</t>
+  </si>
+  <si>
+    <t>Решение 24.10.2026: кабинет ГИД берём готовым комплектом, остальные четыре кабинета – по предметам. Kaspi.kz, код товара 132145355, продавец ZETA ПОЗИТИВ – 449 690 ₸ с НДС, в бюджете без НДС (÷1,16). Доставка 6 995 ₸ покрывается строкой сборки и доставки мебели</t>
+  </si>
+  <si>
+    <t>Премия по итогам работы в октябре 2026 года (выплата в декабре)</t>
+  </si>
+  <si>
+    <t>Отчисления работодателя на премию (ОПВР 3,5% + ООСМС 3% + СН 6% от дохода за вычетом ОПВ и ВОСМС)</t>
+  </si>
+  <si>
+    <t>ИТОГО премия с отчислениями работодателя</t>
+  </si>
+  <si>
+    <t>Социальные отчисления на премию не добавлены: по большинству окладов предел базы (7 МЗП) выбран самим окладом. По низким окладам бухгалтерия добавит СО – ставка отчислений вырастет с 11,78% до 16%.</t>
+  </si>
+  <si>
+    <t>Руководителю проектного офиса «Таза Қазақстан»</t>
+  </si>
+  <si>
+    <t>Решение 23.10.2026: заместителю ГИД, финансовому директору, руководителю проектного офиса «Таза Қазақстан» и советнику. Kaspi.kz, код товара 101065129, продавец RUH MARKET – 70 900 ₸ с НДС (+1 995 ₸ доставка), в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>Кабинеты: ГИД, заместитель ГИД, руководитель проектного офиса «Таза Қазақстан», финансовый директор, советник. Kaspi.kz, код товара 146093286 – 67 576 ₸ с НДС, в бюджете без НДС (÷1,16)</t>
+  </si>
+  <si>
+    <t>Премия за октябрь (1 – да)</t>
+  </si>
+  <si>
+    <t>База: оклады 8 работников проектного офиса «Таза Қазақстан» (столбец Q) за один месяц, гросс</t>
+  </si>
+  <si>
+    <t>1а. Премия 8 работникам проектного офиса по итогам работы в октябре (1 оклад с отчислениями, выплата в декабре)</t>
   </si>
 </sst>
 </file>
@@ -2038,7 +2065,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2084,6 +2111,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E3EF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2133,7 +2166,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2321,10 +2354,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2592,7 +2632,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.7109375" style="4" customWidth="1"/>
@@ -2603,7 +2643,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2616,7 +2656,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B4" s="37">
         <f>SUMIF(Штат!E5:E36,"штат",Штат!G5:G36)</f>
@@ -2625,7 +2665,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B5" s="37">
         <f>Штат!G38</f>
@@ -2634,7 +2674,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B6" s="38">
         <f>SUMIFS(Штат!M5:M36,Штат!E5:E36,"штат")</f>
@@ -2643,119 +2683,128 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>399</v>
+        <v>516</v>
       </c>
       <c r="B7" s="38">
+        <f>Штат!H44</f>
+        <v>9389520</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>396</v>
+      </c>
+      <c r="B8" s="38">
         <f>Аутсорс!J11</f>
         <v>12098200</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
-        <v>368</v>
-      </c>
-      <c r="B8" s="38">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
+        <v>365</v>
+      </c>
+      <c r="B9" s="38">
         <f>Штат!N37</f>
         <v>611142.85714285716</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
-        <v>342</v>
-      </c>
-      <c r="B9" s="38">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
+        <v>339</v>
+      </c>
+      <c r="B10" s="38">
         <f>Командировки!G12</f>
         <v>3799012.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
-        <v>343</v>
-      </c>
-      <c r="B10" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I70,'Оснащение и офис'!A5:A70,"Оснащение")</f>
-        <v>14358335.6</v>
-      </c>
-    </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="B11" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I70,'Оснащение и офис'!A5:A70,"Офис")</f>
+        <f>SUMIFS('Оснащение и офис'!I5:I71,'Оснащение и офис'!A5:A71,"Оснащение")</f>
+        <v>14600176.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
+        <v>355</v>
+      </c>
+      <c r="B12" s="38">
+        <f>SUMIFS('Оснащение и офис'!I5:I71,'Оснащение и офис'!A5:A71,"Офис")</f>
         <v>17053163.496774193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
-        <v>344</v>
-      </c>
-      <c r="B12" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I70,'Оснащение и офис'!A5:A70,"Цифровые")</f>
-        <v>463000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
+        <v>341</v>
+      </c>
+      <c r="B13" s="38">
+        <f>SUMIFS('Оснащение и офис'!I5:I71,'Оснащение и офис'!A5:A71,"Цифровые")</f>
+        <v>463000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>342</v>
+      </c>
+      <c r="B14" s="38">
+        <f>SUMIFS('Оснащение и офис'!I5:I71,'Оснащение и офис'!A5:A71,"Медиа")</f>
+        <v>2350000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="39" t="s">
+        <v>343</v>
+      </c>
+      <c r="B15" s="40">
+        <f>SUM(B6:B14)</f>
+        <v>119552724.95391704</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
+        <v>366</v>
+      </c>
+      <c r="B16" s="38">
+        <f>B15*Резерв+SUMIFS('Оснащение и офис'!I5:I71,'Оснащение и офис'!A5:A71,"Прочие")</f>
+        <v>12005272.495391704</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="B17" s="38">
+        <f>(B15+B16)*НДС</f>
+        <v>21049279.5918894</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="B18" s="42">
+        <f>B15+B16+B17</f>
+        <v>152607277.04119816</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
         <v>345</v>
       </c>
-      <c r="B13" s="38">
-        <f>SUMIFS('Оснащение и офис'!I5:I70,'Оснащение и офис'!A5:A70,"Медиа")</f>
-        <v>2350000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="39" t="s">
-        <v>346</v>
-      </c>
-      <c r="B14" s="40">
-        <f>B6+B7+B8+B9+B10+B11+B12+B13</f>
-        <v>109921364.45391704</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
-        <v>369</v>
-      </c>
-      <c r="B15" s="38">
-        <f>B14*Резерв+SUMIFS('Оснащение и офис'!I5:I70,'Оснащение и офис'!A5:A70,"Прочие")</f>
-        <v>11042136.445391705</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="B16" s="38">
-        <f>(B14+B15)*НДС</f>
-        <v>19354160.143889397</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="B17" s="42">
-        <f>B14+B15+B16</f>
-        <v>140317661.04319814</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
-        <v>348</v>
-      </c>
-      <c r="B18" s="40">
+      <c r="B19" s="40">
         <f>Проекты!G13</f>
         <v>87234320</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="43" t="s">
-        <v>349</v>
-      </c>
-      <c r="B19" s="44">
-        <f>B17+B18</f>
-        <v>227551981.04319814</v>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="B20" s="44">
+        <f>B18+B19</f>
+        <v>239841597.04119816</v>
       </c>
     </row>
   </sheetData>
@@ -2781,45 +2830,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
-        <v>444</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
+      <c r="A1" s="88" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>407</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>409</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>410</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>411</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>412</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2831,13 +2880,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -2852,13 +2901,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -2874,13 +2923,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -2896,7 +2945,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="59" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="55"/>
@@ -2909,7 +2958,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51"/>
       <c r="B9" s="60" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
@@ -2965,45 +3014,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
-        <v>450</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
+      <c r="A1" s="88" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>407</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>409</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>410</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>411</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>412</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3015,13 +3064,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D5" s="55">
         <v>6</v>
@@ -3036,13 +3085,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3058,13 +3107,13 @@
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3079,13 +3128,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D8" s="55">
         <v>9</v>
@@ -3100,13 +3149,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D9" s="74">
         <v>32</v>
@@ -3121,13 +3170,13 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D10" s="55">
         <v>3</v>
@@ -3142,13 +3191,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D11" s="55">
         <v>3</v>
@@ -3165,7 +3214,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="59" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="55"/>
@@ -3178,7 +3227,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
@@ -3231,45 +3280,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
-        <v>458</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
+      <c r="A1" s="88" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>407</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>409</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>410</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>411</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>412</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3281,13 +3330,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3302,13 +3351,13 @@
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3325,7 +3374,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="59" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="55"/>
@@ -3338,7 +3387,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="60" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -3394,45 +3443,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
-        <v>461</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
+      <c r="A1" s="88" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>407</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>409</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>410</v>
-      </c>
-      <c r="D3" s="49" t="s">
-        <v>411</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>412</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3444,13 +3493,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3466,7 +3515,7 @@
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51"/>
       <c r="B6" s="59" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="55"/>
@@ -3480,7 +3529,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="60" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
@@ -3538,7 +3587,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -3585,7 +3634,7 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3721,7 +3770,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3870,7 +3919,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="32"/>
@@ -4136,7 +4185,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -4427,14 +4476,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$36,Штат!$E$5:$E$36,"штат",Штат!$F$5:$F$36,"новая"),-3)</f>
         <v>713000</v>
       </c>
       <c r="C15" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4625,7 +4674,7 @@
         <v>4909152.0999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4663,17 +4712,17 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -4685,7 +4734,7 @@
         <v>340.67</v>
       </c>
       <c r="C42" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -4696,7 +4745,7 @@
         <v>13500</v>
       </c>
       <c r="C43" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -4708,7 +4757,7 @@
         <v>230107.1</v>
       </c>
       <c r="C44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -4730,7 +4779,7 @@
         <v>40000</v>
       </c>
       <c r="C46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -4793,7 +4842,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -4808,7 +4857,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -4817,11 +4866,12 @@
     <col min="4" max="4" width="22.7109375" customWidth="1"/>
     <col min="5" max="15" width="12.7109375" customWidth="1"/>
     <col min="16" max="16" width="80.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4853,7 +4903,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>74</v>
@@ -4862,21 +4912,23 @@
         <v>75</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>78</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q4" s="4"/>
+        <v>322</v>
+      </c>
+      <c r="Q4" s="90" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
@@ -4931,8 +4983,9 @@
         <v>5454690</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>472</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="Q5" s="91"/>
     </row>
     <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
@@ -4942,7 +4995,7 @@
         <v>269</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>82</v>
@@ -4987,8 +5040,9 @@
         <v>4784010</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>468</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="Q6" s="91"/>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
@@ -5043,8 +5097,9 @@
         <v>4784010</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>372</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="Q7" s="91"/>
     </row>
     <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
@@ -5054,7 +5109,7 @@
         <v>212</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>82</v>
@@ -5099,10 +5154,13 @@
         <v>3223292.3809523811</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+      <c r="Q8" s="91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>6</v>
       </c>
@@ -5113,7 +5171,7 @@
         <v>242</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>271</v>
+        <v>511</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>80</v>
@@ -5155,8 +5213,9 @@
         <v>1516842.3809523811</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>386</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="Q9" s="91"/>
     </row>
     <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
@@ -5166,7 +5225,7 @@
         <v>241</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>244</v>
@@ -5211,7 +5270,10 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>388</v>
+        <v>385</v>
+      </c>
+      <c r="Q10" s="91">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5222,7 +5284,7 @@
         <v>241</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>244</v>
@@ -5267,8 +5329,9 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>390</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="Q11" s="91"/>
     </row>
     <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
@@ -5323,8 +5386,9 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>329</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="Q12" s="91"/>
     </row>
     <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
@@ -5334,7 +5398,7 @@
         <v>245</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>247</v>
@@ -5379,8 +5443,9 @@
         <v>2552612.3809523811</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>273</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="Q13" s="91"/>
     </row>
     <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
@@ -5435,7 +5500,10 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>376</v>
+        <v>373</v>
+      </c>
+      <c r="Q14" s="91">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="75" x14ac:dyDescent="0.25">
@@ -5491,7 +5559,10 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>377</v>
+        <v>374</v>
+      </c>
+      <c r="Q15" s="91">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="60" x14ac:dyDescent="0.25">
@@ -5547,10 +5618,13 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="Q16" s="91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>19</v>
       </c>
@@ -5603,10 +5677,11 @@
         <v>0</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+      <c r="Q17" s="91"/>
+    </row>
+    <row r="18" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>19</v>
       </c>
@@ -5659,10 +5734,11 @@
         <v>0</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+      <c r="Q18" s="91"/>
+    </row>
+    <row r="19" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -5715,10 +5791,11 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+      <c r="Q19" s="91"/>
+    </row>
+    <row r="20" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>23</v>
       </c>
@@ -5729,7 +5806,7 @@
         <v>242</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>271</v>
+        <v>511</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>80</v>
@@ -5771,10 +5848,13 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+      <c r="Q20" s="91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>24</v>
       </c>
@@ -5782,7 +5862,7 @@
         <v>249</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>244</v>
@@ -5827,10 +5907,11 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+      <c r="Q21" s="91"/>
+    </row>
+    <row r="22" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>25</v>
       </c>
@@ -5841,7 +5922,7 @@
         <v>252</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>271</v>
+        <v>511</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>80</v>
@@ -5883,10 +5964,11 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="Q22" s="91"/>
+    </row>
+    <row r="23" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>26</v>
       </c>
@@ -5939,10 +6021,13 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+      <c r="Q23" s="91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="20">
         <v>27</v>
       </c>
@@ -5995,10 +6080,11 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="Q24" s="91"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="20">
         <v>28</v>
       </c>
@@ -6051,10 +6137,11 @@
         <v>0</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+      <c r="Q25" s="91"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>29</v>
       </c>
@@ -6062,7 +6149,7 @@
         <v>251</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>213</v>
@@ -6107,10 +6194,13 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+      <c r="Q26" s="91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>30</v>
       </c>
@@ -6163,10 +6253,11 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+      <c r="Q27" s="91"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>31</v>
       </c>
@@ -6221,8 +6312,9 @@
       <c r="P28" s="17" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q28" s="91"/>
+    </row>
+    <row r="29" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="20">
         <v>32</v>
       </c>
@@ -6275,15 +6367,16 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="Q29" s="91"/>
+    </row>
+    <row r="30" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>33</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>84</v>
@@ -6331,15 +6424,16 @@
         <v>4784010</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+      <c r="Q30" s="91"/>
+    </row>
+    <row r="31" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>34</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>85</v>
@@ -6389,19 +6483,20 @@
       <c r="P31" s="17" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q31" s="91"/>
+    </row>
+    <row r="32" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>80</v>
@@ -6443,21 +6538,22 @@
         <v>0</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+      <c r="Q32" s="91"/>
+    </row>
+    <row r="33" spans="1:17" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>35</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>80</v>
@@ -6499,21 +6595,22 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>470</v>
+      </c>
+      <c r="Q33" s="91"/>
+    </row>
+    <row r="34" spans="1:17" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>35</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>80</v>
@@ -6555,18 +6652,19 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+      <c r="Q34" s="91"/>
+    </row>
+    <row r="35" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="20">
         <v>36</v>
       </c>
       <c r="B35" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>275</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>276</v>
       </c>
       <c r="D35" s="21" t="s">
         <v>211</v>
@@ -6611,18 +6709,19 @@
         <v>0</v>
       </c>
       <c r="P35" s="21" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="Q35" s="91"/>
+    </row>
+    <row r="36" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="20">
         <v>37</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D36" s="21" t="s">
         <v>211</v>
@@ -6667,14 +6766,15 @@
         <v>0</v>
       </c>
       <c r="P36" s="21" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+      <c r="Q36" s="91"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -6708,9 +6808,9 @@
       </c>
       <c r="P37" s="7"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G38">
         <f>SUM(G8:G12)+SUM(G13:G29)</f>
@@ -6721,9 +6821,9 @@
         <v>15500000</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G39">
         <f>G37-G38</f>
@@ -6734,9 +6834,46 @@
         <v>8100000</v>
       </c>
     </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C41" s="7" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>515</v>
+      </c>
+      <c r="H42" s="5">
+        <f>SUMPRODUCT(Q5:Q36,H5:H36)</f>
+        <v>8400000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>508</v>
+      </c>
+      <c r="H43" s="5">
+        <f>H42*(Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС))</f>
+        <v>989520</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C44" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="H44" s="6">
+        <f>H42+H43</f>
+        <v>9389520</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>510</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6760,7 +6897,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -6774,19 +6911,19 @@
         <v>69</v>
       </c>
       <c r="D3" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="F3" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="G3" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="G3" s="25" t="s">
-        <v>284</v>
-      </c>
       <c r="H3" s="25" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>76</v>
@@ -6800,13 +6937,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>211</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E4" s="28">
         <v>867500</v>
@@ -6835,13 +6972,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>211</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E5" s="28">
         <v>425600</v>
@@ -6870,13 +7007,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>287</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="D6" s="27" t="s">
         <v>288</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>289</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -6906,13 +7043,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="D7" s="27" t="s">
         <v>291</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>292</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -6942,13 +7079,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="27" t="s">
         <v>293</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>294</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -6978,13 +7115,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -7014,13 +7151,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>295</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>296</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -7048,7 +7185,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -7092,7 +7229,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7117,7 +7254,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>91</v>
@@ -7197,7 +7334,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")</f>
@@ -7220,7 +7357,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
@@ -7243,7 +7380,7 @@
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G20:G21)</f>
@@ -7266,7 +7403,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -7312,7 +7449,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7326,12 +7463,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7354,7 +7491,7 @@
         <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>97</v>
@@ -7386,10 +7523,10 @@
         <v>1</v>
